--- a/Logs/interaction_log.xlsx
+++ b/Logs/interaction_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="111">
   <si>
     <t>timestamp</t>
   </si>
@@ -139,6 +139,27 @@
     <t>2025-09-18T23:37:03.560534</t>
   </si>
   <si>
+    <t>2025-09-19T14:06:32.197514</t>
+  </si>
+  <si>
+    <t>2025-09-19T14:13:27.317855</t>
+  </si>
+  <si>
+    <t>2025-09-19T14:15:43.922507</t>
+  </si>
+  <si>
+    <t>2025-09-19T14:18:59.115028</t>
+  </si>
+  <si>
+    <t>2025-09-19T14:20:51.420441</t>
+  </si>
+  <si>
+    <t>2025-09-19T14:31:02.453473</t>
+  </si>
+  <si>
+    <t>2025-09-19T14:41:22.557021</t>
+  </si>
+  <si>
     <t>What funding did 2024 Technical Reporting cover?</t>
   </si>
   <si>
@@ -149,6 +170,9 @@
   </si>
   <si>
     <t>Summarize the PRMS enhancement cycle and define the Sounding Board.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> What evidence architecture and rigor standards underpin the report’s claims? </t>
   </si>
   <si>
     <t xml:space="preserve">You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:
@@ -190,6 +214,9 @@
   </si>
   <si>
     <t>docx:Engagement Plan 2025 Technical Reporting.docx:u58-61:0.303, pptx:Engagement Plan 2025 Technical Reporting.pptx:s3pt1:0.202, pptx:Information Session on 2025 Technical Reporting.pptx:s12pt1:0.202, pptx:Information Session on 2025 Technical Reporting.pptx:s7pt1:0.160, pptx:Information Session on 2025 Technical Reporting.pptx:s7pt2:0.160, pptx:Information Session on 2025 Technical Reporting.pptx:s7pt3:0.145, pdf:CGIAR_ImpactReport_2022-24.pdf:p32pt2:0.137, docx:User Roles and Rules for the PRMS Reporting.docx:u1-4:0.134, pdf:CGIAR_ImpactReport_2022-24.pdf:p16pt1:0.116, pdf:CGIAR_ImpactReport_2022-24.pdf:p37pt3:0.109, pdf:Portfolio Narrative_2024.pdf:p5pt2:0.109, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt2:0.104, pdf:Type3_2024Report.pdf:p5pt3:0.101, docx:Engagement Plan 2025 Technical Reporting.docx:u10-13:0.101, docx:Using the PRMS Reporting Tool.docx:u1-4:0.100, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p1pt1:0.100, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.098, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.098, docx:Engagement Plan 2025 Technical Reporting.docx:u7-10:0.097, pdf:Type3_2024Report.pdf:p6pt1:0.095, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt1:0.094, pdf:CGIAR_ImpactReport_2022-24.pdf:p40pt2:0.092, pdf:CGIAR_ImpactReport_2022-24.pdf:p9pt1:0.091, docx:2025 Technical Reporting Information (Session 2).docx:u4-7:0.090, pdf:Type3_2024Report.pdf:p4pt2:0.089, pdf:Portfolio Narrative_2024.pdf:p5pt3:0.088, pdf:CGIAR_ImpactReport_2022-24.pdf:p30pt1:0.088, pdf:CGIAR_ImpactReport_2022-24.pdf:p31pt3:0.087, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3:0.087, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt2:0.083, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt1:0.083, pdf:Type3_2024Report.pdf:p4pt3:0.083, pdf:Type3_2024Report.pdf:p5pt4:0.082, pdf:CGIAR_ImpactReport_2022-24.pdf:p19pt1:0.081, pdf:CGIAR_ImpactReport_2022-24.pdf:p43pt1:0.081, pdf:CGIAR_ImpactReport_2022-24.pdf:p15pt2:0.081, pdf:CGIAR_ImpactReport_2022-24.pdf:p37pt2:0.080, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p4pt4:0.080, pdf:CGIAR_ImpactReport_2022-24.pdf:p27pt4:0.079, pdf:Type3_2024Report.pdf:p6pt2:0.078, pdf:CGIAR_ImpactReport_2022-24.pdf:p44pt2:0.078, docx:Engagement Plan 2025 Technical Reporting.docx:u13-16:0.077, pdf:Type3_2024Report.pdf:p11pt3:0.076, pdf:Type3_2024Report.pdf:p5pt2:0.076, pptx:Engagement Plan 2025 Technical Reporting.pptx:s3pt3:0.076, pptx:Information Session on 2025 Technical Reporting.pptx:s12pt3:0.076, pdf:CGIAR_ImpactReport_2022-24.pdf:p64pt3:0.075, pdf:CGIAR_ImpactReport_2022-24.pdf:p36pt1:0.075, pdf:Portfolio Narrative_2024.pdf:p13pt3:0.074, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt3:0.074, pdf:CGIAR_ImpactReport_2022-24.pdf:p45pt2:0.074, docx:2025 Technical Reporting Information (Session 2).docx:u7-10:0.074, docx:Submitting evidence.docx:u19-23:0.073, pdf:Type3_2024Report.pdf:p11pt4:0.073, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt2:0.073, docx:Using the PRMS Reporting Tool.docx:u7-9:0.073, docx:User Roles and Rules for the PRMS Reporting.docx:u7-10:0.072, pdf:Quick style guide Feb 2024 (1).pdf:p4pt1:0.072, docx:2025 Technical Reporting Information (Session 2).docx:u46-49:0.071, pdf:CGIAR_ImpactReport_2022-24.pdf:p42pt1:0.071, docx:2025 Technical Reporting Information (Session 1).docx:u34-37:0.071, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt3:0.071, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt3:0.070, pdf:Portfolio Narrative_2024.pdf:p22pt1:0.070, pdf:CGIAR_ImpactReport_2022-24.pdf:p25pt3:0.070, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt2:0.070, pdf:CGIAR_ImpactReport_2022-24.pdf:p25pt1:0.069, pdf:CGIAR_ImpactReport_2022-24.pdf:p39pt3:0.069, pdf:CGIAR_ImpactReport_2022-24.pdf:p40pt3:0.069, pdf:CGIAR_ImpactReport_2022-24.pdf:p15pt1:0.068, docx:Engagement Plan 2025 Technical Reporting.docx:u4-7:0.068, pdf:CGIAR_ImpactReport_2022-24.pdf:p37pt4:0.067, docx:Guidance on complementary innnov.docx:u7-10:0.067, docx:2025 Technical Reporting Information (Session 2).docx:u25-28:0.067, pdf:CGIAR_ImpactReport_2022-24.pdf:p19pt2:0.066, pdf:Portfolio Narrative_2024.pdf:p10pt1:0.066, pdf:CGIAR_ImpactReport_2022-24.pdf:p44pt4:0.066, docx:2025 Technical Reporting Information (Session 2).docx:u22-25:0.066, docx:User Roles and Rules for the PRMS Reporting.docx:u19-22:0.065, docx:Using the PRMS Reporting Tool.docx:u4-7:0.065, pdf:Portfolio Narrative_2024.pdf:p2pt4:0.065, pdf:Portfolio Narrative_2024.pdf:p41pt2:0.065, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p6pt4:0.064, pdf:CGIAR_ImpactReport_2022-24.pdf:p45pt1:0.064, pdf:CGIAR_ImpactReport_2022-24.pdf:p22pt2:0.063, pdf:CGIAR_ImpactReport_2022-24.pdf:p10pt3:0.063, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt3:0.062, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt1:0.062, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt3:0.062, docx:CGSpace.docx:u7-12:0.062, docx:Engagement Plan 2025 Technical Reporting.docx:u34-37:0.061, pdf:Portfolio Narrative_2024.pdf:p15pt1:0.061, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p6pt3:0.061, docx:Innovation development.docx:u4-7:0.061, docx:2025 Technical Reporting Information (Session 1).docx:u19-22:0.061, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt3:0.061, pdf:CGIAR_ImpactReport_2022-24.pdf:p41pt1:0.061, pdf:Portfolio Narrative_2024.pdf:p68pt2:0.061, pdf:CGIAR_ImpactReport_2022-24.pdf:p38pt4:0.061, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt4:0.060</t>
+  </si>
+  <si>
+    <t>pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1:0.176, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3:0.132, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2:0.127, pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt1:0.125, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt3:0.119, pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt2:0.119, pdf:Type3_2024Report.pdf:p4pt1:0.119, pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt4:0.117, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4:0.109, pdf:Portfolio Narrative_2024.pdf:p6pt1:0.106, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.106, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt3:0.104, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt1:0.102, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p22pt3:0.102, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p1pt1:0.102, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p24pt3:0.101, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p29pt2:0.099, docx:Submitting evidence.docx:u1-4:0.099, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt4:0.098, pdf:CGIAR_ImpactReport_2022-24.pdf:p66pt2:0.097, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4:0.096, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt2:0.095, pdf:CGIAR_ImpactReport_2022-24.pdf:p66pt4:0.095, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p17pt2:0.095, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p1pt1:0.095, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p28pt3:0.093, pdf:CGI21_508012_PORB_Genebanks.pdf:p44pt1:0.092, pdf:CGI21_508012_PORB_Genebanks.pdf:p29pt1:0.092, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p8pt4:0.092, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt1:0.092, pdf:CGI21_508012_PORB_Genebanks.pdf:p47pt1:0.092, pdf:CGI21_508012_PORB_Genebanks.pdf:p35pt1:0.091, pdf:CGI21_508012_PORB_Genebanks.pdf:p38pt1:0.091, pdf:Climate Action_Inception Report 30-06-2025.pdf:p26pt3:0.091, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p4pt4:0.090, pdf:Type3_2024Report.pdf:p4pt2:0.090, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt2:0.090, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt3:0.090, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p16pt1:0.089, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p1pt2:0.089, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p27pt3:0.089, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p9pt2:0.089, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.088, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p17pt1:0.088, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p6pt3:0.088, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p17pt2:0.088, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.087, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt4:0.087, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p1pt1:0.087, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p19pt3:0.087, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p9pt1:0.087, pptx:Information Session on 2025 Technical Reporting.pptx:s5pt1:0.087, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt4:0.087, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p12pt4:0.086, pdf:CGI21_508012_PORB_Genebanks.pdf:p23pt1:0.085, docx:Guidance on ensuring quality over quantity.docx:u4-7:0.084, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt3:0.084, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p30pt1:0.084, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p6pt4:0.084, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.083, pdf:CGI21_508012_PORB_Genebanks.pdf:p5pt3:0.083, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p19pt2:0.082, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.082, pdf:CGIAR_ImpactReport_2022-24.pdf:p1pt3:0.082, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt3:0.082, pdf:CGIAR_ImpactReport_2022-24.pdf:p8pt3:0.080, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p1pt1:0.080, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p4pt1:0.080, pdf:CGI21_508012_PORB_Genebanks.pdf:p26pt1:0.080, pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3:0.080, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p25pt1:0.079, pdf:CGIAR_ImpactReport_2022-24.pdf:p8pt4:0.078, pdf:Climate Action_Inception Report 30-06-2025.pdf:p12pt1:0.078, pdf:Genebanks_Inception Report 30-06-2025.pdf:p1pt1:0.078, pdf:CGI21_508012_PORB_Genebanks.pdf:p32pt1:0.078, pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt3:0.078, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p4pt4:0.078, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p28pt2:0.077, pdf:Climate Action_Inception Report 30-06-2025.pdf:p7pt3:0.077, pdf:Portfolio Narrative_2024.pdf:p6pt2:0.077, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p29pt1:0.077, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p15pt4:0.077, pdf:Genebanks_Inception Report 30-06-2025.pdf:p21pt2:0.077, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p32pt2:0.076, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p15pt2:0.076, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p30pt2:0.076, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt2:0.076, pdf:Portfolio Narrative_2024.pdf:p6pt4:0.075, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p1pt1:0.075, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p13pt3:0.075, pdf:Type3_2024Report.pdf:p1pt1:0.075, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.075, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p9pt3:0.074, pdf:CGI21_508012_PORB_Genebanks.pdf:p40pt4:0.074, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p1pt2:0.074, pdf:Climate Action_Inception Report 30-06-2025.pdf:p5pt2:0.074, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p15pt3:0.073, pdf:Portfolio Narrative_2024.pdf:p5pt3:0.072, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt3:0.072, pdf:CGI21_508012_PORB_Genebanks.pdf:p49pt4:0.072</t>
   </si>
   <si>
     <t>I cannot find information in the provided chunks to answer this.  
@@ -356,6 +383,54 @@
 docx:Engagement Plan 2025 Technical Reporting.docx — section 'PRMS enhancements and feedback process' paragraph 99 to section 'PRMS enhancements and feedback process' paragraph 104 — u58-61</t>
   </si>
   <si>
+    <t>The report's claims are supported by a rigorous evaluation framework that assesses the quality of impact studies based on established criteria. A composite score, ranging from 0 to 9, reflects the adherence to best practices in impact evaluations, with a focus on statistical methods that quantify causal changes due to interventions. The report emphasizes the importance of various methodological components, such as random sampling and treatment assignment, to ensure the reliability of findings. Additionally, it highlights the need for clarity in study methods to maintain rigor and relevance in the evidence presented. 
+Sources:
+File — CGIAR_ImpactReport_2022-24.pdf — p67pt1
+File — CGIAR_ImpactReport_2022-24.pdf — p12pt1
+File — CGIAR_ImpactReport_2022-24.pdf — p48pt4</t>
+  </si>
+  <si>
+    <t>The report's claims are supported by a rigorous evaluation framework that assesses the quality of impact studies based on established criteria. Each impact evaluation was reviewed for relevance and rigor, with a composite score assigned based on the number of best practices followed, which included aspects like random sampling and treatment assignment. The report highlights that while many studies employed rigorous methods, there were limitations in addressing certain criteria, such as heterogeneous treatment effects. Overall, the evidence presented is derived from a diverse set of studies, ensuring a comprehensive understanding of CGIAR's impact. 
+Sources:
+File — CGIAR_ImpactReport_2022-24.pdf — p67pt1
+File — CGIAR_ImpactReport_2022-24.pdf — p12pt1
+File — CGIAR_ImpactReport_2022-24.pdf — p48pt4
+File — CGIAR_ImpactReport_2022-24.pdf — p46pt3</t>
+  </si>
+  <si>
+    <t>The report's claims are supported by a rigorous evaluation framework that assesses the quality of impact studies based on established criteria. Each impact evaluation was reviewed for relevance and rigor, with a composite score assigned to reflect adherence to best practices in research methodology. The report highlights that while many studies employed rigorous methods to establish causal relationships, there were notable gaps in areas such as heterogeneous treatment effects and power calculations. Overall, the evidence presented is derived from a diverse set of studies, with a focus on those that met a minimum threshold of methodological clarity and rigor. 
+Sources:
+File — CGIAR_ImpactReport_2022-24.pdf — p12pt1
+File — CGIAR_ImpactReport_2022-24.pdf — p12pt2
+File — CGIAR_ImpactReport_2022-24.pdf — p48pt4
+File — CGIAR_ImpactReport_2022-24.pdf — p46pt3</t>
+  </si>
+  <si>
+    <t>The report's claims are supported by a rigorous evaluation framework that assesses the quality of impact studies based on established criteria. Each impact evaluation was reviewed for relevance and rigor, with a composite score assigned to reflect adherence to best practices in research methodology. The report highlights that while many studies employed rigorous methods to establish causality, there were notable gaps in areas such as heterogeneous treatment effects and power calculations. Overall, the evidence presented is derived from a diverse set of studies, with a focus on those that met a minimum threshold of methodological clarity and rigor.
+Sources:
+File — CGIAR_ImpactReport_2022-24.pdf — p12pt1
+File — CGIAR_ImpactReport_2022-24.pdf — p12pt2
+File — CGIAR_ImpactReport_2022-24.pdf — p48pt4
+File — CGIAR_ImpactReport_2022-24.pdf — p46pt3</t>
+  </si>
+  <si>
+    <t>The report's claims are supported by a rigorous evaluation framework that assesses the quality of impact studies based on established criteria. Each impact evaluation was reviewed for relevance and rigor, with a composite score assigned to reflect adherence to best practices in research methodology. The report highlights that while many studies employed rigorous methods to establish causality, there were notable gaps in areas such as heterogeneous treatment effects and power calculations. Overall, the evidence presented is derived from a diverse set of studies, ensuring a comprehensive understanding of CGIAR's impact. 
+Sources:
+File — CGIAR_ImpactReport_2022-24.pdf — p67pt1
+File — CGIAR_ImpactReport_2022-24.pdf — p12pt1
+File — CGIAR_ImpactReport_2022-24.pdf — p48pt4
+File — CGIAR_ImpactReport_2022-24.pdf — p46pt3</t>
+  </si>
+  <si>
+    <t>The report's claims are supported by a structured approach to evidence architecture and rigor standards. It includes a comprehensive review of impact evaluations, assessing their relevance and rigor based on established criteria. A composite score reflecting the adherence to best practices in research methodology was assigned to these evaluations, with a focus on key components such as random sampling and treatment assignment. The report emphasizes the importance of using rigorous methods to infer causality and acknowledges the limitations of certain study designs, while also highlighting the relevance of findings for policymaking. 
+Sources:
+File — Location — Cited IDs
+CGIAR_ImpactReport_2022-24.pdf — page 67 part 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1
+CGIAR_ImpactReport_2022-24.pdf — page 12 part 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt1
+CGIAR_ImpactReport_2022-24.pdf — page 12 part 2 — pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt2
+CGIAR_ImpactReport_2022-24.pdf — page 46 part 3 — pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt3</t>
+  </si>
+  <si>
     <t>Information Session on 2025 Technical Reporting.pptx — slide 9 — pptx:Information Session on 2025 Technical Reporting.pptx:s9, Engagement Plan 2025 Technical Reporting.docx — paragraph 2 — docx:Engagement Plan 2025 Technical Reporting.docx:p2, Information Session on 2025 Technical Reporting.pptx — slide 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s2, Guidance on reporting outputs or outcomes.docx — paragraph 22 — docx:Guidance on reporting outputs or outcomes.docx:p22, Engagement Plan 2025 Technical Reporting.docx — section 'Technical Reporting questions' — docx:Engagement Plan 2025 Technical Reporting.docx:p59, CGIAR_ImpactReport_2022-24.pdf — page 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p1, Engagement Plan 2025 Technical Reporting.docx — section 'A single location for all documents and resources' — docx:Engagement Plan 2025 Technical Reporting.docx:p31, Engagement Plan 2025 Technical Reporting.pptx — slide 1 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s1, CGSpace.docx — section 'CGSpace' — docx:CGSpace.docx:p3, CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 5 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5</t>
   </si>
   <si>
@@ -366,6 +441,15 @@
   </si>
   <si>
     <t>Engagement Plan 2025 Technical Reporting.docx — section 'PRMS enhancements and feedback process' paragraph 99 to section 'PRMS enhancements and feedback process' paragraph 104 — docx:Engagement Plan 2025 Technical Reporting.docx:u58-61, Engagement Plan 2025 Technical Reporting.pptx — slide 3 part 1 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s3pt1, Information Session on 2025 Technical Reporting.pptx — slide 12 part 1 — pptx:Information Session on 2025 Technical Reporting.pptx:s12pt1, Information Session on 2025 Technical Reporting.pptx — slide 7 part 1 — pptx:Information Session on 2025 Technical Reporting.pptx:s7pt1, Information Session on 2025 Technical Reporting.pptx — slide 7 part 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s7pt2, Information Session on 2025 Technical Reporting.pptx — slide 7 part 3 — pptx:Information Session on 2025 Technical Reporting.pptx:s7pt3, CGIAR_ImpactReport_2022-24.pdf — page 32 part 2 — pdf:CGIAR_ImpactReport_2022-24.pdf:p32pt2, User Roles and Rules for the PRMS Reporting.docx — section 'User Roles and Rules for the PRMS Reporting Tool' paragraph 1 to section 'Lead and Co-Lead:' paragraph 4 — docx:User Roles and Rules for the PRMS Reporting.docx:u1-4, CGIAR_ImpactReport_2022-24.pdf — page 16 part 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p16pt1, CGIAR_ImpactReport_2022-24.pdf — page 37 part 3 — pdf:CGIAR_ImpactReport_2022-24.pdf:p37pt3</t>
+  </si>
+  <si>
+    <t>CGIAR_ImpactReport_2022-24.pdf — page 67 part 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1, CGIAR_ImpactReport_2022-24.pdf — page 7 part 3 — pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3, Food Frontiers and Security_Inception Report 30-06-2025.pdf — page 1 part 2 — pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2</t>
+  </si>
+  <si>
+    <t>https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf — page 67 part 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1, https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf — page 7 part 3 — pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1 — page 1 part 2 — pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2</t>
+  </si>
+  <si>
+    <t>https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9 — page 67 part 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1, https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9 — page 7 part 3 — pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1 — page 1 part 2 — pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2</t>
   </si>
   <si>
     <t>[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]
@@ -473,6 +557,115 @@
 Trifa, Nicoleta (CGIAR System Organization) 0:48 Yep. OK, good. So thank you. This session is the first of two session plans for today, planned for today, with the second being scheduled later at 3:00 PM CET to accommodate colleagues in other time zones. Technical reporting. My name is Nicoletta Trifa. By the way, I'm part of the Portfolio Performance Unit, the support unit within the Office of the Chief Scientist. Here is an overview of what we'll cover in the next minutes. I believe my presentation will take 2025 minutes and then we'll leave room for questions at the end, if that's OK. So what we'll cover an update of the technical reporting arrangements 2025 to 2030, priorities and changes for 2025, a brief introduction on the annual technical report and the neighbors. So this mean the performance and results. Management system and the quality assurance, the technical reporting timeline, available resources and support and what's next and how to stay engaged. I want to mention that this session marks the start of the conversation around 2025 technical reporting. We want to give you the early look at the key priorities and plans for the months ahead, and the goal is to make sure that you stay informed, prepared and supported with a clear understanding of upcoming deliverables and timelines. And also clarity on who to reach out to if you have questions or if you need help along the way. Good. Technical reporting arrangements for the new portfolio. The 2025 to 2030 portfolio has been approved by the CGR Global Leadership team on in June 2025 and provides the operational basis to plan, monitor, learn and report. On the new portfolio. It is designed to progressively enable programs, accelerators and centers to report on the pooled and window 3 bilateral projects of the new portfolio in an integrated and aligned way without increasing the burden on centers and the scientists. Main changes compared to the previous technical reporting arrangements, streamline reported reporting. So less products, more integration, lower transaction costs, stronger impact, focus results. To be clearly linked and packaged under impacts, outcomes and associated agreed indicator targets and better linkages between the theory of change or so plan of results and budget and technical reporting. The primary audiences for technical reporting are funders and CGR staff at integrated partnership, portfolio and program and accelerator levels. A secondary audience is the partners. Annual technical reporting covers the individual annual technical reports for program and accelerators, as well as a portfolio view of aggregate contribution to thematic and geographic targets. And relevant content from this technical reports are integrated into the CJR corporate reporting. In terms of the 2025 technical reporting priorities, 2025 is a transition year with technical reporting arrangements, implementation again focusing on streamlined reporting and on strengthening the linkages between theory of change. Porb, media and technical reporting. As many of you know, in the previous portfolio these components were not properly linked, so it was a bit challenging to demonstrate progress against the theory of change or the plans, as you know. In terms of deliverables for 2025. These are the program and accelerator technical reports, which are due in April 2026, the portfolio narrative, which is due in 2026 in June. Integration of top 80% of window tree and bilateral projects by central dollar value into reporting and planning. Application of the minimum data standards for window tree and bilateral reporting. And mapping of refinement during the pause and reflect process which will take place early Q 1/20/26. So as I was mentioning, this year is seen more as a transition year towards KPI based planning and reporting and efforts are underway to enable planning and reporting at the KPI level, which is aligned with the system office objective and key results for 2026 and 20. These are to be confirmed, so they haven't been confirmed yet, but I've pasted them here so that you can see the 2026 objective and key results for the system office. So 100% program and accelerate the work plans and budget. An annual technical report. Which provide for software enabled monitoring of erformance and results against smart Ki by center, ear and ooled funds invested. So next year, 80% of cent</t>
   </si>
   <si>
+    <t>[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1]
+Figure 31: Methods and rigor of the impact evaluations included in this report. Note: Some studies used multiple methods or received multiple rigor scores for different reported impact estimates. Therefore, the sum of the number of studies reflected in the graph is more than the total number of 62. 4 1 6 4 15 125 4 5 13 62 43210 98765 Rigor score 0 5 10 15 20 4 3 1 43 32 2 3 5 2 2 13 1 2 1 1 1 1 2 1 1 4 6 2 4 4 1 Other ﬁxed eﬀects models Diﬀerence in diﬀerence Propensity score matching and other matching approaches Instrumental variables Endogenous switching regression Randomized control trial Number of publications by rigor score Rigor of the evidence by study design Figure 32: Proportion of impact evaluation analyses which met each of the best-practice rigor score criteria. Included are 125 studies, which contained 488 indicator analyses. 0 100 200 300 400 Spillovers Sensitivity analysis Representativeness Random treatment assignment Random sampling Power Heterogeneous treatment eﬀects Baseline balance Attrition UncertainDid not meet criteriaMet criteria 1%58% 41% 60%40% 56%15% 29% 81%19% 81% 19% 18% 82% 14% 86% 50% 50% 21% 79% B. Impact indicators CGIAR’s Results Framework contains 19 Impact Area indicators it committed to tracking in the 2022 to 2024 period. These indicators are well aligned with the SDG targets and supporting indicators. CGIAR poverty-related indicators are closely linked with SDG targets 1.1 and 1.2 (on reducing poverty) and target 2.3 (on increasing agricultural productivity on small farms). CGIAR nutrition-related indicators are well aligned with SDG targets 2.1 and 2.2 (on reducing hunger and
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3]
+fully contextualize the results. Are you an implementer? Consider jumping directly to your Impact Area or Continent of interest. But be sure to return and read about the Scope of the Report so that you know what is, and is not, included in this report. Tips on interpretation When interpreting the outcomes reported, be cautious about aggregating across data sources (e.g., as Performance and Results Management System [PRMS] and SPIA country studies), Impact Areas, and continents. Some outcomes are included in more than one of these categories. Pay attention to the specified time period. The report focuses on evidence reported during the 2022 to 2024 period, but outcomes and impacts often developed over much longer periods. Consider the overall weight of the evidence, not individual pieces of evidence. This report presents a body of evidence, drawing on a variety of different epistemological approaches: outcome evidence, impact evaluations, and other types of information, which collectively provide different insights into CGIARs impact. However , only impact evaluations were assessed for the number of best research practices they used, with a composite score of 0 to 9 assigned based on the number of key components of rigor addressed by the study. While weighted equally in this work, these components do not all have equal implications for overall study
+---
+[ID: pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2]
+Report Food Frontiers and Security Science Program Inception Report
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt1]
+All impact study submissions were reviewed for potential inclusion into the evidence base of the report. The two primary inclusion considerations were relevance and rigor (see Annex A. Selection of evidence). Studies were determined to be relevant if they considered the outcomes and impacts of CGIAR-supported interventions, regardless of the authorship of the study. Outcomes reported into the CGIAR PRMS are quality assessed for relevance (that is, CGIAR’s role in the outcome is validated); therefore, none of these reported outcomes were excluded on the basis of relevance. Studies with unclear or misleading methods were excluded on the basis of rigor. Studies meeting this threshold of clarity were then classed as “impact assessments” or “impact evaluations.” Impact evaluations were the primary study designs of interest. Impact evaluations are studies that use statistical methods (experimental or quasi-experimental) to quantify the causal change in a condition that was achieved by an intervention. Studies using other study designs were included under the umbrella term of impact assessments (including impact evaluations), if they provided information relevant to understanding impacts, such as cost- benefit analyses, reviews of CGIAR work, and measures of the adoption of CGIAR technology. These included the country studies supported by CGIAR’s SPIA. While impact evaluations are necessary to establish causal change linking intervention and impact, they can be limited in scope due to practical constraints, such as resources and measurement challenges. Other types of impact assessments can provide valuable insights into CGIAR’s contributions to real-world change in a wider spatial or temporal context; however , they do c This can be common for power calculations. Authors may have conducted power calculations but not r eported that they did so in-text. Assessment is based on what is reported in-text, not what may have been done but not reported. d See Annex A. Included studies and rigor of
+---
+[ID: pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt3]
+underpin the work being done and provide the solid positioning for holding the CA. This collaboration means the work being done relies on the most capable parts of both the CGIAR and the relevant partner and that this collaboration changes over time. A part of the Program’s objectives
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt2]
+challenges. Other types of impact assessments can provide valuable insights into CGIAR’s contributions to real-world change in a wider spatial or temporal context; however , they do c This can be common for power calculations. Authors may have conducted power calculations but not r eported that they did so in-text. Assessment is based on what is reported in-text, not what may have been done but not reported. d See Annex A. Included studies and rigor of evidence for details. Criteria related to random sampling and treatment assignment; reporting of power calculation and sensitivity analysis; consideration of attrition, spillovers, and heterogenous treatment effects; and sample representativeness and baseline balance. not establish causality. Impact evaluations were further appraised to determine the number of best practices followed per study. A composite score45 was calculated to reflect the level of confidence in the findings of a study and to help understand the application of best practices in CGIAR impact evaluation. Nine best practices were identified (see Annex A. Included studies and rigor of evidence), resulting in the composite best- practice score ranging from 0 to 9. Not all the criteria were relevant to all studies, and some studies may have met criteria but did not clearly describe them in the publication.c Studies following three or more best practices were featured preferentially in this report (assuming equality in relevance). Details of the method and analysis of the scores are in Annex A. Included studies and rigor of evidence. Included impact studies Approximately 500 studies were reviewed for eligibility and 125 studies were included in the primary dataset. Of these, 62 were impact evaluations and 63 were impact assessments which did not attempt to establish the causal effect of an intervention on an impact. Randomized controlled trials (RCT) were the most common impact evaluation design (n = 21), followed by
+---
+[ID: pdf:Type3_2024Report.pdf:p4pt1]
+Integration with other outputs The Portfolio Narrative informs the 2024 CGIAR Annual Report – a comprehensive summary of the organization’s collective achievements, impacts, and strategic outlook. Elements of the Type 2 report were integrated into the CGIAR Flagship Report released in April 2025 during the CGIAR Science Week. The Flagship Report synthesizes CGIAR research in an accessible format designed specifically to provide policy- and decisionmakers at national, regional, and global levels with the evidence they require to formulate, develop, and negotiate evidence-based policies and investments. The diagram below illustrates these relationships, emphasizing the interconnectedness of the Type 3 Report with other reporting products. CGIAR Results Dashboard Portfolio Narrative report CGIAR Annual report Type 1 Initiative, Impact Platform, and Science Group Project reports Type 2 CGIAR Contributions to Impact in Agrifood Systems: evidence and learnings from 2022 to 2024 Flagship report Type 3 Portfolio Practice Change report 2024 Technical Reporting Figure 1. CGIAR’s 2024 Technical Reporting components and their integration with other CGIAR reporting products. Section 1: Introduction 1 Under the CGIAR Technical Reporting Arrangement for the next Portfolio (2025-30), relevant aspects of the Type 3 Report will be included in the annual Portfolio Narrative, and a separate Type 3 Report will no longer be produced. The 2024 CGIAR Portfolio Practice Change
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt4]
+against CGIAR’s Results Framework is that, apart from the SPIA country studies, other internal and external studies are designed in an uncoordinated bottom-up way. Because such studies are undertaken to meet specific information needs, opportunities to learn through synthesis or aggregation are missed due to the differences in indicators used and measurement approaches employed. For example, impact assessments are rarely connected with data on innovation use, preventing case study results from being used to extrapolate possible large-scale effects. Thus, moving forward, two areas for improvement are: (1) to collectively undertake strategic impact assessments that will answer high-priority impact assessment questions and (2) to develop and enforce the use of a core set of common indicators and measurement methodsq that should be used in impact assessment studies regardless of who initiates them. In addition, during the 2022 to 2024 period, Initiatives defined targets for outcomes and made commitments to measuring and reporting on those outcomes. They did not have a similar plan or commitment to measuring impacts. As CGIAR evolves to longer-term programs covering the whole of CGIAR, there should be commitments to the consistent measurement of impacts. However , this has been an ongoing challenge within the organization, with similar recommendations from a review of the 2017 to 2021 portfolio.176 Rigor of the evidence All impact evaluations identified were assessed for their rigor based on criteria established by Rao 2025.45 The most common score was a 4 of 9 key elements being present, suggesting moderate overall quality and room for improvement. A high number of impact evaluations used rigorous methods to infer causality between a CGIAR innovation and impacts (see Annex A. Included studies and rigor of evidence). However , many failed to consider heterogeneous treatment effects or report power calculations. Most of the impact evaluations used experimental or quasi-experimental designs with two or more measurement periods. However , a sizeable group of the studies were based on cross-sectional (single measurement) studies. While they are peer-reviewed and employ recommended methods of controlling for unobservable variables to enhance the likelihood of a causal inference, there remain limitations to such designs. In addition to rigor , this study paid attention to the relevance of the studies. Often, studies employing less rigorous, cross-sectional methodologies were able to provide evidence more relevant to policymaking and decision-making Tradititional rice variety in Ilagan, Isabela, the Philippines. Photo credit: Miguel Mamon/CIAT CGIAR Impacts in Agrifood Systems: | Learnings | Page 90 of 130 CGIAR CGIAR CGIAR Impacts in Agrifood Systems: | Learnings| Page 91 of 130
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]
+four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the "challenges and megatrends" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.
+---
+[ID: pdf:Portfolio Narrative_2024.pdf:p6pt1]
+Integration with other outputs The Portfolio Narrative informs the 2024 CGIAR Annual Report – a comprehensive summary of the organization’s collective achievements, impacts, and strategic outlook. Elements of the Type 2 report fed into the CGIAR Flagship Report, released in April 2025 at CGIAR Science Week. The Flagship Report
+---
+[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]
+activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt3]
+to ensure common terminology across the reporting units. At the impact level, there were 19 indicators across the five Impact Areas. The frequency of reporting against exact indicators is very low (18 percent of indicators assessed match those in the Results Framework; Annex B. Impact indicators). In addition, there is an imbalance across Impact Areas and indicators in the frequency with which 2022 to 2024 studies attempt to measure those indicators. There were many impact assessments that measured yields or income related to the poverty indicators, and relatively few that looked at environmental, climate, or gender indicators. This is consistent with what Templeton (2023)176 found in her review of evidence used to support the impact claims made by the CGIAR Research Programs between 2017 and 2021. Thus, there remains a huge challenge to define feasible indicators for
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt1]
+Gender Equality and Inclusion Accelerator Inception Report 32 GEYSI's role vis-a-vis the CGIAR's mandate for climate adaptive agriculture. Emerging Areas of Work. This section is disappointing. It is generic to good gender research rather than specific to gender research in agrifood systems. Most importantly it does not include any reflection of what was learned from the earlier work of the GENDER Platform and HER+ these past few years to help guide what has emerged as priorities for the future, nor does it build out from the lessons and recommendations from the 2023 Independent Evaluation of the GENDER Platform. This is now addressed in detail in Section 1 of this report. Use-Case-based prioritization. What are the top questions
+---
+[ID: pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p22pt3]
+Total Cross-cutting and Management budget 32,118 Area of Work 1: Research and innovation 2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) I-OC 1.1: Key CapSha stakeholders adopt and mainstream CapSha standards and good practices in their Programs and Centers X X X - I-OC 1.2: CapSha standards and good practices inform CGIAR system-level policies X X X High-Level Outputs HLO 1.1.1: Innovative
+---
+[ID: pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p1pt1]
+Scaling For Impact Program Inception Report
+---
+[ID: pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p24pt3]
+68,052 Area of Work 1: Research and innovation 2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) I-OC 1.1: Key CapSha stakeholders adopt and mainstream CapSha standards and good practices in their Programs and Centers X X X - I-OC 1.2: CapSha standards and good practices inform CGIAR system-level policies X X X High-Level Outputs HLO 1.1.1: Innovative research on novel
+---
+[ID: pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p29pt2]
+Data OP 6.1 FAIR Data and Inclusive and Ethical Digital Innovation Standards, Practices, and Policies Digital Green AOW 6 Digital &amp; Data OP 6.1 FAIR Data and Inclusive and Ethical Digital Innovation Standards, Practices, and Policies The Food Systems Implementation Network (IN) within the GO FAIR (Findable, Accessible, Interoperable, and Reusable) AOW 6 Digital &amp; Data OP 6.1 FAIR Data and Inclusive and Ethical Digital Innovation Standards, Practices, and Policies Global Open Data
+---
+[ID: docx:Submitting evidence.docx:u1-4]
+Submitting evidence What is the minimum number of pieces of evidence I can report? Between 1 and 6 pieces are accepted by the system. Submit evidence in order of relevance, starting with the one most directly supportive of the result, and use the text box to indicate where the relevant information can be found within each source (e.g., page number, slide number, or table number). How and where do I submit evidence for results?
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt4]
+only impact evaluations were assessed for the number of best research practices they used, with a composite score of 0 to 9 assigned based on the number of key components of rigor addressed by the study. While weighted equally in this work, these components do not all have equal implications for overall study quality and are not universally important to all impact evaluations. We present information from studies with lower composite scores when they provide meaningful information that informs the overall body of evidence—but we rely more heavily upon the more rigorous studies. Readers should avoid overinterpreting evidence that is indicative, supportive, or suggestive but not conclusive. Be precise in the interpretation of the use of causal and non-causal language. Although this report includes multiple types of information, causal language is only used for impact evaluations addressing three or more key components of rigor . Reported numbers of people reached do not necessarily reflect numbers of people adopting an agricultural technique and reported numbers of adopters do not necessarily translate into impact. However , these values provide evidence along the causal chain between innovation and impact. CGIAR Impacts in Agrifood Systems: | Executive summary | Page 8 of 130 CGIAR CGIAR CGIAR Impacts in Agrifood Systems: | Executive summary | Page 9 of 130
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p66pt2]
+included studies. Synthesis and narrative development Members of CGIAR’s PPU were assigned to review impact assessments related to specific Impact Areas and geographies. They then grouped these into themes (which became subsections in this report) based on their knowledge of CGIAR’s workstreams. They reviewed submissions from CGIAR Center staff as well as PRMS to add nuance to the identified themes and supplemented this information with their own professional knowledge to develop narratives about CGIAR’s real-world impacts. These narratives tried to feature the most compelling, holistic set of evidence on real-world change, not necessarily the largest real-world changes achieved (that is, preference was given to compelling examples of incremental change over suspect examples of large-scale change). This approach to the development of themes to feature is, therefore, rooted in the studies identified through the Selection of Evidence (see Selection of evidence) process, but not strictly limited to those studies. Furthermore, data extraction (see Data extraction) on the rigor of evidence informed decisions on which studies to feature in the narrative, but no hard cut-offs were applied. Women collecting wheat samples, Ciudad Obregon, Mexico. Photo credit: Peter Lowe/CIMMYT Validation of findings An extensive engagement process was leveraged to ensure that the findings presented here accurately reflect the full breadth of CGIAR work. This process included soliciting evidence from CGIAR’s Impact Areas and regions, circulating early drafts of this report to the individuals contacted for contributions, and engaging with CGIAR’s Standing Impact, Monitoring, and Evaluation Committee (SIMEC). However , the overriding consideration was strength of evidence and only secondarily an interest in balance across CGIAR’s breadth of work. Included studies and rigor of evidence Using this approach, 125 unique studies were identified: 62 impact evaluations and 63 supplemental studies.u While the most common impact evaluation design was RCTs, a significant portion used endogenous switching regression and instrumental variable approaches to determine the effects of interventions in contexts where observational data were used (Figure 31). RCTs were used to understand the effects of specific CGIAR interventions. Endogenous switching regression and instrumental variables were often used to understand the effects of adopting
+---
+[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4]
+exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved. Impact assessments are conducted after an intervention has been completed and are used to substantiate claims of sustained results. They seek to measure impact at scale, i.e., benefits to a large number of people/large areas of land. It employs both quantitative and qualitative methods, often combined for deeper insights. IA goes beyond monitoring indicators to evidenced attribution of observed changes to CGIAR interventions. IA will help to ensure that Programs/Accelerators contribute meaningfully to CGIAR’s Results Framework and the 2025–30 Portfolio objectives.
+---
+[ID: pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt2]
+on Codesign)). In other cases, Enable’s CA positioning emerges because of its extensive and specific knowledge of regional breeding networks’ needs and maturity levels, across geographies. Across all of Breeding for Tomorrow’s workstreams, co-implementation and partnerships underpin the work being done and provide the solid positioning for holding
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p66pt4]
+defining component of an impact evaluation, the use of these methods does not guarantee that an impact evaluation is rigorous in all respects. We therefore conducted a rigor assessment, which considered the following criteria:45 1. Did the study employ (partial) random sampling? 2. Was statistical power considered? 3. Was attrition considered? 4. Is the sample representative of the target population? 5. Were spillover effects considered? 6. Were heterogenous treatment effects estimated? 7. Was there (partial) random assignment to treatment? 8. Was baseline balance between treatment and control groups reported and addressed statistically if needed? 9. Were sensitivity checks conducted? Composite scores were then developed reflecting the number of these criteria (0–9) that were fulfilled. These criteria combine established scoring methods with a modified approach that is appropriate for a wide variety of evidence types. They are grounded in widely recognized best practices for transparency, causality, and methodological rigor and build on validated frameworks successfully applied in prior high- quality meta-analyses of international agricultural research. All criteria were given equal weight, although, future studies may wish to consider whether some of these criteria should be considered necessary or less influential in an aggregate measure of overall rigor . Because these criteria are somewhat high- level and not universally applicable to all impact evaluations, we did not use these to exclude studies, only to inform decisions about which to highlight in this report. In cases where study designs did not rigorously establish causation, we reverted to associational language or simply included the studies in Impact assessments references and not in the main text. The 62 impact evaluations serving as the basis of this report were generally rated as being moderately rigorous, with a rating of 4 being the most common score but many studies scored 2 and 3 as well (Figure 31). The most common methodological issues raised related to consideration of heterogeneity in treatment effects and the presentation of power calculations (Figure 32). CGIAR Impacts in Agrifood Systems: | Annexes | Page 126 of 130 CGIAR CGIAR CGIAR Impacts in Agrifood Systems: | Annexes| Page 127 of 130
+---
+[ID: pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p17pt2]
+Program | Inception Report 17
+---
+[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p1pt1]
+Policy Innovations Science Program Inception Report
+---
+[ID: pdf:CGI21-508004-PORB-Digital Transformation.pdf:p28pt3]
+HLO 1.1.1 Common metadata and science data standards X X 98,000 AOW01 HLO 1.1.2 Standards-compliant FAIR science data collection tools X X AOW01 HLO 1.1.6 &amp; 1.2.6 Training on inclusive and ethical FAIR data, AI, and digital solution practices X X X AOW01 HLO 1.2.3 Standards-compliant FAIR data corpus X AOW01 HLO 1.2.4 Scalable, searchable Data ecosystem with analytics pipelines X X AOW01 HLO 1.2.5 Flexible, scalable computing &amp;
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p44pt1]
+Plan of results and budget 2025 | System Organization and center allocations | Page 44 of 52 August 2025 | CGIAR Area of Work 1: Biodiversity Conservation 2025 High-Level Outputs 1.1. All collections conserved according to international standards and best practices X X X X 1,843,000 1.2. Innovations to enhance the efficiency of conserving collections X X X X 1.3. Optimized collection composition and structure to represent crop gene pools X X X X 1.4. Effective and AI-ready data management systems using harmonized data standards across Centers X X X X Total
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p29pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 29 of 52 Area of Work 1: Biodiversity Conservation 2025 High-Level Outputs 1.1. All collections conserved according to international standards and best practices X X X X 3,157,508 1.2. Innovations to enhance the efficiency of conserving collections X X X X 1.3. Optimized collection composition and structure to represent crop gene pools X X X X 1.4. Effective and AI-ready data management systems using harmonized data standards across Centers
+---
+[ID: pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p8pt4]
+to improved agricultural outcomes. Capacity development initiatives and innovation challenges serve as additional acceleration mechanisms. Domain expertise required includes digital platform architecture and innovation network management. This also requires organizational change facilitation, policy development and governance design, and partnership development across research-for-development contexts. This creates an enabling environment that accelerates digital transformation across CGIAR and partners.
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt1]
+24 The key impact evaluation questions addressed in this component are: • To what extent do multistakeholder engagement processes and co-design of science-based processes and tools lead to ownership of results by landscape stakeholders and to the sustainable uptake of solutions? • Through which mechanisms does the multidisciplinary and transdisciplinary science promoted by the Multifunctional Landscapes program generate adoption of bundles of solutions and innovations at the landscape level? • Under what conditions and through which mechanisms agroecological and nature positive approaches, within a multifunctional landscape lens, optimize landscape multifunctionality? • What are the behavioral outcomes of such
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p47pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 47 of 52 Area of Work 1: Biodiversity Conservation 2025 High-Level Outputs 1.1. All collections conserved according to international standards and best practices X X X X 1,533,177 1.2. Innovations to enhance the efficiency of conserving collections X X X X 1.3. Optimized collection composition and structure to represent crop gene pools X X X X 1.4. Effective and AI-ready data management systems using harmonized data standards across Centers
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p35pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 35 of 52 Area of Work 1: Biodiversity Conservation 2025 High-Level Outputs 1.1. All collections conserved according to international standards and best practices X X X X 4,474,278 1.2. Innovations to enhance the efficiency of conserving collections X X X X 1.3. Optimized collection composition and structure to represent crop gene pools X X X X 1.4. Effective and AI-ready data management systems using harmonized data standards across Centers X
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p38pt1]
+Plan of results and budget 2025 | System Organization and center allocations | Page 38 of 52 August 2025 | CGIAR Area of Work 1: Biodiversity Conservation 2025 High-Level Outputs 1.1. All collections conserved according to international standards and best practices X X X X 2,473,014 1.2. Innovations to enhance the efficiency of conserving collections X X X X 1.3. Optimized collection composition and structure to represent crop gene pools X X X X 1.4. Effective and AI-ready data management systems using harmonized data standards across Centers X X X X Total
+---
+[ID: pdf:Climate Action_Inception Report 30-06-2025.pdf:p26pt3]
+socioeconomic contexts through collaborations, for example with Multifunctional Landscapes on Living Labs for locally-led adaptation and all other Programs. FAIR data generation and access is supported through the Digital Accelerator, such as digital twin approaches. This two-way collaboration ensures that climate science is both upstream and downstream, shaping priorities and designs across the Portfolio while drawing on implementation insights to refine tools and frameworks for broader system use. Joint products, such as harmonized, FAIR datasets, decision- support tools, and validation studies, become the core of CGIAR’s consolidated climate offer, and the Hub helps make it accessible to partners (See #3). 3. Harmonized Climate Data and Amplification. The Climate Hub curates and delivers shared datasets, standards, and methods for climate risk, socio-economic vulnerability, GHG emissions, and other core metrics that underpin climate-related work across CGIAR. The gender accelerator is engaged to support following FAIR and GESYI aware data principles. By providing a common evidence base, the Hub reduces duplication, ensures methodological consistency, and enhances the credibility and comparability of results across Programs. In addition to improving internal
+---
+[ID: pdf:CGI21-508004-PORB-Digital Transformation.pdf:p4pt4]
+partners capacitated on responsible use of FAIR, AI-ready data X X High-Level Outputs AOW01 HLO 1.1.1 Common metadata and science data standards X X X X 534,917 AOW01 HLO 1.1.2 Standards-compliant FAIR science data collection tools X X X AOW01 HLO 1.1.6 &amp; 1.2.6 Training on inclusive and ethical FAIR data, AI, and digital solution practices X X X X AOW01 HLO 1.2.3 Standards-compliant FAIR data corpus X X X X CGI21-508004-PORB-Digital Transformation.indd 4CGI21-508004-PORB-Digital Transformation.indd 4 06/08/2025 10:4606/08/2025
+---
+[ID: pdf:Type3_2024Report.pdf:p4pt2]
+with other CGIAR reporting products. Section 1: Introduction 1 Un</t>
+  </si>
+  <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: According to the Annex pie chart, what was total 2024 revenue and the split by funding source?\n\nContext:\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 6\nContent: Research results can be defined according to the nature of the change and the control over it.\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p14]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 14\nContent: Figure 1: Research results according to the kind of change and the control over it.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 23 Annex 2: ISDC feedback relating to pooled &amp; non-pooled alignment5 This section provides a direct extract from the ISDC Feedback on CGIAR Portfolio Narrative 2025- 2030. Comments relating to the alignment of pooled and non -pooled have been extracted from the broader set of comments. They have not been edited to e.g. update Program and Accelerator nomenclature. • Articulation of how the Portfolio, including bilateral and W1 funding, will be bundled into Megaprograms is still lacking. Bilateral funding is restricted and is provided for a specific purpose and with specific intended impacts. This needs to be honored a nd the lack of flexibility in shifting those funds into other areas should be clearly acknowledged. • Alignment of the entire Portfolio with the CGIAR 2030 Research and Innovation Strategy needs to be strong and explicit. How will management ensure that bilateral funding delivers against this Strategy? In addition: o What happens if a bilateral project is not strongly aligned with the Strategy and how will CGIAR ensure that opportunity costs are covered? o Will all bilateral projects across all Centers be mapped to support the Portfolio? • A challenge that should be acknowledged is incorporating bilateral funding into Megaprograms. Each Megaprogram and Accelerator will be large scale and staff will be consumed by the implementation of contracted work. Trying to build Megaprogram linkages in parallel with bilateral funding should be additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative 2025-2030\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p5]\nFile: Type3_2024Report.pdf\nLocation: page 5\nContent: Section 2: Portfolio Performance and Project Coordination Progress 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022-2024. 3. Science Group Projects (SGPs) are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance and fiduciary oversight. 4. EiB II will report through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they will provide a concise, high-level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the technical reports. 2.1. Technical Reporting Arrangement 2022-24 CGIAR Technical Reporting fulfils the System-level programmatic reporting requirements set out in the Standard Provisions annexed to the Funding Agreement or Arrangement signed between each Funder and the System Organization.2 The 2024 Technical Report includes the following Initiatives, Impact Platforms and SGPs3: • All 32 Initiatives • Five Impact Platforms – Gender Equality, Youth and Social Inclusion – Environmental Health and Biodiversity – Nutrition, Health and Food Security – Climate Adaptation and Mitigation – Poverty Reduction, Livelihoods and Jobs • Six SGPs – Accelerated Varietal Improvement and Seed Delivery of Legumes and dryland Cereals in Africa (AVISA) – Roots Tubers and Banana (RTB) Breeding – Accelerating Genetic Gain and Varietal Replacement in Rice - Phase 2 (AGGRi 2) – Excellence in Breeding (EiB) II: Cross-Crop Support Services for Breeding Acceleration4 – Accelerating Crop Improvement Through Genome Editing 2023-2025 – Climate Adaptation Insight For 2024, CGIAR will produce and deliver a total of 46 Technical Reporting outputs: • March 2025: Results from 2024 published on the online CGIAR Results Dashboard (1). • May 2025: Publication of 42 Type 1 (32 x Initiative reports; 5 x Impact Platform reports; 5 x SGP reports) Reports and a Type 3 Report (1). • End of June 2025: Publication of the Portfolio Narrative (1). • End of June 2025: Publication of the Type 2 Report: CGIAR Contributions to Impact in Agrifood Systems (2022-24) (1). Each of these reports is released separately and will be available in PDF format. 2024 Technical Reporting covers USD 370 million (USD 322 million for Initiatives and Impact Platforms, and USD 49 million for W3 SGPs), representing nearly 40 percent of CGIAR’s total pooled and non-pooled funding for 2024. 2.1.1. Streamlining the process and adding value to stakeholders In 2022 CGIAR launched a new 2022-24 Technical Reporting Arrangement, co-developed with the System Council’s Strategic Impact Monitoring and Evaluation Committee (SIMEC). The 2022 rollout was regarded as a “first pancake” or trial phase, establishing minimum viable functionality and setting the foundation for annual improvements. Key achievements of 2022 Technical Reporting included the adoption of a common report template aligned with the Technical Reporting Arrangement for Initiatives and Impact Platforms; integration with CGIAR’s Results Framework; digital linking of results to theories of change (TOCs); and the introduction of quality assurance processes mediated by third parties. Additionally, a new interactive CGIAR Results Dashboard was launched, and the Performance and Results Management System (PRMS) – an online reporting system – was developed, alongside adaptive management processes and the rollout of Innovation Packages and Scaling Readiness plans. Building on this, 2023 Technical Reporting incorporated lessons from a 2022 Learning and Optimization process, documented in a 2022 Learning and Optimization report. Key advancements included transitioning to “Always on” reporting by opening the PRMS from September 2023, more than doubling the reporting window compared to 2022 and allowing greater flexibility for Initiatives, Impact Platforms, and SGPs. Quality assurance was optimized through four staggered batches across 2023 and 2024. Further enhancements included expanding per-result tagging to all five Impact Areas. A Risk Management Module was launched to support risk identification and reporting at the Initiative level. A large number of participants joined training sessions to support reporting, dashboard use, and onboarding, and the rapid uptake of adaptive management strengthened strategic agility, with positive feedback from across the Portfolio. The Research Plans of Results and Budgets section of the CGIAR website was updated to ensure easy open access to Initiative, SGP and Impact Platform Plans of Results and Budgets (PORBs). The 2024 reporting cycle continued this trajectory, integrating insights from the 2023 Learning and Optimization process and Action Plan to further refine CGIAR’s Technical Reporting processes and products. Key improvements in 2024 included: • Launching the PRMS Planning Module to support the replan process: The launch of an online Planning Module synchronized TOC and Planning data in the PRMS, improving the efficiency and quality of planning workflows. Enhanced replan guidelines were provided to help Initiatives, Impact Platforms, and SGPs implement 2023 Reflect recommendations and align budget forecasts with updated budget envelopes. To support continuous learning and adaptive management, a user experience survey on the Planning Module was conducted to assess effectiveness and inform user-centered enhancements for the 2025-30 Portfolio. • Further simplifying reporting processes and tools: A series of enhancements to PRMS functionalities were implemented to improve efficiency and usability. Improved filtering options, enhanced notification systems, and more clearly structured result PDFs now enable quicker access to relevant information. Innovation Packages and Scaling Readiness language and templates were simplified. Reporting was streamlined and modified to suit the final year of reporting for the Portfolio, with an Outcome Indicator Module co-developed with input from Initiatives, Impact Platforms and SGPs to provide them with the opportunity to assess their progress against targets for Work Package outcomes and end-of-Initiative outcomes; summative and yearly highlights were combined into a single report; and adaptive management processes removed. • Improving decision-making within the PRMS: Broader engagement from PRMS testers across reporting entities and Senior Program Managers was integrated into PRMS feature development, ensuring that system updates were aligned with user needs and supported consistent decision-making. • Enhancing product clarity: The Type 1 Annual Report template was reviewed to better accommodate end-of-Initiative outcome reporting for the final year of the Portfolio. Improvements to the Results Dashboard were made to enhance the accessibility of IPSR insights. • Strengthening quality assurance: Examples include updated and enhanced QA guidance, and updated guidance on Impact Area tagging. An AI tool was prototyped and tested on a series of data fields, with the intent to leverage lessons learned and develop an enhanced AI tool that can be applied to a broader set of reported data and integrated into the PRMS, supporting both the reporting and QA phases. • Developing the Semantic Natural Language Processing Aggregator Platform (SNAP): SNAP is an AI-powered tool enhancing access to and analysis of CGIAR’s reported outputs, outcomes, and impacts. It improves access to Portfolio information and results evidence through semantic searches, thematic clustering, and automated summaries, complementing the CGIAR Results Dashboard. SNAP-supported narratives were integrated into the CGIAR 2024 Portfolio Narrative, and ongoing refinements will further enhance its role in Portfolio reporting. • Further integrating SGPs and Impact Platforms: Between 2022 and 2024, CGIAR progressively aligned these entities with its Technical Reporting processes and common systems to enhance consistency and coherence. In 2023, three Impact Platforms – Nutrition, Health and Food Security; Climate Adaptation and Mitigation; and Environmental Health and Biodiversity – were onboarded alongside the Gender Equality, Youth and Social Inclusion Impact Platform (which reported in 2022), each receiving tailored support such as TOC and results framework development. The SGP pilot launched in 2023 further expanded CGIAR’s reporting ecosystem by integrating Center-specific Window 3 awards, with two SGPs submitting first-year results using the PRMS Reporting Tool and Type 1 Report template. In 2024, integration expanded to include the Poverty Reduction, Livelihoods and Jobs Impact Platform and four additional SGPs, further broadening the reporting ecosystem. • Enhancing risk management through the PRMS Risk Module: The Risk Management Module, launched in 2023 to support Initiative management and reporting of risks, was further enhanced in 2024, allowing Initiatives to capture transition-focused risks. It enabled Initiatives to review, update, or close risks, contributing to the design of the 2025-30 Portfolio. The updated Risk Management Module will be used by Programs and Accelerators from 2025 onward. Climate-Smart Village set-up under the Adaptation and Mitigation Initiative in Agriculture (AMIA) of the Department of Agriculture. Credit: Miguel Mamon/CIAT May 2025 54 CGIAR Portfolio Practice Change (Type 3) Report 2024\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 4\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 4 1. Technical Reporting Arrangement purpose, scope, value proposition, delivery and optimization, Purpose The purpose of th e Technical Reporting Arrangement 2025 -2030 (“TRA 25-30”) is to set out the technical reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. The TRA 25-30: • Provides the parameters that e nable the Centers, the CGIAR System Partners and the System Organization to fulfil their technical reporting obligations under the funding agreements that apply to the use of Window 1 and Window 2 funds from the CGIAR Trust Fund (“Pooled Funding”). These parameters also allow the Integrated Partnership Board to fulfil its responsibility under the CGIAR System Charter to report on programmatic performance of CGIAR Research on an annual basis. • Provides, through the establishment of common technical reporting principles, enabling tools and mechanisms, progressive alignment and synergy between the technical reporting requirements that apply to components of the CGIAR Portfolio that are funded by Pooled Funding and those that apply to the components that are funded by other sources of funds (“Non-Pooled Funding”). • Sets transparency, performance tracking, and accountability expectations between CGIAR System Funders and CGIAR including Centres, • Informs decision making at different levels, underpins research management, operationalizes the Performance and Results Management Framework (PRMF), and guides portfolio -level MELIA and the design of the next Performance and Results management System (PRMS). The current Technical Reporting Arrangement that applies to the CGIAR Portfolio during the period 2022-24 (“TRA 22-24”) was co-developed by CGIAR and System Council/Strategic Impact Monitoring and Evaluation Committee (SIMEC) members in 2022. A new TRA is needed to match 2025-30 portfolio parameters, notably the alignment of pooled and non-pooled funding sources, and to apply lessons learnt from 2022-24. Scope The TRA 25-30 provides the operational and enabling basis to plan, monitor, learn and report on the 25-30 Portfolio. It is designed to progressively enable Programs and Accelerators, Centers and their research teams to report on the pooled, bilaterally and W3-funded components of the 2025- 30 portfolio in an integrated and aligned way, without increasing reporting burdens of Centers and Scientists. Going forward, the CGIAR Integrated Partnership will work towards progressively greater alignment of W3/bilateral projects and programs with the 2030 outcomes and theories of change of the Programs and Accelerators. Centers will provide key agreed information on their W3/bilaterally funded projects and programs to enable Program/Accelerator leaderships to explore ways to achieve alignment based on, inter alia, complementarity of results as well as actual or potential thematic, geographic, and partnership overlaps. Reporting on and attribution\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 5\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results framework, underpinned by a new Technical Reporting Arrangement, will provide robust, continuous performance and results reporting across all funding sources, as well as adaptive management of the Portfolio. 1 Value Proposition The TRA 25-30: - Creates value by delivering an integrated approach that tracks the performance of each Program and Accelerator, - Brings together the inputs (including costs), outputs, outcomes and impacts of the total portfolio to allow for easier and more robust Return on Investment (ROI) calculations. - Avoids creating a significant additional and duplicative layer of complex reporting requirements for W3/ bilaterally funded work. - Informs decision making through providing ready access to demand-driven quality raw and curated data products. Delivery The TRA 25 -30 will be delivered in line with Management arrangements for CGIAR’s 2025 —30 science and innovation Portfolio. Specific roles and responsibilities will be defined in 2025. 1 CGIAR Portfolio Narrative, 1 November 2024\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:p7]\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 7\nContent: Trifa, Nicoleta (CGIAR System Organization) 0:48 Yep. OK, good. So thank you. This session is the first of two session plans for today, planned for today, with the second being scheduled later at 3:00 PM CET to accommodate colleagues in other time zones. Technical reporting. My name is Nicoletta Trifa. By the way, I'm part of the Portfolio Performance Unit, the support unit within the Office of the Chief Scientist. Here is an overview of what we'll cover in the next minutes. I believe my presentation will take 2025 minutes and then we'll leave room for questions at the end, if that's OK. So what we'll cover an update of the technical reporting arrangements 2025 to 2030, priorities and changes for 2025, a brief introduction on the annual technical report and the neighbors. So this mean the performance and results. Management system and the quality assurance, the technical reporting timeline, available resources and support and what's next and how to stay engaged. I want to mention that this session marks the start of the conversation around 2025 technical reporting. We want to give you the early look at the key priorities and plans for the months ahead, and the goal is to make sure that you stay informed, prepared and supported with a clear understanding of upcoming deliverables and timelines. And also clarity on who to reach out to if you have questions or if you need help along the way. Good. Technical reporting arrangements for the new portfolio. The 2025 to 2030 portfolio has been approved by the CGR Global Leadership team on in June 2025 and provides the operational basis to plan, monitor, learn and report. On the new portfolio. It is designed to progressively enable programs, accelerators and centers to report on the pooled and window 3 bilateral projects of the new portfolio in an integrated and aligned way without increasing the burden on centers and the scientists. Main changes compared to the previous technical reporting arrangements, streamline reported reporting. So less products, more integration, lower transaction costs, stronger impact, focus results. To be clearly linked and packaged under impacts, outcomes and associated agreed indicator targets and better linkages between the theory of change or so plan of results and budget and technical reporting. The primary audiences for technical reporting are funders and CGR staff at integrated partnership, portfolio and program and accelerator levels. A secondary audience is the partners. Annual technical reporting covers the individual annual technical reports for program and accelerators, as well as a portfolio view of aggregate contribution to thematic and geographic targets. And relevant content from this technical reports are integrated into the CJR corporate reporting. In terms of the 2025 technical reporting priorities, 2025 is a transition year with technical reporting arrangements, implementation again focusing on streamlined reporting and on strengthening the linkages between theory of change. Porb, media and technical reporting. As many of you know, in the previous portfolio these components were not properly linked, so it was a bit challenging to demonstrate progress against the theory of change or the plans, as you know. In terms of deliverables for 2025. These are the program and accelerator technical reports, which are due in April 2026, the portfolio narrative, which is due in 2026 in June. Integration of top 80% of window tree and bilateral projects by central dollar value into reporting and planning. Application of the minimum data standards for window tree and bilateral reporting. And mapping of refinement during the pause and reflect process which will take place early Q 1/20/26. So as I was mentioning, this year is seen more as a transition year towards KPI based planning and reporting and efforts are underway to enable planning and reporting at the KPI level, which is aligned with the system office objective and key results for 2026 and 20. These are to be confirmed, so they haven't been confirmed yet, but I've pasted them here so that you can see the 2026 objective and key results for the system office. So 100% program and accelerate the work plans and budget. An annual technical report. Which provide for software enabled monitoring of erformance and results against smart Ki by center, ear and ooled funds invested. So next year, 80% of centres, CGR, window three and bilateral funded work by value included in 2025 technical reports and then the following year in 2027, this will increase to 90% of centres. Window 3 and bilateral funded work included in 2026 technical reports. The following slides, what I have, what I have included in the following slides, it's a brief introduction into. What is expected in terms of deliverables from programs and accelerators together with an overview of the performance and results management system and the QA. I realized that some in this call some of you are already familiar with the reporting arrangements from the previous portfolio. While for others this might be entirely new. So our goal is to bring everyone to the same level of understanding so that we can move forward with clarity and shared expectations for the 2025 technical reporting. OK, so technical reporting for program and accelerator. We'll focus on three key deliverables. So first is reporting results, the 2025 results in the Performance and Reporting Management system, PRMS. Each program accelerator and mapped window 3 project will report 2025 results in the system and we strongly encourage to report results that were planned and budgeted. So results which have been included in the reports. As the outdated technical reporting system will allow for tracking results against plans. Secondly is the quality assurance of reporting results. As you know, the results submitted go through the quality assessment process and we will share more details on this process in the timeline in an info session scheduled for later. Which we will schedule later in in September, October and the quality assess results will be available on the results dashboard. Inform the pause and reflect and will be included in the technical reports in the annual technical reports. A third deliverable for program and accelerators is drafting estimation of the 2025 Annual Technical Report. So each program and accelerator is responsible for drafting and internally validating quality assessing their 2025 Annual Technical Report. Before submitting it to the PPU, so to the perform portfolio performance unit. Again, guidance on this, the detailed process and validation process will be shared with you timely. Also to support this process, an AI generated V0 draft will be provided as a starting point. The annual technical reports. What are they? This the annual technical report. The the the aim is to make them short, so to 20 to 30 pages, concise and targeted. They provide assurance on annual program accelerator delivery against the boards, so plan of results and budget and progress on theory of change. They are based on quality assess results, the template guidance and as I mentioned and. AI V0 will be provided to all rogram and accelerator teams. Annual technical reports need to be submitted by each program and accelerator in March, April, so more details on this will follow and publication is intended to happen end of April, beginning of May. Here to the right side you have the. Content of the annual the proposed content for the annual technical report as per the technical reporting arrangements. Many of you will notice that there are not no big changes compared to previous portfolio, so the idea is to have a fact sheet and executive summary. The annual progress on theory of change, area of work details, a section on results, section on partnerships, portfolio linkages, adaptive management and then one key result story. But again, we will plan a detailed deep dive session on the annual technical report template and the guidance. So there will be time for you to ask questions in detail about about this and to receive support obviously. I've also included here for reference links to the 2024 Annual Technical Reports from the initiatives and impact platforms, and also a link to the 2024 Portfolio Narrative Report. In case you want to, you want to have a look to see, um, what it captures. PRMS. So this stands for Performance and Results Management System is the system the the the the environment where results need to be submitted. Again, the team is working on updating their resources. There will be. New users onboarding decks created with the links to different information and I I believe the PCU Alison together with the program coordinators. Are. The all the PRMS roles. So PCU is leading a work to define the PRMS roles and to get the information from program and accelerators regarding who from each program accelerator should have what role in PRMS. To enable us to to provide the right access to the platform when the time comes to report. Quality assurance process. So results submitted by program and accelerators in the PRMS will be quality assessed by a quality assessment team in February 2026. Your participation in this process is required. Guidance and resource resources will be provided and also an info session will be scheduled later this year. What is the QA? It is a process that aims to improve the quality of the reported data to provide consistency across the system, ensure reliability of reported results. Inform the learning process and improve the overall CGR accountability and transparency. Quality assess data informs the reflect process which takes place early Q12026, the results dashboard. So once the quality assessment of the results is finalized, the quality assess results will be pushed to results dashboard. You most probably have seen that. Reading. It also informs and are the results. The practices results are included in the annual report, in the portfolio narrative, and then in the overall CGIR annual report. In terms of the the timeline, so we have this info session now to provide an overview on the technical reporting and there will be several other info session and deep dive scheduled. Throughout September and October of reporting 2025 results, we believe that it will be feasible to open the PRMS in November for program and accelerators to to report. The date is still to be confirmed. We're aiming to to, yeah, to meet to to to end November. Hopefully this will be this is feasible from the technical side quality assurance. It's planned for February 2026 reflect process as I was mentioning Q 1/20/26 and then annual technical reports are due in March, April 2026 as well. Where to find information pertaining to technical reporting and planning and media? There is a one stop shop for for um all this. It's called the Performance and Results Hub. I'm gonna stop sharing cause I wanna share. Um, I'm gonna stop sharing the deck. I wanna. We could resent the hub. I'm not going to go through each section, but at least. So that you can see for those who are new more specifically to see and we will also share the link obviously the performance and results hub as I was mentioning it has detail on reporting, planning, reflect, replan. So you come in here, you click on 2025 reporting and then you will have access to the latest information, to the timeline, latest update, upcoming events. So all the information, information. Session dates will be listed here. We'll also have a subsection here with. Recording from from meetings, so that will be posted. For example today after this session we'll post a recording and the deck here for you to access and there is a section on frequently asked question. We recycled a couple of questions from the previous portfolio and updated them so that they are applicable to the program and accelerator teams, so feel free to go here and and browse. As resources become available, we will place them here and we will notify you by e-mail. OK. Going back to my deck. Which? In terms of engagement plan, so in order to streamline communication and optimize support for program accelerators and centers with mapped window 3 bilateral projects, we will send bi-weekly emails to everyone in this. This goal with key updates on technical reporting, with reminders and also with the latest questions and answers available on the hub. There will be targeted emails focusing on specific categories within the program accelerators. We want to engage with some of you on technical reporting, revisions, developments. And the aim is to gather feedback from you. Program coordinators will be copied on these emails. Info session. So a specific topic and we'll plan info session on specific topics, for example the standard indicator, description shades, the guidance on technical reporting, quality assurance. Reporting on innovations, the PRMS, so deep dive on the PRMS, the updates, the tool and so on. And during the reporting phase and the QA we will have weekly drop-ins. So this drop-ins is there will be no presentation. Presentation during the during this drop-ins. The purpose is for us to provide live support, so to answer your questions on the spot and the primary focus will be as I was mentioning, reporting and the QA. For if you know for every question you have, we invite you to use this e-mail address performanceandresults@cgr.org. This is the. The e-mail address we use for all technical reporting questions. So you have the questions right to us at performanceandresult@cjr.org and you will receive a response. We are aiming to respond within the 24 hours. Just to give an example, you know going back here I've gotten the targeted targeted emails and feedback. So this is a good example on for example how we plan to engage and get get feedback from from you on the PRMS enhancements so. Usually we send there's an e-mail sent to invite you to provide feedback on a o</t>
   </si>
   <si>
@@ -480,13 +673,22 @@
   </si>
   <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: Summarize the PRMS enhancement cycle and define the Sounding Board.\n\nContext:\n\n---\n\n[ID: docx:Engagement Plan 2025 Technical Reporting.docx:u58-61]\nFile: Engagement Plan 2025 Technical Reporting.docx\nLocation: section 'PRMS enhancements and feedback process' paragraph 99 to section 'PRMS enhancements and feedback process' paragraph 104\nContent: The PRMS Reporting Tool is continuously improved in response to user needs and feedback. The update process follows these steps: The Sounding Board will consist of representatives from: PRMS Team PCU Team\n\n---\n\n[ID: pptx:Engagement Plan 2025 Technical Reporting.pptx:s3pt1]\nFile: Engagement Plan 2025 Technical Reporting.pptx\nLocation: slide 3 part 1\nContent: PRMS\n\n---\n\n[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s12pt1]\nFile: Information Session on 2025 Technical Reporting.pptx\nLocation: slide 12 part 1\nContent: PRMS\n\n---\n\n[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s7pt1]\nFile: Information Session on 2025 Technical Reporting.pptx\nLocation: slide 7 part 1\nContent: PRMS Reporting Tool PRMS\n\n---\n\n[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s7pt2]\nFile: Information Session on 2025 Technical Reporting.pptx\nLocation: slide 7 part 2\nContent: PRMS REPORTING TOOL PRMS\n\n---\n\n[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s7pt3]\nFile: Information Session on 2025 Technical Reporting.pptx\nLocation: slide 7 part 3\nContent: PRMS roles PRMS resources:\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p32pt2]\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 32 part 2\nContent: and demonstrate how CGIAR acts through multiple workstreams to achieve impact. Each section starts with an overview of current challenges and CGIAR’s work on a continent. We then summarize the evidence identified on the continent. Each continent section primarily focuses on the\n\n---\n\n[ID: docx:User Roles and Rules for the PRMS Reporting.docx:u1-4]\nFile: User Roles and Rules for the PRMS Reporting.docx\nLocation: section 'User Roles and Rules for the PRMS Reporting Tool' paragraph 1 to section 'Lead and Co-Lead:' paragraph 4\nContent: User Roles and Rules for the PRMS Reporting Tool Roles: Roles define the level of responsibility and permissions a user can have within the PRMS. They determine the role a user has in the submission of results and data management within PRMS, ensuring consistent governance, accountability, and clarity of access across Portfolio (or reporting entities – whichever version you plan to use from now on). Lead and Co-Lead:\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p16pt1]\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 16 part 1\nContent: Impacts and outcomes by Impact Area In the following sections, we present evidence of the real- world impacts of CGIAR-supported interventions for each CGIAR Impact Area. Each section starts with an overview of current challenges and CGIAR’s work in that Impact Area. We then summarize the evidence identified pertaining to the Impact Area. Each Impact Area section focuses on the evidence of impact or outcomes on three to four types of work that CGIAR conducts\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p37pt3]\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 37 part 3\nContent: small ruminant producers to markets (PRMS 10489). SMS, voice messages, and mobile tools were used by Jokalante in Senegal to deliver gender-sensitive climate information to nearly 900,000 pastoralists in 2024 alone (PRMS 17907). Meanwhile, iShamba in Kenya reached more than 2 million farmers through a television show on climate and financial literacy (PRMS 17712). A child drinking milk produced by the family cow. Photo credit: Apollo Habtamu/ILRI Engagement with national governmental bodies CGIAR’s impact across Africa was substantially amplified through strategic partnerships with national governments. By providing its expertise to national planning processes, CGIAR translates research into actionable policies. In addition to examples previously mentioned, CGIAR research informed: • Ethiopia’s food-based dietary guidelines (PRMS 247) and food systems transformation agenda (PRMS 6632) • Kenya’s climate action strategies (PRMS 7994) • Morocco’s efforts to mainstream conservation agriculture into national strategies (PRMS 17173) • Rwanda’s Strategic Plan for Agricultural Transformation (PRMS 17043) • Zambia’s National Green Growth Strategy (PRMS 17975) CGIAR’s modeling tools informed multiyear investment plans in Tanzania (PRMS 17039) and Rwanda (PRMS 17043), shaping investment decisions based on measurable outcomes such as GDP growth and poverty reduction. CGIAR also informed public sector investment plans in Madagascar and Senegal (PRMS 8060, 18082) and the development of public-private partnerships in Mali (PRMS 948). CGIAR’s agronomy-as-scale solutions, which focus on conservation agriculture, are incorporated into national strategies and Africa-wide declarations such as the Rabat Declaration by 3ACCA\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p5pt2]\nFile: Portfolio Narrative_2024.pdf\nLocation: page 5 part 2\nContent: of CGIAR’s Technical Reporting Arrangement. It offers a synthesis of Portfolio coherence, synergies, and collective progress across Initiatives, Impact Platforms, and Science Group Projects (SGPs)1, which represent approximately 40 percent of CGIAR’s Portfolio by dollar value. The report does not include Center-managed bilateral projects. As a key pillar of the Technical Report, the Portfolio Narrative integrates data and insights from CGIAR’s Results Dashboard, the Type 1 Initiative, Impact Platform, and SGP Reports, and the Type 3 Portfolio Practice Change Reports to demonstrate how CGIAR has advanced research delivery, fostered partnerships, and addressed global challenges. As 2024 marks the final year of this Portfolio and the 2022–2024 business cycle, the 2024 CGIAR Portfolio Narrative takes a dual approach to its analysis and reporting. Alongside highlighting key achievements, strategic shifts, and operational progress for 2024, the report also provides a cumulative overview of the three-year business cycle, showcasing both the immediate outcomes of 2024 and the broader trajectory of the Portfolio’s contributions to CGIAR’s strategic goals. By presenting both annual and multiyear insights, the report underscores the cumulative impact of CGIAR’s work and sets the stage for the transition to the 2025–2030\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt2]\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 47 part 2\nContent: which could be defined as a more proximate goal. • Potential solution: Define proximate and ultimate Impact Area indicators, which relate to stages in the impact pathways and include more studies that attempt to demonstrate the relationships between the two. Defining common impact pathways used in CGIAR programming would also be beneficial. • There is fragmentation in the indicators measured in impact evaluations and the Impact Area indicators required in the Results Framework. There is also a disconnect between studies that measure innovation use and studies that assess their impacts, especially regarding the ongoing use of innovations. These two issues make aggregation of CGIAR’s progress toward Impact Area indicators challenging. There are very few examples where highly reliable evidence of innovation use is coupled with rigorous impact evaluation evidence. • Potential solution: Integrate impact evaluation into the annual reporting of innovation use, with requirements to use Impact Area indicators in those evaluation studies. More system-level approaches are needed to plan and finance complementary monitoring and impact efforts, especially monitoring ongoing use (or dis-adoption) of impactful innovations. Three of the Impact Area studies identified indicators, developed methodologies, and tested them using examples of CGIAR innovations to try to estimate aggregate CGIAR effects. These preliminary methods are in the proof-of-concept phase and still under internal review. However , the methods explored through these processes and the limitations identified will provide valuable learnings to increase CGIAR’s ability to report on its real-world impacts in the next version of this report. Comparison with 2017–2021 Retrospective analysis of CGIAR’s 2017 to 2021 reporting cycle provides a reference point for assessing progress in outcome reporting and portfolio management under the current Results Framework. While differences in the reporting systems limit direct comparability, several structural patterns from the previous cycle remain relevant. Policy outcomes Learnings from CGIAR’s 2017 to 2021 reporting cycle demonstrate that policy outcomes were mostly oriented toward policies and strategies (75 percent), and the rest influenced budget and investment"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question:  What evidence architecture and rigor standards underpin the report’s claims? \n\nContext:\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1]\nLink: N/A\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 67 part 1\nContent: Figure 31: Methods and rigor of the impact evaluations included in this report. Note: Some studies used multiple methods or received multiple rigor scores for different reported impact estimates. Therefore, the sum of the number of studies reflected in the graph is more than the total number of 62. 4 1 6 4 15 125 4 5 13 62 43210 98765 Rigor score 0 5 10 15 20 4 3 1 43 32 2 3 5 2 2 13 1 2 1 1 1 1 2 1 1 4 6 2 4 4 1 Other ﬁxed eﬀects models Diﬀerence in diﬀerence Propensity score matching and other matching approaches Instrumental variables Endogenous switching regression Randomized control trial Number of publications by rigor score Rigor of the evidence by study design Figure 32: Proportion of impact evaluation analyses which met each of the best-practice rigor score criteria. Included are 125 studies, which contained 488 indicator analyses. 0 100 200 300 400 Spillovers Sensitivity analysis Representativeness Random treatment assignment Random sampling Power Heterogeneous treatment eﬀects Baseline balance Attrition UncertainDid not meet criteriaMet criteria 1%58% 41% 60%40% 56%15% 29% 81%19% 81% 19% 18% 82% 14% 86% 50% 50% 21% 79% B. Impact indicators CGIAR’s Results Framework contains 19 Impact Area indicators it committed to tracking in the 2022 to 2024 period. These indicators are well aligned with the SDG targets and supporting indicators. CGIAR poverty-related indicators are closely linked with SDG targets 1.1 and 1.2 (on reducing poverty) and target 2.3 (on increasing agricultural productivity on small farms). CGIAR nutrition-related indicators are well aligned with SDG targets 2.1 and 2.2 (on reducing hunger and\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3]\nLink: N/A\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 7 part 3\nContent: fully contextualize the results. Are you an implementer? Consider jumping directly to your Impact Area or Continent of interest. But be sure to return and read about the Scope of the Report so that you know what is, and is not, included in this report. Tips on interpretation When interpreting the outcomes reported, be cautious about aggregating across data sources (e.g., as Performance and Results Management System [PRMS] and SPIA country studies), Impact Areas, and continents. Some outcomes are included in more than one of these categories. Pay attention to the specified time period. The report focuses on evidence reported during the 2022 to 2024 period, but outcomes and impacts often developed over much longer periods. Consider the overall weight of the evidence, not individual pieces of evidence. This report presents a body of evidence, drawing on a variety of different epistemological approaches: outcome evidence, impact evaluations, and other types of information, which collectively provide different insights into CGIARs impact. However , only impact evaluations were assessed for the number of best research practices they used, with a composite score of 0 to 9 assigned based on the number of key components of rigor addressed by the study. While weighted equally in this work, these components do not all have equal implications for overall study\n\n---\n\n[ID: pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2]\nLink: N/A\nFile: Food Frontiers and Security_Inception Report 30-06-2025.pdf\nLocation: page 1 part 2\nContent: Report Food Frontiers and Security Science Program Inception Report\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt1]\nLink: N/A\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 12 part 1\nContent: All impact study submissions were reviewed for potential inclusion into the evidence base of the report. The two primary inclusion considerations were relevance and rigor (see Annex A. Selection of evidence). Studies were determined to be relevant if they considered the outcomes and impacts of CGIAR-supported interventions, regardless of the authorship of the study. Outcomes reported into the CGIAR PRMS are quality assessed for relevance (that is, CGIAR’s role in the outcome is validated); therefore, none of these reported outcomes were excluded on the basis of relevance. Studies with unclear or misleading methods were excluded on the basis of rigor. Studies meeting this threshold of clarity were then classed as “impact assessments” or “impact evaluations.” Impact evaluations were the primary study designs of interest. Impact evaluations are studies that use statistical methods (experimental or quasi-experimental) to quantify the causal change in a condition that was achieved by an intervention. Studies using other study designs were included under the umbrella term of impact assessments (including impact evaluations), if they provided information relevant to understanding impacts, such as cost- benefit analyses, reviews of CGIAR work, and measures of the adoption of CGIAR technology. These included the country studies supported by CGIAR’s SPIA. While impact evaluations are necessary to establish causal change linking intervention and impact, they can be limited in scope due to practical constraints, such as resources and measurement challenges. Other types of impact assessments can provide valuable insights into CGIAR’s contributions to real-world change in a wider spatial or temporal context; however , they do c This can be common for power calculations. Authors may have conducted power calculations but not r eported that they did so in-text. Assessment is based on what is reported in-text, not what may have been done but not reported. d See Annex A. Included studies and rigor of\n\n---\n\n[ID: pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt3]\nLink: N/A\nFile: Breeding for Tomorrow_Inception Report 30-06-2025.pdf\nLocation: page 17 part 3\nContent: underpin the work being done and provide the solid positioning for holding the CA. This collaboration means the work being done relies on the most capable parts of both the CGIAR and the relevant partner and that this collaboration changes over time. A part of the Program’s objectives\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt2]\nLink: N/A\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 12 part 2\nContent: challenges. Other types of impact assessments can provide valuable insights into CGIAR’s contributions to real-world change in a wider spatial or temporal context; however , they do c This can be common for power calculations. Authors may have conducted power calculations but not r eported that they did so in-text. Assessment is based on what is reported in-text, not what may have been done but not reported. d See Annex A. Included studies and rigor of evidence for details. Criteria related to random sampling and treatment assignment; reporting of power calculation and sensitivity analysis; consideration of attrition, spillovers, and heterogenous treatment effects; and sample representativeness and baseline balance. not establish causality. Impact evaluations were further appraised to determine the number of best practices followed per study. A composite score45 was calculated to reflect the level of confidence in the findings of a study and to help understand the application of best practices in CGIAR impact evaluation. Nine best practices were identified (see Annex A. Included studies and rigor of evidence), resulting in the composite best- practice score ranging from 0 to 9. Not all the criteria were relevant to all studies, and some studies may have met criteria but did not clearly describe them in the publication.c Studies following three or more best practices were featured preferentially in this report (assuming equality in relevance). Details of the method and analysis of the scores are in Annex A. Included studies and rigor of evidence. Included impact studies Approximately 500 studies were reviewed for eligibility and 125 studies were included in the primary dataset. Of these, 62 were impact evaluations and 63 were impact assessments which did not attempt to establish the causal effect of an intervention on an impact. Randomized controlled trials (RCT) were the most common impact evaluation design (n = 21), followed by\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p4pt1]\nLink: N/A\nFile: Type3_2024Report.pdf\nLocation: page 4 part 1\nContent: Integration with other outputs The Portfolio Narrative informs the 2024 CGIAR Annual Report – a comprehensive summary of the organization’s collective achievements, impacts, and strategic outlook. Elements of the Type 2 report were integrated into the CGIAR Flagship Report released in April 2025 during the CGIAR Science Week. The Flagship Report synthesizes CGIAR research in an accessible format designed specifically to provide policy- and decisionmakers at national, regional, and global levels with the evidence they require to formulate, develop, and negotiate evidence-based policies and investments. The diagram below illustrates these relationships, emphasizing the interconnectedness of the Type 3 Report with other reporting products. CGIAR Results Dashboard Portfolio Narrative report CGIAR Annual report Type 1 Initiative, Impact Platform, and Science Group Project reports Type 2 CGIAR Contributions to Impact in Agrifood Systems: evidence and learnings from 2022 to 2024 Flagship report Type 3 Portfolio Practice Change report 2024 Technical Reporting Figure 1. CGIAR’s 2024 Technical Reporting components and their integration with other CGIAR reporting products. Section 1: Introduction 1 Under the CGIAR Technical Reporting Arrangement for the next Portfolio (2025-30), relevant aspects of the Type 3 Report will be included in the annual Portfolio Narrative, and a separate Type 3 Report will no longer be produced. The 2024 CGIAR Portfolio Practice Change\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt4]\nLink: N/A\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 48 part 4\nContent: against CGIAR’s Results Framework is that, apart from the SPIA country studies, other internal and external studies are designed in an uncoordinated bottom-up way. Because such studies are undertaken to meet specific information needs, opportunities to learn through synthesis or aggregation are missed due to the differences in indicators used and measurement approaches employed. For example, impact assessments are rarely connected with data on innovation use, preventing case study results from being used to extrapolate possible large-scale effects. Thus, moving forward, two areas for improvement are: (1) to collectively undertake strategic impact assessments that will answer high-priority impact assessment questions and (2) to develop and enforce the use of a core set of common indicators and measurement methodsq that should be used in impact assessment studies regardless of who initiates them. In addition, during the 2022 to 2024 period, Initiatives defined targets for outcomes and made commitments to measuring and reporting on those outcomes. They did not have a similar plan or commitment to measuring impacts. As CGIAR evolves to longer-term programs covering the whole of CGIAR, there should be commitments to the consistent measurement of impacts. However , this has been an ongoing challenge within the organization, with similar recommendations from a review of the 2017 to 2021 portfolio.176 Rigor of the evidence All impact evaluations identified were assessed for their rigor based on criteria established by Rao 2025.45 The most common score was a 4 of 9 key elements being present, suggesting moderate overall quality and room for improvement. A high number of impact evaluations used rigorous methods to infer causality between a CGIAR innovation and impacts (see Annex A. Included studies and rigor of evidence). However , many failed to consider heterogeneous treatment effects or report power calculations. Most of the impact evaluations used experimental or quasi-experimental designs with two or more measurement periods. However , a sizeable group of the studies were based on cross-sectional (single measurement) studies. While they are peer-reviewed and employ recommended methods of controlling for unobservable variables to enhance the likelihood of a causal inference, there remain limitations to such designs. In addition to rigor , this study paid attention to the relevance of the studies. Often, studies employing less rigorous, cross-sectional methodologies were able to provide evidence more relevant to policymaking and decision-making Tradititional rice variety in Ilagan, Isabela, the Philippines. Photo credit: Miguel Mamon/CIAT CGIAR Impacts in Agrifood Systems: | Learnings | Page 90 of 130 CGIAR CGIAR CGIAR Impacts in Agrifood Systems: | Learnings| Page 91 of 130\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]\nLink: N/A\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 31 part 4\nContent: four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the \"challenges and megatrends\" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p6pt1]\nLink: N/A\nFile: Portfolio Narrative_2024.pdf\nLocation: page 6 part 1\nContent: Integration with other outputs The Portfolio Narrative informs the 2024 CGIAR Annual Report – a comprehensive summary of the organization’s collective achievements, impacts, and strategic outlook. Elements of the Type 2 report fed into the CGIAR Flagship Report, released in April 2025 at CGIAR Science Week. The Flagship Report\n\n---\n\n[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]\nLink: N/A\nFile: Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 3\nContent: activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt3]\nLink: N/A\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 46 part 3\nContent: to ensure common terminology across the reporting units. At the impact level, there were 19 indicators across the five Impact Areas. The frequency of reporting against exact indicators is very low (18 percent of indicators assessed match those in the Results Framework; Annex B. Impact indicators). In addition, there is an imbalance across Impact Areas and indicators in the frequency with which 2022 to 2024 studies attempt to measure those indicators. There were many impact assessments that measured yields or income related to the poverty indicators, and relatively few that looked at environmental, climate, or gender indicators. This is consistent with what Templeton (2023)176 found in her review of evidence used to support the impact claims made by the CGIAR Research Programs between 2017 and 2021. Thus, there remains a huge challenge to define feasible indicators for"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question:  What evidence architecture and rigor standards underpin the report’s claims? \n\nContext:\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 67 part 1\nContent: Figure 31: Methods and rigor of the impact evaluations included in this report. Note: Some studies used multiple methods or received multiple rigor scores for different reported impact estimates. Therefore, the sum of the number of studies reflected in the graph is more than the total number of 62. 4 1 6 4 15 125 4 5 13 62 43210 98765 Rigor score 0 5 10 15 20 4 3 1 43 32 2 3 5 2 2 13 1 2 1 1 1 1 2 1 1 4 6 2 4 4 1 Other ﬁxed eﬀects models Diﬀerence in diﬀerence Propensity score matching and other matching approaches Instrumental variables Endogenous switching regression Randomized control trial Number of publications by rigor score Rigor of the evidence by study design Figure 32: Proportion of impact evaluation analyses which met each of the best-practice rigor score criteria. Included are 125 studies, which contained 488 indicator analyses. 0 100 200 300 400 Spillovers Sensitivity analysis Representativeness Random treatment assignment Random sampling Power Heterogeneous treatment eﬀects Baseline balance Attrition UncertainDid not meet criteriaMet criteria 1%58% 41% 60%40% 56%15% 29% 81%19% 81% 19% 18% 82% 14% 86% 50% 50% 21% 79% B. Impact indicators CGIAR’s Results Framework contains 19 Impact Area indicators it committed to tracking in the 2022 to 2024 period. These indicators are well aligned with the SDG targets and supporting indicators. CGIAR poverty-related indicators are closely linked with SDG targets 1.1 and 1.2 (on reducing poverty) and target 2.3 (on increasing agricultural productivity on small farms). CGIAR nutrition-related indicators are well aligned with SDG targets 2.1 and 2.2 (on reducing hunger and\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 7 part 3\nContent: fully contextualize the results. Are you an implementer? Consider jumping directly to your Impact Area or Continent of interest. But be sure to return and read about the Scope of the Report so that you know what is, and is not, included in this report. Tips on interpretation When interpreting the outcomes reported, be cautious about aggregating across data sources (e.g., as Performance and Results Management System [PRMS] and SPIA country studies), Impact Areas, and continents. Some outcomes are included in more than one of these categories. Pay attention to the specified time period. The report focuses on evidence reported during the 2022 to 2024 period, but outcomes and impacts often developed over much longer periods. Consider the overall weight of the evidence, not individual pieces of evidence. This report presents a body of evidence, drawing on a variety of different epistemological approaches: outcome evidence, impact evaluations, and other types of information, which collectively provide different insights into CGIARs impact. However , only impact evaluations were assessed for the number of best research practices they used, with a composite score of 0 to 9 assigned based on the number of key components of rigor addressed by the study. While weighted equally in this work, these components do not all have equal implications for overall study\n\n---\n\n[ID: pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1\nFile: Food Frontiers and Security_Inception Report 30-06-2025.pdf\nLocation: page 1 part 2\nContent: Report Food Frontiers and Security Science Program Inception Report\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 12 part 1\nContent: All impact study submissions were reviewed for potential inclusion into the evidence base of the report. The two primary inclusion considerations were relevance and rigor (see Annex A. Selection of evidence). Studies were determined to be relevant if they considered the outcomes and impacts of CGIAR-supported interventions, regardless of the authorship of the study. Outcomes reported into the CGIAR PRMS are quality assessed for relevance (that is, CGIAR’s role in the outcome is validated); therefore, none of these reported outcomes were excluded on the basis of relevance. Studies with unclear or misleading methods were excluded on the basis of rigor. Studies meeting this threshold of clarity were then classed as “impact assessments” or “impact evaluations.” Impact evaluations were the primary study designs of interest. Impact evaluations are studies that use statistical methods (experimental or quasi-experimental) to quantify the causal change in a condition that was achieved by an intervention. Studies using other study designs were included under the umbrella term of impact assessments (including impact evaluations), if they provided information relevant to understanding impacts, such as cost- benefit analyses, reviews of CGIAR work, and measures of the adoption of CGIAR technology. These included the country studies supported by CGIAR’s SPIA. While impact evaluations are necessary to establish causal change linking intervention and impact, they can be limited in scope due to practical constraints, such as resources and measurement challenges. Other types of impact assessments can provide valuable insights into CGIAR’s contributions to real-world change in a wider spatial or temporal context; however , they do c This can be common for power calculations. Authors may have conducted power calculations but not r eported that they did so in-text. Assessment is based on what is reported in-text, not what may have been done but not reported. d See Annex A. Included studies and rigor of\n\n---\n\n[ID: pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_Inception Report 30-06-2025.pdf\nLocation: page 17 part 3\nContent: underpin the work being done and provide the solid positioning for holding the CA. This collaboration means the work being done relies on the most capable parts of both the CGIAR and the relevant partner and that this collaboration changes over time. A part of the Program’s objectives\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt2]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 12 part 2\nContent: challenges. Other types of impact assessments can provide valuable insights into CGIAR’s contributions to real-world change in a wider spatial or temporal context; however , they do c This can be common for power calculations. Authors may have conducted power calculations but not r eported that they did so in-text. Assessment is based on what is reported in-text, not what may have been done but not reported. d See Annex A. Included studies and rigor of evidence for details. Criteria related to random sampling and treatment assignment; reporting of power calculation and sensitivity analysis; consideration of attrition, spillovers, and heterogenous treatment effects; and sample representativeness and baseline balance. not establish causality. Impact evaluations were further appraised to determine the number of best practices followed per study. A composite score45 was calculated to reflect the level of confidence in the findings of a study and to help understand the application of best practices in CGIAR impact evaluation. Nine best practices were identified (see Annex A. Included studies and rigor of evidence), resulting in the composite best- practice score ranging from 0 to 9. Not all the criteria were relevant to all studies, and some studies may have met criteria but did not clearly describe them in the publication.c Studies following three or more best practices were featured preferentially in this report (assuming equality in relevance). Details of the method and analysis of the scores are in Annex A. Included studies and rigor of evidence. Included impact studies Approximately 500 studies were reviewed for eligibility and 125 studies were included in the primary dataset. Of these, 62 were impact evaluations and 63 were impact assessments which did not attempt to establish the causal effect of an intervention on an impact. Randomized controlled trials (RCT) were the most common impact evaluation design (n = 21), followed by\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p4pt1]\nLink: N/A\nFile: Type3_2024Report.pdf\nLocation: page 4 part 1\nContent: Integration with other outputs The Portfolio Narrative informs the 2024 CGIAR Annual Report – a comprehensive summary of the organization’s collective achievements, impacts, and strategic outlook. Elements of the Type 2 report were integrated into the CGIAR Flagship Report released in April 2025 during the CGIAR Science Week. The Flagship Report synthesizes CGIAR research in an accessible format designed specifically to provide policy- and decisionmakers at national, regional, and global levels with the evidence they require to formulate, develop, and negotiate evidence-based policies and investments. The diagram below illustrates these relationships, emphasizing the interconnectedness of the Type 3 Report with other reporting products. CGIAR Results Dashboard Portfolio Narrative report CGIAR Annual report Type 1 Initiative, Impact Platform, and Science Group Project reports Type 2 CGIAR Contributions to Impact in Agrifood Systems: evidence and learnings from 2022 to 2024 Flagship report Type 3 Portfolio Practice Change report 2024 Technical Reporting Figure 1. CGIAR’s 2024 Technical Reporting components and their integration with other CGIAR reporting products. Section 1: Introduction 1 Under the CGIAR Technical Reporting Arrangement for the next Portfolio (2025-30), relevant aspects of the Type 3 Report will be included in the annual Portfolio Narrative, and a separate Type 3 Report will no longer be produced. The 2024 CGIAR Portfolio Practice Change\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 48 part 4\nContent: against CGIAR’s Results Framework is that, apart from the SPIA country studies, other internal and external studies are designed in an uncoordinated bottom-up way. Because such studies are undertaken to meet specific information needs, opportunities to learn through synthesis or aggregation are missed due to the differences in indicators used and measurement approaches employed. For example, impact assessments are rarely connected with data on innovation use, preventing case study results from being used to extrapolate possible large-scale effects. Thus, moving forward, two areas for improvement are: (1) to collectively undertake strategic impact assessments that will answer high-priority impact assessment questions and (2) to develop and enforce the use of a core set of common indicators and measurement methodsq that should be used in impact assessment studies regardless of who initiates them. In addition, during the 2022 to 2024 period, Initiatives defined targets for outcomes and made commitments to measuring and reporting on those outcomes. They did not have a similar plan or commitment to measuring impacts. As CGIAR evolves to longer-term programs covering the whole of CGIAR, there should be commitments to the consistent measurement of impacts. However , this has been an ongoing challenge within the organization, with similar recommendations from a review of the 2017 to 2021 portfolio.176 Rigor of the evidence All impact evaluations identified were assessed for their rigor based on criteria established by Rao 2025.45 The most common score was a 4 of 9 key elements being present, suggesting moderate overall quality and room for improvement. A high number of impact evaluations used rigorous methods to infer causality between a CGIAR innovation and impacts (see Annex A. Included studies and rigor of evidence). However , many failed to consider heterogeneous treatment effects or report power calculations. Most of the impact evaluations used experimental or quasi-experimental designs with two or more measurement periods. However , a sizeable group of the studies were based on cross-sectional (single measurement) studies. While they are peer-reviewed and employ recommended methods of controlling for unobservable variables to enhance the likelihood of a causal inference, there remain limitations to such designs. In addition to rigor , this study paid attention to the relevance of the studies. Often, studies employing less rigorous, cross-sectional methodologies were able to provide evidence more relevant to policymaking and decision-making Tradititional rice variety in Ilagan, Isabela, the Philippines. Photo credit: Miguel Mamon/CIAT CGIAR Impacts in Agrifood Systems: | Learnings | Page 90 of 130 CGIAR CGIAR CGIAR Impacts in Agrifood Systems: | Learnings| Page 91 of 130\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 31 part 4\nContent: four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the \"challenges and megatrends\" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p6pt1]\nLink: N/A\nFile: Portfolio Narrative_2024.pdf\nLocation: page 6 part 1\nContent: Integration with other outputs The Portfolio Narrative informs the 2024 CGIAR Annual Report – a comprehensive summary of the organization’s collective achievements, impacts, and strategic outlook. Elements of the Type 2 report fed into the CGIAR Flagship Report, released in April 2025 at CGIAR Science Week. The Flagship Report\n\n---\n\n[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 3\nContent: activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt3]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 46 part 3\nContent: to ensure common terminology across the reporting units. At the impact level, there were 19 indicators across the five Impact Areas. The frequency of reporting against exact indicators is very low (18 percent of indicators assessed match those in the Results Framework; Annex B. Impact indicators). In addition, there is an imbalance across Impact Areas and indicators in the frequency with which 2022 to 2024 studies attempt to measure those indicators. There were many impact assessments that measured yields or income related to the poverty indicators, and relatively few that looked at environmental, climate, or gender indicators. This is consistent with what Templeton (2023)176 found in her review of evidence used to support the impact claims made by the CGIAR Research Programs between 2017 and 2021. Thus, there remains a huge challenge to define feasible indicators for"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question:  What evidence architecture and rigor standards underpin the report’s claims? \n\nContext:\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 67 part 1\nContent: Figure 31: Methods and rigor of the impact evaluations included in this report. Note: Some studies used multiple methods or received multiple rigor scores for different reported impact estimates. Therefore, the sum of the number of studies reflected in the graph is more than the total number of 62. 4 1 6 4 15 125 4 5 13 62 43210 98765 Rigor score 0 5 10 15 20 4 3 1 43 32 2 3 5 2 2 13 1 2 1 1 1 1 2 1 1 4 6 2 4 4 1 Other ﬁxed eﬀects models Diﬀerence in diﬀerence Propensity score matching and other matching approaches Instrumental variables Endogenous switching regression Randomized control trial Number of publications by rigor score Rigor of the evidence by study design Figure 32: Proportion of impact evaluation analyses which met each of the best-practice rigor score criteria. Included are 125 studies, which contained 488 indicator analyses. 0 100 200 300 400 Spillovers Sensitivity analysis Representativeness Random treatment assignment Random sampling Power Heterogeneous treatment eﬀects Baseline balance Attrition UncertainDid not meet criteriaMet criteria 1%58% 41% 60%40% 56%15% 29% 81%19% 81% 19% 18% 82% 14% 86% 50% 50% 21% 79% B. Impact indicators CGIAR’s Results Framework contains 19 Impact Area indicators it committed to tracking in the 2022 to 2024 period. These indicators are well aligned with the SDG targets and supporting indicators. CGIAR poverty-related indicators are closely linked with SDG targets 1.1 and 1.2 (on reducing poverty) and target 2.3 (on increasing agricultural productivity on small farms). CGIAR nutrition-related indicators are well aligned with SDG targets 2.1 and 2.2 (on reducing hunger and\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 7 part 3\nContent: fully contextualize the results. Are you an implementer? Consider jumping directly to your Impact Area or Continent of interest. But be sure to return and read about the Scope of the Report so that you know what is, and is not, included in this report. Tips on interpretation When interpreting the outcomes reported, be cautious about aggregating across data sources (e.g., as Performance and Results Management System [PRMS] and SPIA country studies), Impact Areas, and continents. Some outcomes are included in more than one of these categories. Pay attention to the specified time period. The report focuses on evidence reported during the 2022 to 2024 period, but outcomes and impacts often developed over much longer periods. Consider the overall weight of the evidence, not individual pieces of evidence. This report presents a body of evidence, drawing on a variety of different epistemological approaches: outcome evidence, impact evaluations, and other types of information, which collectively provide different insights into CGIARs impact. However , only impact evaluations were assessed for the number of best research practices they used, with a composite score of 0 to 9 assigned based on the number of key components of rigor addressed by the study. While weighted equally in this work, these components do not all have equal implications for overall study\n\n---\n\n[ID: pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1\nFile: Food Frontiers and Security_Inception Report 30-06-2025.pdf\nLocation: page 1 part 2\nContent: Report Food Frontiers and Security Science Program Inception Report\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt1]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 12 part 1\nContent: All impact study submissions were reviewed for potential inclusion into the evidence base of the report. The two primary inclusion considerations were relevance and rigor (see Annex A. Selection of evidence). Studies were determined to be relevant if they considered the outcomes and impacts of CGIAR-supported interventions, regardless of the authorship of the study. Outcomes reported into the CGIAR PRMS are quality assessed for relevance (that is, CGIAR’s role in the outcome is validated); therefore, none of these reported outcomes were excluded on the basis of relevance. Studies with unclear or misleading methods were excluded on the basis of rigor. Studies meeting this threshold of clarity were then classed as “impact assessments” or “impact evaluations.” Impact evaluations were the primary study designs of interest. Impact evaluations are studies that use statistical methods (experimental or quasi-experimental) to quantify the causal change in a condition that was achieved by an intervention. Studies using other study designs were included under the umbrella term of impact assessments (including impact evaluations), if they provided information relevant to understanding impacts, such as cost- benefit analyses, reviews of CGIAR work, and measures of the adoption of CGIAR technology. These included the country studies supported by CGIAR’s SPIA. While impact evaluations are necessary to establish causal change linking intervention and impact, they can be limited in scope due to practical constraints, such as resources and measurement challenges. Other types of impact assessments can provide valuable insights into CGIAR’s contributions to real-world change in a wider spatial or temporal context; however , they do c This can be common for power calculations. Authors may have conducted power calculations but not r eported that they did so in-text. Assessment is based on what is reported in-text, not what may have been done but not reported. d See Annex A. Included studies and rigor of\n\n---\n\n[ID: pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_Inception Report 30-06-2025.pdf\nLocation: page 17 part 3\nContent: underpin the work being done and provide the solid positioning for holding the CA. This collaboration means the work being done relies on the most capable parts of both the CGIAR and the relevant partner and that this collaboration changes over time. A part of the Program’s objectives\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt2]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 12 part 2\nContent: challenges. Other types of impact assessments can provide valuable insights into CGIAR’s contributions to real-world change in a wider spatial or temporal context; however , they do c This can be common for power calculations. Authors may have conducted power calculations but not r eported that they did so in-text. Assessment is based on what is reported in-text, not what may have been done but not reported. d See Annex A. Included studies and rigor of evidence for details. Criteria related to random sampling and treatment assignment; reporting of power calculation and sensitivity analysis; consideration of attrition, spillovers, and heterogenous treatment effects; and sample representativeness and baseline balance. not establish causality. Impact evaluations were further appraised to determine the number of best practices followed per study. A composite score45 was calculated to reflect the level of confidence in the findings of a study and to help understand the application of best practices in CGIAR impact evaluation. Nine best practices were identified (see Annex A. Included studies and rigor of evidence), resulting in the composite best- practice score ranging from 0 to 9. Not all the criteria were relevant to all studies, and some studies may have met criteria but did not clearly describe them in the publication.c Studies following three or more best practices were featured preferentially in this report (assuming equality in relevance). Details of the method and analysis of the scores are in Annex A. Included studies and rigor of evidence. Included impact studies Approximately 500 studies were reviewed for eligibility and 125 studies were included in the primary dataset. Of these, 62 were impact evaluations and 63 were impact assessments which did not attempt to establish the causal effect of an intervention on an impact. Randomized controlled trials (RCT) were the most common impact evaluation design (n = 21), followed by\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p4pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 4 part 1\nContent: Integration with other outputs The Portfolio Narrative informs the 2024 CGIAR Annual Report – a comprehensive summary of the organization’s collective achievements, impacts, and strategic outlook. Elements of the Type 2 report were integrated into the CGIAR Flagship Report released in April 2025 during the CGIAR Science Week. The Flagship Report synthesizes CGIAR research in an accessible format designed specifically to provide policy- and decisionmakers at national, regional, and global levels with the evidence they require to formulate, develop, and negotiate evidence-based policies and investments. The diagram below illustrates these relationships, emphasizing the interconnectedness of the Type 3 Report with other reporting products. CGIAR Results Dashboard Portfolio Narrative report CGIAR Annual report Type 1 Initiative, Impact Platform, and Science Group Project reports Type 2 CGIAR Contributions to Impact in Agrifood Systems: evidence and learnings from 2022 to 2024 Flagship report Type 3 Portfolio Practice Change report 2024 Technical Reporting Figure 1. CGIAR’s 2024 Technical Reporting components and their integration with other CGIAR reporting products. Section 1: Introduction 1 Under the CGIAR Technical Reporting Arrangement for the next Portfolio (2025-30), relevant aspects of the Type 3 Report will be included in the annual Portfolio Narrative, and a separate Type 3 Report will no longer be produced. The 2024 CGIAR Portfolio Practice Change\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt4]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 48 part 4\nContent: against CGIAR’s Results Framework is that, apart from the SPIA country studies, other internal and external studies are designed in an uncoordinated bottom-up way. Because such studies are undertaken to meet specific information needs, opportunities to learn through synthesis or aggregation are missed due to the differences in indicators used and measurement approaches employed. For example, impact assessments are rarely connected with data on innovation use, preventing case study results from being used to extrapolate possible large-scale effects. Thus, moving forward, two areas for improvement are: (1) to collectively undertake strategic impact assessments that will answer high-priority impact assessment questions and (2) to develop and enforce the use of a core set of common indicators and measurement methodsq that should be used in impact assessment studies regardless of who initiates them. In addition, during the 2022 to 2024 period, Initiatives defined targets for outcomes and made commitments to measuring and reporting on those outcomes. They did not have a similar plan or commitment to measuring impacts. As CGIAR evolves to longer-term programs covering the whole of CGIAR, there should be commitments to the consistent measurement of impacts. However , this has been an ongoing challenge within the organization, with similar recommendations from a review of the 2017 to 2021 portfolio.176 Rigor of the evidence All impact evaluations identified were assessed for their rigor based on criteria established by Rao 2025.45 The most common score was a 4 of 9 key elements being present, suggesting moderate overall quality and room for improvement. A high number of impact evaluations used rigorous methods to infer causality between a CGIAR innovation and impacts (see Annex A. Included studies and rigor of evidence). However , many failed to consider heterogeneous treatment effects or report power calculations. Most of the impact evaluations used experimental or quasi-experimental designs with two or more measurement periods. However , a sizeable group of the studies were based on cross-sectional (single measurement) studies. While they are peer-reviewed and employ recommended methods of controlling for unobservable variables to enhance the likelihood of a causal inference, there remain limitations to such designs. In addition to rigor , this study paid attention to the relevance of the studies. Often, studies employing less rigorous, cross-sectional methodologies were able to provide evidence more relevant to policymaking and decision-making Tradititional rice variety in Ilagan, Isabela, the Philippines. Photo credit: Miguel Mamon/CIAT CGIAR Impacts in Agrifood Systems: | Learnings | Page 90 of 130 CGIAR CGIAR CGIAR Impacts in Agrifood Systems: | Learnings| Page 91 of 130\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 31 part 4\nContent: four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the \"challenges and megatrends\" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p6pt1]\nLink: https://cgspace.cgiar.org/items/04bd63a9-1b58-4eb5-84f2-b54c8bde226e\nFile: Portfolio Narrative_2024.pdf\nLocation: page 6 part 1\nContent: Integration with other outputs The Portfolio Narrative informs the 2024 CGIAR Annual Report – a comprehensive summary of the organization’s collective achievements, impacts, and strategic outlook. Elements of the Type 2 report fed into the CGIAR Flagship Report, released in April 2025 at CGIAR Science Week. The Flagship Report\n\n---\n\n[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 3\nContent: activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt3]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 46 part 3\nContent: to ensure common terminology across the reporting units. At the impact level, there were 19 indicators across the five Impact Areas. The frequency of reporting against exact indicators is very low (18 percent of indicators assessed match those in the Results Framework; Annex B. Impact indicators). In addition, there is an imbalance across Impact Areas and indicators in the frequency with which 2022 to 2024 studies attempt to measure those indicators. There were many impact assessments that measured yields or income related to the poverty indicators, and relatively few that looked at environmental, climate, or gender indicators. This is consistent with what Templeton (2023)176 found in her review of evidence used to support the impact claims made by the CGIAR Research Programs between 2017 and 2021. Thus, there remains a huge challenge to define feasible indicators for"}]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -501,6 +703,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -535,16 +744,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -837,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -880,7 +1095,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -892,16 +1107,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -909,7 +1124,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -921,16 +1136,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -938,7 +1153,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -950,16 +1165,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -967,7 +1182,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -979,16 +1194,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -996,7 +1211,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1008,16 +1223,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I6" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1025,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1037,16 +1252,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1054,7 +1269,7 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1066,16 +1281,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1083,7 +1298,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1095,16 +1310,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H9" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="I9" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1112,7 +1327,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -1124,16 +1339,16 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H10" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1141,7 +1356,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1153,16 +1368,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1170,7 +1385,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -1182,16 +1397,16 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1199,7 +1414,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -1211,16 +1426,16 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I13" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1228,7 +1443,7 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -1240,16 +1455,16 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I14" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1257,7 +1472,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -1269,16 +1484,16 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G15" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1286,7 +1501,7 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -1298,16 +1513,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G16" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H16" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I16" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1315,7 +1530,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -1327,16 +1542,16 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H17" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1344,7 +1559,7 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -1356,16 +1571,16 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H18" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="I18" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1373,7 +1588,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1385,16 +1600,16 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="I19" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1402,7 +1617,7 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -1414,16 +1629,16 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G20" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H20" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I20" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1431,7 +1646,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -1443,22 +1658,22 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G21" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H21" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I21" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J21" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="K21" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1466,7 +1681,7 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -1478,22 +1693,22 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G22" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H22" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I22" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J22" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="K22" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1501,7 +1716,7 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -1513,22 +1728,22 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G23" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H23" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I23" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J23" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="K23" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1536,7 +1751,7 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -1548,22 +1763,22 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G24" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="H24" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I24" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J24" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="K24" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1571,7 +1786,7 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -1583,22 +1798,22 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G25" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="H25" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I25" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J25" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="K25" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1606,7 +1821,7 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -1618,22 +1833,22 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G26" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H26" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="J26" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="K26" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1641,7 +1856,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -1653,22 +1868,22 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G27" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H27" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="J27" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="K27" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1676,7 +1891,7 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -1688,22 +1903,22 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G28" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H28" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="J28" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="K28" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1711,7 +1926,7 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -1723,22 +1938,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G29" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H29" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="J29" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="K29" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1746,7 +1961,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -1758,22 +1973,22 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G30" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="H30" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I30" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="K30" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1781,37 +1996,290 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31">
+        <v>100</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I31" t="s">
+        <v>97</v>
+      </c>
+      <c r="J31" t="s">
+        <v>103</v>
+      </c>
+      <c r="K31" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32">
+        <v>100</v>
+      </c>
+      <c r="D32">
+        <v>100</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I32" t="s">
+        <v>98</v>
+      </c>
+      <c r="J32" t="s">
+        <v>104</v>
+      </c>
+      <c r="K32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33">
+        <v>100</v>
+      </c>
+      <c r="D33">
+        <v>100</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" t="s">
+        <v>65</v>
+      </c>
+      <c r="H33" t="s">
+        <v>89</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" t="s">
+        <v>104</v>
+      </c>
+      <c r="K33" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34">
+        <v>100</v>
+      </c>
+      <c r="D34">
+        <v>100</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" t="s">
+        <v>65</v>
+      </c>
+      <c r="H34" t="s">
+        <v>90</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J34" t="s">
+        <v>104</v>
+      </c>
+      <c r="K34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
         <v>44</v>
       </c>
-      <c r="C31">
-        <v>100</v>
-      </c>
-      <c r="D31">
-        <v>100</v>
-      </c>
-      <c r="E31" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35">
+        <v>100</v>
+      </c>
+      <c r="D35">
+        <v>100</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" t="s">
+        <v>90</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J35" t="s">
+        <v>104</v>
+      </c>
+      <c r="K35" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
         <v>45</v>
       </c>
-      <c r="G31" t="s">
-        <v>56</v>
-      </c>
-      <c r="H31" t="s">
-        <v>78</v>
-      </c>
-      <c r="I31" t="s">
-        <v>82</v>
-      </c>
-      <c r="J31" t="s">
-        <v>85</v>
-      </c>
-      <c r="K31" t="s">
-        <v>88</v>
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36">
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <v>100</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" t="s">
+        <v>65</v>
+      </c>
+      <c r="H36" t="s">
+        <v>91</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J36" t="s">
+        <v>104</v>
+      </c>
+      <c r="K36" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37">
+        <v>100</v>
+      </c>
+      <c r="D37">
+        <v>100</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" t="s">
+        <v>65</v>
+      </c>
+      <c r="H37" t="s">
+        <v>92</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J37" t="s">
+        <v>104</v>
+      </c>
+      <c r="K37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38">
+        <v>100</v>
+      </c>
+      <c r="D38">
+        <v>100</v>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G38" t="s">
+        <v>65</v>
+      </c>
+      <c r="H38" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J38" t="s">
+        <v>104</v>
+      </c>
+      <c r="K38" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I33" r:id="rId1"/>
+    <hyperlink ref="I34" r:id="rId2"/>
+    <hyperlink ref="I35" r:id="rId3"/>
+    <hyperlink ref="I36" r:id="rId4"/>
+    <hyperlink ref="I37" r:id="rId5"/>
+    <hyperlink ref="I38" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Logs/interaction_log.xlsx
+++ b/Logs/interaction_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="123">
   <si>
     <t>timestamp</t>
   </si>
@@ -160,6 +160,21 @@
     <t>2025-09-19T14:41:22.557021</t>
   </si>
   <si>
+    <t>2025-09-19T15:45:45.428812</t>
+  </si>
+  <si>
+    <t>2025-09-19T15:48:16.253621</t>
+  </si>
+  <si>
+    <t>2025-09-19T15:50:58.980303</t>
+  </si>
+  <si>
+    <t>2025-09-19T15:57:36.879063</t>
+  </si>
+  <si>
+    <t>2025-09-19T15:59:13.835247</t>
+  </si>
+  <si>
     <t>What funding did 2024 Technical Reporting cover?</t>
   </si>
   <si>
@@ -173,6 +188,9 @@
   </si>
   <si>
     <t xml:space="preserve"> What evidence architecture and rigor standards underpin the report’s claims? </t>
+  </si>
+  <si>
+    <t>What is the 2025–30 Impact Assessment (IA) strategy addressing, and what will be delivered to funders and managers?</t>
   </si>
   <si>
     <t xml:space="preserve">You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:
@@ -217,6 +235,9 @@
   </si>
   <si>
     <t>pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1:0.176, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3:0.132, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2:0.127, pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt1:0.125, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt3:0.119, pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt2:0.119, pdf:Type3_2024Report.pdf:p4pt1:0.119, pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt4:0.117, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4:0.109, pdf:Portfolio Narrative_2024.pdf:p6pt1:0.106, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.106, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt3:0.104, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt1:0.102, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p22pt3:0.102, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p1pt1:0.102, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p24pt3:0.101, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p29pt2:0.099, docx:Submitting evidence.docx:u1-4:0.099, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt4:0.098, pdf:CGIAR_ImpactReport_2022-24.pdf:p66pt2:0.097, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4:0.096, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt2:0.095, pdf:CGIAR_ImpactReport_2022-24.pdf:p66pt4:0.095, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p17pt2:0.095, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p1pt1:0.095, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p28pt3:0.093, pdf:CGI21_508012_PORB_Genebanks.pdf:p44pt1:0.092, pdf:CGI21_508012_PORB_Genebanks.pdf:p29pt1:0.092, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p8pt4:0.092, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt1:0.092, pdf:CGI21_508012_PORB_Genebanks.pdf:p47pt1:0.092, pdf:CGI21_508012_PORB_Genebanks.pdf:p35pt1:0.091, pdf:CGI21_508012_PORB_Genebanks.pdf:p38pt1:0.091, pdf:Climate Action_Inception Report 30-06-2025.pdf:p26pt3:0.091, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p4pt4:0.090, pdf:Type3_2024Report.pdf:p4pt2:0.090, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt2:0.090, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt3:0.090, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p16pt1:0.089, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p1pt2:0.089, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p27pt3:0.089, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p9pt2:0.089, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.088, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p17pt1:0.088, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p6pt3:0.088, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p17pt2:0.088, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.087, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt4:0.087, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p1pt1:0.087, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p19pt3:0.087, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p9pt1:0.087, pptx:Information Session on 2025 Technical Reporting.pptx:s5pt1:0.087, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt4:0.087, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p12pt4:0.086, pdf:CGI21_508012_PORB_Genebanks.pdf:p23pt1:0.085, docx:Guidance on ensuring quality over quantity.docx:u4-7:0.084, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt3:0.084, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p30pt1:0.084, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p6pt4:0.084, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.083, pdf:CGI21_508012_PORB_Genebanks.pdf:p5pt3:0.083, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p19pt2:0.082, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.082, pdf:CGIAR_ImpactReport_2022-24.pdf:p1pt3:0.082, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt3:0.082, pdf:CGIAR_ImpactReport_2022-24.pdf:p8pt3:0.080, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p1pt1:0.080, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p4pt1:0.080, pdf:CGI21_508012_PORB_Genebanks.pdf:p26pt1:0.080, pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3:0.080, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p25pt1:0.079, pdf:CGIAR_ImpactReport_2022-24.pdf:p8pt4:0.078, pdf:Climate Action_Inception Report 30-06-2025.pdf:p12pt1:0.078, pdf:Genebanks_Inception Report 30-06-2025.pdf:p1pt1:0.078, pdf:CGI21_508012_PORB_Genebanks.pdf:p32pt1:0.078, pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt3:0.078, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p4pt4:0.078, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p28pt2:0.077, pdf:Climate Action_Inception Report 30-06-2025.pdf:p7pt3:0.077, pdf:Portfolio Narrative_2024.pdf:p6pt2:0.077, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p29pt1:0.077, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p15pt4:0.077, pdf:Genebanks_Inception Report 30-06-2025.pdf:p21pt2:0.077, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p32pt2:0.076, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p15pt2:0.076, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p30pt2:0.076, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt2:0.076, pdf:Portfolio Narrative_2024.pdf:p6pt4:0.075, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p1pt1:0.075, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p13pt3:0.075, pdf:Type3_2024Report.pdf:p1pt1:0.075, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.075, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p9pt3:0.074, pdf:CGI21_508012_PORB_Genebanks.pdf:p40pt4:0.074, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p1pt2:0.074, pdf:Climate Action_Inception Report 30-06-2025.pdf:p5pt2:0.074, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p15pt3:0.073, pdf:Portfolio Narrative_2024.pdf:p5pt3:0.072, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt3:0.072, pdf:CGI21_508012_PORB_Genebanks.pdf:p49pt4:0.072</t>
+  </si>
+  <si>
+    <t>docx:Engagement Plan 2025 Technical Reporting.docx:u46-49:0.248, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4:0.241, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1:0.233, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4:0.225, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt3:0.220, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p10pt1:0.215, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p2pt3:0.215, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1:0.213, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p25pt1:0.205, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.203, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p2pt2:0.195, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt3:0.194, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p14pt1:0.192, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt2:0.191, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p12pt3:0.190, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt2:0.189, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p2pt2:0.188, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p2pt2:0.185, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p1pt3:0.183, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p1pt2:0.183, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt3:0.183, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p13pt3:0.183, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p1pt2:0.182, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p1pt2:0.182, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p1pt2:0.182, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p1pt2:0.182, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p1pt2:0.182, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p1pt2:0.182, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p29pt4:0.182, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p10pt4:0.182, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt4:0.180, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt2:0.179, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p8pt2:0.179, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p19pt4:0.178, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p2pt4:0.177, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt2:0.177, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p50pt3:0.177, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.176, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25pt3:0.176, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt3:0.175, pptx:Information Session on 2025 Technical Reporting.pptx:s3pt1:0.175, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt1:0.174, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.173, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p2pt3:0.171, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p12pt4:0.171, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.170, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt3:0.169, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p2pt2:0.167, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p2pt3:0.165, pdf:CGIAR_ImpactReport_2022-24.pdf:p9pt1:0.164, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p16pt3:0.164, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p27pt3:0.162, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.162, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p25pt1:0.161, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p1pt2:0.160, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt3:0.160, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p2pt3:0.158, pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3:0.157, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p35pt1:0.157, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt2:0.156, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18pt1:0.156, pdf:Type3_2024Report.pdf:p6pt2:0.156, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.155, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.154, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt1:0.154, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt4:0.153, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p34pt4:0.153, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt4:0.152, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p10pt1:0.151, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p46pt3:0.151, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p10pt2:0.150, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p16pt3:0.150, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p22pt4:0.149, pdf:Climate Action_Inception Report 30-06-2025.pdf:p16pt3:0.149, pdf:Type3_2024Report.pdf:p11pt1:0.148, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt1:0.148, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p9pt1:0.147, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p10pt4:0.147, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.147, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt2:0.147, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p20pt4:0.147, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p6pt3:0.146, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p25pt2:0.146, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt3:0.146, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p17pt3:0.146, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.146, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p15pt2:0.146, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p16pt2:0.145, docx:2025 Technical Reporting Information (Session 2).docx:u4-7:0.145, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p15pt1:0.144, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p22pt4:0.144, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p15pt2:0.144, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt4:0.144, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p14pt2:0.143, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p22pt3:0.143, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p14pt4:0.143, pptx:Information Session on 2025 Technical Reporting.pptx:s15pt3:0.143, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1pt1:0.142, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4:0.141, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p2pt2:0.141</t>
   </si>
   <si>
     <t>I cannot find information in the provided chunks to answer this.  
@@ -431,6 +452,22 @@
 CGIAR_ImpactReport_2022-24.pdf — page 46 part 3 — pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt3</t>
   </si>
   <si>
+    <t>The 2025–30 Impact Assessment (IA) strategy focuses on evaluating the causal effects of research outputs and related activities, aiming to measure the magnitude of impact achieved across various interventions. It emphasizes a bottom-up approach to ensure that the assessments provide sufficient evidence against CGIAR impact indicators. Deliverables to funders and managers will include comprehensive reports on the findings from these assessments, which will be accessible to program managers, researchers, and external stakeholders. This strategy aims to enhance the coherence and quality of information sourced from different funding avenues over time. 
+Sources:
+File — Location — Cited IDs
+pdf:Genebanks_MELIA Plan 30-06-2025.pdf — page 8 part 4 — [ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4]
+pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 17 part 1 — [ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1]
+pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf — page 18 part 3 — [ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt3]</t>
+  </si>
+  <si>
+    <t>The 2025–30 Impact Assessment (IA) strategy focuses on evaluating the causal effects of research outputs and related activities, aiming to measure the magnitude of impact achieved across various interventions. It emphasizes a bottom-up approach to ensure that the assessments provide sufficient evidence against CGIAR impact indicators. Deliverables to funders and managers will include comprehensive reports on the impact assessments, which will be informed by both quantitative and qualitative data, and will help in making necessary adjustments to program implementations based on the findings. This strategy is designed to enhance the coherence and quality of information sourced from different funding avenues over time. 
+Sources:
+File — Location — Cited IDs
+pdf:Genebanks_MELIA Plan 30-06-2025.pdf — page 8 part 4 — 4
+pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 17 part 1 — 6
+pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf — page 18 part 3 — 4</t>
+  </si>
+  <si>
     <t>Information Session on 2025 Technical Reporting.pptx — slide 9 — pptx:Information Session on 2025 Technical Reporting.pptx:s9, Engagement Plan 2025 Technical Reporting.docx — paragraph 2 — docx:Engagement Plan 2025 Technical Reporting.docx:p2, Information Session on 2025 Technical Reporting.pptx — slide 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s2, Guidance on reporting outputs or outcomes.docx — paragraph 22 — docx:Guidance on reporting outputs or outcomes.docx:p22, Engagement Plan 2025 Technical Reporting.docx — section 'Technical Reporting questions' — docx:Engagement Plan 2025 Technical Reporting.docx:p59, CGIAR_ImpactReport_2022-24.pdf — page 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p1, Engagement Plan 2025 Technical Reporting.docx — section 'A single location for all documents and resources' — docx:Engagement Plan 2025 Technical Reporting.docx:p31, Engagement Plan 2025 Technical Reporting.pptx — slide 1 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s1, CGSpace.docx — section 'CGSpace' — docx:CGSpace.docx:p3, CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 5 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5</t>
   </si>
   <si>
@@ -450,6 +487,9 @@
   </si>
   <si>
     <t>https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9 — page 67 part 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1, https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9 — page 7 part 3 — pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1 — page 1 part 2 — pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2</t>
+  </si>
+  <si>
+    <t>Engagement Plan: 2025 Technical Reporting (Full Word document) — section 'Fortnightly update emails' paragraph 80 to section 'Fortnightly update emails' paragraph 83 — docx:Engagement Plan 2025 Technical Reporting.docx:u46-49, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1 — page 29 part 4 — pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4, https://docs.google.com/presentation/d/1iH7kEQrUqQywkG9wVkCCBq_tRp-d1Ws0/edit?slide=id.p1#slide=id.p1 — slide 2 part 1 — pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1</t>
   </si>
   <si>
     <t>[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]
@@ -666,6 +706,148 @@
 with other CGIAR reporting products. Section 1: Introduction 1 Un</t>
   </si>
   <si>
+    <t>[ID: docx:Engagement Plan 2025 Technical Reporting.docx:u46-49]
+CGSpace Team Lead KM Managers Curators/Repository Managers PRMS Team
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4]
+The current funding landscape uncertainty as well as a realistic assessment of resources that can be dedicated to IA led us to prioritize IA activities in 6 countries, where we can easily leverage on human and financial resources for impact assessment: Colombia, Peru, Tunisia, Kenya, India, Vietnam. The site prioritization, as well as prioritization of the key impact indicators that the IA should target (potential indicators are presented in the table below), will be a specific action of the MELIA team at the end of 2025, when future financial capacity will be clearer. Further funding for IA studies will be sought in 2026 and during the implementation of
+---
+[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1]
+Agenda Technical Reporting Arrangement 2025-30 Technical reporting priorities for 2025 What
+---
+[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4]
+exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved. Impact assessments are conducted after an intervention has been completed and are used to substantiate claims of sustained results. They seek to measure impact at scale, i.e., benefits to a large number of people/large areas of land. It employs both quantitative and qualitative methods, often combined for deeper insights. IA goes beyond monitoring indicators to evidenced attribution of observed changes to CGIAR interventions. IA will help to ensure that Programs/Accelerators contribute meaningfully to CGIAR’s Results Framework and the 2025–30 Portfolio objectives.
+---
+[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt3]
+the learnings and what are other critical areas that require further focused support? (AoW 5) Evaluation collaboration plans Genebanks will seek to collaborate with the Multifunctional Landscapes Program to study in situ and on farm site monitoring of diversity conservation. Genebanks will also collaborate with the Crop Trust and Aarhus University to review the Scientific Impact of the Seed Quality Management and Quality Management System Communities of Practice. Collaborations with W3/bilateral projects will be explored during phase 2 of the mapping exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved.
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p10pt1]
+CGIAR Technical Reporting Arrangement 2025-30 June 2025 10 Thematic Impact 2022-30 Report The Thematic Impact 2022 -30 Report provides a m acro level view of CGIAR’s role in Food, Land and Water System Transformation covering the period 2022 -30. It will be released in 2031. Its format and content will be developed during the period 2025-30. Results Dashboard • The Results Dashboard will be enhanced to better present curated information a gainst Impact Area targets, geographies and key topics. • Headline impacts and outcomes will be more clearly communicated in the Dashboard. • Using AI, users will be able to easily query the results data and underlying sources of evidence data using
+---
+[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p2pt3]
+Impact assessment (IA) .............................................................................................................. 13 Program impact overview .................................................................................................................... 13 IA activities and collaboration plans ..................................................................................................... 14 IA studies ........................................................................................................................................... 15 5. Learning and adaptive management ........................................................................................... 16 Learning ............................................................................................................................................. 16 Annual review and adaptive planning ...................................................................................................
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1]
+CGIAR Technical Reporting Arrangement 2025-30 June 2025 17 The amount of quality information sourced from different funding sources, and the coherence between those different information sources will increase over time (specific metrics and targets to be developed) 6. Impact Assessment Strategy/ Approach/ Case studies CGIAR will develop a 2025 -30 Impact Assessment Plan and integrate its design, budgeting and delivery into the 25-30 Portfolio. The bottom-up approach to impact assessment that has been used within CGIAR for the past decades has not produced sufficient quantity or quality of studies to prov ide evidence against CGIAR impact indicators. SPIA fills in some of this gap, but even their new undertaking of country studies will likely not be able to contribute to most of the indicators
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p25pt1]
+• Bilateral/W3-funded projects: to identify embedded impact assessment opportunities and avoid duplication. • CGIAR IA teams : to contribute to portfolio -level meta -evaluation and harmonize data with common CGIAR indicators. Priority will be given to impact in integrative countries, where multiple AoWs operate. These broader IA studies will assess the synergies between interventions and provide system -level insights into the pathways driving impact. Potential integrative countries include Bangladesh, Ethiopia, Nigeria, and Tanzania, based on portfolio density and MELIA feasibility. A senior Impact Specialist will guide study design and implementation, ensure alignment with the CGIAR results framework indicators, and coordinate data quality assurance across IA efforts. Impact assessment studies The Program has identified initial IA study themes for inclusion in the MELIA studies. However , these initial themes are not included in the
+---
+[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]
+activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable
+---
+[ID: pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p2pt2]
+................................ ................................ ............... 7 Data collection strategy ................................ ................................ ................................ 7 3. Evaluation plan ................................ ................................ ................................ ..................... 7 Evaluation studies ................................ ................................ ................................ ....... 7 Evaluation collaboration plans ................................ ................................ ....................... 8 4. Impact assessment ................................ ................................ ................................ ............... 8 Program/Accelerator impact overview ................................ ................................ ............ 8 IA activities and collaboration
+---
+[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt3]
+All the knowledge generated by these studies will be available not only to Program managers, but also researchers, the CGIAR community, and external stakeholders. Finally, analyzing monitoring data will be a continuous process, and results, along with recommendations, will be made available to Program managers to make any necessary adjustments to the Program implementation. Annual review and adaptive planning The Climate Action Program will implement an annual review and adaptive planning process, building on the experience and lessons from the 2022–24 CGIAR Portfolio and aligned with evolving guidance on the Reﬂect and Re-Plan processes. Each year, the Program will conduct structured annual performance reviews at both program-wide and AoW levels. These reviews will assess progress toward the intended outputs and outcomes, using both quantitative and qualitative data drawn from the CGIAR Performance and Results Management System
+---
+[ID: pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p14pt1]
+14 5. Impact assessment Impact Assessment (IA) is a key approach for evaluating the effectiveness and impact of innovations, technologies, or practices on target populations and geographies. By systematically measuring outcomes and impacts, IA will help to ensure that Programs/Accelerators contribute meaningfully to CGIAR’s Results Framework and the 2025–30 Portfolio objectives. IA goes beyond monitoring indicators, requiring a rigorous approach to attribut ing observed changes to CGIAR interventions (e.g., innovations, policies). It employs both quantitative and qualitative methods, often combined for deeper insights. Program/Accelerator impact overview The AoWs of the Sustainable Framing Program will collectively contribute to the program’s outcomes and expected impacts by co -developing and delivering whole -farm innovation bundles to at least five million farmers, with positive impacts on socially equitable and sustainable agronomic gain across two million ha of land. At least 50 public and private development partners are expected to facilitate the scaling of solutions to farming communities and integrating innovations in their investments.
+---
+[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s2pt2]
+2025 What Annual Technical Reports Performance and Reporting Management System (PRMS)
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p12pt3]
+the Policy Program is no exception. Recurring assumptions in the ToC revolve around empowering actors and creating improved knowledge and building capacity to empower these actors. This theme is at the heart of the P olicy Program's operations, encompassing concepts such as co -creation and demand-driven research that build capacity and create the right conditions for policy change to occur. IA activities and collaboration plans The Impact Assessment (IA) strategy employs a combination of quantitative (both experimental and non-experimental) and qualitative (outcome evidencing) research methods to substantiate the Program's contributions to CGIAR's Impact Areas. Additionally, rapid impact assessment methods are utilized when necessary to track achievements and support swift policy responses. Aligned with the learning objectives of the Monitoring, Evaluation, and Learning (MEL) component, the IA strategy provides empirical evidence on the Program's effects, aiming to understand the causal mechanisms underlying both expected and unanticipated outcomes. Each of the 2030
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt2]
+into Megaprograms is still lacking. Bilateral funding is restricted and is provided for a specific purpose and with specific intended impacts. This needs to be honored a nd the lack of flexibility in shifting those funds into other areas should be clearly acknowledged. • Alignment of the entire Portfolio with the CGIAR 2030 Research and Innovation Strategy needs to be strong and explicit. How will management ensure that bilateral funding delivers against this Strategy? In addition: o What happens if a bilateral project is not strongly aligned with the Strategy and how will CGIAR ensure that opportunity costs are covered? o Will all bilateral projects
+---
+[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p2pt2]
+Monitoring plan for HLOs and outcomes ........................................................................................ 7 Data collection strategy ...................................................................................................... 7 3. Evaluation plan ................................................................................................................................ 8 Evaluation studies .............................................................................................................. 8 Evaluation collaboration plans ............................................................................................ 8 4. Impact assessment .......................................................................................................................... 8 Program/Accelerator impact overview ................................................................................. 9 IA activities
+---
+[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p2pt2]
+for high-level outputs (HLOs) and outcomes ........................................................ 7 Data collection strategy ........................................................................................................................ 7 3. Evaluation plan ........................................................................................................................... 9 Evaluation studies .............................................................................................................................. 10 Evaluation collaboration plans ............................................................................................................ 12 4. Impact assessment (IA) .............................................................................................................. 13 Program impact overview ....................................................................................................................
+---
+[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p1pt3]
+and Impact Assessment (MELIA)
+---
+[ID: pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p1pt2]
+and Impact Assessment (MELIA)
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt3]
+section): • Under what conditions and through which mechanisms agroecological and nature positive approaches, within a multifunctional landscape lens, optimize landscape multifunctionality? • What are the behavioral outcomes of such a multifunctional landscapes approach? For whom? Under what conditions? The following MELIA studies will allow us to answer these questions through multiple analysis angles. System Based Theory of Change: in order to analyze how the changes at the landscape level influenced by the Program will generate changes at the country level and be influenced by changes at the country level, we will implement System Based Theory of Change methodology developed by Worldfish (see references in the Evidence Base section under Impact Assessment). We will engage relevant landscape stakeholders in pilot landscapes (e.g. Peru, Kenya,
+---
+[ID: pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p13pt3]
+is built on the assumption that shifting harmful gender norms and unequal power dynamics is foundational to achieving sustained, system -level transformation in FLWS. Detailed assumptions can be found in the (please refer to the Results Framework attachment ). Strong relationships with Science Programs such as Breeding for Tomorrow, Climate Action, Food Frontiers and Security, Better Diets for Nutrition, and Scaling for Impact, ensuring gender-focused research is integrated across CGIAR’s Portfolio. IA activities and collaboration plans The Gender Accelerator’s approach to impact assessment (IA) relies on the premise that research questions should drive the methodological approach and depending on the decisions that need to be informed, the appropriate type of evidence must be generated. Based on this, the IA activities of the Accelerator use both causal and non -causal impact assessments — recognizing that only causal
+---
+[ID: pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p1pt2]
+Learning and Impact Assessment
+---
+[ID: pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p1pt2]
+Learning and Impact Assessment
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p1pt2]
+Learning and Impact Assessment
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p1pt2]
+Learning and Impact Assessment
+---
+[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p1pt2]
+Learning and Impact Assessment
+---
+[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p1pt2]
+Learning and Impact Assessment
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p29pt4]
+on ground results, and if not, why not (AOW2 AB)? RQ14 What additional impact could be achieved with additional investment? (AOW1 MI) RQ15 What is the trajectory of genetic gain for each crop, and what benefits could this mean for smallholder farmers who adopt improved products? (AOW4 BR) RQ16 When is the scale of adoption for recently released varieties and products in the pipeline expected to be sufficient to reduce weighted average variety age (WAVA) in targeted market segments to 10 years or less? (AOW3 ID) Demonstrate impacts achieved by B4T and encourage ongoing investment Identify opportunities to improve uptake and adoption, to maximize impact Guide future target
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p10pt4]
+of environmental conditions controlled and high heritability of targeted traits. Quality of science is required for Research questions will contribute to KEQ2 on effectiveness: To what extent has B4T and its AOW effectively achieved the intended The first part of RQ15 What is the trajectory of genetic gain for each crop, is relevant here. RQ21 To what extent have market set targets been successfully converted into breeding targets? (AOW2 AB) 1 It would be ideal to question if the level of benefit gained from adoption of improved varieties was sufficient for empowerme nt. However, determining the sufficiency of benefit is likely to be unfeasible in the timeframe and resourcing available. Opportun ities to incorporate data collection at this depth of enquiry should be keep in mind.
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt4]
+and duplicative layer of complex reporting requirements for W3/ bilaterally funded work. - Informs decision making through providing ready access to demand-driven quality raw and curated data products. Delivery The TRA 25 -30 will be delivered in line with Management arrangements for CGIAR’s 2025 —30 science and innovation Portfolio. Specific roles and responsibilities will be defined in 2025. 1 CGIAR Portfolio Narrative, 1 November 2024
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt2]
+Reports are shared for integration, Centers will have a role in r eviewing and validating how their information is represented in aggregate Program/Accelerator and Portfolio reporting. 5. A set of Impact Studies responding to the CGIAR Results Framework and key strategic questions from Funders/Partners/Global Leadership will be integrated into the design and delivery of the Programs &amp; Accelerators; W3/bilaterals may contribute to these. 6. Funders and Centers will be able to adopt more/fully aligned monitoring and reporting approaches for their w3 and bilateral projects during development. It will also be possible to increase alignment during the implementation of a w3/bilateral project through e.g. the contribution to Impact Case Studies. 7. Common CGIAR best of class indicators, data collection protocols, tools, and systems will be promoted for use in W3/bilateral project design. The CGIAR Monitoring, Evaluation and Learning Community of
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p8pt2]
+results from other authoritative internal and external databases. The Results Dashboard will provide greater access to evidence of CGIAR’s contribution to impact based on quality-assured data. Triennial reports covering the periods 25-27 and 28-30 will consolidate Portfolio -level contribution to Impact targets. A Thematic Impact report will compile results delivered against the CGIAR Research and Innovation Strategy for the full period 2022-30. Technical Report product Content overview – All content will progressively integrate pooled and non-pooled content Periodicity Annual Program/ Accelerator Report - Annual
+---
+[ID: pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p19pt4]
+IFPRI Kenya Causal impact assessment Q4 2025 Q1 2027 Effectivenes s of STIBs; research question: what are the TBD in WCA, ESA, SA Causal impact assessment
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p2pt4]
+.................................................................. 27 7. Plan of Results and Budget ............................................................................................ 28 8. Cross-Portfolio linkages and geographic coordination .................................................... 30 8.1 Cross-portfolio linkages .......................................................................................... 30 8.2 Geographic coordination ......................................................................................... 30 9. Risk management .......................................................................................................... 31 10. Addressing feedback on select topics .......................................................................... 33 Appendix 1: Addressing specific feedback..........................................................................
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt2]
+outcomes and i mpacts of the whole portfolio through progressive alignment of reporting on w3/bilaterally funded components with a common framework. • Line of sight: The TRA is designed to meet the needs of diverse funders, ensuring transparency and accountability by linking investment to results, both for pooled and non-pooled funds. • Impact focus: Research results will be better linked to CGIAR’s 2030 targets using enhanced impact area indicators. Impact assessments will be integrated into Program/Accelerator design. The use of geographically-bounded targets will be explored for priority locations. A robust approach to project cross-Portfolio benefits by Impact Area for different funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified reporting: Overly complex requirements will be avoided, aiming to
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p50pt3]
+adaptive management and learning. Lessons are used to proactively reflect on and adapt the Theory of Change. Impact assessment strategy outlined. The MELIA approach will be managed by dedicated full-time officers and monitored regularly. Data collection is aligned with the key elements of the Theory of Change, which could be improved with better monitoring for other unintended outcomes, political instability, urban framing, displacement and the integration of generative AI tools for monitoring. One problem is that it is not clear at what stage various people will become involved in the process, and those who are supposed to benefit will be associated. An early assessment should be whether the new varieties are appreciated by the target farmers or not. More information could be given regarding the feedback loops among the various Areas of Work. For example, How MARKET INTELLIGENCE, ACCELERATED BREEDING, INCLUSIVE DELIVERY and BREEDING RESOURCES are related to learning opportunities. A robust framework for MELIA has been
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2]
+has CGIAR-NARES prioritization of products encouraged targeted investment for breeding? (AOW2 AB) RQ9 To what extent has the amount and quality of active collaboration on products increased? (AOW5 E) RQ11 To what extent has B4T influenced more equitable access to improved varieties by marginalized groups? (AOW3 ID) RQ27 To what extent have interoperable tools and services
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25pt3]
+-30. The list is extracted from the Management Response Actions Tracker. Annex 5: Relevant materials • CGIAR Research and Innovation Strategy 2022-30 • Performance and Results Management Framework
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt3]
+promote agroecological transitions: https://reporting.cgiar.org/reports/result-details/17243 • Feed pellet mechanized production based on locally availably by product s: https://hdl.handle.net/10568/173132 • Capacity strengthening of advisory services: https://reporting.cgiar.org/reports/result- details/18088 IA studies The impact assessment strategy aims to gauge the outcomes of interventions in multifunctional landscapes at different levels, from farmers, to organizations, market systems, policies and global actors. This strategy also seeks a clear understanding of the mechanisms and reasons behind the impacts achieved under the main program assumption, as outlined in the MELIA plan. The current funding landscape uncertainty as well as a realistic assessment of resources that can be dedicated to IA led us to prioritize IA activities in 6
+---
+[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s3pt1]
+Technical Reporting Arrangement (TRA) 2025-30 Approved by the CGIAR Global Leadership Team on 5 June 2025, provides the operational basis to plan, monitor, learn, and report on the 2025-30 Portfolio. It is designed to progressively enable Programs and Accelerators, Centers and their research teams to report on the pooled and W3/bilateral projects of the 2025-30 portfolio in
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt1]
+24 The key impact evaluation questions addressed in this component are: • To what extent do multistakeholder engagement processes and co-design of science-based processes and tools lead to ownership of results by landscape stakeholders and to the sustainable uptake of solutions? • Through which mechanisms does the multidisciplinary and transdisciplinary science promoted by the Multifunctional Landscapes program generate adoption of bundles of solutions and innovations at the landscape level? • Under what conditions and through which mechanisms agroecological and nature positive approaches, within a multifunctional landscape lens, optimize landscape multifunctionality? • What are the behavioral outcomes of such
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4]
+the extent of improvement in the individual product and the number of smallholder farmers that adopt the product. KEQ1 How has B4T’s contribution to the impact areas (return on investment) been maximized? The research questions for relevance also apply here. The research questions on learning and effectiveness will assist contribution analysis. RQ13 Have the expected projections from product concept and design translated into on-farm trial results, and if different why/how has more or less been achieved? (AOW2 AB, AOW3 ID)? RQ14 What additional impact could be achieved with additional investment? (AOW1 MI) RQ15 What is the trajectory of genetic gain for each crop, and what benefits could this mean
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p2pt3]
+................................ ................................ ................................ ..... 23 Program/Accelerator impact overview ................................ ................................ ....... 25 IA activities and collaboration plans ................................ ................................ .......... 26 IA studies ................................ ................................ ................................ ................ 29 Learning and adaptive management ................................ ................................ ......... 33 Reporting
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p12pt4]
+the learning objectives of the Monitoring, Evaluation, and Learning (MEL) component, the IA strategy provides empirical evidence on the Program's effects, aiming to understand the causal mechanisms underlying both expected and unanticipated outcomes. Each of the 2030 outcomes is associated with an impact assessment study designed to evaluate the impact of the Policy Program's Theory of Change (ToC). Several Areas of Work (AoWs) have planned IA studies that explore the impact pathways between intermedia te outcomes and the 2030 outcomes. Additionally, some impact evaluations are planned to test the validity of the research questions underpinning the Policy Program. The specific research questions addressed and the exact nature of each study (quantitative, qualitative, or mixed methods) are currently under consideration. While IA studies assess the achievements of the Policy Program, their objective is not to internally evaluate the Program's work. These studies are conducted in collaboration with other programs and
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u31-34]
+Nirmal, Rajalakshmi (IFPRI) 36:04 But. Colomer, Julien (One CGIAR - France) 36:06 Yeah, yeah. Basically anything that's not finished or nailed down, I get to answer for. So and then I SO look, 2025 is a Transition year and. We everybody recognizes like the amount of pressure that everyone's under. So that final step of transferring over the, let's say, key Performance indicator or target output and target outcome values from the window three and bilaterals into the theory of change. And into the planning module, et cetera, will not be done for the 2025 Technical report. So for the 2025 Technical report, IT being a Transition year, we want programs to report against the targets that they've already got in there obviously. And for the Window 3 bilats that have been mapped, we will really ask them to contribute the Results that they can contribute to in this first year. We have an objective and key result there for the System organization, which says that 80% of Window 3 bilats are included. In the Technical reports, exactly what is included is not defined. So we kind of have a bit of a Long leash there or You know, wide goal posts, but that's a discussion to have with centers and we'll be working with centers and with the Program and accelerators to better define like what can be reported, what is the lowest cost. Path to report, et cetera for 2025. Now for 2026, however, Nicoletta put up that objective which said something like 100% of Program and accelerator plans and Results and budget and Technical reports, You know, allow for that sort of, You know, what did You plan, what did you? Deliver. And in that context, the 2026 plan of Results and budget and 2026 Technical reports, we will be asking the mapping of Window 3 bilateral targets down to the specific, You know, KPI within the high level outputs or at the intermediate outcome level. And then asking centres to then report against what they what they had planned. So that's gonna be for 2026 plan of Results and budget and the 2026 Technical report. 2025 is a Transition year. So that final step of transferring over the target information is not being done. Is that clear? Nirmal, Rajalakshmi (IFPRI) 38:32 Yeah. So for 2025, we are not reporting against bilateral projects in the RMS, right? Colomer, Julien (One CGIAR - France) 38:38 We will be, we will be. It's just that we will not be entering in target values. Yeah. So, SO I mean, unless that is useful in some way, like it's either if it's more useful to enter them in.
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt3]
+funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified r</t>
+  </si>
+  <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: According to the Annex pie chart, what was total 2024 revenue and the split by funding source?\n\nContext:\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 6\nContent: Research results can be defined according to the nature of the change and the control over it.\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p14]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 14\nContent: Figure 1: Research results according to the kind of change and the control over it.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 23 Annex 2: ISDC feedback relating to pooled &amp; non-pooled alignment5 This section provides a direct extract from the ISDC Feedback on CGIAR Portfolio Narrative 2025- 2030. Comments relating to the alignment of pooled and non -pooled have been extracted from the broader set of comments. They have not been edited to e.g. update Program and Accelerator nomenclature. • Articulation of how the Portfolio, including bilateral and W1 funding, will be bundled into Megaprograms is still lacking. Bilateral funding is restricted and is provided for a specific purpose and with specific intended impacts. This needs to be honored a nd the lack of flexibility in shifting those funds into other areas should be clearly acknowledged. • Alignment of the entire Portfolio with the CGIAR 2030 Research and Innovation Strategy needs to be strong and explicit. How will management ensure that bilateral funding delivers against this Strategy? In addition: o What happens if a bilateral project is not strongly aligned with the Strategy and how will CGIAR ensure that opportunity costs are covered? o Will all bilateral projects across all Centers be mapped to support the Portfolio? • A challenge that should be acknowledged is incorporating bilateral funding into Megaprograms. Each Megaprogram and Accelerator will be large scale and staff will be consumed by the implementation of contracted work. Trying to build Megaprogram linkages in parallel with bilateral funding should be additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative 2025-2030\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p5]\nFile: Type3_2024Report.pdf\nLocation: page 5\nContent: Section 2: Portfolio Performance and Project Coordination Progress 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022-2024. 3. Science Group Projects (SGPs) are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance and fiduciary oversight. 4. EiB II will report through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they will provide a concise, high-level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the technical reports. 2.1. Technical Reporting Arrangement 2022-24 CGIAR Technical Reporting fulfils the System-level programmatic reporting requirements set out in the Standard Provisions annexed to the Funding Agreement or Arrangement signed between each Funder and the System Organization.2 The 2024 Technical Report includes the following Initiatives, Impact Platforms and SGPs3: • All 32 Initiatives • Five Impact Platforms – Gender Equality, Youth and Social Inclusion – Environmental Health and Biodiversity – Nutrition, Health and Food Security – Climate Adaptation and Mitigation – Poverty Reduction, Livelihoods and Jobs • Six SGPs – Accelerated Varietal Improvement and Seed Delivery of Legumes and dryland Cereals in Africa (AVISA) – Roots Tubers and Banana (RTB) Breeding – Accelerating Genetic Gain and Varietal Replacement in Rice - Phase 2 (AGGRi 2) – Excellence in Breeding (EiB) II: Cross-Crop Support Services for Breeding Acceleration4 – Accelerating Crop Improvement Through Genome Editing 2023-2025 – Climate Adaptation Insight For 2024, CGIAR will produce and deliver a total of 46 Technical Reporting outputs: • March 2025: Results from 2024 published on the online CGIAR Results Dashboard (1). • May 2025: Publication of 42 Type 1 (32 x Initiative reports; 5 x Impact Platform reports; 5 x SGP reports) Reports and a Type 3 Report (1). • End of June 2025: Publication of the Portfolio Narrative (1). • End of June 2025: Publication of the Type 2 Report: CGIAR Contributions to Impact in Agrifood Systems (2022-24) (1). Each of these reports is released separately and will be available in PDF format. 2024 Technical Reporting covers USD 370 million (USD 322 million for Initiatives and Impact Platforms, and USD 49 million for W3 SGPs), representing nearly 40 percent of CGIAR’s total pooled and non-pooled funding for 2024. 2.1.1. Streamlining the process and adding value to stakeholders In 2022 CGIAR launched a new 2022-24 Technical Reporting Arrangement, co-developed with the System Council’s Strategic Impact Monitoring and Evaluation Committee (SIMEC). The 2022 rollout was regarded as a “first pancake” or trial phase, establishing minimum viable functionality and setting the foundation for annual improvements. Key achievements of 2022 Technical Reporting included the adoption of a common report template aligned with the Technical Reporting Arrangement for Initiatives and Impact Platforms; integration with CGIAR’s Results Framework; digital linking of results to theories of change (TOCs); and the introduction of quality assurance processes mediated by third parties. Additionally, a new interactive CGIAR Results Dashboard was launched, and the Performance and Results Management System (PRMS) – an online reporting system – was developed, alongside adaptive management processes and the rollout of Innovation Packages and Scaling Readiness plans. Building on this, 2023 Technical Reporting incorporated lessons from a 2022 Learning and Optimization process, documented in a 2022 Learning and Optimization report. Key advancements included transitioning to “Always on” reporting by opening the PRMS from September 2023, more than doubling the reporting window compared to 2022 and allowing greater flexibility for Initiatives, Impact Platforms, and SGPs. Quality assurance was optimized through four staggered batches across 2023 and 2024. Further enhancements included expanding per-result tagging to all five Impact Areas. A Risk Management Module was launched to support risk identification and reporting at the Initiative level. A large number of participants joined training sessions to support reporting, dashboard use, and onboarding, and the rapid uptake of adaptive management strengthened strategic agility, with positive feedback from across the Portfolio. The Research Plans of Results and Budgets section of the CGIAR website was updated to ensure easy open access to Initiative, SGP and Impact Platform Plans of Results and Budgets (PORBs). The 2024 reporting cycle continued this trajectory, integrating insights from the 2023 Learning and Optimization process and Action Plan to further refine CGIAR’s Technical Reporting processes and products. Key improvements in 2024 included: • Launching the PRMS Planning Module to support the replan process: The launch of an online Planning Module synchronized TOC and Planning data in the PRMS, improving the efficiency and quality of planning workflows. Enhanced replan guidelines were provided to help Initiatives, Impact Platforms, and SGPs implement 2023 Reflect recommendations and align budget forecasts with updated budget envelopes. To support continuous learning and adaptive management, a user experience survey on the Planning Module was conducted to assess effectiveness and inform user-centered enhancements for the 2025-30 Portfolio. • Further simplifying reporting processes and tools: A series of enhancements to PRMS functionalities were implemented to improve efficiency and usability. Improved filtering options, enhanced notification systems, and more clearly structured result PDFs now enable quicker access to relevant information. Innovation Packages and Scaling Readiness language and templates were simplified. Reporting was streamlined and modified to suit the final year of reporting for the Portfolio, with an Outcome Indicator Module co-developed with input from Initiatives, Impact Platforms and SGPs to provide them with the opportunity to assess their progress against targets for Work Package outcomes and end-of-Initiative outcomes; summative and yearly highlights were combined into a single report; and adaptive management processes removed. • Improving decision-making within the PRMS: Broader engagement from PRMS testers across reporting entities and Senior Program Managers was integrated into PRMS feature development, ensuring that system updates were aligned with user needs and supported consistent decision-making. • Enhancing product clarity: The Type 1 Annual Report template was reviewed to better accommodate end-of-Initiative outcome reporting for the final year of the Portfolio. Improvements to the Results Dashboard were made to enhance the accessibility of IPSR insights. • Strengthening quality assurance: Examples include updated and enhanced QA guidance, and updated guidance on Impact Area tagging. An AI tool was prototyped and tested on a series of data fields, with the intent to leverage lessons learned and develop an enhanced AI tool that can be applied to a broader set of reported data and integrated into the PRMS, supporting both the reporting and QA phases. • Developing the Semantic Natural Language Processing Aggregator Platform (SNAP): SNAP is an AI-powered tool enhancing access to and analysis of CGIAR’s reported outputs, outcomes, and impacts. It improves access to Portfolio information and results evidence through semantic searches, thematic clustering, and automated summaries, complementing the CGIAR Results Dashboard. SNAP-supported narratives were integrated into the CGIAR 2024 Portfolio Narrative, and ongoing refinements will further enhance its role in Portfolio reporting. • Further integrating SGPs and Impact Platforms: Between 2022 and 2024, CGIAR progressively aligned these entities with its Technical Reporting processes and common systems to enhance consistency and coherence. In 2023, three Impact Platforms – Nutrition, Health and Food Security; Climate Adaptation and Mitigation; and Environmental Health and Biodiversity – were onboarded alongside the Gender Equality, Youth and Social Inclusion Impact Platform (which reported in 2022), each receiving tailored support such as TOC and results framework development. The SGP pilot launched in 2023 further expanded CGIAR’s reporting ecosystem by integrating Center-specific Window 3 awards, with two SGPs submitting first-year results using the PRMS Reporting Tool and Type 1 Report template. In 2024, integration expanded to include the Poverty Reduction, Livelihoods and Jobs Impact Platform and four additional SGPs, further broadening the reporting ecosystem. • Enhancing risk management through the PRMS Risk Module: The Risk Management Module, launched in 2023 to support Initiative management and reporting of risks, was further enhanced in 2024, allowing Initiatives to capture transition-focused risks. It enabled Initiatives to review, update, or close risks, contributing to the design of the 2025-30 Portfolio. The updated Risk Management Module will be used by Programs and Accelerators from 2025 onward. Climate-Smart Village set-up under the Adaptation and Mitigation Initiative in Agriculture (AMIA) of the Department of Agriculture. Credit: Miguel Mamon/CIAT May 2025 54 CGIAR Portfolio Practice Change (Type 3) Report 2024\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 4\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 4 1. Technical Reporting Arrangement purpose, scope, value proposition, delivery and optimization, Purpose The purpose of th e Technical Reporting Arrangement 2025 -2030 (“TRA 25-30”) is to set out the technical reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. The TRA 25-30: • Provides the parameters that e nable the Centers, the CGIAR System Partners and the System Organization to fulfil their technical reporting obligations under the funding agreements that apply to the use of Window 1 and Window 2 funds from the CGIAR Trust Fund (“Pooled Funding”). These parameters also allow the Integrated Partnership Board to fulfil its responsibility under the CGIAR System Charter to report on programmatic performance of CGIAR Research on an annual basis. • Provides, through the establishment of common technical reporting principles, enabling tools and mechanisms, progressive alignment and synergy between the technical reporting requirements that apply to components of the CGIAR Portfolio that are funded by Pooled Funding and those that apply to the components that are funded by other sources of funds (“Non-Pooled Funding”). • Sets transparency, performance tracking, and accountability expectations between CGIAR System Funders and CGIAR including Centres, • Informs decision making at different levels, underpins research management, operationalizes the Performance and Results Management Framework (PRMF), and guides portfolio -level MELIA and the design of the next Performance and Results management System (PRMS). The current Technical Reporting Arrangement that applies to the CGIAR Portfolio during the period 2022-24 (“TRA 22-24”) was co-developed by CGIAR and System Council/Strategic Impact Monitoring and Evaluation Committee (SIMEC) members in 2022. A new TRA is needed to match 2025-30 portfolio parameters, notably the alignment of pooled and non-pooled funding sources, and to apply lessons learnt from 2022-24. Scope The TRA 25-30 provides the operational and enabling basis to plan, monitor, learn and report on the 25-30 Portfolio. It is designed to progressively enable Programs and Accelerators, Centers and their research teams to report on the pooled, bilaterally and W3-funded components of the 2025- 30 portfolio in an integrated and aligned way, without increasing reporting burdens of Centers and Scientists. Going forward, the CGIAR Integrated Partnership will work towards progressively greater alignment of W3/bilateral projects and programs with the 2030 outcomes and theories of change of the Programs and Accelerators. Centers will provide key agreed information on their W3/bilaterally funded projects and programs to enable Program/Accelerator leaderships to explore ways to achieve alignment based on, inter alia, complementarity of results as well as actual or potential thematic, geographic, and partnership overlaps. Reporting on and attribution\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 5\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results framework, underpinned by a new Technical Reporting Arrangement, will provide robust, continuous performance and results reporting across all funding sources, as well as adaptive management of the Portfolio. 1 Value Proposition The TRA 25-30: - Creates value by delivering an integrated approach that tracks the performance of each Program and Accelerator, - Brings together the inputs (including costs), outputs, outcomes and impacts of the total portfolio to allow for easier and more robust Return on Investment (ROI) calculations. - Avoids creating a significant additional and duplicative layer of complex reporting requirements for W3/ bilaterally funded work. - Informs decision making through providing ready access to demand-driven quality raw and curated data products. Delivery The TRA 25 -30 will be delivered in line with Management arrangements for CGIAR’s 2025 —30 science and innovation Portfolio. Specific roles and responsibilities will be defined in 2025. 1 CGIAR Portfolio Narrative, 1 November 2024\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:p7]\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 7\nContent: Trifa, Nicoleta (CGIAR System Organization) 0:48 Yep. OK, good. So thank you. This session is the first of two session plans for today, planned for today, with the second being scheduled later at 3:00 PM CET to accommodate colleagues in other time zones. Technical reporting. My name is Nicoletta Trifa. By the way, I'm part of the Portfolio Performance Unit, the support unit within the Office of the Chief Scientist. Here is an overview of what we'll cover in the next minutes. I believe my presentation will take 2025 minutes and then we'll leave room for questions at the end, if that's OK. So what we'll cover an update of the technical reporting arrangements 2025 to 2030, priorities and changes for 2025, a brief introduction on the annual technical report and the neighbors. So this mean the performance and results. Management system and the quality assurance, the technical reporting timeline, available resources and support and what's next and how to stay engaged. I want to mention that this session marks the start of the conversation around 2025 technical reporting. We want to give you the early look at the key priorities and plans for the months ahead, and the goal is to make sure that you stay informed, prepared and supported with a clear understanding of upcoming deliverables and timelines. And also clarity on who to reach out to if you have questions or if you need help along the way. Good. Technical reporting arrangements for the new portfolio. The 2025 to 2030 portfolio has been approved by the CGR Global Leadership team on in June 2025 and provides the operational basis to plan, monitor, learn and report. On the new portfolio. It is designed to progressively enable programs, accelerators and centers to report on the pooled and window 3 bilateral projects of the new portfolio in an integrated and aligned way without increasing the burden on centers and the scientists. Main changes compared to the previous technical reporting arrangements, streamline reported reporting. So less products, more integration, lower transaction costs, stronger impact, focus results. To be clearly linked and packaged under impacts, outcomes and associated agreed indicator targets and better linkages between the theory of change or so plan of results and budget and technical reporting. The primary audiences for technical reporting are funders and CGR staff at integrated partnership, portfolio and program and accelerator levels. A secondary audience is the partners. Annual technical reporting covers the individual annual technical reports for program and accelerators, as well as a portfolio view of aggregate contribution to thematic and geographic targets. And relevant content from this technical reports are integrated into the CJR corporate reporting. In terms of the 2025 technical reporting priorities, 2025 is a transition year with technical reporting arrangements, implementation again focusing on streamlined reporting and on strengthening the linkages between theory of change. Porb, media and technical reporting. As many of you know, in the previous portfolio these components were not properly linked, so it was a bit challenging to demonstrate progress against the theory of change or the plans, as you know. In terms of deliverables for 2025. These are the program and accelerator technical reports, which are due in April 2026, the portfolio narrative, which is due in 2026 in June. Integration of top 80% of window tree and bilateral projects by central dollar value into reporting and planning. Application of the minimum data standards for window tree and bilateral reporting. And mapping of refinement during the pause and reflect process which will take place early Q 1/20/26. So as I was mentioning, this year is seen more as a transition year towards KPI based planning and reporting and efforts are underway to enable planning and reporting at the KPI level, which is aligned with the system office objective and key results for 2026 and 20. These are to be confirmed, so they haven't been confirmed yet, but I've pasted them here so that you can see the 2026 objective and key results for the system office. So 100% program and accelerate the work plans and budget. An annual technical report. Which provide for software enabled monitoring of erformance and results against smart Ki by center, ear and ooled funds invested. So next year, 80% of centres, CGR, window three and bilateral funded work by value included in 2025 technical reports and then the following year in 2027, this will increase to 90% of centres. Window 3 and bilateral funded work included in 2026 technical reports. The following slides, what I have, what I have included in the following slides, it's a brief introduction into. What is expected in terms of deliverables from programs and accelerators together with an overview of the performance and results management system and the QA. I realized that some in this call some of you are already familiar with the reporting arrangements from the previous portfolio. While for others this might be entirely new. So our goal is to bring everyone to the same level of understanding so that we can move forward with clarity and shared expectations for the 2025 technical reporting. OK, so technical reporting for program and accelerator. We'll focus on three key deliverables. So first is reporting results, the 2025 results in the Performance and Reporting Management system, PRMS. Each program accelerator and mapped window 3 project will report 2025 results in the system and we strongly encourage to report results that were planned and budgeted. So results which have been included in the reports. As the outdated technical reporting system will allow for tracking results against plans. Secondly is the quality assurance of reporting results. As you know, the results submitted go through the quality assessment process and we will share more details on this process in the timeline in an info session scheduled for later. Which we will schedule later in in September, October and the quality assess results will be available on the results dashboard. Inform the pause and reflect and will be included in the technical reports in the annual technical reports. A third deliverable for program and accelerators is drafting estimation of the 2025 Annual Technical Report. So each program and accelerator is responsible for drafting and internally validating quality assessing their 2025 Annual Technical Report. Before submitting it to the PPU, so to the perform portfolio performance unit. Again, guidance on this, the detailed process and validation process will be shared with you timely. Also to support this process, an AI generated V0 draft will be provided as a starting point. The annual technical reports. What are they? This the annual technical report. The the the aim is to make them short, so to 20 to 30 pages, concise and targeted. They provide assurance on annual program accelerator delivery against the boards, so plan of results and budget and progress on theory of change. They are based on quality assess results, the template guidance and as I mentioned and. AI V0 will be provided to all rogram and accelerator teams. Annual technical reports need to be submitted by each program and accelerator in March, April, so more details on this will follow and publication is intended to happen end of April, beginning of May. Here to the right side you have the. Content of the annual the proposed content for the annual technical report as per the technical reporting arrangements. Many of you will notice that there are not no big changes compared to previous portfolio, so the idea is to have a fact sheet and executive summary. The annual progress on theory of change, area of work details, a section on results, section on partnerships, portfolio linkages, adaptive management and then one key result story. But again, we will plan a detailed deep dive session on the annual technical report template and the guidance. So there will be time for you to ask questions in detail about about this and to receive support obviously. I've also included here for reference links to the 2024 Annual Technical Reports from the initiatives and impact platforms, and also a link to the 2024 Portfolio Narrative Report. In case you want to, you want to have a look to see, um, what it captures. PRMS. So this stands for Performance and Results Management System is the system the the the the environment where results need to be submitted. Again, the team is working on updating their resources. There will be. New users onboarding decks created with the links to different information and I I believe the PCU Alison together with the program coordinators. Are. The all the PRMS roles. So PCU is leading a work to define the PRMS roles and to get the information from program and accelerators regarding who from each program accelerator should have what role in PRMS. To enable us to to provide the right access to the platform when the time comes to report. Quality assurance process. So results submitted by program and accelerators in the PRMS will be quality assessed by a quality assessment team in February 2026. Your participation in this process is required. Guidance and resource resources will be provided and also an info session will be scheduled later this year. What is the QA? It is a process that aims to improve the quality of the reported data to provide consistency across the system, ensure reliability of reported results. Inform the learning process and improve the overall CGR accountability and transparency. Quality assess data informs the reflect process which takes place early Q12026, the results dashboard. So once the quality assessment of the results is finalized, the quality assess results will be pushed to results dashboard. You most probably have seen that. Reading. It also informs and are the results. The practices results are included in the annual report, in the portfolio narrative, and then in the overall CGIR annual report. In terms of the the timeline, so we have this info session now to provide an overview on the technical reporting and there will be several other info session and deep dive scheduled. Throughout September and October of reporting 2025 results, we believe that it will be feasible to open the PRMS in November for program and accelerators to to report. The date is still to be confirmed. We're aiming to to, yeah, to meet to to to end November. Hopefully this will be this is feasible from the technical side quality assurance. It's planned for February 2026 reflect process as I was mentioning Q 1/20/26 and then annual technical reports are due in March, April 2026 as well. Where to find information pertaining to technical reporting and planning and media? There is a one stop shop for for um all this. It's called the Performance and Results Hub. I'm gonna stop sharing cause I wanna share. Um, I'm gonna stop sharing the deck. I wanna. We could resent the hub. I'm not going to go through each section, but at least. So that you can see for those who are new more specifically to see and we will also share the link obviously the performance and results hub as I was mentioning it has detail on reporting, planning, reflect, replan. So you come in here, you click on 2025 reporting and then you will have access to the latest information, to the timeline, latest update, upcoming events. So all the information, information. Session dates will be listed here. We'll also have a subsection here with. Recording from from meetings, so that will be posted. For example today after this session we'll post a recording and the deck here for you to access and there is a section on frequently asked question. We recycled a couple of questions from the previous portfolio and updated them so that they are applicable to the program and accelerator teams, so feel free to go here and and browse. As resources become available, we will place them here and we will notify you by e-mail. OK. Going back to my deck. Which? In terms of engagement plan, so in order to streamline communication and optimize support for program accelerators and centers with mapped window 3 bilateral projects, we will send bi-weekly emails to everyone in this. This goal with key updates on technical reporting, with reminders and also with the latest questions and answers available on the hub. There will be targeted emails focusing on specific categories within the program accelerators. We want to engage with some of you on technical reporting, revisions, developments. And the aim is to gather feedback from you. Program coordinators will be copied on these emails. Info session. So a specific topic and we'll plan info session on specific topics, for example the standard indicator, description shades, the guidance on technical reporting, quality assurance. Reporting on innovations, the PRMS, so deep dive on the PRMS, the updates, the tool and so on. And during the reporting phase and the QA we will have weekly drop-ins. So this drop-ins is there will be no presentation. Presentation during the during this drop-ins. The purpose is for us to provide live support, so to answer your questions on the spot and the primary focus will be as I was mentioning, reporting and the QA. For if you know for every question you have, we invite you to use this e-mail address performanceandresults@cgr.org. This is the. The e-mail address we use for all technical reporting questions. So you have the questions right to us at performanceandresult@cjr.org and you will receive a response. We are aiming to respond within the 24 hours. Just to give an example, you know going back here I've gotten the targeted targeted emails and feedback. So this is a good example on for example how we plan to engage and get get feedback from from you on the PRMS enhancements so. Usually we send there's an e-mail sent to invite you to provide feedback on a o</t>
   </si>
   <si>
@@ -682,6 +864,9 @@
   </si>
   <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question:  What evidence architecture and rigor standards underpin the report’s claims? \n\nContext:\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt1]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 67 part 1\nContent: Figure 31: Methods and rigor of the impact evaluations included in this report. Note: Some studies used multiple methods or received multiple rigor scores for different reported impact estimates. Therefore, the sum of the number of studies reflected in the graph is more than the total number of 62. 4 1 6 4 15 125 4 5 13 62 43210 98765 Rigor score 0 5 10 15 20 4 3 1 43 32 2 3 5 2 2 13 1 2 1 1 1 1 2 1 1 4 6 2 4 4 1 Other ﬁxed eﬀects models Diﬀerence in diﬀerence Propensity score matching and other matching approaches Instrumental variables Endogenous switching regression Randomized control trial Number of publications by rigor score Rigor of the evidence by study design Figure 32: Proportion of impact evaluation analyses which met each of the best-practice rigor score criteria. Included are 125 studies, which contained 488 indicator analyses. 0 100 200 300 400 Spillovers Sensitivity analysis Representativeness Random treatment assignment Random sampling Power Heterogeneous treatment eﬀects Baseline balance Attrition UncertainDid not meet criteriaMet criteria 1%58% 41% 60%40% 56%15% 29% 81%19% 81% 19% 18% 82% 14% 86% 50% 50% 21% 79% B. Impact indicators CGIAR’s Results Framework contains 19 Impact Area indicators it committed to tracking in the 2022 to 2024 period. These indicators are well aligned with the SDG targets and supporting indicators. CGIAR poverty-related indicators are closely linked with SDG targets 1.1 and 1.2 (on reducing poverty) and target 2.3 (on increasing agricultural productivity on small farms). CGIAR nutrition-related indicators are well aligned with SDG targets 2.1 and 2.2 (on reducing hunger and\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 7 part 3\nContent: fully contextualize the results. Are you an implementer? Consider jumping directly to your Impact Area or Continent of interest. But be sure to return and read about the Scope of the Report so that you know what is, and is not, included in this report. Tips on interpretation When interpreting the outcomes reported, be cautious about aggregating across data sources (e.g., as Performance and Results Management System [PRMS] and SPIA country studies), Impact Areas, and continents. Some outcomes are included in more than one of these categories. Pay attention to the specified time period. The report focuses on evidence reported during the 2022 to 2024 period, but outcomes and impacts often developed over much longer periods. Consider the overall weight of the evidence, not individual pieces of evidence. This report presents a body of evidence, drawing on a variety of different epistemological approaches: outcome evidence, impact evaluations, and other types of information, which collectively provide different insights into CGIARs impact. However , only impact evaluations were assessed for the number of best research practices they used, with a composite score of 0 to 9 assigned based on the number of key components of rigor addressed by the study. While weighted equally in this work, these components do not all have equal implications for overall study\n\n---\n\n[ID: pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p1pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1\nFile: Food Frontiers and Security_Inception Report 30-06-2025.pdf\nLocation: page 1 part 2\nContent: Report Food Frontiers and Security Science Program Inception Report\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt1]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 12 part 1\nContent: All impact study submissions were reviewed for potential inclusion into the evidence base of the report. The two primary inclusion considerations were relevance and rigor (see Annex A. Selection of evidence). Studies were determined to be relevant if they considered the outcomes and impacts of CGIAR-supported interventions, regardless of the authorship of the study. Outcomes reported into the CGIAR PRMS are quality assessed for relevance (that is, CGIAR’s role in the outcome is validated); therefore, none of these reported outcomes were excluded on the basis of relevance. Studies with unclear or misleading methods were excluded on the basis of rigor. Studies meeting this threshold of clarity were then classed as “impact assessments” or “impact evaluations.” Impact evaluations were the primary study designs of interest. Impact evaluations are studies that use statistical methods (experimental or quasi-experimental) to quantify the causal change in a condition that was achieved by an intervention. Studies using other study designs were included under the umbrella term of impact assessments (including impact evaluations), if they provided information relevant to understanding impacts, such as cost- benefit analyses, reviews of CGIAR work, and measures of the adoption of CGIAR technology. These included the country studies supported by CGIAR’s SPIA. While impact evaluations are necessary to establish causal change linking intervention and impact, they can be limited in scope due to practical constraints, such as resources and measurement challenges. Other types of impact assessments can provide valuable insights into CGIAR’s contributions to real-world change in a wider spatial or temporal context; however , they do c This can be common for power calculations. Authors may have conducted power calculations but not r eported that they did so in-text. Assessment is based on what is reported in-text, not what may have been done but not reported. d See Annex A. Included studies and rigor of\n\n---\n\n[ID: pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_Inception Report 30-06-2025.pdf\nLocation: page 17 part 3\nContent: underpin the work being done and provide the solid positioning for holding the CA. This collaboration means the work being done relies on the most capable parts of both the CGIAR and the relevant partner and that this collaboration changes over time. A part of the Program’s objectives\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt2]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 12 part 2\nContent: challenges. Other types of impact assessments can provide valuable insights into CGIAR’s contributions to real-world change in a wider spatial or temporal context; however , they do c This can be common for power calculations. Authors may have conducted power calculations but not r eported that they did so in-text. Assessment is based on what is reported in-text, not what may have been done but not reported. d See Annex A. Included studies and rigor of evidence for details. Criteria related to random sampling and treatment assignment; reporting of power calculation and sensitivity analysis; consideration of attrition, spillovers, and heterogenous treatment effects; and sample representativeness and baseline balance. not establish causality. Impact evaluations were further appraised to determine the number of best practices followed per study. A composite score45 was calculated to reflect the level of confidence in the findings of a study and to help understand the application of best practices in CGIAR impact evaluation. Nine best practices were identified (see Annex A. Included studies and rigor of evidence), resulting in the composite best- practice score ranging from 0 to 9. Not all the criteria were relevant to all studies, and some studies may have met criteria but did not clearly describe them in the publication.c Studies following three or more best practices were featured preferentially in this report (assuming equality in relevance). Details of the method and analysis of the scores are in Annex A. Included studies and rigor of evidence. Included impact studies Approximately 500 studies were reviewed for eligibility and 125 studies were included in the primary dataset. Of these, 62 were impact evaluations and 63 were impact assessments which did not attempt to establish the causal effect of an intervention on an impact. Randomized controlled trials (RCT) were the most common impact evaluation design (n = 21), followed by\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p4pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 4 part 1\nContent: Integration with other outputs The Portfolio Narrative informs the 2024 CGIAR Annual Report – a comprehensive summary of the organization’s collective achievements, impacts, and strategic outlook. Elements of the Type 2 report were integrated into the CGIAR Flagship Report released in April 2025 during the CGIAR Science Week. The Flagship Report synthesizes CGIAR research in an accessible format designed specifically to provide policy- and decisionmakers at national, regional, and global levels with the evidence they require to formulate, develop, and negotiate evidence-based policies and investments. The diagram below illustrates these relationships, emphasizing the interconnectedness of the Type 3 Report with other reporting products. CGIAR Results Dashboard Portfolio Narrative report CGIAR Annual report Type 1 Initiative, Impact Platform, and Science Group Project reports Type 2 CGIAR Contributions to Impact in Agrifood Systems: evidence and learnings from 2022 to 2024 Flagship report Type 3 Portfolio Practice Change report 2024 Technical Reporting Figure 1. CGIAR’s 2024 Technical Reporting components and their integration with other CGIAR reporting products. Section 1: Introduction 1 Under the CGIAR Technical Reporting Arrangement for the next Portfolio (2025-30), relevant aspects of the Type 3 Report will be included in the annual Portfolio Narrative, and a separate Type 3 Report will no longer be produced. The 2024 CGIAR Portfolio Practice Change\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt4]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 48 part 4\nContent: against CGIAR’s Results Framework is that, apart from the SPIA country studies, other internal and external studies are designed in an uncoordinated bottom-up way. Because such studies are undertaken to meet specific information needs, opportunities to learn through synthesis or aggregation are missed due to the differences in indicators used and measurement approaches employed. For example, impact assessments are rarely connected with data on innovation use, preventing case study results from being used to extrapolate possible large-scale effects. Thus, moving forward, two areas for improvement are: (1) to collectively undertake strategic impact assessments that will answer high-priority impact assessment questions and (2) to develop and enforce the use of a core set of common indicators and measurement methodsq that should be used in impact assessment studies regardless of who initiates them. In addition, during the 2022 to 2024 period, Initiatives defined targets for outcomes and made commitments to measuring and reporting on those outcomes. They did not have a similar plan or commitment to measuring impacts. As CGIAR evolves to longer-term programs covering the whole of CGIAR, there should be commitments to the consistent measurement of impacts. However , this has been an ongoing challenge within the organization, with similar recommendations from a review of the 2017 to 2021 portfolio.176 Rigor of the evidence All impact evaluations identified were assessed for their rigor based on criteria established by Rao 2025.45 The most common score was a 4 of 9 key elements being present, suggesting moderate overall quality and room for improvement. A high number of impact evaluations used rigorous methods to infer causality between a CGIAR innovation and impacts (see Annex A. Included studies and rigor of evidence). However , many failed to consider heterogeneous treatment effects or report power calculations. Most of the impact evaluations used experimental or quasi-experimental designs with two or more measurement periods. However , a sizeable group of the studies were based on cross-sectional (single measurement) studies. While they are peer-reviewed and employ recommended methods of controlling for unobservable variables to enhance the likelihood of a causal inference, there remain limitations to such designs. In addition to rigor , this study paid attention to the relevance of the studies. Often, studies employing less rigorous, cross-sectional methodologies were able to provide evidence more relevant to policymaking and decision-making Tradititional rice variety in Ilagan, Isabela, the Philippines. Photo credit: Miguel Mamon/CIAT CGIAR Impacts in Agrifood Systems: | Learnings | Page 90 of 130 CGIAR CGIAR CGIAR Impacts in Agrifood Systems: | Learnings| Page 91 of 130\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 31 part 4\nContent: four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the \"challenges and megatrends\" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p6pt1]\nLink: https://cgspace.cgiar.org/items/04bd63a9-1b58-4eb5-84f2-b54c8bde226e\nFile: Portfolio Narrative_2024.pdf\nLocation: page 6 part 1\nContent: Integration with other outputs The Portfolio Narrative informs the 2024 CGIAR Annual Report – a comprehensive summary of the organization’s collective achievements, impacts, and strategic outlook. Elements of the Type 2 report fed into the CGIAR Flagship Report, released in April 2025 at CGIAR Science Week. The Flagship Report\n\n---\n\n[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 3\nContent: activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt3]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 46 part 3\nContent: to ensure common terminology across the reporting units. At the impact level, there were 19 indicators across the five Impact Areas. The frequency of reporting against exact indicators is very low (18 percent of indicators assessed match those in the Results Framework; Annex B. Impact indicators). In addition, there is an imbalance across Impact Areas and indicators in the frequency with which 2022 to 2024 studies attempt to measure those indicators. There were many impact assessments that measured yields or income related to the poverty indicators, and relatively few that looked at environmental, climate, or gender indicators. This is consistent with what Templeton (2023)176 found in her review of evidence used to support the impact claims made by the CGIAR Research Programs between 2017 and 2021. Thus, there remains a huge challenge to define feasible indicators for"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: What is the 2025–30 Impact Assessment (IA) strategy addressing, and what will be delivered to funders and managers?\n\nContext:\n\n---\n\n[ID: docx:Engagement Plan 2025 Technical Reporting.docx:u46-49]\nLink: Engagement Plan: 2025 Technical Reporting (Full Word document)\nFile: Engagement Plan 2025 Technical Reporting.docx\nLocation: section 'Fortnightly update emails' paragraph 80 to section 'Fortnightly update emails' paragraph 83\nContent: CGSpace Team Lead KM Managers Curators/Repository Managers PRMS Team\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 29 part 4\nContent: The current funding landscape uncertainty as well as a realistic assessment of resources that can be dedicated to IA led us to prioritize IA activities in 6 countries, where we can easily leverage on human and financial resources for impact assessment: Colombia, Peru, Tunisia, Kenya, India, Vietnam. The site prioritization, as well as prioritization of the key impact indicators that the IA should target (potential indicators are presented in the table below), will be a specific action of the MELIA team at the end of 2025, when future financial capacity will be clearer. Further funding for IA studies will be sought in 2026 and during the implementation of\n\n---\n\n[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1]\nLink: https://docs.google.com/presentation/d/1iH7kEQrUqQywkG9wVkCCBq_tRp-d1Ws0/edit?slide=id.p1#slide=id.p1\nFile: Information Session on 2025 Technical Reporting.pptx\nLocation: slide 2 part 1\nContent: Agenda Technical Reporting Arrangement 2025-30 Technical reporting priorities for 2025 What\n\n---\n\n[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_MELIA Plan 30-06-2025.pdf\nLocation: page 8 part 4\nContent: exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved. Impact assessments are conducted after an intervention has been completed and are used to substantiate claims of sustained results. They seek to measure impact at scale, i.e., benefits to a large number of people/large areas of land. It employs both quantitative and qualitative methods, often combined for deeper insights. IA goes beyond monitoring indicators to evidenced attribution of observed changes to CGIAR interventions. IA will help to ensure that Programs/Accelerators contribute meaningfully to CGIAR’s Results Framework and the 2025–30 Portfolio objectives.\n\n---\n\n[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_MELIA Plan 30-06-2025.pdf\nLocation: page 8 part 3\nContent: the learnings and what are other critical areas that require further focused support? (AoW 5) Evaluation collaboration plans Genebanks will seek to collaborate with the Multifunctional Landscapes Program to study in situ and on farm site monitoring of diversity conservation. Genebanks will also collaborate with the Crop Trust and Aarhus University to review the Scientific Impact of the Seed Quality Management and Quality Management System Communities of Practice. Collaborations with W3/bilateral projects will be explored during phase 2 of the mapping exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p10pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 10 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 10 Thematic Impact 2022-30 Report The Thematic Impact 2022 -30 Report provides a m acro level view of CGIAR’s role in Food, Land and Water System Transformation covering the period 2022 -30. It will be released in 2031. Its format and content will be developed during the period 2025-30. Results Dashboard • The Results Dashboard will be enhanced to better present curated information a gainst Impact Area targets, geographies and key topics. • Headline impacts and outcomes will be more clearly communicated in the Dashboard. • Using AI, users will be able to easily query the results data and underlying sources of evidence data using\n\n---\n\n[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p2pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 2 part 3\nContent: Impact assessment (IA) .............................................................................................................. 13 Program impact overview .................................................................................................................... 13 IA activities and collaboration plans ..................................................................................................... 14 IA studies ........................................................................................................................................... 15 5. Learning and adaptive management ........................................................................................... 16 Learning ............................................................................................................................................. 16 Annual review and adaptive planning ...................................................................................................\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 17 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 17 The amount of quality information sourced from different funding sources, and the coherence between those different information sources will increase over time (specific metrics and targets to be developed) 6. Impact Assessment Strategy/ Approach/ Case studies CGIAR will develop a 2025 -30 Impact Assessment Plan and integrate its design, budgeting and delivery into the 25-30 Portfolio. The bottom-up approach to impact assessment that has been used within CGIAR for the past decades has not produced sufficient quantity or quality of studies to prov ide evidence against CGIAR impact indicators. SPIA fills in some of this gap, but even their new undertaking of country studies will likely not be able to contribute to most of the indicators\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p25pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 25 part 1\nContent: • Bilateral/W3-funded projects: to identify embedded impact assessment opportunities and avoid duplication. • CGIAR IA teams : to contribute to portfolio -level meta -evaluation and harmonize data with common CGIAR indicators. Priority will be given to impact in integrative countries, where multiple AoWs operate. These broader IA studies will assess the synergies between interventions and provide system -level insights into the pathways driving impact. Potential integrative countries include Bangladesh, Ethiopia, Nigeria, and Tanzania, based on portfolio density and MELIA feasibility. A senior Impact Specialist will guide study design and implementation, ensure alignment with the CGIAR results framework indicators, and coordinate data quality assurance across IA efforts. Impact assessment studies The Program has identified initial IA study themes for inclusion in the MELIA studies. However , these initial themes are not included in the\n\n---\n\n[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 3\nContent: activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable\n\n---\n\n[ID: pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p2pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP03%20%2D%20Sustainable%20Animal%20and%20Aquatic%20Foods%2FSustainable%20Animal%20and%20Aquatic%20Foods%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP03%20%2D%20Sustainable%20Animal%20and%20Aquatic%20Foods&amp;p=true&amp;ga=1\nFile: Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf\nLocation: page 2 part 2\nContent: ................................ ................................ ............... 7 Data collection strategy ................................ ................................ ................................ 7 3. Evaluation plan ................................ ................................ ................................ ..................... 7 Evaluation studies ................................ ................................ ................................ ....... 7 Evaluation collaboration plans ................................ ................................ ....................... 8 4. Impact assessment ................................ ................................ ................................ ............... 8 Program/Accelerator impact overview ................................ ................................ ............ 8 IA activities and collaboration\n\n---\n\n[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 18 part 3\nContent: All the knowledge generated by these studies will be available not only to Program managers, but also researchers, the CGIAR community, and external stakeholders. Finally, analyzing monitoring data will be a continuous process, and results, along with recommendations, will be made available to Program managers to make any necessary adjustments to the Program implementation. Annual review and adaptive planning The Climate Action Program will implement an annual review and adaptive planning process, building on the experience and lessons from the 2022–24 CGIAR Portfolio and aligned with evolving guidance on the Reﬂect and Re-Plan processes. Each year, the Program will conduct structured annual performance reviews at both program-wide and AoW levels. These reviews will assess progress toward the intended outputs and outcomes, using both quantitative and qualitative data drawn from the CGIAR Performance and Results Management System"}]</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1095,7 +1280,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1107,16 +1292,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1124,7 +1309,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1136,16 +1321,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1153,7 +1338,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -1165,16 +1350,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1182,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1194,16 +1379,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1211,7 +1396,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1223,16 +1408,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1240,7 +1425,7 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1252,16 +1437,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1269,7 +1454,7 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1281,16 +1466,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1298,7 +1483,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1310,16 +1495,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1327,7 +1512,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -1339,16 +1524,16 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1356,7 +1541,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1368,16 +1553,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1385,7 +1570,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -1397,16 +1582,16 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1414,7 +1599,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -1426,16 +1611,16 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1443,7 +1628,7 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -1455,16 +1640,16 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I14" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1472,7 +1657,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -1484,16 +1669,16 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I15" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1501,7 +1686,7 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -1513,16 +1698,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I16" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1530,7 +1715,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -1542,16 +1727,16 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1559,7 +1744,7 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -1571,16 +1756,16 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G18" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H18" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I18" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1588,7 +1773,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1600,16 +1785,16 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1617,7 +1802,7 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -1629,16 +1814,16 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G20" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1646,7 +1831,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -1658,22 +1843,22 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G21" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H21" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="J21" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K21" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1681,7 +1866,7 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -1693,22 +1878,22 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H22" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="J22" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K22" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1716,7 +1901,7 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -1728,22 +1913,22 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="J23" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K23" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1751,7 +1936,7 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -1763,22 +1948,22 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G24" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H24" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="J24" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K24" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1786,7 +1971,7 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -1798,22 +1983,22 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H25" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="J25" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K25" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1821,7 +2006,7 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -1833,22 +2018,22 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H26" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J26" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K26" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1856,7 +2041,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -1868,22 +2053,22 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H27" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J27" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K27" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1891,7 +2076,7 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -1903,22 +2088,22 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H28" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J28" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K28" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1926,7 +2111,7 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -1938,22 +2123,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H29" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J29" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K29" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1961,7 +2146,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -1973,22 +2158,22 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H30" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I30" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J30" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K30" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1996,7 +2181,7 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -2008,22 +2193,22 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G31" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H31" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="J31" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K31" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2031,7 +2216,7 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -2043,22 +2228,22 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G32" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H32" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I32" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J32" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K32" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2066,7 +2251,7 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -2078,22 +2263,22 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G33" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H33" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J33" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K33" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2101,7 +2286,7 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -2113,22 +2298,22 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G34" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H34" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J34" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K34" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2136,7 +2321,7 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -2148,22 +2333,22 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G35" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H35" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J35" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K35" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2171,7 +2356,7 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -2183,22 +2368,22 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G36" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H36" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J36" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K36" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2206,7 +2391,7 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -2218,22 +2403,22 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G37" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H37" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J37" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K37" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2241,34 +2426,209 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38">
+        <v>100</v>
+      </c>
+      <c r="D38">
+        <v>100</v>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" t="s">
+        <v>71</v>
+      </c>
+      <c r="H38" t="s">
+        <v>100</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J38" t="s">
+        <v>114</v>
+      </c>
+      <c r="K38" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39">
+        <v>100</v>
+      </c>
+      <c r="D39">
+        <v>100</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" t="s">
+        <v>101</v>
+      </c>
+      <c r="I39" t="s">
+        <v>110</v>
+      </c>
+      <c r="J39" t="s">
+        <v>115</v>
+      </c>
+      <c r="K39" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40">
+        <v>100</v>
+      </c>
+      <c r="D40">
+        <v>100</v>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" t="s">
+        <v>72</v>
+      </c>
+      <c r="H40" t="s">
+        <v>101</v>
+      </c>
+      <c r="I40" t="s">
+        <v>110</v>
+      </c>
+      <c r="J40" t="s">
+        <v>115</v>
+      </c>
+      <c r="K40" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41">
+        <v>100</v>
+      </c>
+      <c r="D41">
+        <v>100</v>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>59</v>
+      </c>
+      <c r="G41" t="s">
+        <v>72</v>
+      </c>
+      <c r="H41" t="s">
+        <v>101</v>
+      </c>
+      <c r="I41" t="s">
+        <v>110</v>
+      </c>
+      <c r="J41" t="s">
+        <v>115</v>
+      </c>
+      <c r="K41" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42">
+        <v>100</v>
+      </c>
+      <c r="D42">
+        <v>100</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>59</v>
+      </c>
+      <c r="G42" t="s">
+        <v>72</v>
+      </c>
+      <c r="H42" t="s">
+        <v>101</v>
+      </c>
+      <c r="I42" t="s">
+        <v>110</v>
+      </c>
+      <c r="J42" t="s">
+        <v>115</v>
+      </c>
+      <c r="K42" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
         <v>52</v>
       </c>
-      <c r="C38">
-        <v>100</v>
-      </c>
-      <c r="D38">
-        <v>100</v>
-      </c>
-      <c r="E38" t="b">
-        <v>1</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
-      </c>
-      <c r="G38" t="s">
-        <v>65</v>
-      </c>
-      <c r="H38" t="s">
-        <v>93</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="J38" t="s">
-        <v>104</v>
-      </c>
-      <c r="K38" t="s">
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43">
+        <v>100</v>
+      </c>
+      <c r="D43">
+        <v>100</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" t="s">
+        <v>72</v>
+      </c>
+      <c r="H43" t="s">
+        <v>102</v>
+      </c>
+      <c r="I43" t="s">
         <v>110</v>
+      </c>
+      <c r="J43" t="s">
+        <v>115</v>
+      </c>
+      <c r="K43" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Logs/interaction_log.xlsx
+++ b/Logs/interaction_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="136">
   <si>
     <t>timestamp</t>
   </si>
@@ -173,6 +173,21 @@
   </si>
   <si>
     <t>2025-09-19T15:59:13.835247</t>
+  </si>
+  <si>
+    <t>2025-09-19T16:13:20.734840</t>
+  </si>
+  <si>
+    <t>2025-09-19T16:14:35.098736</t>
+  </si>
+  <si>
+    <t>2025-09-19T16:14:56.209259</t>
+  </si>
+  <si>
+    <t>2025-09-19T16:16:20.378710</t>
+  </si>
+  <si>
+    <t>2025-09-19T16:22:47.723531</t>
   </si>
   <si>
     <t>What funding did 2024 Technical Reporting cover?</t>
@@ -468,6 +483,43 @@
 pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf — page 18 part 3 — 4</t>
   </si>
   <si>
+    <t>The 2025–30 Impact Assessment (IA) strategy focuses on evaluating the causal effects of research outputs and related activities, aiming to substantiate claims of sustained results and measure impacts at scale. It will prioritize IA activities in six countries, leveraging available human and financial resources. Deliverables for funders and managers will include comprehensive reports on the impact assessments, which will provide insights into the effectiveness of interventions and align with CGIAR's Results Framework. Additionally, the strategy will enhance the Results Dashboard to better communicate headline impacts and outcomes. 
+Sources:
+File — Location — Cited IDs
+pdf:Genebanks_MELIA Plan 30-06-2025.pdf — page 8 part 4 — [ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4]
+pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 17 part 1 — [ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1]
+pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf — page 18 part 3 — [ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt3]</t>
+  </si>
+  <si>
+    <t>I cannot find information in the provided chunks to answer this.</t>
+  </si>
+  <si>
+    <t>The 2025–30 Impact Assessment (IA) strategy focuses on evaluating the causal effects of research outputs and related activities, aiming to measure the magnitude of impact achieved across various interventions. It emphasizes a bottom-up approach to ensure that the assessments provide sufficient evidence against CGIAR impact indicators. Deliverables to funders and managers will include comprehensive reports on the findings from these assessments, which will be accessible to program managers, researchers, and external stakeholders. This knowledge will support informed decision-making and adjustments in program implementation based on the insights gained. 
+Sources:
+File — Location — Cited IDs
+pdf:Genebanks_MELIA Plan 30-06-2025.pdf — page 8 part 4 — 4
+pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 17 part 1 — 6
+pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf — page 18 part 3 — 4</t>
+  </si>
+  <si>
+    <t>The 2025–30 Impact Assessment (IA) strategy focuses on evaluating the causal effects of research outputs and related activities, aiming to measure the magnitude of impact achieved across various interventions. It will prioritize activities in six countries, leveraging available human and financial resources for effective assessments. Deliverables to funders and managers will include comprehensive reports on the impact of these assessments, which will substantiate claims of sustained results and ensure alignment with CGIAR's Results Framework. Additionally, knowledge generated from these studies will be accessible to a broader audience, including researchers and external stakeholders, facilitating informed decision-making and program adjustments. 
+Sources:
+File — Location — Cited IDs
+pdf:Genebanks_MELIA Plan 30-06-2025.pdf — page 8 part 4 — [ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4]
+pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 17 part 1 — [ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1]
+pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf — page 18 part 3 — [ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt3]</t>
+  </si>
+  <si>
+    <t>The 2025–30 Impact Assessment (IA) strategy focuses on evaluating the causal effects of research outputs and related activities, aiming to substantiate claims of sustained results and measure impacts at scale. It will prioritize IA activities in six countries, leveraging available resources to assess key impact indicators. Deliverables for funders and managers will include comprehensive reports and insights derived from these assessments, which will inform program adjustments and enhance alignment with CGIAR's Results Framework. The strategy emphasizes collaboration and continuous data analysis to ensure effective implementation and adaptation of programs. 
+Sources:
+File — Location — Cited IDs
+docx:Engagement Plan 2025 Technical Reporting.docx — section 'Fortnightly update emails' paragraph 80 to section 'Fortnightly update emails' paragraph 83 — u46-49
+pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf — page 29 part 4 — p29pt4
+pdf:Genebanks_MELIA Plan 30-06-2025.pdf — page 8 part 4 — p8pt4
+pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 10 part 1 — p10pt1
+pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 17 part 1 — p17pt1</t>
+  </si>
+  <si>
     <t>Information Session on 2025 Technical Reporting.pptx — slide 9 — pptx:Information Session on 2025 Technical Reporting.pptx:s9, Engagement Plan 2025 Technical Reporting.docx — paragraph 2 — docx:Engagement Plan 2025 Technical Reporting.docx:p2, Information Session on 2025 Technical Reporting.pptx — slide 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s2, Guidance on reporting outputs or outcomes.docx — paragraph 22 — docx:Guidance on reporting outputs or outcomes.docx:p22, Engagement Plan 2025 Technical Reporting.docx — section 'Technical Reporting questions' — docx:Engagement Plan 2025 Technical Reporting.docx:p59, CGIAR_ImpactReport_2022-24.pdf — page 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p1, Engagement Plan 2025 Technical Reporting.docx — section 'A single location for all documents and resources' — docx:Engagement Plan 2025 Technical Reporting.docx:p31, Engagement Plan 2025 Technical Reporting.pptx — slide 1 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s1, CGSpace.docx — section 'CGSpace' — docx:CGSpace.docx:p3, CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 5 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5</t>
   </si>
   <si>
@@ -490,6 +542,9 @@
   </si>
   <si>
     <t>Engagement Plan: 2025 Technical Reporting (Full Word document) — section 'Fortnightly update emails' paragraph 80 to section 'Fortnightly update emails' paragraph 83 — docx:Engagement Plan 2025 Technical Reporting.docx:u46-49, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1 — page 29 part 4 — pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4, https://docs.google.com/presentation/d/1iH7kEQrUqQywkG9wVkCCBq_tRp-d1Ws0/edit?slide=id.p1#slide=id.p1 — slide 2 part 1 — pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1bxyVhlOayJqgreqiv4xhOu9xQ3Vz3Ymg/edit — section 'Fortnightly update emails' paragraph 80 to section 'Fortnightly update emails' paragraph 83 — docx:Engagement Plan 2025 Technical Reporting.docx:u46-49, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1 — page 29 part 4 — pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4, https://docs.google.com/presentation/d/1iH7kEQrUqQywkG9wVkCCBq_tRp-d1Ws0/edit?slide=id.p1#slide=id.p1 — slide 2 part 1 — pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1</t>
   </si>
   <si>
     <t>[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]
@@ -867,6 +922,12 @@
   </si>
   <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: What is the 2025–30 Impact Assessment (IA) strategy addressing, and what will be delivered to funders and managers?\n\nContext:\n\n---\n\n[ID: docx:Engagement Plan 2025 Technical Reporting.docx:u46-49]\nLink: Engagement Plan: 2025 Technical Reporting (Full Word document)\nFile: Engagement Plan 2025 Technical Reporting.docx\nLocation: section 'Fortnightly update emails' paragraph 80 to section 'Fortnightly update emails' paragraph 83\nContent: CGSpace Team Lead KM Managers Curators/Repository Managers PRMS Team\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 29 part 4\nContent: The current funding landscape uncertainty as well as a realistic assessment of resources that can be dedicated to IA led us to prioritize IA activities in 6 countries, where we can easily leverage on human and financial resources for impact assessment: Colombia, Peru, Tunisia, Kenya, India, Vietnam. The site prioritization, as well as prioritization of the key impact indicators that the IA should target (potential indicators are presented in the table below), will be a specific action of the MELIA team at the end of 2025, when future financial capacity will be clearer. Further funding for IA studies will be sought in 2026 and during the implementation of\n\n---\n\n[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1]\nLink: https://docs.google.com/presentation/d/1iH7kEQrUqQywkG9wVkCCBq_tRp-d1Ws0/edit?slide=id.p1#slide=id.p1\nFile: Information Session on 2025 Technical Reporting.pptx\nLocation: slide 2 part 1\nContent: Agenda Technical Reporting Arrangement 2025-30 Technical reporting priorities for 2025 What\n\n---\n\n[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_MELIA Plan 30-06-2025.pdf\nLocation: page 8 part 4\nContent: exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved. Impact assessments are conducted after an intervention has been completed and are used to substantiate claims of sustained results. They seek to measure impact at scale, i.e., benefits to a large number of people/large areas of land. It employs both quantitative and qualitative methods, often combined for deeper insights. IA goes beyond monitoring indicators to evidenced attribution of observed changes to CGIAR interventions. IA will help to ensure that Programs/Accelerators contribute meaningfully to CGIAR’s Results Framework and the 2025–30 Portfolio objectives.\n\n---\n\n[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_MELIA Plan 30-06-2025.pdf\nLocation: page 8 part 3\nContent: the learnings and what are other critical areas that require further focused support? (AoW 5) Evaluation collaboration plans Genebanks will seek to collaborate with the Multifunctional Landscapes Program to study in situ and on farm site monitoring of diversity conservation. Genebanks will also collaborate with the Crop Trust and Aarhus University to review the Scientific Impact of the Seed Quality Management and Quality Management System Communities of Practice. Collaborations with W3/bilateral projects will be explored during phase 2 of the mapping exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p10pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 10 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 10 Thematic Impact 2022-30 Report The Thematic Impact 2022 -30 Report provides a m acro level view of CGIAR’s role in Food, Land and Water System Transformation covering the period 2022 -30. It will be released in 2031. Its format and content will be developed during the period 2025-30. Results Dashboard • The Results Dashboard will be enhanced to better present curated information a gainst Impact Area targets, geographies and key topics. • Headline impacts and outcomes will be more clearly communicated in the Dashboard. • Using AI, users will be able to easily query the results data and underlying sources of evidence data using\n\n---\n\n[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p2pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 2 part 3\nContent: Impact assessment (IA) .............................................................................................................. 13 Program impact overview .................................................................................................................... 13 IA activities and collaboration plans ..................................................................................................... 14 IA studies ........................................................................................................................................... 15 5. Learning and adaptive management ........................................................................................... 16 Learning ............................................................................................................................................. 16 Annual review and adaptive planning ...................................................................................................\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 17 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 17 The amount of quality information sourced from different funding sources, and the coherence between those different information sources will increase over time (specific metrics and targets to be developed) 6. Impact Assessment Strategy/ Approach/ Case studies CGIAR will develop a 2025 -30 Impact Assessment Plan and integrate its design, budgeting and delivery into the 25-30 Portfolio. The bottom-up approach to impact assessment that has been used within CGIAR for the past decades has not produced sufficient quantity or quality of studies to prov ide evidence against CGIAR impact indicators. SPIA fills in some of this gap, but even their new undertaking of country studies will likely not be able to contribute to most of the indicators\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p25pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 25 part 1\nContent: • Bilateral/W3-funded projects: to identify embedded impact assessment opportunities and avoid duplication. • CGIAR IA teams : to contribute to portfolio -level meta -evaluation and harmonize data with common CGIAR indicators. Priority will be given to impact in integrative countries, where multiple AoWs operate. These broader IA studies will assess the synergies between interventions and provide system -level insights into the pathways driving impact. Potential integrative countries include Bangladesh, Ethiopia, Nigeria, and Tanzania, based on portfolio density and MELIA feasibility. A senior Impact Specialist will guide study design and implementation, ensure alignment with the CGIAR results framework indicators, and coordinate data quality assurance across IA efforts. Impact assessment studies The Program has identified initial IA study themes for inclusion in the MELIA studies. However , these initial themes are not included in the\n\n---\n\n[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 3\nContent: activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable\n\n---\n\n[ID: pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p2pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP03%20%2D%20Sustainable%20Animal%20and%20Aquatic%20Foods%2FSustainable%20Animal%20and%20Aquatic%20Foods%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP03%20%2D%20Sustainable%20Animal%20and%20Aquatic%20Foods&amp;p=true&amp;ga=1\nFile: Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf\nLocation: page 2 part 2\nContent: ................................ ................................ ............... 7 Data collection strategy ................................ ................................ ................................ 7 3. Evaluation plan ................................ ................................ ................................ ..................... 7 Evaluation studies ................................ ................................ ................................ ....... 7 Evaluation collaboration plans ................................ ................................ ....................... 8 4. Impact assessment ................................ ................................ ................................ ............... 8 Program/Accelerator impact overview ................................ ................................ ............ 8 IA activities and collaboration\n\n---\n\n[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 18 part 3\nContent: All the knowledge generated by these studies will be available not only to Program managers, but also researchers, the CGIAR community, and external stakeholders. Finally, analyzing monitoring data will be a continuous process, and results, along with recommendations, will be made available to Program managers to make any necessary adjustments to the Program implementation. Annual review and adaptive planning The Climate Action Program will implement an annual review and adaptive planning process, building on the experience and lessons from the 2022–24 CGIAR Portfolio and aligned with evolving guidance on the Reﬂect and Re-Plan processes. Each year, the Program will conduct structured annual performance reviews at both program-wide and AoW levels. These reviews will assess progress toward the intended outputs and outcomes, using both quantitative and qualitative data drawn from the CGIAR Performance and Results Management System"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: \n\nContext:"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: What is the 2025–30 Impact Assessment (IA) strategy addressing, and what will be delivered to funders and managers?\n\nContext:\n\n---\n\n[ID: docx:Engagement Plan 2025 Technical Reporting.docx:u46-49]\nLink: https://docs.google.com/document/d/1bxyVhlOayJqgreqiv4xhOu9xQ3Vz3Ymg/edit\nFile: Engagement Plan 2025 Technical Reporting.docx\nLocation: section 'Fortnightly update emails' paragraph 80 to section 'Fortnightly update emails' paragraph 83\nContent: CGSpace Team Lead KM Managers Curators/Repository Managers PRMS Team\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 29 part 4\nContent: The current funding landscape uncertainty as well as a realistic assessment of resources that can be dedicated to IA led us to prioritize IA activities in 6 countries, where we can easily leverage on human and financial resources for impact assessment: Colombia, Peru, Tunisia, Kenya, India, Vietnam. The site prioritization, as well as prioritization of the key impact indicators that the IA should target (potential indicators are presented in the table below), will be a specific action of the MELIA team at the end of 2025, when future financial capacity will be clearer. Further funding for IA studies will be sought in 2026 and during the implementation of\n\n---\n\n[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1]\nLink: https://docs.google.com/presentation/d/1iH7kEQrUqQywkG9wVkCCBq_tRp-d1Ws0/edit?slide=id.p1#slide=id.p1\nFile: Information Session on 2025 Technical Reporting.pptx\nLocation: slide 2 part 1\nContent: Agenda Technical Reporting Arrangement 2025-30 Technical reporting priorities for 2025 What\n\n---\n\n[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_MELIA Plan 30-06-2025.pdf\nLocation: page 8 part 4\nContent: exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved. Impact assessments are conducted after an intervention has been completed and are used to substantiate claims of sustained results. They seek to measure impact at scale, i.e., benefits to a large number of people/large areas of land. It employs both quantitative and qualitative methods, often combined for deeper insights. IA goes beyond monitoring indicators to evidenced attribution of observed changes to CGIAR interventions. IA will help to ensure that Programs/Accelerators contribute meaningfully to CGIAR’s Results Framework and the 2025–30 Portfolio objectives.\n\n---\n\n[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_MELIA Plan 30-06-2025.pdf\nLocation: page 8 part 3\nContent: the learnings and what are other critical areas that require further focused support? (AoW 5) Evaluation collaboration plans Genebanks will seek to collaborate with the Multifunctional Landscapes Program to study in situ and on farm site monitoring of diversity conservation. Genebanks will also collaborate with the Crop Trust and Aarhus University to review the Scientific Impact of the Seed Quality Management and Quality Management System Communities of Practice. Collaborations with W3/bilateral projects will be explored during phase 2 of the mapping exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p10pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 10 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 10 Thematic Impact 2022-30 Report The Thematic Impact 2022 -30 Report provides a m acro level view of CGIAR’s role in Food, Land and Water System Transformation covering the period 2022 -30. It will be released in 2031. Its format and content will be developed during the period 2025-30. Results Dashboard • The Results Dashboard will be enhanced to better present curated information a gainst Impact Area targets, geographies and key topics. • Headline impacts and outcomes will be more clearly communicated in the Dashboard. • Using AI, users will be able to easily query the results data and underlying sources of evidence data using\n\n---\n\n[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p2pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 2 part 3\nContent: Impact assessment (IA) .............................................................................................................. 13 Program impact overview .................................................................................................................... 13 IA activities and collaboration plans ..................................................................................................... 14 IA studies ........................................................................................................................................... 15 5. Learning and adaptive management ........................................................................................... 16 Learning ............................................................................................................................................. 16 Annual review and adaptive planning ...................................................................................................\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 17 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 17 The amount of quality information sourced from different funding sources, and the coherence between those different information sources will increase over time (specific metrics and targets to be developed) 6. Impact Assessment Strategy/ Approach/ Case studies CGIAR will develop a 2025 -30 Impact Assessment Plan and integrate its design, budgeting and delivery into the 25-30 Portfolio. The bottom-up approach to impact assessment that has been used within CGIAR for the past decades has not produced sufficient quantity or quality of studies to prov ide evidence against CGIAR impact indicators. SPIA fills in some of this gap, but even their new undertaking of country studies will likely not be able to contribute to most of the indicators\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p25pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 25 part 1\nContent: • Bilateral/W3-funded projects: to identify embedded impact assessment opportunities and avoid duplication. • CGIAR IA teams : to contribute to portfolio -level meta -evaluation and harmonize data with common CGIAR indicators. Priority will be given to impact in integrative countries, where multiple AoWs operate. These broader IA studies will assess the synergies between interventions and provide system -level insights into the pathways driving impact. Potential integrative countries include Bangladesh, Ethiopia, Nigeria, and Tanzania, based on portfolio density and MELIA feasibility. A senior Impact Specialist will guide study design and implementation, ensure alignment with the CGIAR results framework indicators, and coordinate data quality assurance across IA efforts. Impact assessment studies The Program has identified initial IA study themes for inclusion in the MELIA studies. However , these initial themes are not included in the\n\n---\n\n[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 3\nContent: activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable\n\n---\n\n[ID: pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p2pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP03%20%2D%20Sustainable%20Animal%20and%20Aquatic%20Foods%2FSustainable%20Animal%20and%20Aquatic%20Foods%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP03%20%2D%20Sustainable%20Animal%20and%20Aquatic%20Foods&amp;p=true&amp;ga=1\nFile: Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf\nLocation: page 2 part 2\nContent: ................................ ................................ ............... 7 Data collection strategy ................................ ................................ ................................ 7 3. Evaluation plan ................................ ................................ ................................ ..................... 7 Evaluation studies ................................ ................................ ................................ ....... 7 Evaluation collaboration plans ................................ ................................ ....................... 8 4. Impact assessment ................................ ................................ ................................ ............... 8 Program/Accelerator impact overview ................................ ................................ ............ 8 IA activities and collaboration\n\n---\n\n[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 18 part 3\nContent: All the knowledge generated by these studies will be available not only to Program managers, but also researchers, the CGIAR community, and external stakeholders. Finally, analyzing monitoring data will be a continuous process, and results, along with recommendations, will be made available to Program managers to make any necessary adjustments to the Program implementation. Annual review and adaptive planning The Climate Action Program will implement an annual review and adaptive planning process, building on the experience and lessons from the 2022–24 CGIAR Portfolio and aligned with evolving guidance on the Reﬂect and Re-Plan processes. Each year, the Program will conduct structured annual performance reviews at both program-wide and AoW levels. These reviews will assess progress toward the intended outputs and outcomes, using both quantitative and qualitative data drawn from the CGIAR Performance and Results Management System"}]</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1280,7 +1341,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1292,16 +1353,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1309,7 +1370,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1321,16 +1382,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1338,7 +1399,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -1350,16 +1411,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I4" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1367,7 +1428,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1379,16 +1440,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1396,7 +1457,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1408,16 +1469,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I6" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1425,7 +1486,7 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1437,16 +1498,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1454,7 +1515,7 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1466,16 +1527,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1483,7 +1544,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1495,16 +1556,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1512,7 +1573,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -1524,16 +1585,16 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1541,7 +1602,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1553,16 +1614,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1570,7 +1631,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -1582,16 +1643,16 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1599,7 +1660,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -1611,16 +1672,16 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H13" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1628,7 +1689,7 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -1640,16 +1701,16 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1657,7 +1718,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -1669,16 +1730,16 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H15" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1686,7 +1747,7 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -1698,16 +1759,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H16" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I16" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1715,7 +1776,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -1727,16 +1788,16 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1744,7 +1805,7 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -1756,16 +1817,16 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1773,7 +1834,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1785,16 +1846,16 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I19" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1802,7 +1863,7 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -1814,16 +1875,16 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H20" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1831,7 +1892,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -1843,22 +1904,22 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H21" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I21" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J21" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="K21" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1866,7 +1927,7 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -1878,22 +1939,22 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H22" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J22" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="K22" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1901,7 +1962,7 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -1913,22 +1974,22 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H23" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J23" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="K23" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1936,7 +1997,7 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -1948,22 +2009,22 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I24" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J24" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="K24" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1971,7 +2032,7 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -1983,22 +2044,22 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H25" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J25" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="K25" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2006,7 +2067,7 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -2018,22 +2079,22 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I26" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J26" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K26" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2041,7 +2102,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -2053,22 +2114,22 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G27" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I27" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J27" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K27" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2076,7 +2137,7 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -2088,22 +2149,22 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G28" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H28" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I28" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J28" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K28" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2111,7 +2172,7 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -2123,22 +2184,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G29" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H29" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I29" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J29" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K29" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2146,7 +2207,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -2158,22 +2219,22 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I30" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J30" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="K30" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2181,7 +2242,7 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -2193,22 +2254,22 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I31" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J31" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="K31" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2216,7 +2277,7 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -2228,22 +2289,22 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G32" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H32" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I32" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="J32" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="K32" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2251,7 +2312,7 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -2263,22 +2324,22 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G33" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H33" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J33" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="K33" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2286,7 +2347,7 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -2298,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G34" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H34" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J34" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="K34" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2321,7 +2382,7 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -2333,22 +2394,22 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G35" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H35" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J35" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="K35" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2356,7 +2417,7 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -2368,22 +2429,22 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G36" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J36" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="K36" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2391,7 +2452,7 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -2403,22 +2464,22 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G37" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="J37" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="K37" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2426,7 +2487,7 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -2438,22 +2499,22 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G38" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J38" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="K38" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2461,7 +2522,7 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -2473,22 +2534,22 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G39" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I39" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J39" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K39" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2496,7 +2557,7 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -2508,22 +2569,22 @@
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G40" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I40" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J40" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K40" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2531,7 +2592,7 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -2543,22 +2604,22 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G41" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I41" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J41" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K41" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2566,7 +2627,7 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -2578,22 +2639,22 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G42" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H42" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I42" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J42" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K42" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2601,7 +2662,7 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -2613,22 +2674,185 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G43" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I43" t="s">
+        <v>120</v>
+      </c>
+      <c r="J43" t="s">
+        <v>126</v>
+      </c>
+      <c r="K43" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44">
+        <v>100</v>
+      </c>
+      <c r="D44">
+        <v>100</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>64</v>
+      </c>
+      <c r="G44" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44" t="s">
+        <v>108</v>
+      </c>
+      <c r="I44" t="s">
+        <v>120</v>
+      </c>
+      <c r="J44" t="s">
+        <v>126</v>
+      </c>
+      <c r="K44" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45">
+        <v>100</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>64</v>
+      </c>
+      <c r="H45" t="s">
+        <v>109</v>
+      </c>
+      <c r="K45" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46">
+        <v>100</v>
+      </c>
+      <c r="D46">
+        <v>100</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" t="s">
+        <v>77</v>
+      </c>
+      <c r="H46" t="s">
         <v>110</v>
       </c>
-      <c r="J43" t="s">
-        <v>115</v>
-      </c>
-      <c r="K43" t="s">
-        <v>122</v>
+      <c r="I46" t="s">
+        <v>120</v>
+      </c>
+      <c r="J46" t="s">
+        <v>126</v>
+      </c>
+      <c r="K46" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47">
+        <v>100</v>
+      </c>
+      <c r="D47">
+        <v>100</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="s">
+        <v>64</v>
+      </c>
+      <c r="G47" t="s">
+        <v>77</v>
+      </c>
+      <c r="H47" t="s">
+        <v>111</v>
+      </c>
+      <c r="I47" t="s">
+        <v>120</v>
+      </c>
+      <c r="J47" t="s">
+        <v>126</v>
+      </c>
+      <c r="K47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48">
+        <v>100</v>
+      </c>
+      <c r="D48">
+        <v>100</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" t="s">
+        <v>77</v>
+      </c>
+      <c r="H48" t="s">
+        <v>112</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J48" t="s">
+        <v>126</v>
+      </c>
+      <c r="K48" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2639,6 +2863,7 @@
     <hyperlink ref="I36" r:id="rId4"/>
     <hyperlink ref="I37" r:id="rId5"/>
     <hyperlink ref="I38" r:id="rId6"/>
+    <hyperlink ref="I48" r:id="rId7" location="slide=id.p1 — slide 2 part 1 — pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Logs/interaction_log.xlsx
+++ b/Logs/interaction_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="156">
   <si>
     <t>timestamp</t>
   </si>
@@ -190,6 +190,18 @@
     <t>2025-09-19T16:22:47.723531</t>
   </si>
   <si>
+    <t>2025-09-24T09:03:11.833588</t>
+  </si>
+  <si>
+    <t>2025-09-24T09:14:41.463489</t>
+  </si>
+  <si>
+    <t>2025-09-24T09:24:27.981490</t>
+  </si>
+  <si>
+    <t>2025-09-24T09:25:37.525385</t>
+  </si>
+  <si>
     <t>What funding did 2024 Technical Reporting cover?</t>
   </si>
   <si>
@@ -206,6 +218,12 @@
   </si>
   <si>
     <t>What is the 2025–30 Impact Assessment (IA) strategy addressing, and what will be delivered to funders and managers?</t>
+  </si>
+  <si>
+    <t>Who coordinates funders’ M&amp;E requirements across the CGIAR Portfolio and how is duplication avoided?</t>
+  </si>
+  <si>
+    <t>¿Quién tiene la responsabilidad fiduciaria y programática?</t>
   </si>
   <si>
     <t xml:space="preserve">You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:
@@ -231,6 +249,12 @@
     <t>review deeper, and answer the user question and explain it</t>
   </si>
   <si>
+    <t>You are a RAG assistant. Preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If the information is not obtainable, respond with the exact phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.</t>
+  </si>
+  <si>
+    <t>You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.</t>
+  </si>
+  <si>
     <t>pptx:Information Session on 2025 Technical Reporting.pptx:s9:0.307, docx:Engagement Plan 2025 Technical Reporting.docx:p2:0.304, pptx:Information Session on 2025 Technical Reporting.pptx:s2:0.299, docx:Guidance on reporting outputs or outcomes.docx:p22:0.263, docx:Engagement Plan 2025 Technical Reporting.docx:p59:0.244, pdf:CGIAR_ImpactReport_2022-24.pdf:p1:0.239, docx:Engagement Plan 2025 Technical Reporting.docx:p31:0.208, pptx:Engagement Plan 2025 Technical Reporting.pptx:s1:0.202, docx:CGSpace.docx:p3:0.201, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5:0.200, docx:General information on Technical Reporting .docx:p1:0.196, pptx:Information Session on 2025 Technical Reporting.pptx:s15:0.184, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1:0.176, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23:0.166, docx:Guidance on reporting outputs or outcomes.docx:p21:0.163, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4:0.160, docx:Guidance on reporting outputs or outcomes.docx:p30:0.160, docx:2025 Technical Reporting Information (Session 2).docx:p5:0.152, docx:2025 Technical Reporting Information (Session 2).docx:p32:0.138, docx:Guidance on reporting outputs or outcomes.docx:p24:0.138, pdf:Type3_2024Report.pdf:p1:0.136, pptx:Information Session on 2025 Technical Reporting.pptx:s13:0.134, docx:Using the PRMS Reporting Tool.docx:p12:0.133, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7:0.133, docx:Guidance on reporting outputs or outcomes.docx:p31:0.133, docx:General information on Technical Reporting .docx:p4:0.131, pptx:Information Session on 2025 Technical Reporting.pptx:s7:0.128, pdf:Type3_2024Report.pdf:p5:0.124, pptx:Information Session on 2025 Technical Reporting.pptx:s5:0.124, pdf:Portfolio Narrative_2024.pdf:p1:0.124, pdf:Portfolio Narrative_2024.pdf:p5:0.124, pptx:Information Session on 2025 Technical Reporting.pptx:s3:0.123, docx:Innovation use.docx:p7:0.121, pptx:Information Session on 2025 Technical Reporting.pptx:s6:0.121, docx:Innovation development.docx:p31:0.120, docx:2025 Technical Reporting Information (Session 1).docx:p26:0.119, pptx:Information Session on 2025 Technical Reporting.pptx:s10:0.118, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p16:0.118, docx:2025 Technical Reporting Information (Session 1).docx:p7:0.117, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p6:0.116, pdf:Portfolio Narrative_2024.pdf:p6:0.110, docx:2025 Technical Reporting Information (Session 2).docx:p1:0.110, docx:2025 Technical Reporting Information (Session 1).docx:p1:0.110, docx:Guidance on reporting outputs or outcomes.docx:p26:0.109, docx:Innovation development.docx:p13:0.108, docx:Submitting evidence.docx:p3:0.108, docx:Guidance on complementary innnov.docx:p38:0.107, docx:Engagement Plan 2025 Technical Reporting.docx:p61:0.106, docx:Engagement Plan 2025 Technical Reporting.docx:p27:0.102, pptx:Information Session on 2025 Technical Reporting.pptx:s1:0.099, pdf:Type3_2024Report.pdf:p11:0.099, pdf:Type3_2024Report.pdf:p4:0.099, docx:General information on Technical Reporting .docx:p5:0.098, docx:Engagement Plan 2025 Technical Reporting.docx:p39:0.097, docx:Guidance on complementary innnov.docx:p10:0.097, pptx:Information Session on 2025 Technical Reporting.pptx:s4:0.094, pptx:Information Session on 2025 Technical Reporting.pptx:s11:0.092, pptx:Engagement Plan 2025 Technical Reporting.pptx:s2:0.092, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18:0.090, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22:0.089, docx:2025 Technical Reporting Information (Session 2).docx:p26:0.089, docx:Using the PRMS Reporting Tool.docx:p1:0.089, docx:2025 Technical Reporting MELIA glossary.docx:p6:0.089, docx:Engagement Plan 2025 Technical Reporting.docx:p106:0.088, pdf:Type3_2024Report.pdf:p6:0.087, docx:Engagement Plan 2025 Technical Reporting.docx:p42:0.086, docx:General reporting guidance.docx:p1:0.085, docx:General reporting guidance.docx:p5:0.084, docx:2025 Technical Reporting Information (Session 1).docx:p30:0.084, docx:Engagement Plan 2025 Technical Reporting.docx:p17:0.083, docx:Guidance on reporting outputs or outcomes.docx:p2:0.082, docx:2025 Technical Reporting Information (Session 2).docx:p11:0.081, docx:Engagement Plan 2025 Technical Reporting.docx:p69:0.080, pdf:CGIAR_ImpactReport_2022-24.pdf:p2:0.080, docx:Engagement Plan 2025 Technical Reporting.docx:p25:0.079, docx:Reporting the geographic location of results.docx:p1:0.078, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3:0.074, docx:Engagement Plan 2025 Technical Reporting.docx:p45:0.072, docx:Innovation use.docx:p22:0.072, pdf:Portfolio Narrative_2024.pdf:p37:0.071, docx:General reporting guidance.docx:p3:0.071, docx:2025 Technical Reporting Information (Session 2).docx:p41:0.071, docx:Engagement Plan 2025 Technical Reporting.docx:p8:0.071, docx:Engagement Plan 2025 Technical Reporting.docx:p10:0.070, docx:2025 Technical Reporting Information (Session 1).docx:p41:0.068, docx:Guidance on ensuring quality over quantity.docx:p3:0.066, docx:Engagement Plan 2025 Technical Reporting.docx:p55:0.066, pdf:Type3_2024Report.pdf:p3:0.066, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p9:0.066, docx:Innovation development.docx:p40:0.066, docx:Guidance on ensuring quality over quantity.docx:p5:0.066, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15:0.065, docx:Knowledge products.docx:p11:0.065, pdf:Portfolio Narrative_2024.pdf:p72:0.065, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25:0.065, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p2:0.064, docx:2025 Technical Reporting Information (Session 2).docx:p7:0.064, docx:2025 Technical Reporting Information (Session 1).docx:p15:0.064, docx:2025 Technical Reporting Information (Session 2).docx:p14:0.063, docx:2025 Technical Reporting Information (Session 1).docx:p33:0.063</t>
   </si>
   <si>
@@ -253,6 +277,12 @@
   </si>
   <si>
     <t>docx:Engagement Plan 2025 Technical Reporting.docx:u46-49:0.248, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4:0.241, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1:0.233, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4:0.225, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt3:0.220, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p10pt1:0.215, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p2pt3:0.215, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1:0.213, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p25pt1:0.205, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.203, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p2pt2:0.195, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt3:0.194, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p14pt1:0.192, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt2:0.191, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p12pt3:0.190, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt2:0.189, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p2pt2:0.188, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p2pt2:0.185, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p1pt3:0.183, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p1pt2:0.183, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt3:0.183, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p13pt3:0.183, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p1pt2:0.182, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p1pt2:0.182, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p1pt2:0.182, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p1pt2:0.182, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p1pt2:0.182, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p1pt2:0.182, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p29pt4:0.182, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p10pt4:0.182, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt4:0.180, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt2:0.179, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p8pt2:0.179, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p19pt4:0.178, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p2pt4:0.177, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt2:0.177, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p50pt3:0.177, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.176, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25pt3:0.176, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt3:0.175, pptx:Information Session on 2025 Technical Reporting.pptx:s3pt1:0.175, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt1:0.174, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.173, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p2pt3:0.171, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p12pt4:0.171, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.170, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt3:0.169, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p2pt2:0.167, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p2pt3:0.165, pdf:CGIAR_ImpactReport_2022-24.pdf:p9pt1:0.164, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p16pt3:0.164, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p27pt3:0.162, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.162, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p25pt1:0.161, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p1pt2:0.160, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt3:0.160, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p2pt3:0.158, pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3:0.157, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p35pt1:0.157, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt2:0.156, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18pt1:0.156, pdf:Type3_2024Report.pdf:p6pt2:0.156, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.155, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.154, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt1:0.154, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt4:0.153, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p34pt4:0.153, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt4:0.152, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p10pt1:0.151, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p46pt3:0.151, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p10pt2:0.150, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p16pt3:0.150, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p22pt4:0.149, pdf:Climate Action_Inception Report 30-06-2025.pdf:p16pt3:0.149, pdf:Type3_2024Report.pdf:p11pt1:0.148, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt1:0.148, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p9pt1:0.147, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p10pt4:0.147, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.147, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt2:0.147, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p20pt4:0.147, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p6pt3:0.146, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p25pt2:0.146, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt3:0.146, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p17pt3:0.146, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.146, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p15pt2:0.146, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p16pt2:0.145, docx:2025 Technical Reporting Information (Session 2).docx:u4-7:0.145, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p15pt1:0.144, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p22pt4:0.144, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p15pt2:0.144, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt4:0.144, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p14pt2:0.143, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p22pt3:0.143, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p14pt4:0.143, pptx:Information Session on 2025 Technical Reporting.pptx:s15pt3:0.143, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1pt1:0.142, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4:0.141, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p2pt2:0.141</t>
+  </si>
+  <si>
+    <t>pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt4:0.209, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4:0.205, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt2:0.174, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p33pt2:0.173, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p39pt4:0.167, pdf:Type3_2024Report.pdf:p6pt1:0.166, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p30pt4:0.165, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt2:0.164, pdf:Type3_2024Report.pdf:p2pt4:0.160, pdf:Genebanks_Inception Report 30-06-2025.pdf:p32pt1:0.156, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p25pt1:0.154, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt3:0.153, docx:Standard Provisions 2026.docx:u103-106:0.149, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1pt2:0.149, pdf:Type3_2024Report.pdf:p8pt4:0.149, pdf:Type3_2024Report.pdf:p6pt2:0.148, pdf:Portfolio Narrative_2024.pdf:p87pt2:0.147, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p26pt2:0.147, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p33pt1:0.146, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4:0.141, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p22pt4:0.139, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p12pt3:0.139, pdf:Portfolio Narrative_2024.pdf:p5pt3:0.137, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p11pt1:0.137, pdf:Portfolio Narrative_2024.pdf:p5pt2:0.136, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt2:0.134, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p10pt4:0.133, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt1:0.131, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p6pt4:0.131, docx:Standard Provisions 2026.docx:u22-25:0.130, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p28pt2:0.129, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt2:0.129, pdf:Portfolio Narrative_2024.pdf:p1pt1:0.129, pdf:Portfolio Narrative_2024.pdf:p87pt3:0.126, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p26pt1:0.125, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt4:0.125, docx:Guidance on reporting outputs or outcomes.docx:u10-13:0.125, pdf:Genebanks_Inception Report 30-06-2025.pdf:p8pt2:0.124, pdf:Portfolio Narrative_2024.pdf:p82pt4:0.123, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p27pt2:0.121, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p9pt4:0.121, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p28pt3:0.120, docx:Standard Provisions 2026.docx:u127-130:0.120, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18pt4:0.119, pdf:Type3_2024Report.pdf:p4pt3:0.119, pdf:Portfolio Narrative_2024.pdf:p83pt3:0.119, pdf:Portfolio Narrative_2024.pdf:p83pt4:0.118, pdf:Portfolio Narrative_2024.pdf:p2pt4:0.118, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p8pt1:0.117, pdf:Type3_2024Report.pdf:p11pt1:0.117, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p30pt1:0.116, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p22pt1:0.116, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt4:0.115, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt3:0.115, pdf:Portfolio Narrative_2024.pdf:p83pt1:0.114, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p11pt2:0.113, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p33pt3:0.113, docx:Standard Provisions 2026.docx:u100-103:0.112, pdf:Type3_2024Report.pdf:p4pt2:0.111, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1pt1:0.111, pptx:Information Session on 2025 Technical Reporting.pptx:s1pt2:0.110, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p29pt2:0.110, pdf:Type3_2024Report.pdf:p4pt4:0.109, pdf:Climate Action_Inception Report 30-06-2025.pdf:p26pt4:0.109, pdf:Genebanks_Inception Report 30-06-2025.pdf:p8pt3:0.109, pdf:Climate Action_Inception Report 30-06-2025.pdf:p26pt3:0.108, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p8pt4:0.108, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt4:0.108, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt3:0.106, pdf:CGIAR_ImpactReport_2022-24.pdf:p4pt2:0.106, pdf:Type3_2024Report.pdf:p1pt1:0.106, pdf:CGIAR_ImpactReport_2022-24.pdf:p6pt1:0.105, pdf:Type3_2024Report.pdf:p7pt1:0.105, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4:0.105, pdf:Type3_2024Report.pdf:p7pt2:0.105, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p1pt3:0.104, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p49pt1:0.104, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p28pt3:0.104, docx:Standard Provisions 2026.docx:u115-118:0.104, pdf:Portfolio Narrative_2024.pdf:p83pt2:0.104, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p26pt2:0.103, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p31pt4:0.103, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p25pt1:0.102, pptx:Information Session on 2025 Technical Reporting.pptx:s3pt3:0.102, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p23pt1:0.102, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p28pt1:0.102, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p27pt1:0.101, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p10pt2:0.101, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p9pt2:0.100, pdf:Type3_2024Report.pdf:p4pt1:0.099, docx:Standard Provisions 2026.docx:u154-157:0.098, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p36pt3:0.098, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p27pt1:0.098, pdf:Type3_2024Report.pdf:p8pt3:0.098, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p32pt2:0.097, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p23pt4:0.097, pdf:Portfolio Narrative_2024.pdf:p87pt4:0.097, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18pt2:0.096, pdf:Type3_2024Report.pdf:p11pt3:0.096, pdf:Portfolio Narrative_2024.pdf:p5pt1:0.096, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p35pt2:0.096, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p26pt1:0.095, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p29pt3:0.095, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p29pt2:0.095, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt2:0.095, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p20pt4:0.095, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt1:0.094, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p8pt3:0.094, docx:Standard Provisions 2026.docx:u106-109:0.094, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt1:0.094, docx:Standard Provisions 2026.docx:u46-49:0.094, pdf:Climate Action_Inception Report 30-06-2025.pdf:p32pt4:0.093, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p26pt3:0.093, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt3:0.093, docx:Standard Provisions 2026.docx:u130-133:0.093, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p27pt3:0.092, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p5pt2:0.092, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p23pt4:0.092, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p41pt1:0.092, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt2:0.092, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p14pt1:0.091, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p32pt4:0.091, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt3:0.091, pdf:Type3_2024Report.pdf:p10pt4:0.090, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p49pt2:0.090, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p29pt1:0.090, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p29pt3:0.089, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p26pt1:0.089, pdf:CGIAR_ImpactReport_2022-24.pdf:p39pt3:0.089, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p16pt3:0.089, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p37pt4:0.089, pdf:Type3_2024Report.pdf:p9pt1:0.088, docx:2025 Technical Reporting Information (Session 2).docx:u25-28:0.088, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt3:0.088, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt3:0.088, docx:Standard Provisions 2026.docx:u85-88:0.087, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p24pt1:0.087, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p15pt2:0.087, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p37pt4:0.086, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1pt4:0.086, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p4pt1:0.086, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p12pt2:0.086, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p49pt4:0.086, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p33pt2:0.086, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p16pt1:0.085, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p19pt2:0.085, pdf:Genebanks_Inception Report 30-06-2025.pdf:p29pt1:0.085, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p35pt3:0.085, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p35pt4:0.085, pdf:Climate Action_Inception Report 30-06-2025.pdf:p24pt4:0.085, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p24pt2:0.084, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p25pt2:0.084, pdf:CGIAR_ImpactReport_2022-24.pdf:p39pt2:0.084, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p5pt2:0.083, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p28pt1:0.083, pptx:Information Session on 2025 Technical Reporting.pptx:s3pt1:0.083, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p28pt4:0.083, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p30pt1:0.083, pdf:Portfolio Narrative_2024.pdf:p81pt4:0.083, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.083, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p8pt4:0.083, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p22pt2:0.083, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p18pt1:0.083, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p3pt1:0.083, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p21pt2:0.082, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p12pt3:0.082, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p18pt3:0.082, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p4pt4:0.082, pdf:CGIAR_ImpactReport_2022-24.pdf:p6pt2:0.082, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.082, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p31pt3:0.082, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p12pt1:0.081, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt4:0.081, pdf:Climate Action_Inception Report 30-06-2025.pdf:p15pt4:0.081, pdf:Type3_2024Report.pdf:p11pt2:0.081, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p4pt3:0.081, docx:2025 Technical Reporting Information (Session 2).docx:u22-25:0.081, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p24pt3:0.081, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p9pt2:0.081, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p14pt2:0.081, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt3:0.080, docx:2025 Technical Reporting Information (Session 2).docx:u4-7:0.080, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p28pt4:0.080, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt3:0.080, docx:Standard Provisions 2026.docx:u97-100:0.080, pdf:Type3_2024Report.pdf:p3pt2:0.080, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p19pt4:0.079, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p20pt3:0.079, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p10pt4:0.079, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p12pt1:0.079, pdf:Genebanks_Inception Report 30-06-2025.pdf:p13pt2:0.079, pdf:CGIAR_ImpactReport_2022-24.pdf:p49pt1:0.079, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p26pt2:0.078, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p23pt1:0.078, pdf:Climate Action_Inception Report 30-06-2025.pdf:p12pt2:0.078, pdf:Portfolio Narrative_2024.pdf:p6pt3:0.078, pdf:Portfolio Narrative_2024.pdf:p82pt1:0.078, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p24pt3:0.078, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p12pt4:0.078, pdf:Portfolio Narrative_2024.pdf:p87pt1:0.078</t>
+  </si>
+  <si>
+    <t>pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2:0.396, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3:0.387, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1:0.364, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1:0.361, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1:0.330, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3:0.327, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2:0.319, pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2:0.283, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1:0.210, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4:0.204, docx:2025 Technical Reporting Information (Session 2).docx:u52-56:0.204, docx:2025 Technical Reporting Information (Session 1).docx:u1-4:0.196, docx:2025 Technical Reporting Information (Session 1).docx:u43-45:0.193, docx:2025 Technical Reporting Information (Session 2).docx:u1-4:0.193, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1:0.157, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4:0.151, pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3:0.144, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p25pt1:0.144, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt1:0.142, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt2:0.141, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3:0.137, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p36pt4:0.133, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt2:0.133, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt2:0.129, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt2:0.120, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt3:0.119, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2:0.113, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt3:0.111, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1:0.108, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt3:0.102, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p36pt1:0.102, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3:0.099, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt2:0.091, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1:0.088, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p55pt1:0.084, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt1:0.080, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p53pt4:0.074, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt3:0.072, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p40pt4:0.064, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt2:0.062, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt4:0.055, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p32pt3:0.047, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p32pt2:0.047</t>
   </si>
   <si>
     <t>I cannot find information in the provided chunks to answer this.  
@@ -520,6 +550,36 @@
 pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 17 part 1 — p17pt1</t>
   </si>
   <si>
+    <t>The coordination of funders' M&amp;E requirements across the CGIAR Portfolio is primarily managed by the Portfolio Performance Unit, which leads the technical reporting arrangements. To avoid duplication, the CGIAR employs a structured approach that includes mapping efforts across programs to identify common interests and synergies. This is further supported by the development of a Technical Reporting Arrangement that promotes alignment between reporting requirements for pooled and bilateral funding, ensuring that all components work towards shared results without overlap. 
+Sources:
+File — Location — Cited IDs
+CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 23 part 4 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt4
+CGIAR_ImpactReport_2022-24.pdf — page 2 part 4 — pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4
+Type3_2024Report.pdf — page 6 part 1 — pdf:Type3_2024Report.pdf:p6pt1
+Scaling for Impact_Inception Report 30-06-2025.pdf — page 30 part 4 — pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p30pt4
+CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 3 part 2 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt2</t>
+  </si>
+  <si>
+    <t>I cannot find information in the provided chunks to answer this.  
+Sources:  
+File — Location — Cited IDs  
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2  
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 24 part 3 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3  
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 22 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1  
+Genebanks_Inception Report 30-06-2025.pdf — page 22 part 1 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1  
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1</t>
+  </si>
+  <si>
+    <t>I cannot find information in the provided chunks to answer this. The context does not specify who holds the fiduciary and programmatic responsibilities. For a detailed understanding of these roles, further information or specific documents would be necessary. Please consult additional resources or documents that may clarify these responsibilities. 
+Sources:
+File — Location — Cited IDs
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 24 part 3 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 22 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1
+Genebanks_Inception Report 30-06-2025.pdf — page 22 part 1 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1</t>
+  </si>
+  <si>
     <t>Information Session on 2025 Technical Reporting.pptx — slide 9 — pptx:Information Session on 2025 Technical Reporting.pptx:s9, Engagement Plan 2025 Technical Reporting.docx — paragraph 2 — docx:Engagement Plan 2025 Technical Reporting.docx:p2, Information Session on 2025 Technical Reporting.pptx — slide 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s2, Guidance on reporting outputs or outcomes.docx — paragraph 22 — docx:Guidance on reporting outputs or outcomes.docx:p22, Engagement Plan 2025 Technical Reporting.docx — section 'Technical Reporting questions' — docx:Engagement Plan 2025 Technical Reporting.docx:p59, CGIAR_ImpactReport_2022-24.pdf — page 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p1, Engagement Plan 2025 Technical Reporting.docx — section 'A single location for all documents and resources' — docx:Engagement Plan 2025 Technical Reporting.docx:p31, Engagement Plan 2025 Technical Reporting.pptx — slide 1 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s1, CGSpace.docx — section 'CGSpace' — docx:CGSpace.docx:p3, CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 5 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5</t>
   </si>
   <si>
@@ -545,6 +605,12 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1bxyVhlOayJqgreqiv4xhOu9xQ3Vz3Ymg/edit — section 'Fortnightly update emails' paragraph 80 to section 'Fortnightly update emails' paragraph 83 — docx:Engagement Plan 2025 Technical Reporting.docx:u46-49, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1 — page 29 part 4 — pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4, https://docs.google.com/presentation/d/1iH7kEQrUqQywkG9wVkCCBq_tRp-d1Ws0/edit?slide=id.p1#slide=id.p1 — slide 2 part 1 — pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1</t>
+  </si>
+  <si>
+    <t>https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 23 part 4 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt4, https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9 — page 2 part 4 — pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1 — page 29 part 2 — pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt2</t>
+  </si>
+  <si>
+    <t>https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543 — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2, https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543 — page 24 part 3 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3, https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543 — page 22 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1</t>
   </si>
   <si>
     <t>[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]
@@ -903,6 +969,251 @@
 funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified r</t>
   </si>
   <si>
+    <t>[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt4]
+additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4]
+report is part of the CGIAR System Organisations’ technical reporting arrangement. We would like to thank all funders who supported this work through their contributions to the CGIAR Trust Fund, and those who supported bilaterally: https://www.cgiar .org/funders. The report was led by the Portfolio Performance Unit, with expert technical support from the Food Security Evidence Brokerage. We gratefully acknowledge the contributions and insights from many CGIAR staff who provided access to source materials, selected prominent themes, and reviewed drafts. This included Impact Area Platform Directors, regional leaders, CGIAR Center assessment and monitoring specialists, the Independent Advisory and Evaluation Services, the Donor Relations and Business Development unit, the Communications and Advocacy unit, CGIAR research leaders and senior
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt2]
+of information on how climate mitigation is covered in the Portfolio. There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. There is a lack of information on how orphan and opportunity crops and pulses are covered in the Portfolio. There is a lack of information on how
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p33pt2]
+is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. N/A There is a lack of information on how orphan and opportunity crops and pulses are covered in the Portfolio. N/A There is a lack of information on how youth and social inclusion (that does not relate to gender) is covered in the Portfolio. N/A There is a lack of information on how capacity sharing (as it relates to internal learning and decolonization of research) is covered in the Portfolio. Capacity sharing is foundational to
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p39pt4]
+more details on ToC, Areas of Work, etc. We have significantly reworked and streamlined the research questions. They are now underpinned by the assumptions formulated in the revised ToC these also serve as hypotheses (in terms of fulfilled assumptions) for the research questions. Linkages with other Programs and Accelerators A concern is how the accelerator will effectively work with and build on other capacity sharing activities at CGIAR (with other Programs and Accelerators) without duplication or competition (pp. 85). The Accelerator will include a matrix analysis of Programs and other Accelerator during inception, to map Programs’ AoW and its own AoW, in order to define common interests in research questions or challenges, synergies, alignments, complementarities, and avoid duplication of actions. Section 8 of the inception report details how the accelerator would work with other programs to ensure synergy, and avoid duplication and support complementarity in terms of delivery of its service portfolio.
+---
+[ID: pdf:Type3_2024Report.pdf:p6pt1]
+2.2. Close-out of the 2022-24 Portfolio As the 2022-24 Portfolio closed, close-out guidelines were designed to ensure a smooth transition to the new Portfolio, building on past achievements while maintaining continuity in science and innovation delivery. The close-out process focused on the timely preparation and submission of 2024 technical and financial reports, ensuring all CGIAR teams and partners met Portfolio deliverables, and facilitating effective engagement and continuous communication with stakeholders. Proactive mitigation measures were identified to manage risks associated with the transition to the new research Portfolio. Focus was placed on sustaining partnerships beyond the conclusion of the 2022-24 Portfolio to ensure ongoing collaboration. The guidelines included a section on SGPs to ensure alignment. This structured approach ensures that the achievements and collaborations of the 2022-24 cycle are seamlessly integrated into the new Portfolio. 2.3. Transitioning to the 2025-30 Portfolio Support was provided to the CGIAR Portfolio Transition Team, which included the development of Inception Guidelines that outlined the principles and processes to assist Transition Teams in planning and achieving inception deliverables for the 2025-30 CGIAR Portfolio. In 2024 work began on developing a new Technical Reporting Arrangement for 2025-30 (TRA 25-30) to define the Technical Reporting requirements for the next CGIAR Portfolio. A cross-CGIAR working group – comprising Center experts and System functions – led its development. The TRA 25-30 will promote progressive alignment between reporting requirements for pooled and non-pooled
+---
+[ID: pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p30pt4]
+S4I will map scaling efforts across Programs to reduce duplication, achieve synergies, and strengthen system-wide coherence.
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt2]
+outcomes and i mpacts of the whole portfolio through progressive alignment of reporting on w3/bilaterally funded components with a common framework. • Line of sight: The TRA is designed to meet the needs of diverse funders, ensuring transparency and accountability by linking investment to results, both for pooled and non-pooled funds. • Impact focus: Research results will be better linked to CGIAR’s 2030 targets using enhanced impact area indicators. Impact assessments will be integrated into Program/Accelerator design. The use of geographically-bounded targets will be explored for priority locations. A robust approach to project cross-Portfolio benefits by Impact Area for different funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified reporting: Overly complex requirements will be avoided, aiming to
+---
+[ID: pdf:Type3_2024Report.pdf:p2pt4]
+reviewed and validated by the authors to ensure accuracy, coherence, and alignment with the original intent. Acknowledgements This work is part of the CGIAR System Organization. We would like to thank all funders who supported this research through their contributions to the CGIAR Trust Fund:
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p32pt1]
+Genebanks Accelerator Inception Report 31 10. Addressing feedback on selects topics Concise summary of feedback Details on how the Program/ Accelerator has addressed or will address this feedback (in the Inception Phase or beyond) There is a lack of information on how water systems are covered in the Portfolio. N/A There is a lack of information on how climate mitigation is covered in the Portfolio. N/A There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. The Genebanks proposal noted that activities will lead to a stronger overall global system of international and national institutions, policies, and mechanisms contributing
+---
+[ID: pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p25pt1]
+Food Frontiers and Security Program | Inception Report 25 operational efficiency, avoid duplication, and generate broader, more context-responsive insights than either program could produce alone, delivering greater value to partners and stakeholders across the CGIAR portfolio. Together with The Climate Action SP,
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt3]
+funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified reporting: Overly complex requirements will be avoided, aiming to reduce the reporting burden on Centers. Technical Report products include the following: • A Results Dashboard including AI functionalities will be updated several times a year (e.g. quarterly) to offer funders and partners closer to real-time data. • Annual Program/Accelerator Technical Reports will be complemented by an Annual Portfolio Report which will convey progress by Impact Area, geographic and thematic priorities and include information on CGIAR’s internal practice change and learning. • Portfolio outcomes and impacts will be consolidated in a specific report every 3 years. Evidence of CGIAR contributions to impact will be synthesized and regularly updated through an
+---
+[ID: docx:Standard Provisions 2026.docx:u103-106]
+Intellectual Property rights. The System Organization and each Center will, respectively, ensure that necessary intellectual property rights are obtained to allow the rights referred to under this paragraph 6 to be granted. If third party copyright restrictions or attribution requirements apply to such documents, this will be indicated on the documents. Monitoring and Evaluations General Funders will manage their monitoring and evaluation requirements with respect to the CGIAR Portfolio, collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to conduct duplicative evaluations, provided that Funders providing Window 3 Funds may require supplemental monitoring and evaluations with respect to Window 3 Funds, the costs of which, including the internal costs to the System Organization or Center, would be paid by the requesting Funder.
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1pt2]
+reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. Prepared by; Content developed by the Portfolio Performance Unit in collaboration with a x- CGIAR working group and System Council Strategic Impact Monitoring and Evaluation Committee members. Note to readers: 2024 Annual Technical Reports including the 2022-24 Type 2 Report are
+---
+[ID: pdf:Type3_2024Report.pdf:p8pt4]
+other organizations as well as by funders. “CGIAR’s efforts to mainstream scaling put it at the cutting edge …” compared to other research and innovation organizations, and development organizations generally (Global Scaling Community of Practice). Figure 5: A pile of LEGO pieces that represents CGIAR’s innovation portfolio management pre-2022. What was once a fragmented system is now becoming more structured and strategic. Until 2022, there was no efficient way to manage ‘’CGIAR’s innovation portfolio’’. Innovation data was scattered, not up-to-date and lacked evidence. Furthermore, there was no operational framework to track or support scaling for impact. It led to organizational risks and inefficiencies as leadership, partners and funders could not easily access CGIAR innovations. This changed under the CGIAR 2030 Research and Innovation Strategy that embraced a more systematic and evidence-based innovation management based on principles of the Scaling Readiness approach. Currently, information on more than 1,325 innovations under development or use are now easily accessible on the CGIAR Results Dashboard, which is widely used by partners and funders. The World Bank Group, FAO, Gates Foundation, GIZ, ENABEL, and the African Development Bank are among organizations that have embraced (elements of) the CGIAR innovation management approach. CGIAR is actively sharing its innovation portfolio management journey with other organizations. The Gates Foundation partnered with CGIAR to co-develop a protocol for scaling strategies aimed at high-impact innovations. Internally, CGIAR Centers such as the Alliance of Bioversity and CIAT (ABC) and the International Livestock Research Institute (ILRI) and CGIAR projects such as the Accelerate for Impact Platform (A4IP), Technologies for African Agricultural Transformation (TAAT) and HarvestPlus Solutions have adopted elements of innovation portfolio management. May 2025 1110 CGIAR Portfolio Practice Change (Type 3)
+---
+[ID: pdf:Type3_2024Report.pdf:p6pt2]
+2025-30 CGIAR Portfolio. In 2024 work began on developing a new Technical Reporting Arrangement for 2025-30 (TRA 25-30) to define the Technical Reporting requirements for the next CGIAR Portfolio. A cross-CGIAR working group – comprising Center experts and System functions – led its development. The TRA 25-30 will promote progressive alignment between reporting requirements for pooled and non-pooled funding components, and sets expectations for transparency, performance tracking, and accountability across CGIAR and with funders. It will also operationalize the PRMF , inform decision-making, and provide direction for Portfolio-level monitoring, evaluation, learning and impact assessment (MELIA) and the design of the next version of the PRMS. The TRA 25-30 is expected to be endorsed in the first half of 2025. A durum wheat field at Toluca Station. Credit: Alfonso Cortés/CIMMYT Section 3: Implementation Status: Management Responses to CGIAR Evaluations 5. For more information see the CGIAR Evaluation Policy, the CGIAR Evaluation Guidelines, and the Process Note on Developing, Tracking and Reporting on Management Responses to Evaluations. A Management Response is a formal mechanism through which Evaluation Recommendations are addressed by management. These responses are designed to ensure that Evaluations inform decision-making, enhance organizational effectiveness, promote learning, and strengthen accountability. They include time-bound commitments from management to implement Evaluation Recommendations and are systematically followed up as outlined in the CGIAR Evaluation Policy, which identifies follow-up as a critical component of the evaluative process.5 Since
+---
+[ID: pdf:Portfolio Narrative_2024.pdf:p87pt2]
+2025–2030 The creation of a Scaling for Impact Program in CGIAR’s Portfolio 2025–2030 creates even more space and resources for innovation and scaling work. The Scaling for Impact Program plays an important role in catalyzing innovation scaling on the ground with CGIAR colleagues and partners while more System-wide innovation portfolio management functions continue to be delivered by CGIAR’s Portfolio Performance Unit. In CGIAR’s 2025–2030 Portfolio (Figure 6.4), innovation management is not just a process or tool — it is the central instrument for driving coherence and collaboration between the Science Programs and the Scaling for Impact Program while also aligning demand with supply and guiding strategic Portfolio priorities. Figure 6.4. Schematic overview of the CGIAR 2025–2030 Portfolio. CGIAR’s Portfolio Performance Unit and Project Coordination Unit work closely with the Scaling for Impact Program to deliver key innovation portfolio management functions for the 2025–2030 Portfolio. These two units continue to mainstream innovation and scaling tracking and performance across the
+---
+[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p26pt2]
+to national policy research ecosystems through coordinated capacity sharing activities. A prime example of this effective coordination and the efficiencies it generates is the policy program hub in Kenya. This hub actively coordinates with other CGIAR Programs, Accelerators, and individual CGIAR Centers building on efforts that the CGIAR country convener for Kenya had started. It therefore also provides an integration mechanism with W3/bilateral projects. Coordination is fundamental for avoiding duplication of efforts: They serve as a critical platform to share research plans, identify synergies, and proactively prevent overlapping activities, thereby ensuring a highly efficient deployment of collective resources across various CGIAR programs in Kenya. Beyond internal CGIAR coordination, the Kenya hub takes a leading role in planning joint policy dialogue series, country policy notes, bringing diverse stakeholders together for impactful co- design and co-implementation.
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p33pt1]
+Capacity Sharing Accelerator Inception Report 33 10. Addressing feedback on select topics Only one feedback (lack of information on how capacity sharing) applies directly to the CapSha Accelerator. Concise summary of feedback Details on how the Program/ Accelerator has addressed or will address this feedback (in the Inception Phase or beyond) There is a lack of information on how water systems are covered in the Portfolio. N/A There is a lack of information on how climate mitigation is covered in the Portfolio. N/A There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4]
+CGIAR Results Framework – Portfolio Outcome
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p22pt4]
+and outcomes. It will assess whether these projects introduce innovations or partnerships that can be scaled through the core program, or whether integration challenges persist. 5. Internal Learning and Use of MELIA Results (Type: Other MELIA activity – focused on adaptive management and learning use) This evaluation will focus on how MELIA findings—especially from studies and monitoring efforts—are being used for decision-making at AoW and program levels. It will assess the enabling and limiting factors for evidence uptake across teams. 6. Portfolio-Level Nutrition Contribution (Type: Program/project evaluation) This evaluation will assess how the CGIAR Portfolio, including Better Diets and Nutrition and related P/A, contributes to system -wide IA on Nutrition targets. It will also explore how synergies or duplication arise across programs and identify areas for collective learning. Findings will inform CGIAR-level ToC for the IA on Nutrition
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p12pt3]
+those data flows will form part of ongoing engagement with the Genebanks. • Streamline results reporting requirements The reporting burden will be minimized by a) critically assessing each data field against requirements, b) where a data field is required, AI augmented solutions will be among the support provided to results submitters. MELIA: Program and Accelerator MELIA plans wil l be informed by the Evaluability Assessment Framework, and will ad here to standards such as quality theories of change, SMART indicators, baselines where relevant, and the development and use of a monitoring plan. Guidance and support to Programs and Accelerators will be provided through the inception phase to ensure standardization, coherence and quality. Indicator rationalization and toolkit: Recognizing that Portfolio components including w3 and bilateral projects will continue to have specific indicator requirements,
+---
+[ID: pdf:Portfolio Narrative_2024.pdf:p5pt3]
+business cycle, showcasing both the immediate outcomes of 2024 and the broader trajectory of the Portfolio’s contributions to CGIAR’s strategic goals. By presenting both annual and multiyear insights, the report underscores the cumulative impact of CGIAR’s work and sets the stage for the transition to the 2025–2030 Portfolio. Role within the broader Technical Reporting framework CGIAR Technical Reporting fulfils the System-level programmatic reporting requirements set out in the Standard Provisions annexed to the Funding Agreement or Arrangement signed between each Funder and the System Organization.2 The Portfolio Narrative serves as the synthesis layer of CGIAR’s Technical Reporting system, and is a key component of the 2024 Technical Report, which comprises: • Type 1 Initia tive, Impact Platform, and SGP Reports: These annual reports present progress toward end-of-Initiative/Impact Platform/SGP outcomes and provide quality-assured results accessible via the CGIAR Results Dashboard. • The Type 3 C GIAR Portfolio Practice Change Report: Highlights operational and strategic progress in Portfolio performance and project coordination and innovation portfolio management. • The Type 2 C GIAR Impacts in Agrifood Systems: Evidence and Learnings from 2022-2024: This report offers a high-level summary of CGIAR’s contributions to its
+---
+[ID: pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p11pt1]
+11 reviews, promoting context-speciﬁc prioritization, reducing duplication, and enhancing the responsiveness and legitimacy of CGIAR’s scaling portfolio. Further details on this point will be further updated in subsequent iterations of the MELIA plan. 6. Reporting Reporting is a critical process for both internal and
+---
+[ID: pdf:Portfolio Narrative_2024.pdf:p5pt2]
+of CGIAR’s Technical Reporting Arrangement. It offers a synthesis of Portfolio coherence, synergies, and collective progress across Initiatives, Impact Platforms, and Science Group Projects (SGPs)1, which represent approximately 40 percent of CGIAR’s Portfolio by dollar value. The report does not include Center-managed bilateral projects. As a key pillar of the Technical Report, the Portfolio Narrative integrates data and insights from CGIAR’s Results Dashboard, the Type 1 Initiative, Impact Platform, and SGP Reports, and the Type 3 Portfolio Practice Change Reports to demonstrate how CGIAR has advanced research delivery, fostered partnerships, and addressed global challenges. As 2024 marks the final year of this Portfolio and the 2022–2024 business cycle, the 2024 CGIAR Portfolio Narrative takes a dual approach to its analysis and reporting. Alongside highlighting key achievements, strategic shifts, and operational progress for 2024, the report also provides a cumulative overview of the three-year business cycle, showcasing both the immediate outcomes of 2024 and the broader trajectory of the Portfolio’s contributions to CGIAR’s strategic goals. By presenting both annual and multiyear insights, the report underscores the cumulative impact of CGIAR’s work and sets the stage for the transition to the 2025–2030
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt2]
+These parameters also allow the Integrated Partnership Board to fulfil its responsibility under the CGIAR System Charter to report on programmatic performance of CGIAR Research on an annual basis. • Provides, through the establishment of common technical reporting principles, enabling tools and mechanisms, progressive alignment and synergy between the technical reporting requirements that apply to components of the CGIAR Portfolio that are funded by Pooled Funding and those that apply to the components that are funded by other sources of funds (“Non-Pooled Funding”). • Sets transparency, performance tracking, and accountability expectations between CGIAR System Funders and CGIAR including Centres, • Informs decision making at different levels, underpins research management, operationalizes the Performance and Results Management Framework (PRMF), and guides portfolio -level MELIA and the design of the next Performance and Results management
+---
+[ID: pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p10pt4]
+at the request of partners. These relate to the UN Food Systems Summit (UNFSS) process, which started in 2021, and the Coalition of Action on Healthy Diets from Sustainable Food Systems for Children and All, in particular; the 3rd International Agrobiodiversity Congress; and the next 10-year Comprehensive Africa Agriculture Development Program. The Program’s engagement provides opportunities to disseminate and discuss evidence from research to influence policy processes and decisions, to multiply this to countries other than our 15 countries, and to adjust and adapt research to new and cross-cutting priorities including climate and biodiversity. Funder engagement Regularly talking with funders to hear their views will be a priority. The Leadership Team will organize an annual call for all funders and quarterly calls with the group of funders who are keen to discuss our work in more detail. The Leadership Team expects to work closely with bilateral fundraising efforts of CGIAR Centers to bring additional bilateral resources to the
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt1]
+Gender Equality and Inclusion Accelerator Inception Report 29 10. Addressing feedback on select topics Concise summary of feedback Details on how the Program/ Accelerator has addressed or will address this feedback (in the Inception Phase or beyond) There is a lack of information on how water systems are covered in the Portfolio. There is a lack of information on how climate mitigation is covered in the Portfolio. There is a lack of information on
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p6pt4]
+the initial Minimum Data Standard proposed by Center MEL Focal Points and approved by the GST for integrating the top 80% by Center portfolio value 2025 w3/bilateral results into 2025 Program, Accelerator and Portfolio Technical Reports. • Additionally, provide the capability for optional submission of W3/bilateral Technical Reports into 2025 Program, Accelerator and Portfolio Technical Reports to simplify reporting requirements and consolidate information. Where Technical Reports are shared for integration, Centers will have a role in reviewing and validating how their information is represented in aggregate Program/Accelerator and Portfolio reporting.
+---
+[ID: docx:Standard Provisions 2026.docx:u22-25]
+monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions. Window 3 Funds. Window 3 Funds are directed by Funders to individual Centers. Funders may designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization.
+---
+[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p28pt2]
+nexus and directly works with Ministries of water, irrigation, climate change, environment and agriculture to co-design more resilient water and food futures across countries in South and Central Asia, Sub-Sahara Africa and globally. There is a lack of information on how climate mitigation is covered in the Portfolio. The contribution to this important portfolio-wide issue from the policy program is mainly from AoW1 that includes CO2 emissions as one of the main indicators for measuring mitigating in several of its products, including the RIAPA modeling framework. AoW4 also covers the effects of climate change on food systems and includes solar-irrigation and other water- related mitigation action in its nexus solution portfolio. There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. Analyzing trade-offs and synergies and deriving related prioritization and policy recommendations is at the
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt2]
+Reports are shared for integration, Centers will have a role in r eviewing and validating how their information is represented in aggregate Program/Accelerator and Portfolio reporting. 5. A set of Impact Studies responding to the CGIAR Results Framework and key strategic questions from Funders/Partners/Global Leadership will be integrated into the design and delivery of the Programs &amp; Accelerators; W3/bilaterals may contribute to these. 6. Funders and Centers will be able to adopt more/fully aligned monitoring and reporting approaches for their w3 and bilateral projects during development. It will also be possible to increase alignment during the implementation of a w3/bilateral project through e.g. the contribution to Impact Case Studies. 7. Common CGIAR best of class indicators, data collection protocols, tools, and systems will be promoted for use in W3/bilateral project design. The CGIAR Monitoring, Evaluation and Learning Community of
+---
+[ID: pdf:Portfolio Narrative_2024.pdf:p1pt1]
+CGIAR Portfolio Narrative 2024
+---
+[ID: pdf:Portfolio Narrative_2024.pdf:p87pt3]
+Performance Unit and Project Coordination Unit work closely with the Scaling for Impact Program to deliver key innovation portfolio management functions for the 2025–2030 Portfolio. These two units continue to mainstream innovation and scaling tracking and performance across the CGIAR System through instruments such as CGIAR’s Technical Reporting Arrangement and Performance and Results Management Framework. And these units also support evidence-based Portfolio prioritization through the office of CGIAR’s Chief Scientist. The Scaling for Impact Program supports innovation demand-supply alignment, works with other parts of CGIAR on more hands-on and in-situ innovation bundling and packaging activities, and supports the design, financing, and implementation of scaling strategies with partners. An effective innovation portfolio management approach will be critical to maximizing the impact of the new CGIAR Portfolio of Programs and Accelerators. In December 2024, CGIAR convened internal and external stakeholders to co-create a vision for innovation management for the CGIAR 2025–2030 Portfolio. Representatives from the Independent Science for Development Council,
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p26pt1]
+AoW Integration and ToC Optimization We will assess whether the current configuration of AoW operations —especially AoW2 and AoW3—can be optimized to contribute to shared outcomes. This analysis will draw on field-level implementation in selected countries (e.g., Bangladesh, Benin, Ethiopia, Ghana, Honduras, Kenya, Nigeria, Tanzania, or Uganda). Recommendations will be brought to the attention of program leadership to inform ToC adjustments in 2026. Value Addition of the W3/Bilateral Projects In countries where bilateral projects are active, we will assess whether and how these projects contribute to program-level HLOs and outcomes. The study will identify quick wins for integration and propose mechanisms to avoid duplication of monitoring effo rts. Findings will support portfolio management decisions and help shape the design of future bilateral engagements. Portfolio-Level Nutrition Contribution Lastly, we will conduct a portfolio -level review of how the CGIAR Portfolio contributes to the Nutrition Impact Area Targets, with a focus
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt4]
+evidence gaps are also being identified, and the Accelerator is continuing to engage with young farmers and young farmer groups. Starting in 2025, it will be vital to identify more resources to implement a more ambitious agenda on social inclusion and gender. Initial discussions have started with some funders. There is a lack of information on how capacity sharing (as it relates to internal learning and decolonization of research) is covered in the Portfolio.
+---
+[ID: docx:Guidance on reporting outputs or outcomes.docx:u10-13]
+The following questions could help to clarify whether a product is an output (direct and controlled) or an outcome (influenced and external): Who controls the results Who has control over this product or result? Was this directly produced by the research team (output)?
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p8pt2]
+● Deploy AI-enabled analytics to transform how users explore and select germplasm. ● Centralize and integrate data tools, platforms, and service pipelines to create a seamless user experience fr</t>
+  </si>
+  <si>
+    <t>[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]
+el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]
+business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]
+Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]
+at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and
+---
+[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2]
+II) ICRISAT AOW02 Digital Advisories and Climate Risk Management $89,064 N-343001-GCAN INITIATIVE IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $1,321,123 N-601158-SPIR II IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $201,213 PJ-003953: APPUI A LA TRANSFORMATION ET A LA RESILIENCE DES SYSTEMES ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]
+- 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness" 411,914 "Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 "Andean Crop Diversity for Climate Change P-1560-DGUL" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 "Youth, Citizen Science and E-commerce:
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4]
+Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations, and evidence-based programs for enhancing inclusive informal food markets that effectively create quality jobs for young women and men and deliver safe and healthy foods in urban environments University of Peradeniya, Wayamba University of Sri Lanka, Asian Development Bank, World Food Programme International Food Policy Research Institute 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents CGI21-507031-PORB-Food Frontiers and Security.indd 24CGI21-507031-PORB-Food Frontiers and Security.indd 24 29/07/2025 19:3929/07/2025 19:39
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u52-56]
+Aryal, Bishal (IFPRI) 44:47 Thank you. Thank you. Nirmal, Rajalakshmi (IFPRI) 44:50 Thank you. Bye, bye. Trifa, Nicoleta (CGIAR System Organization) 44:53 Hi. Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción
+---
+[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]
+2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción
+---
+[ID: docx:2025 Technical Reporting Information (Session 1).docx:u43-45]
+Colomer, Julien (One CGIAR - France) 48:19 Thanks. Hurt, Chris (ILRI) 48:19 Thank you. Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u1-4]
+2025 Technical Reporting Information (Session 2)-20250729_150218-Meeting Recording 29 de julio de 2025, 1:02p.m. 47 min 36 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 32 of 90 August 2025 | CGIAR Contracted partner Center Current Status of Partnership Area of Work Title and Number High level output (If Available) Dirección de Coordinación Regional y Extensión Rural (DICORER) CIMMYT Potential AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Fundación para la Innovación Tecnológica Agropecuaria y Forestal
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]
+nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.
+---
+[ID: pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3]
+Frameworks for Climate Services PLACA Climate Action Platform for Agriculture in Latin America and the Caribbean / La Plataforma de Acción Climática en Agricultura de Latinoamérica y el Caribe PMU Program Management Unit PPU Portfolio Performance Unit PRMS Performance and Results Management System REMET Reducing Methane Emissions from Rice project ROI Return on investment S4I Scaling for Impact (Program) SA South Asia SB
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p25pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 25 of 44 Partner Center Area of Work Title and Number High level output (If Available) Local Governments for Sustainability, Nairobi City County, Dhaka North City Corporation, Local Government of Quezon City (Philippines), RUAF Foundation International Potato Center / Centro Internacional de la Papa 3.5.5 Urban food systems governance - Delivering knowledge products, evidence and capacity sharing with policy makers to guide interventions aimed at strengthening
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt1]
+Capacity Sharing Accelerator Inception Report 4 ISNAR International Service for National Agricultural Research ISRA Institut Sénégalais de la Recherche Agricole (Senegalese Agricultural Research Institute) ITU International Telecommunication Union KOICA Korea International Cooperation Agency KPIs Key Performance Indicators. MELIA Monitoring, Evaluation, Learning, and Impact Assessment NARES National Agricultural Research and Extension Systems NARS National Agricultural Research System PCT Program Coordination Team
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt2]
+&amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Fundación para la Innovación Tecnológica Agropecuaria y Forestal (FUNDIT) Guatemala CIMMYT Potential AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Indian Council of Agricultural Research (ICAR) CIMMYT Potential AoW 2 - Pathways to Scale in Agrifood Systems Advanced Chemical Industries (ACI), Bangladesh CIMMYT Potential AoW 2 - Pathways to Scale in
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3]
+(INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID DEPLOY Institut National pour l'Etude et la Recherche Agronomiques (INERA) - RDC CIMMYT AB, ID DEPLOY Instituto de Investigação Agronómica (IIA) - Angola CIMMYT AB, ID DEPLOY Instituto de Investigación Agropecuaria de Panamá CIMMYT AB, ID STRATEGIZE/REFOCUS, PARTNER / TRANSFORM, OPTIMIZE / ACCELERATE, CREATE Invicta Agritech India Private Limited CIMMYT ID DEPLOY JAMSONI COMPANY LIMITED CIMMYT ID DEPLOY Jardins da Yoba CIMMYT ID
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p36pt4]
+metrics, monitoring and evaluations. HLO 5.3: Curated analytics for innovation portfolio management and decision-making, including Scaling Readiness evaluations and customized assessment tools for target countries, both ongoing and as part of the annual adaptive management process, to ensure continuous learning and improvement Foundation SpectAct, Morocco ICARDA Existing AoW 3 - Enabling Environment Lab Institut National de la Recherche Agronomique a Tunisie (INRAT) ICARDA Existing AoW 3 - Enabling Environment Lab CGI21-508007-PORB-Scaling for Impact.indd 36CGI21-508007-PORB-Scaling for Impact.indd 36 07/08/2025 13:2407/08/2025 13:24
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt2]
+(SME) Private Ltd CIMMYT ID DEPLOY IFFA Seed Co Ltd CIMMYT ID DEPLOY Indian Institute of Maize Research CIMMYT AB, ID DEPLOY Indo American Hybrid Seeds (India) Pvt. Ltd CIMMYT ID DEPLOY Institut de Recherche Agricole pour le Développement (IRAD) CIMMYT AB, ID DEPLOY Institut des Sciences Agronomiques du Burundi (ISABU) CIMMYT AB, ID DEPLOY Institut National de la Recherche Agronomique du Niger (INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt2]
+Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The World Bank, German Red Cross (Germany), Dhaka City North Corporation, Nairobi City County, International Water Management Institute, WorldFish International Food Policy Research Institute 1.2.2 Evidence Synthesis and Adaptive Learning - Co-develop knowledge products and action plans, and identify key investment and innovation priorities for stakeholders and partners to guide interventions aimed at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt2]
+la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics (Breeding for Tomorrow) ● T-PJ-003670- Long-term funding of Ex Situ collections of germplasm (IITA) (Breeding for Tomorrow and CapSha) ● L-LTG001-Long term funding of ex situ collections of germplasm (ILRI) (Breeding for Tomorrow) ● R-A-2023-9-Genebank-AI (Breeding for Tomorrow) ● T-PJ-003575: Cassava Allele Mining Project: (IITA) Mining useful alleles for climate change adaptation in the cassava from CGIAR Genebanks (Breeding for Tomorrow and Climate Action) ● T-PJ-003576- (IITA) Mining useful alleles for climate change adaptation cowpea (Cowpea Allele mining project: Mining useful alleles for climate change adaptation in cowpea from CGIAR Genebanks (year 2022-26) (Breeding for Tomorrow, CapSha, and Climate Acti on) ● T-PJ-004017-VACS (IITA): Vision for Adapted Crops and Soil: Bambara Groundnut (Breeding for Tomorrow, CapSha and
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt3]
+International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations, and evidence- based programs for enhancing inclusive informal food markets that effectively create quality jobs for young women and men and deliver safe and healthy foods in urban environments $454,738 T-PJ-003812-ETH/IITA - CITY REGIONS FOOD SYSTEMS, RUNRES (TH International Institute of Tropical Agriculture Urban Food Systems - AOW3 3.1.1 Safe urban food production - Evidence- based innovations and business models to improve safe, nutritious, and
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2]
+de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation Globally (AOW05) High Level Output 5.4. Unique crop diversity under threat is safeguarded through the integration of in situ and ex situ conservation strategies 50,000 "Revealing the Diversity of Barley Quality Traits through Synergies between On-farm Practices and Technological Innovations D-100735" ICARDA Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 237,008 Long Term Partnership Agreement ICARDA Biodiversity
+---
+[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt3]
+ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance Contract IITA AOW02 Digital Advisories and Climate Risk Management T-PJ-003517: Chicken, Fish and Pigs Feed and Organic Fertilizer Value Chain Development Using BSF-Based Urban Biowaste Processing in Ghana, Mali, Niger and the Democratic Republic of Congo IITA AOW03 Locally-led Adaptation, AOW04 Low- emission Transitions $470,249 L-CIA023-Accelerating Impacts of CGIAR Climate Research for Africa II ILRI AOW01 Prioritization
+---
+[ID: pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 13 of 86 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD FRANCE – FFEM Promover Oportunidades Sostenibles en la Cadena de Valor del Cacao de Excelencia (IA Lead of A1537) Alliance Bioversity CIAT AoW 3-Markets and Business Models; AoW 5-Gender Equality, Social Inclusion and Fairness Intermediate Outcome - AOW-IOC 3.2. Local producer organizations, national and sub-national public actors and private sector actors co-design or strengthen inclusive business models; 2030 Outcome - 2030 OC-4. Marginalized people participate in implementing innovations; 2030 Outcome - 2030 OC-3 Government, market and finance actors implement
+---
+[ID: pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt3]
+Lebanese Agriculture Research Institute (LARI), Institut National De La Recherche Agronmique en Tunisie (INRAT) IFPRI, Alliance, ICARDA Area of Work: Accelerating Solutions for Impact 1.4.3: Evidence on effectiveness of solutions for inclusive leadership TBD GENDER Accelerator Area of Work: Accelerating Solutions for Impact 1.5.1: Analysis of constraints and pathways for youth in FLWS n/a n/a Area of Work: Accelerating Solutions for Impact 1.5.2: Co-designed approaches to engaging youth in FLWS n/a n/a Area of Work: Accelerating Solutions for Impact 1.5.3: Evidence on effectiveness of approaches to engaging youth in FLWS AGRA, IFAD, FAO, WFP IFPRI Area of Work: Accelerating Change Through Evidence 2.1.1: Guidance on ethical gender research AGRA, IFAD,
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p36pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 36 of 86 August 2025 | CGIAR External collaborations/partners Center Area of Work Title and Number High level output (If Available) L’Institut Tchadien de Recherche Agronomique pour le Développement – ITRAD – Chad CIMMYT AB, ID, MI, Enable l’Institut National de la Recherche Agronomique du Niger – INRAN – Niger CIMMYT AB, ID, MI, Enable Ministry of Agriculture and Food Security – MAFS – Sudan CIMMYT AB, ID, MI, Enable MyAgro – USA CIMMYT ID National Agricultural Research Organization
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]
+Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2
+---
+[ID: pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt2]
+Solutions for Impact 1.4.1: Tools for measuring women's voice and leadership ActionAid, NOIPolls, University of Malawi, IPOR, Tropenbos, CBD Women's Caucus, The Indigenous Partnership China, UNEP - NBSAP Accelerator Partnership, Fondation Spect'Act, Oxfam IFPRI, Alliance, ICARDA Area of Work: Accelerating Solutions for Impact 1.4.2: Strategies for increasing women's voice and leadership Mormon Church, George Washington University, Evaluasi, CARE, LoftyInc, PRADAN, SkillGreen, Odisha State Ministry of Agriculture, Bangladesh Ministry of Agriculture, SEWA, Ethical Tea Partnership, Action Aid, Foundation for Ecological Security, Volcafé, Oxfam Morocco, Lebanese Agriculture Research Institute (LARI), Institut National De La Recherche Agronmique en Tunisie (INRAT) IFPRI, Alliance, ICARDA Area of Work: Accelerating Solutions for Impact 1.4.3: Evidence on
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1]
+23 Bilateral Contribution to Multifunctional Landscapes MELIA Studies UK FCDO - Seed to tree: value chains and partnerships for resilient restored forests in Malaysia • Actor engagement and outcome tracking UK – GCBC (UK-Defra) - Deploying Diversity as a Strategic Asset for Scaling of Ethiopia’s Green Legacy Initiative for Climate Change Resilience and Livelihoods • Program learning review • Actor engagement and outcome tracking FRANCE – FFEM Promover Oportunidades Sostenibles en la Cadena de Valor del Cacao de Excelencia (IA Lead of A1537) • Actor engagement and outcome tracking CoIMPACT INDIA • Program learning review Fruitful Lands India Phase II • Actor engagement and outcome tracking Sustainable Investments for Large-scale Rangeland R • Actor engagement and outcome tracking Building Community
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p55pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 55 of 86 External collaborations/partners Center Area of Work Title and Number High level output (If Available) Arab Center for the Studies of Arid Zones and Dry Areas - ACSAD ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing Institut National de la Recherche Agronomique de Tunisie; National Agricultural Research Institute of Tunisia - INRAT ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing Institut National de Recherche Agronomique de Tunisie. INRAT. ICARDA AoW2, AoW3 HLO: Accelerate - Stage2 &amp; Stage 3 testing &amp; Deploy Ankara University, Faculty of Agriculture ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 23 of 86 External collaborations/partners Center Area of Work Title and Number High level output (If Available) Mekere University IRRI AB AB HLO: Strategize, Partner , Discover , Accelerate Iramba District Agricultural Office IRRI AB AB HLO: Strategize, Partner , Discover , Accelerate University of Nairobi IRRI AB AB HLO: Strategize, Partner , Discover , Accelerate Institut Nationale pour l'Etude et la Recherche Agronomique (INERA), Congo IRRI AB AB HLO: Strategize, Partner , Discover , Accelerate Service National de Semences (National Seed Service) -SENASEM
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p53pt4]
+testing Società Italiana Sementi S.p.A - SIS ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing Ministry of Agriculture - MoA Jordan ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing National Agricultural Research Center (National Center for Agricultural Research and Extension) - NARC (NCARE) ICARDA AoW2, AoW3 HLO: Accelerate - Stage2 &amp; Stage 3 testing &amp; Deploy Krasniy Vodopad Agricultural Experiment Station ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing Institute National de la Recherche Agronomique de Morocco - INRA Morocco ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing CGI21-508008-PORB-Breeding for Tomorrow.indd 53CGI21-508008-PORB-Breeding for Tomorrow.indd 53 08/08/2025 16:0208/08/2025 16:02
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt3]
+Bolivia CIMMYT Phenotyping ZARI - Zambia Agricultural Research Institute, Zambia CIMMYT Phenotyping INIA Chile -Instituto de Investigaciones Agropecuarias, Chile CIMMYT Phenotyping INIA Uruguay -Instituto Ncional de Investigacion Agropecuaria, Uruguay CIMMYT Phenotyping IRESA - Institution de la Recherche et de l’Enseignement Supérieur Agricoles, Tunisia CIMMYT Phenotyping TAGEM - Ministry of Food Agriculture and Livestock, Turkey CIMMYT Phenotyping KALRO- Kenya Agricultural &amp; Livestock Research Organization, Kenya ARIA, Afghanistan CIMMYT Phenotyping-Int Nurseries ITGC, Algeria CIMMYT Phenotyping-Int
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p40pt4]
+CIMMYT ID DEPLOY Ethio Agri CEFT PLC CIMMYT ID DEPLOY Ethio VegFru Plc (ETVF) CIMMYT ID DEPLOY Ethiopian Agricultural Business Corporation (EABC) CIMMYT ID DEPLOY Ethiopian Institute of Agricultural Research (EIAR) CIMMYT AB, ID STRATEGIZE/REFOCUS, PARTNER / TRANSFORM, OPTIMIZE / ACCELERATE, CREATE Ets . Baraka CIMMYT ID DEPLOY Ets Bika la Menagère CIMMYT ID DEPLOY Ets FAS-NK CIMMYT ID DEPLOY Ets SEMKI CIMMYT ID DEPLOY CGI21-508008-PORB-Breeding for Tomorrow.indd 40CGI21-508008-PORB-Breeding for Tomorrow.indd 40 08/08/2025 16:0208/08/2025
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt2]
+et la Recherche Agronomique (INERA), Congo IRRI AB AB HLO: Strategize, Partner , Discover , Accelerate Service National de Semences (National Seed Service) -SENASEM Mozambique IRRI AB AB HLO: Strategize, Partner , Discover , Accelerate Bangladesh Rice Research Institute IRRI AB AB HLO: Strategize, Partner , Discover , Accelerate Punjab Agricultural University IRRI AB AB HLO: Strategize, Partner , Discover , Accelerate Acharya NG Ranga Agricultural University IRRI AB AB HLO: Strategize, Partner , Discover , Accelerate Aranya Agricultural Alternatives IRRI ID ID HLO: Position, Deploy, Track Indira Gandhi Krishi Vishwavidyalaya IRRI ID ID HLO: Position, Deploy, Track Indian
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt4]
+and Specialist Services (DR&amp;SS), Zimbabwe CIAT ID ID HLO: Position, Deploy, Track, Power Institut des Sciences Agronomiques du Burundi (ISABU), Burundi CIAT ID ID HLO: Position, Deploy, Track, Power Instituto Nacional de Innovación Agraria (INIA), Peru CIP ID ID HLO: Deploy Universidad de Huancavelica, Peru CIP ID ID HLO: Deploy Asociación YANAPAI, Peru CIP ID ID HLO: Deploy Universidad Nacional Agraria La Molina (UNALM), Peru CIP ID ID HLO: Deploy Instituto de Investigación Nutricional (IIN), Peru CIP ID ID HLO: Deploy CGI21-508008-PORB-Breeding for Tomorrow.indd 50CGI21-508008-PORB-Breeding for Tomorrow.indd 50 08/08/2025 16:0208/08/2025 16:02
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p32pt3]
+Semillas La Fuerte SA, Mexico CIMMYT Phenotyping-Int Nurseries Fertilizantes Tepeyac, Mexico CIMMYT Phenotyping-Int Nurseries INRA-Morocco, Morocco CIMMYT Phenotyping-Int Nurseries ICARDA-Morocco, Morocco CIMMYT Phenotyping-Int Nurseries ARI - Chokwe Research Station, Mozambique CIMMYT Phenotyping-Int Nurseries Department of Agricultural Research , Myanmar CIMMYT Phenotyping-Int Nurseries NWRP , NARC, Nepal CIMMYT Phenotyping-Int Nurseries WIERSUM Plantbreeding BV, Netherlands CIMMYT Phenotyping-Int Nurseries National Agricultural Research Institute of Niger (INRAN), Niger CIMMYT Phenotyping-Int Nurseries Dan Dicko Dankoulodo Univ., Niger CIMMYT Phenotyping-Int Nurseries Lake Chad
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p32pt2]
+LLP Kazakh RI of Ag &amp; Plt Grow, Kazakhstan CIMMYT Phenotyping-Int Nurseries The Kyrgyz Research Institute of Livestock and Pasture, Kyrgyzstan CIMMYT Phenotyping-Int Nurseries NAFRI, Laos CIMMYT Phenotyping-Int Nurseries Misurata Agric. Res. Stn., Libya CIMMYT Phenotyping-Int Nurseries Pixus Agriculture Malawi Ltd., Malawi CIMMYT Phenotyping-Int Nurseries INIFAP , Mexico CIMMYT Phenotyping-Int Nurseries ICAMEX, Mexico CIMMYT Phenotyping-Int Nurseries Agroq. y Semillas La Fuerte SA, Mexico CIMMYT Phenotyping-Int Nurseries Fertilizantes Tepeyac, Mexico CIMMYT Phenotyping-Int Nurseries INRA-Morocco, Morocco CIMMYT Phenotyping-Int Nurseries</t>
+  </si>
+  <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: According to the Annex pie chart, what was total 2024 revenue and the split by funding source?\n\nContext:\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 6\nContent: Research results can be defined according to the nature of the change and the control over it.\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p14]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 14\nContent: Figure 1: Research results according to the kind of change and the control over it.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 23 Annex 2: ISDC feedback relating to pooled &amp; non-pooled alignment5 This section provides a direct extract from the ISDC Feedback on CGIAR Portfolio Narrative 2025- 2030. Comments relating to the alignment of pooled and non -pooled have been extracted from the broader set of comments. They have not been edited to e.g. update Program and Accelerator nomenclature. • Articulation of how the Portfolio, including bilateral and W1 funding, will be bundled into Megaprograms is still lacking. Bilateral funding is restricted and is provided for a specific purpose and with specific intended impacts. This needs to be honored a nd the lack of flexibility in shifting those funds into other areas should be clearly acknowledged. • Alignment of the entire Portfolio with the CGIAR 2030 Research and Innovation Strategy needs to be strong and explicit. How will management ensure that bilateral funding delivers against this Strategy? In addition: o What happens if a bilateral project is not strongly aligned with the Strategy and how will CGIAR ensure that opportunity costs are covered? o Will all bilateral projects across all Centers be mapped to support the Portfolio? • A challenge that should be acknowledged is incorporating bilateral funding into Megaprograms. Each Megaprogram and Accelerator will be large scale and staff will be consumed by the implementation of contracted work. Trying to build Megaprogram linkages in parallel with bilateral funding should be additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative 2025-2030\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p5]\nFile: Type3_2024Report.pdf\nLocation: page 5\nContent: Section 2: Portfolio Performance and Project Coordination Progress 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022-2024. 3. Science Group Projects (SGPs) are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance and fiduciary oversight. 4. EiB II will report through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they will provide a concise, high-level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the technical reports. 2.1. Technical Reporting Arrangement 2022-24 CGIAR Technical Reporting fulfils the System-level programmatic reporting requirements set out in the Standard Provisions annexed to the Funding Agreement or Arrangement signed between each Funder and the System Organization.2 The 2024 Technical Report includes the following Initiatives, Impact Platforms and SGPs3: • All 32 Initiatives • Five Impact Platforms – Gender Equality, Youth and Social Inclusion – Environmental Health and Biodiversity – Nutrition, Health and Food Security – Climate Adaptation and Mitigation – Poverty Reduction, Livelihoods and Jobs • Six SGPs – Accelerated Varietal Improvement and Seed Delivery of Legumes and dryland Cereals in Africa (AVISA) – Roots Tubers and Banana (RTB) Breeding – Accelerating Genetic Gain and Varietal Replacement in Rice - Phase 2 (AGGRi 2) – Excellence in Breeding (EiB) II: Cross-Crop Support Services for Breeding Acceleration4 – Accelerating Crop Improvement Through Genome Editing 2023-2025 – Climate Adaptation Insight For 2024, CGIAR will produce and deliver a total of 46 Technical Reporting outputs: • March 2025: Results from 2024 published on the online CGIAR Results Dashboard (1). • May 2025: Publication of 42 Type 1 (32 x Initiative reports; 5 x Impact Platform reports; 5 x SGP reports) Reports and a Type 3 Report (1). • End of June 2025: Publication of the Portfolio Narrative (1). • End of June 2025: Publication of the Type 2 Report: CGIAR Contributions to Impact in Agrifood Systems (2022-24) (1). Each of these reports is released separately and will be available in PDF format. 2024 Technical Reporting covers USD 370 million (USD 322 million for Initiatives and Impact Platforms, and USD 49 million for W3 SGPs), representing nearly 40 percent of CGIAR’s total pooled and non-pooled funding for 2024. 2.1.1. Streamlining the process and adding value to stakeholders In 2022 CGIAR launched a new 2022-24 Technical Reporting Arrangement, co-developed with the System Council’s Strategic Impact Monitoring and Evaluation Committee (SIMEC). The 2022 rollout was regarded as a “first pancake” or trial phase, establishing minimum viable functionality and setting the foundation for annual improvements. Key achievements of 2022 Technical Reporting included the adoption of a common report template aligned with the Technical Reporting Arrangement for Initiatives and Impact Platforms; integration with CGIAR’s Results Framework; digital linking of results to theories of change (TOCs); and the introduction of quality assurance processes mediated by third parties. Additionally, a new interactive CGIAR Results Dashboard was launched, and the Performance and Results Management System (PRMS) – an online reporting system – was developed, alongside adaptive management processes and the rollout of Innovation Packages and Scaling Readiness plans. Building on this, 2023 Technical Reporting incorporated lessons from a 2022 Learning and Optimization process, documented in a 2022 Learning and Optimization report. Key advancements included transitioning to “Always on” reporting by opening the PRMS from September 2023, more than doubling the reporting window compared to 2022 and allowing greater flexibility for Initiatives, Impact Platforms, and SGPs. Quality assurance was optimized through four staggered batches across 2023 and 2024. Further enhancements included expanding per-result tagging to all five Impact Areas. A Risk Management Module was launched to support risk identification and reporting at the Initiative level. A large number of participants joined training sessions to support reporting, dashboard use, and onboarding, and the rapid uptake of adaptive management strengthened strategic agility, with positive feedback from across the Portfolio. The Research Plans of Results and Budgets section of the CGIAR website was updated to ensure easy open access to Initiative, SGP and Impact Platform Plans of Results and Budgets (PORBs). The 2024 reporting cycle continued this trajectory, integrating insights from the 2023 Learning and Optimization process and Action Plan to further refine CGIAR’s Technical Reporting processes and products. Key improvements in 2024 included: • Launching the PRMS Planning Module to support the replan process: The launch of an online Planning Module synchronized TOC and Planning data in the PRMS, improving the efficiency and quality of planning workflows. Enhanced replan guidelines were provided to help Initiatives, Impact Platforms, and SGPs implement 2023 Reflect recommendations and align budget forecasts with updated budget envelopes. To support continuous learning and adaptive management, a user experience survey on the Planning Module was conducted to assess effectiveness and inform user-centered enhancements for the 2025-30 Portfolio. • Further simplifying reporting processes and tools: A series of enhancements to PRMS functionalities were implemented to improve efficiency and usability. Improved filtering options, enhanced notification systems, and more clearly structured result PDFs now enable quicker access to relevant information. Innovation Packages and Scaling Readiness language and templates were simplified. Reporting was streamlined and modified to suit the final year of reporting for the Portfolio, with an Outcome Indicator Module co-developed with input from Initiatives, Impact Platforms and SGPs to provide them with the opportunity to assess their progress against targets for Work Package outcomes and end-of-Initiative outcomes; summative and yearly highlights were combined into a single report; and adaptive management processes removed. • Improving decision-making within the PRMS: Broader engagement from PRMS testers across reporting entities and Senior Program Managers was integrated into PRMS feature development, ensuring that system updates were aligned with user needs and supported consistent decision-making. • Enhancing product clarity: The Type 1 Annual Report template was reviewed to better accommodate end-of-Initiative outcome reporting for the final year of the Portfolio. Improvements to the Results Dashboard were made to enhance the accessibility of IPSR insights. • Strengthening quality assurance: Examples include updated and enhanced QA guidance, and updated guidance on Impact Area tagging. An AI tool was prototyped and tested on a series of data fields, with the intent to leverage lessons learned and develop an enhanced AI tool that can be applied to a broader set of reported data and integrated into the PRMS, supporting both the reporting and QA phases. • Developing the Semantic Natural Language Processing Aggregator Platform (SNAP): SNAP is an AI-powered tool enhancing access to and analysis of CGIAR’s reported outputs, outcomes, and impacts. It improves access to Portfolio information and results evidence through semantic searches, thematic clustering, and automated summaries, complementing the CGIAR Results Dashboard. SNAP-supported narratives were integrated into the CGIAR 2024 Portfolio Narrative, and ongoing refinements will further enhance its role in Portfolio reporting. • Further integrating SGPs and Impact Platforms: Between 2022 and 2024, CGIAR progressively aligned these entities with its Technical Reporting processes and common systems to enhance consistency and coherence. In 2023, three Impact Platforms – Nutrition, Health and Food Security; Climate Adaptation and Mitigation; and Environmental Health and Biodiversity – were onboarded alongside the Gender Equality, Youth and Social Inclusion Impact Platform (which reported in 2022), each receiving tailored support such as TOC and results framework development. The SGP pilot launched in 2023 further expanded CGIAR’s reporting ecosystem by integrating Center-specific Window 3 awards, with two SGPs submitting first-year results using the PRMS Reporting Tool and Type 1 Report template. In 2024, integration expanded to include the Poverty Reduction, Livelihoods and Jobs Impact Platform and four additional SGPs, further broadening the reporting ecosystem. • Enhancing risk management through the PRMS Risk Module: The Risk Management Module, launched in 2023 to support Initiative management and reporting of risks, was further enhanced in 2024, allowing Initiatives to capture transition-focused risks. It enabled Initiatives to review, update, or close risks, contributing to the design of the 2025-30 Portfolio. The updated Risk Management Module will be used by Programs and Accelerators from 2025 onward. Climate-Smart Village set-up under the Adaptation and Mitigation Initiative in Agriculture (AMIA) of the Department of Agriculture. Credit: Miguel Mamon/CIAT May 2025 54 CGIAR Portfolio Practice Change (Type 3) Report 2024\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 4\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 4 1. Technical Reporting Arrangement purpose, scope, value proposition, delivery and optimization, Purpose The purpose of th e Technical Reporting Arrangement 2025 -2030 (“TRA 25-30”) is to set out the technical reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. The TRA 25-30: • Provides the parameters that e nable the Centers, the CGIAR System Partners and the System Organization to fulfil their technical reporting obligations under the funding agreements that apply to the use of Window 1 and Window 2 funds from the CGIAR Trust Fund (“Pooled Funding”). These parameters also allow the Integrated Partnership Board to fulfil its responsibility under the CGIAR System Charter to report on programmatic performance of CGIAR Research on an annual basis. • Provides, through the establishment of common technical reporting principles, enabling tools and mechanisms, progressive alignment and synergy between the technical reporting requirements that apply to components of the CGIAR Portfolio that are funded by Pooled Funding and those that apply to the components that are funded by other sources of funds (“Non-Pooled Funding”). • Sets transparency, performance tracking, and accountability expectations between CGIAR System Funders and CGIAR including Centres, • Informs decision making at different levels, underpins research management, operationalizes the Performance and Results Management Framework (PRMF), and guides portfolio -level MELIA and the design of the next Performance and Results management System (PRMS). The current Technical Reporting Arrangement that applies to the CGIAR Portfolio during the period 2022-24 (“TRA 22-24”) was co-developed by CGIAR and System Council/Strategic Impact Monitoring and Evaluation Committee (SIMEC) members in 2022. A new TRA is needed to match 2025-30 portfolio parameters, notably the alignment of pooled and non-pooled funding sources, and to apply lessons learnt from 2022-24. Scope The TRA 25-30 provides the operational and enabling basis to plan, monitor, learn and report on the 25-30 Portfolio. It is designed to progressively enable Programs and Accelerators, Centers and their research teams to report on the pooled, bilaterally and W3-funded components of the 2025- 30 portfolio in an integrated and aligned way, without increasing reporting burdens of Centers and Scientists. Going forward, the CGIAR Integrated Partnership will work towards progressively greater alignment of W3/bilateral projects and programs with the 2030 outcomes and theories of change of the Programs and Accelerators. Centers will provide key agreed information on their W3/bilaterally funded projects and programs to enable Program/Accelerator leaderships to explore ways to achieve alignment based on, inter alia, complementarity of results as well as actual or potential thematic, geographic, and partnership overlaps. Reporting on and attribution\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 5\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results framework, underpinned by a new Technical Reporting Arrangement, will provide robust, continuous performance and results reporting across all funding sources, as well as adaptive management of the Portfolio. 1 Value Proposition The TRA 25-30: - Creates value by delivering an integrated approach that tracks the performance of each Program and Accelerator, - Brings together the inputs (including costs), outputs, outcomes and impacts of the total portfolio to allow for easier and more robust Return on Investment (ROI) calculations. - Avoids creating a significant additional and duplicative layer of complex reporting requirements for W3/ bilaterally funded work. - Informs decision making through providing ready access to demand-driven quality raw and curated data products. Delivery The TRA 25 -30 will be delivered in line with Management arrangements for CGIAR’s 2025 —30 science and innovation Portfolio. Specific roles and responsibilities will be defined in 2025. 1 CGIAR Portfolio Narrative, 1 November 2024\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:p7]\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 7\nContent: Trifa, Nicoleta (CGIAR System Organization) 0:48 Yep. OK, good. So thank you. This session is the first of two session plans for today, planned for today, with the second being scheduled later at 3:00 PM CET to accommodate colleagues in other time zones. Technical reporting. My name is Nicoletta Trifa. By the way, I'm part of the Portfolio Performance Unit, the support unit within the Office of the Chief Scientist. Here is an overview of what we'll cover in the next minutes. I believe my presentation will take 2025 minutes and then we'll leave room for questions at the end, if that's OK. So what we'll cover an update of the technical reporting arrangements 2025 to 2030, priorities and changes for 2025, a brief introduction on the annual technical report and the neighbors. So this mean the performance and results. Management system and the quality assurance, the technical reporting timeline, available resources and support and what's next and how to stay engaged. I want to mention that this session marks the start of the conversation around 2025 technical reporting. We want to give you the early look at the key priorities and plans for the months ahead, and the goal is to make sure that you stay informed, prepared and supported with a clear understanding of upcoming deliverables and timelines. And also clarity on who to reach out to if you have questions or if you need help along the way. Good. Technical reporting arrangements for the new portfolio. The 2025 to 2030 portfolio has been approved by the CGR Global Leadership team on in June 2025 and provides the operational basis to plan, monitor, learn and report. On the new portfolio. It is designed to progressively enable programs, accelerators and centers to report on the pooled and window 3 bilateral projects of the new portfolio in an integrated and aligned way without increasing the burden on centers and the scientists. Main changes compared to the previous technical reporting arrangements, streamline reported reporting. So less products, more integration, lower transaction costs, stronger impact, focus results. To be clearly linked and packaged under impacts, outcomes and associated agreed indicator targets and better linkages between the theory of change or so plan of results and budget and technical reporting. The primary audiences for technical reporting are funders and CGR staff at integrated partnership, portfolio and program and accelerator levels. A secondary audience is the partners. Annual technical reporting covers the individual annual technical reports for program and accelerators, as well as a portfolio view of aggregate contribution to thematic and geographic targets. And relevant content from this technical reports are integrated into the CJR corporate reporting. In terms of the 2025 technical reporting priorities, 2025 is a transition year with technical reporting arrangements, implementation again focusing on streamlined reporting and on strengthening the linkages between theory of change. Porb, media and technical reporting. As many of you know, in the previous portfolio these components were not properly linked, so it was a bit challenging to demonstrate progress against the theory of change or the plans, as you know. In terms of deliverables for 2025. These are the program and accelerator technical reports, which are due in April 2026, the portfolio narrative, which is due in 2026 in June. Integration of top 80% of window tree and bilateral projects by central dollar value into reporting and planning. Application of the minimum data standards for window tree and bilateral reporting. And mapping of refinement during the pause and reflect process which will take place early Q 1/20/26. So as I was mentioning, this year is seen more as a transition year towards KPI based planning and reporting and efforts are underway to enable planning and reporting at the KPI level, which is aligned with the system office objective and key results for 2026 and 20. These are to be confirmed, so they haven't been confirmed yet, but I've pasted them here so that you can see the 2026 objective and key results for the system office. So 100% program and accelerate the work plans and budget. An annual technical report. Which provide for software enabled monitoring of erformance and results against smart Ki by center, ear and ooled funds invested. So next year, 80% of centres, CGR, window three and bilateral funded work by value included in 2025 technical reports and then the following year in 2027, this will increase to 90% of centres. Window 3 and bilateral funded work included in 2026 technical reports. The following slides, what I have, what I have included in the following slides, it's a brief introduction into. What is expected in terms of deliverables from programs and accelerators together with an overview of the performance and results management system and the QA. I realized that some in this call some of you are already familiar with the reporting arrangements from the previous portfolio. While for others this might be entirely new. So our goal is to bring everyone to the same level of understanding so that we can move forward with clarity and shared expectations for the 2025 technical reporting. OK, so technical reporting for program and accelerator. We'll focus on three key deliverables. So first is reporting results, the 2025 results in the Performance and Reporting Management system, PRMS. Each program accelerator and mapped window 3 project will report 2025 results in the system and we strongly encourage to report results that were planned and budgeted. So results which have been included in the reports. As the outdated technical reporting system will allow for tracking results against plans. Secondly is the quality assurance of reporting results. As you know, the results submitted go through the quality assessment process and we will share more details on this process in the timeline in an info session scheduled for later. Which we will schedule later in in September, October and the quality assess results will be available on the results dashboard. Inform the pause and reflect and will be included in the technical reports in the annual technical reports. A third deliverable for program and accelerators is drafting estimation of the 2025 Annual Technical Report. So each program and accelerator is responsible for drafting and internally validating quality assessing their 2025 Annual Technical Report. Before submitting it to the PPU, so to the perform portfolio performance unit. Again, guidance on this, the detailed process and validation process will be shared with you timely. Also to support this process, an AI generated V0 draft will be provided as a starting point. The annual technical reports. What are they? This the annual technical report. The the the aim is to make them short, so to 20 to 30 pages, concise and targeted. They provide assurance on annual program accelerator delivery against the boards, so plan of results and budget and progress on theory of change. They are based on quality assess results, the template guidance and as I mentioned and. AI V0 will be provided to all rogram and accelerator teams. Annual technical reports need to be submitted by each program and accelerator in March, April, so more details on this will follow and publication is intended to happen end of April, beginning of May. Here to the right side you have the. Content of the annual the proposed content for the annual technical report as per the technical reporting arrangements. Many of you will notice that there are not no big changes compared to previous portfolio, so the idea is to have a fact sheet and executive summary. The annual progress on theory of change, area of work details, a section on results, section on partnerships, portfolio linkages, adaptive management and then one key result story. But again, we will plan a detailed deep dive session on the annual technical report template and the guidance. So there will be time for you to ask questions in detail about about this and to receive support obviously. I've also included here for reference links to the 2024 Annual Technical Reports from the initiatives and impact platforms, and also a link to the 2024 Portfolio Narrative Report. In case you want to, you want to have a look to see, um, what it captures. PRMS. So this stands for Performance and Results Management System is the system the the the the environment where results need to be submitted. Again, the team is working on updating their resources. There will be. New users onboarding decks created with the links to different information and I I believe the PCU Alison together with the program coordinators. Are. The all the PRMS roles. So PCU is leading a work to define the PRMS roles and to get the information from program and accelerators regarding who from each program accelerator should have what role in PRMS. To enable us to to provide the right access to the platform when the time comes to report. Quality assurance process. So results submitted by program and accelerators in the PRMS will be quality assessed by a quality assessment team in February 2026. Your participation in this process is required. Guidance and resource resources will be provided and also an info session will be scheduled later this year. What is the QA? It is a process that aims to improve the quality of the reported data to provide consistency across the system, ensure reliability of reported results. Inform the learning process and improve the overall CGR accountability and transparency. Quality assess data informs the reflect process which takes place early Q12026, the results dashboard. So once the quality assessment of the results is finalized, the quality assess results will be pushed to results dashboard. You most probably have seen that. Reading. It also informs and are the results. The practices results are included in the annual report, in the portfolio narrative, and then in the overall CGIR annual report. In terms of the the timeline, so we have this info session now to provide an overview on the technical reporting and there will be several other info session and deep dive scheduled. Throughout September and October of reporting 2025 results, we believe that it will be feasible to open the PRMS in November for program and accelerators to to report. The date is still to be confirmed. We're aiming to to, yeah, to meet to to to end November. Hopefully this will be this is feasible from the technical side quality assurance. It's planned for February 2026 reflect process as I was mentioning Q 1/20/26 and then annual technical reports are due in March, April 2026 as well. Where to find information pertaining to technical reporting and planning and media? There is a one stop shop for for um all this. It's called the Performance and Results Hub. I'm gonna stop sharing cause I wanna share. Um, I'm gonna stop sharing the deck. I wanna. We could resent the hub. I'm not going to go through each section, but at least. So that you can see for those who are new more specifically to see and we will also share the link obviously the performance and results hub as I was mentioning it has detail on reporting, planning, reflect, replan. So you come in here, you click on 2025 reporting and then you will have access to the latest information, to the timeline, latest update, upcoming events. So all the information, information. Session dates will be listed here. We'll also have a subsection here with. Recording from from meetings, so that will be posted. For example today after this session we'll post a recording and the deck here for you to access and there is a section on frequently asked question. We recycled a couple of questions from the previous portfolio and updated them so that they are applicable to the program and accelerator teams, so feel free to go here and and browse. As resources become available, we will place them here and we will notify you by e-mail. OK. Going back to my deck. Which? In terms of engagement plan, so in order to streamline communication and optimize support for program accelerators and centers with mapped window 3 bilateral projects, we will send bi-weekly emails to everyone in this. This goal with key updates on technical reporting, with reminders and also with the latest questions and answers available on the hub. There will be targeted emails focusing on specific categories within the program accelerators. We want to engage with some of you on technical reporting, revisions, developments. And the aim is to gather feedback from you. Program coordinators will be copied on these emails. Info session. So a specific topic and we'll plan info session on specific topics, for example the standard indicator, description shades, the guidance on technical reporting, quality assurance. Reporting on innovations, the PRMS, so deep dive on the PRMS, the updates, the tool and so on. And during the reporting phase and the QA we will have weekly drop-ins. So this drop-ins is there will be no presentation. Presentation during the during this drop-ins. The purpose is for us to provide live support, so to answer your questions on the spot and the primary focus will be as I was mentioning, reporting and the QA. For if you know for every question you have, we invite you to use this e-mail address performanceandresults@cgr.org. This is the. The e-mail address we use for all technical reporting questions. So you have the questions right to us at performanceandresult@cjr.org and you will receive a response. We are aiming to respond within the 24 hours. Just to give an example, you know going back here I've gotten the targeted targeted emails and feedback. So this is a good example on for example how we plan to engage and get get feedback from from you on the PRMS enhancements so. Usually we send there's an e-mail sent to invite you to provide feedback on a o</t>
   </si>
   <si>
@@ -928,6 +1239,15 @@
   </si>
   <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: What is the 2025–30 Impact Assessment (IA) strategy addressing, and what will be delivered to funders and managers?\n\nContext:\n\n---\n\n[ID: docx:Engagement Plan 2025 Technical Reporting.docx:u46-49]\nLink: https://docs.google.com/document/d/1bxyVhlOayJqgreqiv4xhOu9xQ3Vz3Ymg/edit\nFile: Engagement Plan 2025 Technical Reporting.docx\nLocation: section 'Fortnightly update emails' paragraph 80 to section 'Fortnightly update emails' paragraph 83\nContent: CGSpace Team Lead KM Managers Curators/Repository Managers PRMS Team\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p29pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 29 part 4\nContent: The current funding landscape uncertainty as well as a realistic assessment of resources that can be dedicated to IA led us to prioritize IA activities in 6 countries, where we can easily leverage on human and financial resources for impact assessment: Colombia, Peru, Tunisia, Kenya, India, Vietnam. The site prioritization, as well as prioritization of the key impact indicators that the IA should target (potential indicators are presented in the table below), will be a specific action of the MELIA team at the end of 2025, when future financial capacity will be clearer. Further funding for IA studies will be sought in 2026 and during the implementation of\n\n---\n\n[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1]\nLink: https://docs.google.com/presentation/d/1iH7kEQrUqQywkG9wVkCCBq_tRp-d1Ws0/edit?slide=id.p1#slide=id.p1\nFile: Information Session on 2025 Technical Reporting.pptx\nLocation: slide 2 part 1\nContent: Agenda Technical Reporting Arrangement 2025-30 Technical reporting priorities for 2025 What\n\n---\n\n[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_MELIA Plan 30-06-2025.pdf\nLocation: page 8 part 4\nContent: exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved. Impact assessments are conducted after an intervention has been completed and are used to substantiate claims of sustained results. They seek to measure impact at scale, i.e., benefits to a large number of people/large areas of land. It employs both quantitative and qualitative methods, often combined for deeper insights. IA goes beyond monitoring indicators to evidenced attribution of observed changes to CGIAR interventions. IA will help to ensure that Programs/Accelerators contribute meaningfully to CGIAR’s Results Framework and the 2025–30 Portfolio objectives.\n\n---\n\n[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_MELIA Plan 30-06-2025.pdf\nLocation: page 8 part 3\nContent: the learnings and what are other critical areas that require further focused support? (AoW 5) Evaluation collaboration plans Genebanks will seek to collaborate with the Multifunctional Landscapes Program to study in situ and on farm site monitoring of diversity conservation. Genebanks will also collaborate with the Crop Trust and Aarhus University to review the Scientific Impact of the Seed Quality Management and Quality Management System Communities of Practice. Collaborations with W3/bilateral projects will be explored during phase 2 of the mapping exercise. 4. Impact assessment Impact assessment (IA) is assessment that estimates the causal effects of research outputs and related activities and assesses the magnitude of impact achieved.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p10pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 10 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 10 Thematic Impact 2022-30 Report The Thematic Impact 2022 -30 Report provides a m acro level view of CGIAR’s role in Food, Land and Water System Transformation covering the period 2022 -30. It will be released in 2031. Its format and content will be developed during the period 2025-30. Results Dashboard • The Results Dashboard will be enhanced to better present curated information a gainst Impact Area targets, geographies and key topics. • Headline impacts and outcomes will be more clearly communicated in the Dashboard. • Using AI, users will be able to easily query the results data and underlying sources of evidence data using\n\n---\n\n[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p2pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 2 part 3\nContent: Impact assessment (IA) .............................................................................................................. 13 Program impact overview .................................................................................................................... 13 IA activities and collaboration plans ..................................................................................................... 14 IA studies ........................................................................................................................................... 15 5. Learning and adaptive management ........................................................................................... 16 Learning ............................................................................................................................................. 16 Annual review and adaptive planning ...................................................................................................\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 17 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 17 The amount of quality information sourced from different funding sources, and the coherence between those different information sources will increase over time (specific metrics and targets to be developed) 6. Impact Assessment Strategy/ Approach/ Case studies CGIAR will develop a 2025 -30 Impact Assessment Plan and integrate its design, budgeting and delivery into the 25-30 Portfolio. The bottom-up approach to impact assessment that has been used within CGIAR for the past decades has not produced sufficient quantity or quality of studies to prov ide evidence against CGIAR impact indicators. SPIA fills in some of this gap, but even their new undertaking of country studies will likely not be able to contribute to most of the indicators\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p25pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 25 part 1\nContent: • Bilateral/W3-funded projects: to identify embedded impact assessment opportunities and avoid duplication. • CGIAR IA teams : to contribute to portfolio -level meta -evaluation and harmonize data with common CGIAR indicators. Priority will be given to impact in integrative countries, where multiple AoWs operate. These broader IA studies will assess the synergies between interventions and provide system -level insights into the pathways driving impact. Potential integrative countries include Bangladesh, Ethiopia, Nigeria, and Tanzania, based on portfolio density and MELIA feasibility. A senior Impact Specialist will guide study design and implementation, ensure alignment with the CGIAR results framework indicators, and coordinate data quality assurance across IA efforts. Impact assessment studies The Program has identified initial IA study themes for inclusion in the MELIA studies. However , these initial themes are not included in the\n\n---\n\n[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 3\nContent: activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable\n\n---\n\n[ID: pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p2pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP03%20%2D%20Sustainable%20Animal%20and%20Aquatic%20Foods%2FSustainable%20Animal%20and%20Aquatic%20Foods%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP03%20%2D%20Sustainable%20Animal%20and%20Aquatic%20Foods&amp;p=true&amp;ga=1\nFile: Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf\nLocation: page 2 part 2\nContent: ................................ ................................ ............... 7 Data collection strategy ................................ ................................ ................................ 7 3. Evaluation plan ................................ ................................ ................................ ..................... 7 Evaluation studies ................................ ................................ ................................ ....... 7 Evaluation collaboration plans ................................ ................................ ....................... 8 4. Impact assessment ................................ ................................ ................................ ............... 8 Program/Accelerator impact overview ................................ ................................ ............ 8 IA activities and collaboration\n\n---\n\n[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p18pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 18 part 3\nContent: All the knowledge generated by these studies will be available not only to Program managers, but also researchers, the CGIAR community, and external stakeholders. Finally, analyzing monitoring data will be a continuous process, and results, along with recommendations, will be made available to Program managers to make any necessary adjustments to the Program implementation. Annual review and adaptive planning The Climate Action Program will implement an annual review and adaptive planning process, building on the experience and lessons from the 2022–24 CGIAR Portfolio and aligned with evolving guidance on the Reﬂect and Re-Plan processes. Each year, the Program will conduct structured annual performance reviews at both program-wide and AoW levels. These reviews will assess progress toward the intended outputs and outcomes, using both quantitative and qualitative data drawn from the CGIAR Performance and Results Management System"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant. Preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If the information is not obtainable, respond with the exact phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: Who coordinates funders’ M&amp;E requirements across the CGIAR Portfolio and how is duplication avoided?\n\nContext:\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23 part 4\nContent: additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 2 part 4\nContent: report is part of the CGIAR System Organisations’ technical reporting arrangement. We would like to thank all funders who supported this work through their contributions to the CGIAR Trust Fund, and those who supported bilaterally: https://www.cgiar .org/funders. The report was led by the Portfolio Performance Unit, with expert technical support from the Food Security Evidence Brokerage. We gratefully acknowledge the contributions and insights from many CGIAR staff who provided access to source materials, selected prominent themes, and reviewed drafts. This included Impact Area Platform Directors, regional leaders, CGIAR Center assessment and monitoring specialists, the Independent Advisory and Evaluation Services, the Donor Relations and Business Development unit, the Communications and Advocacy unit, CGIAR research leaders and senior\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 29 part 2\nContent: of information on how climate mitigation is covered in the Portfolio. There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. There is a lack of information on how orphan and opportunity crops and pulses are covered in the Portfolio. There is a lack of information on how\n\n---\n\n[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p33pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_Inception Report 30-06-2025.pdf\nLocation: page 33 part 2\nContent: is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. N/A There is a lack of information on how orphan and opportunity crops and pulses are covered in the Portfolio. N/A There is a lack of information on how youth and social inclusion (that does not relate to gender) is covered in the Portfolio. N/A There is a lack of information on how capacity sharing (as it relates to internal learning and decolonization of research) is covered in the Portfolio. Capacity sharing is foundational to\n\n---\n\n[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p39pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_Inception Report 30-06-2025.pdf\nLocation: page 39 part 4\nContent: more details on ToC, Areas of Work, etc. We have significantly reworked and streamlined the research questions. They are now underpinned by the assumptions formulated in the revised ToC these also serve as hypotheses (in terms of fulfilled assumptions) for the research questions. Linkages with other Programs and Accelerators A concern is how the accelerator will effectively work with and build on other capacity sharing activities at CGIAR (with other Programs and Accelerators) without duplication or competition (pp. 85). The Accelerator will include a matrix analysis of Programs and other Accelerator during inception, to map Programs’ AoW and its own AoW, in order to define common interests in research questions or challenges, synergies, alignments, complementarities, and avoid duplication of actions. Section 8 of the inception report details how the accelerator would work with other programs to ensure synergy, and avoid duplication and support complementarity in terms of delivery of its service portfolio.\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p6pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 6 part 1\nContent: 2.2. Close-out of the 2022-24 Portfolio As the 2022-24 Portfolio closed, close-out guidelines were designed to ensure a smooth transition to the new Portfolio, building on past achievements while maintaining continuity in science and innovation delivery. The close-out process focused on the timely preparation and submission of 2024 technical and financial reports, ensuring all CGIAR teams and partners met Portfolio deliverables, and facilitating effective engagement and continuous communication with stakeholders. Proactive mitigation measures were identified to manage risks associated with the transition to the new research Portfolio. Focus was placed on sustaining partnerships beyond the conclusion of the 2022-24 Portfolio to ensure ongoing collaboration. The guidelines included a section on SGPs to ensure alignment. This structured approach ensures that the achievements and collaborations of the 2022-24 cycle are seamlessly integrated into the new Portfolio. 2.3. Transitioning to the 2025-30 Portfolio Support was provided to the CGIAR Portfolio Transition Team, which included the development of Inception Guidelines that outlined the principles and processes to assist Transition Teams in planning and achieving inception deliverables for the 2025-30 CGIAR Portfolio. In 2024 work began on developing a new Technical Reporting Arrangement for 2025-30 (TRA 25-30) to define the Technical Reporting requirements for the next CGIAR Portfolio. A cross-CGIAR working group – comprising Center experts and System functions – led its development. The TRA 25-30 will promote progressive alignment between reporting requirements for pooled and non-pooled\n\n---\n\n[ID: pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p30pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact%2FScaling%20for%20Impact%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact&amp;p=true&amp;ga=1\nFile: Scaling for Impact_Inception Report 30-06-2025.pdf\nLocation: page 30 part 4\nContent: S4I will map scaling efforts across Programs to reduce duplication, achieve synergies, and strengthen system-wide coherence.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt2]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 3 part 2\nContent: outcomes and i mpacts of the whole portfolio through progressive alignment of reporting on w3/bilaterally funded components with a common framework. • Line of sight: The TRA is designed to meet the needs of diverse funders, ensuring transparency and accountability by linking investment to results, both for pooled and non-pooled funds. • Impact focus: Research results will be better linked to CGIAR’s 2030 targets using enhanced impact area indicators. Impact assessments will be integrated into Program/Accelerator design. The use of geographically-bounded targets will be explored for priority locations. A robust approach to project cross-Portfolio benefits by Impact Area for different funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified reporting: Overly complex requirements will be avoided, aiming to\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p2pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 2 part 4\nContent: reviewed and validated by the authors to ensure accuracy, coherence, and alignment with the original intent. Acknowledgements This work is part of the CGIAR System Organization. We would like to thank all funders who supported this research through their contributions to the CGIAR Trust Fund:\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p32pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 32 part 1\nContent: Genebanks Accelerator Inception Report 31 10. Addressing feedback on selects topics Concise summary of feedback Details on how the Program/ Accelerator has addressed or will address this feedback (in the Inception Phase or beyond) There is a lack of information on how water systems are covered in the Portfolio. N/A There is a lack of information on how climate mitigation is covered in the Portfolio. N/A There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. The Genebanks proposal noted that activities will lead to a stronger overall global system of international and national institutions, policies, and mechanisms contributing\n\n---\n\n[ID: pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p25pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1\nFile: Food Frontiers and Security_Inception Report 30-06-2025.pdf\nLocation: page 25 part 1\nContent: Food Frontiers and Security Program | Inception Report 25 operational efficiency, avoid duplication, and generate broader, more context-responsive insights than either program could produce alone, delivering greater value to partners and stakeholders across the CGIAR portfolio. Together with The Climate Action SP,\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt3]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 3 part 3\nContent: funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified reporting: Overly complex requirements will be avoided, aiming to reduce the reporting burden on Centers. Technical Report products include the following: • A Results Dashboard including AI functionalities will be updated several times a year (e.g. quarterly) to offer funders and partners closer to real-time data. • Annual Program/Accelerator Technical Reports will be complemented by an Annual Portfolio Report which will convey progress by Impact Area, geographic and thematic priorities and include information on CGIAR’s internal practice change and learning. • Portfolio outcomes and impacts will be consolidated in a specific report every 3 years. Evidence of CGIAR contributions to impact will be synthesized and regularly updated through an"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant. Preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If the information is not obtainable, respond with the exact phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: ¿Quién tiene la responsabilidad fiduciaria y programática?\n\nContext:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 2\nContent: el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 3\nContent: business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 1\nContent: Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 1\nContent: Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 1\nContent: CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 3\nContent: at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and\n\n---\n\n[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2]\nLink: https://cgspace.cgiar.org/items/8acc660f-7305-4e4b-ab21-1c192611b017\nFile: CGI21-507032-PORB-Climate Action.pdf\nLocation: page 11 part 2\nContent: II) ICRISAT AOW02 Digital Advisories and Climate Risk Management $89,064 N-343001-GCAN INITIATIVE IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $1,321,123 N-601158-SPIR II IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $201,213 PJ-003953: APPUI A LA TRANSFORMATION ET A LA RESILIENCE DES SYSTEMES ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 10 part 2\nContent: - 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness\" 411,914 \"Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO\" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 \"Andean Crop Diversity for Climate Change P-1560-DGUL\" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 \"Youth, Citizen Science and E-commerce:\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 1\nContent: CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 4\nContent: Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations, and evidence-based programs for enhancing inclusive informal food markets that effectively create quality jobs for young women and men and deliver safe and healthy foods in urban environments University of Peradeniya, Wayamba University of Sri Lanka, Asian Development Bank, World Food Programme International Food Policy Research Institute 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents CGI21-507031-PORB-Food Frontiers and Security.indd 24CGI21-507031-PORB-Food Frontiers and Security.indd 24 29/07/2025 19:3929/07/2025 19:39\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 2).docx:u52-56]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%202%29%2D20250729%5F150218%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E57e21346%2Dc6ca%2D4c63%2D8839%2D3e2a327c5116\nFile: 2025 Technical Reporting Information (Session 2).docx\nLocation: paragraph 52 to paragraph 55\nContent: Aryal, Bishal (IFPRI) 44:47 Thank you. Thank you. Nirmal, Rajalakshmi (IFPRI) 44:50 Thank you. Bye, bye. Trifa, Nicoleta (CGIAR System Organization) 44:53 Hi. Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%201%29%2D20250729%5F100141%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E76da6c8e%2D6234%2D41ff%2Dba2c%2Dc2068392ed82\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: ¿Quién tiene la responsabilidad fiduciaria y programática?\n\nContext:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 2\nContent: el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 3\nContent: business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 1\nContent: Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 1\nContent: Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 1\nContent: CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 3\nContent: at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and\n\n---\n\n[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2]\nLink: https://cgspace.cgiar.org/items/8acc660f-7305-4e4b-ab21-1c192611b017\nFile: CGI21-507032-PORB-Climate Action.pdf\nLocation: page 11 part 2\nContent: II) ICRISAT AOW02 Digital Advisories and Climate Risk Management $89,064 N-343001-GCAN INITIATIVE IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $1,321,123 N-601158-SPIR II IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $201,213 PJ-003953: APPUI A LA TRANSFORMATION ET A LA RESILIENCE DES SYSTEMES ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 10 part 2\nContent: - 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness\" 411,914 \"Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO\" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 \"Andean Crop Diversity for Climate Change P-1560-DGUL\" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 \"Youth, Citizen Science and E-commerce:\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 1\nContent: CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 4\nContent: Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations, and evidence-based programs for enhancing inclusive informal food markets that effectively create quality jobs for young women and men and deliver safe and healthy foods in urban environments University of Peradeniya, Wayamba University of Sri Lanka, Asian Development Bank, World Food Programme International Food Policy Research Institute 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents CGI21-507031-PORB-Food Frontiers and Security.indd 24CGI21-507031-PORB-Food Frontiers and Security.indd 24 29/07/2025 19:3929/07/2025 19:39\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 2).docx:u52-56]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%202%29%2D20250729%5F150218%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E57e21346%2Dc6ca%2D4c63%2D8839%2D3e2a327c5116\nFile: 2025 Technical Reporting Information (Session 2).docx\nLocation: paragraph 52 to paragraph 55\nContent: Aryal, Bishal (IFPRI) 44:47 Thank you. Thank you. Nirmal, Rajalakshmi (IFPRI) 44:50 Thank you. Bye, bye. Trifa, Nicoleta (CGIAR System Organization) 44:53 Hi. Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%201%29%2D20250729%5F100141%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E76da6c8e%2D6234%2D41ff%2Dba2c%2Dc2068392ed82\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción"}]</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1341,7 +1661,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1353,16 +1673,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1370,7 +1690,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1382,16 +1702,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I3" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1399,7 +1719,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -1411,16 +1731,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1428,7 +1748,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1440,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1457,7 +1777,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1469,16 +1789,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1486,7 +1806,7 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1498,16 +1818,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1515,7 +1835,7 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1527,16 +1847,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="I8" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1544,7 +1864,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1556,16 +1876,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G9" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I9" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1573,7 +1893,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -1585,16 +1905,16 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I10" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1602,7 +1922,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1614,16 +1934,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1631,7 +1951,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -1643,16 +1963,16 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I12" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1660,7 +1980,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -1672,16 +1992,16 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="I13" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1689,7 +2009,7 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -1701,16 +2021,16 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="I14" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1718,7 +2038,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -1730,16 +2050,16 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="I15" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1747,7 +2067,7 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -1759,16 +2079,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I16" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1776,7 +2096,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -1788,16 +2108,16 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="I17" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1805,7 +2125,7 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -1817,16 +2137,16 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="I18" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1834,7 +2154,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1846,16 +2166,16 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="I19" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1863,7 +2183,7 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -1875,16 +2195,16 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1892,7 +2212,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -1904,22 +2224,22 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="J21" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="K21" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1927,7 +2247,7 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -1939,22 +2259,22 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I22" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="J22" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="K22" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1962,7 +2282,7 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -1974,22 +2294,22 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="J23" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="K23" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1997,7 +2317,7 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -2009,22 +2329,22 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="J24" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="K24" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2032,7 +2352,7 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -2044,22 +2364,22 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="J25" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="K25" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2067,7 +2387,7 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -2079,22 +2399,22 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="I26" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="J26" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="K26" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2102,7 +2422,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -2114,22 +2434,22 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="I27" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="J27" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="K27" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2137,7 +2457,7 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -2149,22 +2469,22 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I28" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="J28" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="K28" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2172,7 +2492,7 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -2184,22 +2504,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G29" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I29" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="J29" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="K29" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2207,7 +2527,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -2219,22 +2539,22 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="I30" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="J30" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="K30" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2242,7 +2562,7 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -2254,22 +2574,22 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="I31" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="J31" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="K31" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2277,7 +2597,7 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -2289,22 +2609,22 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G32" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I32" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="J32" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K32" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2312,7 +2632,7 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -2324,22 +2644,22 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G33" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="J33" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K33" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2347,7 +2667,7 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -2359,22 +2679,22 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G34" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="J34" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K34" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2382,7 +2702,7 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -2394,22 +2714,22 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G35" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H35" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="J35" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K35" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2417,7 +2737,7 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -2429,22 +2749,22 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G36" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="J36" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K36" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2452,7 +2772,7 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -2464,22 +2784,22 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G37" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="J37" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K37" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2487,7 +2807,7 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -2499,22 +2819,22 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G38" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="J38" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K38" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2522,7 +2842,7 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -2534,22 +2854,22 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G39" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H39" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I39" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J39" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K39" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2557,7 +2877,7 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -2569,22 +2889,22 @@
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G40" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I40" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J40" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K40" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2592,7 +2912,7 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -2604,22 +2924,22 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G41" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I41" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J41" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K41" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2627,7 +2947,7 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -2639,22 +2959,22 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G42" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H42" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I42" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J42" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K42" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2662,7 +2982,7 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -2674,22 +2994,22 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G43" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="I43" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J43" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K43" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2697,7 +3017,7 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -2709,22 +3029,22 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G44" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="I44" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J44" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K44" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2741,13 +3061,13 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H45" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="K45" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -2755,7 +3075,7 @@
         <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -2767,22 +3087,22 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G46" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="I46" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J46" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K46" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2790,7 +3110,7 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C47">
         <v>100</v>
@@ -2802,22 +3122,22 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G47" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I47" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J47" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="K47" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2825,7 +3145,7 @@
         <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C48">
         <v>100</v>
@@ -2837,22 +3157,162 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G48" t="s">
+        <v>85</v>
+      </c>
+      <c r="H48" t="s">
+        <v>122</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J48" t="s">
+        <v>141</v>
+      </c>
+      <c r="K48" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49">
+        <v>200</v>
+      </c>
+      <c r="D49">
+        <v>200</v>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>76</v>
+      </c>
+      <c r="G49" t="s">
+        <v>86</v>
+      </c>
+      <c r="H49" t="s">
+        <v>123</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="J49" t="s">
+        <v>142</v>
+      </c>
+      <c r="K49" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50">
+        <v>200</v>
+      </c>
+      <c r="D50">
+        <v>43</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>76</v>
+      </c>
+      <c r="G50" t="s">
+        <v>87</v>
+      </c>
+      <c r="H50" t="s">
+        <v>124</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J50" t="s">
+        <v>143</v>
+      </c>
+      <c r="K50" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51">
+        <v>200</v>
+      </c>
+      <c r="D51">
+        <v>43</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>76</v>
+      </c>
+      <c r="G51" t="s">
+        <v>87</v>
+      </c>
+      <c r="H51" t="s">
+        <v>124</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J51" t="s">
+        <v>143</v>
+      </c>
+      <c r="K51" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52">
+        <v>200</v>
+      </c>
+      <c r="D52">
+        <v>43</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
         <v>77</v>
       </c>
-      <c r="H48" t="s">
-        <v>112</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J48" t="s">
-        <v>126</v>
-      </c>
-      <c r="K48" t="s">
-        <v>135</v>
+      <c r="G52" t="s">
+        <v>87</v>
+      </c>
+      <c r="H52" t="s">
+        <v>125</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J52" t="s">
+        <v>143</v>
+      </c>
+      <c r="K52" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2864,6 +3324,10 @@
     <hyperlink ref="I37" r:id="rId5"/>
     <hyperlink ref="I38" r:id="rId6"/>
     <hyperlink ref="I48" r:id="rId7" location="slide=id.p1 — slide 2 part 1 — pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1"/>
+    <hyperlink ref="I49" r:id="rId8"/>
+    <hyperlink ref="I50" r:id="rId9"/>
+    <hyperlink ref="I51" r:id="rId10"/>
+    <hyperlink ref="I52" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Logs/interaction_log.xlsx
+++ b/Logs/interaction_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="176">
   <si>
     <t>timestamp</t>
   </si>
@@ -202,6 +202,18 @@
     <t>2025-09-24T09:25:37.525385</t>
   </si>
   <si>
+    <t>2025-09-24T09:37:22.340959</t>
+  </si>
+  <si>
+    <t>2025-09-24T09:58:46.173297</t>
+  </si>
+  <si>
+    <t>2025-09-24T10:08:10.540962</t>
+  </si>
+  <si>
+    <t>2025-09-24T10:32:33.484279</t>
+  </si>
+  <si>
     <t>What funding did 2024 Technical Reporting cover?</t>
   </si>
   <si>
@@ -224,6 +236,15 @@
   </si>
   <si>
     <t>¿Quién tiene la responsabilidad fiduciaria y programática?</t>
+  </si>
+  <si>
+    <t>Se reportan desvíos potenciales en su uso. ¿Quién tiene la responsabilidad fiduciaria y programática, qué debe informar el Center y qué facultades de acción tiene la System Organization (SO)?</t>
+  </si>
+  <si>
+    <t>¿Quién gestiona colectivamente los requisitos de M&amp;E de los Funders y cómo se evita la duplicación?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who coordinates funders’ M&amp;E requirements across the CGIAR Portfolio and how is duplication avoided? </t>
   </si>
   <si>
     <t xml:space="preserve">You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:
@@ -283,6 +304,12 @@
   </si>
   <si>
     <t>pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2:0.396, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3:0.387, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1:0.364, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1:0.361, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1:0.330, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3:0.327, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2:0.319, pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2:0.283, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1:0.210, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4:0.204, docx:2025 Technical Reporting Information (Session 2).docx:u52-56:0.204, docx:2025 Technical Reporting Information (Session 1).docx:u1-4:0.196, docx:2025 Technical Reporting Information (Session 1).docx:u43-45:0.193, docx:2025 Technical Reporting Information (Session 2).docx:u1-4:0.193, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1:0.157, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4:0.151, pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3:0.144, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p25pt1:0.144, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt1:0.142, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt2:0.141, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3:0.137, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p36pt4:0.133, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt2:0.133, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt2:0.129, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt2:0.120, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt3:0.119, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2:0.113, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt3:0.111, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1:0.108, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt3:0.102, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p36pt1:0.102, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3:0.099, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt2:0.091, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1:0.088, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p55pt1:0.084, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt1:0.080, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p53pt4:0.074, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt3:0.072, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p40pt4:0.064, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt2:0.062, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt4:0.055, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p32pt3:0.047, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p32pt2:0.047</t>
+  </si>
+  <si>
+    <t>pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2:0.403, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1:0.368, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1:0.344, pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3:0.316, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1:0.310, pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2:0.288, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1:0.238, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4:0.218, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3:0.215, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3:0.211, docx:2025 Technical Reporting Information (Session 1).docx:u1-4:0.199, docx:2025 Technical Reporting Information (Session 2).docx:u1-4:0.196, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2:0.190, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p24pt1:0.186, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p30pt1:0.186, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3:0.157, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2:0.154, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p55pt2:0.152, docx:2025 Technical Reporting Information (Session 2).docx:u52-56:0.149, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1:0.136, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p31pt1:0.132, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3:0.130, docx:2025 Technical Reporting Information (Session 1).docx:u43-45:0.129, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3:0.127, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1:0.122, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p57pt2:0.122, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p25pt1:0.121, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3:0.121, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p28pt1:0.119, pdf:CGI21-507032-PORB-Climate Action.pdf:p38pt1:0.117, pdf:CGI21_508012_PORB_Genebanks.pdf:p20pt1:0.116, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p55pt1:0.114, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4:0.114, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p51pt1:0.114, pdf:CGI21-507032-PORB-Climate Action.pdf:p27pt1:0.114, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p31pt1:0.113, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p49pt2:0.113, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p25pt1:0.113, pdf:CGI21_508012_PORB_Genebanks.pdf:p21pt1:0.113, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p33pt1:0.110, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4:0.110, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt1:0.109, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p81pt2:0.109, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt1:0.108, pdf:CGI21-507032-PORB-Climate Action.pdf:p30pt1:0.108, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p42pt1:0.107, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p49pt4:0.107, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt2:0.107, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt2:0.106, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p29pt1:0.106, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p24pt1:0.106, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p36pt1:0.105, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p58pt3:0.105, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1:0.105, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt3:0.104, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p22pt1:0.104, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p37pt1:0.102, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p59pt1:0.101, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p21pt1:0.101, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p49pt1:0.099, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p71pt1:0.097, docx:2025 Technical Reporting Information (Session 2).docx:u25-28:0.097, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt2:0.096, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt3:0.095, docx:Standard Provisions 2026.docx:u7-10:0.095, docx:2025 Technical Reporting Information (Session 2).docx:u22-25:0.095, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p36pt4:0.095, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt2:0.094, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt2:0.093, pdf:Portfolio Narrative_2024.pdf:p47pt3:0.093, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt3:0.092, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p13pt1:0.092, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p11pt1:0.092, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p8pt2:0.091, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p52pt1:0.091, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p37pt1:0.091, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p23pt1:0.090, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p43pt1:0.090, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p21pt1:0.088, docx:Standard Provisions 2026.docx:u142-145:0.088, docx:2025 Technical Reporting Information (Session 2).docx:u7-10:0.088, docx:Standard Provisions 2026.docx:u148-151:0.086, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p51pt1:0.086, pdf:Type3_2024Report.pdf:p2pt1:0.085, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3:0.084, docx:Standard Provisions 2026.docx:u139-142:0.083, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.081, pdf:CGI21_508012_PORB_Genebanks.pdf:p3pt2:0.081, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p23pt1:0.081, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p67pt1:0.081, docx:2025 Technical Reporting Information (Session 2).docx:u4-7:0.080, docx:2025 Technical Reporting Information (Session 1).docx:u19-22:0.080, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt4:0.080, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt3:0.079, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p39pt1:0.079, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt3:0.079, docx:Standard Provisions 2026.docx:u115-118:0.079, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p41pt1:0.079, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p34pt3:0.078, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p33pt1:0.078, docx:2025 Technical Reporting Information (Session 1).docx:u22-25:0.077, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p32pt1:0.077, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt2:0.076, pdf:CGI21_508012_PORB_Genebanks.pdf:p42pt1:0.075, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p53pt4:0.075, docx:Standard Provisions 2026.docx:u40-43:0.075, docx:2025 Technical Reporting Information (Session 1).docx:u37-40:0.074, docx:Standard Provisions 2026.docx:u124-127:0.074, pdf:Portfolio Narrative_2024.pdf:p47pt2:0.074, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.074, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p3pt2:0.073, docx:Standard Provisions 2026.docx:u175-178:0.073, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p62pt1:0.073, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p12pt1:0.073, docx:2025 Technical Reporting Information (Session 1).docx:u34-37:0.072, docx:Standard Provisions 2026.docx:u151-154:0.071, pdf:CGI21_508012_PORB_Genebanks.pdf:p3pt1:0.071, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p70pt1:0.071, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p64pt1:0.070, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p3pt1:0.070, pdf:Quick style guide Feb 2024 (1).pdf:p9pt2:0.070, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.069, docx:2025 Technical Reporting Information (Session 1).docx:u40-43:0.068, docx:2025 Technical Reporting Information (Session 2).docx:u46-49:0.068, docx:Standard Provisions 2026.docx:u52-55:0.068, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p66pt1:0.068, pdf:CGI21-507032-PORB-Climate Action.pdf:p26pt1:0.067, docx:2025 Technical Reporting Information (Session 2).docx:u10-13:0.067, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p3pt1:0.067, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p82pt1:0.066, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p63pt1:0.066, docx:Standard Provisions 2026.docx:u112-115:0.066, docx:Standard Provisions 2026.docx:u73-76:0.066, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p35pt4:0.065, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p64pt1:0.065, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p28pt2:0.065, docx:Standard Provisions 2026.docx:u88-91:0.065, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p27pt1:0.065, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p8pt3:0.065, docx:Standard Provisions 2026.docx:u127-130:0.065, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p53pt1:0.064, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p3pt2:0.064, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p26pt1:0.064, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p42pt1:0.064, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p63pt1:0.064, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p80pt1:0.064, pdf:Climate Action_Inception Report 30-06-2025.pdf:p8pt3:0.064, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p48pt1:0.064, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p46pt1:0.064, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p85pt1:0.063, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p58pt2:0.063, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p64pt1:0.063, docx:Standard Provisions 2026.docx:u4-7:0.063, docx:Standard Provisions 2026.docx:u100-103:0.063, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p10pt1:0.062, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt1:0.062, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p3pt1:0.062, pdf:Climate Action_Inception Report 30-06-2025.pdf:p8pt4:0.062, docx:Standard Provisions 2026.docx:u160-163:0.062, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p52pt1:0.062, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p26pt1:0.062, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p3pt1:0.062, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p28pt1:0.062, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p36pt1:0.061, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p53pt1:0.061, docx:Standard Provisions 2026.docx:u85-88:0.061, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt2:0.061, pdf:CGI21-507032-PORB-Climate Action.pdf:p37pt1:0.061, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p17pt1:0.061, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p3pt1:0.061, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p3pt1:0.061, docx:Standard Provisions 2026.docx:u154-157:0.060, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p14pt1:0.060, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p50pt1:0.060, pdf:CGI21-507032-PORB-Climate Action.pdf:p3pt1:0.060, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p44pt1:0.060, docx:Standard Provisions 2026.docx:u97-100:0.059, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p40pt1:0.059, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p3pt1:0.059, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p51pt1:0.059, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p3pt1:0.059, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p56pt1:0.059, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt2:0.059, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt4:0.059, docx:2025 Technical Reporting Information (Session 1).docx:u31-34:0.059, docx:Standard Provisions 2026.docx:u16-19:0.058, pdf:CGI21-507032-PORB-Climate Action.pdf:p36pt1:0.058, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p51pt1:0.058, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p18pt1:0.058, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p79pt1:0.058, docx:Standard Provisions 2026.docx:u130-133:0.058, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p38pt1:0.058, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p80pt1:0.057, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p15pt1:0.057, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p70pt1:0.057, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p1pt2:0.057, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p3pt1:0.056, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p3pt1:0.056, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p3pt2:0.056, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p25pt1:0.056</t>
+  </si>
+  <si>
+    <t>pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2:0.321, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1:0.276, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1:0.272, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3:0.256, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1:0.252, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3:0.231, pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2:0.216, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3:0.198, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4:0.196, docx:2025 Technical Reporting Information (Session 1).docx:u1-4:0.186, docx:2025 Technical Reporting Information (Session 2).docx:u1-4:0.184, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3:0.166, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4:0.163, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt4:0.157, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2:0.146, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1:0.138, pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3:0.137, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p55pt1:0.137, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3:0.130, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3:0.124, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2:0.121, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt2:0.120, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt3:0.118, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p35pt4:0.118, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt2:0.116, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p28pt2:0.112, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p1pt2:0.112, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p32pt1:0.106, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt2:0.106, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p13pt4:0.104, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt2:0.104, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3:0.103, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1:0.103, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt2:0.102, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt2:0.101, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt4:0.100, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p36pt1:0.097, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt3:0.096, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1:0.096, pdf:CGI21-507032-PORB-Climate Action.pdf:p21pt3:0.094, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p35pt3:0.092, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p42pt3:0.091, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p25pt1:0.088, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p21pt4:0.087, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt1:0.087, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1:0.083, pdf:Portfolio Narrative_2024.pdf:p47pt3:0.082, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p28pt2:0.082, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p36pt4:0.081, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p48pt4:0.081, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt2:0.079, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt2:0.078, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p42pt4:0.078, pdf:Portfolio Narrative_2024.pdf:p47pt4:0.075, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p7pt4:0.075, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p28pt1:0.075, pdf:CGIAR_ImpactReport_2022-24.pdf:p56pt2:0.073, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt3:0.072, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt4:0.072, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p23pt1:0.072, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p53pt4:0.070, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p21pt2:0.070, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt3:0.068, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt1:0.067, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p29pt1:0.066, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p54pt3:0.066, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p48pt3:0.065, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt2:0.064, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt3:0.063, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt2:0.062, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt3:0.062, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt4:0.062, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p9pt3:0.061, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p38pt1:0.060, docx:Standard Provisions 2026.docx:u22-25:0.060, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p21pt1:0.059, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p10pt4:0.059, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p28pt3:0.058, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p49pt4:0.058, docx:Standard Provisions 2026.docx:u115-118:0.057, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p28pt3:0.057, pdf:Climate Action_Inception Report 30-06-2025.pdf:p11pt3:0.057, pdf:Portfolio Narrative_2024.pdf:p47pt2:0.056, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p25pt4:0.056, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p47pt4:0.056, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt2:0.056, pdf:CGIAR_ImpactReport_2022-24.pdf:p61pt1:0.054, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4:0.054, docx:2025 Technical Reporting Information (Session 2).docx:u52-56:0.054, docx:Standard Provisions 2026.docx:u127-130:0.053, docx:2025 Technical Reporting Information (Session 1).docx:u43-45:0.051, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p28pt4:0.050, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt2:0.049, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt1:0.049, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p30pt1:0.048, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p47pt4:0.048, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt4:0.048, docx:Standard Provisions 2026.docx:u100-103:0.048, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt2:0.047, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt1:0.047, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt1:0.045, pdf:CGIAR_ImpactReport_2022-24.pdf:p34pt1:0.045, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt2:0.045, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt4:0.044, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p43pt4:0.044, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p44pt4:0.044, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4:0.044, pdf:Type3_2024Report.pdf:p2pt4:0.043, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt3:0.043, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p40pt4:0.042, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p27pt2:0.042, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p18pt2:0.042, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p30pt2:0.041, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p22pt2:0.041, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p38pt2:0.041, pdf:Climate Action_Inception Report 30-06-2025.pdf:p8pt3:0.041, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p27pt1:0.041, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p30pt1:0.040, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p52pt3:0.040, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p22pt1:0.040, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt3:0.040, pdf:Climate Action_Inception Report 30-06-2025.pdf:p8pt4:0.040, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p22pt2:0.040, pdf:Portfolio Narrative_2024.pdf:p83pt1:0.040, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p6pt2:0.040, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt1:0.040, pdf:Type3_2024Report.pdf:p8pt4:0.039, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p9pt4:0.038, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt2:0.038, pptx:Information Session on 2025 Technical Reporting.pptx:s3pt3:0.038, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt2:0.038, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt2:0.038, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p39pt3:0.037, docx:Standard Provisions 2026.docx:u103-106:0.037, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p13pt4:0.037, pdf:Portfolio Narrative_2024.pdf:p28pt4:0.037, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt4:0.036, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt2:0.036, pdf:CGIAR_ImpactReport_2022-24.pdf:p45pt4:0.035, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p22pt1:0.035, pdf:Portfolio Narrative_2024.pdf:p19pt1:0.035, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p26pt1:0.035, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt4:0.034, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p39pt2:0.034, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p18pt1:0.034, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p30pt3:0.033, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p51pt1:0.033, pdf:CGIAR_ImpactReport_2022-24.pdf:p61pt2:0.033, docx:Standard Provisions 2026.docx:u85-88:0.033, docx:Standard Provisions 2026.docx:u172-175:0.033, docx:Standard Provisions 2026.docx:u124-127:0.032, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p20pt2:0.032, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p17pt3:0.032, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p47pt3:0.031, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p13pt1:0.031, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p9pt3:0.030, pdf:CGIAR_ImpactReport_2022-24.pdf:p53pt4:0.030, pdf:CGIAR_ImpactReport_2022-24.pdf:p23pt4:0.030, pdf:Type3_2024Report.pdf:p10pt4:0.030, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p49pt3:0.030, docx:Standard Provisions 2026.docx:u82-85:0.029, pdf:CGIAR_ImpactReport_2022-24.pdf:p53pt3:0.029, docx:Standard Provisions 2026.docx:u97-100:0.029, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p22pt2:0.028, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p39pt2:0.028, pdf:CGIAR_ImpactReport_2022-24.pdf:p41pt4:0.028, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p15pt2:0.028, docx:Standard Provisions 2026.docx:u52-55:0.027, pdf:CGIAR_ImpactReport_2022-24.pdf:p4pt2:0.027, pdf:Portfolio Narrative_2024.pdf:p82pt4:0.026, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p6pt4:0.026, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p6pt3:0.026, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p15pt3:0.026, docx:Standard Provisions 2026.docx:u112-115:0.026, pdf:CGI21-507032-PORB-Climate Action.pdf:p24pt2:0.026, docx:Standard Provisions 2026.docx:u106-109:0.025, pdf:CGI21-507032-PORB-Climate Action.pdf:p24pt3:0.025, pdf:CGIAR_ImpactReport_2022-24.pdf:p40pt1:0.025, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt3:0.024, docx:Standard Provisions 2026.docx:u7-10:0.024, docx:Standard Provisions 2026.docx:u130-133:0.024, docx:Standard Provisions 2026.docx:u4-7:0.024, pdf:Type3_2024Report.pdf:p7pt2:0.024, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p16pt1:0.024, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p22pt2:0.024, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt3:0.024, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p37pt4:0.023, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt3:0.023, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p37pt3:0.023, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p22pt1:0.023, docx:Standard Provisions 2026.docx:u34-37:0.023, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p14pt3:0.023, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p22pt2:0.023, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt4:0.023, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p18pt1:0.022, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p17pt4:0.022, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18pt4:0.022, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p47pt2:0.022, pdf:Quick style guide Feb 2024 (1).pdf:p5pt1:0.022, pdf:Climate Action_Inception Report 30-06-2025.pdf:p28pt3:0.022</t>
   </si>
   <si>
     <t>I cannot find information in the provided chunks to answer this.  
@@ -580,6 +607,46 @@
 CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1</t>
   </si>
   <si>
+    <t>I cannot find information in the provided chunks to answer this. The documents do not specify the fiduciary and programmatic responsibilities, the reporting obligations of the Center, or the action powers of the System Organization (SO) regarding potential deviations in usage. For detailed insights on these topics, further context or specific documents may be required. 
+Sources:
+File — Location — Cited IDs
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2
+Genebanks_Inception Report 30-06-2025.pdf — page 22 part 1 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1
+Climate Action_Inception Report 30-06-2025.pdf — page 4 part 3 — pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3
+CGI21_508012_PORB_Genebanks.pdf — page 11 part 1 — pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1</t>
+  </si>
+  <si>
+    <t>I cannot find information in the provided chunks to answer this. The documents do not specify who collectively manages the M&amp;E requirements of the Funders or the methods used to avoid duplication. Further details on these processes may be found in other sources or documents not included in the provided chunks. 
+Sources:
+File — Location — Cited IDs
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2
+Genebanks_Inception Report 30-06-2025.pdf — page 22 part 1 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1
+CGI21_508012_PORB_Genebanks.pdf — page 11 part 1 — pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1
+CGIAR_PORB_Breeding_Tomorrow.pdf — page 45 part 3 — pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1</t>
+  </si>
+  <si>
+    <t>I cannot find information in the provided chunks to answer this. The documents do not specify who collectively manages the M&amp;E requirements of the Funders or the methods used to avoid duplication. Further details on these processes may be found in other resources or specific reports related to M&amp;E practices within the relevant organizations. 
+Sources:
+File — Location — Cited IDs
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2
+Genebanks_Inception Report 30-06-2025.pdf — page 22 part 1 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1
+CGI21_508012_PORB_Genebanks.pdf — page 11 part 1 — pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1
+CGIAR_PORB_Breeding_Tomorrow.pdf — page 45 part 3 — pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3
+CGIAR_PORB_Scaling_4Impact.pdf — page 23 part 3 — pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3</t>
+  </si>
+  <si>
+    <t>The coordination of funders' M&amp;E requirements across the CGIAR Portfolio is primarily managed by the Portfolio Performance Unit, which collaborates with a cross-CGIAR working group that includes Center experts and System functions. To avoid duplication, the Technical Reporting Arrangement (TRA) for 2025-30 aims to promote progressive alignment between reporting requirements for pooled and non-pooled funding components. This structured approach is designed to ensure transparency and accountability while facilitating effective engagement and communication among stakeholders, thereby minimizing overlapping evaluations and activities. 
+Sources:
+File — Location — Cited IDs
+CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 23 part 4 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt4
+CGIAR_ImpactReport_2022-24.pdf — page 2 part 4 — pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4
+Type3_2024Report.pdf — page 6 part 1 — pdf:Type3_2024Report.pdf:p6pt1
+Capacity Sharing_Inception Report 30-06-2025.pdf — page 39 part 4 — pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p39pt4
+Standard Provisions 2026.docx — section 'Monitoring and Evaluations' paragraph 115 — docx:Standard Provisions 2026.docx:u103-106</t>
+  </si>
+  <si>
     <t>Information Session on 2025 Technical Reporting.pptx — slide 9 — pptx:Information Session on 2025 Technical Reporting.pptx:s9, Engagement Plan 2025 Technical Reporting.docx — paragraph 2 — docx:Engagement Plan 2025 Technical Reporting.docx:p2, Information Session on 2025 Technical Reporting.pptx — slide 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s2, Guidance on reporting outputs or outcomes.docx — paragraph 22 — docx:Guidance on reporting outputs or outcomes.docx:p22, Engagement Plan 2025 Technical Reporting.docx — section 'Technical Reporting questions' — docx:Engagement Plan 2025 Technical Reporting.docx:p59, CGIAR_ImpactReport_2022-24.pdf — page 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p1, Engagement Plan 2025 Technical Reporting.docx — section 'A single location for all documents and resources' — docx:Engagement Plan 2025 Technical Reporting.docx:p31, Engagement Plan 2025 Technical Reporting.pptx — slide 1 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s1, CGSpace.docx — section 'CGSpace' — docx:CGSpace.docx:p3, CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 5 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5</t>
   </si>
   <si>
@@ -611,6 +678,12 @@
   </si>
   <si>
     <t>https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543 — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2, https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543 — page 24 part 3 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3, https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543 — page 22 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1</t>
+  </si>
+  <si>
+    <t>https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543 — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1 — page 22 part 1 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1, https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543 — page 9 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1</t>
+  </si>
+  <si>
+    <t>https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543 — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1 — page 22 part 1 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1, CGI21_508012_PORB_Genebanks.pdf — page 11 part 1 — pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1</t>
   </si>
   <si>
     <t>[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]
@@ -1214,6 +1287,347 @@
 LLP Kazakh RI of Ag &amp; Plt Grow, Kazakhstan CIMMYT Phenotyping-Int Nurseries The Kyrgyz Research Institute of Livestock and Pasture, Kyrgyzstan CIMMYT Phenotyping-Int Nurseries NAFRI, Laos CIMMYT Phenotyping-Int Nurseries Misurata Agric. Res. Stn., Libya CIMMYT Phenotyping-Int Nurseries Pixus Agriculture Malawi Ltd., Malawi CIMMYT Phenotyping-Int Nurseries INIFAP , Mexico CIMMYT Phenotyping-Int Nurseries ICAMEX, Mexico CIMMYT Phenotyping-Int Nurseries Agroq. y Semillas La Fuerte SA, Mexico CIMMYT Phenotyping-Int Nurseries Fertilizantes Tepeyac, Mexico CIMMYT Phenotyping-Int Nurseries INRA-Morocco, Morocco CIMMYT Phenotyping-Int Nurseries</t>
   </si>
   <si>
+    <t>[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]
+el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]
+Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos
+---
+[ID: pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3]
+Frameworks for Climate Services PLACA Climate Action Platform for Agriculture in Latin America and the Caribbean / La Plataforma de Acción Climática en Agricultura de Latinoamérica y el Caribe PMU Program Management Unit PPU Portfolio Performance Unit PRMS Performance and Results Management System REMET Reducing Methane Emissions from Rice project ROI Return on investment S4I Scaling for Impact (Program) SA South Asia SB
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]
+- 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness" 411,914 "Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 "Andean Crop Diversity for Climate Change P-1560-DGUL" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 "Youth, Citizen Science and E-commerce:
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]
+nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]
+business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]
+at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and
+---
+[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]
+2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u1-4]
+2025 Technical Reporting Information (Session 2)-20250729_150218-Meeting Recording 29 de julio de 2025, 1:02p.m. 47 min 36 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción
+---
+[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2]
+II) ICRISAT AOW02 Digital Advisories and Climate Risk Management $89,064 N-343001-GCAN INITIATIVE IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $1,321,123 N-601158-SPIR II IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $201,213 PJ-003953: APPUI A LA TRANSFORMATION ET A LA RESILIENCE DES SYSTEMES ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance
+---
+[ID: pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p24pt1]
+System Organization and center allocations
+---
+[ID: pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p30pt1]
+System Organization and center allocations
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]
+Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2]
+de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation Globally (AOW05) High Level Output 5.4. Unique crop diversity under threat is safeguarded through the integration of in situ and ex situ conservation strategies 50,000 "Revealing the Diversity of Barley Quality Traits through Synergies between On-farm Practices and Technological Innovations D-100735" ICARDA Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 237,008 Long Term Partnership Agreement ICARDA Biodiversity
+---
+[ID: pdf:CGI21-507033-PORB-Policy Innovations.pdf:p55pt2]
+budget 2025 | System Organization and center allocations | Page
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u52-56]
+Aryal, Bishal (IFPRI) 44:47 Thank you. Thank you. Nirmal, Rajalakshmi (IFPRI) 44:50 Thank you. Bye, bye. Trifa, Nicoleta (CGIAR System Organization) 44:53 Hi. Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción
+---
+[ID: pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 13 of 86 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD FRANCE – FFEM Promover Oportunidades Sostenibles en la Cadena de Valor del Cacao de Excelencia (IA Lead of A1537) Alliance Bioversity CIAT AoW 3-Markets and Business Models; AoW 5-Gender Equality, Social Inclusion and Fairness Intermediate Outcome - AOW-IOC 3.2. Local producer organizations, national and sub-national public actors and private sector actors co-design or strengthen inclusive business models; 2030 Outcome - 2030 OC-4. Marginalized people participate in implementing innovations; 2030 Outcome - 2030 OC-3 Government, market and finance actors implement
+---
+[ID: pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p31pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 31 of 56 System Organization:
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3]
+Seed Ltd CIMMYT ID DEPLOY PROASE Productores Asociados de Semillas S.C. de R.L. de C.V. CIMMYT ID DEPLOY Productora de Semillas Azteca S.P .R. de R.L. CIMMYT ID DEPLOY PRODUCTORA DE SEMILLAS SMART SEEDS SAS DE CV CIMMYT ID DEPLOY Productora de Semillas Zarco S.P .R. de R.L. CIMMYT ID DEPLOY Productores de Semilla de Copandaro S.P .R. de R.L. CIMMYT ID DEPLOY Productos y Servicios Agrícolas S.P .R. de R.L. CIMMYT ID DEPLOY QualiBasic Seed Company (QBS) CIMMYT AB, ID
+---
+[ID: docx:2025 Technical Reporting Information (Session 1).docx:u43-45]
+Colomer, Julien (One CGIAR - France) 48:19 Thanks. Hurt, Chris (ILRI) 48:19 Thank you. Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3]
+de Cajas Rurales de Ahorro y Crédito Comunidades de Oriente (CECRUCSO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organización para el Desarrollo del Corquin (ODECO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organismo Cristiano de Desarrollo Integral de Honduras (OCDIH) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 32 of 90 August 2025 | CGIAR Contracted partner Center Current Status of Partnership Area of Work Title and Number High level output (If Available) Dirección de Coordinación Regional y Extensión Rural (DICORER) CIMMYT Potential AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Fundación para la Innovación Tecnológica Agropecuaria y Forestal
+---
+[ID: pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p57pt2]
+2025 | System Organization and center allocations | Page 57 of
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p25pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 25 of 44 Partner Center Area of Work Title and Number High level output (If Available) Local Governments for Sustainability, Nairobi City County, Dhaka North City Corporation, Local Government of Quezon City (Philippines), RUAF Foundation International Potato Center / Centro Internacional de la Papa 3.5.5 Urban food systems governance - Delivering knowledge products, evidence and capacity sharing with policy makers to guide interventions aimed at strengthening
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3]
+(INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID DEPLOY Institut National pour l'Etude et la Recherche Agronomiques (INERA) - RDC CIMMYT AB, ID DEPLOY Instituto de Investigação Agronómica (IIA) - Angola CIMMYT AB, ID DEPLOY Instituto de Investigación Agropecuaria de Panamá CIMMYT AB, ID STRATEGIZE/REFOCUS, PARTNER / TRANSFORM, OPTIMIZE / ACCELERATE, CREATE Invicta Agritech India Private Limited CIMMYT ID DEPLOY JAMSONI COMPANY LIMITED CIMMYT ID DEPLOY Jardins da Yoba CIMMYT ID
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p28pt1]
+System Organization and center allocations Herder
+---
+[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p38pt1]
+Plan of results and budget 2025 | System Organization and center allocations | Page 38
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p20pt1]
+System Organization and center allocations Multispectral
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p55pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 55 of 86 External collaborations/partners Center Area of Work Title and Number High level output (If Available) Arab Center for the Studies of Arid Zones and Dry Areas - ACSAD ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing Institut National de la Recherche Agronomique de Tunisie; National Agricultural Research Institute of Tunisia - INRAT ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing Institut National de Recherche Agronomique de Tunisie. INRAT. ICARDA AoW2, AoW3 HLO: Accelerate - Stage2 &amp; Stage 3 testing &amp; Deploy Ankara University, Faculty of Agriculture ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4]
+to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación Regionalde Servicios Agropecuarios de Oriente (ARSAGRO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Cooperación para el Desarrollo Rural de Occidente-CDRO - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems CGI21-508007-PORB-Scaling for Impact.indd 22CGI21-508007-PORB-Scaling for Impact.indd 22 07/08/2025 13:2407/08/2025 13:24
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p51pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 51 of 90 System Organization: Scaling for Impact Implementation timelines (2025) Pooled
+---
+[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p27pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 27 of 50 System Organization: Climate Action Implementation timelines (2025) Pooled
+---
+[ID: pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p31pt1]
+CGIAR | September 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 31 of 84 System Organization: Sustainable Farming Implementation timelines (2025)
+---
+[ID: pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p49pt2]
+2025 | System Organization and center allocations | Page 49 of 86
+---
+[ID: pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p25pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 25 of 86 System Organization: Multifunctional Landscapes Implementation timelines (2025) Pooled
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p21pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 21 of 52 System Organization: Genebanks Implementation timelines (2025) Pooled funding
+---
+[ID: pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p33pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 33 of 52 System Organization: Sustainable Animal and Aquatic Foods Implementation timelines (2025)
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4]
+Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations, and evidence-based programs for enhancing inclusive informal food markets that effectively create quality jobs for young women and men and deliver safe and healthy foods in urban environments University of Peradeniya, Wayamba University of Sri Lanka, Asian Development Bank, World Food Programme International Food Policy Research Institute 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents CGI21-507031-PORB-Food Frontiers and Security.indd 24CGI21-507031-PORB-Food Frontiers and Security.indd 24 29/07/2025 19:3929/07/2025 19:39
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 50 of 86 August 2025 | CGIAR External collaborations/partners Center Area of Work Title and Number High level output (If Available) CSIR-CRI - Ghana AfricaRice AB, EN Accelerate, Transform EIAR-Ethiopia AfricaRice AB, EN Accelerate, Transform IER-Mali AfricaRice AB, EN Accelerate, Transform CNRA- Côte d'Ivoire AfricaRice AB, MI, ID, EN Accelerate, Transform, Share, Design, Invest ITRAD-Chad AfricaRice AB Accelerate FOFIFA-Madagascar AfricaRice AB, ID, MI, EN Accelerate, Transform, Share, Design, Invest NARO-Uganda AfricaRice MI Design, Invest NARI - the Gambia AfricaRice ID
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p81pt2]
+2025 | System Organization and center allocations | Page 81 of 86
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt1]
+Capacity Sharing Accelerator Inception Report 4 ISNAR International Service for National Agricultural Research ISRA Institut Sénégalais de la Recherche Agricole (Senegalese Agricultural Research Institute) ITU International Telecommunication Union KOICA Korea International Cooperation Agency KPIs Key Performance Indicators. MELIA Monitoring, Evaluation, Learning, and Impact Assessment NARES National Agricultural Research and Extension Systems NARS National Agricultural Research System PCT Program Coordination Team
+---
+[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p30pt1]
+Plan of results and budget 2025 | System Organization and center allocations | Page 30 of 50
+---
+[ID: pdf:CGI21-507033-PORB-Policy Innovations.pdf:p42pt1]
+System Organization and center allocations Taking care of the
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p49pt4]
+Accelerate, Design, Umudike Seed IITA ID, MI Accelerate, Design, INERA-Burkina Faso AfricaRice AB, EN Accelerate, Transform INERA-DRC AfricaRice AB, MI, EN Accelerate, Transform, Share ISRA- Senegal AfricaRice AB, ID, MI, EN Accelerate, Transform, Design, Invest CARI- Liberia AfricaRice AB Accelerate NCRI-Nigeria AfricaRice AB, ID, MI, EN Accelerate, Transform, Share, Design, Invest SLARI-Sierra Leone AfricaRice AB, MI, EN Accelerate, Transform INRAB-Benin AfricaRice AB Accelerate IRAG-Guinea Conakry AfricaRice AB, EN Accelerate, Transform INRAN-Niger AfricaRice AB, EN Accelerate, Transform CGI21-508008-PORB-Breeding for Tomorrow.indd 49CGI21-508008-PORB-Breeding for Tomorrow.indd 49 08/08/2025 16:0208/08/2025 16:02
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt2]
+Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The World Bank, German Red Cross (Germany), Dhaka City North Corporation, Nairobi City County, International Water Management Institute, WorldFish International Food Policy Research Institute 1.2.2 Evidence Synthesis and Adaptive Learning - Co-develop knowledge products and action plans, and identify key investment and innovation priorities for stakeholders and partners to guide interventions aimed at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt2]
+(SME) Private Ltd CIMMYT ID DEPLOY IFFA Seed Co Ltd CIMMYT ID DEPLOY Indian Institute of Maize Research CIMMYT AB, ID DEPLOY Indo American Hybrid Seeds (India) Pvt. Ltd CIMMYT ID DEPLOY Institut de Recherche Agricole pour le Développement (IRAD) CIMMYT AB, ID DEPLOY Institut des Sciences Agronomiques du Burundi (ISABU) CIMMYT AB, ID DEPLOY Institut National de la Recherche Agronomique du Niger (INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p29pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 29 of 44 System Organization: Food Frontiers and Security Implementation timelines (2025) Pooled funding Budget
+---
+[ID: pdf:CGI21-508004-PORB-Digital Transformation.pdf:p24pt1]
+Plan of results and budget 2025 | System Organization and center allocations | Page 24 of 38
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p36pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 36 of 86 August 2025 | CGIAR External collaborations/partners Center Area of Work Title and Number High level output (If Available) L’Institut Tchadien de Recherche Agronomique pour le Développement – ITRAD – Chad CIMMYT AB, ID, MI, Enable l’Institut National de la Recherche Agronomique du Niger – INRAN – Niger CIMMYT AB, ID, MI, Enable Ministry of Agriculture and Food Security – MAFS – Sudan CIMMYT AB, ID, MI, Enable MyAgro – USA CIMMYT ID National Agricultural Research Organization
+---
+[ID: pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p58pt3]
+| System Organization and center allocations | Page 58 of 86 August 2025
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1]
+23 Bilateral Contribution to Multifunctional Landscapes MELIA Studies UK FCDO - Seed to tree: value chains and partnerships for resilient restored forests in Malaysia • Actor engagement and outcome tracking UK – GCBC (UK-Defra) - Deploying Diversity as a Strategic Asset for Scaling of Ethiopia’s Green Legacy Initiative for Climate Change Resilience and Livelihoods • Program learning review • Actor engagement and outcome tracking FRANCE – FFEM Promover Oportunidades Sostenibles en la Cadena de Valor del Cacao de Excelencia (IA Lead of A1537) • Actor engagement and outcome tracking CoIMPACT INDIA • Program learning review Fruitful Lands India Phase II • Actor engagement and outcome tracking Sustainable Investments for Large-scale Rangeland R • Actor engagement and outcome tracking Building Community
+---
+[ID: pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt3]
+Lebanese Agriculture Research Institute (LARI), Institut National De La Recherche Agronmique en Tunisie (INRAT) IFPRI, Alliance, ICARDA Area of Work: Accelerating Solutions for Impact 1.4.3: Evidence on effectiveness of solutions for inclusive leadership TBD GENDER Accelerator Area of Work: Accelerating Solutions for Impact 1.5.1: Analysis of constraints and pathways for youth in FLWS n/a n/a Area of Work: Accelerating Solutions for Impact 1.5.2: Co-designed approaches to engaging youth in FLWS n/a n/a Area of Work: Accelerating Solutions for Impact 1.5.3: Evidence on effectiveness of approaches to engaging youth in FLWS AGRA, IFAD, FAO, WFP IFPRI Area of Work: Accelerating Change Through Evidence 2.1.1: Guidance on ethical gender research AGRA, IFAD,
+---
+[ID: pdf:CGI21-508004-PORB-Digital Transformation.pdf:p22pt1]
+Plan of results and budget 2025 | System Organization and center allocations | Page 22 of 38
+---
+[ID: pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p37pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 37
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p59pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 59 of 86 System Organization: Breeding for Tomorrow Implementation timelines (2025) Pooled funding Budget Total Program Q1 Q2
+---
+[ID: pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p21pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 21 of 42 System Organization: Gender Equality and Inclusion Implementation timelines (2025) Pooled funding Budget Total Accelerator Q1 Q2
+---
+[ID: pdf:CGI21-507033-PORB-Policy Innovations.pdf:p49pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 49
+---
+[ID: pdf:CGI21-507033-PORB-Policy Innovations.pdf:p71pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 71
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u25-28]
+Trifa, Nicoleta (CGIAR System Organization) 33:46 Yes, the answer is more people beyond Media can access PRMS. We are now actually taking the user role from PRMS reporting from the previous portfolio and. Make sure that they apply to this portfolio as well. So I will share my screen again just to give you a quick insight into that. So the roles we use in the previous portfolio were, you know, lead, what the lead can do, co-lead, coordinator, member and admin and then a guest. And then so these are the roles. I will share this link with you so if you have a better look at the definition who is part of what category. So based on these roles we have asked the program coordinators to. Put a name next to each role for PRMS from their own teams. So they had to, you know, ask in the teams to see, OK, who will play the, who will play, who will be a colleague, a lead, an admin, a guest and so on in PRMS. So I believe that list is still a work in progress. We did not receive. Feedback from old programs and accelerators by now, but based on that list, basically we will give initial access to PRMS reporting and obviously if in the meantime people come and go and so on, if there are requests to add new people to the list. It's never an exhaustive list, so this is a live list throughout the year. So you can request to be added to the list with you know certain a certain role and that will be you know in enabled in the system. Nirmal, Rajalakshmi (IFPRI) 35:30 Right. My, I had another question, Nicoletta, if it's OK on the reporting for the bilateral projects, right. So when we did the TOC, we just mapped it to each area of work and the, you know, and put them under the high level outputs. Trifa, Nicoleta (CGIAR System Organization) 35:34 Go ahead. Sure. Nirmal, Rajalakshmi (IFPRI) 35:48 But we haven't gone to the level of mentioning the targets or indicators for these bilateral projects that were mapped, right. So when we are about to start the reporting process, what's the plan? How are we going to go about this part? Yeah, Mandy Jules.
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt2]
+capacity AfriSeed, Zambia CIMMYT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact HLO 5.2: Insights for CGIAR scaling success through impact assessments.HLO 2.2: Co-designed scaling pathways for regional and national agrifood systems through improved stakeholder capacity Secretaría de Agricultura y Desarrollo Rural (SADER) de México CIMMYT Potential AoW1 - Engage and Empower HLO 1.1: A toolbox of methods, data, and dashboards HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Agencia Mexicana de Cooperación Internacional para el Desarrollo (AMEXCID) CIMMYT Potential AoW1 - Engage and Empower HLO
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt3]
+Bolivia CIMMYT Phenotyping ZARI - Zambia Agricultural Research Institute, Zambia CIMMYT Phenotyping INIA Chile -Instituto de Investigaciones Agropecuarias, Chile CIMMYT Phenotyping INIA Uruguay -Instituto Ncional de Investigacion Agropecuaria, Uruguay CIMMYT Phenotyping IRESA - Institution de la Recherche et de l’Enseignement Supérieur Agricoles, Tunisia CIMMYT Phenotyping TAGEM - Ministry of Food Agriculture and Livestock, Turkey CIMMYT Phenotyping KALRO- Kenya Agricultural &amp; Livestock Research Organization, Kenya ARIA, Afghanistan CIMMYT Phenotyping-Int Nurseries ITGC, Algeria CIMMYT Phenotyping-Int
+---
+[ID: docx:Standard Provisions 2026.docx:u7-10]
+between Funders and the System Organization apply to each Funding Agreement or Arrangement between a Funder and the System Organization; between the System Organization and each Center apply to the Financial Framework Agreement between the System Organization and each Center; and between a Funder and a Center apply to each Window 3 Side Agreement or Arrangement between a Funder and a Center. Use and administration of the Contributions
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u22-25]
+Colomer, Julien (One CGIAR - France) 32:14 Mm-hmm. Yeah. Yeah, thanks. No, I I hear You and and that's really the also the the intent was to um. Build a sort of, um, a bridge between outputs and outcomes, right? So to IT wouldn't be either an output or an outcome, and IT would be the sort of category that spanned both and we would use IT to collect evidence of all of the things that Help foment or catalyze. You know, outcomes, right. But yeah, either we Go or we don't. So I I think, You know, we've been sort of umming and ahhing for too Long now an</t>
+  </si>
+  <si>
+    <t>[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]
+el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]
+Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3]
+Seed Ltd CIMMYT ID DEPLOY PROASE Productores Asociados de Semillas S.C. de R.L. de C.V. CIMMYT ID DEPLOY Productora de Semillas Azteca S.P .R. de R.L. CIMMYT ID DEPLOY PRODUCTORA DE SEMILLAS SMART SEEDS SAS DE CV CIMMYT ID DEPLOY Productora de Semillas Zarco S.P .R. de R.L. CIMMYT ID DEPLOY Productores de Semilla de Copandaro S.P .R. de R.L. CIMMYT ID DEPLOY Productos y Servicios Agrícolas S.P .R. de R.L. CIMMYT ID DEPLOY QualiBasic Seed Company (QBS) CIMMYT AB, ID
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]
+Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]
+- 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness" 411,914 "Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 "Andean Crop Diversity for Climate Change P-1560-DGUL" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 "Youth, Citizen Science and E-commerce:
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3]
+de Cajas Rurales de Ahorro y Crédito Comunidades de Oriente (CECRUCSO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organización para el Desarrollo del Corquin (ODECO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organismo Cristiano de Desarrollo Integral de Honduras (OCDIH) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]
+nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.
+---
+[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]
+2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u1-4]
+2025 Technical Reporting Information (Session 2)-20250729_150218-Meeting Recording 29 de julio de 2025, 1:02p.m. 47 min 36 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3]
+C.V. CIMMYT ID DEPLOY Semillas Barriga S.R.P . de R.L. CIMMYT ID DEPLOY Semillas Berentsen S.A. de C.V. CIMMYT ID DEPLOY Semillas Cinteotl S.P .R de R.L. CIMMYT ID DEPLOY Semillas Iyadilpro y Ya S.A. de C.V. CIMMYT ID DEPLOY SEMILLAS MEJORADAS S.A. CIMMYT ID DEPLOY Semillas Ocso S.P .R. de R.L. CIMMYT ID DEPLOY Semillas Proseso SA DE CV CIMMYT ID DEPLOY Semillas y Agroinsumos Golden S.P .R. de R.L. de C.V. CIMMYT ID DEPLOY Semillas PROSASOL S.P .R. de R.L.
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4]
+to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación Regionalde Servicios Agropecuarios de Oriente (ARSAGRO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Cooperación para el Desarrollo Rural de Occidente-CDRO - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems CGI21-508007-PORB-Scaling for Impact.indd 22CGI21-508007-PORB-Scaling for Impact.indd 22 07/08/2025 13:2407/08/2025 13:24
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt4]
+del Bienestar (SEBIEN) de Quintana Roo CIMMYT Contracted AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Secretaría de Desarrollo Agropecuario (SEDAGRO) de Morelos CIMMYT Contracted AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Ministerio de Agricultura, Ganadería y Alimentación (MAGA) de Guatemala CIMMYT Potential AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio CGI21-508007-PORB-Scaling for Impact.indd 31CGI21-508007-PORB-Scaling for Impact.indd 31
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2]
+de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation Globally (AOW05) High Level Output 5.4. Unique crop diversity under threat is safeguarded through the integration of in situ and ex situ conservation strategies 50,000 "Revealing the Diversity of Barley Quality Traits through Synergies between On-farm Practices and Technological Innovations D-100735" ICARDA Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 237,008 Long Term Partnership Agreement ICARDA Biodiversity
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The
+---
+[ID: pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3]
+Frameworks for Climate Services PLACA Climate Action Platform for Agriculture in Latin America and the Caribbean / La Plataforma de Acción Climática en Agricultura de Latinoamérica y el Caribe PMU Program Management Unit PPU Portfolio Performance Unit PRMS Performance and Results Management System REMET Reducing Methane Emissions from Rice project ROI Return on investment S4I Scaling for Impact (Program) SA South Asia SB
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p55pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 55 of 86 External collaborations/partners Center Area of Work Title and Number High level output (If Available) Arab Center for the Studies of Arid Zones and Dry Areas - ACSAD ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing Institut National de la Recherche Agronomique de Tunisie; National Agricultural Research Institute of Tunisia - INRAT ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing Institut National de Recherche Agronomique de Tunisie. INRAT. ICARDA AoW2, AoW3 HLO: Accelerate - Stage2 &amp; Stage 3 testing &amp; Deploy Ankara University, Faculty of Agriculture ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3]
+(INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID DEPLOY Institut National pour l'Etude et la Recherche Agronomiques (INERA) - RDC CIMMYT AB, ID DEPLOY Instituto de Investigação Agronómica (IIA) - Angola CIMMYT AB, ID DEPLOY Instituto de Investigación Agropecuaria de Panamá CIMMYT AB, ID STRATEGIZE/REFOCUS, PARTNER / TRANSFORM, OPTIMIZE / ACCELERATE, CREATE Invicta Agritech India Private Limited CIMMYT ID DEPLOY JAMSONI COMPANY LIMITED CIMMYT ID DEPLOY Jardins da Yoba CIMMYT ID
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]
+at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and
+---
+[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2]
+II) ICRISAT AOW02 Digital Advisories and Climate Risk Management $89,064 N-343001-GCAN INITIATIVE IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $1,321,123 N-601158-SPIR II IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $201,213 PJ-003953: APPUI A LA TRANSFORMATION ET A LA RESILIENCE DES SYSTEMES ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt2]
+(SLARI) Africa Rice Potential AoW 4 - Achieving Impact by Unlocking Finance and Partnerships GrainPro Inc Africa Rice Potential AoW 2 - Pathways to Scale in Agrifood Systems African Development Bank Africa Rice Contracted AoW 4 - Achieving Impact by Unlocking Finance and Partnerships Seed Development and Certification Agency, Liberia Africa Rice Potential AoW 3 - Enabling Environment Lab Central de Cajas Rurales de Ahorro y Crédito Comunidades de Oriente (CECRUCSO) - Honduras CIAT Contracted AoW 2 - Pathways to
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt3]
+Bolivia CIMMYT Phenotyping ZARI - Zambia Agricultural Research Institute, Zambia CIMMYT Phenotyping INIA Chile -Instituto de Investigaciones Agropecuarias, Chile CIMMYT Phenotyping INIA Uruguay -Instituto Ncional de Investigacion Agropecuaria, Uruguay CIMMYT Phenotyping IRESA - Institution de la Recherche et de l’Enseignement Supérieur Agricoles, Tunisia CIMMYT Phenotyping TAGEM - Ministry of Food Agriculture and Livestock, Turkey CIMMYT Phenotyping KALRO- Kenya Agricultural &amp; Livestock Research Organization, Kenya ARIA, Afghanistan CIMMYT Phenotyping-Int Nurseries ITGC, Algeria CIMMYT Phenotyping-Int
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p35pt4]
+Senegalais de Recherches Agricoles – ISRA – Senegal CIMMYT AB, ID, MI, Enable Instituto de Investigacao Agraria de Mocambique – IIAM – Mozambique CIMMYT AB, ID, MI, Enable International Institute of Tropical Agriculture – IITA – Nigeria CIMMYT AB, ID, MI, Enable Kenya Agricultural and Livestock Research Organization – KALRO – Kenya CIMMYT AB, ID, MI, Enable Lake Chad Research Institute – LCRI – Nigeria CIMMYT AB, ID, MI, Enable L’Institut de l’Environnement et de Recherches Agricoles – INERA – Burkina Faso CIMMYT AB, ID, MI, Enable CGI21-508008-PORB-Breeding for Tomorrow.indd 35CGI21-508008-PORB-Breeding for Tomorrow.indd 35 08/08/2025 16:0208/08/2025
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt2]
+capacity AfriSeed, Zambia CIMMYT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact HLO 5.2: Insights for CGIAR scaling success through impact assessments.HLO 2.2: Co-designed scaling pathways for regional and national agrifood systems through improved stakeholder capacity Secretaría de Agricultura y Desarrollo Rural (SADER) de México CIMMYT Potential AoW1 - Engage and Empower HLO 1.1: A toolbox of methods, data, and dashboards HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Agencia Mexicana de Cooperación Internacional para el Desarrollo (AMEXCID) CIMMYT Potential AoW1 - Engage and Empower HLO
+---
+[ID: pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p28pt2]
+system Provincial govt. AOW 4 Market Systems, Policy Solutions and Scaling OP 4.2. Decision-support tools for efficient animal and aquatic food system Colombian Roundtable for Sustainable Cattle AOW 4 Market Systems, Policy Solutions and Scaling OP 4.2. Decision-support tools for efficient animal and aquatic food system Universidad del Cauca AOW 4 Market Systems, Policy Solutions and Scaling OP 4.2. Decision-support tools for efficient animal and aquatic food system Universidad de los Andes AOW 4 Market Systems, Policy Solutions and Scaling OP 4.2. Decision-support tools for efficient animal and aquatic food system EAFIT University Colombia AOW 4 Market Systems, Policy Solutions and
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p1pt2]
+Report June 2025 Contact: Nicoline de Haan (n.dehaan@cgiar.org)
+---
+[ID: pdf:CGI21-507033-PORB-Policy Innovations.pdf:p32pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 32 of 72 July 2025 | CGIAR Contracted partner Center Area of Work Title and Number High level output (If Available) University of Los Andes CIAT Governance and Political Economy (AOW03) 3.3: New communities of practice, political economy and policy process tools are developed and strengthened, bringing together decision makers and diverse stakeholders to strengthen science diplomacy, science policy engagement, design, and implementation. Tegemeo Institute in Kenya IFPRI Governance and Political Economy (AOW03) 3.3: New communities of practice, political economy
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt2]
+Research for Development (IRAD) Africa Rice Contracted AoW 2 - Pathways to Scale in Agrifood Systems Centre National de Recherche Agronomique (CNRA) Africa Rice Contracted AoW 2 - Pathways to Scale in Agrifood Systems The Council for Scientific and Industrial Research – Savannah Agricultural Research Institute (CSIR- SARI) Africa Rice Contracted AoW 2 - Pathways to Scale in Agrifood Systems Centre National de Recherche Appliqué au Développement Rural (FOFIFA/CENRADERU) Africa Rice Contracted AoW 2 - Pathways to Scale in Agrifood Systems L’Institut Sénégalais de Recherches
+---
+[ID: pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p13pt4]
+for delivering SAAF outputs and outcomes. These organizations are either think tanks and consultancy firms (e.g. MacKenzie), governmental extension services (Fisheries Commission Ghana), or NGOs (Heifer International, CARE). In those instances, CGIAR is well-positioned to undertake the work. Still, stakeholder engagement can be pursued with stakeholders to transition toward sustainability and scaling. The remaining 80% have been rated as moderately efficient and impactful in undertaking HLO work. This group encompasses NARES (KALRO, IFReDI), NGOs (Vétérinaires Sans Frontières); private sector organizations (EON Aquaculture Limited, Githunguri Dairy Cooperative); international organizations (FAO, World Bank, AfDB); universities from the Global North (Corwell, Kiel) or targeted countries (Universidad de los Andes, University of Nairobi, Hanoi University of Public Health). While CGIAR is well or moderately positioned in most instances, there are significant opportunities for collaboration, stakeholder engagement, and in some instances, formal partnerships. Sustainable Animal &amp; Aquatic Food Science Program Comparative Advantage analysis
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt2]
+(SME) Private Ltd CIMMYT ID DEPLOY IFFA Seed Co Ltd CIMMYT ID DEPLOY Indian Institute of Maize Research CIMMYT AB, ID DEPLOY Indo American Hybrid Seeds (India) Pvt. Ltd CIMMYT ID DEPLOY Institut de Recherche Agricole pour le Développement (IRAD) CIMMYT AB, ID DEPLOY Institut des Sciences Agronomiques du Burundi (ISABU) CIMMYT AB, ID DEPLOY Institut National de la Recherche Agronomique du Niger (INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]
+business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,
+---
+[ID: pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 13 of 86 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD FRANCE – FFEM Promover Oportunidades Sostenibles en la Cadena de Valor del Cacao de Excelencia (IA Lead of A1537) Alliance Bioversity CIAT AoW 3-Markets and Business Models; AoW 5-Gender Equality, Social Inclusion and Fairness Intermediate Outcome - AOW-IOC 3.2. Local producer organizations, national and sub-national public actors and private sector actors co-design or strengthen inclusive business models; 2030 Outcome - 2030 OC-4. Marginalized people participate in implementing innovations; 2030 Outcome - 2030 OC-3 Government, market and finance actors implement
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt2]
+National Agricultural Research and Extension Systems NARS National Agricultural Research System PCT Program Coordination Team PMU Program Management Unit PORB Plans of Results and Budgets RAB Rwanda Agriculture and Animal Resources Development Board RELASER Red Latinoamericana de Servicios de Extensión Rural (Latin American Network for Rural Extension Services) RUFORUM Regional Universities Forum for Capacity Building in Agriculture SAARC South Asian
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt2]
+la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics (Breeding for Tomorrow) ● T-PJ-003670- Long-term funding of Ex Situ collections of germplasm (IITA) (Breeding for Tomorrow and CapSha) ● L-LTG001-Long term funding of ex situ collections of germplasm (ILRI) (Breeding for Tomorrow) ● R-A-2023-9-Genebank-AI (Breeding for Tomorrow) ● T-PJ-003575: Cassava Allele Mining Project: (IITA) Mining useful alleles for climate change adaptation in the cassava from CGIAR Genebanks (Breeding for Tomorrow and Climate Action) ● T-PJ-003576- (IITA) Mining useful alleles for climate change adaptation cowpea (Cowpea Allele mining project: Mining useful alleles for climate change adaptation in cowpea from CGIAR Genebanks (year 2022-26) (Breeding for Tomorrow, CapSha, and Climate Acti on) ● T-PJ-004017-VACS (IITA): Vision for Adapted Crops and Soil: Bambara Groundnut (Breeding for Tomorrow, CapSha and
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt4]
+Cooperation TAP Tropical Agriculture Platform ToC Theory of Change ToR Terms of References TPI The Partnering Initiative UM6P Université Mohammed VI Polytechnique UNCTAD United Nations Conference on Trade and Development UNESCO United Nations Educational, Scientific and Cultural Organization. UNICEF United Nations International Children's Emergency Fund UPLB University of the Philippines Los Baños W3 Window 3 WCDI Wageningen Centre for Development
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p36pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 36 of 86 August 2025 | CGIAR External collaborations/partners Center Area of Work Title and Number High level output (If Available) L’Institut Tchadien de Recherche Agronomique pour le Développement – ITRAD – Chad CIMMYT AB, ID, MI, Enable l’Institut National de la Recherche Agronomique du Niger – INRAN – Niger CIMMYT AB, ID, MI, Enable Ministry of Agriculture and Food Security – MAFS – Sudan CIMMYT AB, ID, MI, Enable MyAgro – USA CIMMYT ID National Agricultural Research Organization
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt3]
+management of research &amp; scaling activities across CGIAR’s portfolio Agencia Mexicana de Cooperación Internacional para el Desarrollo (AMEXCID) CIMMYT Potential AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Secretaría de Fomento Agroalimentario y Desarrollo Rural (SEFADER) Oaxaca CIMMYT Contracted AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Secretaría del Bienestar (SEBIEN) de Quintana Roo CIMMYT Contracted AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp;
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 32 of 90 August 2025 | CGIAR Contracted partner Center Current Status of Partnership Area of Work Title and Number High level output (If Available) Dirección de Coordinación Regional y Extensión Rural (DICORER) CIMMYT Potential AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Fundación para la Innovación Tecnológica Agropecuaria y Forestal
+---
+[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p21pt3]
+and Technology (DOST) Philippines IRRI AoW03 Locally led adaptation 3.3, 3.4 and 3.5--- for 3.5 Policies, institutions, and interventions for equitable climate change adaptation Ministry of Agriculture Kenya IRRI AoW03 Locally led adaptation HLO 3.5 Recommendations on policies and institutions for addressing the root causes of inequality University of the Philippines, Los Banos and Xavier University IRRI AoW03 Locally led adaptation 3.3 and 3.4 - for 3.4 Novel framework and methods for avoiding maladaptation Royal University of Agriculture, Cambodia IRRI Aow04 Low-emission transitions 4.2 and 4.4
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p35pt3]
+MI, Enable Ethiopian Institute of Agricultural Research – EIAR – Ethiopia CIMMYT AB, ID, MI, Enable Institut d’Economie Rurale – IER – Mali CIMMYT AB, ID, MI, Enable Institute for Agricultural Research, Samaru – IAR – Nigeria CIMMYT AB, ID, MI, Enable Institute Togolais de Recherche Agronomique – ITRA – Togo CIMMYT AB, ID, MI, Enable Insitute of Agricultural Research for Development – IRAD – Cameroon CIMMYT AB, ID, MI, Enable Institut Senegalais de Recherches Agricoles – ISRA – Senegal CIMMYT AB, ID, MI, Enable Instituto de Investigacao Agraria de Mocambique – IIAM – Mozambique CIMMYT
+---
+[ID: pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p42pt3]
+producer with Felistus Chipungu (right), OFSP breeder and scientist, CIP . Credit: C. de Bode/CGIAR
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p25pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 25 of 44 Partner Center Area of Work Title and Number High level output (If Available) Local Governments for Sustainability, Nairobi City County, Dhaka North City Corporation, Local Government of Quezon City (Philippines), RUAF Foundation International Potato Center / Centro Internacional de la Papa 3.5.5 Urban food systems governance - Delivering knowledge products, evidence and capacity sharing with policy makers to guide interventions aimed at strengthening
+---
+[ID: pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p21pt4]
+3.3, 5.2, 5.3, 5.4 or 5.5. Climate adaptation Overall the impact area with third highest prioritized activities. Broad prioritization of AoW2&gt;AoW4&gt;AoW 3&gt;AoW 1&gt;AoW5 Relatively moderate priority. No priority for HLO 1.2, 1.5, 5.1, 5.4 or 5.5. Relatively moderate priority. No priority for HLO 1.5, 5.4 or 5.5. Second Highest ABI priority for IA Relatively moderate priority. No priority for HLO 1.5, 5.1, 5.4 or 5.5. Highest ABI priority for IA Relatively moderate priority. No priority for HLO 1.5, 5.4 or 5.5. Third Highest ABI priority for IA Relatively moderate priority. Relatively moderate priority. Environmental Health Moderate-low prioritization. Third highest prioritization of regions. De- prioritization of HLO 1.2, 1.5, 5.1 and 5.5 Relative low prioritization. Lowest across regions. De- prioritization of HLO 1.2, 1.5, 3.3, 5.1, 5.3 and 5.5 Moderate-low prioritization with additional de- prioritization of HLO 1.5, 5.4 and 5.5 Moderate- low prioritization . De- prioritization of HLO 1.5, 5.1 and 5.5 Moderate-low prioritization. Second highest prioritization of regions. De- prioritization of HLO 1.5, 5.1 and 5.5 Moderate-low prioritization. Highest prioritization of regions. De- prioritization of HLO 1.5, 5.1 and
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt1]
+Capacity Sharing Accelerator Inception Report 4 ISNAR International Service for National Agricultural Research ISRA Institut Sénégalais de la Recherche Agricole (Senegalese Agricultural Research Institute) ITU International Telecommunication Union KOICA Korea International Cooperation Agency KPIs Key Performance Indicators. MELIA Monitoring, Evaluation, Learning, and Impact Assessment NARES National Agricultural Research and Extension Systems NARS National Agricultural Research System PCT Program Coordination Team
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1]
+23 Bilateral Contribution to Multifunctional Landscapes MELIA Studies UK FCDO - Seed to tree: value chains and partnerships for resilient restored forests in Malaysia • Actor engagement and outcome tracking UK – GCBC (UK-Defra) - Deploying Diversity as a Strategic Asset for Scaling of Ethiopia’s Green Legacy Initiative for Climate Change Resilience and Livelihoods • Program learning review • Actor engagement and outcome tracking FRANCE – FFEM Promover Oportunidades Sostenibles en la Cadena de Valor del Cacao de Excelencia (IA Lead of A1537) • Actor engagement and outcome tracking CoIMPACT INDIA • Program learning review Fruitful Lands India Phase II • Actor engagement and outcome tracking Sustainable Investments for Large-scale Rangeland R • Actor engagement and outcome tracking Building Community
+---
+[ID: pdf:Portfolio Narrative_2024.pdf:p47pt3]
+Research Organization Centre de coopération internationale en recherche agronomique pour le développement Wageningen University and Research Centre Cornell University Zambia Agriculture Research Institute Ethiopian Institute of Agricultural Research Agricultural Research Institute - Tanzania Food and Agriculture Organization of the United Nations Indian Council of Agricultural Research 176 118 135 111 106 87 98 80 79 78 Food and Agriculture Organization of the United Nations Agricultural Research Institute - Tanzania National Agricultural Research Organisation (Uganda) Ministry of Agriculture and Rural Development (Vietnam) Kenya Agricultural and Livestock Research Organization Instituto de Investigacao Agraria de Mozambique Department of Agriculture Extension (Bangladesh) Indian Council of Agricultural Research Zambia Agric</t>
+  </si>
+  <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: According to the Annex pie chart, what was total 2024 revenue and the split by funding source?\n\nContext:\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 6\nContent: Research results can be defined according to the nature of the change and the control over it.\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p14]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 14\nContent: Figure 1: Research results according to the kind of change and the control over it.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 23 Annex 2: ISDC feedback relating to pooled &amp; non-pooled alignment5 This section provides a direct extract from the ISDC Feedback on CGIAR Portfolio Narrative 2025- 2030. Comments relating to the alignment of pooled and non -pooled have been extracted from the broader set of comments. They have not been edited to e.g. update Program and Accelerator nomenclature. • Articulation of how the Portfolio, including bilateral and W1 funding, will be bundled into Megaprograms is still lacking. Bilateral funding is restricted and is provided for a specific purpose and with specific intended impacts. This needs to be honored a nd the lack of flexibility in shifting those funds into other areas should be clearly acknowledged. • Alignment of the entire Portfolio with the CGIAR 2030 Research and Innovation Strategy needs to be strong and explicit. How will management ensure that bilateral funding delivers against this Strategy? In addition: o What happens if a bilateral project is not strongly aligned with the Strategy and how will CGIAR ensure that opportunity costs are covered? o Will all bilateral projects across all Centers be mapped to support the Portfolio? • A challenge that should be acknowledged is incorporating bilateral funding into Megaprograms. Each Megaprogram and Accelerator will be large scale and staff will be consumed by the implementation of contracted work. Trying to build Megaprogram linkages in parallel with bilateral funding should be additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative 2025-2030\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p5]\nFile: Type3_2024Report.pdf\nLocation: page 5\nContent: Section 2: Portfolio Performance and Project Coordination Progress 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022-2024. 3. Science Group Projects (SGPs) are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance and fiduciary oversight. 4. EiB II will report through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they will provide a concise, high-level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the technical reports. 2.1. Technical Reporting Arrangement 2022-24 CGIAR Technical Reporting fulfils the System-level programmatic reporting requirements set out in the Standard Provisions annexed to the Funding Agreement or Arrangement signed between each Funder and the System Organization.2 The 2024 Technical Report includes the following Initiatives, Impact Platforms and SGPs3: • All 32 Initiatives • Five Impact Platforms – Gender Equality, Youth and Social Inclusion – Environmental Health and Biodiversity – Nutrition, Health and Food Security – Climate Adaptation and Mitigation – Poverty Reduction, Livelihoods and Jobs • Six SGPs – Accelerated Varietal Improvement and Seed Delivery of Legumes and dryland Cereals in Africa (AVISA) – Roots Tubers and Banana (RTB) Breeding – Accelerating Genetic Gain and Varietal Replacement in Rice - Phase 2 (AGGRi 2) – Excellence in Breeding (EiB) II: Cross-Crop Support Services for Breeding Acceleration4 – Accelerating Crop Improvement Through Genome Editing 2023-2025 – Climate Adaptation Insight For 2024, CGIAR will produce and deliver a total of 46 Technical Reporting outputs: • March 2025: Results from 2024 published on the online CGIAR Results Dashboard (1). • May 2025: Publication of 42 Type 1 (32 x Initiative reports; 5 x Impact Platform reports; 5 x SGP reports) Reports and a Type 3 Report (1). • End of June 2025: Publication of the Portfolio Narrative (1). • End of June 2025: Publication of the Type 2 Report: CGIAR Contributions to Impact in Agrifood Systems (2022-24) (1). Each of these reports is released separately and will be available in PDF format. 2024 Technical Reporting covers USD 370 million (USD 322 million for Initiatives and Impact Platforms, and USD 49 million for W3 SGPs), representing nearly 40 percent of CGIAR’s total pooled and non-pooled funding for 2024. 2.1.1. Streamlining the process and adding value to stakeholders In 2022 CGIAR launched a new 2022-24 Technical Reporting Arrangement, co-developed with the System Council’s Strategic Impact Monitoring and Evaluation Committee (SIMEC). The 2022 rollout was regarded as a “first pancake” or trial phase, establishing minimum viable functionality and setting the foundation for annual improvements. Key achievements of 2022 Technical Reporting included the adoption of a common report template aligned with the Technical Reporting Arrangement for Initiatives and Impact Platforms; integration with CGIAR’s Results Framework; digital linking of results to theories of change (TOCs); and the introduction of quality assurance processes mediated by third parties. Additionally, a new interactive CGIAR Results Dashboard was launched, and the Performance and Results Management System (PRMS) – an online reporting system – was developed, alongside adaptive management processes and the rollout of Innovation Packages and Scaling Readiness plans. Building on this, 2023 Technical Reporting incorporated lessons from a 2022 Learning and Optimization process, documented in a 2022 Learning and Optimization report. Key advancements included transitioning to “Always on” reporting by opening the PRMS from September 2023, more than doubling the reporting window compared to 2022 and allowing greater flexibility for Initiatives, Impact Platforms, and SGPs. Quality assurance was optimized through four staggered batches across 2023 and 2024. Further enhancements included expanding per-result tagging to all five Impact Areas. A Risk Management Module was launched to support risk identification and reporting at the Initiative level. A large number of participants joined training sessions to support reporting, dashboard use, and onboarding, and the rapid uptake of adaptive management strengthened strategic agility, with positive feedback from across the Portfolio. The Research Plans of Results and Budgets section of the CGIAR website was updated to ensure easy open access to Initiative, SGP and Impact Platform Plans of Results and Budgets (PORBs). The 2024 reporting cycle continued this trajectory, integrating insights from the 2023 Learning and Optimization process and Action Plan to further refine CGIAR’s Technical Reporting processes and products. Key improvements in 2024 included: • Launching the PRMS Planning Module to support the replan process: The launch of an online Planning Module synchronized TOC and Planning data in the PRMS, improving the efficiency and quality of planning workflows. Enhanced replan guidelines were provided to help Initiatives, Impact Platforms, and SGPs implement 2023 Reflect recommendations and align budget forecasts with updated budget envelopes. To support continuous learning and adaptive management, a user experience survey on the Planning Module was conducted to assess effectiveness and inform user-centered enhancements for the 2025-30 Portfolio. • Further simplifying reporting processes and tools: A series of enhancements to PRMS functionalities were implemented to improve efficiency and usability. Improved filtering options, enhanced notification systems, and more clearly structured result PDFs now enable quicker access to relevant information. Innovation Packages and Scaling Readiness language and templates were simplified. Reporting was streamlined and modified to suit the final year of reporting for the Portfolio, with an Outcome Indicator Module co-developed with input from Initiatives, Impact Platforms and SGPs to provide them with the opportunity to assess their progress against targets for Work Package outcomes and end-of-Initiative outcomes; summative and yearly highlights were combined into a single report; and adaptive management processes removed. • Improving decision-making within the PRMS: Broader engagement from PRMS testers across reporting entities and Senior Program Managers was integrated into PRMS feature development, ensuring that system updates were aligned with user needs and supported consistent decision-making. • Enhancing product clarity: The Type 1 Annual Report template was reviewed to better accommodate end-of-Initiative outcome reporting for the final year of the Portfolio. Improvements to the Results Dashboard were made to enhance the accessibility of IPSR insights. • Strengthening quality assurance: Examples include updated and enhanced QA guidance, and updated guidance on Impact Area tagging. An AI tool was prototyped and tested on a series of data fields, with the intent to leverage lessons learned and develop an enhanced AI tool that can be applied to a broader set of reported data and integrated into the PRMS, supporting both the reporting and QA phases. • Developing the Semantic Natural Language Processing Aggregator Platform (SNAP): SNAP is an AI-powered tool enhancing access to and analysis of CGIAR’s reported outputs, outcomes, and impacts. It improves access to Portfolio information and results evidence through semantic searches, thematic clustering, and automated summaries, complementing the CGIAR Results Dashboard. SNAP-supported narratives were integrated into the CGIAR 2024 Portfolio Narrative, and ongoing refinements will further enhance its role in Portfolio reporting. • Further integrating SGPs and Impact Platforms: Between 2022 and 2024, CGIAR progressively aligned these entities with its Technical Reporting processes and common systems to enhance consistency and coherence. In 2023, three Impact Platforms – Nutrition, Health and Food Security; Climate Adaptation and Mitigation; and Environmental Health and Biodiversity – were onboarded alongside the Gender Equality, Youth and Social Inclusion Impact Platform (which reported in 2022), each receiving tailored support such as TOC and results framework development. The SGP pilot launched in 2023 further expanded CGIAR’s reporting ecosystem by integrating Center-specific Window 3 awards, with two SGPs submitting first-year results using the PRMS Reporting Tool and Type 1 Report template. In 2024, integration expanded to include the Poverty Reduction, Livelihoods and Jobs Impact Platform and four additional SGPs, further broadening the reporting ecosystem. • Enhancing risk management through the PRMS Risk Module: The Risk Management Module, launched in 2023 to support Initiative management and reporting of risks, was further enhanced in 2024, allowing Initiatives to capture transition-focused risks. It enabled Initiatives to review, update, or close risks, contributing to the design of the 2025-30 Portfolio. The updated Risk Management Module will be used by Programs and Accelerators from 2025 onward. Climate-Smart Village set-up under the Adaptation and Mitigation Initiative in Agriculture (AMIA) of the Department of Agriculture. Credit: Miguel Mamon/CIAT May 2025 54 CGIAR Portfolio Practice Change (Type 3) Report 2024\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 4\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 4 1. Technical Reporting Arrangement purpose, scope, value proposition, delivery and optimization, Purpose The purpose of th e Technical Reporting Arrangement 2025 -2030 (“TRA 25-30”) is to set out the technical reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. The TRA 25-30: • Provides the parameters that e nable the Centers, the CGIAR System Partners and the System Organization to fulfil their technical reporting obligations under the funding agreements that apply to the use of Window 1 and Window 2 funds from the CGIAR Trust Fund (“Pooled Funding”). These parameters also allow the Integrated Partnership Board to fulfil its responsibility under the CGIAR System Charter to report on programmatic performance of CGIAR Research on an annual basis. • Provides, through the establishment of common technical reporting principles, enabling tools and mechanisms, progressive alignment and synergy between the technical reporting requirements that apply to components of the CGIAR Portfolio that are funded by Pooled Funding and those that apply to the components that are funded by other sources of funds (“Non-Pooled Funding”). • Sets transparency, performance tracking, and accountability expectations between CGIAR System Funders and CGIAR including Centres, • Informs decision making at different levels, underpins research management, operationalizes the Performance and Results Management Framework (PRMF), and guides portfolio -level MELIA and the design of the next Performance and Results management System (PRMS). The current Technical Reporting Arrangement that applies to the CGIAR Portfolio during the period 2022-24 (“TRA 22-24”) was co-developed by CGIAR and System Council/Strategic Impact Monitoring and Evaluation Committee (SIMEC) members in 2022. A new TRA is needed to match 2025-30 portfolio parameters, notably the alignment of pooled and non-pooled funding sources, and to apply lessons learnt from 2022-24. Scope The TRA 25-30 provides the operational and enabling basis to plan, monitor, learn and report on the 25-30 Portfolio. It is designed to progressively enable Programs and Accelerators, Centers and their research teams to report on the pooled, bilaterally and W3-funded components of the 2025- 30 portfolio in an integrated and aligned way, without increasing reporting burdens of Centers and Scientists. Going forward, the CGIAR Integrated Partnership will work towards progressively greater alignment of W3/bilateral projects and programs with the 2030 outcomes and theories of change of the Programs and Accelerators. Centers will provide key agreed information on their W3/bilaterally funded projects and programs to enable Program/Accelerator leaderships to explore ways to achieve alignment based on, inter alia, complementarity of results as well as actual or potential thematic, geographic, and partnership overlaps. Reporting on and attribution\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 5\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results framework, underpinned by a new Technical Reporting Arrangement, will provide robust, continuous performance and results reporting across all funding sources, as well as adaptive management of the Portfolio. 1 Value Proposition The TRA 25-30: - Creates value by delivering an integrated approach that tracks the performance of each Program and Accelerator, - Brings together the inputs (including costs), outputs, outcomes and impacts of the total portfolio to allow for easier and more robust Return on Investment (ROI) calculations. - Avoids creating a significant additional and duplicative layer of complex reporting requirements for W3/ bilaterally funded work. - Informs decision making through providing ready access to demand-driven quality raw and curated data products. Delivery The TRA 25 -30 will be delivered in line with Management arrangements for CGIAR’s 2025 —30 science and innovation Portfolio. Specific roles and responsibilities will be defined in 2025. 1 CGIAR Portfolio Narrative, 1 November 2024\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:p7]\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 7\nContent: Trifa, Nicoleta (CGIAR System Organization) 0:48 Yep. OK, good. So thank you. This session is the first of two session plans for today, planned for today, with the second being scheduled later at 3:00 PM CET to accommodate colleagues in other time zones. Technical reporting. My name is Nicoletta Trifa. By the way, I'm part of the Portfolio Performance Unit, the support unit within the Office of the Chief Scientist. Here is an overview of what we'll cover in the next minutes. I believe my presentation will take 2025 minutes and then we'll leave room for questions at the end, if that's OK. So what we'll cover an update of the technical reporting arrangements 2025 to 2030, priorities and changes for 2025, a brief introduction on the annual technical report and the neighbors. So this mean the performance and results. Management system and the quality assurance, the technical reporting timeline, available resources and support and what's next and how to stay engaged. I want to mention that this session marks the start of the conversation around 2025 technical reporting. We want to give you the early look at the key priorities and plans for the months ahead, and the goal is to make sure that you stay informed, prepared and supported with a clear understanding of upcoming deliverables and timelines. And also clarity on who to reach out to if you have questions or if you need help along the way. Good. Technical reporting arrangements for the new portfolio. The 2025 to 2030 portfolio has been approved by the CGR Global Leadership team on in June 2025 and provides the operational basis to plan, monitor, learn and report. On the new portfolio. It is designed to progressively enable programs, accelerators and centers to report on the pooled and window 3 bilateral projects of the new portfolio in an integrated and aligned way without increasing the burden on centers and the scientists. Main changes compared to the previous technical reporting arrangements, streamline reported reporting. So less products, more integration, lower transaction costs, stronger impact, focus results. To be clearly linked and packaged under impacts, outcomes and associated agreed indicator targets and better linkages between the theory of change or so plan of results and budget and technical reporting. The primary audiences for technical reporting are funders and CGR staff at integrated partnership, portfolio and program and accelerator levels. A secondary audience is the partners. Annual technical reporting covers the individual annual technical reports for program and accelerators, as well as a portfolio view of aggregate contribution to thematic and geographic targets. And relevant content from this technical reports are integrated into the CJR corporate reporting. In terms of the 2025 technical reporting priorities, 2025 is a transition year with technical reporting arrangements, implementation again focusing on streamlined reporting and on strengthening the linkages between theory of change. Porb, media and technical reporting. As many of you know, in the previous portfolio these components were not properly linked, so it was a bit challenging to demonstrate progress against the theory of change or the plans, as you know. In terms of deliverables for 2025. These are the program and accelerator technical reports, which are due in April 2026, the portfolio narrative, which is due in 2026 in June. Integration of top 80% of window tree and bilateral projects by central dollar value into reporting and planning. Application of the minimum data standards for window tree and bilateral reporting. And mapping of refinement during the pause and reflect process which will take place early Q 1/20/26. So as I was mentioning, this year is seen more as a transition year towards KPI based planning and reporting and efforts are underway to enable planning and reporting at the KPI level, which is aligned with the system office objective and key results for 2026 and 20. These are to be confirmed, so they haven't been confirmed yet, but I've pasted them here so that you can see the 2026 objective and key results for the system office. So 100% program and accelerate the work plans and budget. An annual technical report. Which provide for software enabled monitoring of erformance and results against smart Ki by center, ear and ooled funds invested. So next year, 80% of centres, CGR, window three and bilateral funded work by value included in 2025 technical reports and then the following year in 2027, this will increase to 90% of centres. Window 3 and bilateral funded work included in 2026 technical reports. The following slides, what I have, what I have included in the following slides, it's a brief introduction into. What is expected in terms of deliverables from programs and accelerators together with an overview of the performance and results management system and the QA. I realized that some in this call some of you are already familiar with the reporting arrangements from the previous portfolio. While for others this might be entirely new. So our goal is to bring everyone to the same level of understanding so that we can move forward with clarity and shared expectations for the 2025 technical reporting. OK, so technical reporting for program and accelerator. We'll focus on three key deliverables. So first is reporting results, the 2025 results in the Performance and Reporting Management system, PRMS. Each program accelerator and mapped window 3 project will report 2025 results in the system and we strongly encourage to report results that were planned and budgeted. So results which have been included in the reports. As the outdated technical reporting system will allow for tracking results against plans. Secondly is the quality assurance of reporting results. As you know, the results submitted go through the quality assessment process and we will share more details on this process in the timeline in an info session scheduled for later. Which we will schedule later in in September, October and the quality assess results will be available on the results dashboard. Inform the pause and reflect and will be included in the technical reports in the annual technical reports. A third deliverable for program and accelerators is drafting estimation of the 2025 Annual Technical Report. So each program and accelerator is responsible for drafting and internally validating quality assessing their 2025 Annual Technical Report. Before submitting it to the PPU, so to the perform portfolio performance unit. Again, guidance on this, the detailed process and validation process will be shared with you timely. Also to support this process, an AI generated V0 draft will be provided as a starting point. The annual technical reports. What are they? This the annual technical report. The the the aim is to make them short, so to 20 to 30 pages, concise and targeted. They provide assurance on annual program accelerator delivery against the boards, so plan of results and budget and progress on theory of change. They are based on quality assess results, the template guidance and as I mentioned and. AI V0 will be provided to all rogram and accelerator teams. Annual technical reports need to be submitted by each program and accelerator in March, April, so more details on this will follow and publication is intended to happen end of April, beginning of May. Here to the right side you have the. Content of the annual the proposed content for the annual technical report as per the technical reporting arrangements. Many of you will notice that there are not no big changes compared to previous portfolio, so the idea is to have a fact sheet and executive summary. The annual progress on theory of change, area of work details, a section on results, section on partnerships, portfolio linkages, adaptive management and then one key result story. But again, we will plan a detailed deep dive session on the annual technical report template and the guidance. So there will be time for you to ask questions in detail about about this and to receive support obviously. I've also included here for reference links to the 2024 Annual Technical Reports from the initiatives and impact platforms, and also a link to the 2024 Portfolio Narrative Report. In case you want to, you want to have a look to see, um, what it captures. PRMS. So this stands for Performance and Results Management System is the system the the the the environment where results need to be submitted. Again, the team is working on updating their resources. There will be. New users onboarding decks created with the links to different information and I I believe the PCU Alison together with the program coordinators. Are. The all the PRMS roles. So PCU is leading a work to define the PRMS roles and to get the information from program and accelerators regarding who from each program accelerator should have what role in PRMS. To enable us to to provide the right access to the platform when the time comes to report. Quality assurance process. So results submitted by program and accelerators in the PRMS will be quality assessed by a quality assessment team in February 2026. Your participation in this process is required. Guidance and resource resources will be provided and also an info session will be scheduled later this year. What is the QA? It is a process that aims to improve the quality of the reported data to provide consistency across the system, ensure reliability of reported results. Inform the learning process and improve the overall CGR accountability and transparency. Quality assess data informs the reflect process which takes place early Q12026, the results dashboard. So once the quality assessment of the results is finalized, the quality assess results will be pushed to results dashboard. You most probably have seen that. Reading. It also informs and are the results. The practices results are included in the annual report, in the portfolio narrative, and then in the overall CGIR annual report. In terms of the the timeline, so we have this info session now to provide an overview on the technical reporting and there will be several other info session and deep dive scheduled. Throughout September and October of reporting 2025 results, we believe that it will be feasible to open the PRMS in November for program and accelerators to to report. The date is still to be confirmed. We're aiming to to, yeah, to meet to to to end November. Hopefully this will be this is feasible from the technical side quality assurance. It's planned for February 2026 reflect process as I was mentioning Q 1/20/26 and then annual technical reports are due in March, April 2026 as well. Where to find information pertaining to technical reporting and planning and media? There is a one stop shop for for um all this. It's called the Performance and Results Hub. I'm gonna stop sharing cause I wanna share. Um, I'm gonna stop sharing the deck. I wanna. We could resent the hub. I'm not going to go through each section, but at least. So that you can see for those who are new more specifically to see and we will also share the link obviously the performance and results hub as I was mentioning it has detail on reporting, planning, reflect, replan. So you come in here, you click on 2025 reporting and then you will have access to the latest information, to the timeline, latest update, upcoming events. So all the information, information. Session dates will be listed here. We'll also have a subsection here with. Recording from from meetings, so that will be posted. For example today after this session we'll post a recording and the deck here for you to access and there is a section on frequently asked question. We recycled a couple of questions from the previous portfolio and updated them so that they are applicable to the program and accelerator teams, so feel free to go here and and browse. As resources become available, we will place them here and we will notify you by e-mail. OK. Going back to my deck. Which? In terms of engagement plan, so in order to streamline communication and optimize support for program accelerators and centers with mapped window 3 bilateral projects, we will send bi-weekly emails to everyone in this. This goal with key updates on technical reporting, with reminders and also with the latest questions and answers available on the hub. There will be targeted emails focusing on specific categories within the program accelerators. We want to engage with some of you on technical reporting, revisions, developments. And the aim is to gather feedback from you. Program coordinators will be copied on these emails. Info session. So a specific topic and we'll plan info session on specific topics, for example the standard indicator, description shades, the guidance on technical reporting, quality assurance. Reporting on innovations, the PRMS, so deep dive on the PRMS, the updates, the tool and so on. And during the reporting phase and the QA we will have weekly drop-ins. So this drop-ins is there will be no presentation. Presentation during the during this drop-ins. The purpose is for us to provide live support, so to answer your questions on the spot and the primary focus will be as I was mentioning, reporting and the QA. For if you know for every question you have, we invite you to use this e-mail address performanceandresults@cgr.org. This is the. The e-mail address we use for all technical reporting questions. So you have the questions right to us at performanceandresult@cjr.org and you will receive a response. We are aiming to respond within the 24 hours. Just to give an example, you know going back here I've gotten the targeted targeted emails and feedback. So this is a good example on for example how we plan to engage and get get feedback from from you on the PRMS enhancements so. Usually we send there's an e-mail sent to invite you to provide feedback on a o</t>
   </si>
   <si>
@@ -1248,6 +1662,15 @@
   </si>
   <si>
     <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: ¿Quién tiene la responsabilidad fiduciaria y programática?\n\nContext:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 2\nContent: el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 3\nContent: business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 1\nContent: Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 1\nContent: Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 1\nContent: CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 3\nContent: at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and\n\n---\n\n[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2]\nLink: https://cgspace.cgiar.org/items/8acc660f-7305-4e4b-ab21-1c192611b017\nFile: CGI21-507032-PORB-Climate Action.pdf\nLocation: page 11 part 2\nContent: II) ICRISAT AOW02 Digital Advisories and Climate Risk Management $89,064 N-343001-GCAN INITIATIVE IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $1,321,123 N-601158-SPIR II IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $201,213 PJ-003953: APPUI A LA TRANSFORMATION ET A LA RESILIENCE DES SYSTEMES ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 10 part 2\nContent: - 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness\" 411,914 \"Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO\" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 \"Andean Crop Diversity for Climate Change P-1560-DGUL\" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 \"Youth, Citizen Science and E-commerce:\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 1\nContent: CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 4\nContent: Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations, and evidence-based programs for enhancing inclusive informal food markets that effectively create quality jobs for young women and men and deliver safe and healthy foods in urban environments University of Peradeniya, Wayamba University of Sri Lanka, Asian Development Bank, World Food Programme International Food Policy Research Institute 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents CGI21-507031-PORB-Food Frontiers and Security.indd 24CGI21-507031-PORB-Food Frontiers and Security.indd 24 29/07/2025 19:3929/07/2025 19:39\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 2).docx:u52-56]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%202%29%2D20250729%5F150218%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E57e21346%2Dc6ca%2D4c63%2D8839%2D3e2a327c5116\nFile: 2025 Technical Reporting Information (Session 2).docx\nLocation: paragraph 52 to paragraph 55\nContent: Aryal, Bishal (IFPRI) 44:47 Thank you. Thank you. Nirmal, Rajalakshmi (IFPRI) 44:50 Thank you. Bye, bye. Trifa, Nicoleta (CGIAR System Organization) 44:53 Hi. Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%201%29%2D20250729%5F100141%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E76da6c8e%2D6234%2D41ff%2Dba2c%2Dc2068392ed82\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: Se reportan desvíos potenciales en su uso. ¿Quién tiene la responsabilidad fiduciaria y programática, qué debe informar el Center y qué facultades de acción tiene la System Organization (SO)?\n\nContext:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 2\nContent: el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 1\nContent: Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 1\nContent: CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos\n\n---\n\n[ID: pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_Inception Report 30-06-2025.pdf\nLocation: page 4 part 3\nContent: Frameworks for Climate Services PLACA Climate Action Platform for Agriculture in Latin America and the Caribbean / La Plataforma de Acción Climática en Agricultura de Latinoamérica y el Caribe PMU Program Management Unit PPU Portfolio Performance Unit PRMS Performance and Results Management System REMET Reducing Methane Emissions from Rice project ROI Return on investment S4I Scaling for Impact (Program) SA South Asia SB\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 1\nContent: CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 10 part 2\nContent: - 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness\" 411,914 \"Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO\" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 \"Andean Crop Diversity for Climate Change P-1560-DGUL\" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 \"Youth, Citizen Science and E-commerce:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 1\nContent: Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 4\nContent: nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 3\nContent: business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 3\nContent: at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%201%29%2D20250729%5F100141%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E76da6c8e%2D6234%2D41ff%2Dba2c%2Dc2068392ed82\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 2).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%202%29%2D20250729%5F150218%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E57e21346%2Dc6ca%2D4c63%2D8839%2D3e2a327c5116\nFile: 2025 Technical Reporting Information (Session 2).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 2)-20250729_150218-Meeting Recording 29 de julio de 2025, 1:02p.m. 47 min 36 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: ¿Quién gestiona colectivamente los requisitos de M&amp;E de los Funders y cómo se evita la duplicación?\n\nContext:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 2\nContent: el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 1\nContent: Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 1\nContent: CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 45 part 3\nContent: Seed Ltd CIMMYT ID DEPLOY PROASE Productores Asociados de Semillas S.C. de R.L. de C.V. CIMMYT ID DEPLOY Productora de Semillas Azteca S.P .R. de R.L. CIMMYT ID DEPLOY PRODUCTORA DE SEMILLAS SMART SEEDS SAS DE CV CIMMYT ID DEPLOY Productora de Semillas Zarco S.P .R. de R.L. CIMMYT ID DEPLOY Productores de Semilla de Copandaro S.P .R. de R.L. CIMMYT ID DEPLOY Productos y Servicios Agrícolas S.P .R. de R.L. CIMMYT ID DEPLOY QualiBasic Seed Company (QBS) CIMMYT AB, ID\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 1\nContent: CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 23 part 3\nContent: Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 10 part 2\nContent: - 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness\" 411,914 \"Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO\" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 \"Andean Crop Diversity for Climate Change P-1560-DGUL\" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 \"Youth, Citizen Science and E-commerce:\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 22 part 3\nContent: de Cajas Rurales de Ahorro y Crédito Comunidades de Oriente (CECRUCSO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organización para el Desarrollo del Corquin (ODECO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organismo Cristiano de Desarrollo Integral de Honduras (OCDIH) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 4\nContent: nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%201%29%2D20250729%5F100141%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E76da6c8e%2D6234%2D41ff%2Dba2c%2Dc2068392ed82\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 2).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%202%29%2D20250729%5F150218%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E57e21346%2Dc6ca%2D4c63%2D8839%2D3e2a327c5116\nFile: 2025 Technical Reporting Information (Session 2).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 2)-20250729_150218-Meeting Recording 29 de julio de 2025, 1:02p.m. 47 min 36 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 46 part 3\nContent: C.V. CIMMYT ID DEPLOY Semillas Barriga S.R.P . de R.L. CIMMYT ID DEPLOY Semillas Berentsen S.A. de C.V. CIMMYT ID DEPLOY Semillas Cinteotl S.P .R de R.L. CIMMYT ID DEPLOY Semillas Iyadilpro y Ya S.A. de C.V. CIMMYT ID DEPLOY SEMILLAS MEJORADAS S.A. CIMMYT ID DEPLOY Semillas Ocso S.P .R. de R.L. CIMMYT ID DEPLOY Semillas Proseso SA DE CV CIMMYT ID DEPLOY Semillas y Agroinsumos Golden S.P .R. de R.L. de C.V. CIMMYT ID DEPLOY Semillas PROSASOL S.P .R. de R.L."}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: Who coordinates funders’ M&amp;E requirements across the CGIAR Portfolio and how is duplication avoided? \n\nContext:\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23 part 4\nContent: additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 2 part 4\nContent: report is part of the CGIAR System Organisations’ technical reporting arrangement. We would like to thank all funders who supported this work through their contributions to the CGIAR Trust Fund, and those who supported bilaterally: https://www.cgiar .org/funders. The report was led by the Portfolio Performance Unit, with expert technical support from the Food Security Evidence Brokerage. We gratefully acknowledge the contributions and insights from many CGIAR staff who provided access to source materials, selected prominent themes, and reviewed drafts. This included Impact Area Platform Directors, regional leaders, CGIAR Center assessment and monitoring specialists, the Independent Advisory and Evaluation Services, the Donor Relations and Business Development unit, the Communications and Advocacy unit, CGIAR research leaders and senior\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 29 part 2\nContent: of information on how climate mitigation is covered in the Portfolio. There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. There is a lack of information on how orphan and opportunity crops and pulses are covered in the Portfolio. There is a lack of information on how\n\n---\n\n[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p33pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_Inception Report 30-06-2025.pdf\nLocation: page 33 part 2\nContent: is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. N/A There is a lack of information on how orphan and opportunity crops and pulses are covered in the Portfolio. N/A There is a lack of information on how youth and social inclusion (that does not relate to gender) is covered in the Portfolio. N/A There is a lack of information on how capacity sharing (as it relates to internal learning and decolonization of research) is covered in the Portfolio. Capacity sharing is foundational to\n\n---\n\n[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p39pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_Inception Report 30-06-2025.pdf\nLocation: page 39 part 4\nContent: more details on ToC, Areas of Work, etc. We have significantly reworked and streamlined the research questions. They are now underpinned by the assumptions formulated in the revised ToC these also serve as hypotheses (in terms of fulfilled assumptions) for the research questions. Linkages with other Programs and Accelerators A concern is how the accelerator will effectively work with and build on other capacity sharing activities at CGIAR (with other Programs and Accelerators) without duplication or competition (pp. 85). The Accelerator will include a matrix analysis of Programs and other Accelerator during inception, to map Programs’ AoW and its own AoW, in order to define common interests in research questions or challenges, synergies, alignments, complementarities, and avoid duplication of actions. Section 8 of the inception report details how the accelerator would work with other programs to ensure synergy, and avoid duplication and support complementarity in terms of delivery of its service portfolio.\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p6pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 6 part 1\nContent: 2.2. Close-out of the 2022-24 Portfolio As the 2022-24 Portfolio closed, close-out guidelines were designed to ensure a smooth transition to the new Portfolio, building on past achievements while maintaining continuity in science and innovation delivery. The close-out process focused on the timely preparation and submission of 2024 technical and financial reports, ensuring all CGIAR teams and partners met Portfolio deliverables, and facilitating effective engagement and continuous communication with stakeholders. Proactive mitigation measures were identified to manage risks associated with the transition to the new research Portfolio. Focus was placed on sustaining partnerships beyond the conclusion of the 2022-24 Portfolio to ensure ongoing collaboration. The guidelines included a section on SGPs to ensure alignment. This structured approach ensures that the achievements and collaborations of the 2022-24 cycle are seamlessly integrated into the new Portfolio. 2.3. Transitioning to the 2025-30 Portfolio Support was provided to the CGIAR Portfolio Transition Team, which included the development of Inception Guidelines that outlined the principles and processes to assist Transition Teams in planning and achieving inception deliverables for the 2025-30 CGIAR Portfolio. In 2024 work began on developing a new Technical Reporting Arrangement for 2025-30 (TRA 25-30) to define the Technical Reporting requirements for the next CGIAR Portfolio. A cross-CGIAR working group – comprising Center experts and System functions – led its development. The TRA 25-30 will promote progressive alignment between reporting requirements for pooled and non-pooled\n\n---\n\n[ID: pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p30pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact%2FScaling%20for%20Impact%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact&amp;p=true&amp;ga=1\nFile: Scaling for Impact_Inception Report 30-06-2025.pdf\nLocation: page 30 part 4\nContent: S4I will map scaling efforts across Programs to reduce duplication, achieve synergies, and strengthen system-wide coherence.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt2]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 3 part 2\nContent: outcomes and i mpacts of the whole portfolio through progressive alignment of reporting on w3/bilaterally funded components with a common framework. • Line of sight: The TRA is designed to meet the needs of diverse funders, ensuring transparency and accountability by linking investment to results, both for pooled and non-pooled funds. • Impact focus: Research results will be better linked to CGIAR’s 2030 targets using enhanced impact area indicators. Impact assessments will be integrated into Program/Accelerator design. The use of geographically-bounded targets will be explored for priority locations. A robust approach to project cross-Portfolio benefits by Impact Area for different funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified reporting: Overly complex requirements will be avoided, aiming to\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p2pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 2 part 4\nContent: reviewed and validated by the authors to ensure accuracy, coherence, and alignment with the original intent. Acknowledgements This work is part of the CGIAR System Organization. We would like to thank all funders who supported this research through their contributions to the CGIAR Trust Fund:\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p32pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 32 part 1\nContent: Genebanks Accelerator Inception Report 31 10. Addressing feedback on selects topics Concise summary of feedback Details on how the Program/ Accelerator has addressed or will address this feedback (in the Inception Phase or beyond) There is a lack of information on how water systems are covered in the Portfolio. N/A There is a lack of information on how climate mitigation is covered in the Portfolio. N/A There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. The Genebanks proposal noted that activities will lead to a stronger overall global system of international and national institutions, policies, and mechanisms contributing\n\n---\n\n[ID: pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p25pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1\nFile: Food Frontiers and Security_Inception Report 30-06-2025.pdf\nLocation: page 25 part 1\nContent: Food Frontiers and Security Program | Inception Report 25 operational efficiency, avoid duplication, and generate broader, more context-responsive insights than either program could produce alone, delivering greater value to partners and stakeholders across the CGIAR portfolio. Together with The Climate Action SP,\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt3]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 3 part 3\nContent: funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified reporting: Overly complex requirements will be avoided, aiming to reduce the reporting burden on Centers. Technical Report products include the following: • A Results Dashboard including AI functionalities will be updated several times a year (e.g. quarterly) to offer funders and partners closer to real-time data. • Annual Program/Accelerator Technical Reports will be complemented by an Annual Portfolio Report which will convey progress by Impact Area, geographic and thematic priorities and include information on CGIAR’s internal practice change and learning. • Portfolio outcomes and impacts will be consolidated in a specific report every 3 years. Evidence of CGIAR contributions to impact will be synthesized and regularly updated through an\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u103-106]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use of Materials' paragraph 108 to section 'Monitoring and Evaluations' paragraph 115\nContent: Intellectual Property rights. The System Organization and each Center will, respectively, ensure that necessary intellectual property rights are obtained to allow the rights referred to under this paragraph 6 to be granted. If third party copyright restrictions or attribution requirements apply to such documents, this will be indicated on the documents. Monitoring and Evaluations General Funders will manage their monitoring and evaluation requirements with respect to the CGIAR Portfolio, collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to conduct duplicative evaluations, provided that Funders providing Window 3 Funds may require supplemental monitoring and evaluations with respect to Window 3 Funds, the costs of which, including the internal costs to the System Organization or Center, would be paid by the requesting Funder.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1pt2]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 1 part 2\nContent: reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. Prepared by; Content developed by the Portfolio Performance Unit in collaboration with a x- CGIAR working group and System Council Strategic Impact Monitoring and Evaluation Committee members. Note to readers: 2024 Annual Technical Reports including the 2022-24 Type 2 Report are\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p8pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 8 part 4\nContent: other organizations as well as by funders. “CGIAR’s efforts to mainstream scaling put it at the cutting edge …” compared to other research and innovation organizations, and development organizations generally (Global Scaling Community of Practice). Figure 5: A pile of LEGO pieces that represents CGIAR’s innovation portfolio management pre-2022. What was once a fragmented system is now becoming more structured and strategic. Until 2022, there was no efficient way to manage ‘’CGIAR’s innovation portfolio’’. Innovation data was scattered, not up-to-date and lacked evidence. Furthermore, there was no operational framework to track or support scaling for impact. It led to organizational risks and inefficiencies as leadership, partners and funders could not easily access CGIAR innovations. This changed under the CGIAR 2030 Research and Innovation Strategy that embraced a more systematic and evidence-based innovation management based on principles of the Scaling Readiness approach. Currently, information on more than 1,325 innovations under development or use are now easily accessible on the CGIAR Results Dashboard, which is widely used by partners and funders. The World Bank Group, FAO, Gates Foundation, GIZ, ENABEL, and the African Development Bank are among organizations that have embraced (elements of) the CGIAR innovation management approach. CGIAR is actively sharing its innovation portfolio management journey with other organizations. The Gates Foundation partnered with CGIAR to co-develop a protocol for scaling strategies aimed at high-impact innovations. Internally, CGIAR Centers such as the Alliance of Bioversity and CIAT (ABC) and the International Livestock Research Institute (ILRI) and CGIAR projects such as the Accelerate for Impact Platform (A4IP), Technologies for African Agricultural Transformation (TAAT) and HarvestPlus Solutions have adopted elements of innovation portfolio management. May 2025 1110 CGIAR Portfolio Practice Change (Type 3)\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p6pt2]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 6 part 2\nContent: 2025-30 CGIAR Portfolio. In 2024 work began on developing a new Technical Reporting Arrangement for 2025-30 (TRA 25-30) to define the Technical Reporting requirements for the next CGIAR Portfolio. A cross-CGIAR working group – comprising Center experts and System functions – led its development. The TRA 25-30 will promote progressive alignment between reporting requirements for pooled and non-pooled funding components, and sets expectations for transparency, performance tracking, and accountability across CGIAR and with funders. It will also operationalize the PRMF , inform decision-making, and provide direction for Portfolio-level monitoring, evaluation, learning and impact assessment (MELIA) and the design of the next version of the PRMS. The TRA 25-30 is expected to be endorsed in the first half of 2025. A durum wheat field at Toluca Station. Credit: Alfonso Cortés/CIMMYT Section 3: Implementation Status: Management Responses to CGIAR Evaluations 5. For more information see the CGIAR Evaluation Policy, the CGIAR Evaluation Guidelines, and the Process Note on Developing, Tracking and Reporting on Management Responses to Evaluations. A Management Response is a formal mechanism through which Evaluation Recommendations are addressed by management. These responses are designed to ensure that Evaluations inform decision-making, enhance organizational effectiveness, promote learning, and strengthen accountability. They include time-bound commitments from management to implement Evaluation Recommendations and are systematically followed up as outlined in the CGIAR Evaluation Policy, which identifies follow-up as a critical component of the evaluative process.5 Since\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p87pt2]\nLink: https://cgspace.cgiar.org/items/04bd63a9-1b58-4eb5-84f2-b54c8bde226e\nFile: Portfolio Narrative_2024.pdf\nLocation: page 87 part 2\nContent: 2025–2030 The creation of a Scaling for Impact Program in CGIAR’s Portfolio 2025–2030 creates even more space and resources for innovation and scaling work. The Scaling for Impact Program plays an important role in catalyzing innovation scaling on the ground with CGIAR colleagues and partners while more System-wide innovation portfolio management functions continue to be delivered by CGIAR’s Portfolio Performance Unit. In CGIAR’s 2025–2030 Portfolio (Figure 6.4), innovation management is not just a process or tool — it is the central instrument for driving coherence and collaboration between the Science Programs and the Scaling for Impact Program while also aligning demand with supply and guiding strategic Portfolio priorities. Figure 6.4. Schematic overview of the CGIAR 2025–2030 Portfolio. CGIAR’s Portfolio Performance Unit and Project Coordination Unit work closely with the Scaling for Impact Program to deliver key innovation portfolio management functions for the 2025–2030 Portfolio. These two units continue to mainstream innovation and scaling tracking and performance across the\n\n---\n\n[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p26pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations_Inception Report 30-06-2025.pdf\nLocation: page 26 part 2\nContent: to national policy research ecosystems through coordinated capacity sharing activities. A prime example of this effective coordination and the efficiencies it generates is the policy program hub in Kenya. This hub actively coordinates with other CGIAR Programs, Accelerators, and individual CGIAR Centers building on efforts that the CGIAR country convener for Kenya had started. It therefore also provides an integration mechanism with W3/bilateral projects. Coordination is fundamental for avoiding duplication of efforts: They serve as a critical platform to share research plans, identify synergies, and proactively prevent overlapping activities, thereby ensuring a highly efficient deployment of collective resources across various CGIAR programs in Kenya. Beyond internal CGIAR coordination, the Kenya hub takes a leading role in planning joint policy dialogue series, country policy notes, bringing diverse stakeholders together for impactful co- design and co-implementation.\n\n---\n\n[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p33pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_Inception Report 30-06-2025.pdf\nLocation: page 33 part 1\nContent: Capacity Sharing Accelerator Inception Report 33 10. Addressing feedback on select topics Only one feedback (lack of information on how capacity sharing) applies directly to the CapSha Accelerator. Concise summary of feedback Details on how the Program/ Accelerator has addressed or will address this feedback (in the Inception Phase or beyond) There is a lack of information on how water systems are covered in the Portfolio. N/A There is a lack of information on how climate mitigation is covered in the Portfolio. N/A There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 22 part 4\nContent: CGIAR Results Framework – Portfolio Outcome"}]</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +2041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1661,7 +2084,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1673,16 +2096,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1690,7 +2113,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1702,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1719,7 +2142,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -1731,16 +2154,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="I4" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1748,7 +2171,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1760,16 +2183,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="I5" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1777,7 +2200,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1789,16 +2212,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1806,7 +2229,7 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1818,16 +2241,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="I7" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1835,7 +2258,7 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1847,16 +2270,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H8" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="I8" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1864,7 +2287,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1876,16 +2299,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="I9" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1893,7 +2316,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -1905,16 +2328,16 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="I10" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1922,7 +2345,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -1934,16 +2357,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I11" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1951,7 +2374,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -1963,16 +2386,16 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I12" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1980,7 +2403,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -1992,16 +2415,16 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="I13" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2009,7 +2432,7 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -2021,16 +2444,16 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I14" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2038,7 +2461,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -2050,16 +2473,16 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G15" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I15" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2067,7 +2490,7 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -2079,16 +2502,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I16" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2096,7 +2519,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -2108,16 +2531,16 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I17" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2125,7 +2548,7 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -2137,16 +2560,16 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="I18" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2154,7 +2577,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -2166,16 +2589,16 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I19" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2183,7 +2606,7 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -2195,16 +2618,16 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I20" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2212,7 +2635,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -2224,22 +2647,22 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I21" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="J21" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="K21" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2247,7 +2670,7 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -2259,22 +2682,22 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I22" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="J22" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="K22" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2282,7 +2705,7 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -2294,22 +2717,22 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I23" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="J23" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="K23" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2317,7 +2740,7 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -2329,22 +2752,22 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I24" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="J24" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="K24" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2352,7 +2775,7 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -2364,22 +2787,22 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I25" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="J25" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="K25" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2387,7 +2810,7 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -2399,22 +2822,22 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I26" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J26" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K26" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2422,7 +2845,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -2434,22 +2857,22 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="I27" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J27" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K27" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2457,7 +2880,7 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -2469,22 +2892,22 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I28" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J28" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K28" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2492,7 +2915,7 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -2504,22 +2927,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I29" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J29" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="K29" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2527,7 +2950,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -2539,22 +2962,22 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I30" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="J30" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="K30" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2562,7 +2985,7 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -2574,22 +2997,22 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I31" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="J31" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="K31" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2597,7 +3020,7 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -2609,22 +3032,22 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I32" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="J32" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K32" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2632,7 +3055,7 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -2644,22 +3067,22 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="J33" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K33" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2667,7 +3090,7 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -2679,22 +3102,22 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="J34" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K34" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2702,7 +3125,7 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -2714,22 +3137,22 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="J35" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K35" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2737,7 +3160,7 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -2749,22 +3172,22 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="J36" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K36" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2772,7 +3195,7 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -2784,22 +3207,22 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="J37" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K37" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2807,7 +3230,7 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -2819,22 +3242,22 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="J38" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K38" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2842,7 +3265,7 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -2854,22 +3277,22 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I39" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J39" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K39" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2877,7 +3300,7 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -2889,22 +3312,22 @@
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I40" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J40" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K40" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2912,7 +3335,7 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -2924,22 +3347,22 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I41" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J41" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K41" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2947,7 +3370,7 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -2959,22 +3382,22 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I42" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J42" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K42" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2982,7 +3405,7 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -2994,22 +3417,22 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I43" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J43" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K43" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3017,7 +3440,7 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -3029,22 +3452,22 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I44" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J44" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K44" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3061,13 +3484,13 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H45" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="K45" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -3075,7 +3498,7 @@
         <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -3087,22 +3510,22 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G46" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="I46" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J46" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K46" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -3110,7 +3533,7 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C47">
         <v>100</v>
@@ -3122,22 +3545,22 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G47" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="I47" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J47" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K47" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -3145,7 +3568,7 @@
         <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>100</v>
@@ -3157,22 +3580,22 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G48" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="J48" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K48" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -3180,7 +3603,7 @@
         <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -3192,22 +3615,22 @@
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G49" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="J49" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="K49" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -3215,7 +3638,7 @@
         <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -3227,22 +3650,22 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G50" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J50" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="K50" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3250,7 +3673,7 @@
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -3262,22 +3685,22 @@
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J51" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="K51" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3285,7 +3708,7 @@
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -3297,22 +3720,162 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G52" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="I52" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J52" t="s">
+        <v>158</v>
+      </c>
+      <c r="K52" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53">
+        <v>200</v>
+      </c>
+      <c r="D53">
+        <v>200</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>84</v>
+      </c>
+      <c r="G53" t="s">
+        <v>95</v>
+      </c>
+      <c r="H53" t="s">
+        <v>135</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J53" t="s">
+        <v>159</v>
+      </c>
+      <c r="K53" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54">
+        <v>200</v>
+      </c>
+      <c r="D54">
+        <v>200</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>84</v>
+      </c>
+      <c r="G54" t="s">
+        <v>96</v>
+      </c>
+      <c r="H54" t="s">
         <v>136</v>
       </c>
-      <c r="J52" t="s">
-        <v>143</v>
-      </c>
-      <c r="K52" t="s">
-        <v>155</v>
+      <c r="I54" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J54" t="s">
+        <v>160</v>
+      </c>
+      <c r="K54" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55">
+        <v>200</v>
+      </c>
+      <c r="D55">
+        <v>200</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>84</v>
+      </c>
+      <c r="G55" t="s">
+        <v>96</v>
+      </c>
+      <c r="H55" t="s">
+        <v>137</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J55" t="s">
+        <v>160</v>
+      </c>
+      <c r="K55" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56">
+        <v>200</v>
+      </c>
+      <c r="D56">
+        <v>200</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>84</v>
+      </c>
+      <c r="G56" t="s">
+        <v>93</v>
+      </c>
+      <c r="H56" t="s">
+        <v>138</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J56" t="s">
+        <v>157</v>
+      </c>
+      <c r="K56" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3328,6 +3891,10 @@
     <hyperlink ref="I50" r:id="rId9"/>
     <hyperlink ref="I51" r:id="rId10"/>
     <hyperlink ref="I52" r:id="rId11"/>
+    <hyperlink ref="I53" r:id="rId12"/>
+    <hyperlink ref="I54" r:id="rId13"/>
+    <hyperlink ref="I55" r:id="rId14"/>
+    <hyperlink ref="I56" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Logs/interaction_log.xlsx
+++ b/Logs/interaction_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="203">
   <si>
     <t>timestamp</t>
   </si>
@@ -214,6 +214,21 @@
     <t>2025-09-24T10:32:33.484279</t>
   </si>
   <si>
+    <t>2025-09-24T14:07:12.455528</t>
+  </si>
+  <si>
+    <t>2025-09-24T14:07:44.638768</t>
+  </si>
+  <si>
+    <t>2025-09-24T14:09:48.670116</t>
+  </si>
+  <si>
+    <t>2025-09-24T15:17:26.408043</t>
+  </si>
+  <si>
+    <t>2025-09-25T00:45:44.397869</t>
+  </si>
+  <si>
     <t>What funding did 2024 Technical Reporting cover?</t>
   </si>
   <si>
@@ -245,6 +260,12 @@
   </si>
   <si>
     <t xml:space="preserve">Who coordinates funders’ M&amp;E requirements across the CGIAR Portfolio and how is duplication avoided? </t>
+  </si>
+  <si>
+    <t>¿Quién tiene la responsabilidad fiduciaria sobre los fondos de Ventanas 1 y 2 y qué debe garantizar?</t>
+  </si>
+  <si>
+    <t>Who holds fiduciary responsibility over Window 1 and Window 2 Funds?</t>
   </si>
   <si>
     <t xml:space="preserve">You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:
@@ -276,6 +297,12 @@
     <t>You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.</t>
   </si>
   <si>
+    <t>deeper research</t>
+  </si>
+  <si>
+    <t>You are a RAG assistant for deeper research. Use all the chunks that you receive. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.</t>
+  </si>
+  <si>
     <t>pptx:Information Session on 2025 Technical Reporting.pptx:s9:0.307, docx:Engagement Plan 2025 Technical Reporting.docx:p2:0.304, pptx:Information Session on 2025 Technical Reporting.pptx:s2:0.299, docx:Guidance on reporting outputs or outcomes.docx:p22:0.263, docx:Engagement Plan 2025 Technical Reporting.docx:p59:0.244, pdf:CGIAR_ImpactReport_2022-24.pdf:p1:0.239, docx:Engagement Plan 2025 Technical Reporting.docx:p31:0.208, pptx:Engagement Plan 2025 Technical Reporting.pptx:s1:0.202, docx:CGSpace.docx:p3:0.201, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5:0.200, docx:General information on Technical Reporting .docx:p1:0.196, pptx:Information Session on 2025 Technical Reporting.pptx:s15:0.184, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1:0.176, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23:0.166, docx:Guidance on reporting outputs or outcomes.docx:p21:0.163, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4:0.160, docx:Guidance on reporting outputs or outcomes.docx:p30:0.160, docx:2025 Technical Reporting Information (Session 2).docx:p5:0.152, docx:2025 Technical Reporting Information (Session 2).docx:p32:0.138, docx:Guidance on reporting outputs or outcomes.docx:p24:0.138, pdf:Type3_2024Report.pdf:p1:0.136, pptx:Information Session on 2025 Technical Reporting.pptx:s13:0.134, docx:Using the PRMS Reporting Tool.docx:p12:0.133, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7:0.133, docx:Guidance on reporting outputs or outcomes.docx:p31:0.133, docx:General information on Technical Reporting .docx:p4:0.131, pptx:Information Session on 2025 Technical Reporting.pptx:s7:0.128, pdf:Type3_2024Report.pdf:p5:0.124, pptx:Information Session on 2025 Technical Reporting.pptx:s5:0.124, pdf:Portfolio Narrative_2024.pdf:p1:0.124, pdf:Portfolio Narrative_2024.pdf:p5:0.124, pptx:Information Session on 2025 Technical Reporting.pptx:s3:0.123, docx:Innovation use.docx:p7:0.121, pptx:Information Session on 2025 Technical Reporting.pptx:s6:0.121, docx:Innovation development.docx:p31:0.120, docx:2025 Technical Reporting Information (Session 1).docx:p26:0.119, pptx:Information Session on 2025 Technical Reporting.pptx:s10:0.118, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p16:0.118, docx:2025 Technical Reporting Information (Session 1).docx:p7:0.117, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p6:0.116, pdf:Portfolio Narrative_2024.pdf:p6:0.110, docx:2025 Technical Reporting Information (Session 2).docx:p1:0.110, docx:2025 Technical Reporting Information (Session 1).docx:p1:0.110, docx:Guidance on reporting outputs or outcomes.docx:p26:0.109, docx:Innovation development.docx:p13:0.108, docx:Submitting evidence.docx:p3:0.108, docx:Guidance on complementary innnov.docx:p38:0.107, docx:Engagement Plan 2025 Technical Reporting.docx:p61:0.106, docx:Engagement Plan 2025 Technical Reporting.docx:p27:0.102, pptx:Information Session on 2025 Technical Reporting.pptx:s1:0.099, pdf:Type3_2024Report.pdf:p11:0.099, pdf:Type3_2024Report.pdf:p4:0.099, docx:General information on Technical Reporting .docx:p5:0.098, docx:Engagement Plan 2025 Technical Reporting.docx:p39:0.097, docx:Guidance on complementary innnov.docx:p10:0.097, pptx:Information Session on 2025 Technical Reporting.pptx:s4:0.094, pptx:Information Session on 2025 Technical Reporting.pptx:s11:0.092, pptx:Engagement Plan 2025 Technical Reporting.pptx:s2:0.092, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18:0.090, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22:0.089, docx:2025 Technical Reporting Information (Session 2).docx:p26:0.089, docx:Using the PRMS Reporting Tool.docx:p1:0.089, docx:2025 Technical Reporting MELIA glossary.docx:p6:0.089, docx:Engagement Plan 2025 Technical Reporting.docx:p106:0.088, pdf:Type3_2024Report.pdf:p6:0.087, docx:Engagement Plan 2025 Technical Reporting.docx:p42:0.086, docx:General reporting guidance.docx:p1:0.085, docx:General reporting guidance.docx:p5:0.084, docx:2025 Technical Reporting Information (Session 1).docx:p30:0.084, docx:Engagement Plan 2025 Technical Reporting.docx:p17:0.083, docx:Guidance on reporting outputs or outcomes.docx:p2:0.082, docx:2025 Technical Reporting Information (Session 2).docx:p11:0.081, docx:Engagement Plan 2025 Technical Reporting.docx:p69:0.080, pdf:CGIAR_ImpactReport_2022-24.pdf:p2:0.080, docx:Engagement Plan 2025 Technical Reporting.docx:p25:0.079, docx:Reporting the geographic location of results.docx:p1:0.078, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3:0.074, docx:Engagement Plan 2025 Technical Reporting.docx:p45:0.072, docx:Innovation use.docx:p22:0.072, pdf:Portfolio Narrative_2024.pdf:p37:0.071, docx:General reporting guidance.docx:p3:0.071, docx:2025 Technical Reporting Information (Session 2).docx:p41:0.071, docx:Engagement Plan 2025 Technical Reporting.docx:p8:0.071, docx:Engagement Plan 2025 Technical Reporting.docx:p10:0.070, docx:2025 Technical Reporting Information (Session 1).docx:p41:0.068, docx:Guidance on ensuring quality over quantity.docx:p3:0.066, docx:Engagement Plan 2025 Technical Reporting.docx:p55:0.066, pdf:Type3_2024Report.pdf:p3:0.066, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p9:0.066, docx:Innovation development.docx:p40:0.066, docx:Guidance on ensuring quality over quantity.docx:p5:0.066, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15:0.065, docx:Knowledge products.docx:p11:0.065, pdf:Portfolio Narrative_2024.pdf:p72:0.065, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25:0.065, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p2:0.064, docx:2025 Technical Reporting Information (Session 2).docx:p7:0.064, docx:2025 Technical Reporting Information (Session 1).docx:p15:0.064, docx:2025 Technical Reporting Information (Session 2).docx:p14:0.063, docx:2025 Technical Reporting Information (Session 1).docx:p33:0.063</t>
   </si>
   <si>
@@ -310,6 +337,15 @@
   </si>
   <si>
     <t>pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2:0.321, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1:0.276, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1:0.272, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3:0.256, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1:0.252, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3:0.231, pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2:0.216, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3:0.198, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4:0.196, docx:2025 Technical Reporting Information (Session 1).docx:u1-4:0.186, docx:2025 Technical Reporting Information (Session 2).docx:u1-4:0.184, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3:0.166, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4:0.163, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt4:0.157, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2:0.146, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1:0.138, pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3:0.137, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p55pt1:0.137, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3:0.130, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3:0.124, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2:0.121, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt2:0.120, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt3:0.118, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p35pt4:0.118, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt2:0.116, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p28pt2:0.112, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p1pt2:0.112, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p32pt1:0.106, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt2:0.106, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p13pt4:0.104, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt2:0.104, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3:0.103, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1:0.103, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt2:0.102, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt2:0.101, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt4:0.100, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p36pt1:0.097, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt3:0.096, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1:0.096, pdf:CGI21-507032-PORB-Climate Action.pdf:p21pt3:0.094, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p35pt3:0.092, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p42pt3:0.091, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p25pt1:0.088, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p21pt4:0.087, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt1:0.087, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1:0.083, pdf:Portfolio Narrative_2024.pdf:p47pt3:0.082, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p28pt2:0.082, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p36pt4:0.081, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p48pt4:0.081, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt2:0.079, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt2:0.078, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p42pt4:0.078, pdf:Portfolio Narrative_2024.pdf:p47pt4:0.075, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p7pt4:0.075, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p28pt1:0.075, pdf:CGIAR_ImpactReport_2022-24.pdf:p56pt2:0.073, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt3:0.072, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt4:0.072, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p23pt1:0.072, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p53pt4:0.070, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p21pt2:0.070, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt3:0.068, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt1:0.067, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p29pt1:0.066, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p54pt3:0.066, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p48pt3:0.065, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt2:0.064, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt3:0.063, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt2:0.062, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt3:0.062, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt4:0.062, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p9pt3:0.061, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p38pt1:0.060, docx:Standard Provisions 2026.docx:u22-25:0.060, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p21pt1:0.059, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p10pt4:0.059, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p28pt3:0.058, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p49pt4:0.058, docx:Standard Provisions 2026.docx:u115-118:0.057, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p28pt3:0.057, pdf:Climate Action_Inception Report 30-06-2025.pdf:p11pt3:0.057, pdf:Portfolio Narrative_2024.pdf:p47pt2:0.056, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p25pt4:0.056, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p47pt4:0.056, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt2:0.056, pdf:CGIAR_ImpactReport_2022-24.pdf:p61pt1:0.054, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4:0.054, docx:2025 Technical Reporting Information (Session 2).docx:u52-56:0.054, docx:Standard Provisions 2026.docx:u127-130:0.053, docx:2025 Technical Reporting Information (Session 1).docx:u43-45:0.051, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p28pt4:0.050, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt2:0.049, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt1:0.049, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p30pt1:0.048, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p47pt4:0.048, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt4:0.048, docx:Standard Provisions 2026.docx:u100-103:0.048, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt2:0.047, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt1:0.047, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt1:0.045, pdf:CGIAR_ImpactReport_2022-24.pdf:p34pt1:0.045, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt2:0.045, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt4:0.044, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p43pt4:0.044, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p44pt4:0.044, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4:0.044, pdf:Type3_2024Report.pdf:p2pt4:0.043, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt3:0.043, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p40pt4:0.042, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p27pt2:0.042, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p18pt2:0.042, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p30pt2:0.041, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p22pt2:0.041, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p38pt2:0.041, pdf:Climate Action_Inception Report 30-06-2025.pdf:p8pt3:0.041, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p27pt1:0.041, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p30pt1:0.040, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p52pt3:0.040, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p22pt1:0.040, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt3:0.040, pdf:Climate Action_Inception Report 30-06-2025.pdf:p8pt4:0.040, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p22pt2:0.040, pdf:Portfolio Narrative_2024.pdf:p83pt1:0.040, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p6pt2:0.040, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt1:0.040, pdf:Type3_2024Report.pdf:p8pt4:0.039, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p9pt4:0.038, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt2:0.038, pptx:Information Session on 2025 Technical Reporting.pptx:s3pt3:0.038, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt2:0.038, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt2:0.038, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p39pt3:0.037, docx:Standard Provisions 2026.docx:u103-106:0.037, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p13pt4:0.037, pdf:Portfolio Narrative_2024.pdf:p28pt4:0.037, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt4:0.036, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt2:0.036, pdf:CGIAR_ImpactReport_2022-24.pdf:p45pt4:0.035, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p22pt1:0.035, pdf:Portfolio Narrative_2024.pdf:p19pt1:0.035, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p26pt1:0.035, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt4:0.034, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p39pt2:0.034, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p18pt1:0.034, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p30pt3:0.033, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p51pt1:0.033, pdf:CGIAR_ImpactReport_2022-24.pdf:p61pt2:0.033, docx:Standard Provisions 2026.docx:u85-88:0.033, docx:Standard Provisions 2026.docx:u172-175:0.033, docx:Standard Provisions 2026.docx:u124-127:0.032, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p20pt2:0.032, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p17pt3:0.032, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p47pt3:0.031, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p13pt1:0.031, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p9pt3:0.030, pdf:CGIAR_ImpactReport_2022-24.pdf:p53pt4:0.030, pdf:CGIAR_ImpactReport_2022-24.pdf:p23pt4:0.030, pdf:Type3_2024Report.pdf:p10pt4:0.030, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p49pt3:0.030, docx:Standard Provisions 2026.docx:u82-85:0.029, pdf:CGIAR_ImpactReport_2022-24.pdf:p53pt3:0.029, docx:Standard Provisions 2026.docx:u97-100:0.029, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p22pt2:0.028, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p39pt2:0.028, pdf:CGIAR_ImpactReport_2022-24.pdf:p41pt4:0.028, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p15pt2:0.028, docx:Standard Provisions 2026.docx:u52-55:0.027, pdf:CGIAR_ImpactReport_2022-24.pdf:p4pt2:0.027, pdf:Portfolio Narrative_2024.pdf:p82pt4:0.026, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p6pt4:0.026, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p6pt3:0.026, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p15pt3:0.026, docx:Standard Provisions 2026.docx:u112-115:0.026, pdf:CGI21-507032-PORB-Climate Action.pdf:p24pt2:0.026, docx:Standard Provisions 2026.docx:u106-109:0.025, pdf:CGI21-507032-PORB-Climate Action.pdf:p24pt3:0.025, pdf:CGIAR_ImpactReport_2022-24.pdf:p40pt1:0.025, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt3:0.024, docx:Standard Provisions 2026.docx:u7-10:0.024, docx:Standard Provisions 2026.docx:u130-133:0.024, docx:Standard Provisions 2026.docx:u4-7:0.024, pdf:Type3_2024Report.pdf:p7pt2:0.024, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p16pt1:0.024, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p22pt2:0.024, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt3:0.024, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p37pt4:0.023, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt3:0.023, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p37pt3:0.023, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p22pt1:0.023, docx:Standard Provisions 2026.docx:u34-37:0.023, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p14pt3:0.023, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p22pt2:0.023, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt4:0.023, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p18pt1:0.022, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p17pt4:0.022, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18pt4:0.022, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p47pt2:0.022, pdf:Quick style guide Feb 2024 (1).pdf:p5pt1:0.022, pdf:Climate Action_Inception Report 30-06-2025.pdf:p28pt3:0.022</t>
+  </si>
+  <si>
+    <t>pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2:0.450, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1:0.393, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1:0.359, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1:0.347, pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2:0.308, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3:0.272, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3:0.271, docx:2025 Technical Reporting Information (Session 1).docx:u1-4:0.252, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4:0.249, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1:0.249, docx:2025 Technical Reporting Information (Session 2).docx:u1-4:0.249, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3:0.223, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2:0.218, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3:0.217, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3:0.209, pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3:0.186, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2:0.186, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3:0.176, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3:0.175, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4:0.172, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p55pt1:0.169, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt4:0.166, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt2:0.147, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1:0.146, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt3:0.145, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt2:0.141, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1:0.139, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p25pt1:0.133, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt1:0.131, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p36pt1:0.131, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt2:0.127, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p35pt4:0.124, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p36pt4:0.123, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt2:0.123, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt2:0.120, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p28pt2:0.119, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p1pt2:0.119, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4:0.114, docx:2025 Technical Reporting Information (Session 2).docx:u52-56:0.114, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1:0.113, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p32pt1:0.112, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt2:0.112, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p13pt4:0.110, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt3:0.110, docx:2025 Technical Reporting Information (Session 1).docx:u43-45:0.109, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt2:0.108, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt4:0.105, pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt3:0.103, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt3:0.101, pdf:CGI21-507032-PORB-Climate Action.pdf:p21pt3:0.099, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p35pt3:0.097, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p42pt3:0.096, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p53pt4:0.095, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt3:0.095, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p21pt4:0.092, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt4:0.091, pdf:Portfolio Narrative_2024.pdf:p47pt3:0.087, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p28pt2:0.086, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p48pt4:0.086, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p16pt2:0.084, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt2:0.083, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p42pt4:0.082, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt2:0.079, pdf:Portfolio Narrative_2024.pdf:p47pt4:0.079, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p7pt4:0.079, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p28pt1:0.079, pdf:CGIAR_ImpactReport_2022-24.pdf:p56pt2:0.077, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p23pt1:0.076, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt1:0.074, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p21pt2:0.074, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt1:0.071, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p29pt1:0.070, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p54pt3:0.070, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p48pt3:0.069, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt2:0.067, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt3:0.066, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt2:0.066, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt4:0.065, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p38pt1:0.064, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p21pt1:0.062, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p28pt3:0.062, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p49pt4:0.062, pdf:Climate Action_Inception Report 30-06-2025.pdf:p11pt3:0.060, pdf:Portfolio Narrative_2024.pdf:p47pt2:0.059, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p25pt4:0.059, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p47pt4:0.059, pdf:CGIAR_ImpactReport_2022-24.pdf:p61pt1:0.057, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p23pt2:0.057, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p28pt4:0.053, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p47pt4:0.051, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt4:0.051, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt1:0.049, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt1:0.048, pdf:CGIAR_ImpactReport_2022-24.pdf:p34pt1:0.047, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt2:0.047, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt4:0.047, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p43pt4:0.046, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p44pt4:0.046, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p41pt3:0.045, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p27pt2:0.044, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p18pt2:0.044, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p22pt2:0.044, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p38pt2:0.043, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p27pt1:0.043, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt3:0.042, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p6pt2:0.042, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt1:0.042, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p9pt4:0.040, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt2:0.040, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p39pt3:0.039, pdf:Portfolio Narrative_2024.pdf:p28pt4:0.039, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt4:0.038, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt2:0.038, pdf:CGIAR_ImpactReport_2022-24.pdf:p45pt4:0.037, pdf:Portfolio Narrative_2024.pdf:p19pt1:0.037, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p26pt1:0.036, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p39pt2:0.036, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p40pt4:0.036, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p30pt3:0.035, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p51pt1:0.035, pdf:CGIAR_ImpactReport_2022-24.pdf:p61pt2:0.035, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p20pt2:0.034, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p17pt3:0.033, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p47pt3:0.033, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p9pt3:0.032, pdf:CGIAR_ImpactReport_2022-24.pdf:p53pt4:0.032, pdf:CGIAR_ImpactReport_2022-24.pdf:p23pt4:0.032, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p49pt3:0.031, pdf:CGIAR_ImpactReport_2022-24.pdf:p53pt3:0.031, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p22pt2:0.030, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p39pt2:0.030, pdf:CGIAR_ImpactReport_2022-24.pdf:p41pt4:0.030, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p15pt2:0.030, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p15pt3:0.027, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p32pt3:0.027, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p32pt2:0.027, pdf:CGIAR_ImpactReport_2022-24.pdf:p40pt1:0.026, pdf:Type3_2024Report.pdf:p7pt2:0.025, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p37pt4:0.025, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p37pt3:0.024, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p17pt4:0.024, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p47pt2:0.023, pdf:Quick style guide Feb 2024 (1).pdf:p5pt1:0.023, pdf:CGIAR_ImpactReport_2022-24.pdf:p58pt1:0.023, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p22pt4:0.022, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p29pt1:0.022, pdf:CGIAR_ImpactReport_2022-24.pdf:p25pt1:0.022, pdf:CGIAR_ImpactReport_2022-24.pdf:p10pt3:0.020</t>
+  </si>
+  <si>
+    <t>docx:Standard Provisions 2026.docx:u19-22:0.692, docx:Standard Provisions 2026.docx:u16-19:0.656, docx:Standard Provisions 2026.docx:u181-184:0.470, docx:Standard Provisions 2026.docx:u28-31:0.467, docx:Standard Provisions 2026.docx:u178-181:0.421, docx:Standard Provisions 2026.docx:u31-34:0.413, docx:Standard Provisions 2026.docx:u13-16:0.406, docx:Standard Provisions 2026.docx:u22-25:0.379, docx:Standard Provisions 2026.docx:u34-37:0.332, docx:Standard Provisions 2026.docx:u172-175:0.314, docx:Standard Provisions 2026.docx:u25-28:0.307, docx:Standard Provisions 2026.docx:u55-58:0.277, docx:Standard Provisions 2026.docx:u46-49:0.240, docx:Standard Provisions 2026.docx:u184-189:0.235, docx:Standard Provisions 2026.docx:u175-178:0.234, docx:Standard Provisions 2026.docx:u4-7:0.231, docx:Standard Provisions 2026.docx:u106-109:0.212, docx:Standard Provisions 2026.docx:u58-61:0.209, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt4:0.187, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt2:0.184, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p5pt2:0.183, docx:Standard Provisions 2026.docx:u10-13:0.179, docx:Standard Provisions 2026.docx:u67-70:0.169, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p3pt1:0.168, docx:Standard Provisions 2026.docx:u163-166:0.163, docx:Standard Provisions 2026.docx:u157-160:0.162, docx:Standard Provisions 2026.docx:u64-67:0.160, docx:Standard Provisions 2026.docx:u73-76:0.159, docx:Standard Provisions 2026.docx:u37-40:0.159, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p5pt1:0.152, docx:Standard Provisions 2026.docx:u121-124:0.147, docx:Standard Provisions 2026.docx:u52-55:0.147, docx:Standard Provisions 2026.docx:u70-73:0.146, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt1:0.142, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p19pt2:0.140, docx:Standard Provisions 2026.docx:u133-136:0.140, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p3pt2:0.136, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p4pt4:0.135, docx:Standard Provisions 2026.docx:u103-106:0.133, pdf:Portfolio Narrative_2024.pdf:p5pt1:0.128, pdf:Climate Action_Inception Report 30-06-2025.pdf:p16pt3:0.127, docx:Standard Provisions 2026.docx:u43-46:0.124, docx:Standard Provisions 2026.docx:u61-64:0.123, docx:Guidance on reporting outputs or outcomes.docx:u10-13:0.123, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p4pt4:0.122, docx:Standard Provisions 2026.docx:u109-112:0.121, docx:Standard Provisions 2026.docx:u166-169:0.120, docx:Standard Provisions 2026.docx:u130-133:0.114, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p2pt3:0.113, docx:Standard Provisions 2026.docx:u160-163:0.113, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p18pt1:0.111, docx:Standard Provisions 2026.docx:u82-85:0.105, docx:Standard Provisions 2026.docx:u97-100:0.105, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.100, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p18pt4:0.099, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p16pt1:0.098, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt3:0.098, docx:Standard Provisions 2026.docx:u145-148:0.097, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p2pt4:0.096, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p19pt3:0.094, docx:Standard Provisions 2026.docx:u94-97:0.093, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p20pt1:0.093, docx:Standard Provisions 2026.docx:u112-115:0.092, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt2:0.090, docx:2025 Technical Reporting Information (Session 1).docx:u40-43:0.089, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt3:0.089, pptx:Information Session on 2025 Technical Reporting.pptx:s4pt4:0.088, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.087, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt1:0.087, pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3:0.086, pdf:CGI21_508012_PORB_Genebanks.pdf:p2pt2:0.085, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt3:0.085, docx:Standard Provisions 2026.docx:u1-4:0.084, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p16pt1:0.084, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p2pt2:0.084, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p19pt1:0.083, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p2pt2:0.083, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p2pt2:0.083, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p2pt2:0.082, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p2pt2:0.082, pdf:CGI21-507032-PORB-Climate Action.pdf:p2pt2:0.082, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p2pt2:0.082, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p2pt2:0.082, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt1:0.082, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p2pt2:0.081, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p2pt2:0.081, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p2pt2:0.081, docx:Standard Provisions 2026.docx:u76-79:0.078, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p22pt4:0.077, pdf:Portfolio Narrative_2024.pdf:p37pt4:0.076, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p6pt3:0.075, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p27pt1:0.075, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p2pt2:0.074, pdf:Type3_2024Report.pdf:p5pt1:0.074, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p3pt4:0.073, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt2:0.072, pdf:Genebanks_Inception Report 30-06-2025.pdf:p8pt2:0.072, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p3pt3:0.071, docx:Standard Provisions 2026.docx:u88-91:0.071, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p23pt1:0.070, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4:0.070, pdf:Genebanks_Inception Report 30-06-2025.pdf:p3pt4:0.067, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p21pt1:0.067, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p2pt1:0.067, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p23pt3:0.066, pdf:Genebanks_Inception Report 30-06-2025.pdf:p8pt3:0.066, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt2:0.066, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p21pt1:0.060, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p14pt2:0.060, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt4:0.060, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p23pt2:0.060, docx:Standard Provisions 2026.docx:u7-10:0.059, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p26pt1:0.059, docx:Standard Provisions 2026.docx:u85-88:0.059, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p17pt2:0.059, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p4pt3:0.058, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt4:0.057, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt1:0.057, pdf:Genebanks_Inception Report 30-06-2025.pdf:p29pt1:0.056, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p29pt4:0.056, docx:User Roles and Rules for the PRMS Reporting.docx:u1-4:0.055, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p24pt2:0.054, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p4pt2:0.054, docx:Standard Provisions 2026.docx:u148-151:0.053, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p14pt1:0.053, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p3pt3:0.052, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p9pt2:0.051, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p22pt1:0.051, docx:2025 Technical Reporting Information (Session 2).docx:u28-31:0.051, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p6pt4:0.051, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p5pt1:0.050, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p15pt1:0.050, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p27pt2:0.049, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p32pt4:0.049, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p6pt4:0.049, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p3pt2:0.049, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p15pt2:0.048, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p14pt3:0.048, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p4pt2:0.047, docx:Engagement Plan 2025 Technical Reporting.docx:u55-58:0.046, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p25pt2:0.046, pdf:Type3_2024Report.pdf:p2pt4:0.046, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt3:0.046, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p16pt4:0.046, pdf:Genebanks_Inception Report 30-06-2025.pdf:p29pt2:0.045, docx:Standard Provisions 2026.docx:u169-172:0.044, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p17pt2:0.044, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p16pt3:0.044, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p17pt3:0.044, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p10pt4:0.043, docx:Guidance on reporting outputs or outcomes.docx:u7-10:0.043, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p13pt4:0.043, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p8pt1:0.043, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p5pt2:0.043, docx:Standard Provisions 2026.docx:u100-103:0.043, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p22pt1:0.043, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p6pt2:0.043, pdf:Genebanks_Inception Report 30-06-2025.pdf:p21pt2:0.042, docx:Standard Provisions 2026.docx:u151-154:0.042, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p18pt2:0.041, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p10pt4:0.041, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p11pt1:0.041, pdf:Genebanks_Inception Report 30-06-2025.pdf:p39pt3:0.040, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p14pt4:0.040, pdf:Portfolio Narrative_2024.pdf:p14pt2:0.040, pdf:Genebanks_Inception Report 30-06-2025.pdf:p17pt4:0.040, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p25pt4:0.040, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p25pt3:0.040, pdf:Portfolio Narrative_2024.pdf:p7pt3:0.040, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p5pt4:0.039, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.039, pdf:Portfolio Narrative_2024.pdf:p20pt1:0.039, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p22pt1:0.039, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p17pt4:0.039, pdf:Genebanks_Inception Report 30-06-2025.pdf:p9pt3:0.039, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p11pt2:0.038, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p15pt4:0.038, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt2:0.038, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p33pt4:0.038, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p14pt4:0.038, docx:Guidance on reporting outputs or outcomes.docx:u4-7:0.037, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p21pt3:0.037, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.037, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p13pt2:0.037, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p14pt3:0.037, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p36pt4:0.037, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p10pt4:0.037, pdf:Genebanks_Inception Report 30-06-2025.pdf:p37pt2:0.037, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p21pt2:0.037, pdf:CGIAR_ImpactReport_2022-24.pdf:p10pt2:0.036, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p6pt1:0.036, pdf:Portfolio Narrative_2024.pdf:p41pt1:0.036, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p27pt3:0.036, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p15pt2:0.035, pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt3:0.035, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p11pt3:0.035, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p15pt2:0.035, pdf:Genebanks_Inception Report 30-06-2025.pdf:p35pt1:0.035, pdf:Genebanks_Inception Report 30-06-2025.pdf:p18pt1:0.035, pdf:Genebanks_Inception Report 30-06-2025.pdf:p36pt4:0.034</t>
+  </si>
+  <si>
+    <t>docx:Standard Provisions 2026.docx:u19-22:0.155, docx:Standard Provisions 2026.docx:u16-19:0.145, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p72pt2:0.090, docx:Standard Provisions 2026.docx:u31-34:0.085, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1:0.078, docx:Standard Provisions 2026.docx:u28-31:0.078, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1:0.077, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1:0.075, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2:0.074, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p52pt1:0.069, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4:0.067, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p15pt4:0.067, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3:0.066, pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2:0.064, docx:Standard Provisions 2026.docx:u70-73:0.063, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p37pt3:0.062, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1:0.061, pdf:Portfolio Narrative_2024.pdf:p5pt1:0.060, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.059, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3:0.057, docx:Standard Provisions 2026.docx:u163-166:0.057, docx:Standard Provisions 2026.docx:u67-70:0.056, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p29pt3:0.055, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p21pt2:0.053, pdf:Type3_2024Report.pdf:p6pt3:0.052, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3:0.052, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p17pt2:0.051, pdf:Type3_2024Report.pdf:p6pt4:0.051, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p10pt2:0.051, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p40pt3:0.051, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3:0.049, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt4:0.048, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p29pt2:0.048, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p35pt2:0.047, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p17pt2:0.047, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p31pt2:0.047, pdf:Genebanks_Inception Report 30-06-2025.pdf:p38pt1:0.046, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p6pt1:0.045, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p6pt4:0.045, pdf:Type3_2024Report.pdf:p3pt2:0.045, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p49pt2:0.044, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p20pt2:0.044, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt4:0.044, pdf:Climate Action_Inception Report 30-06-2025.pdf:p22pt2:0.043, pdf:Type3_2024Report.pdf:p6pt2:0.043, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p19pt4:0.043, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p28pt2:0.043, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p10pt1:0.043, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p1pt2:0.042, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt3:0.042, pdf:Type3_2024Report.pdf:p5pt1:0.042, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p20pt3:0.041, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p26pt3:0.041, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt3:0.041, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4:0.041, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4:0.041, docx:User Roles and Rules for the PRMS Reporting.docx:u4-7:0.040, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p30pt4:0.040, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p13pt4:0.039, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p20pt4:0.039, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p22pt3:0.039, pdf:Portfolio Narrative_2024.pdf:p29pt3:0.039, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p10pt2:0.039, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p51pt1:0.039, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p6pt2:0.039, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p5pt2:0.039, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p29pt3:0.038, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p4pt4:0.038, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3:0.038, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt2:0.038, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p9pt2:0.038, pdf:Portfolio Narrative_2024.pdf:p82pt2:0.038, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1:0.038, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p8pt3:0.038, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt3:0.038, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p30pt2:0.038, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p24pt1:0.037, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p6pt2:0.037, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt3:0.037, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2:0.037, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p16pt4:0.037, pdf:Portfolio Narrative_2024.pdf:p89pt4:0.037, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt4:0.037, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt4:0.037, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt4:0.037, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p30pt1:0.037, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt2:0.037, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p15pt2:0.036, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p4pt1:0.036, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p31pt4:0.036, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p29pt4:0.036, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p31pt2:0.036, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p22pt3:0.036, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p5pt3:0.036, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p8pt2:0.036, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p26pt4:0.035, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p31pt1:0.035, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p16pt1:0.035, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p46pt2:0.035, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p11pt4:0.035, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p12pt2:0.035, docx:Standard Provisions 2026.docx:u58-61:0.035, pdf:Portfolio Narrative_2024.pdf:p29pt4:0.035, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p17pt3:0.035, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p18pt4:0.034, pdf:CGIAR_ImpactReport_2022-24.pdf:p28pt1:0.034, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p26pt4:0.034, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p37pt4:0.034, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p26pt3:0.034, pdf:Genebanks_Inception Report 30-06-2025.pdf:p15pt2:0.034, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p11pt1:0.034, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p11pt2:0.034, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p29pt4:0.034, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p19pt1:0.034, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p7pt4:0.034, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p22pt4:0.034, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p1pt2:0.034, pdf:Climate Action_Inception Report 30-06-2025.pdf:p22pt3:0.034, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p18pt3:0.034, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p13pt2:0.034, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p36pt3:0.034, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p15pt4:0.034, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p17pt3:0.034, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p9pt4:0.034, pdf:Climate Action_Inception Report 30-06-2025.pdf:p17pt3:0.034, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p29pt1:0.034, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p9pt3:0.034, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p3pt2:0.034, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p19pt2:0.033, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p10pt4:0.033, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p5pt1:0.033, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p13pt2:0.033, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p31pt1:0.033, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p4pt4:0.033, pptx:Information Session on 2025 Technical Reporting.pptx:s8pt2:0.033, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p11pt2:0.033, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p12pt3:0.033, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p5pt2:0.033, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt2:0.033, pdf:Portfolio Narrative_2024.pdf:p17pt1:0.033, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p15pt1:0.033, pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3:0.033, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p35pt1:0.033, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt2:0.033, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p33pt4:0.033, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p24pt4:0.033, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p3pt1:0.033, pdf:Portfolio Narrative_2024.pdf:p82pt3:0.033, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p13pt3:0.033, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p10pt2:0.033, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt4:0.033, pdf:Type3_2024Report.pdf:p7pt1:0.032, docx:User Roles and Rules for the PRMS Reporting.docx:u1-4:0.032, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p18pt1:0.032, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p7pt2:0.032, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p26pt1:0.032, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p56pt3:0.032, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p6pt1:0.032, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p27pt4:0.032, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p30pt4:0.032, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p32pt3:0.032, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p10pt2:0.032, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p5pt1:0.032, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p9pt2:0.032, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p21pt3:0.032, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt3:0.032, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p3pt3:0.032, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p18pt4:0.032, pdf:Type3_2024Report.pdf:p8pt3:0.032, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p17pt3:0.032, pdf:Portfolio Narrative_2024.pdf:p53pt4:0.032, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25pt3:0.032, pdf:Genebanks_Inception Report 30-06-2025.pdf:p17pt4:0.032, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p4pt2:0.032, docx:Standard Provisions 2026.docx:u73-76:0.032, pdf:Portfolio Narrative_2024.pdf:p38pt4:0.032, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p46pt3:0.032, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p53pt3:0.032, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p8pt1:0.032, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt2:0.032, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt1:0.031, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p22pt3:0.031, pdf:CGI21_508012_PORB_Genebanks.pdf:p2pt1:0.031, pdf:Type3_2024Report.pdf:p7pt4:0.031, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p26pt3:0.031, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt2:0.031, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p7pt2:0.031, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p4pt4:0.031, pdf:Portfolio Narrative_2024.pdf:p47pt4:0.031, docx:Standard Provisions 2026.docx:u4-7:0.031, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p12pt3:0.031, pdf:Genebanks_Inception Report 30-06-2025.pdf:p35pt4:0.031, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p31pt3:0.031, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p40pt4:0.031, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p47pt4:0.031, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p14pt4:0.031, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p16pt2:0.031, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p13pt4:0.031, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p7pt1:0.031, pdf:Climate Action_Inception Report 30-06-2025.pdf:p19pt3:0.031</t>
   </si>
   <si>
     <t>I cannot find information in the provided chunks to answer this.  
@@ -647,6 +683,57 @@
 Standard Provisions 2026.docx — section 'Monitoring and Evaluations' paragraph 115 — docx:Standard Provisions 2026.docx:u103-106</t>
   </si>
   <si>
+    <t>I cannot find information in the provided chunks to answer this. The documents do not specify who holds fiduciary responsibility over the funds of Ventanas 1 and 2 or what guarantees are required. For detailed information on fiduciary responsibilities and guarantees related to these funds, further context or specific documents may be necessary. 
+Sources:
+File — Location — Cited IDs
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2
+Genebanks_Inception Report 30-06-2025.pdf — page 22 part 1 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1
+CGI21_508012_PORB_Genebanks.pdf — page 11 part 1 — pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1
+CGI21_508012_PORB_Genebanks.pdf — page 10 part 2 — pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2</t>
+  </si>
+  <si>
+    <t>La responsabilidad fiduciaria sobre los fondos de Ventanas 1 y 2 recae en el CGIAR (Grupo Consultivo sobre Investigación Agrícola Internacional). Este organismo debe garantizar que los fondos se utilicen de manera eficiente y efectiva para la conservación y el uso sostenible de los recursos genéticos de cultivos, así como para el desarrollo de soluciones innovadoras que aborden los desafíos de la seguridad alimentaria y la sostenibilidad agrícola.
+En particular, el CGIAR tiene la obligación de asegurar que los proyectos financiados bajo estas ventanas contribuyan a los resultados deseados en términos de conservación de la biodiversidad agrícola, mejora de la calidad de la dieta y adaptación al cambio climático, entre otros objetivos estratégicos. Esto implica una gestión cuidadosa de los recursos, la rendición de cuentas y la transparencia en el uso de los fondos asignados.</t>
+  </si>
+  <si>
+    <t>I cannot find information in the provided chunks to answer this. 
+Sources:
+File — Location — Cited IDs
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2
+Genebanks_Inception Report 30-06-2025.pdf — page 22 part 1 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 9 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1
+CGI21_508012_PORB_Genebanks.pdf — page 11 part 1 — pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1
+CGI21_508012_PORB_Genebanks.pdf — page 10 part 2 — pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2
+CGIAR_PORB_Scaling_4Impact.pdf — page 23 part 3 — pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3
+CGIAR_PORB_Breeding_Tomorrow.pdf — page 45 part 3 — pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3
+2025 Technical Reporting Information (Session 1).docx — paragraph 1 to paragraph 4 — docx:2025 Technical Reporting Information (Session 1).docx:u1-4
+Genebanks_Inception Report 30-06-2025.pdf — page 22 part 4 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 22 part 1 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1
+docx:2025 Technical Reporting Information (Session 2).docx — paragraph 1 to paragraph 4 — docx:2025 Technical Reporting Information (Session 2).docx:u1-4
+CGI21-507031-PORB-Food Frontiers and Security.pdf — page 22 part 3 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3
+CGI21-507032-PORB-Climate Action.pdf — page 11 part 2 — pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2
+CGI21_508012_PORB_Genebanks.pdf — page 11 part 2 — pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2
+CGIAR_PORB_Breeding_Tomorrow.pdf — page 42 part 3 — pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3
+CGIAR_PORB_Breeding_Tomorrow.pdf — page 46 part 3 — pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3
+CGIAR_PORB_Scaling_4Impact.pdf — page 22 part 4 — pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4
+Climate Action_Inception Report 30-06-2025.pdf — page 4 part 3 — pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3</t>
+  </si>
+  <si>
+    <t>The fiduciary responsibility over Window 1 and Window 2 Funds is held by the System Organization toward the Funders, while each Center has fiduciary responsibility toward the System Organization for the funds it receives. This means that the System Organization must ensure that the funds are used for their intended purposes and in accordance with relevant agreements, while Centers must manage the funds they receive in a similar manner. Both entities are required to monitor, evaluate, and report on the use of these funds to ensure compliance with established standards. 
+Sources:
+File — Location — Cited IDs
+docx:Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24 — u19-22
+docx:Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21 — u16-19</t>
+  </si>
+  <si>
+    <t>The fiduciary responsibility for the use of Window 1 and Window 2 Funds lies with the System Organization towards the Funders, while each Center holds fiduciary responsibility towards the System Organization for the funds it receives. They must ensure that these funds are used exclusively for their intended purposes and administered in accordance with the CGIAR System Charter, the CGIAR System Framework, and applicable Fund Use Agreements. Additionally, they are required to monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by these resources. 
+Sources:
+File — Location — Cited IDs
+Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24 — docx:Standard Provisions 2026.docx:u19-22
+Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21 — docx:Standard Provisions 2026.docx:u16-19</t>
+  </si>
+  <si>
     <t>Information Session on 2025 Technical Reporting.pptx — slide 9 — pptx:Information Session on 2025 Technical Reporting.pptx:s9, Engagement Plan 2025 Technical Reporting.docx — paragraph 2 — docx:Engagement Plan 2025 Technical Reporting.docx:p2, Information Session on 2025 Technical Reporting.pptx — slide 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s2, Guidance on reporting outputs or outcomes.docx — paragraph 22 — docx:Guidance on reporting outputs or outcomes.docx:p22, Engagement Plan 2025 Technical Reporting.docx — section 'Technical Reporting questions' — docx:Engagement Plan 2025 Technical Reporting.docx:p59, CGIAR_ImpactReport_2022-24.pdf — page 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p1, Engagement Plan 2025 Technical Reporting.docx — section 'A single location for all documents and resources' — docx:Engagement Plan 2025 Technical Reporting.docx:p31, Engagement Plan 2025 Technical Reporting.pptx — slide 1 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s1, CGSpace.docx — section 'CGSpace' — docx:CGSpace.docx:p3, CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 5 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5</t>
   </si>
   <si>
@@ -684,6 +771,12 @@
   </si>
   <si>
     <t>https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543 — page 9 part 2 — pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1 — page 22 part 1 — pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1, CGI21_508012_PORB_Genebanks.pdf — page 11 part 1 — pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1</t>
+  </si>
+  <si>
+    <t>Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24 — docx:Standard Provisions 2026.docx:u19-22, Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21 — docx:Standard Provisions 2026.docx:u16-19, Standard Provisions 2026.docx — section 'Return of Funds. Unexpended or Uncommitted Funding.' paragraph 198 to section 'Misused Fund' paragraph 202 — docx:Standard Provisions 2026.docx:u181-184</t>
+  </si>
+  <si>
+    <t>Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24 — docx:Standard Provisions 2026.docx:u19-22, Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21 — docx:Standard Provisions 2026.docx:u16-19, https://cgspace.cgiar.org/items/a88f8775-4ba9-41b6-9525-0d698d83cfb4 — page 72 part 2 — pdf:CGI21-507033-PORB-Policy Innovations.pdf:p72pt2</t>
   </si>
   <si>
     <t>[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]
@@ -1628,6 +1721,381 @@
 Research Organization Centre de coopération internationale en recherche agronomique pour le développement Wageningen University and Research Centre Cornell University Zambia Agriculture Research Institute Ethiopian Institute of Agricultural Research Agricultural Research Institute - Tanzania Food and Agriculture Organization of the United Nations Indian Council of Agricultural Research 176 118 135 111 106 87 98 80 79 78 Food and Agriculture Organization of the United Nations Agricultural Research Institute - Tanzania National Agricultural Research Organisation (Uganda) Ministry of Agriculture and Rural Development (Vietnam) Kenya Agricultural and Livestock Research Organization Instituto de Investigacao Agraria de Mozambique Department of Agriculture Extension (Bangladesh) Indian Council of Agricultural Research Zambia Agric</t>
   </si>
   <si>
+    <t>[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]
+el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]
+Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]
+- 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness" 411,914 "Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 "Andean Crop Diversity for Climate Change P-1560-DGUL" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 "Youth, Citizen Science and E-commerce:
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]
+Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3]
+Seed Ltd CIMMYT ID DEPLOY PROASE Productores Asociados de Semillas S.C. de R.L. de C.V. CIMMYT ID DEPLOY Productora de Semillas Azteca S.P .R. de R.L. CIMMYT ID DEPLOY PRODUCTORA DE SEMILLAS SMART SEEDS SAS DE CV CIMMYT ID DEPLOY Productora de Semillas Zarco S.P .R. de R.L. CIMMYT ID DEPLOY Productores de Semilla de Copandaro S.P .R. de R.L. CIMMYT ID DEPLOY Productos y Servicios Agrícolas S.P .R. de R.L. CIMMYT ID DEPLOY QualiBasic Seed Company (QBS) CIMMYT AB, ID
+---
+[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]
+2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]
+nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u1-4]
+2025 Technical Reporting Information (Session 2)-20250729_150218-Meeting Recording 29 de julio de 2025, 1:02p.m. 47 min 36 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]
+at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and
+---
+[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2]
+II) ICRISAT AOW02 Digital Advisories and Climate Risk Management $89,064 N-343001-GCAN INITIATIVE IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $1,321,123 N-601158-SPIR II IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $201,213 PJ-003953: APPUI A LA TRANSFORMATION ET A LA RESILIENCE DES SYSTEMES ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]
+business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3]
+de Cajas Rurales de Ahorro y Crédito Comunidades de Oriente (CECRUCSO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organización para el Desarrollo del Corquin (ODECO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organismo Cristiano de Desarrollo Integral de Honduras (OCDIH) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW
+---
+[ID: pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3]
+Frameworks for Climate Services PLACA Climate Action Platform for Agriculture in Latin America and the Caribbean / La Plataforma de Acción Climática en Agricultura de Latinoamérica y el Caribe PMU Program Management Unit PPU Portfolio Performance Unit PRMS Performance and Results Management System REMET Reducing Methane Emissions from Rice project ROI Return on investment S4I Scaling for Impact (Program) SA South Asia SB
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2]
+de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation Globally (AOW05) High Level Output 5.4. Unique crop diversity under threat is safeguarded through the integration of in situ and ex situ conservation strategies 50,000 "Revealing the Diversity of Barley Quality Traits through Synergies between On-farm Practices and Technological Innovations D-100735" ICARDA Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 237,008 Long Term Partnership Agreement ICARDA Biodiversity
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3]
+(INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID DEPLOY Institut National pour l'Etude et la Recherche Agronomiques (INERA) - RDC CIMMYT AB, ID DEPLOY Instituto de Investigação Agronómica (IIA) - Angola CIMMYT AB, ID DEPLOY Instituto de Investigación Agropecuaria de Panamá CIMMYT AB, ID STRATEGIZE/REFOCUS, PARTNER / TRANSFORM, OPTIMIZE / ACCELERATE, CREATE Invicta Agritech India Private Limited CIMMYT ID DEPLOY JAMSONI COMPANY LIMITED CIMMYT ID DEPLOY Jardins da Yoba CIMMYT ID
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3]
+C.V. CIMMYT ID DEPLOY Semillas Barriga S.R.P . de R.L. CIMMYT ID DEPLOY Semillas Berentsen S.A. de C.V. CIMMYT ID DEPLOY Semillas Cinteotl S.P .R de R.L. CIMMYT ID DEPLOY Semillas Iyadilpro y Ya S.A. de C.V. CIMMYT ID DEPLOY SEMILLAS MEJORADAS S.A. CIMMYT ID DEPLOY Semillas Ocso S.P .R. de R.L. CIMMYT ID DEPLOY Semillas Proseso SA DE CV CIMMYT ID DEPLOY Semillas y Agroinsumos Golden S.P .R. de R.L. de C.V. CIMMYT ID DEPLOY Semillas PROSASOL S.P .R. de R.L.
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4]
+to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación Regionalde Servicios Agropecuarios de Oriente (ARSAGRO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Cooperación para el Desarrollo Rural de Occidente-CDRO - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems CGI21-508007-PORB-Scaling for Impact.indd 22CGI21-508007-PORB-Scaling for Impact.indd 22 07/08/2025 13:2407/08/2025 13:24
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p55pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 55 of 86 External collaborations/partners Center Area of Work Title and Number High level output (If Available) Arab Center for the Studies of Arid Zones and Dry Areas - ACSAD ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing Institut National de la Recherche Agronomique de Tunisie; National Agricultural Research Institute of Tunisia - INRAT ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing Institut National de Recherche Agronomique de Tunisie. INRAT. ICARDA AoW2, AoW3 HLO: Accelerate - Stage2 &amp; Stage 3 testing &amp; Deploy Ankara University, Faculty of Agriculture ICARDA AoW2 HLO: Accelerate Stage2 &amp; Stage 3 testing
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt4]
+del Bienestar (SEBIEN) de Quintana Roo CIMMYT Contracted AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Secretaría de Desarrollo Agropecuario (SEDAGRO) de Morelos CIMMYT Contracted AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Ministerio de Agricultura, Ganadería y Alimentación (MAGA) de Guatemala CIMMYT Potential AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio CGI21-508007-PORB-Scaling for Impact.indd 31CGI21-508007-PORB-Scaling for Impact.indd 31
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt2]
+(SME) Private Ltd CIMMYT ID DEPLOY IFFA Seed Co Ltd CIMMYT ID DEPLOY Indian Institute of Maize Research CIMMYT AB, ID DEPLOY Indo American Hybrid Seeds (India) Pvt. Ltd CIMMYT ID DEPLOY Institut de Recherche Agricole pour le Développement (IRAD) CIMMYT AB, ID DEPLOY Institut des Sciences Agronomiques du Burundi (ISABU) CIMMYT AB, ID DEPLOY Institut National de la Recherche Agronomique du Niger (INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 32 of 90 August 2025 | CGIAR Contracted partner Center Current Status of Partnership Area of Work Title and Number High level output (If Available) Dirección de Coordinación Regional y Extensión Rural (DICORER) CIMMYT Potential AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Fundación para la Innovación Tecnológica Agropecuaria y Forestal
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p27pt3]
+Bolivia CIMMYT Phenotyping ZARI - Zambia Agricultural Research Institute, Zambia CIMMYT Phenotyping INIA Chile -Instituto de Investigaciones Agropecuarias, Chile CIMMYT Phenotyping INIA Uruguay -Instituto Ncional de Investigacion Agropecuaria, Uruguay CIMMYT Phenotyping IRESA - Institution de la Recherche et de l’Enseignement Supérieur Agricoles, Tunisia CIMMYT Phenotyping TAGEM - Ministry of Food Agriculture and Livestock, Turkey CIMMYT Phenotyping KALRO- Kenya Agricultural &amp; Livestock Research Organization, Kenya ARIA, Afghanistan CIMMYT Phenotyping-Int Nurseries ITGC, Algeria CIMMYT Phenotyping-Int
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt2]
+la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics (Breeding for Tomorrow) ● T-PJ-003670- Long-term funding of Ex Situ collections of germplasm (IITA) (Breeding for Tomorrow and CapSha) ● L-LTG001-Long term funding of ex situ collections of germplasm (ILRI) (Breeding for Tomorrow) ● R-A-2023-9-Genebank-AI (Breeding for Tomorrow) ● T-PJ-003575: Cassava Allele Mining Project: (IITA) Mining useful alleles for climate change adaptation in the cassava from CGIAR Genebanks (Breeding for Tomorrow and Climate Action) ● T-PJ-003576- (IITA) Mining useful alleles for climate change adaptation cowpea (Cowpea Allele mining project: Mining useful alleles for climate change adaptation in cowpea from CGIAR Genebanks (year 2022-26) (Breeding for Tomorrow, CapSha, and Climate Acti on) ● T-PJ-004017-VACS (IITA): Vision for Adapted Crops and Soil: Bambara Groundnut (Breeding for Tomorrow, CapSha and
+---
+[ID: pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 13 of 86 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD FRANCE – FFEM Promover Oportunidades Sostenibles en la Cadena de Valor del Cacao de Excelencia (IA Lead of A1537) Alliance Bioversity CIAT AoW 3-Markets and Business Models; AoW 5-Gender Equality, Social Inclusion and Fairness Intermediate Outcome - AOW-IOC 3.2. Local producer organizations, national and sub-national public actors and private sector actors co-design or strengthen inclusive business models; 2030 Outcome - 2030 OC-4. Marginalized people participate in implementing innovations; 2030 Outcome - 2030 OC-3 Government, market and finance actors implement
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p25pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 25 of 44 Partner Center Area of Work Title and Number High level output (If Available) Local Governments for Sustainability, Nairobi City County, Dhaka North City Corporation, Local Government of Quezon City (Philippines), RUAF Foundation International Potato Center / Centro Internacional de la Papa 3.5.5 Urban food systems governance - Delivering knowledge products, evidence and capacity sharing with policy makers to guide interventions aimed at strengthening
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt1]
+Capacity Sharing Accelerator Inception Report 4 ISNAR International Service for National Agricultural Research ISRA Institut Sénégalais de la Recherche Agricole (Senegalese Agricultural Research Institute) ITU International Telecommunication Union KOICA Korea International Cooperation Agency KPIs Key Performance Indicators. MELIA Monitoring, Evaluation, Learning, and Impact Assessment NARES National Agricultural Research and Extension Systems NARS National Agricultural Research System PCT Program Coordination Team
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p36pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 36 of 86 August 2025 | CGIAR External collaborations/partners Center Area of Work Title and Number High level output (If Available) L’Institut Tchadien de Recherche Agronomique pour le Développement – ITRAD – Chad CIMMYT AB, ID, MI, Enable l’Institut National de la Recherche Agronomique du Niger – INRAN – Niger CIMMYT AB, ID, MI, Enable Ministry of Agriculture and Food Security – MAFS – Sudan CIMMYT AB, ID, MI, Enable MyAgro – USA CIMMYT ID National Agricultural Research Organization
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt2]
+(SLARI) Africa Rice Potential AoW 4 - Achieving Impact by Unlocking Finance and Partnerships GrainPro Inc Africa Rice Potential AoW 2 - Pathways to Scale in Agrifood Systems African Development Bank Africa Rice Contracted AoW 4 - Achieving Impact by Unlocking Finance and Partnerships Seed Development and Certification Agency, Liberia Africa Rice Potential AoW 3 - Enabling Environment Lab Central de Cajas Rurales de Ahorro y Crédito Comunidades de Oriente (CECRUCSO) - Honduras CIAT Contracted AoW 2 - Pathways to
+---
+[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p35pt4]
+Senegalais de Recherches Agricoles – ISRA – Senegal CIMMYT AB, ID, MI, Enable Instituto de Investigacao Agraria de Mocambique – IIAM – Mozambique CIMMYT AB, ID, MI, Enable International Institute of Tropical Agriculture – IITA – Nigeria CIMMYT AB, ID, MI, Enable Kenya Agricultural and Livestock Research Organization – KALRO – Kenya CIMMYT AB, ID, MI, Enable Lake Chad Research Institute – LCRI – Nigeria CIMMYT AB, ID, MI, Enable L’Institut de l’Environnement et de Recherches Agricoles – INERA – Burkina Faso CIMMYT AB, ID, MI, Enable CGI21-508008-PORB-Breeding for Tomorrow.indd 35CGI21-508008-PORB-Breeding for Tomorrow.indd 35 08/08/2025 16:0208/08/2025
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p36pt4]
+metrics, monitoring and evaluations. HLO 5.3: Curated analytics for innovation portfolio management and decision-making, including Scaling Readiness evaluations and customized assessment tools for target countries, both ongoing and as part of the annual adaptive management process, to ensure continuous learning and improvement Foundation SpectAct, Morocco ICARDA Existing AoW 3 - Enabling Environment Lab Institut National de la Recherche Agronomique a Tunisie (INRAT) ICARDA Existing AoW 3 - Enabling Environment Lab CGI21-508007-PORB-Scaling for Impact.indd 36CGI21-508007-PORB-Scaling for Impact.indd 36 07/08/2025 13:2407/08/2025 13:24
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt2]
+capacity AfriSeed, Zambia CIMMYT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact HLO 5.2: Insights for CGIAR scaling success through impact assessments.HLO 2.2: Co-designed scaling pathways for regional and national agrifood systems through improved stakeholder capacity Secretaría de Agricultura y Desarrollo Rural (SADER) de México CIMMYT Potential AoW1 - Engage and Empower HLO 1.1: A toolbox of methods, data, and dashboards HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Agencia Mexicana de Cooperación Internacional para el Desarrollo (AMEXCID) CIMMYT Potential AoW1 - Engage and Empower HLO
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt2]
+Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The World Bank, German Red Cross (Germany), Dhaka City North Corporation, Nairobi City County, International Water Management Institute, WorldFish International Food Policy Research Institute 1.2.2 Evidence Synthesis and Adaptive Learning - Co-develop knowledge products and action plans, and identify key investment and innovation priorities for stakeholders and partners to guide interventions aimed at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National
+---
+[ID: pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p28pt2]
+system Provincial govt. AOW 4 Market Systems, Policy Solutions and Scaling OP 4.2. Decision-support tools for efficient animal and aquatic food system Colombian Roundtable for Sustainable Cattle AOW 4 Market Systems, Policy Solutions and Scaling OP 4.2. Decision-support tools for efficient animal and aquatic food system Universidad del Cauca AOW 4 Market Systems, Policy Solutions and Scaling OP 4.2. Decision-support tools for efficient animal and aquatic food system Universidad de los Andes AOW 4 Market Systems, Policy Solutions and Scaling OP 4.2. Decision-support tools for efficient animal and aquatic food system EAFIT University Colombia AOW 4 Market Systems, Policy Solutions and
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p1pt2]
+Report June 2025 Contact: Nicoline de Haan (n.dehaan@cgiar.org)
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4]
+Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations, and evidence-based programs for enhancing inclusive informal food markets that effectively create quality jobs for young women and men and deliver safe and healthy foods in urban environments University of Peradeniya, Wayamba University of Sri Lanka, Asian Development Bank, World Food Programme International Food Policy Research Institute 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents CGI21-507031-PORB-Food Frontiers and Security.indd 24CGI21-507031-PORB-Food Frontiers and Security.indd 24 29/07/2025 19:3929/07/2025 19:39
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u52-56]
+Aryal, Bishal (IFPRI) 44:47 Thank you. Thank you. Nirmal, Rajalakshmi (IFPRI) 44:50 Thank you. Bye, bye. Trifa, Nicoleta (CGIAR System Organization) 44:53 Hi. Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1]
+23 Bilateral Contribution to Multifunctional Landscapes MELIA Studies UK FCDO - Seed to tree: value chains and partnerships for resilient restored forests in Malaysia • Actor engagement and outcome tracking UK – GCBC (UK-Defra) - Deploying Diversity as a Strategic Asset for Scaling of Ethiopia’s Green Legacy Initiative for Climate Change Resilience and Livelihoods • Program learning review • Actor engagement and outcome tracking FRANCE – FFEM Promover Oportunidades Sostenibles en la Cadena de Valor del Cacao de Excelencia (IA Lead of A1537) • Actor engagement and outcome tracking CoIMPACT INDIA • Program learning review Fruitful Lands India Phase II • Actor engagement and outcome tracking Sustainable Investments for Large-scale Rangeland R • Actor engagement and outcome tracking Building Community
+---
+[ID: pdf:CGI21-507033-PORB-Policy Innovations.pdf:p32pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 32 of 72 July 2025 | CGIAR Contracted partner Center Area of Work Title and Number High level output (If Available) University of Los Andes CIAT Governance and Political Economy (AOW03) 3.3: New communities of practice, political economy and policy process tools are developed and strengthened, bringing together decision makers and diverse stakeholders to strengthen science diplomacy, science policy engagement, design, and implementation. Tegemeo Institute in Kenya IFPRI Governance and Political Economy (AOW03) 3.3: New communities of practice, political economy
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p21pt2]
+Research for Development (IRAD) Africa Rice Contracted AoW 2 - Pathways to Scale in Agrifood Systems Centre National de Recherche Agronomique (CNRA) Africa Rice Contracted AoW 2 - Pathways to Scale in Agrifood Systems The Council for Scientific and Industrial Research – Savannah Agricultural Research Institute (CSIR- SARI) Africa Rice Contracted AoW 2 - Pathways to Scale in Agrifood Systems Centre National de Recherche Appliqué au Développement Rural (FOFIFA/CENRADERU) Africa Rice Contracted AoW 2 - Pathways to Scale in Agrifood Systems L’Institut Sénégalais de Recherches
+---
+[ID: pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p13pt4]
+for delivering SAAF outputs and outcomes. These organizations are either think tanks and consultancy firms (e.g. MacKenzie), governmental extension services (Fisheries Commission Ghana), or NGOs (Heifer International, CARE). In those instances, CGIAR is well-positioned to undertake the work. Still, stakeholder engagement can be pursued with stakeholders to transition toward sustainability and scaling. The remaining 80% have been rated as moderately efficient and impactful in undertaking HLO work. This group encompasses NARES (KALRO, IFReDI), NGOs (Vétérinaires Sans Frontières); private sector organizations (EON Aquaculture Limited, Githunguri Dairy Cooperative); international organizations (FAO, World Bank, AfDB); universities from the Global North (Corwell, Kiel) or targeted countries (Universidad de los Andes, University of Nairobi, Hanoi University of Public Health). While CGIAR is well or moderately positioned in most instances, there are significant opportunities for collaboration, stakeholder engagement, and in some instances, formal partnerships. Sustainable Animal &amp; Aquatic Food Science Program Comparative Advantage analysis
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt3]
+International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations, and evidence- based programs for enhancing inclusive informal food markets that effectively create quality jobs for young women and men and deliver safe and healthy foods in urban environments $454,738 T-PJ-003812-ETH/IITA - CITY REGIONS FOOD SYSTEMS, RUNRES (TH International Institute of Tropical Agriculture Urban Food Systems - AOW3 3.1.1 Safe urban food production - Evidence- based innovations and business models to improve safe, nutritious, and
+---
+[ID: docx:2025 Technical Reporting Information (Session 1).docx:u43-45]
+Colomer, Julien (One CGIAR - France) 48:19 Thanks. Hurt, Chris (ILRI) 48:19 Thank you. Trifa, Nicoleta (CGIAR System Organization) ha detenido la transcripción
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt2]
+National Agricultural Research and Extension Systems NARS National Agricultural Research System PCT Program Coordination Team PMU Program Management Unit PORB Plans of Results and Budgets RAB Rwanda Agriculture and Animal Resources Development Board RELASER Red Latinoamericana de Servicios de Extensión Rural (Latin American Network for Rural Extension Services) RUFORUM Regional Universities Forum for Capacity Building in Agriculture SAARC South Asian
+---
+[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p4pt4]
+Cooperation TAP Tropical Agriculture Platform ToC Theory of Change ToR Terms of References TPI The Partnering Initiative UM6P Université Mohammed VI Polytechnique UNCTAD United Nations Conference on Trade and Development UNESCO United Nations Educational, Scientific and Cultural Organization. UNICEF United Nations International Children's Emergency Fund UPLB University of the Philippines Los Baños W3 Window 3 WCDI Wageningen Centre for Development
+---
+[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt3]
+ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance Contract IITA AOW02 Digital Advisories and Climate Risk Management T-PJ-003517: Chicken, Fish and Pigs Feed and Organic Fertilizer Value Chain Development Using BSF-Based Urban Biowaste Processing in Ghana, Mali, Niger and the Democratic Republic of Congo IITA AOW03 Locally-led Adaptation, AOW04 Low- emission Transitions $470,249 L-CIA023-Accelerating Impacts of CGIAR Climate Research for Africa II ILRI AOW01 Prioritization
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt3]
+management of research &amp; scaling activities across CGIAR’s portfolio Agencia Mexicana de</t>
+  </si>
+  <si>
+    <t>[ID: docx:Standard Provisions 2026.docx:u19-22]
+Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively: ensure that such Window 1 and Window 2 Funds are used exclusively for their intended purposes; ensure that such Window 1 and Window 2 Funds are administered, used and expended in accordance with the CGIAR System Charter, the CGIAR System Framework and the applicable Fund Use Agreements entered into by it, including by taking corrective action with respect to Window 1 and Window 2 Funds not used in accordance with the relevant Fund Use Agreement; and monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions.
+---
+[ID: docx:Standard Provisions 2026.docx:u16-19]
+Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research. Disbursement to Centers. The System Organization may, from time to time, initiate disbursements of Window 1 and Window 2 Funds to a Center for approved CGIAR Programs. Disbursement to a Program Participant. Subject to paragraph 2.4 of the Standard Provisions, Centers receiving Window 1 and Window 2 Funds may make further disbursements of such funds to Program Participants for the relevant CGIAR Program under Subagreements. Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively:
+---
+[ID: docx:Standard Provisions 2026.docx:u181-184]
+Window 3 Funds. At the written direction of an individual Funder, the System Organization will require Centers to promptly return any portion of Window 3 Funds that are unexpended or uncommitted at the completion of the CGIAR Research for which it was provided (including approved extensions). Such returned funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding. Misused Fund Window 1 and Window 2 Funds. The System Organization and each Center will, respectively, refund any portion of Window 1 and Window 2 Funds not used in accordance with the applicable Fund Use Agreements, and such funds will be deposited to Window 1 of the Trust Fund. Window 3 Funds. Subject to paragraph 2.3.4 of these Standard Provisions, the System Organization will require Centers to refund any portion of Window 3 Funds not used in accordance with the applicable Fund Use Agreement, and such Funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding.
+---
+[ID: docx:Standard Provisions 2026.docx:u28-31]
+ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements; monitor, evaluate as applicable, and provide quality assurance and financial and technical reporting for activities funded by Window 3 Funds in accordance with the relevant terms of these Standard Provisions; and if the Window 3 Funds are mapped to a CGIAR Program (i.e. provided for CGIAR Research activities that are aligned to the CGIAR Program's high-level outcomes and theory of change), continuously inform the System Organization and the project management unit of such CGIAR Program of the receipt of any Window 3 Funds and their use. The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds.
+---
+[ID: docx:Standard Provisions 2026.docx:u178-181]
+appropriate, the corrective action undertaken to address the concern, which may include suspension of transfer of Window 1 and Window 2 Funds to the Center. Return of Funds. Unexpended or Uncommitted Funding. Window 1 and Window 2 Funds. The System Organization and each Center will, respectively, promptly return any portion of Window 1 and Window 2 Funds that is unexpended or uncommitted at the completion of a CGIAR Program or activities under the CGIAR Program for which it was provided (including approved extensions) or at the termination of a Financial Framework Agreement between the System Organization and a Center, unless decided otherwise by the System Council. Such returned funds will be deposited to Window 1 of the Trust Fund. Window 3 Funds. At the written direction of an individual Funder, the System Organization will require Centers to promptly return any portion of Window 3 Funds that are unexpended or uncommitted at the completion of the CGIAR Research for which it was provided (including approved extensions). Such returned funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding.
+---
+[ID: docx:Standard Provisions 2026.docx:u31-34]
+The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds. The System Organization may, however: upon request of a Funder providing Window 3 Funds and acting through the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center; or in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such
+---
+[ID: docx:Standard Provisions 2026.docx:u13-16]
+In addition to the designation of contributions to the Trust Fund in accordance with the CGIAR Trustee Agreement and the Contribution Agreements or Arrangements, Funders may further designate Window 1 Funds and/or Window 2 Funds for specific purposes at the operational level subject to a decision of the System Council enabling such designations, and in accordance with a procedure for designation of funds at operational level, as may be adopted from time to time. Responsibilities over Window 1 and Window 2 Funds Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research.
+---
+[ID: docx:Standard Provisions 2026.docx:u22-25]
+monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions. Window 3 Funds. Window 3 Funds are directed by Funders to individual Centers. Funders may designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization.
+---
+[ID: docx:Standard Provisions 2026.docx:u34-37]
+in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center. Window 3 Side Agreements or Arrangements. Nothing in the Funding Agreements or Arrangements is intended to preclude Funders and Centers from entering into Window 3 Side Agreements or Arrangements in regard to the terms governing the administration and use of Window 3 Funds. Funders may choose to make a Contribution to a Center through Window 3 without entering into a Window 3 Side Agreement or Arrangement, provided that such Contribution is made without any additional conditions attached to it. Any Window 3 Side Agreement or Arrangement will be consistent with these Standard Provisions and substantially in the form of Schedule 1 (Form of Window 3 Side Agreement or Arrangement) attached to these Standard Provisions, as may be amended from time to time. Program Participants. In engaging a Program Participant with respect to Window 1, 2 and 3 Funds, Centers will incorporate in the relevant Subagreements, and cause, and monitor, compliance with the obligations set out in the Standard Provisions, including but not limited to those set out in paragraphs 2.5-2.6, 4-6, 7.2.2, 7.1.3, 7.3.2, 8.3, 8.4.4,
+---
+[ID: docx:Standard Provisions 2026.docx:u172-175]
+Acknowledgement of Funders All communications products on CGIAR Research funded by Window 1, 2 and 3 Funds, whether online or in hard copy form (e.g., publications, press releases, newsletters, website stories, blogs, posters, etc.), must acknowledge support received from Funders in accordance with applicable CGIAR Policies and Procedures on branding and communication. Suspending Transfers of Funding from Window 1 and 2 Suspension by the System Organization. The System Organization may, at any time, suspend transfers of Window 1 and Window 2 Funds allocated to a specific Center by providing a written notice to the relevant Center: (a) if the System Organization has a credible concern that the Window 1, 2 and 3 Funds are not used in accordance with the applicable Fund Use Agreements, or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) in the event of non-compliance by the Center with any of its obligations under an applicable Fund Use Agreement.
+---
+[ID: docx:Standard Provisions 2026.docx:u25-28]
+designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization. Centers receiving Window 3 Funds are responsible for the use of such funds and will: ensure that Window 3 Funds are used exclusively for their intended purposes; ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements;
+---
+[ID: docx:Standard Provisions 2026.docx:u55-58]
+Efficiency. The System Organization and each Center will, respectively: ensure that Window 1, 2 and 3 Funds are used with due regard to economy and efficiency, and that the highest standards of integrity in the administration of the funds are upheld; and ensure that Window 1, 2 and 3 Funds are used in accordance with applicable CGIAR Policies and Procedures on cost allocation, which set forth the principles of allowability, allocability, and reasonableness. Investment Income. The System Organization and each Center will, respectively, ensure that any investment income generated by the portions of the Window 1, 2 and 3 Funds they receive, including currency conversion gains, will be used for CGIAR Research or, if not needed for such purposes, returned to the Trustee for deposit into Window 1 to be made available for allocation by the System Council.
+---
+[ID: docx:Standard Provisions 2026.docx:u46-49]
+Window 1, 2 and 3 Funds. Centers will not have any obligation to collect or otherwise pay the CSP on funds disbursed through Windows 1, 2 or 3. The Funders, the System Organization and the Centers recognize that the Trustee of the CGIAR Trust Fund will collect the CSP before such funds are disbursed from the Trust Fund. Requirements on the Use of Window 1, 2 and 3 Funds CGIAR Policies and Procedures. The System Organization and each Center will, respectively ensure that Window 1, 2 and 3 Funds are used in accordance with applicable CGIAR Policies and Procedures and the relevant entity's own policies and procedures. All CGIAR Policies and Procedures will be available on the System Organization's web site. Standard of care.
+---
+[ID: docx:Standard Provisions 2026.docx:u184-189]
+Window 3 Funds. Subject to paragraph 2.3.4 of these Standard Provisions, the System Organization will require Centers to refund any portion of Window 3 Funds not used in accordance with the applicable Fund Use Agreement, and such Funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding. Inconsistency In the event of any inconsistency between the Cover Pages and these Standard Provisions, these Standard Provisions will prevail. Amendments Amendments These Standard Provisions may only be amended by approval of the System Council subject to concurrence of the Integrated Partnership Board. The System Organization will promptly notify the Funders and Centers in writing of any such amendments to these Standard Provisions.
+---
+[ID: docx:Standard Provisions 2026.docx:u175-178]
+Suspension by the System Organization. The System Organization may, at any time, suspend transfers of Window 1 and Window 2 Funds allocated to a specific Center by providing a written notice to the relevant Center: (a) if the System Organization has a credible concern that the Window 1, 2 and 3 Funds are not used in accordance with the applicable Fund Use Agreements, or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) in the event of non-compliance by the Center with any of its obligations under an applicable Fund Use Agreement. Before taking such action under paragraph 13.1, the System Organization will notify the relevant Center in writing, and consult with the System Council as well as the relevant Center with a view to identify ways and means to manage the suspension and mitigate the impact on the implementation of CGIAR Research until such time that the suspension may be lifted. If such suspension is lifted by the System Organization, it will notify the relevant Center in writing. Request by a Funder. If a Funder has a credible concern: (a) that Window 1, 2 and 3 Funds are not used by a Center in accordance with the applicable Fund Use Agreement or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) of a non-compliance by a Center with any of its obligations under an applicable Fund Use Agreement, the Funder may request, through the System Council, the System Organization to review the specific concern and, as relevant, to take appropriate corrective action. The System Organization will report to the System Council on the outcome of the review and, as appropriate, the corrective action undertaken to address the concern, which may include suspension of transfer of Window 1 and Window 2 Funds to the Center.
+---
+[ID: docx:Standard Provisions 2026.docx:u4-7]
+the Financial Framework Agreement between the System Organization and each Center with respect to Window 1, 2 and 3 Funds; and any Window 3 Side Agreement or Arrangement between a Funder and a Center with respect to Window 3 Funds. Interpretation of the Standard Provisions. Unless the context requires otherwise, the terms of these Standard Provisions governing the roles and responsibilities: between Funders and the System Organization apply to each Funding Agreement or Arrangement between a Funder and the System Organization;
+---
+[ID: docx:Standard Provisions 2026.docx:u106-109]
+Funders will manage their monitoring and evaluation requirements with respect to the CGIAR Portfolio, collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to conduct duplicative evaluations, provided that Funders providing Window 3 Funds may require supplemental monitoring and evaluations with respect to Window 3 Funds, the costs of which, including the internal costs to the System Organization or Center, would be paid by the requesting Funder. If an individual Funder wishes to request, on an exceptional basis, a review or evaluation of any activities financed with Window 1 and Window 2 Funds, such Funder will consult with a designated representative from the System Organization on the most appropriate scope and terms of reference of such review or evaluation. The designated representative will assist in arranging for such review or evaluation in accordance with the applicable CGIAR Policies and Procedures. The costs of any such review or evaluation, including the internal costs of the System Organization or Center with respect to such review or evaluation, will be paid by the requesting Funder. The System Organization and each Center will, respectively collaborate on any monitoring or evaluations conducted in connection with CGIAR Research activities funded with Window 1, 2 and 3 Funds. Monitoring
+---
+[ID: docx:Standard Provisions 2026.docx:u58-61]
+Investment Income. The System Organization and each Center will, respectively, ensure that any investment income generated by the portions of the Window 1, 2 and 3 Funds they receive, including currency conversion gains, will be used for CGIAR Research or, if not needed for such purposes, returned to the Trustee for deposit into Window 1 to be made available for allocation by the System Council. Procurement. In the event that consultants are employed or services or goods are procured with Window 1, 2 and 3 Funds, the System Organization and each Center will, respectively, ensure that the employment and supervision of such consultants and the procurement of such services or goods will be the responsibility of each entity employing or contracting such consultants or carrying out such procurement and will be conducted in conformity with applicable CGIAR Policies and Procedures on procurement, in line with the following basic principles of equal treatment and non-discrimination on grounds of nationality, competition, predictability, transparency, verifiability, and proportionality. No taxation. The System Organization and each Center will, respectively, use best efforts, to the extent allowed by applicable agreements, such as those signed with host governments, and applicable laws, to ensure that the use of Window 1, 2 and 3 Funds will be free from any taxation or fees imposed under local laws. Insurance. The System Organization and each Center will, respectively, maintain insurance coverage sufficient to cover the activities, risks, and potential omissions of the activities funded by Window 1, 2 and 3 Funds in accordance with generally accepted industry standards and as required by law.
+---
+[ID: pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt4]
+the continuity of prior work that is less fit for purpose in the Program’s ToC. Windows 1, 2, 3 and bilateral funding: Approximately half of S4I’s 2025 funding is from Window 1, with the remainder from Window 2, including two $1.25 million designated W2 allocations specifically for AoWs 4 and 5. The PORB also reflects stronger alignment of Window 3 and bilateral funding with Program logic: in 2025, 47 mapped W3 and bilateral investments totaling $44.8 million support the Program ($0.42M, $26.47M, $1.55M, $15.37M, and $0.99M across AoWs 1 through 5, respectively), with 74% of these funds active in Africa, 19% in Asia, and 7% in Latin America. Engage and Empower (AoW 1): This AoW is allocated $2.98 million in W1/W2 funding and supported by $0.42 million in W3/bilaterals. It anchors S4I’s stakeholder demand intelligence 9 The section on AoW 4 in the PORB description highlights major inception period successes in leveraging Window 3 investments, with an anticipated, two-year bilateral investment in HLO 4.1 to transition TAAT into the Scaling Program that will support new work that was not part of the RIIs or NPS.
+---
+[ID: pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt2]
+reducing producers' incomes and ability to invest in innovations; iv. Adverse national policy shifts regarding inclusion and equality; and v. Increased frequency of extreme climate events, which could undermine social progress and resilience. Please refer to the following link with the Program/Accelerator's full risk register. This link is open to ISDC colleagues and others will be granted access, on request. Category Risk Description Current Risk Level Target Risk Level Actions to Manage Risk Funding Reduced Window 1 &amp; 2 Funds Reduced Window 1 &amp; 2 funds caused by political changes from national governments which donate the bulk of CGIAR funds or other changes in donor priorities. This could result in outcome achievements failing to reach the
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p5pt2]
+CGIAR Centers, and cross-cutting functions. Additional Window 3 and bilateral funds (~$8.8 million) complement this, especially enhancing research on socio-technical innovations and inclusion. Key risks identified include inadequate funding, insufficient in-house
+---
+[ID: docx:Standard Provisions 2026.docx:u10-13]
+Use and administration of the Contributions General Provisions in Respect of the Contributions The Contributions, including the funds, assets and receipts thereof, held in the Trust Fund are administered in accordance with the terms of the CGIAR Trustee Agreement and each Contribution Agreement or Arrangement. In addition to the designation of contributions to the Trust Fund in accordance with the CGIAR Trustee Agreement and the Contribution Agreements or Arrangements, Funders may further designate Window 1 Funds and/or Window 2 Funds for specific purposes at the operational level subject to a decision of the System Council enabling such designations, and in accordance with a procedure for designation of funds at operational
+---
+[ID: docx:Standard Provisions 2026.docx:u67-70]
+Electioneering. The System Organization and each Center will, respectively, ensure that Window 1, 2 and 3 Funds will not be used to influence the outcome of any specific public election or to directly or indirectly carry on any voter registration drive. Drug trafficking. The System Organization and each Center, respectively, confirms that they have no reasonable basis to suspect that Window 1, 2 and 3 Funds would be diverted in support of drug trafficking. Discrimination against people with disabilities. The System Organization and each Center will, respectively, agree not to discriminate against persons with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and
+---
+[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p3pt1]
+Inception Report: Policy Innovations Science Program 3 Acronyms FLW Food, Land, and Water MELIA Monitoring, Evaluation, Learning, and Impact Assessment HLO High-Level Output W3 Window 3 (bilateral
+---
+[ID: docx:Standard Provisions 2026.docx:u163-166]
+In providing funds under: Funding Agreements or Arrangements, or Window 3 Side Agreements or Arrangements, Funders do not accept any responsibility or liability towards any third parties including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund; and Financial Framework Agreements, the System Organization does not accept, any responsibility or liability towards any third parties, including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund. No Additional Obligations
+---
+[ID: docx:Standard Provisions 2026.docx:u157-160]
+Change in Reporting Requirements. Unless decided otherwise by the System Council and/or the Integrated Partnership Board as the case may be, any change in the form or substance or periodicity of a technical or financial report will become effective only in the following calendar year. Additional Audits / Financial Reviews / Technical Reporting Funders will manage their audits, financial reviews and technical reporting with respect to the Window 1, 2 and 3 Funds collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to require duplicative reporting, provided that a Funder may require supplemental audits, financial reviews and technical reporting with respect to Window 3 Funds pursuant to its Window 3 Side Agreement or Arrangement, the costs of which would be paid by the requesting Funder. If a Funder wishes to request, on an exceptional basis, that the System Organization or a Center has an external audit or provides additional financial reviews or technical reports with respect to Window 1 and Window 2 Funds, and the requesting Funder has a statutory, regulatory or policy environment requiring such Funder's ability to make such a request unilaterally, such Funder will decide with the System Organization or the relevant Center on the most appropriate scope and terms of such audit, review or reporting. The costs of which, including the internal costs of the System Organization or any Center with respect to such additional audits, reviews or reporting, will be paid by the requesting Funder.
+---
+[ID: docx:Standard Provisions 2026.docx:u64-67]
+ensure, consistent with its governing arrangements, CGIAR Policies and Procedures and the respective entities’ policies and procedures, including those pertaining to combating financing for terrorists, that Window 1, 2 and 3 Funds are used for their intended purposes and are not diverted to individuals or entities associated with terrorism, as identified in accordance with relevant United Nations Security Council Sanctions resolution; and not use such Window 1, 2 and 3 Funds for the purpose of any payment to persons or entities, or for the import of goods, if such payment or import, to its knowledge or belief is prohibited by a decision of the United Nations Security Council taken under Chapter VII of the Charter of the United Nations or directed to a person or entity, appearing on the Consolidated United Nations Security Council Sanctions List. Lobbying. The System Organization and each Center will, respectively, ensure that none of Window 1, 2 and 3 Funds is earmarked for lobbying activity, defined as attempting to influence legislation (i) through affecting the opinion of the general public or any segment thereof (i.e. grassroots lobbying), or (ii) through communications with any member or employee of a legislative body, except in the case of both (i) and (ii) to the extent such activities arise inherently in relation to CGIAR Research comprising policy development. Electioneering. The System Organization and each Center will, respectively, ensure that Window 1, 2 and 3 Funds will not be used to influence the outcome of any specific public election or to directly or indirectly carry on any voter registration drive.
+---
+[ID: docx:Standard Provisions 2026.docx:u73-76]
+The System Organization and each Center will, respectively, take all necessary precautions to avoid or manage any Conflicts of Interest in all matters related to Window 1, 2 and 3 Funds. If a Conflict of Interest occurs, the System Organization and each Center will, respectively take, without delay, all necessary measures to resolve the conflict, e.g. by replacing the person in question or by obtaining independent verification of the terms of the proposed decision or transaction. Environmental and Social Standards. The System Organization and each Center will, respectively ensure: that Window 1, 2 and 3 Funds are used with due regard to environmental sustainability; and
+---
+[ID: docx:Standard Provisions 2026.docx:u37-40]
+Program Participants. In engaging a Program Participant with respect to Window 1, 2 and 3 Funds, Centers will incorporate in the relevant Subagreements, and cause, and monitor, compliance with the obligations set out in the Standard Provisions, including but not limited to those set out in paragraphs 2.5-2.6, 4-6, 7.2.2, 7.1.3, 7.3.2, 8.3, 8.4.4, 9.1.1, 9.1.2, 9.2-9.4 and 13-15. Due Diligence. Each Center will conduct due diligence and review of the CGIAR System Partners to which it is disbursing funding from the Window 1, 2 and 3 Funds to the extent deemed necessary or appropriate by such Center. Cooperation. Centers will cooperate with the System Organization in order for the System Organization to fulfill its obligations under the relevant Fund Use Agreements.
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p5pt1]
+Gender Equality and Inclusion Accelerator Inception Report 5 A total of $9 million in pooled funding for 2025 is strategically distributed across AoWs, 12 CGIAR Centers, and cross-cutting functions. Additional Window
+---
+[ID: docx:Standard Provisions 2026.docx:u121-124]
+be prepared in accordance with International Financial Reporting Standards (IFRS) or U.S. Generally Accepted Accounting Principles and in each case audited by an independent certified auditor of international standard in accordance with international audit standards; be prepared as of 31 December of each year to be submitted within six (6) months after the end of each calendar year; and disclose the use of Window 1 and Window 2 Funds in accordance with applicable CGIAR Policies and Procedures on reporting. Financial Reports
+---
+[ID: docx:Standard Provisions 2026.docx:u52-55]
+carry out all regulated research activities under high standards (set with reference to internationally accepted practices) and in accordance with applicable CGIAR Policies and Procedures, and applicable laws and regulations. Responsibility to Inform. Centers will promptly inform the System Organization, and the System Organization will promptly inform Funders through the System Council, should substantial deviation from the CGIAR Research supported with Window 1, 2 and 3 Funds develop. Financial, Economic and Administrative Standards Efficiency. The System Organization and each Center will, respectively:
+---
+[ID: docx:Standard Provisions 2026.docx:u70-73]
+with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of perso</t>
+  </si>
+  <si>
+    <t>[ID: docx:Standard Provisions 2026.docx:u19-22]
+Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively: ensure that such Window 1 and Window 2 Funds are used exclusively for their intended purposes; ensure that such Window 1 and Window 2 Funds are administered, used and expended in accordance with the CGIAR System Charter, the CGIAR System Framework and the applicable Fund Use Agreements entered into by it, including by taking corrective action with respect to Window 1 and Window 2 Funds not used in accordance with the relevant Fund Use Agreement; and monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions.
+---
+[ID: docx:Standard Provisions 2026.docx:u16-19]
+Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research. Disbursement to Centers. The System Organization may, from time to time, initiate disbursements of Window 1 and Window 2 Funds to a Center for approved CGIAR Programs. Disbursement to a Program Participant. Subject to paragraph 2.4 of the Standard Provisions, Centers receiving Window 1 and Window 2 Funds may make further disbursements of such funds to Program Participants for the relevant CGIAR Program under Subagreements. Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively:
+---
+[ID: pdf:CGI21-507033-PORB-Policy Innovations.pdf:p72pt2]
+of green bananas on her head.
+---
+[ID: docx:Standard Provisions 2026.docx:u31-34]
+The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds. The System Organization may, however: upon request of a Funder providing Window 3 Funds and acting through the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center; or in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]
+Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for
+---
+[ID: docx:Standard Provisions 2026.docx:u28-31]
+ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements; monitor, evaluate as applicable, and provide quality assurance and financial and technical reporting for activities funded by Window 3 Funds in accordance with the relevant terms of these Standard Provisions; and if the Window 3 Funds are mapped to a CGIAR Program (i.e. provided for CGIAR Research activities that are aligned to the CGIAR Program's high-level outcomes and theory of change), continuously inform the System Organization and the project management unit of such CGIAR Program of the receipt of any Window 3 Funds and their use. The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds.
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]
+CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]
+el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,
+---
+[ID: pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p52pt1]
+A pig farmer in Tien Lu district, Hung
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]
+nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p15pt4]
+HLOs
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]
+business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]
+- 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness" 411,914 "Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 "Andean Crop Diversity for Climate Change P-1560-DGUL" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 "Youth, Citizen Science and E-commerce:
+---
+[ID: docx:Standard Provisions 2026.docx:u70-73]
+with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and (viii) respect for the evolving capacities of children with disabilities. Conflicts of Interest. The System Organization and each Center will, respectively, take all necessary precautions to avoid or manage any Conflicts of Interest in all matters related to Window 1, 2 and 3 Funds.
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p37pt3]
+2.2 Better designed emergency response in fragile settings - Government, humanitarian, and NGO actors use evidence and tools in fragile settings to guide emergency responses X X X X High-Level Outputs 2.1.1 Prevent - Guidance on anticipatory action and disaster risk reduction (DRR) for FCA food systems that showcase impacts and scalability. X X X X 180,781.00 2.2.2 Respond - Guidance to improve the effectiveness of humanitarian responses to benefit individuals and communities affected by ongoing conflict and crisis X X X X Total AoW 2 budget 180,781.00 Area of Work 3:
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]
+Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The
+---
+[ID: pdf:Portfolio Narrative_2024.pdf:p5pt1]
+Section 1: Connecting impact and insight: The 2024 CGIAR Portfolio Narrative 1. SGPs are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance, and fiduciary oversight. 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022–2024. 3. EiB II reported through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they provided a concise, high- level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the Technical Reports. The 2024 CGIAR Portfolio Narrative is a cornerstone of CGIAR’s Technical Reporting Arrangement. It offers a synthesis of Portfolio coherence, synergies, and collective progress across Initiatives, Impact Platforms, and Science Group Projects (SGPs)1, which represent approximately 40 percent of CGIAR’s Portfolio by dollar value. The report does not include Center-managed bilateral projects. As a key
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2]
+protocols for data anonymization and access requests Implementation and oversight Data management responsibilities will be integrated into research staff roles with the ultimate responsibility being the
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]
+Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2
+---
+[ID: docx:Standard Provisions 2026.docx:u163-166]
+In providing funds under: Funding Agreements or Arrangements, or Window 3 Side Agreements or Arrangements, Funders do not accept any responsibility or liability towards any third parties including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund; and Financial Framework Agreements, the System Organization does not accept, any responsibility or liability towards any third parties, including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund. No Additional Obligations
+---
+[ID: docx:Standard Provisions 2026.docx:u67-70]
+Electioneering. The System Organization and each Center will, respectively, ensure that Window 1, 2 and 3 Funds will not be used to influence the outcome of any specific public election or to directly or indirectly carry on any voter registration drive. Drug trafficking. The System Organization and each Center, respectively, confirms that they have no reasonable basis to suspect that Window 1, 2 and 3 Funds would be diverted in support of drug trafficking. Discrimination against people with disabilities. The System Organization and each Center will, respectively, agree not to discriminate against persons with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and
+---
+[ID: pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p29pt3]
+in fragile settings Respond Policy change instance s and Quantity of new innovatio n uses identified Mozambi que Surveys and KII CASP 2024 2026 100,000 Evaluate UNHCR’s Sustainable Land Management and Environmental Rehabilitation Project in Bangladesh Adam Savelli (CIAT) I-OC 2.2 Better designed emergen cy response in fragile settings Respond Policy change instance s and Quantity of new innovatio n
+---
+[ID: pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p21pt2]
+for the stud y End date for the stud y Study cost (USD) How related to past evaluations (SG or others) Gendered Labor Impacts of Herder-Related Violence in Nigeria Jeff Bloem (IFPRI) I-OC 2.2 Better designed emergen cy response in fragile settings Respond Policy change instance s and Quantity of new innovatio n uses identified Nigeria Household survey (panel) n/a 2024 2025 13,100 n/a Analyzing
+---
+[ID: pdf:Type3_2024Report.pdf:p6pt3]
+Evaluation Recommendations are addressed by management. These responses are designed to ensure that Evaluations inform decision-making, enhance organizational effectiveness, promote learning, and strengthen accountability. They include time-bound commitments from management to implement Evaluation Recommendations and are systematically followed up as outlined in the CGIAR Evaluation Policy, which identifies follow-up as a critical component of the evaluative process.5 Since the launch of formal tracking in CGIAR’s 2022 Technical Report, the systematic monitoring and reporting of Management Response Actions has continued to evolve. This 2024 report provides information on (9) Evaluations and one (1) Evaluability Assessment (EA) completed during 2021-24 – all of which are available on the updated Evaluation and Management Response Actions Tracker. These Evaluations generated a total of 319 Recommendations and sub-Recommendations, underscoring the organization’s commitment to learning and continuous improvement. Evaluation title Date completed Date of Management Response No. of Recs. and sub-Recs No. of Actions Max. completion date for Actions Links to Evaluation Reports and Management Responses 2021 Synthesis of Learning from a Decade of CGIAR Research Programs June 2021 June 2022 41 41 2024 • Synthesis of Learning • Management Response Evaluation of CGIAR Platform for Big Data in Agriculture December 2021 February 2022 43 36 2030 • Evaluation Report • Management Response Evaluation of CGIAR Excellence in Breeding Platform April 2022 May 2022 47 35 2024 • Evaluation Report • Management Response Study of the PRMS Project
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]
+at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p17pt2]
+2.1.1 Prevent - Guidance on anticipatory action and disaster risk reduction (DRR) for FCA food systems that showcase impacts and scalability. SP04 and SP078 will implement joint research on natural resources management and rangelands governance. Food Frontiers and Security SP04- Multifunctional Landscapes 2.2.2 Respond - Guidance to improve the effectiveness of humanitarian responses to benefit individuals and communities affected by ongoing conflict and crisis
+---
+[ID: pdf:Type3_2024Report.pdf:p6pt4]
+2022 41 41 2024 • Synthesis of Learning • Management Response Evaluation of CGIAR Platform for Big Data in Agriculture December 2021 February 2022 43 36 2030 • Evaluation Report • Management Response Evaluation of CGIAR Excellence in Breeding Platform April 2022 May 2022 47 35 2024 • Evaluation Report • Management Response Study of the PRMS Project Management Approaches and Fit-for-Purpose Information Products December 2022 December 2022 36 19 2024 • Advisory Report GENDER (Generating Evidence and New Directions for Equitable Results) Platform Evaluation December 2023 January 2024 22 21 2024 • Evaluation Report • Management Response CGIAR Genebank Platform Evaluation March 2024 March 2024 32 26 2027 • Evaluation Report • Management Response Evaluability Assessment Review of Four Regional Integrated Initiatives June 2024 June 2024 9 8 2026 • Evaluation Report • Management Response Genetic Innovation Science Group Evaluation August 2024 September 2024 42 28* 2030 • Evaluation Report • Management Response Resilient Agrifood Systems Science Group Evaluation August 2024 September 2024 26 22* 2027 • Evaluation Report • Management Response Systems Transformation Science Group Evaluation August 2024 September 2024 21 12* TBC • Evaluation Report • Management Response Total 319 248 Table 1. Evaluation details and associated Management Responses and Actions *The number of Management Response Actions for the Science Group Evaluations will likely change after Q2, 2025. May 2025 7 6 CGIAR Portfolio Practice Change (Type 3) Report
+---
+[ID: pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p10pt2]
+use cases respond to clear demand from both
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p40pt3]
+settings - Government, humanitarian, and NGO actors use evidence and tools in fragile settings to guide emergency responses X X X X 2.3 Programs and policies to promote recovery and stabilize livelihoods in fragile settings - Government, humanitarian, and NGO actors use evidence and tools in fragile settings to design programs and policies that will promote recovery and stabilize livelihoods X X X X High-Level Outputs 2.1.1 Prevent - Guidance on anticipatory action and disaster risk reduction (DRR) for FCA food systems that showcase impacts and scalability. X X X X 759,052.00 2.2.2 Respond - Guidance to improve the effectiveness of humanitarian responses to benefit individuals and communities affected by ongoing conflict and crisis X X X X 2.3.3 Recover -
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3]
+de Cajas Rurales de Ahorro y Crédito Comunidades de Oriente (CECRUCSO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organización para el Desarrollo del Corquin (ODECO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organismo Cristiano de Desarrollo Integral de Honduras (OCDIH) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW
+---
+[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt4]
+del Bienestar (SEBIEN) de Quintana Roo CIMMYT Contracted AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Secretaría de Desarrollo Agropecuario (SEDAGRO) de Morelos CIMMYT Contracted AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio Ministerio de Agricultura, Ganadería y Alimentación (MAGA) de Guatemala CIMMYT Potential AoW1 - Engage and Empower HLO 1.2. Institutional innovations supporting prioritization, feedback, &amp; adaptive management of research &amp; scaling activities across CGIAR’s portfolio CGI21-508007-PORB-Scaling for Impact.indd 31CGI21-508007-PORB-Scaling for Impact.indd 31
+---
+[ID: pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p29pt2]
+erato r(s) Start date for the stud y End date for the stud y Study cost (USD) How related to past evaluations (SG or others) fragile settings Evaluation of UNHCR's climate resilient shelter in Mozambique Adam Savelli (CIAT) I-OC 2.2 Better designed emergen cy response in fragile settings Respond Policy change instance s and Quantity of new innovatio n uses
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p35pt2]
+use evidence and tools in fragile settings to design programs and policies that will promote recovery and stabilize livelihoods X X X X 1,001,985.01 High-Level Outputs 2.1.1 Prevent - Guidance on anticipatory action and disaster risk reduction (DRR) for FCA food systems that showcase impacts and scalability. X X X X 458,103.86 2.2.2 Respond - Guidance to improve the effectiveness of humanitarian responses to benefit individuals and communities affected by ongoing conflict and crisis X X X X 2.3.3 Recover - Guidance for policymakers and project implementers on programming options to stabilize household and community livelihoods, promote recovery, and build resilience in FCA settings (especially for
+---
+[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p17pt2]
+the stud y End date for the stud y Stud y cost (USD ) How related to past evaluations (SG or others) From Exchange to Impact: How GHUs Catalyze Genebanks- Breeding Germplasm Exchange for Invasive Cassava Disease Management IITA Intermediat e Outcome CGIAR and internal and external partners exchange genetic resources without the risk of spreading quarantine pests
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p31pt2]
+stabilize livelihoods X X X X 30,000.00 High-Level Outputs 2.1.1 Prevent - Guidance on anticipatory action and disaster risk reduction (DRR) for FCA food systems that showcase impacts and scalability. X X X X 1,031,051.00 2.2.2 Respond - Guidance to improve the effectiveness of humanitarian responses to benefit individuals and communities affected by ongoing conflict and crisis X X X X 2.3.3 Recover - Guidance for policymakers and project implementers on programming options to stabilize household and community livelihoods, promote recovery, and build resilience in FCA settings (especially for the underserved) X X X X Total AoW 2 budget 1,131,051.00 Area of Work 3: Urban Food Systems 2025 Outcome Q1 Q2 Q3
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p38pt1]
+Genebanks Accelerator Inception Report 37 are few alternative sources, especially for roots, tubers and bananas, that can provide the same assurance. AoW1 Emphasize the inclusion of NUS in Genebank collections and clarify measurement criteria for process improvements. Identify specific bottlenecks and establish accountability for targets, along with clear baselines. Provide rationale for chosen technologies and detail how various platforms integrate to enhance effectiveness. Set funding milestones to ensure support for additional activities. See above for response on NUS. Note also that CGIAR genebanks will always be responsible for the conservation and availability of the major staple crops, mandate crops of the Centers that host the genebank, and that resources cannot necessarily be moved from these to other crops especially given the frequency of requests for these crops. Hundreds of small genebank process adjustments and improvements are made annually. These are extremely hard to monitor and document but a better job should be
+---
+[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p6pt1]
+Plan of results and budget 2025 | Page 6 of 44 July 2025 | CGIAR Area of Work 2: Fragile and Conflict-affected Food Systems 2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) High-Level Outputs 2.1.1 Prevent - Guidance on anticipatory action and disaster risk reduction (DRR) for FCA food systems that showcase impacts and scalability. X X X X 2,428,987.86 2.2.2 Respond - Guidance to improve the effectiveness of humanitarian responses to benefit individuals and communities affected by ongoing conflict and crisis X X X X 2.3.3 Recover - Guidance for policymakers and project implementers on programming options to stabilize household and community livelihoods, promote recovery, and build resilience in FCA settings (especially for the underserved) X X X X
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p6pt4]
+in rural communities and the overall capacity of populations to innovate and to build and maintain resilient livelihoods and landscapes. AoW5 contributes to this vision by: a) developing or strengthen ing participatory research tools and methodologies for understanding the context, history, causes and influences of fairness and GEYSI in each multifunctional landscape; b) co-designing gender transformative approaches to change discourses and norms; c) supporting the gender responsive and fair implementation of innovations and interventions; d) strengthening capacity of partners on transdisciplinary, gender responsive a nd socially inclusive approaches; e) supporting the development and implementation of re sponsible scaling strategies; f) adapting GEYSI -responsive and -transformative approaches to landscape perspective; and g) develop research on emerging (new) topics and generating evidence on new directions for achieving quality of life and social equity r esilience from a human perspective. These lead to two key outputs: GEYSI-responsive and transformative approaches and methodologies from
+---
+[ID: pdf:Type3_2024Report.pdf:p3pt2]
+stakeholders 4 2.2. Close-out of the 2022-24 Portfolio 6 2.3. Transitioning to the 2025-30 Portfolio 6 Section 3: Implementation Status: Management Responses to CGIAR Evaluations 7 3.1. Key developments in 2024 for tracking Evaluation Recommendations and Management Response Actions 10
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p49pt2]
+TOC is pivotal to mapping out the complex connections across a holistic B4T program and enabling clarity in responsibilities for MELIA and accountabilities for outcomes. ISDC Feedback The ISDC Feedback was summarized for the System Council. This summarized feedback is shown in Table 7, along with how the points of feedback have been considered in the revision of the TOC and MELIA framework. Table 7 Response to ISDC Feedback from MELIA perspective Assessment Criteria Comment Response 2. Evidence that the Science Program is demand driven through codesign with key stakeholders and partners (NARES, governments, farmers, private sector, funders) and research collaborators within and outside CGIAR. This Program targets “impactful geographics and user needs,” seeking to identify areas with the lowest 35% impact and reallocate these resources to the top 25% impact. However, more acknowledgement could be given to the crucial role of the NARES and farmers and their local knowledge which should be integrated with modern tools to enhance adoption. While targeting “the highest
+---
+[ID: pdf:CGI21-507033-PORB-Policy Innovations.pdf:p20pt2]
+evaluate the returns to R&amp;D investments in different regions and different crop and anima</t>
+  </si>
+  <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: According to the Annex pie chart, what was total 2024 revenue and the split by funding source?\n\nContext:\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 6\nContent: Research results can be defined according to the nature of the change and the control over it.\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p14]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 14\nContent: Figure 1: Research results according to the kind of change and the control over it.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 23 Annex 2: ISDC feedback relating to pooled &amp; non-pooled alignment5 This section provides a direct extract from the ISDC Feedback on CGIAR Portfolio Narrative 2025- 2030. Comments relating to the alignment of pooled and non -pooled have been extracted from the broader set of comments. They have not been edited to e.g. update Program and Accelerator nomenclature. • Articulation of how the Portfolio, including bilateral and W1 funding, will be bundled into Megaprograms is still lacking. Bilateral funding is restricted and is provided for a specific purpose and with specific intended impacts. This needs to be honored a nd the lack of flexibility in shifting those funds into other areas should be clearly acknowledged. • Alignment of the entire Portfolio with the CGIAR 2030 Research and Innovation Strategy needs to be strong and explicit. How will management ensure that bilateral funding delivers against this Strategy? In addition: o What happens if a bilateral project is not strongly aligned with the Strategy and how will CGIAR ensure that opportunity costs are covered? o Will all bilateral projects across all Centers be mapped to support the Portfolio? • A challenge that should be acknowledged is incorporating bilateral funding into Megaprograms. Each Megaprogram and Accelerator will be large scale and staff will be consumed by the implementation of contracted work. Trying to build Megaprogram linkages in parallel with bilateral funding should be additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative 2025-2030\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p5]\nFile: Type3_2024Report.pdf\nLocation: page 5\nContent: Section 2: Portfolio Performance and Project Coordination Progress 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022-2024. 3. Science Group Projects (SGPs) are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance and fiduciary oversight. 4. EiB II will report through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they will provide a concise, high-level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the technical reports. 2.1. Technical Reporting Arrangement 2022-24 CGIAR Technical Reporting fulfils the System-level programmatic reporting requirements set out in the Standard Provisions annexed to the Funding Agreement or Arrangement signed between each Funder and the System Organization.2 The 2024 Technical Report includes the following Initiatives, Impact Platforms and SGPs3: • All 32 Initiatives • Five Impact Platforms – Gender Equality, Youth and Social Inclusion – Environmental Health and Biodiversity – Nutrition, Health and Food Security – Climate Adaptation and Mitigation – Poverty Reduction, Livelihoods and Jobs • Six SGPs – Accelerated Varietal Improvement and Seed Delivery of Legumes and dryland Cereals in Africa (AVISA) – Roots Tubers and Banana (RTB) Breeding – Accelerating Genetic Gain and Varietal Replacement in Rice - Phase 2 (AGGRi 2) – Excellence in Breeding (EiB) II: Cross-Crop Support Services for Breeding Acceleration4 – Accelerating Crop Improvement Through Genome Editing 2023-2025 – Climate Adaptation Insight For 2024, CGIAR will produce and deliver a total of 46 Technical Reporting outputs: • March 2025: Results from 2024 published on the online CGIAR Results Dashboard (1). • May 2025: Publication of 42 Type 1 (32 x Initiative reports; 5 x Impact Platform reports; 5 x SGP reports) Reports and a Type 3 Report (1). • End of June 2025: Publication of the Portfolio Narrative (1). • End of June 2025: Publication of the Type 2 Report: CGIAR Contributions to Impact in Agrifood Systems (2022-24) (1). Each of these reports is released separately and will be available in PDF format. 2024 Technical Reporting covers USD 370 million (USD 322 million for Initiatives and Impact Platforms, and USD 49 million for W3 SGPs), representing nearly 40 percent of CGIAR’s total pooled and non-pooled funding for 2024. 2.1.1. Streamlining the process and adding value to stakeholders In 2022 CGIAR launched a new 2022-24 Technical Reporting Arrangement, co-developed with the System Council’s Strategic Impact Monitoring and Evaluation Committee (SIMEC). The 2022 rollout was regarded as a “first pancake” or trial phase, establishing minimum viable functionality and setting the foundation for annual improvements. Key achievements of 2022 Technical Reporting included the adoption of a common report template aligned with the Technical Reporting Arrangement for Initiatives and Impact Platforms; integration with CGIAR’s Results Framework; digital linking of results to theories of change (TOCs); and the introduction of quality assurance processes mediated by third parties. Additionally, a new interactive CGIAR Results Dashboard was launched, and the Performance and Results Management System (PRMS) – an online reporting system – was developed, alongside adaptive management processes and the rollout of Innovation Packages and Scaling Readiness plans. Building on this, 2023 Technical Reporting incorporated lessons from a 2022 Learning and Optimization process, documented in a 2022 Learning and Optimization report. Key advancements included transitioning to “Always on” reporting by opening the PRMS from September 2023, more than doubling the reporting window compared to 2022 and allowing greater flexibility for Initiatives, Impact Platforms, and SGPs. Quality assurance was optimized through four staggered batches across 2023 and 2024. Further enhancements included expanding per-result tagging to all five Impact Areas. A Risk Management Module was launched to support risk identification and reporting at the Initiative level. A large number of participants joined training sessions to support reporting, dashboard use, and onboarding, and the rapid uptake of adaptive management strengthened strategic agility, with positive feedback from across the Portfolio. The Research Plans of Results and Budgets section of the CGIAR website was updated to ensure easy open access to Initiative, SGP and Impact Platform Plans of Results and Budgets (PORBs). The 2024 reporting cycle continued this trajectory, integrating insights from the 2023 Learning and Optimization process and Action Plan to further refine CGIAR’s Technical Reporting processes and products. Key improvements in 2024 included: • Launching the PRMS Planning Module to support the replan process: The launch of an online Planning Module synchronized TOC and Planning data in the PRMS, improving the efficiency and quality of planning workflows. Enhanced replan guidelines were provided to help Initiatives, Impact Platforms, and SGPs implement 2023 Reflect recommendations and align budget forecasts with updated budget envelopes. To support continuous learning and adaptive management, a user experience survey on the Planning Module was conducted to assess effectiveness and inform user-centered enhancements for the 2025-30 Portfolio. • Further simplifying reporting processes and tools: A series of enhancements to PRMS functionalities were implemented to improve efficiency and usability. Improved filtering options, enhanced notification systems, and more clearly structured result PDFs now enable quicker access to relevant information. Innovation Packages and Scaling Readiness language and templates were simplified. Reporting was streamlined and modified to suit the final year of reporting for the Portfolio, with an Outcome Indicator Module co-developed with input from Initiatives, Impact Platforms and SGPs to provide them with the opportunity to assess their progress against targets for Work Package outcomes and end-of-Initiative outcomes; summative and yearly highlights were combined into a single report; and adaptive management processes removed. • Improving decision-making within the PRMS: Broader engagement from PRMS testers across reporting entities and Senior Program Managers was integrated into PRMS feature development, ensuring that system updates were aligned with user needs and supported consistent decision-making. • Enhancing product clarity: The Type 1 Annual Report template was reviewed to better accommodate end-of-Initiative outcome reporting for the final year of the Portfolio. Improvements to the Results Dashboard were made to enhance the accessibility of IPSR insights. • Strengthening quality assurance: Examples include updated and enhanced QA guidance, and updated guidance on Impact Area tagging. An AI tool was prototyped and tested on a series of data fields, with the intent to leverage lessons learned and develop an enhanced AI tool that can be applied to a broader set of reported data and integrated into the PRMS, supporting both the reporting and QA phases. • Developing the Semantic Natural Language Processing Aggregator Platform (SNAP): SNAP is an AI-powered tool enhancing access to and analysis of CGIAR’s reported outputs, outcomes, and impacts. It improves access to Portfolio information and results evidence through semantic searches, thematic clustering, and automated summaries, complementing the CGIAR Results Dashboard. SNAP-supported narratives were integrated into the CGIAR 2024 Portfolio Narrative, and ongoing refinements will further enhance its role in Portfolio reporting. • Further integrating SGPs and Impact Platforms: Between 2022 and 2024, CGIAR progressively aligned these entities with its Technical Reporting processes and common systems to enhance consistency and coherence. In 2023, three Impact Platforms – Nutrition, Health and Food Security; Climate Adaptation and Mitigation; and Environmental Health and Biodiversity – were onboarded alongside the Gender Equality, Youth and Social Inclusion Impact Platform (which reported in 2022), each receiving tailored support such as TOC and results framework development. The SGP pilot launched in 2023 further expanded CGIAR’s reporting ecosystem by integrating Center-specific Window 3 awards, with two SGPs submitting first-year results using the PRMS Reporting Tool and Type 1 Report template. In 2024, integration expanded to include the Poverty Reduction, Livelihoods and Jobs Impact Platform and four additional SGPs, further broadening the reporting ecosystem. • Enhancing risk management through the PRMS Risk Module: The Risk Management Module, launched in 2023 to support Initiative management and reporting of risks, was further enhanced in 2024, allowing Initiatives to capture transition-focused risks. It enabled Initiatives to review, update, or close risks, contributing to the design of the 2025-30 Portfolio. The updated Risk Management Module will be used by Programs and Accelerators from 2025 onward. Climate-Smart Village set-up under the Adaptation and Mitigation Initiative in Agriculture (AMIA) of the Department of Agriculture. Credit: Miguel Mamon/CIAT May 2025 54 CGIAR Portfolio Practice Change (Type 3) Report 2024\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 4\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 4 1. Technical Reporting Arrangement purpose, scope, value proposition, delivery and optimization, Purpose The purpose of th e Technical Reporting Arrangement 2025 -2030 (“TRA 25-30”) is to set out the technical reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. The TRA 25-30: • Provides the parameters that e nable the Centers, the CGIAR System Partners and the System Organization to fulfil their technical reporting obligations under the funding agreements that apply to the use of Window 1 and Window 2 funds from the CGIAR Trust Fund (“Pooled Funding”). These parameters also allow the Integrated Partnership Board to fulfil its responsibility under the CGIAR System Charter to report on programmatic performance of CGIAR Research on an annual basis. • Provides, through the establishment of common technical reporting principles, enabling tools and mechanisms, progressive alignment and synergy between the technical reporting requirements that apply to components of the CGIAR Portfolio that are funded by Pooled Funding and those that apply to the components that are funded by other sources of funds (“Non-Pooled Funding”). • Sets transparency, performance tracking, and accountability expectations between CGIAR System Funders and CGIAR including Centres, • Informs decision making at different levels, underpins research management, operationalizes the Performance and Results Management Framework (PRMF), and guides portfolio -level MELIA and the design of the next Performance and Results management System (PRMS). The current Technical Reporting Arrangement that applies to the CGIAR Portfolio during the period 2022-24 (“TRA 22-24”) was co-developed by CGIAR and System Council/Strategic Impact Monitoring and Evaluation Committee (SIMEC) members in 2022. A new TRA is needed to match 2025-30 portfolio parameters, notably the alignment of pooled and non-pooled funding sources, and to apply lessons learnt from 2022-24. Scope The TRA 25-30 provides the operational and enabling basis to plan, monitor, learn and report on the 25-30 Portfolio. It is designed to progressively enable Programs and Accelerators, Centers and their research teams to report on the pooled, bilaterally and W3-funded components of the 2025- 30 portfolio in an integrated and aligned way, without increasing reporting burdens of Centers and Scientists. Going forward, the CGIAR Integrated Partnership will work towards progressively greater alignment of W3/bilateral projects and programs with the 2030 outcomes and theories of change of the Programs and Accelerators. Centers will provide key agreed information on their W3/bilaterally funded projects and programs to enable Program/Accelerator leaderships to explore ways to achieve alignment based on, inter alia, complementarity of results as well as actual or potential thematic, geographic, and partnership overlaps. Reporting on and attribution\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 5\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results framework, underpinned by a new Technical Reporting Arrangement, will provide robust, continuous performance and results reporting across all funding sources, as well as adaptive management of the Portfolio. 1 Value Proposition The TRA 25-30: - Creates value by delivering an integrated approach that tracks the performance of each Program and Accelerator, - Brings together the inputs (including costs), outputs, outcomes and impacts of the total portfolio to allow for easier and more robust Return on Investment (ROI) calculations. - Avoids creating a significant additional and duplicative layer of complex reporting requirements for W3/ bilaterally funded work. - Informs decision making through providing ready access to demand-driven quality raw and curated data products. Delivery The TRA 25 -30 will be delivered in line with Management arrangements for CGIAR’s 2025 —30 science and innovation Portfolio. Specific roles and responsibilities will be defined in 2025. 1 CGIAR Portfolio Narrative, 1 November 2024\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:p7]\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 7\nContent: Trifa, Nicoleta (CGIAR System Organization) 0:48 Yep. OK, good. So thank you. This session is the first of two session plans for today, planned for today, with the second being scheduled later at 3:00 PM CET to accommodate colleagues in other time zones. Technical reporting. My name is Nicoletta Trifa. By the way, I'm part of the Portfolio Performance Unit, the support unit within the Office of the Chief Scientist. Here is an overview of what we'll cover in the next minutes. I believe my presentation will take 2025 minutes and then we'll leave room for questions at the end, if that's OK. So what we'll cover an update of the technical reporting arrangements 2025 to 2030, priorities and changes for 2025, a brief introduction on the annual technical report and the neighbors. So this mean the performance and results. Management system and the quality assurance, the technical reporting timeline, available resources and support and what's next and how to stay engaged. I want to mention that this session marks the start of the conversation around 2025 technical reporting. We want to give you the early look at the key priorities and plans for the months ahead, and the goal is to make sure that you stay informed, prepared and supported with a clear understanding of upcoming deliverables and timelines. And also clarity on who to reach out to if you have questions or if you need help along the way. Good. Technical reporting arrangements for the new portfolio. The 2025 to 2030 portfolio has been approved by the CGR Global Leadership team on in June 2025 and provides the operational basis to plan, monitor, learn and report. On the new portfolio. It is designed to progressively enable programs, accelerators and centers to report on the pooled and window 3 bilateral projects of the new portfolio in an integrated and aligned way without increasing the burden on centers and the scientists. Main changes compared to the previous technical reporting arrangements, streamline reported reporting. So less products, more integration, lower transaction costs, stronger impact, focus results. To be clearly linked and packaged under impacts, outcomes and associated agreed indicator targets and better linkages between the theory of change or so plan of results and budget and technical reporting. The primary audiences for technical reporting are funders and CGR staff at integrated partnership, portfolio and program and accelerator levels. A secondary audience is the partners. Annual technical reporting covers the individual annual technical reports for program and accelerators, as well as a portfolio view of aggregate contribution to thematic and geographic targets. And relevant content from this technical reports are integrated into the CJR corporate reporting. In terms of the 2025 technical reporting priorities, 2025 is a transition year with technical reporting arrangements, implementation again focusing on streamlined reporting and on strengthening the linkages between theory of change. Porb, media and technical reporting. As many of you know, in the previous portfolio these components were not properly linked, so it was a bit challenging to demonstrate progress against the theory of change or the plans, as you know. In terms of deliverables for 2025. These are the program and accelerator technical reports, which are due in April 2026, the portfolio narrative, which is due in 2026 in June. Integration of top 80% of window tree and bilateral projects by central dollar value into reporting and planning. Application of the minimum data standards for window tree and bilateral reporting. And mapping of refinement during the pause and reflect process which will take place early Q 1/20/26. So as I was mentioning, this year is seen more as a transition year towards KPI based planning and reporting and efforts are underway to enable planning and reporting at the KPI level, which is aligned with the system office objective and key results for 2026 and 20. These are to be confirmed, so they haven't been confirmed yet, but I've pasted them here so that you can see the 2026 objective and key results for the system office. So 100% program and accelerate the work plans and budget. An annual technical report. Which provide for software enabled monitoring of erformance and results against smart Ki by center, ear and ooled funds invested. So next year, 80% of centres, CGR, window three and bilateral funded work by value included in 2025 technical reports and then the following year in 2027, this will increase to 90% of centres. Window 3 and bilateral funded work included in 2026 technical reports. The following slides, what I have, what I have included in the following slides, it's a brief introduction into. What is expected in terms of deliverables from programs and accelerators together with an overview of the performance and results management system and the QA. I realized that some in this call some of you are already familiar with the reporting arrangements from the previous portfolio. While for others this might be entirely new. So our goal is to bring everyone to the same level of understanding so that we can move forward with clarity and shared expectations for the 2025 technical reporting. OK, so technical reporting for program and accelerator. We'll focus on three key deliverables. So first is reporting results, the 2025 results in the Performance and Reporting Management system, PRMS. Each program accelerator and mapped window 3 project will report 2025 results in the system and we strongly encourage to report results that were planned and budgeted. So results which have been included in the reports. As the outdated technical reporting system will allow for tracking results against plans. Secondly is the quality assurance of reporting results. As you know, the results submitted go through the quality assessment process and we will share more details on this process in the timeline in an info session scheduled for later. Which we will schedule later in in September, October and the quality assess results will be available on the results dashboard. Inform the pause and reflect and will be included in the technical reports in the annual technical reports. A third deliverable for program and accelerators is drafting estimation of the 2025 Annual Technical Report. So each program and accelerator is responsible for drafting and internally validating quality assessing their 2025 Annual Technical Report. Before submitting it to the PPU, so to the perform portfolio performance unit. Again, guidance on this, the detailed process and validation process will be shared with you timely. Also to support this process, an AI generated V0 draft will be provided as a starting point. The annual technical reports. What are they? This the annual technical report. The the the aim is to make them short, so to 20 to 30 pages, concise and targeted. They provide assurance on annual program accelerator delivery against the boards, so plan of results and budget and progress on theory of change. They are based on quality assess results, the template guidance and as I mentioned and. AI V0 will be provided to all rogram and accelerator teams. Annual technical reports need to be submitted by each program and accelerator in March, April, so more details on this will follow and publication is intended to happen end of April, beginning of May. Here to the right side you have the. Content of the annual the proposed content for the annual technical report as per the technical reporting arrangements. Many of you will notice that there are not no big changes compared to previous portfolio, so the idea is to have a fact sheet and executive summary. The annual progress on theory of change, area of work details, a section on results, section on partnerships, portfolio linkages, adaptive management and then one key result story. But again, we will plan a detailed deep dive session on the annual technical report template and the guidance. So there will be time for you to ask questions in detail about about this and to receive support obviously. I've also included here for reference links to the 2024 Annual Technical Reports from the initiatives and impact platforms, and also a link to the 2024 Portfolio Narrative Report. In case you want to, you want to have a look to see, um, what it captures. PRMS. So this stands for Performance and Results Management System is the system the the the the environment where results need to be submitted. Again, the team is working on updating their resources. There will be. New users onboarding decks created with the links to different information and I I believe the PCU Alison together with the program coordinators. Are. The all the PRMS roles. So PCU is leading a work to define the PRMS roles and to get the information from program and accelerators regarding who from each program accelerator should have what role in PRMS. To enable us to to provide the right access to the platform when the time comes to report. Quality assurance process. So results submitted by program and accelerators in the PRMS will be quality assessed by a quality assessment team in February 2026. Your participation in this process is required. Guidance and resource resources will be provided and also an info session will be scheduled later this year. What is the QA? It is a process that aims to improve the quality of the reported data to provide consistency across the system, ensure reliability of reported results. Inform the learning process and improve the overall CGR accountability and transparency. Quality assess data informs the reflect process which takes place early Q12026, the results dashboard. So once the quality assessment of the results is finalized, the quality assess results will be pushed to results dashboard. You most probably have seen that. Reading. It also informs and are the results. The practices results are included in the annual report, in the portfolio narrative, and then in the overall CGIR annual report. In terms of the the timeline, so we have this info session now to provide an overview on the technical reporting and there will be several other info session and deep dive scheduled. Throughout September and October of reporting 2025 results, we believe that it will be feasible to open the PRMS in November for program and accelerators to to report. The date is still to be confirmed. We're aiming to to, yeah, to meet to to to end November. Hopefully this will be this is feasible from the technical side quality assurance. It's planned for February 2026 reflect process as I was mentioning Q 1/20/26 and then annual technical reports are due in March, April 2026 as well. Where to find information pertaining to technical reporting and planning and media? There is a one stop shop for for um all this. It's called the Performance and Results Hub. I'm gonna stop sharing cause I wanna share. Um, I'm gonna stop sharing the deck. I wanna. We could resent the hub. I'm not going to go through each section, but at least. So that you can see for those who are new more specifically to see and we will also share the link obviously the performance and results hub as I was mentioning it has detail on reporting, planning, reflect, replan. So you come in here, you click on 2025 reporting and then you will have access to the latest information, to the timeline, latest update, upcoming events. So all the information, information. Session dates will be listed here. We'll also have a subsection here with. Recording from from meetings, so that will be posted. For example today after this session we'll post a recording and the deck here for you to access and there is a section on frequently asked question. We recycled a couple of questions from the previous portfolio and updated them so that they are applicable to the program and accelerator teams, so feel free to go here and and browse. As resources become available, we will place them here and we will notify you by e-mail. OK. Going back to my deck. Which? In terms of engagement plan, so in order to streamline communication and optimize support for program accelerators and centers with mapped window 3 bilateral projects, we will send bi-weekly emails to everyone in this. This goal with key updates on technical reporting, with reminders and also with the latest questions and answers available on the hub. There will be targeted emails focusing on specific categories within the program accelerators. We want to engage with some of you on technical reporting, revisions, developments. And the aim is to gather feedback from you. Program coordinators will be copied on these emails. Info session. So a specific topic and we'll plan info session on specific topics, for example the standard indicator, description shades, the guidance on technical reporting, quality assurance. Reporting on innovations, the PRMS, so deep dive on the PRMS, the updates, the tool and so on. And during the reporting phase and the QA we will have weekly drop-ins. So this drop-ins is there will be no presentation. Presentation during the during this drop-ins. The purpose is for us to provide live support, so to answer your questions on the spot and the primary focus will be as I was mentioning, reporting and the QA. For if you know for every question you have, we invite you to use this e-mail address performanceandresults@cgr.org. This is the. The e-mail address we use for all technical reporting questions. So you have the questions right to us at performanceandresult@cjr.org and you will receive a response. We are aiming to respond within the 24 hours. Just to give an example, you know going back here I've gotten the targeted targeted emails and feedback. So this is a good example on for example how we plan to engage and get get feedback from from you on the PRMS enhancements so. Usually we send there's an e-mail sent to invite you to provide feedback on a o</t>
   </si>
   <si>
@@ -1671,6 +2139,21 @@
   </si>
   <si>
     <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: Who coordinates funders’ M&amp;E requirements across the CGIAR Portfolio and how is duplication avoided? \n\nContext:\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23 part 4\nContent: additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 2 part 4\nContent: report is part of the CGIAR System Organisations’ technical reporting arrangement. We would like to thank all funders who supported this work through their contributions to the CGIAR Trust Fund, and those who supported bilaterally: https://www.cgiar .org/funders. The report was led by the Portfolio Performance Unit, with expert technical support from the Food Security Evidence Brokerage. We gratefully acknowledge the contributions and insights from many CGIAR staff who provided access to source materials, selected prominent themes, and reviewed drafts. This included Impact Area Platform Directors, regional leaders, CGIAR Center assessment and monitoring specialists, the Independent Advisory and Evaluation Services, the Donor Relations and Business Development unit, the Communications and Advocacy unit, CGIAR research leaders and senior\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p29pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 29 part 2\nContent: of information on how climate mitigation is covered in the Portfolio. There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. There is a lack of information on how orphan and opportunity crops and pulses are covered in the Portfolio. There is a lack of information on how\n\n---\n\n[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p33pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_Inception Report 30-06-2025.pdf\nLocation: page 33 part 2\nContent: is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. N/A There is a lack of information on how orphan and opportunity crops and pulses are covered in the Portfolio. N/A There is a lack of information on how youth and social inclusion (that does not relate to gender) is covered in the Portfolio. N/A There is a lack of information on how capacity sharing (as it relates to internal learning and decolonization of research) is covered in the Portfolio. Capacity sharing is foundational to\n\n---\n\n[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p39pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_Inception Report 30-06-2025.pdf\nLocation: page 39 part 4\nContent: more details on ToC, Areas of Work, etc. We have significantly reworked and streamlined the research questions. They are now underpinned by the assumptions formulated in the revised ToC these also serve as hypotheses (in terms of fulfilled assumptions) for the research questions. Linkages with other Programs and Accelerators A concern is how the accelerator will effectively work with and build on other capacity sharing activities at CGIAR (with other Programs and Accelerators) without duplication or competition (pp. 85). The Accelerator will include a matrix analysis of Programs and other Accelerator during inception, to map Programs’ AoW and its own AoW, in order to define common interests in research questions or challenges, synergies, alignments, complementarities, and avoid duplication of actions. Section 8 of the inception report details how the accelerator would work with other programs to ensure synergy, and avoid duplication and support complementarity in terms of delivery of its service portfolio.\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p6pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 6 part 1\nContent: 2.2. Close-out of the 2022-24 Portfolio As the 2022-24 Portfolio closed, close-out guidelines were designed to ensure a smooth transition to the new Portfolio, building on past achievements while maintaining continuity in science and innovation delivery. The close-out process focused on the timely preparation and submission of 2024 technical and financial reports, ensuring all CGIAR teams and partners met Portfolio deliverables, and facilitating effective engagement and continuous communication with stakeholders. Proactive mitigation measures were identified to manage risks associated with the transition to the new research Portfolio. Focus was placed on sustaining partnerships beyond the conclusion of the 2022-24 Portfolio to ensure ongoing collaboration. The guidelines included a section on SGPs to ensure alignment. This structured approach ensures that the achievements and collaborations of the 2022-24 cycle are seamlessly integrated into the new Portfolio. 2.3. Transitioning to the 2025-30 Portfolio Support was provided to the CGIAR Portfolio Transition Team, which included the development of Inception Guidelines that outlined the principles and processes to assist Transition Teams in planning and achieving inception deliverables for the 2025-30 CGIAR Portfolio. In 2024 work began on developing a new Technical Reporting Arrangement for 2025-30 (TRA 25-30) to define the Technical Reporting requirements for the next CGIAR Portfolio. A cross-CGIAR working group – comprising Center experts and System functions – led its development. The TRA 25-30 will promote progressive alignment between reporting requirements for pooled and non-pooled\n\n---\n\n[ID: pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p30pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact%2FScaling%20for%20Impact%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact&amp;p=true&amp;ga=1\nFile: Scaling for Impact_Inception Report 30-06-2025.pdf\nLocation: page 30 part 4\nContent: S4I will map scaling efforts across Programs to reduce duplication, achieve synergies, and strengthen system-wide coherence.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt2]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 3 part 2\nContent: outcomes and i mpacts of the whole portfolio through progressive alignment of reporting on w3/bilaterally funded components with a common framework. • Line of sight: The TRA is designed to meet the needs of diverse funders, ensuring transparency and accountability by linking investment to results, both for pooled and non-pooled funds. • Impact focus: Research results will be better linked to CGIAR’s 2030 targets using enhanced impact area indicators. Impact assessments will be integrated into Program/Accelerator design. The use of geographically-bounded targets will be explored for priority locations. A robust approach to project cross-Portfolio benefits by Impact Area for different funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified reporting: Overly complex requirements will be avoided, aiming to\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p2pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 2 part 4\nContent: reviewed and validated by the authors to ensure accuracy, coherence, and alignment with the original intent. Acknowledgements This work is part of the CGIAR System Organization. We would like to thank all funders who supported this research through their contributions to the CGIAR Trust Fund:\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p32pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 32 part 1\nContent: Genebanks Accelerator Inception Report 31 10. Addressing feedback on selects topics Concise summary of feedback Details on how the Program/ Accelerator has addressed or will address this feedback (in the Inception Phase or beyond) There is a lack of information on how water systems are covered in the Portfolio. N/A There is a lack of information on how climate mitigation is covered in the Portfolio. N/A There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how environmental health and biodiversity is covered in the Portfolio. The Genebanks proposal noted that activities will lead to a stronger overall global system of international and national institutions, policies, and mechanisms contributing\n\n---\n\n[ID: pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p25pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1\nFile: Food Frontiers and Security_Inception Report 30-06-2025.pdf\nLocation: page 25 part 1\nContent: Food Frontiers and Security Program | Inception Report 25 operational efficiency, avoid duplication, and generate broader, more context-responsive insights than either program could produce alone, delivering greater value to partners and stakeholders across the CGIAR portfolio. Together with The Climate Action SP,\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt3]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 3 part 3\nContent: funding scenarios will be developed; these projections will be used to set the targets and milestones against which progress will be reported. • Simplified reporting: Overly complex requirements will be avoided, aiming to reduce the reporting burden on Centers. Technical Report products include the following: • A Results Dashboard including AI functionalities will be updated several times a year (e.g. quarterly) to offer funders and partners closer to real-time data. • Annual Program/Accelerator Technical Reports will be complemented by an Annual Portfolio Report which will convey progress by Impact Area, geographic and thematic priorities and include information on CGIAR’s internal practice change and learning. • Portfolio outcomes and impacts will be consolidated in a specific report every 3 years. Evidence of CGIAR contributions to impact will be synthesized and regularly updated through an\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u103-106]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use of Materials' paragraph 108 to section 'Monitoring and Evaluations' paragraph 115\nContent: Intellectual Property rights. The System Organization and each Center will, respectively, ensure that necessary intellectual property rights are obtained to allow the rights referred to under this paragraph 6 to be granted. If third party copyright restrictions or attribution requirements apply to such documents, this will be indicated on the documents. Monitoring and Evaluations General Funders will manage their monitoring and evaluation requirements with respect to the CGIAR Portfolio, collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to conduct duplicative evaluations, provided that Funders providing Window 3 Funds may require supplemental monitoring and evaluations with respect to Window 3 Funds, the costs of which, including the internal costs to the System Organization or Center, would be paid by the requesting Funder.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1pt2]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 1 part 2\nContent: reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. Prepared by; Content developed by the Portfolio Performance Unit in collaboration with a x- CGIAR working group and System Council Strategic Impact Monitoring and Evaluation Committee members. Note to readers: 2024 Annual Technical Reports including the 2022-24 Type 2 Report are\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p8pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 8 part 4\nContent: other organizations as well as by funders. “CGIAR’s efforts to mainstream scaling put it at the cutting edge …” compared to other research and innovation organizations, and development organizations generally (Global Scaling Community of Practice). Figure 5: A pile of LEGO pieces that represents CGIAR’s innovation portfolio management pre-2022. What was once a fragmented system is now becoming more structured and strategic. Until 2022, there was no efficient way to manage ‘’CGIAR’s innovation portfolio’’. Innovation data was scattered, not up-to-date and lacked evidence. Furthermore, there was no operational framework to track or support scaling for impact. It led to organizational risks and inefficiencies as leadership, partners and funders could not easily access CGIAR innovations. This changed under the CGIAR 2030 Research and Innovation Strategy that embraced a more systematic and evidence-based innovation management based on principles of the Scaling Readiness approach. Currently, information on more than 1,325 innovations under development or use are now easily accessible on the CGIAR Results Dashboard, which is widely used by partners and funders. The World Bank Group, FAO, Gates Foundation, GIZ, ENABEL, and the African Development Bank are among organizations that have embraced (elements of) the CGIAR innovation management approach. CGIAR is actively sharing its innovation portfolio management journey with other organizations. The Gates Foundation partnered with CGIAR to co-develop a protocol for scaling strategies aimed at high-impact innovations. Internally, CGIAR Centers such as the Alliance of Bioversity and CIAT (ABC) and the International Livestock Research Institute (ILRI) and CGIAR projects such as the Accelerate for Impact Platform (A4IP), Technologies for African Agricultural Transformation (TAAT) and HarvestPlus Solutions have adopted elements of innovation portfolio management. May 2025 1110 CGIAR Portfolio Practice Change (Type 3)\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p6pt2]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 6 part 2\nContent: 2025-30 CGIAR Portfolio. In 2024 work began on developing a new Technical Reporting Arrangement for 2025-30 (TRA 25-30) to define the Technical Reporting requirements for the next CGIAR Portfolio. A cross-CGIAR working group – comprising Center experts and System functions – led its development. The TRA 25-30 will promote progressive alignment between reporting requirements for pooled and non-pooled funding components, and sets expectations for transparency, performance tracking, and accountability across CGIAR and with funders. It will also operationalize the PRMF , inform decision-making, and provide direction for Portfolio-level monitoring, evaluation, learning and impact assessment (MELIA) and the design of the next version of the PRMS. The TRA 25-30 is expected to be endorsed in the first half of 2025. A durum wheat field at Toluca Station. Credit: Alfonso Cortés/CIMMYT Section 3: Implementation Status: Management Responses to CGIAR Evaluations 5. For more information see the CGIAR Evaluation Policy, the CGIAR Evaluation Guidelines, and the Process Note on Developing, Tracking and Reporting on Management Responses to Evaluations. A Management Response is a formal mechanism through which Evaluation Recommendations are addressed by management. These responses are designed to ensure that Evaluations inform decision-making, enhance organizational effectiveness, promote learning, and strengthen accountability. They include time-bound commitments from management to implement Evaluation Recommendations and are systematically followed up as outlined in the CGIAR Evaluation Policy, which identifies follow-up as a critical component of the evaluative process.5 Since\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p87pt2]\nLink: https://cgspace.cgiar.org/items/04bd63a9-1b58-4eb5-84f2-b54c8bde226e\nFile: Portfolio Narrative_2024.pdf\nLocation: page 87 part 2\nContent: 2025–2030 The creation of a Scaling for Impact Program in CGIAR’s Portfolio 2025–2030 creates even more space and resources for innovation and scaling work. The Scaling for Impact Program plays an important role in catalyzing innovation scaling on the ground with CGIAR colleagues and partners while more System-wide innovation portfolio management functions continue to be delivered by CGIAR’s Portfolio Performance Unit. In CGIAR’s 2025–2030 Portfolio (Figure 6.4), innovation management is not just a process or tool — it is the central instrument for driving coherence and collaboration between the Science Programs and the Scaling for Impact Program while also aligning demand with supply and guiding strategic Portfolio priorities. Figure 6.4. Schematic overview of the CGIAR 2025–2030 Portfolio. CGIAR’s Portfolio Performance Unit and Project Coordination Unit work closely with the Scaling for Impact Program to deliver key innovation portfolio management functions for the 2025–2030 Portfolio. These two units continue to mainstream innovation and scaling tracking and performance across the\n\n---\n\n[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p26pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations_Inception Report 30-06-2025.pdf\nLocation: page 26 part 2\nContent: to national policy research ecosystems through coordinated capacity sharing activities. A prime example of this effective coordination and the efficiencies it generates is the policy program hub in Kenya. This hub actively coordinates with other CGIAR Programs, Accelerators, and individual CGIAR Centers building on efforts that the CGIAR country convener for Kenya had started. It therefore also provides an integration mechanism with W3/bilateral projects. Coordination is fundamental for avoiding duplication of efforts: They serve as a critical platform to share research plans, identify synergies, and proactively prevent overlapping activities, thereby ensuring a highly efficient deployment of collective resources across various CGIAR programs in Kenya. Beyond internal CGIAR coordination, the Kenya hub takes a leading role in planning joint policy dialogue series, country policy notes, bringing diverse stakeholders together for impactful co- design and co-implementation.\n\n---\n\n[ID: pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p33pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_Inception Report 30-06-2025.pdf\nLocation: page 33 part 1\nContent: Capacity Sharing Accelerator Inception Report 33 10. Addressing feedback on select topics Only one feedback (lack of information on how capacity sharing) applies directly to the CapSha Accelerator. Concise summary of feedback Details on how the Program/ Accelerator has addressed or will address this feedback (in the Inception Phase or beyond) There is a lack of information on how water systems are covered in the Portfolio. N/A There is a lack of information on how climate mitigation is covered in the Portfolio. N/A There is a lack of information on how tradeoffs and synergies in mixed systems are covered in the Portfolio. N/A There is a lack of information on how\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 22 part 4\nContent: CGIAR Results Framework – Portfolio Outcome"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: ¿Quién tiene la responsabilidad fiduciaria sobre los fondos de Ventanas 1 y 2 y qué debe garantizar?\n\nContext:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 2\nContent: el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 1\nContent: Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 1\nContent: CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 1\nContent: CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 10 part 2\nContent: - 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness\" 411,914 \"Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO\" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 \"Andean Crop Diversity for Climate Change P-1560-DGUL\" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 \"Youth, Citizen Science and E-commerce:\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 23 part 3\nContent: Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 45 part 3\nContent: Seed Ltd CIMMYT ID DEPLOY PROASE Productores Asociados de Semillas S.C. de R.L. de C.V. CIMMYT ID DEPLOY Productora de Semillas Azteca S.P .R. de R.L. CIMMYT ID DEPLOY PRODUCTORA DE SEMILLAS SMART SEEDS SAS DE CV CIMMYT ID DEPLOY Productora de Semillas Zarco S.P .R. de R.L. CIMMYT ID DEPLOY Productores de Semilla de Copandaro S.P .R. de R.L. CIMMYT ID DEPLOY Productos y Servicios Agrícolas S.P .R. de R.L. CIMMYT ID DEPLOY QualiBasic Seed Company (QBS) CIMMYT AB, ID\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%201%29%2D20250729%5F100141%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E76da6c8e%2D6234%2D41ff%2Dba2c%2Dc2068392ed82\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 4\nContent: nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 1\nContent: Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 2).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%202%29%2D20250729%5F150218%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E57e21346%2Dc6ca%2D4c63%2D8839%2D3e2a327c5116\nFile: 2025 Technical Reporting Information (Session 2).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 2)-20250729_150218-Meeting Recording 29 de julio de 2025, 1:02p.m. 47 min 36 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 3\nContent: at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and\n\n---\n\n[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2]\nLink: https://cgspace.cgiar.org/items/8acc660f-7305-4e4b-ab21-1c192611b017\nFile: CGI21-507032-PORB-Climate Action.pdf\nLocation: page 11 part 2\nContent: II) ICRISAT AOW02 Digital Advisories and Climate Risk Management $89,064 N-343001-GCAN INITIATIVE IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $1,321,123 N-601158-SPIR II IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $201,213 PJ-003953: APPUI A LA TRANSFORMATION ET A LA RESILIENCE DES SYSTEMES ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 3\nContent: business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 22 part 3\nContent: de Cajas Rurales de Ahorro y Crédito Comunidades de Oriente (CECRUCSO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organización para el Desarrollo del Corquin (ODECO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organismo Cristiano de Desarrollo Integral de Honduras (OCDIH) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW\n\n---\n\n[ID: pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_Inception Report 30-06-2025.pdf\nLocation: page 4 part 3\nContent: Frameworks for Climate Services PLACA Climate Action Platform for Agriculture in Latin America and the Caribbean / La Plataforma de Acción Climática en Agricultura de Latinoamérica y el Caribe PMU Program Management Unit PPU Portfolio Performance Unit PRMS Performance and Results Management System REMET Reducing Methane Emissions from Rice project ROI Return on investment S4I Scaling for Impact (Program) SA South Asia SB\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 2\nContent: de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation Globally (AOW05) High Level Output 5.4. Unique crop diversity under threat is safeguarded through the integration of in situ and ex situ conservation strategies 50,000 \"Revealing the Diversity of Barley Quality Traits through Synergies between On-farm Practices and Technological Innovations D-100735\" ICARDA Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 237,008 Long Term Partnership Agreement ICARDA Biodiversity\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 42 part 3\nContent: (INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID DEPLOY Institut National pour l'Etude et la Recherche Agronomiques (INERA) - RDC CIMMYT AB, ID DEPLOY Instituto de Investigação Agronómica (IIA) - Angola CIMMYT AB, ID DEPLOY Instituto de Investigación Agropecuaria de Panamá CIMMYT AB, ID STRATEGIZE/REFOCUS, PARTNER / TRANSFORM, OPTIMIZE / ACCELERATE, CREATE Invicta Agritech India Private Limited CIMMYT ID DEPLOY JAMSONI COMPANY LIMITED CIMMYT ID DEPLOY Jardins da Yoba CIMMYT ID\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 46 part 3\nContent: C.V. CIMMYT ID DEPLOY Semillas Barriga S.R.P . de R.L. CIMMYT ID DEPLOY Semillas Berentsen S.A. de C.V. CIMMYT ID DEPLOY Semillas Cinteotl S.P .R de R.L. CIMMYT ID DEPLOY Semillas Iyadilpro y Ya S.A. de C.V. CIMMYT ID DEPLOY SEMILLAS MEJORADAS S.A. CIMMYT ID DEPLOY Semillas Ocso S.P .R. de R.L. CIMMYT ID DEPLOY Semillas Proseso SA DE CV CIMMYT ID DEPLOY Semillas y Agroinsumos Golden S.P .R. de R.L. de C.V. CIMMYT ID DEPLOY Semillas PROSASOL S.P .R. de R.L.\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 22 part 4\nContent: to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación Regionalde Servicios Agropecuarios de Oriente (ARSAGRO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Cooperación para el Desarrollo Rural de Occidente-CDRO - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems CGI21-508007-PORB-Scaling for Impact.indd 22CGI21-508007-PORB-Scaling for Impact.indd 22 07/08/2025 13:2407/08/2025 13:24"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "deeper research"}, {"role": "user", "content": "Question: ¿Quién tiene la responsabilidad fiduciaria sobre los fondos de Ventanas 1 y 2 y qué debe garantizar?\n\nContext:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 2\nContent: el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 1\nContent: Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 1\nContent: CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 1\nContent: CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 10 part 2\nContent: - 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness\" 411,914 \"Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO\" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 \"Andean Crop Diversity for Climate Change P-1560-DGUL\" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 \"Youth, Citizen Science and E-commerce:\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 23 part 3\nContent: Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 45 part 3\nContent: Seed Ltd CIMMYT ID DEPLOY PROASE Productores Asociados de Semillas S.C. de R.L. de C.V. CIMMYT ID DEPLOY Productora de Semillas Azteca S.P .R. de R.L. CIMMYT ID DEPLOY PRODUCTORA DE SEMILLAS SMART SEEDS SAS DE CV CIMMYT ID DEPLOY Productora de Semillas Zarco S.P .R. de R.L. CIMMYT ID DEPLOY Productores de Semilla de Copandaro S.P .R. de R.L. CIMMYT ID DEPLOY Productos y Servicios Agrícolas S.P .R. de R.L. CIMMYT ID DEPLOY QualiBasic Seed Company (QBS) CIMMYT AB, ID\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%201%29%2D20250729%5F100141%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E76da6c8e%2D6234%2D41ff%2Dba2c%2Dc2068392ed82\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 4\nContent: nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 1\nContent: Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 2).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%202%29%2D20250729%5F150218%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E57e21346%2Dc6ca%2D4c63%2D8839%2D3e2a327c5116\nFile: 2025 Technical Reporting Information (Session 2).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 2)-20250729_150218-Meeting Recording 29 de julio de 2025, 1:02p.m. 47 min 36 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 3\nContent: at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and\n\n---\n\n[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2]\nLink: https://cgspace.cgiar.org/items/8acc660f-7305-4e4b-ab21-1c192611b017\nFile: CGI21-507032-PORB-Climate Action.pdf\nLocation: page 11 part 2\nContent: II) ICRISAT AOW02 Digital Advisories and Climate Risk Management $89,064 N-343001-GCAN INITIATIVE IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $1,321,123 N-601158-SPIR II IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $201,213 PJ-003953: APPUI A LA TRANSFORMATION ET A LA RESILIENCE DES SYSTEMES ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 3\nContent: business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 22 part 3\nContent: de Cajas Rurales de Ahorro y Crédito Comunidades de Oriente (CECRUCSO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organización para el Desarrollo del Corquin (ODECO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organismo Cristiano de Desarrollo Integral de Honduras (OCDIH) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW\n\n---\n\n[ID: pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_Inception Report 30-06-2025.pdf\nLocation: page 4 part 3\nContent: Frameworks for Climate Services PLACA Climate Action Platform for Agriculture in Latin America and the Caribbean / La Plataforma de Acción Climática en Agricultura de Latinoamérica y el Caribe PMU Program Management Unit PPU Portfolio Performance Unit PRMS Performance and Results Management System REMET Reducing Methane Emissions from Rice project ROI Return on investment S4I Scaling for Impact (Program) SA South Asia SB\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 2\nContent: de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation Globally (AOW05) High Level Output 5.4. Unique crop diversity under threat is safeguarded through the integration of in situ and ex situ conservation strategies 50,000 \"Revealing the Diversity of Barley Quality Traits through Synergies between On-farm Practices and Technological Innovations D-100735\" ICARDA Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 237,008 Long Term Partnership Agreement ICARDA Biodiversity\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 42 part 3\nContent: (INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID DEPLOY Institut National pour l'Etude et la Recherche Agronomiques (INERA) - RDC CIMMYT AB, ID DEPLOY Instituto de Investigação Agronómica (IIA) - Angola CIMMYT AB, ID DEPLOY Instituto de Investigación Agropecuaria de Panamá CIMMYT AB, ID STRATEGIZE/REFOCUS, PARTNER / TRANSFORM, OPTIMIZE / ACCELERATE, CREATE Invicta Agritech India Private Limited CIMMYT ID DEPLOY JAMSONI COMPANY LIMITED CIMMYT ID DEPLOY Jardins da Yoba CIMMYT ID\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 46 part 3\nContent: C.V. CIMMYT ID DEPLOY Semillas Barriga S.R.P . de R.L. CIMMYT ID DEPLOY Semillas Berentsen S.A. de C.V. CIMMYT ID DEPLOY Semillas Cinteotl S.P .R de R.L. CIMMYT ID DEPLOY Semillas Iyadilpro y Ya S.A. de C.V. CIMMYT ID DEPLOY SEMILLAS MEJORADAS S.A. CIMMYT ID DEPLOY Semillas Ocso S.P .R. de R.L. CIMMYT ID DEPLOY Semillas Proseso SA DE CV CIMMYT ID DEPLOY Semillas y Agroinsumos Golden S.P .R. de R.L. de C.V. CIMMYT ID DEPLOY Semillas PROSASOL S.P .R. de R.L.\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 22 part 4\nContent: to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación Regionalde Servicios Agropecuarios de Oriente (ARSAGRO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Cooperación para el Desarrollo Rural de Occidente-CDRO - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems CGI21-508007-PORB-Scaling for Impact.indd 22CGI21-508007-PORB-Scaling for Impact.indd 22 07/08/2025 13:2407/08/2025 13:24"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Use all the chunks that you receive. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: ¿Quién tiene la responsabilidad fiduciaria sobre los fondos de Ventanas 1 y 2 y qué debe garantizar?\n\nContext:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 2\nContent: el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 1\nContent: Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 1\nContent: CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 1\nContent: CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 10 part 2\nContent: - 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness\" 411,914 \"Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO\" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 \"Andean Crop Diversity for Climate Change P-1560-DGUL\" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 \"Youth, Citizen Science and E-commerce:\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 23 part 3\nContent: Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 45 part 3\nContent: Seed Ltd CIMMYT ID DEPLOY PROASE Productores Asociados de Semillas S.C. de R.L. de C.V. CIMMYT ID DEPLOY Productora de Semillas Azteca S.P .R. de R.L. CIMMYT ID DEPLOY PRODUCTORA DE SEMILLAS SMART SEEDS SAS DE CV CIMMYT ID DEPLOY Productora de Semillas Zarco S.P .R. de R.L. CIMMYT ID DEPLOY Productores de Semilla de Copandaro S.P .R. de R.L. CIMMYT ID DEPLOY Productos y Servicios Agrícolas S.P .R. de R.L. CIMMYT ID DEPLOY QualiBasic Seed Company (QBS) CIMMYT AB, ID\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%201%29%2D20250729%5F100141%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E76da6c8e%2D6234%2D41ff%2Dba2c%2Dc2068392ed82\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 1)-20250729_100141-Meeting Recording 29 de julio de 2025, 8:01a.m. 53 min 5 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 4\nContent: nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 1\nContent: Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 2).docx:u1-4]\nLink: https://cgiar.sharepoint.com/sites/InitiativeDesignTeams/_layouts/15/stream.aspx?id=%2Fsites%2FInitiativeDesignTeams%2FShared%20Documents%2FGeneral%2FC%2E%20Meeting%20Recordings%5FFeb%202022%20and%20beyond%2F2025%20Technical%20Reporting%20Information%20%28Session%202%29%2D20250729%5F150218%2DMeeting%20Recording%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E57e21346%2Dc6ca%2D4c63%2D8839%2D3e2a327c5116\nFile: 2025 Technical Reporting Information (Session 2).docx\nLocation: paragraph 1 to paragraph 4\nContent: 2025 Technical Reporting Information (Session 2)-20250729_150218-Meeting Recording 29 de julio de 2025, 1:02p.m. 47 min 36 s Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 3\nContent: at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and\n\n---\n\n[ID: pdf:CGI21-507032-PORB-Climate Action.pdf:p11pt2]\nLink: https://cgspace.cgiar.org/items/8acc660f-7305-4e4b-ab21-1c192611b017\nFile: CGI21-507032-PORB-Climate Action.pdf\nLocation: page 11 part 2\nContent: II) ICRISAT AOW02 Digital Advisories and Climate Risk Management $89,064 N-343001-GCAN INITIATIVE IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $1,321,123 N-601158-SPIR II IFPRI AOW01 Prioritization and Coordination of Climate Action, AOW05 Finance and Policy for Scaling Solutions $201,213 PJ-003953: APPUI A LA TRANSFORMATION ET A LA RESILIENCE DES SYSTEMES ALIMENTAIRES DE MADAGASCAR A TRAVERS LA RECHERCHE POUR LE DEVELOPPEMENT IITA AOW03 Locally-led Adaptation $82,949 PJ-004108: ACRESAL Technical Assistance\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 3\nContent: business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 22 part 3\nContent: de Cajas Rurales de Ahorro y Crédito Comunidades de Oriente (CECRUCSO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organización para el Desarrollo del Corquin (ODECO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Organismo Cristiano de Desarrollo Integral de Honduras (OCDIH) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW\n\n---\n\n[ID: pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action%2FClimate%20Action%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP06%20%2D%20Climate%20Action&amp;p=true&amp;ga=1\nFile: Climate Action_Inception Report 30-06-2025.pdf\nLocation: page 4 part 3\nContent: Frameworks for Climate Services PLACA Climate Action Platform for Agriculture in Latin America and the Caribbean / La Plataforma de Acción Climática en Agricultura de Latinoamérica y el Caribe PMU Program Management Unit PPU Portfolio Performance Unit PRMS Performance and Results Management System REMET Reducing Methane Emissions from Rice project ROI Return on investment S4I Scaling for Impact (Program) SA South Asia SB\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 2\nContent: de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation Globally (AOW05) High Level Output 5.4. Unique crop diversity under threat is safeguarded through the integration of in situ and ex situ conservation strategies 50,000 \"Revealing the Diversity of Barley Quality Traits through Synergies between On-farm Practices and Technological Innovations D-100735\" ICARDA Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 237,008 Long Term Partnership Agreement ICARDA Biodiversity\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p42pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 42 part 3\nContent: (INRAN) CIMMYT AB, ID DEPLOY Institut National de Recherché pour l’Agriculture, la Pêche et l’Environnement (INRAPE) - Comoros CIMMYT AB, ID DEPLOY Institut National pour l'Etude et la Recherche Agronomiques (INERA) - RDC CIMMYT AB, ID DEPLOY Instituto de Investigação Agronómica (IIA) - Angola CIMMYT AB, ID DEPLOY Instituto de Investigación Agropecuaria de Panamá CIMMYT AB, ID STRATEGIZE/REFOCUS, PARTNER / TRANSFORM, OPTIMIZE / ACCELERATE, CREATE Invicta Agritech India Private Limited CIMMYT ID DEPLOY JAMSONI COMPANY LIMITED CIMMYT ID DEPLOY Jardins da Yoba CIMMYT ID\n\n---\n\n[ID: pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p46pt3]\nLink: https://cgspace.cgiar.org/items/e5edf9cd-51b3-4b13-80dd-3bb21975fdcf\nFile: CGIAR_PORB_Breeding_Tomorrow.pdf\nLocation: page 46 part 3\nContent: C.V. CIMMYT ID DEPLOY Semillas Barriga S.R.P . de R.L. CIMMYT ID DEPLOY Semillas Berentsen S.A. de C.V. CIMMYT ID DEPLOY Semillas Cinteotl S.P .R de R.L. CIMMYT ID DEPLOY Semillas Iyadilpro y Ya S.A. de C.V. CIMMYT ID DEPLOY SEMILLAS MEJORADAS S.A. CIMMYT ID DEPLOY Semillas Ocso S.P .R. de R.L. CIMMYT ID DEPLOY Semillas Proseso SA DE CV CIMMYT ID DEPLOY Semillas y Agroinsumos Golden S.P .R. de R.L. de C.V. CIMMYT ID DEPLOY Semillas PROSASOL S.P .R. de R.L.\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 22 part 4\nContent: to Scale in Agrifood Systems Mancomunidad de Municipios del Parque Nacional Montaña de Celaque (MAPANCE) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación Regionalde Servicios Agropecuarios de Oriente (ARSAGRO) - Honduras CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Cooperación para el Desarrollo Rural de Occidente-CDRO - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems CGI21-508007-PORB-Scaling for Impact.indd 22CGI21-508007-PORB-Scaling for Impact.indd 22 07/08/2025 13:2407/08/2025 13:24"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: Who holds fiduciary responsibility over Window 1 and Window 2 Funds?\n\nContext:\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u19-22]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24\nContent: Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively: ensure that such Window 1 and Window 2 Funds are used exclusively for their intended purposes; ensure that such Window 1 and Window 2 Funds are administered, used and expended in accordance with the CGIAR System Charter, the CGIAR System Framework and the applicable Fund Use Agreements entered into by it, including by taking corrective action with respect to Window 1 and Window 2 Funds not used in accordance with the relevant Fund Use Agreement; and monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u16-19]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21\nContent: Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research. Disbursement to Centers. The System Organization may, from time to time, initiate disbursements of Window 1 and Window 2 Funds to a Center for approved CGIAR Programs. Disbursement to a Program Participant. Subject to paragraph 2.4 of the Standard Provisions, Centers receiving Window 1 and Window 2 Funds may make further disbursements of such funds to Program Participants for the relevant CGIAR Program under Subagreements. Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively:\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u181-184]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Return of Funds. Unexpended or Uncommitted Funding.' paragraph 198 to section 'Misused Fund' paragraph 202\nContent: Window 3 Funds. At the written direction of an individual Funder, the System Organization will require Centers to promptly return any portion of Window 3 Funds that are unexpended or uncommitted at the completion of the CGIAR Research for which it was provided (including approved extensions). Such returned funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding. Misused Fund Window 1 and Window 2 Funds. The System Organization and each Center will, respectively, refund any portion of Window 1 and Window 2 Funds not used in accordance with the applicable Fund Use Agreements, and such funds will be deposited to Window 1 of the Trust Fund. Window 3 Funds. Subject to paragraph 2.3.4 of these Standard Provisions, the System Organization will require Centers to refund any portion of Window 3 Funds not used in accordance with the applicable Fund Use Agreement, and such Funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u28-31]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 30 to section 'Window 3 Funds.' paragraph 33\nContent: ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements; monitor, evaluate as applicable, and provide quality assurance and financial and technical reporting for activities funded by Window 3 Funds in accordance with the relevant terms of these Standard Provisions; and if the Window 3 Funds are mapped to a CGIAR Program (i.e. provided for CGIAR Research activities that are aligned to the CGIAR Program's high-level outcomes and theory of change), continuously inform the System Organization and the project management unit of such CGIAR Program of the receipt of any Window 3 Funds and their use. The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u178-181]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Acknowledgement of Funders' paragraph 194 to section 'Return of Funds. Unexpended or Uncommitted Funding.' paragraph 198\nContent: appropriate, the corrective action undertaken to address the concern, which may include suspension of transfer of Window 1 and Window 2 Funds to the Center. Return of Funds. Unexpended or Uncommitted Funding. Window 1 and Window 2 Funds. The System Organization and each Center will, respectively, promptly return any portion of Window 1 and Window 2 Funds that is unexpended or uncommitted at the completion of a CGIAR Program or activities under the CGIAR Program for which it was provided (including approved extensions) or at the termination of a Financial Framework Agreement between the System Organization and a Center, unless decided otherwise by the System Council. Such returned funds will be deposited to Window 1 of the Trust Fund. Window 3 Funds. At the written direction of an individual Funder, the System Organization will require Centers to promptly return any portion of Window 3 Funds that are unexpended or uncommitted at the completion of the CGIAR Research for which it was provided (including approved extensions). Such returned funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u31-34]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 33 to section 'Window 3 Funds.' paragraph 36\nContent: The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds. The System Organization may, however: upon request of a Funder providing Window 3 Funds and acting through the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center; or in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u13-16]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 15 to section 'Use and administration of the Contributions' paragraph 18\nContent: In addition to the designation of contributions to the Trust Fund in accordance with the CGIAR Trustee Agreement and the Contribution Agreements or Arrangements, Funders may further designate Window 1 Funds and/or Window 2 Funds for specific purposes at the operational level subject to a decision of the System Council enabling such designations, and in accordance with a procedure for designation of funds at operational level, as may be adopted from time to time. Responsibilities over Window 1 and Window 2 Funds Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u22-25]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 24 to section 'Window 3 Funds.' paragraph 27\nContent: monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions. Window 3 Funds. Window 3 Funds are directed by Funders to individual Centers. Funders may designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u34-37]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 36 to section 'Window 3 Funds.' paragraph 39\nContent: in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center. Window 3 Side Agreements or Arrangements. Nothing in the Funding Agreements or Arrangements is intended to preclude Funders and Centers from entering into Window 3 Side Agreements or Arrangements in regard to the terms governing the administration and use of Window 3 Funds. Funders may choose to make a Contribution to a Center through Window 3 without entering into a Window 3 Side Agreement or Arrangement, provided that such Contribution is made without any additional conditions attached to it. Any Window 3 Side Agreement or Arrangement will be consistent with these Standard Provisions and substantially in the form of Schedule 1 (Form of Window 3 Side Agreement or Arrangement) attached to these Standard Provisions, as may be amended from time to time. Program Participants. In engaging a Program Participant with respect to Window 1, 2 and 3 Funds, Centers will incorporate in the relevant Subagreements, and cause, and monitor, compliance with the obligations set out in the Standard Provisions, including but not limited to those set out in paragraphs 2.5-2.6, 4-6, 7.2.2, 7.1.3, 7.3.2, 8.3, 8.4.4,\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u172-175]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Acknowledgement of Funders' paragraph 187 to section 'Acknowledgement of Funders' paragraph 191\nContent: Acknowledgement of Funders All communications products on CGIAR Research funded by Window 1, 2 and 3 Funds, whether online or in hard copy form (e.g., publications, press releases, newsletters, website stories, blogs, posters, etc.), must acknowledge support received from Funders in accordance with applicable CGIAR Policies and Procedures on branding and communication. Suspending Transfers of Funding from Window 1 and 2 Suspension by the System Organization. The System Organization may, at any time, suspend transfers of Window 1 and Window 2 Funds allocated to a specific Center by providing a written notice to the relevant Center: (a) if the System Organization has a credible concern that the Window 1, 2 and 3 Funds are not used in accordance with the applicable Fund Use Agreements, or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) in the event of non-compliance by the Center with any of its obligations under an applicable Fund Use Agreement.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u25-28]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 27 to section 'Window 3 Funds.' paragraph 30\nContent: designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization. Centers receiving Window 3 Funds are responsible for the use of such funds and will: ensure that Window 3 Funds are used exclusively for their intended purposes; ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements;\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u55-58]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Financial, Economic and Administrative Standards' paragraph 59 to section 'Financial, Economic and Administrative Standards' paragraph 62\nContent: Efficiency. The System Organization and each Center will, respectively: ensure that Window 1, 2 and 3 Funds are used with due regard to economy and efficiency, and that the highest standards of integrity in the administration of the funds are upheld; and ensure that Window 1, 2 and 3 Funds are used in accordance with applicable CGIAR Policies and Procedures on cost allocation, which set forth the principles of allowability, allocability, and reasonableness. Investment Income. The System Organization and each Center will, respectively, ensure that any investment income generated by the portions of the Window 1, 2 and 3 Funds they receive, including currency conversion gains, will be used for CGIAR Research or, if not needed for such purposes, returned to the Trustee for deposit into Window 1 to be made available for allocation by the System Council.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u46-49]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Cost Sharing Percentage' paragraph 49 to section 'Standard of care.' paragraph 53\nContent: Window 1, 2 and 3 Funds. Centers will not have any obligation to collect or otherwise pay the CSP on funds disbursed through Windows 1, 2 or 3. The Funders, the System Organization and the Centers recognize that the Trustee of the CGIAR Trust Fund will collect the CSP before such funds are disbursed from the Trust Fund. Requirements on the Use of Window 1, 2 and 3 Funds CGIAR Policies and Procedures. The System Organization and each Center will, respectively ensure that Window 1, 2 and 3 Funds are used in accordance with applicable CGIAR Policies and Procedures and the relevant entity's own policies and procedures. All CGIAR Policies and Procedures will be available on the System Organization's web site. Standard of care.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u184-189]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Misused Fund' paragraph 202 to section 'Inconsistency' paragraph 207\nContent: Window 3 Funds. Subject to paragraph 2.3.4 of these Standard Provisions, the System Organization will require Centers to refund any portion of Window 3 Funds not used in accordance with the applicable Fund Use Agreement, and such Funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding. Inconsistency In the event of any inconsistency between the Cover Pages and these Standard Provisions, these Standard Provisions will prevail. Amendments Amendments These Standard Provisions may only be amended by approval of the System Council subject to concurrence of the Integrated Partnership Board. The System Organization will promptly notify the Funders and Centers in writing of any such amendments to these Standard Provisions.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u175-178]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Acknowledgement of Funders' paragraph 191 to section 'Acknowledgement of Funders' paragraph 194\nContent: Suspension by the System Organization. The System Organization may, at any time, suspend transfers of Window 1 and Window 2 Funds allocated to a specific Center by providing a written notice to the relevant Center: (a) if the System Organization has a credible concern that the Window 1, 2 and 3 Funds are not used in accordance with the applicable Fund Use Agreements, or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) in the event of non-compliance by the Center with any of its obligations under an applicable Fund Use Agreement. Before taking such action under paragraph 13.1, the System Organization will notify the relevant Center in writing, and consult with the System Council as well as the relevant Center with a view to identify ways and means to manage the suspension and mitigate the impact on the implementation of CGIAR Research until such time that the suspension may be lifted. If such suspension is lifted by the System Organization, it will notify the relevant Center in writing. Request by a Funder. If a Funder has a credible concern: (a) that Window 1, 2 and 3 Funds are not used by a Center in accordance with the applicable Fund Use Agreement or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) of a non-compliance by a Center with any of its obligations under an applicable Fund Use Agreement, the Funder may request, through the System Council, the System Organization to review the specific concern and, as relevant, to take appropriate corrective action. The System Organization will report to the System Council on the outcome of the review and, as appropriate, the corrective action undertaken to address the concern, which may include suspension of transfer of Window 1 and Window 2 Funds to the Center.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u4-7]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Introductory Provisions' paragraph 5 to section 'Introductory Provisions' paragraph 8\nContent: the Financial Framework Agreement between the System Organization and each Center with respect to Window 1, 2 and 3 Funds; and any Window 3 Side Agreement or Arrangement between a Funder and a Center with respect to Window 3 Funds. Interpretation of the Standard Provisions. Unless the context requires otherwise, the terms of these Standard Provisions governing the roles and responsibilities: between Funders and the System Organization apply to each Funding Agreement or Arrangement between a Funder and the System Organization;\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u106-109]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Monitoring and Evaluations' paragraph 115 to section 'Monitoring' paragraph 118\nContent: Funders will manage their monitoring and evaluation requirements with respect to the CGIAR Portfolio, collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to conduct duplicative evaluations, provided that Funders providing Window 3 Funds may require supplemental monitoring and evaluations with respect to Window 3 Funds, the costs of which, including the internal costs to the System Organization or Center, would be paid by the requesting Funder. If an individual Funder wishes to request, on an exceptional basis, a review or evaluation of any activities financed with Window 1 and Window 2 Funds, such Funder will consult with a designated representative from the System Organization on the most appropriate scope and terms of reference of such review or evaluation. The designated representative will assist in arranging for such review or evaluation in accordance with the applicable CGIAR Policies and Procedures. The costs of any such review or evaluation, including the internal costs of the System Organization or Center with respect to such review or evaluation, will be paid by the requesting Funder. The System Organization and each Center will, respectively collaborate on any monitoring or evaluations conducted in connection with CGIAR Research activities funded with Window 1, 2 and 3 Funds. Monitoring\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u58-61]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Financial, Economic and Administrative Standards' paragraph 62 to section 'Financial, Economic and Administrative Standards' paragraph 65\nContent: Investment Income. The System Organization and each Center will, respectively, ensure that any investment income generated by the portions of the Window 1, 2 and 3 Funds they receive, including currency conversion gains, will be used for CGIAR Research or, if not needed for such purposes, returned to the Trustee for deposit into Window 1 to be made available for allocation by the System Council. Procurement. In the event that consultants are employed or services or goods are procured with Window 1, 2 and 3 Funds, the System Organization and each Center will, respectively, ensure that the employment and supervision of such consultants and the procurement of such services or goods will be the responsibility of each entity employing or contracting such consultants or carrying out such procurement and will be conducted in conformity with applicable CGIAR Policies and Procedures on procurement, in line with the following basic principles of equal treatment and non-discrimination on grounds of nationality, competition, predictability, transparency, verifiability, and proportionality. No taxation. The System Organization and each Center will, respectively, use best efforts, to the extent allowed by applicable agreements, such as those signed with host governments, and applicable laws, to ensure that the use of Window 1, 2 and 3 Funds will be free from any taxation or fees imposed under local laws. Insurance. The System Organization and each Center will, respectively, maintain insurance coverage sufficient to cover the activities, risks, and potential omissions of the activities funded by Window 1, 2 and 3 Funds in accordance with generally accepted industry standards and as required by law.\n\n---\n\n[ID: pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact%2FScaling%20for%20Impact%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact&amp;p=true&amp;ga=1\nFile: Scaling for Impact_Inception Report 30-06-2025.pdf\nLocation: page 24 part 4\nContent: the continuity of prior work that is less fit for purpose in the Program’s ToC. Windows 1, 2, 3 and bilateral funding: Approximately half of S4I’s 2025 funding is from Window 1, with the remainder from Window 2, including two $1.25 million designated W2 allocations specifically for AoWs 4 and 5. The PORB also reflects stronger alignment of Window 3 and bilateral funding with Program logic: in 2025, 47 mapped W3 and bilateral investments totaling $44.8 million support the Program ($0.42M, $26.47M, $1.55M, $15.37M, and $0.99M across AoWs 1 through 5, respectively), with 74% of these funds active in Africa, 19% in Asia, and 7% in Latin America. Engage and Empower (AoW 1): This AoW is allocated $2.98 million in W1/W2 funding and supported by $0.42 million in W3/bilaterals. It anchors S4I’s stakeholder demand intelligence 9 The section on AoW 4 in the PORB description highlights major inception period successes in leveraging Window 3 investments, with an anticipated, two-year bilateral investment in HLO 4.1 to transition TAAT into the Scaling Program that will support new work that was not part of the RIIs or NPS.\n\n---\n\n[ID: pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP03%20%2D%20Sustainable%20Animal%20and%20Aquatic%20Foods%2FSustainable%20Animal%20and%20Aquatic%20Foods%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP03%20%2D%20Sustainable%20Animal%20and%20Aquatic%20Foods&amp;p=true&amp;ga=1\nFile: Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf\nLocation: page 21 part 2\nContent: reducing producers' incomes and ability to invest in innovations; iv. Adverse national policy shifts regarding inclusion and equality; and v. Increased frequency of extreme climate events, which could undermine social progress and resilience. Please refer to the following link with the Program/Accelerator's full risk register. This link is open to ISDC colleagues and others will be granted access, on request. Category Risk Description Current Risk Level Target Risk Level Actions to Manage Risk Funding Reduced Window 1 &amp; 2 Funds Reduced Window 1 &amp; 2 funds caused by political changes from national governments which donate the bulk of CGIAR funds or other changes in donor priorities. This could result in outcome achievements failing to reach the"}]</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: ¿Quién tiene la responsabilidad fiduciaria sobre los fondos de Ventanas 1 y 2 y qué debe garantizar?\n\nContext:\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u19-22]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24\nContent: Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively: ensure that such Window 1 and Window 2 Funds are used exclusively for their intended purposes; ensure that such Window 1 and Window 2 Funds are administered, used and expended in accordance with the CGIAR System Charter, the CGIAR System Framework and the applicable Fund Use Agreements entered into by it, including by taking corrective action with respect to Window 1 and Window 2 Funds not used in accordance with the relevant Fund Use Agreement; and monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u16-19]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21\nContent: Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research. Disbursement to Centers. The System Organization may, from time to time, initiate disbursements of Window 1 and Window 2 Funds to a Center for approved CGIAR Programs. Disbursement to a Program Participant. Subject to paragraph 2.4 of the Standard Provisions, Centers receiving Window 1 and Window 2 Funds may make further disbursements of such funds to Program Participants for the relevant CGIAR Program under Subagreements. Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively:\n\n---\n\n[ID: pdf:CGI21-507033-PORB-Policy Innovations.pdf:p72pt2]\nLink: https://cgspace.cgiar.org/items/a88f8775-4ba9-41b6-9525-0d698d83cfb4\nFile: CGI21-507033-PORB-Policy Innovations.pdf\nLocation: page 72 part 2\nContent: of green bananas on her head.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u31-34]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 33 to section 'Window 3 Funds.' paragraph 36\nContent: The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds. The System Organization may, however: upon request of a Funder providing Window 3 Funds and acting through the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center; or in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 1\nContent: Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u28-31]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 30 to section 'Window 3 Funds.' paragraph 33\nContent: ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements; monitor, evaluate as applicable, and provide quality assurance and financial and technical reporting for activities funded by Window 3 Funds in accordance with the relevant terms of these Standard Provisions; and if the Window 3 Funds are mapped to a CGIAR Program (i.e. provided for CGIAR Research activities that are aligned to the CGIAR Program's high-level outcomes and theory of change), continuously inform the System Organization and the project management unit of such CGIAR Program of the receipt of any Window 3 Funds and their use. The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds.\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 1\nContent: CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 1\nContent: CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 2\nContent: el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p52pt1]\nLink: https://cgspace.cgiar.org/items/302ea600-c601-403e-8b29-e65bfa501e95\nFile: CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf\nLocation: page 52 part 1\nContent: A pig farmer in Tien Lu district, Hung\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 4\nContent: nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p15pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 15 part 4\nContent: HLOs\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 3\nContent: business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 10 part 2\nContent: - 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness\" 411,914 \"Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO\" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 \"Andean Crop Diversity for Climate Change P-1560-DGUL\" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 \"Youth, Citizen Science and E-commerce:\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u70-73]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Ethical Standards' paragraph 74 to section 'Conflicts of Interest.' paragraph 77\nContent: with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and (viii) respect for the evolving capacities of children with disabilities. Conflicts of Interest. The System Organization and each Center will, respectively, take all necessary precautions to avoid or manage any Conflicts of Interest in all matters related to Window 1, 2 and 3 Funds.\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p37pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 37 part 3\nContent: 2.2 Better designed emergency response in fragile settings - Government, humanitarian, and NGO actors use evidence and tools in fragile settings to guide emergency responses X X X X High-Level Outputs 2.1.1 Prevent - Guidance on anticipatory action and disaster risk reduction (DRR) for FCA food systems that showcase impacts and scalability. X X X X 180,781.00 2.2.2 Respond - Guidance to improve the effectiveness of humanitarian responses to benefit individuals and communities affected by ongoing conflict and crisis X X X X Total AoW 2 budget 180,781.00 Area of Work 3:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 1\nContent: Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p5pt1]\nLink: https://cgspace.cgiar.org/items/04bd63a9-1b58-4eb5-84f2-b54c8bde226e\nFile: Portfolio Narrative_2024.pdf\nLocation: page 5 part 1\nContent: Section 1: Connecting impact and insight: The 2024 CGIAR Portfolio Narrative 1. SGPs are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance, and fiduciary oversight. 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022–2024. 3. EiB II reported through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they provided a concise, high- level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the Technical Reports. The 2024 CGIAR Portfolio Narrative is a cornerstone of CGIAR’s Technical Reporting Arrangement. It offers a synthesis of Portfolio coherence, synergies, and collective progress across Initiatives, Impact Platforms, and Science Group Projects (SGPs)1, which represent approximately 40 percent of CGIAR’s Portfolio by dollar value. The report does not include Center-managed bilateral projects. As a key\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 31 part 2\nContent: protocols for data anonymization and access requests Implementation and oversight Data management responsibilities will be integrated into research staff roles with the ultimate responsibility being the\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 23 part 3\nContent: Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u163-166]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Limitation of Liabilities' paragraph 176 to section 'No Additional Obligations' paragraph 180\nContent: In providing funds under: Funding Agreements or Arrangements, or Window 3 Side Agreements or Arrangements, Funders do not accept any responsibility or liability towards any third parties including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund; and Financial Framework Agreements, the System Organization does not accept, any responsibility or liability towards any third parties, including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund. No Additional Obligations\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u67-70]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Ethical Standards' paragraph 71 to section 'Ethical Standards' paragraph 74\nContent: Electioneering. The System Organization and each Center will, respectively, ensure that Window 1, 2 and 3 Funds will not be used to influence the outcome of any specific public election or to directly or indirectly carry on any voter registration drive. Drug trafficking. The System Organization and each Center, respectively, confirms that they have no reasonable basis to suspect that Window 1, 2 and 3 Funds would be diverted in support of drug trafficking. Discrimination against people with disabilities. The System Organization and each Center will, respectively, agree not to discriminate against persons with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and\n\n---\n\n[ID: pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p29pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1\nFile: Food Frontiers and Security_MELIA Plan 30-06-2025.pdf\nLocation: page 29 part 3\nContent: in fragile settings Respond Policy change instance s and Quantity of new innovatio n uses identified Mozambi que Surveys and KII CASP 2024 2026 100,000 Evaluate UNHCR’s Sustainable Land Management and Environmental Rehabilitation Project in Bangladesh Adam Savelli (CIAT) I-OC 2.2 Better designed emergen cy response in fragile settings Respond Policy change instance s and Quantity of new innovatio n\n\n---\n\n[ID: pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p21pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1\nFile: Food Frontiers and Security_MELIA Plan 30-06-2025.pdf\nLocation: page 21 part 2\nContent: for the stud y End date for the stud y Study cost (USD) How related to past evaluations (SG or others) Gendered Labor Impacts of Herder-Related Violence in Nigeria Jeff Bloem (IFPRI) I-OC 2.2 Better designed emergen cy response in fragile settings Respond Policy change instance s and Quantity of new innovatio n uses identified Nigeria Household survey (panel) n/a 2024 2025 13,100 n/a Analyzing\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p6pt3]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 6 part 3\nContent: Evaluation Recommendations are addressed by management. These responses are designed to ensure that Evaluations inform decision-making, enhance organizational effectiveness, promote learning, and strengthen accountability. They include time-bound commitments from management to implement Evaluation Recommendations and are systematically followed up as outlined in the CGIAR Evaluation Policy, which identifies follow-up as a critical component of the evaluative process.5 Since the launch of formal tracking in CGIAR’s 2022 Technical Report, the systematic monitoring and reporting of Management Response Actions has continued to evolve. This 2024 report provides information on (9) Evaluations and one (1) Evaluability Assessment (EA) completed during 2021-24 – all of which are available on the updated Evaluation and Management Response Actions Tracker. These Evaluations generated a total of 319 Recommendations and sub-Recommendations, underscoring the organization’s commitment to learning and continuous improvement. Evaluation title Date completed Date of Management Response No. of Recs. and sub-Recs No. of Actions Max. completion date for Actions Links to Evaluation Reports and Management Responses 2021 Synthesis of Learning from a Decade of CGIAR Research Programs June 2021 June 2022 41 41 2024 • Synthesis of Learning • Management Response Evaluation of CGIAR Platform for Big Data in Agriculture December 2021 February 2022 43 36 2030 • Evaluation Report • Management Response Evaluation of CGIAR Excellence in Breeding Platform April 2022 May 2022 47 35 2024 • Evaluation Report • Management Response Study of the PRMS Project\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 3\nContent: at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p17pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 17 part 2\nContent: 2.1.1 Prevent - Guidance on anticipatory action and disaster risk reduction (DRR) for FCA food systems that showcase impacts and scalability. SP04 and SP078 will implement joint research on natural resources management and rangelands governance. Food Frontiers and Security SP04- Multifunctional Landscapes 2.2.2 Respond - Guidance to improve the effectiveness of humanitarian responses to benefit individuals and communities affected by ongoing conflict and crisis\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p6pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 6 part 4\nContent: 2022 41 41 2024 • Synthesis of Learning • Management Response Evaluation of CGIAR Platform for Big Data in Agriculture December 2021 February 2022 43 36 2030 • Evaluation Report • Management Response Evaluation of CGIAR Excellence in Breeding Platform April 2022 May 2022 47 35 2024 • Evaluation Report • Management Response Study of the PRMS Project Management Approaches and Fit-for-Purpose Information Products December 2022 December 2022 36 19 2024 • Advisory Report GENDER (Generating Evidence and New Directions for Equitable Results) Platform Evaluation December 2023 January 2024 22 21 2024 • Evaluation Report • Management Response CGIAR Genebank Platform Evaluation March 2024 March 2024 32 26 2027 • Evaluation Report • Management Response Evaluability Assessment Review of Four Regional Integrated Initiatives June 2024 June 2024 9 8 2026 • Evaluation Report • Management Response Genetic Innovation Science Group Evaluation August 2024 September 2024 42 28* 2030 • Evaluation Report • Management Response Resilient Agrifood Systems Science Group Evaluation August 2024 September 2024 26 22* 2027 • Evaluation Report • Management Response Systems Transformation Science Group Evaluation August 2024 September 2024 21 12* TBC • Evaluation Report • Management Response Total 319 248 Table 1. Evaluation details and associated Management Responses and Actions *The number of Management Response Actions for the Science Group Evaluations will likely change after Q2, 2025. May 2025 7 6 CGIAR Portfolio Practice Change (Type 3) Report\n\n---\n\n[ID: pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p10pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP12%20%2D%20Digital%20Transformation%2FDigital%20Transformation%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP12%20%2D%20Digital%20Transformation&amp;p=true&amp;ga=1\nFile: Digital Transformation_Inception Report 30-06-2025.pdf\nLocation: page 10 part 2\nContent: use cases respond to clear demand from both\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p40pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-98</t>
   </si>
 </sst>
 </file>
@@ -2041,7 +2524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2084,7 +2567,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2096,16 +2579,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2113,7 +2596,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -2125,16 +2608,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G3" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2142,7 +2625,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -2154,16 +2637,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H4" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I4" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2171,7 +2654,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -2183,16 +2666,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="I5" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2200,7 +2683,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -2212,16 +2695,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="I6" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2229,7 +2712,7 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -2241,16 +2724,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H7" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="I7" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2258,7 +2741,7 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -2270,16 +2753,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="H8" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I8" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2287,7 +2770,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -2299,16 +2782,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="H9" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="I9" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2316,7 +2799,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -2328,16 +2811,16 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="H10" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="I10" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2345,7 +2828,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -2357,16 +2840,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G11" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H11" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I11" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2374,7 +2857,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -2386,16 +2869,16 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H12" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I12" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2403,7 +2886,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -2415,16 +2898,16 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H13" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="I13" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2432,7 +2915,7 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -2444,16 +2927,16 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="I14" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2461,7 +2944,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -2473,16 +2956,16 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H15" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I15" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2490,7 +2973,7 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -2502,16 +2985,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I16" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2519,7 +3002,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -2531,16 +3014,16 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="I17" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2548,7 +3031,7 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -2560,16 +3043,16 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="I18" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2577,7 +3060,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -2589,16 +3072,16 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H19" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="I19" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2606,7 +3089,7 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -2618,16 +3101,16 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I20" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2635,7 +3118,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -2647,22 +3130,22 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I21" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="J21" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="K21" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2670,7 +3153,7 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -2682,22 +3165,22 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I22" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="J22" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="K22" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2705,7 +3188,7 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -2717,22 +3200,22 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H23" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I23" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="J23" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="K23" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2740,7 +3223,7 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -2752,22 +3235,22 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H24" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I24" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="J24" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="K24" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2775,7 +3258,7 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -2787,22 +3270,22 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="H25" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I25" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="J25" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="K25" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2810,7 +3293,7 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -2822,22 +3305,22 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I26" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="J26" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2845,7 +3328,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -2857,22 +3340,22 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H27" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="I27" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="J27" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2880,7 +3363,7 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -2892,22 +3375,22 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G28" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H28" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I28" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="J28" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="K28" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2915,7 +3398,7 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -2927,22 +3410,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G29" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="I29" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="J29" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="K29" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2950,7 +3433,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -2962,22 +3445,22 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H30" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="I30" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="J30" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="K30" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2985,7 +3468,7 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -2997,22 +3480,22 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G31" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H31" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I31" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="J31" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="K31" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3020,7 +3503,7 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -3032,22 +3515,22 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H32" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="I32" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="J32" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="K32" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3055,7 +3538,7 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -3067,22 +3550,22 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G33" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H33" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="J33" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="K33" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3090,7 +3573,7 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -3102,22 +3585,22 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G34" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H34" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="J34" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="K34" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3125,7 +3608,7 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -3137,22 +3620,22 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G35" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H35" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="J35" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="K35" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3160,7 +3643,7 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -3172,22 +3655,22 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G36" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H36" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="J36" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="K36" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3195,7 +3678,7 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -3207,22 +3690,22 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H37" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="J37" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="K37" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3230,7 +3713,7 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -3242,22 +3725,22 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G38" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H38" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="J38" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="K38" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3265,7 +3748,7 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -3277,22 +3760,22 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G39" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H39" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I39" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J39" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="K39" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3300,7 +3783,7 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -3312,22 +3795,22 @@
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G40" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H40" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I40" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J40" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="K40" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3335,7 +3818,7 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -3347,22 +3830,22 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G41" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H41" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I41" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J41" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="K41" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3370,7 +3853,7 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -3382,22 +3865,22 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G42" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H42" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I42" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J42" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="K42" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3405,7 +3888,7 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -3417,22 +3900,22 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G43" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H43" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I43" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J43" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="K43" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3440,7 +3923,7 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -3452,22 +3935,22 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G44" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H44" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="I44" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J44" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="K44" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3484,13 +3967,13 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="K45" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -3498,7 +3981,7 @@
         <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -3510,22 +3993,22 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G46" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H46" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="I46" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J46" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="K46" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -3533,7 +4016,7 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C47">
         <v>100</v>
@@ -3545,22 +4028,22 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G47" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H47" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="I47" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J47" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="K47" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -3568,7 +4051,7 @@
         <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C48">
         <v>100</v>
@@ -3580,22 +4063,22 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G48" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H48" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="J48" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="K48" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -3603,7 +4086,7 @@
         <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -3615,22 +4098,22 @@
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H49" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="J49" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="K49" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -3638,7 +4121,7 @@
         <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -3650,22 +4133,22 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H50" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="J50" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="K50" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3673,7 +4156,7 @@
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -3685,22 +4168,22 @@
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H51" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="J51" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="K51" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3708,7 +4191,7 @@
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -3720,22 +4203,22 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G52" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H52" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="J52" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="K52" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -3743,7 +4226,7 @@
         <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -3755,22 +4238,22 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G53" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H53" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="J53" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="K53" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -3778,7 +4261,7 @@
         <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -3790,22 +4273,22 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G54" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H54" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="J54" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K54" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -3813,7 +4296,7 @@
         <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -3825,22 +4308,22 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H55" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="J55" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K55" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -3848,7 +4331,7 @@
         <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -3860,22 +4343,197 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G56" t="s">
+        <v>102</v>
+      </c>
+      <c r="H56" t="s">
+        <v>150</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J56" t="s">
+        <v>176</v>
+      </c>
+      <c r="K56" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" t="s">
+        <v>82</v>
+      </c>
+      <c r="C57">
+        <v>200</v>
+      </c>
+      <c r="D57">
+        <v>148</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>91</v>
+      </c>
+      <c r="G57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H57" t="s">
+        <v>151</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J57" t="s">
+        <v>180</v>
+      </c>
+      <c r="K57" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58">
+        <v>200</v>
+      </c>
+      <c r="D58">
+        <v>148</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>92</v>
+      </c>
+      <c r="G58" t="s">
+        <v>106</v>
+      </c>
+      <c r="H58" t="s">
+        <v>152</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J58" t="s">
+        <v>180</v>
+      </c>
+      <c r="K58" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59">
+        <v>200</v>
+      </c>
+      <c r="D59">
+        <v>148</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
         <v>93</v>
       </c>
-      <c r="H56" t="s">
-        <v>138</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J56" t="s">
-        <v>157</v>
-      </c>
-      <c r="K56" t="s">
-        <v>175</v>
+      <c r="G59" t="s">
+        <v>106</v>
+      </c>
+      <c r="H59" t="s">
+        <v>153</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J59" t="s">
+        <v>180</v>
+      </c>
+      <c r="K59" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60">
+        <v>200</v>
+      </c>
+      <c r="D60">
+        <v>200</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>91</v>
+      </c>
+      <c r="G60" t="s">
+        <v>107</v>
+      </c>
+      <c r="H60" t="s">
+        <v>154</v>
+      </c>
+      <c r="I60" t="s">
+        <v>169</v>
+      </c>
+      <c r="J60" t="s">
+        <v>181</v>
+      </c>
+      <c r="K60" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61">
+        <v>200</v>
+      </c>
+      <c r="D61">
+        <v>200</v>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>91</v>
+      </c>
+      <c r="G61" t="s">
+        <v>108</v>
+      </c>
+      <c r="H61" t="s">
+        <v>155</v>
+      </c>
+      <c r="I61" t="s">
+        <v>170</v>
+      </c>
+      <c r="J61" t="s">
+        <v>182</v>
+      </c>
+      <c r="K61" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -3895,6 +4553,9 @@
     <hyperlink ref="I54" r:id="rId13"/>
     <hyperlink ref="I55" r:id="rId14"/>
     <hyperlink ref="I56" r:id="rId15"/>
+    <hyperlink ref="I57" r:id="rId16"/>
+    <hyperlink ref="I58" r:id="rId17"/>
+    <hyperlink ref="I59" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Logs/interaction_log.xlsx
+++ b/Logs/interaction_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="210">
   <si>
     <t>timestamp</t>
   </si>
@@ -229,6 +229,9 @@
     <t>2025-09-25T00:45:44.397869</t>
   </si>
   <si>
+    <t>2025-09-25T01:18:56.051769</t>
+  </si>
+  <si>
     <t>What funding did 2024 Technical Reporting cover?</t>
   </si>
   <si>
@@ -266,6 +269,9 @@
   </si>
   <si>
     <t>Who holds fiduciary responsibility over Window 1 and Window 2 Funds?</t>
+  </si>
+  <si>
+    <t>Who has fiduciary responsibility over the Windows 1 and 2 funds, and what must they guarantee?</t>
   </si>
   <si>
     <t xml:space="preserve">You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:
@@ -346,6 +352,9 @@
   </si>
   <si>
     <t>docx:Standard Provisions 2026.docx:u19-22:0.155, docx:Standard Provisions 2026.docx:u16-19:0.145, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p72pt2:0.090, docx:Standard Provisions 2026.docx:u31-34:0.085, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1:0.078, docx:Standard Provisions 2026.docx:u28-31:0.078, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1:0.077, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1:0.075, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2:0.074, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p52pt1:0.069, pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4:0.067, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p15pt4:0.067, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3:0.066, pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2:0.064, docx:Standard Provisions 2026.docx:u70-73:0.063, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p37pt3:0.062, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1:0.061, pdf:Portfolio Narrative_2024.pdf:p5pt1:0.060, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.059, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3:0.057, docx:Standard Provisions 2026.docx:u163-166:0.057, docx:Standard Provisions 2026.docx:u67-70:0.056, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p29pt3:0.055, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p21pt2:0.053, pdf:Type3_2024Report.pdf:p6pt3:0.052, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3:0.052, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p17pt2:0.051, pdf:Type3_2024Report.pdf:p6pt4:0.051, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p10pt2:0.051, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p40pt3:0.051, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt3:0.049, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt4:0.048, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p29pt2:0.048, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p35pt2:0.047, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p17pt2:0.047, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p31pt2:0.047, pdf:Genebanks_Inception Report 30-06-2025.pdf:p38pt1:0.046, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p6pt1:0.045, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p6pt4:0.045, pdf:Type3_2024Report.pdf:p3pt2:0.045, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p49pt2:0.044, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p20pt2:0.044, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p50pt4:0.044, pdf:Climate Action_Inception Report 30-06-2025.pdf:p22pt2:0.043, pdf:Type3_2024Report.pdf:p6pt2:0.043, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p19pt4:0.043, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p28pt2:0.043, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p10pt1:0.043, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p1pt2:0.042, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt3:0.042, pdf:Type3_2024Report.pdf:p5pt1:0.042, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p20pt3:0.041, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p26pt3:0.041, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p31pt3:0.041, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt4:0.041, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt4:0.041, docx:User Roles and Rules for the PRMS Reporting.docx:u4-7:0.040, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p30pt4:0.040, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p13pt4:0.039, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p20pt4:0.039, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p22pt3:0.039, pdf:Portfolio Narrative_2024.pdf:p29pt3:0.039, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p10pt2:0.039, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p51pt1:0.039, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p6pt2:0.039, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p5pt2:0.039, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p29pt3:0.038, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p4pt4:0.038, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p45pt3:0.038, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt2:0.038, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p9pt2:0.038, pdf:Portfolio Narrative_2024.pdf:p82pt2:0.038, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt1:0.038, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p8pt3:0.038, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt3:0.038, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p30pt2:0.038, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p24pt1:0.037, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p6pt2:0.037, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt3:0.037, pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt2:0.037, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p16pt4:0.037, pdf:Portfolio Narrative_2024.pdf:p89pt4:0.037, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt4:0.037, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt4:0.037, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt4:0.037, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p30pt1:0.037, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt2:0.037, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p15pt2:0.036, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p4pt1:0.036, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p31pt4:0.036, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p29pt4:0.036, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p31pt2:0.036, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p22pt3:0.036, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p5pt3:0.036, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p8pt2:0.036, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p26pt4:0.035, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p31pt1:0.035, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p16pt1:0.035, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p46pt2:0.035, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p11pt4:0.035, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p12pt2:0.035, docx:Standard Provisions 2026.docx:u58-61:0.035, pdf:Portfolio Narrative_2024.pdf:p29pt4:0.035, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p17pt3:0.035, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p18pt4:0.034, pdf:CGIAR_ImpactReport_2022-24.pdf:p28pt1:0.034, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p26pt4:0.034, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p37pt4:0.034, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p26pt3:0.034, pdf:Genebanks_Inception Report 30-06-2025.pdf:p15pt2:0.034, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p11pt1:0.034, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p11pt2:0.034, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p29pt4:0.034, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p19pt1:0.034, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p7pt4:0.034, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p22pt4:0.034, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p1pt2:0.034, pdf:Climate Action_Inception Report 30-06-2025.pdf:p22pt3:0.034, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p18pt3:0.034, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p13pt2:0.034, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p36pt3:0.034, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p15pt4:0.034, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p17pt3:0.034, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p9pt4:0.034, pdf:Climate Action_Inception Report 30-06-2025.pdf:p17pt3:0.034, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p29pt1:0.034, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p9pt3:0.034, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p3pt2:0.034, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p19pt2:0.033, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p10pt4:0.033, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p5pt1:0.033, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p13pt2:0.033, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p31pt1:0.033, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p4pt4:0.033, pptx:Information Session on 2025 Technical Reporting.pptx:s8pt2:0.033, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p11pt2:0.033, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p12pt3:0.033, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p5pt2:0.033, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p22pt2:0.033, pdf:Portfolio Narrative_2024.pdf:p17pt1:0.033, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p15pt1:0.033, pdf:Climate Action_Inception Report 30-06-2025.pdf:p4pt3:0.033, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p35pt1:0.033, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p32pt2:0.033, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p33pt4:0.033, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p24pt4:0.033, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p3pt1:0.033, pdf:Portfolio Narrative_2024.pdf:p82pt3:0.033, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p13pt3:0.033, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p10pt2:0.033, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt4:0.033, pdf:Type3_2024Report.pdf:p7pt1:0.032, docx:User Roles and Rules for the PRMS Reporting.docx:u1-4:0.032, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p18pt1:0.032, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p7pt2:0.032, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p26pt1:0.032, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p56pt3:0.032, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p6pt1:0.032, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p27pt4:0.032, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p30pt4:0.032, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p32pt3:0.032, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p10pt2:0.032, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p5pt1:0.032, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p9pt2:0.032, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p21pt3:0.032, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt3:0.032, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p3pt3:0.032, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p18pt4:0.032, pdf:Type3_2024Report.pdf:p8pt3:0.032, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p17pt3:0.032, pdf:Portfolio Narrative_2024.pdf:p53pt4:0.032, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25pt3:0.032, pdf:Genebanks_Inception Report 30-06-2025.pdf:p17pt4:0.032, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p4pt2:0.032, docx:Standard Provisions 2026.docx:u73-76:0.032, pdf:Portfolio Narrative_2024.pdf:p38pt4:0.032, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p46pt3:0.032, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p53pt3:0.032, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p8pt1:0.032, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt2:0.032, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt1:0.031, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p22pt3:0.031, pdf:CGI21_508012_PORB_Genebanks.pdf:p2pt1:0.031, pdf:Type3_2024Report.pdf:p7pt4:0.031, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p26pt3:0.031, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p23pt2:0.031, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p7pt2:0.031, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p4pt4:0.031, pdf:Portfolio Narrative_2024.pdf:p47pt4:0.031, docx:Standard Provisions 2026.docx:u4-7:0.031, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p12pt3:0.031, pdf:Genebanks_Inception Report 30-06-2025.pdf:p35pt4:0.031, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p31pt3:0.031, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p40pt4:0.031, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p47pt4:0.031, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p14pt4:0.031, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p16pt2:0.031, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p13pt4:0.031, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p7pt1:0.031, pdf:Climate Action_Inception Report 30-06-2025.pdf:p19pt3:0.031</t>
+  </si>
+  <si>
+    <t>docx:Standard Provisions 2026.docx:u19-22:0.500, docx:Standard Provisions 2026.docx:u16-19:0.437, docx:Standard Provisions 2026.docx:u28-31:0.324, docx:Standard Provisions 2026.docx:u31-34:0.319, docx:Standard Provisions 2026.docx:u181-184:0.262, docx:Standard Provisions 2026.docx:u13-16:0.242, docx:Standard Provisions 2026.docx:u178-181:0.234, docx:Standard Provisions 2026.docx:u22-25:0.214, docx:Standard Provisions 2026.docx:u172-175:0.211, docx:Standard Provisions 2026.docx:u4-7:0.200, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.198, docx:Standard Provisions 2026.docx:u46-49:0.196, docx:Standard Provisions 2026.docx:u55-58:0.195, docx:Standard Provisions 2026.docx:u25-28:0.191, docx:Standard Provisions 2026.docx:u34-37:0.182, docx:Standard Provisions 2026.docx:u163-166:0.181, docx:Standard Provisions 2026.docx:u58-61:0.179, docx:Standard Provisions 2026.docx:u106-109:0.167, docx:Standard Provisions 2026.docx:u175-178:0.167, docx:Standard Provisions 2026.docx:u184-189:0.160, pdf:Portfolio Narrative_2024.pdf:p5pt1:0.159, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt1:0.157, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt4:0.156, docx:Standard Provisions 2026.docx:u67-70:0.155, docx:Standard Provisions 2026.docx:u157-160:0.154, docx:Standard Provisions 2026.docx:u43-46:0.148, docx:Standard Provisions 2026.docx:u70-73:0.147, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt2:0.146, docx:Standard Provisions 2026.docx:u160-163:0.140, docx:Standard Provisions 2026.docx:u10-13:0.139, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.136, pdf:Genebanks_Inception Report 30-06-2025.pdf:p21pt2:0.136, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p4pt4:0.134, docx:Standard Provisions 2026.docx:u112-115:0.133, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt3:0.132, docx:Standard Provisions 2026.docx:u103-106:0.132, docx:2025 Technical Reporting Information (Session 1).docx:u40-43:0.131, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt1:0.129, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p19pt2:0.129, docx:Standard Provisions 2026.docx:u52-55:0.128, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p4pt1:0.127, pdf:Climate Action_Inception Report 30-06-2025.pdf:p30pt2:0.125, docx:Standard Provisions 2026.docx:u109-112:0.125, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt3:0.124, docx:User Roles and Rules for the PRMS Reporting.docx:u1-4:0.123, docx:Standard Provisions 2026.docx:u73-76:0.121, docx:Standard Provisions 2026.docx:u64-67:0.121, pdf:Climate Action_Inception Report 30-06-2025.pdf:p30pt3:0.120, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p2pt2:0.118, docx:Standard Provisions 2026.docx:u37-40:0.118, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p12pt1:0.118, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p3pt2:0.118, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p4pt4:0.118, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p2pt2:0.118, docx:2025 Technical Reporting MELIA glossary.docx:u55-58:0.118, docx:Standard Provisions 2026.docx:u166-169:0.117, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p18pt1:0.117, pdf:Type3_2024Report.pdf:p5pt1:0.116, pdf:CGI21_508012_PORB_Genebanks.pdf:p2pt2:0.116, docx:Standard Provisions 2026.docx:u97-100:0.116, pdf:Genebanks_Inception Report 30-06-2025.pdf:p35pt4:0.116, pdf:CGI21-507032-PORB-Climate Action.pdf:p2pt2:0.115, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p2pt2:0.115, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p2pt2:0.115, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p37pt4:0.115, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p2pt2:0.115, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p2pt2:0.115, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p2pt2:0.115, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt2:0.114, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt3:0.113, docx:Standard Provisions 2026.docx:u1-4:0.112, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.112, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p37pt3:0.110, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p18pt4:0.110, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.110, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p32pt1:0.108, pdf:Climate Action_Inception Report 30-06-2025.pdf:p16pt3:0.107, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p26pt3:0.107, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p2pt1:0.107, docx:User Roles and Rules for the PRMS Reporting.docx:u4-7:0.106, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p49pt2:0.105, docx:Standard Provisions 2026.docx:u61-64:0.105, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p19pt3:0.104, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p17pt2:0.103, docx:2025 Technical Reporting Information (Session 2).docx:u4-7:0.103, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p30pt2:0.103, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p5pt1:0.103, docx:Standard Provisions 2026.docx:u76-79:0.103, docx:User Roles and Rules for the PRMS Reporting.docx:u16-19:0.102, pdf:CGI21_508012_PORB_Genebanks.pdf:p2pt1:0.102, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt3:0.102, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt4:0.101, pdf:Genebanks_Inception Report 30-06-2025.pdf:p18pt1:0.101, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p18pt3:0.100, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p8pt3:0.100, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p14pt4:0.100, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p6pt4:0.099, pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3:0.099, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p12pt4:0.099, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt4:0.098, docx:Standard Provisions 2026.docx:u100-103:0.097, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p25pt4:0.097, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt2:0.097, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p29pt2:0.097, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p4pt2:0.096, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p2pt1:0.096, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p5pt2:0.095, docx:Standard Provisions 2026.docx:u148-151:0.095, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p19pt1:0.095, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p3pt3:0.095, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p11pt4:0.095, pptx:Information Session on 2025 Technical Reporting.pptx:s8pt2:0.095, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p2pt1:0.095, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p2pt1:0.094, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p2pt1:0.094, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p8pt4:0.094, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p5pt1:0.094, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt4:0.094, docx:Standard Provisions 2026.docx:u133-136:0.094, docx:Standard Provisions 2026.docx:u130-133:0.093, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p15pt1:0.093, docx:Standard Provisions 2026.docx:u88-91:0.093, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p2pt1:0.093, pdf:CGI21-507032-PORB-Climate Action.pdf:p2pt1:0.093, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p2pt1:0.093, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p15pt1:0.093, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p24pt1:0.093, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p29pt3:0.093, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p13pt4:0.093, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p12pt3:0.093, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p32pt4:0.092, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p2pt1:0.092, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p12pt2:0.092, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p19pt2:0.092, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt2:0.092, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p16pt1:0.092, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p20pt4:0.092, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p14pt4:0.092, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p26pt1:0.091, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p19pt1:0.091, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p3pt3:0.091, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4:0.091, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.091, pptx:Engagement Plan 2025 Technical Reporting.pptx:s3pt3:0.091, pptx:Information Session on 2025 Technical Reporting.pptx:s12pt3:0.091, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt1:0.091, pdf:Portfolio Narrative_2024.pdf:p2pt4:0.091, docx:Standard Provisions 2026.docx:u151-154:0.090, pdf:Genebanks_Inception Report 30-06-2025.pdf:p35pt1:0.090, pdf:Genebanks_Inception Report 30-06-2025.pdf:p21pt1:0.090, docx:Guidance on reporting outputs or outcomes.docx:u10-13:0.090, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p15pt2:0.089, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p47pt4:0.089, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p7pt2:0.089, docx:Standard Provisions 2026.docx:u145-148:0.089, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p9pt2:0.089, pdf:Genebanks_Inception Report 30-06-2025.pdf:p21pt3:0.089, docx:Standard Provisions 2026.docx:u82-85:0.089, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p35pt3:0.088, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p22pt1:0.088, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt1:0.088, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt4:0.088, pdf:Portfolio Narrative_2024.pdf:p82pt2:0.088, docx:2025 Technical Reporting Information (Session 2).docx:u46-49:0.088, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p9pt2:0.088, pdf:Genebanks_Inception Report 30-06-2025.pdf:p9pt2:0.088, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p9pt3:0.088, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p2pt1:0.088, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p27pt2:0.088, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p35pt4:0.088, docx:2025 Technical Reporting Information (Session 2).docx:u25-28:0.088, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt2:0.087, docx:Standard Provisions 2026.docx:u94-97:0.087, pdf:Genebanks_Inception Report 30-06-2025.pdf:p24pt2:0.087, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4:0.087, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.087, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.087, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt3:0.087, docx:Standard Provisions 2026.docx:u169-172:0.086, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.086, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p32pt2:0.086, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p31pt2:0.086, pdf:Genebanks_Inception Report 30-06-2025.pdf:p8pt3:0.086, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p5pt2:0.086, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p23pt1:0.086, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p7pt2:0.086, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p25pt1:0.086, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p5pt2:0.085, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p25pt3:0.085, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p4pt2:0.085, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p40pt4:0.084, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p33pt4:0.084, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p27pt1:0.084, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p49pt3:0.084, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p31pt2:0.084, docx:Standard Provisions 2026.docx:u85-88:0.084, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p2pt1:0.084, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p2pt1:0.084, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt3:0.084, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p24pt4:0.084</t>
   </si>
   <si>
     <t>I cannot find information in the provided chunks to answer this.  
@@ -734,6 +743,13 @@
 Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21 — docx:Standard Provisions 2026.docx:u16-19</t>
   </si>
   <si>
+    <t>The fiduciary responsibility over the Window 1 and Window 2 funds lies with the System Organization, which is accountable to the Funders, while each Center has fiduciary responsibility toward the System Organization for the funds it receives. They must guarantee that these funds are used exclusively for their intended purposes and administered in accordance with the CGIAR System Charter, the CGIAR System Framework, and the applicable Fund Use Agreements. Additionally, they are required to monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by these windows. 
+Sources:
+File — Location — Cited IDs
+docx:Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24 — u19-22
+docx:Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21 — u16-19</t>
+  </si>
+  <si>
     <t>Information Session on 2025 Technical Reporting.pptx — slide 9 — pptx:Information Session on 2025 Technical Reporting.pptx:s9, Engagement Plan 2025 Technical Reporting.docx — paragraph 2 — docx:Engagement Plan 2025 Technical Reporting.docx:p2, Information Session on 2025 Technical Reporting.pptx — slide 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s2, Guidance on reporting outputs or outcomes.docx — paragraph 22 — docx:Guidance on reporting outputs or outcomes.docx:p22, Engagement Plan 2025 Technical Reporting.docx — section 'Technical Reporting questions' — docx:Engagement Plan 2025 Technical Reporting.docx:p59, CGIAR_ImpactReport_2022-24.pdf — page 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p1, Engagement Plan 2025 Technical Reporting.docx — section 'A single location for all documents and resources' — docx:Engagement Plan 2025 Technical Reporting.docx:p31, Engagement Plan 2025 Technical Reporting.pptx — slide 1 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s1, CGSpace.docx — section 'CGSpace' — docx:CGSpace.docx:p3, CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 5 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5</t>
   </si>
   <si>
@@ -777,6 +793,9 @@
   </si>
   <si>
     <t>Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24 — docx:Standard Provisions 2026.docx:u19-22, Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21 — docx:Standard Provisions 2026.docx:u16-19, https://cgspace.cgiar.org/items/a88f8775-4ba9-41b6-9525-0d698d83cfb4 — page 72 part 2 — pdf:CGI21-507033-PORB-Policy Innovations.pdf:p72pt2</t>
+  </si>
+  <si>
+    <t>Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24 — docx:Standard Provisions 2026.docx:u19-22, Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21 — docx:Standard Provisions 2026.docx:u16-19, Standard Provisions 2026.docx — section 'Window 3 Funds.' paragraph 30 to section 'Window 3 Funds.' paragraph 33 — docx:Standard Provisions 2026.docx:u28-31</t>
   </si>
   <si>
     <t>[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]
@@ -2096,6 +2115,100 @@
 evaluate the returns to R&amp;D investments in different regions and different crop and anima</t>
   </si>
   <si>
+    <t>[ID: docx:Standard Provisions 2026.docx:u19-22]
+Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively: ensure that such Window 1 and Window 2 Funds are used exclusively for their intended purposes; ensure that such Window 1 and Window 2 Funds are administered, used and expended in accordance with the CGIAR System Charter, the CGIAR System Framework and the applicable Fund Use Agreements entered into by it, including by taking corrective action with respect to Window 1 and Window 2 Funds not used in accordance with the relevant Fund Use Agreement; and monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions.
+---
+[ID: docx:Standard Provisions 2026.docx:u16-19]
+Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research. Disbursement to Centers. The System Organization may, from time to time, initiate disbursements of Window 1 and Window 2 Funds to a Center for approved CGIAR Programs. Disbursement to a Program Participant. Subject to paragraph 2.4 of the Standard Provisions, Centers receiving Window 1 and Window 2 Funds may make further disbursements of such funds to Program Participants for the relevant CGIAR Program under Subagreements. Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively:
+---
+[ID: docx:Standard Provisions 2026.docx:u28-31]
+ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements; monitor, evaluate as applicable, and provide quality assurance and financial and technical reporting for activities funded by Window 3 Funds in accordance with the relevant terms of these Standard Provisions; and if the Window 3 Funds are mapped to a CGIAR Program (i.e. provided for CGIAR Research activities that are aligned to the CGIAR Program's high-level outcomes and theory of change), continuously inform the System Organization and the project management unit of such CGIAR Program of the receipt of any Window 3 Funds and their use. The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds.
+---
+[ID: docx:Standard Provisions 2026.docx:u31-34]
+The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds. The System Organization may, however: upon request of a Funder providing Window 3 Funds and acting through the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center; or in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such
+---
+[ID: docx:Standard Provisions 2026.docx:u181-184]
+Window 3 Funds. At the written direction of an individual Funder, the System Organization will require Centers to promptly return any portion of Window 3 Funds that are unexpended or uncommitted at the completion of the CGIAR Research for which it was provided (including approved extensions). Such returned funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding. Misused Fund Window 1 and Window 2 Funds. The System Organization and each Center will, respectively, refund any portion of Window 1 and Window 2 Funds not used in accordance with the applicable Fund Use Agreements, and such funds will be deposited to Window 1 of the Trust Fund. Window 3 Funds. Subject to paragraph 2.3.4 of these Standard Provisions, the System Organization will require Centers to refund any portion of Window 3 Funds not used in accordance with the applicable Fund Use Agreement, and such Funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding.
+---
+[ID: docx:Standard Provisions 2026.docx:u13-16]
+In addition to the designation of contributions to the Trust Fund in accordance with the CGIAR Trustee Agreement and the Contribution Agreements or Arrangements, Funders may further designate Window 1 Funds and/or Window 2 Funds for specific purposes at the operational level subject to a decision of the System Council enabling such designations, and in accordance with a procedure for designation of funds at operational level, as may be adopted from time to time. Responsibilities over Window 1 and Window 2 Funds Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research.
+---
+[ID: docx:Standard Provisions 2026.docx:u178-181]
+appropriate, the corrective action undertaken to address the concern, which may include suspension of transfer of Window 1 and Window 2 Funds to the Center. Return of Funds. Unexpended or Uncommitted Funding. Window 1 and Window 2 Funds. The System Organization and each Center will, respectively, promptly return any portion of Window 1 and Window 2 Funds that is unexpended or uncommitted at the completion of a CGIAR Program or activities under the CGIAR Program for which it was provided (including approved extensions) or at the termination of a Financial Framework Agreement between the System Organization and a Center, unless decided otherwise by the System Council. Such returned funds will be deposited to Window 1 of the Trust Fund. Window 3 Funds. At the written direction of an individual Funder, the System Organization will require Centers to promptly return any portion of Window 3 Funds that are unexpended or uncommitted at the completion of the CGIAR Research for which it was provided (including approved extensions). Such returned funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding.
+---
+[ID: docx:Standard Provisions 2026.docx:u22-25]
+monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions. Window 3 Funds. Window 3 Funds are directed by Funders to individual Centers. Funders may designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization.
+---
+[ID: docx:Standard Provisions 2026.docx:u172-175]
+Acknowledgement of Funders All communications products on CGIAR Research funded by Window 1, 2 and 3 Funds, whether online or in hard copy form (e.g., publications, press releases, newsletters, website stories, blogs, posters, etc.), must acknowledge support received from Funders in accordance with applicable CGIAR Policies and Procedures on branding and communication. Suspending Transfers of Funding from Window 1 and 2 Suspension by the System Organization. The System Organization may, at any time, suspend transfers of Window 1 and Window 2 Funds allocated to a specific Center by providing a written notice to the relevant Center: (a) if the System Organization has a credible concern that the Window 1, 2 and 3 Funds are not used in accordance with the applicable Fund Use Agreements, or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) in the event of non-compliance by the Center with any of its obligations under an applicable Fund Use Agreement.
+---
+[ID: docx:Standard Provisions 2026.docx:u4-7]
+the Financial Framework Agreement between the System Organization and each Center with respect to Window 1, 2 and 3 Funds; and any Window 3 Side Agreement or Arrangement between a Funder and a Center with respect to Window 3 Funds. Interpretation of the Standard Provisions. Unless the context requires otherwise, the terms of these Standard Provisions governing the roles and responsibilities: between Funders and the System Organization apply to each Funding Agreement or Arrangement between a Funder and the System Organization;
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2]
+protocols for data anonymization and access requests Implementation and oversight Data management responsibilities will be integrated into research staff roles with the ultimate responsibility being the
+---
+[ID: docx:Standard Provisions 2026.docx:u46-49]
+Window 1, 2 and 3 Funds. Centers will not have any obligation to collect or otherwise pay the CSP on funds disbursed through Windows 1, 2 or 3. The Funders, the System Organization and the Centers recognize that the Trustee of the CGIAR Trust Fund will collect the CSP before such funds are disbursed from the Trust Fund. Requirements on the Use of Window 1, 2 and 3 Funds CGIAR Policies and Procedures. The System Organization and each Center will, respectively ensure that Window 1, 2 and 3 Funds are used in accordance with applicable CGIAR Policies and Procedures and the relevant entity's own policies and procedures. All CGIAR Policies and Procedures will be available on the System Organization's web site. Standard of care.
+---
+[ID: docx:Standard Provisions 2026.docx:u55-58]
+Efficiency. The System Organization and each Center will, respectively: ensure that Window 1, 2 and 3 Funds are used with due regard to economy and efficiency, and that the highest standards of integrity in the administration of the funds are upheld; and ensure that Window 1, 2 and 3 Funds are used in accordance with applicable CGIAR Policies and Procedures on cost allocation, which set forth the principles of allowability, allocability, and reasonableness. Investment Income. The System Organization and each Center will, respectively, ensure that any investment income generated by the portions of the Window 1, 2 and 3 Funds they receive, including currency conversion gains, will be used for CGIAR Research or, if not needed for such purposes, returned to the Trustee for deposit into Window 1 to be made available for allocation by the System Council.
+---
+[ID: docx:Standard Provisions 2026.docx:u25-28]
+designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization. Centers receiving Window 3 Funds are responsible for the use of such funds and will: ensure that Window 3 Funds are used exclusively for their intended purposes; ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements;
+---
+[ID: docx:Standard Provisions 2026.docx:u34-37]
+in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center. Window 3 Side Agreements or Arrangements. Nothing in the Funding Agreements or Arrangements is intended to preclude Funders and Centers from entering into Window 3 Side Agreements or Arrangements in regard to the terms governing the administration and use of Window 3 Funds. Funders may choose to make a Contribution to a Center through Window 3 without entering into a Window 3 Side Agreement or Arrangement, provided that such Contribution is made without any additional conditions attached to it. Any Window 3 Side Agreement or Arrangement will be consistent with these Standard Provisions and substantially in the form of Schedule 1 (Form of Window 3 Side Agreement or Arrangement) attached to these Standard Provisions, as may be amended from time to time. Program Participants. In engaging a Program Participant with respect to Window 1, 2 and 3 Funds, Centers will incorporate in the relevant Subagreements, and cause, and monitor, compliance with the obligations set out in the Standard Provisions, including but not limited to those set out in paragraphs 2.5-2.6, 4-6, 7.2.2, 7.1.3, 7.3.2, 8.3, 8.4.4,
+---
+[ID: docx:Standard Provisions 2026.docx:u163-166]
+In providing funds under: Funding Agreements or Arrangements, or Window 3 Side Agreements or Arrangements, Funders do not accept any responsibility or liability towards any third parties including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund; and Financial Framework Agreements, the System Organization does not accept, any responsibility or liability towards any third parties, including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund. No Additional Obligations
+---
+[ID: docx:Standard Provisions 2026.docx:u58-61]
+Investment Income. The System Organization and each Center will, respectively, ensure that any investment income generated by the portions of the Window 1, 2 and 3 Funds they receive, including currency conversion gains, will be used for CGIAR Research or, if not needed for such purposes, returned to the Trustee for deposit into Window 1 to be made available for allocation by the System Council. Procurement. In the event that consultants are employed or services or goods are procured with Window 1, 2 and 3 Funds, the System Organization and each Center will, respectively, ensure that the employment and supervision of such consultants and the procurement of such services or goods will be the responsibility of each entity employing or contracting such consultants or carrying out such procurement and will be conducted in conformity with applicable CGIAR Policies and Procedures on procurement, in line with the following basic principles of equal treatment and non-discrimination on grounds of nationality, competition, predictability, transparency, verifiability, and proportionality. No taxation. The System Organization and each Center will, respectively, use best efforts, to the extent allowed by applicable agreements, such as those signed with host governments, and applicable laws, to ensure that the use of Window 1, 2 and 3 Funds will be free from any taxation or fees imposed under local laws. Insurance. The System Organization and each Center will, respectively, maintain insurance coverage sufficient to cover the activities, risks, and potential omissions of the activities funded by Window 1, 2 and 3 Funds in accordance with generally accepted industry standards and as required by law.
+---
+[ID: docx:Standard Provisions 2026.docx:u106-109]
+Funders will manage their monitoring and evaluation requirements with respect to the CGIAR Portfolio, collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to conduct duplicative evaluations, provided that Funders providing Window 3 Funds may require supplemental monitoring and evaluations with respect to Window 3 Funds, the costs of which, including the internal costs to the System Organization or Center, would be paid by the requesting Funder. If an individual Funder wishes to request, on an exceptional basis, a review or evaluation of any activities financed with Window 1 and Window 2 Funds, such Funder will consult with a designated representative from the System Organization on the most appropriate scope and terms of reference of such review or evaluation. The designated representative will assist in arranging for such review or evaluation in accordance with the applicable CGIAR Policies and Procedures. The costs of any such review or evaluation, including the internal costs of the System Organization or Center with respect to such review or evaluation, will be paid by the requesting Funder. The System Organization and each Center will, respectively collaborate on any monitoring or evaluations conducted in connection with CGIAR Research activities funded with Window 1, 2 and 3 Funds. Monitoring
+---
+[ID: docx:Standard Provisions 2026.docx:u175-178]
+Suspension by the System Organization. The System Organization may, at any time, suspend transfers of Window 1 and Window 2 Funds allocated to a specific Center by providing a written notice to the relevant Center: (a) if the System Organization has a credible concern that the Window 1, 2 and 3 Funds are not used in accordance with the applicable Fund Use Agreements, or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) in the event of non-compliance by the Center with any of its obligations under an applicable Fund Use Agreement. Before taking such action under paragraph 13.1, the System Organization will notify the relevant Center in writing, and consult with the System Council as well as the relevant Center with a view to identify ways and means to manage the suspension and mitigate the impact on the implementation of CGIAR Research until such time that the suspension may be lifted. If such suspension is lifted by the System Organization, it will notify the relevant Center in writing. Request by a Funder. If a Funder has a credible concern: (a) that Window 1, 2 and 3 Funds are not used by a Center in accordance with the applicable Fund Use Agreement or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) of a non-compliance by a Center with any of its obligations under an applicable Fund Use Agreement, the Funder may request, through the System Council, the System Organization to review the specific concern and, as relevant, to take appropriate corrective action. The System Organization will report to the System Council on the outcome of the review and, as appropriate, the corrective action undertaken to address the concern, which may include suspension of transfer of Window 1 and Window 2 Funds to the Center.
+---
+[ID: docx:Standard Provisions 2026.docx:u184-189]
+Window 3 Funds. Subject to paragraph 2.3.4 of these Standard Provisions, the System Organization will require Centers to refund any portion of Window 3 Funds not used in accordance with the applicable Fund Use Agreement, and such Funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding. Inconsistency In the event of any inconsistency between the Cover Pages and these Standard Provisions, these Standard Provisions will prevail. Amendments Amendments These Standard Provisions may only be amended by approval of the System Council subject to concurrence of the Integrated Partnership Board. The System Organization will promptly notify the Funders and Centers in writing of any such amendments to these Standard Provisions.
+---
+[ID: pdf:Portfolio Narrative_2024.pdf:p5pt1]
+Section 1: Connecting impact and insight: The 2024 CGIAR Portfolio Narrative 1. SGPs are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance, and fiduciary oversight. 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022–2024. 3. EiB II reported through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they provided a concise, high- level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the Technical Reports. The 2024 CGIAR Portfolio Narrative is a cornerstone of CGIAR’s Technical Reporting Arrangement. It offers a synthesis of Portfolio coherence, synergies, and collective progress across Initiatives, Impact Platforms, and Science Group Projects (SGPs)1, which represent approximately 40 percent of CGIAR’s Portfolio by dollar value. The report does not include Center-managed bilateral projects. As a key
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt1]
+CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results
+---
+[ID: pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt4]
+the continuity of prior work that is less fit for purpose in the Program’s ToC. Windows 1, 2, 3 and bilateral funding: Approximately half of S4I’s 2025 funding is from Window 1, with the remainder from Window 2, including two $1.25 million designated W2 allocations specifically for AoWs 4 and 5. The PORB also reflects stronger alignment of Window 3 and bilateral funding with Program logic: in 2025, 47 mapped W3 and bilateral investments totaling $44.8 million support the Program ($0.42M, $26.47M, $1.55M, $15.37M, and $0.99M across AoWs 1 through 5, respectively), with 74% of these funds active in Africa, 19% in Asia, and 7% in Latin America. Engage and Empower (AoW 1): This AoW is allocated $2.98 million in W1/W2 funding and supported by $0.42 million in W3/bilaterals. It anchors S4I’s stakeholder demand intelligence 9 The section on AoW 4 in the PORB description highlights major inception period successes in leveraging Window 3 investments, with an anticipated, two-year bilateral investment in HLO 4.1 to transition TAAT into the Scaling Program that will support new work that was not part of the RIIs or NPS.
+---
+[ID: docx:Standard Provisions 2026.docx:u67-70]
+Electioneering. The System Organization and each Center will, respectively, ensure that Window 1, 2 and 3 Funds will not be used to influence the outcome of any specific public election or to directly or indirectly carry on any voter registration drive. Drug trafficking. The System Organization and each Center, respectively, confirms that they have no reasonable basis to suspect that Window 1, 2 and 3 Funds would be diverted in support of drug trafficking. Discrimination against people with disabilities. The System Organization and each Center will, respectively, agree not to discriminate against persons with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and
+---
+[ID: docx:Standard Provisions 2026.docx:u157-160]
+Change in Reporting Requirements. Unless decided otherwise by the System Council and/or the Integrated Partnership Board as the case may be, any change in the form or substance or periodicity of a technical or financial report will become effective only in the following calendar year. Additional Audits / Financial Reviews / Technical Reporting Funders will manage their audits, financial reviews and technical reporting with respect to the Window 1, 2 and 3 Funds collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to require duplicative reporting, provided that a Funder may require supplemental audits, financial reviews and technical reporting with respect to Window 3 Funds pursuant to its Window 3 Side Agreement or Arrangement, the costs of which would be paid by the requesting Funder. If a Funder wishes to request, on an exceptional basis, that the System Organization or a Center has an external audit or provides additional financial reviews or technical reports with respect to Window 1 and Window 2 Funds, and the requesting Funder has a statutory, regulatory or policy environment requiring such Funder's ability to make such a request unilaterally, such Funder will decide with the System Organization or the relevant Center on the most appropriate scope and terms of such audit, review or reporting. The costs of which, including the internal costs of the System Organization or any Center with respect to such additional audits, reviews or reporting, will be paid by the requesting Funder.
+---
+[ID: docx:Standard Provisions 2026.docx:u43-46]
+The Cost Sharing Percentage or CSP will be collected by the System Organization in accordance with applicable CGIAR Policies and Procedures on System Costs financing. Until and unless amended by CGIAR Policies and Procedures on System Costs financing, Centers will pay the CSP to the System Organization on any Bilateral Funding received for the implementation of CGIAR Research unless this requirement is exceptionally waived by the System Council. The System Organization will transfer the corresponding funds to the Trust Fund. Unless otherwise agreed by the System Council, if a Center does not pay any CSP which is due, the amount of such CSP which is due may be offset, after the Center has been adequately consulted, against Window 1 Funds that are otherwise to be disbursed to such Center. Window 1, 2 and 3 Funds. Centers will not have any obligation to collect or otherwise pay the CSP on funds disbursed through Windows 1, 2 or 3. The Funders, the System Organization and the Centers recognize that the Trustee of the CGIAR Trust Fund will collect the CSP before such funds are disbursed from the Trust Fund.
+---
+[ID: docx:Standard Provisions 2026.docx:u70-73]
+with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and (viii) respect for the evolving capacities of children with disabilities. Conflicts of Interest. The System Organization and each Center will, respectively, take all necessary precautions to avoid or manage any Conflicts of Interest in all matters related to Window 1, 2 and 3 Funds.
+---
+[ID: pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt2]
+reducing producers' incomes and ability to invest in innovations; iv. Adverse national policy shifts regarding inclusion and equality; and v. Increased frequency of extreme climate events, which could undermine social progress and resilience. Please refer to the following link with the Program/Accelerator's full risk register. This link is open to ISDC colleagues and others will be granted access, on request. Category Risk Description Current Risk Level Target Risk Level Actions to Manage Risk Funding Reduced Window 1 &amp; 2 Funds Reduced Window 1 &amp; 2 funds caused by political changes from national governments which donate the bulk of CGIAR funds or other changes in donor priorities. This could result in outcome achievements failing to reach the
+---
+[ID: docx:Standard Provisions 2026.docx:u160-163]
+If a Funder wishes to request, on an exceptional basis, that the System Organization or a Center has an external audit or provides additional financial reviews or technical reports with respect to Window 1 and Window 2 Funds, and the requesting Funder has a statutory, regulatory or policy environment requiring such Funder's ability to make such a request unilaterally, such Funder will decide with the System Organization or the relevant Center on the most appropriate scope and terms of such audit, review or reporting. The costs of which, including the internal costs of the System Organization or any Center with respect to such additional audits, reviews or reporting, will be paid by the requesting Funder. The System Organization and each Center will, respectively, collaborate on any audits, financial reviews or technical reporting conducted in connection with CGIAR Research activities. Limitation of Liabilities In providing funds under:
+---
+[ID: docx:Standard Provisions 2026.docx:u10-13]
+Use and administration of the Contributions General Provisions in Respect of the Contributions The Contributions, including the funds, assets and receipts thereof, held in the Trust Fund are administered in accordance with the terms of the CGIAR Trustee Agreement and each Contribution Agreement or Arrangement. In addition to the designation of contributions to the Trust Fund in accordance with the CGIAR Trustee Agreement and the Contribution Agreements or Arrangements, Funders may further designate Window 1 Funds and/or Window 2 Funds for specific purposes at the operational level subject to a decision of the System Council enabling such designations, and in accordance with a procedure for designation of funds at operational
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u31-34]
+Nirmal, Rajalakshmi (IFPRI) 36:04 But. Colomer, Julien (One CGIAR - France) 36:06 Yeah, yeah. Basically anything that's not finished or nailed down, I get to answer for. So and then I SO look, 2025 is a Transition year and. We everybody recognizes like the amount of pressure that everyone's under. So that final step of transferring over the, let's say, key Performance indicator or target output and target outcome values from the window three and bilaterals into the theory of chan</t>
+  </si>
+  <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: According to the Annex pie chart, what was total 2024 revenue and the split by funding source?\n\nContext:\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 6\nContent: Research results can be defined according to the nature of the change and the control over it.\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p14]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 14\nContent: Figure 1: Research results according to the kind of change and the control over it.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 23 Annex 2: ISDC feedback relating to pooled &amp; non-pooled alignment5 This section provides a direct extract from the ISDC Feedback on CGIAR Portfolio Narrative 2025- 2030. Comments relating to the alignment of pooled and non -pooled have been extracted from the broader set of comments. They have not been edited to e.g. update Program and Accelerator nomenclature. • Articulation of how the Portfolio, including bilateral and W1 funding, will be bundled into Megaprograms is still lacking. Bilateral funding is restricted and is provided for a specific purpose and with specific intended impacts. This needs to be honored a nd the lack of flexibility in shifting those funds into other areas should be clearly acknowledged. • Alignment of the entire Portfolio with the CGIAR 2030 Research and Innovation Strategy needs to be strong and explicit. How will management ensure that bilateral funding delivers against this Strategy? In addition: o What happens if a bilateral project is not strongly aligned with the Strategy and how will CGIAR ensure that opportunity costs are covered? o Will all bilateral projects across all Centers be mapped to support the Portfolio? • A challenge that should be acknowledged is incorporating bilateral funding into Megaprograms. Each Megaprogram and Accelerator will be large scale and staff will be consumed by the implementation of contracted work. Trying to build Megaprogram linkages in parallel with bilateral funding should be additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative 2025-2030\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p5]\nFile: Type3_2024Report.pdf\nLocation: page 5\nContent: Section 2: Portfolio Performance and Project Coordination Progress 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022-2024. 3. Science Group Projects (SGPs) are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance and fiduciary oversight. 4. EiB II will report through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they will provide a concise, high-level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the technical reports. 2.1. Technical Reporting Arrangement 2022-24 CGIAR Technical Reporting fulfils the System-level programmatic reporting requirements set out in the Standard Provisions annexed to the Funding Agreement or Arrangement signed between each Funder and the System Organization.2 The 2024 Technical Report includes the following Initiatives, Impact Platforms and SGPs3: • All 32 Initiatives • Five Impact Platforms – Gender Equality, Youth and Social Inclusion – Environmental Health and Biodiversity – Nutrition, Health and Food Security – Climate Adaptation and Mitigation – Poverty Reduction, Livelihoods and Jobs • Six SGPs – Accelerated Varietal Improvement and Seed Delivery of Legumes and dryland Cereals in Africa (AVISA) – Roots Tubers and Banana (RTB) Breeding – Accelerating Genetic Gain and Varietal Replacement in Rice - Phase 2 (AGGRi 2) – Excellence in Breeding (EiB) II: Cross-Crop Support Services for Breeding Acceleration4 – Accelerating Crop Improvement Through Genome Editing 2023-2025 – Climate Adaptation Insight For 2024, CGIAR will produce and deliver a total of 46 Technical Reporting outputs: • March 2025: Results from 2024 published on the online CGIAR Results Dashboard (1). • May 2025: Publication of 42 Type 1 (32 x Initiative reports; 5 x Impact Platform reports; 5 x SGP reports) Reports and a Type 3 Report (1). • End of June 2025: Publication of the Portfolio Narrative (1). • End of June 2025: Publication of the Type 2 Report: CGIAR Contributions to Impact in Agrifood Systems (2022-24) (1). Each of these reports is released separately and will be available in PDF format. 2024 Technical Reporting covers USD 370 million (USD 322 million for Initiatives and Impact Platforms, and USD 49 million for W3 SGPs), representing nearly 40 percent of CGIAR’s total pooled and non-pooled funding for 2024. 2.1.1. Streamlining the process and adding value to stakeholders In 2022 CGIAR launched a new 2022-24 Technical Reporting Arrangement, co-developed with the System Council’s Strategic Impact Monitoring and Evaluation Committee (SIMEC). The 2022 rollout was regarded as a “first pancake” or trial phase, establishing minimum viable functionality and setting the foundation for annual improvements. Key achievements of 2022 Technical Reporting included the adoption of a common report template aligned with the Technical Reporting Arrangement for Initiatives and Impact Platforms; integration with CGIAR’s Results Framework; digital linking of results to theories of change (TOCs); and the introduction of quality assurance processes mediated by third parties. Additionally, a new interactive CGIAR Results Dashboard was launched, and the Performance and Results Management System (PRMS) – an online reporting system – was developed, alongside adaptive management processes and the rollout of Innovation Packages and Scaling Readiness plans. Building on this, 2023 Technical Reporting incorporated lessons from a 2022 Learning and Optimization process, documented in a 2022 Learning and Optimization report. Key advancements included transitioning to “Always on” reporting by opening the PRMS from September 2023, more than doubling the reporting window compared to 2022 and allowing greater flexibility for Initiatives, Impact Platforms, and SGPs. Quality assurance was optimized through four staggered batches across 2023 and 2024. Further enhancements included expanding per-result tagging to all five Impact Areas. A Risk Management Module was launched to support risk identification and reporting at the Initiative level. A large number of participants joined training sessions to support reporting, dashboard use, and onboarding, and the rapid uptake of adaptive management strengthened strategic agility, with positive feedback from across the Portfolio. The Research Plans of Results and Budgets section of the CGIAR website was updated to ensure easy open access to Initiative, SGP and Impact Platform Plans of Results and Budgets (PORBs). The 2024 reporting cycle continued this trajectory, integrating insights from the 2023 Learning and Optimization process and Action Plan to further refine CGIAR’s Technical Reporting processes and products. Key improvements in 2024 included: • Launching the PRMS Planning Module to support the replan process: The launch of an online Planning Module synchronized TOC and Planning data in the PRMS, improving the efficiency and quality of planning workflows. Enhanced replan guidelines were provided to help Initiatives, Impact Platforms, and SGPs implement 2023 Reflect recommendations and align budget forecasts with updated budget envelopes. To support continuous learning and adaptive management, a user experience survey on the Planning Module was conducted to assess effectiveness and inform user-centered enhancements for the 2025-30 Portfolio. • Further simplifying reporting processes and tools: A series of enhancements to PRMS functionalities were implemented to improve efficiency and usability. Improved filtering options, enhanced notification systems, and more clearly structured result PDFs now enable quicker access to relevant information. Innovation Packages and Scaling Readiness language and templates were simplified. Reporting was streamlined and modified to suit the final year of reporting for the Portfolio, with an Outcome Indicator Module co-developed with input from Initiatives, Impact Platforms and SGPs to provide them with the opportunity to assess their progress against targets for Work Package outcomes and end-of-Initiative outcomes; summative and yearly highlights were combined into a single report; and adaptive management processes removed. • Improving decision-making within the PRMS: Broader engagement from PRMS testers across reporting entities and Senior Program Managers was integrated into PRMS feature development, ensuring that system updates were aligned with user needs and supported consistent decision-making. • Enhancing product clarity: The Type 1 Annual Report template was reviewed to better accommodate end-of-Initiative outcome reporting for the final year of the Portfolio. Improvements to the Results Dashboard were made to enhance the accessibility of IPSR insights. • Strengthening quality assurance: Examples include updated and enhanced QA guidance, and updated guidance on Impact Area tagging. An AI tool was prototyped and tested on a series of data fields, with the intent to leverage lessons learned and develop an enhanced AI tool that can be applied to a broader set of reported data and integrated into the PRMS, supporting both the reporting and QA phases. • Developing the Semantic Natural Language Processing Aggregator Platform (SNAP): SNAP is an AI-powered tool enhancing access to and analysis of CGIAR’s reported outputs, outcomes, and impacts. It improves access to Portfolio information and results evidence through semantic searches, thematic clustering, and automated summaries, complementing the CGIAR Results Dashboard. SNAP-supported narratives were integrated into the CGIAR 2024 Portfolio Narrative, and ongoing refinements will further enhance its role in Portfolio reporting. • Further integrating SGPs and Impact Platforms: Between 2022 and 2024, CGIAR progressively aligned these entities with its Technical Reporting processes and common systems to enhance consistency and coherence. In 2023, three Impact Platforms – Nutrition, Health and Food Security; Climate Adaptation and Mitigation; and Environmental Health and Biodiversity – were onboarded alongside the Gender Equality, Youth and Social Inclusion Impact Platform (which reported in 2022), each receiving tailored support such as TOC and results framework development. The SGP pilot launched in 2023 further expanded CGIAR’s reporting ecosystem by integrating Center-specific Window 3 awards, with two SGPs submitting first-year results using the PRMS Reporting Tool and Type 1 Report template. In 2024, integration expanded to include the Poverty Reduction, Livelihoods and Jobs Impact Platform and four additional SGPs, further broadening the reporting ecosystem. • Enhancing risk management through the PRMS Risk Module: The Risk Management Module, launched in 2023 to support Initiative management and reporting of risks, was further enhanced in 2024, allowing Initiatives to capture transition-focused risks. It enabled Initiatives to review, update, or close risks, contributing to the design of the 2025-30 Portfolio. The updated Risk Management Module will be used by Programs and Accelerators from 2025 onward. Climate-Smart Village set-up under the Adaptation and Mitigation Initiative in Agriculture (AMIA) of the Department of Agriculture. Credit: Miguel Mamon/CIAT May 2025 54 CGIAR Portfolio Practice Change (Type 3) Report 2024\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 4\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 4 1. Technical Reporting Arrangement purpose, scope, value proposition, delivery and optimization, Purpose The purpose of th e Technical Reporting Arrangement 2025 -2030 (“TRA 25-30”) is to set out the technical reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. The TRA 25-30: • Provides the parameters that e nable the Centers, the CGIAR System Partners and the System Organization to fulfil their technical reporting obligations under the funding agreements that apply to the use of Window 1 and Window 2 funds from the CGIAR Trust Fund (“Pooled Funding”). These parameters also allow the Integrated Partnership Board to fulfil its responsibility under the CGIAR System Charter to report on programmatic performance of CGIAR Research on an annual basis. • Provides, through the establishment of common technical reporting principles, enabling tools and mechanisms, progressive alignment and synergy between the technical reporting requirements that apply to components of the CGIAR Portfolio that are funded by Pooled Funding and those that apply to the components that are funded by other sources of funds (“Non-Pooled Funding”). • Sets transparency, performance tracking, and accountability expectations between CGIAR System Funders and CGIAR including Centres, • Informs decision making at different levels, underpins research management, operationalizes the Performance and Results Management Framework (PRMF), and guides portfolio -level MELIA and the design of the next Performance and Results management System (PRMS). The current Technical Reporting Arrangement that applies to the CGIAR Portfolio during the period 2022-24 (“TRA 22-24”) was co-developed by CGIAR and System Council/Strategic Impact Monitoring and Evaluation Committee (SIMEC) members in 2022. A new TRA is needed to match 2025-30 portfolio parameters, notably the alignment of pooled and non-pooled funding sources, and to apply lessons learnt from 2022-24. Scope The TRA 25-30 provides the operational and enabling basis to plan, monitor, learn and report on the 25-30 Portfolio. It is designed to progressively enable Programs and Accelerators, Centers and their research teams to report on the pooled, bilaterally and W3-funded components of the 2025- 30 portfolio in an integrated and aligned way, without increasing reporting burdens of Centers and Scientists. Going forward, the CGIAR Integrated Partnership will work towards progressively greater alignment of W3/bilateral projects and programs with the 2030 outcomes and theories of change of the Programs and Accelerators. Centers will provide key agreed information on their W3/bilaterally funded projects and programs to enable Program/Accelerator leaderships to explore ways to achieve alignment based on, inter alia, complementarity of results as well as actual or potential thematic, geographic, and partnership overlaps. Reporting on and attribution\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 5\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results framework, underpinned by a new Technical Reporting Arrangement, will provide robust, continuous performance and results reporting across all funding sources, as well as adaptive management of the Portfolio. 1 Value Proposition The TRA 25-30: - Creates value by delivering an integrated approach that tracks the performance of each Program and Accelerator, - Brings together the inputs (including costs), outputs, outcomes and impacts of the total portfolio to allow for easier and more robust Return on Investment (ROI) calculations. - Avoids creating a significant additional and duplicative layer of complex reporting requirements for W3/ bilaterally funded work. - Informs decision making through providing ready access to demand-driven quality raw and curated data products. Delivery The TRA 25 -30 will be delivered in line with Management arrangements for CGIAR’s 2025 —30 science and innovation Portfolio. Specific roles and responsibilities will be defined in 2025. 1 CGIAR Portfolio Narrative, 1 November 2024\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:p7]\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 7\nContent: Trifa, Nicoleta (CGIAR System Organization) 0:48 Yep. OK, good. So thank you. This session is the first of two session plans for today, planned for today, with the second being scheduled later at 3:00 PM CET to accommodate colleagues in other time zones. Technical reporting. My name is Nicoletta Trifa. By the way, I'm part of the Portfolio Performance Unit, the support unit within the Office of the Chief Scientist. Here is an overview of what we'll cover in the next minutes. I believe my presentation will take 2025 minutes and then we'll leave room for questions at the end, if that's OK. So what we'll cover an update of the technical reporting arrangements 2025 to 2030, priorities and changes for 2025, a brief introduction on the annual technical report and the neighbors. So this mean the performance and results. Management system and the quality assurance, the technical reporting timeline, available resources and support and what's next and how to stay engaged. I want to mention that this session marks the start of the conversation around 2025 technical reporting. We want to give you the early look at the key priorities and plans for the months ahead, and the goal is to make sure that you stay informed, prepared and supported with a clear understanding of upcoming deliverables and timelines. And also clarity on who to reach out to if you have questions or if you need help along the way. Good. Technical reporting arrangements for the new portfolio. The 2025 to 2030 portfolio has been approved by the CGR Global Leadership team on in June 2025 and provides the operational basis to plan, monitor, learn and report. On the new portfolio. It is designed to progressively enable programs, accelerators and centers to report on the pooled and window 3 bilateral projects of the new portfolio in an integrated and aligned way without increasing the burden on centers and the scientists. Main changes compared to the previous technical reporting arrangements, streamline reported reporting. So less products, more integration, lower transaction costs, stronger impact, focus results. To be clearly linked and packaged under impacts, outcomes and associated agreed indicator targets and better linkages between the theory of change or so plan of results and budget and technical reporting. The primary audiences for technical reporting are funders and CGR staff at integrated partnership, portfolio and program and accelerator levels. A secondary audience is the partners. Annual technical reporting covers the individual annual technical reports for program and accelerators, as well as a portfolio view of aggregate contribution to thematic and geographic targets. And relevant content from this technical reports are integrated into the CJR corporate reporting. In terms of the 2025 technical reporting priorities, 2025 is a transition year with technical reporting arrangements, implementation again focusing on streamlined reporting and on strengthening the linkages between theory of change. Porb, media and technical reporting. As many of you know, in the previous portfolio these components were not properly linked, so it was a bit challenging to demonstrate progress against the theory of change or the plans, as you know. In terms of deliverables for 2025. These are the program and accelerator technical reports, which are due in April 2026, the portfolio narrative, which is due in 2026 in June. Integration of top 80% of window tree and bilateral projects by central dollar value into reporting and planning. Application of the minimum data standards for window tree and bilateral reporting. And mapping of refinement during the pause and reflect process which will take place early Q 1/20/26. So as I was mentioning, this year is seen more as a transition year towards KPI based planning and reporting and efforts are underway to enable planning and reporting at the KPI level, which is aligned with the system office objective and key results for 2026 and 20. These are to be confirmed, so they haven't been confirmed yet, but I've pasted them here so that you can see the 2026 objective and key results for the system office. So 100% program and accelerate the work plans and budget. An annual technical report. Which provide for software enabled monitoring of erformance and results against smart Ki by center, ear and ooled funds invested. So next year, 80% of centres, CGR, window three and bilateral funded work by value included in 2025 technical reports and then the following year in 2027, this will increase to 90% of centres. Window 3 and bilateral funded work included in 2026 technical reports. The following slides, what I have, what I have included in the following slides, it's a brief introduction into. What is expected in terms of deliverables from programs and accelerators together with an overview of the performance and results management system and the QA. I realized that some in this call some of you are already familiar with the reporting arrangements from the previous portfolio. While for others this might be entirely new. So our goal is to bring everyone to the same level of understanding so that we can move forward with clarity and shared expectations for the 2025 technical reporting. OK, so technical reporting for program and accelerator. We'll focus on three key deliverables. So first is reporting results, the 2025 results in the Performance and Reporting Management system, PRMS. Each program accelerator and mapped window 3 project will report 2025 results in the system and we strongly encourage to report results that were planned and budgeted. So results which have been included in the reports. As the outdated technical reporting system will allow for tracking results against plans. Secondly is the quality assurance of reporting results. As you know, the results submitted go through the quality assessment process and we will share more details on this process in the timeline in an info session scheduled for later. Which we will schedule later in in September, October and the quality assess results will be available on the results dashboard. Inform the pause and reflect and will be included in the technical reports in the annual technical reports. A third deliverable for program and accelerators is drafting estimation of the 2025 Annual Technical Report. So each program and accelerator is responsible for drafting and internally validating quality assessing their 2025 Annual Technical Report. Before submitting it to the PPU, so to the perform portfolio performance unit. Again, guidance on this, the detailed process and validation process will be shared with you timely. Also to support this process, an AI generated V0 draft will be provided as a starting point. The annual technical reports. What are they? This the annual technical report. The the the aim is to make them short, so to 20 to 30 pages, concise and targeted. They provide assurance on annual program accelerator delivery against the boards, so plan of results and budget and progress on theory of change. They are based on quality assess results, the template guidance and as I mentioned and. AI V0 will be provided to all rogram and accelerator teams. Annual technical reports need to be submitted by each program and accelerator in March, April, so more details on this will follow and publication is intended to happen end of April, beginning of May. Here to the right side you have the. Content of the annual the proposed content for the annual technical report as per the technical reporting arrangements. Many of you will notice that there are not no big changes compared to previous portfolio, so the idea is to have a fact sheet and executive summary. The annual progress on theory of change, area of work details, a section on results, section on partnerships, portfolio linkages, adaptive management and then one key result story. But again, we will plan a detailed deep dive session on the annual technical report template and the guidance. So there will be time for you to ask questions in detail about about this and to receive support obviously. I've also included here for reference links to the 2024 Annual Technical Reports from the initiatives and impact platforms, and also a link to the 2024 Portfolio Narrative Report. In case you want to, you want to have a look to see, um, what it captures. PRMS. So this stands for Performance and Results Management System is the system the the the the environment where results need to be submitted. Again, the team is working on updating their resources. There will be. New users onboarding decks created with the links to different information and I I believe the PCU Alison together with the program coordinators. Are. The all the PRMS roles. So PCU is leading a work to define the PRMS roles and to get the information from program and accelerators regarding who from each program accelerator should have what role in PRMS. To enable us to to provide the right access to the platform when the time comes to report. Quality assurance process. So results submitted by program and accelerators in the PRMS will be quality assessed by a quality assessment team in February 2026. Your participation in this process is required. Guidance and resource resources will be provided and also an info session will be scheduled later this year. What is the QA? It is a process that aims to improve the quality of the reported data to provide consistency across the system, ensure reliability of reported results. Inform the learning process and improve the overall CGR accountability and transparency. Quality assess data informs the reflect process which takes place early Q12026, the results dashboard. So once the quality assessment of the results is finalized, the quality assess results will be pushed to results dashboard. You most probably have seen that. Reading. It also informs and are the results. The practices results are included in the annual report, in the portfolio narrative, and then in the overall CGIR annual report. In terms of the the timeline, so we have this info session now to provide an overview on the technical reporting and there will be several other info session and deep dive scheduled. Throughout September and October of reporting 2025 results, we believe that it will be feasible to open the PRMS in November for program and accelerators to to report. The date is still to be confirmed. We're aiming to to, yeah, to meet to to to end November. Hopefully this will be this is feasible from the technical side quality assurance. It's planned for February 2026 reflect process as I was mentioning Q 1/20/26 and then annual technical reports are due in March, April 2026 as well. Where to find information pertaining to technical reporting and planning and media? There is a one stop shop for for um all this. It's called the Performance and Results Hub. I'm gonna stop sharing cause I wanna share. Um, I'm gonna stop sharing the deck. I wanna. We could resent the hub. I'm not going to go through each section, but at least. So that you can see for those who are new more specifically to see and we will also share the link obviously the performance and results hub as I was mentioning it has detail on reporting, planning, reflect, replan. So you come in here, you click on 2025 reporting and then you will have access to the latest information, to the timeline, latest update, upcoming events. So all the information, information. Session dates will be listed here. We'll also have a subsection here with. Recording from from meetings, so that will be posted. For example today after this session we'll post a recording and the deck here for you to access and there is a section on frequently asked question. We recycled a couple of questions from the previous portfolio and updated them so that they are applicable to the program and accelerator teams, so feel free to go here and and browse. As resources become available, we will place them here and we will notify you by e-mail. OK. Going back to my deck. Which? In terms of engagement plan, so in order to streamline communication and optimize support for program accelerators and centers with mapped window 3 bilateral projects, we will send bi-weekly emails to everyone in this. This goal with key updates on technical reporting, with reminders and also with the latest questions and answers available on the hub. There will be targeted emails focusing on specific categories within the program accelerators. We want to engage with some of you on technical reporting, revisions, developments. And the aim is to gather feedback from you. Program coordinators will be copied on these emails. Info session. So a specific topic and we'll plan info session on specific topics, for example the standard indicator, description shades, the guidance on technical reporting, quality assurance. Reporting on innovations, the PRMS, so deep dive on the PRMS, the updates, the tool and so on. And during the reporting phase and the QA we will have weekly drop-ins. So this drop-ins is there will be no presentation. Presentation during the during this drop-ins. The purpose is for us to provide live support, so to answer your questions on the spot and the primary focus will be as I was mentioning, reporting and the QA. For if you know for every question you have, we invite you to use this e-mail address performanceandresults@cgr.org. This is the. The e-mail address we use for all technical reporting questions. So you have the questions right to us at performanceandresult@cjr.org and you will receive a response. We are aiming to respond within the 24 hours. Just to give an example, you know going back here I've gotten the targeted targeted emails and feedback. So this is a good example on for example how we plan to engage and get get feedback from from you on the PRMS enhancements so. Usually we send there's an e-mail sent to invite you to provide feedback on a o</t>
   </si>
   <si>
@@ -2154,6 +2267,9 @@
   </si>
   <si>
     <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: ¿Quién tiene la responsabilidad fiduciaria sobre los fondos de Ventanas 1 y 2 y qué debe garantizar?\n\nContext:\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u19-22]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24\nContent: Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively: ensure that such Window 1 and Window 2 Funds are used exclusively for their intended purposes; ensure that such Window 1 and Window 2 Funds are administered, used and expended in accordance with the CGIAR System Charter, the CGIAR System Framework and the applicable Fund Use Agreements entered into by it, including by taking corrective action with respect to Window 1 and Window 2 Funds not used in accordance with the relevant Fund Use Agreement; and monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u16-19]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21\nContent: Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research. Disbursement to Centers. The System Organization may, from time to time, initiate disbursements of Window 1 and Window 2 Funds to a Center for approved CGIAR Programs. Disbursement to a Program Participant. Subject to paragraph 2.4 of the Standard Provisions, Centers receiving Window 1 and Window 2 Funds may make further disbursements of such funds to Program Participants for the relevant CGIAR Program under Subagreements. Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively:\n\n---\n\n[ID: pdf:CGI21-507033-PORB-Policy Innovations.pdf:p72pt2]\nLink: https://cgspace.cgiar.org/items/a88f8775-4ba9-41b6-9525-0d698d83cfb4\nFile: CGI21-507033-PORB-Policy Innovations.pdf\nLocation: page 72 part 2\nContent: of green bananas on her head.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u31-34]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 33 to section 'Window 3 Funds.' paragraph 36\nContent: The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds. The System Organization may, however: upon request of a Funder providing Window 3 Funds and acting through the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center; or in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 1\nContent: Genebanks Accelerator Inception Report 21 ● GCDT-Long-term conservation and sustainable use of plant genetic resources (Alliance Bioversity - CIAT) ● 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales ● P-1560-DGUL-Andean Crop Diversity for Climate Change ● 1571-FAO0 - Youth, Citizen Science and E-commerce: scaling integrated conservation solutions and farmers’ rights by connecting key diversity hotspots: Bolivia, Chile, and Peru ● P-1530-GIZ0-Construction and implementation of a new Cryobank ● Conservation of ICRISAT genetic resources for food and nutrition security in the semi -arid tropics The following Genebanks projects were erroneously listed as belonging to other Science Programs/Accelerators: ● 1572-MIPO (CIP) Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP, a través de la Bioeconomía y los Alimentos Funcionales (Better Diets and Nutrition) ● P-1560-DGUL (CIP)-Andean Crop Diversity for Climate Change (Better Diets and Nutrition) ● Conservation of ICRISAT genetic resources for\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u28-31]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 30 to section 'Window 3 Funds.' paragraph 33\nContent: ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements; monitor, evaluate as applicable, and provide quality assurance and financial and technical reporting for activities funded by Window 3 Funds in accordance with the relevant terms of these Standard Provisions; and if the Window 3 Funds are mapped to a CGIAR Program (i.e. provided for CGIAR Research activities that are aligned to the CGIAR Program's high-level outcomes and theory of change), continuously inform the System Organization and the project management unit of such CGIAR Program of the receipt of any Window 3 Funds and their use. The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds.\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 1\nContent: CGIAR | July 2025 Plan of results and budget 2025 | W3 Mapping | Page 9 of 44 W3 Mapping W3/Bilateral project mapping to Food Frontiers and Security W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD 1572-MIPO Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p11pt1]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 11 part 1\nContent: CGIAR | August 2025 Plan of results and budget 2025 | W3 Mapping | Page 11 of 52 W3/Bilateral project mapping to P/As W3/Bilateral project name Center Area of Work Title and Number High level output or Outcome (If Available) Total AoW Proposed W3/Bilateral budget (Jan- Dec 2025), USD Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo- Puno CIP Strengthening Capacity for In Situ and Ex Situ Conservation\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p9pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 9 part 2\nContent: el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.4.4 Healthy diets - Innovations, adaptation of tools and assessments, and evidence generation to support interventions for improving diet quality for urban residents $84,231 P-1529-UNGP-Technical Assistance for Sweetpotato processing International Potato Center / Centro Internacional de la Papa Urban Food Systems - AOW3 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p52pt1]\nLink: https://cgspace.cgiar.org/items/302ea600-c601-403e-8b29-e65bfa501e95\nFile: CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf\nLocation: page 52 part 1\nContent: A pig farmer in Tien Lu district, Hung\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p22pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 22 part 4\nContent: nevertheless important for the core functions of the genebanks as well as to track relevant indicators associated with the Accelerator’s theory of change. • Long Term Partnership Grant for conservation of the rice biodiversity at AfricaRice genebank (AfricaRice) • Long Term Partnership Grant (CIP) • Fortalecimiento de la conservación y uso sostenible de variedades locales de raíces y tubérculos andinos libres de enfermedades en la Zona de Agrobiodiversidad Andenes de Cuyocuyo - Puno (CIP) • Long Term Partnership Agreement (ICARDA) • Providing for the long-term funding of ex situ collections of germplasm (Bioversity) • Long Term Partnership Grant (ICRISAT) • Defining new phynotypes for forage and crop residue improvement based on rumen function and greenhouse gas emissions (UK-CGIAR) Finally, there are projects which are crucial to the work of Genebanks but were either not assigned to a Science Program/Accelerator during the mapping exercise, or that have no budget assigned to the Genebanks but are still relevant in terms of work and objectives for the Genebanks team.\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p15pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 15 part 4\nContent: HLOs\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p24pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 24 part 3\nContent: business models for circular bioeconomy, integrating organic waste recycling and wastewater reuse for urban production United Nations High Commissioner for Refugees, Kanya Dairy Board, Global Alliance for Improved Nutrition, Food and Agriculture Organization of the United Nations, Work for Better Bangladesh Trust, Dhaka North City Corporation, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, Welthungerhilfe, Consortium for Health, Environment, and Development / Consorcio por la Salud, Ambiente y Desarrollo, Food and Nutrition Research Institute Philippines, Quezon City University, Local Government of Quezon City (Philippines), Kenya Dairy Board, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina International Livestock Research Institute 3.3.3 Informal food markets - Guidelines, innovations,\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p10pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 10 part 2\nContent: - 1.1. Crop Trust signs Long-Term Partnership Agreements with CGIAR Intermediate Outcome - 1.2. CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness\" 411,914 \"Impulsando la Agroindustria Rural y el Uso de la Diversidad del Yacón conservada en Pataz y CIP , a través de la Bioeconomía y los Alimentos Funcionales 1572-MIPO\" CIP Strategic User Engagement (AOW02) High Level Output 2.2. Enhanced germplasm information for more precise accession targeting 84,231 \"Andean Crop Diversity for Climate Change P-1560-DGUL\" CIP Strategic User Engagement (AOW02) High Level Ouput 2.2 Enhanced germplasm information for more precise accession targeting 674,036 \"Youth, Citizen Science and E-commerce:\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u70-73]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Ethical Standards' paragraph 74 to section 'Conflicts of Interest.' paragraph 77\nContent: with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and (viii) respect for the evolving capacities of children with disabilities. Conflicts of Interest. The System Organization and each Center will, respectively, take all necessary precautions to avoid or manage any Conflicts of Interest in all matters related to Window 1, 2 and 3 Funds.\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p37pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 37 part 3\nContent: 2.2 Better designed emergency response in fragile settings - Government, humanitarian, and NGO actors use evidence and tools in fragile settings to guide emergency responses X X X X High-Level Outputs 2.1.1 Prevent - Guidance on anticipatory action and disaster risk reduction (DRR) for FCA food systems that showcase impacts and scalability. X X X X 180,781.00 2.2.2 Respond - Guidance to improve the effectiveness of humanitarian responses to benefit individuals and communities affected by ongoing conflict and crisis X X X X Total AoW 2 budget 180,781.00 Area of Work 3:\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt1]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 1\nContent: Plan of results and budget 2025 | W3 Mapping | Page 22 of 44 July 2025 | CGIAR Partners (CRAs, sub-grant agreement, LoI, MoU ) Partner Center Area of Work Title and Number High level output (If Available) National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, RUAF Foundation, Alliance of Bioversity and CIAT - Headquarter (Bioversity International) International Potato Center / Centro Internacional de la Papa Future Food Systems Lab - AOW1 1.1.1 Envisioning Food System Futures - Tools and evidence for policymakers and partners to navigate emerging trends and future scenarios within relevant food systems. The\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p5pt1]\nLink: https://cgspace.cgiar.org/items/04bd63a9-1b58-4eb5-84f2-b54c8bde226e\nFile: Portfolio Narrative_2024.pdf\nLocation: page 5 part 1\nContent: Section 1: Connecting impact and insight: The 2024 CGIAR Portfolio Narrative 1. SGPs are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance, and fiduciary oversight. 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022–2024. 3. EiB II reported through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they provided a concise, high- level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the Technical Reports. The 2024 CGIAR Portfolio Narrative is a cornerstone of CGIAR’s Technical Reporting Arrangement. It offers a synthesis of Portfolio coherence, synergies, and collective progress across Initiatives, Impact Platforms, and Science Group Projects (SGPs)1, which represent approximately 40 percent of CGIAR’s Portfolio by dollar value. The report does not include Center-managed bilateral projects. As a key\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 31 part 2\nContent: protocols for data anonymization and access requests Implementation and oversight Data management responsibilities will be integrated into research staff roles with the ultimate responsibility being the\n\n---\n\n[ID: pdf:CGIAR_PORB_Scaling_4Impact.pdf:p23pt3]\nLink: https://cgspace.cgiar.org/items/a5c4b258-81b8-42ba-84d5-dad9f42e91dc\nFile: CGIAR_PORB_Scaling_4Impact.pdf\nLocation: page 23 part 3\nContent: Agrifood Systems Federación de Cafeteros del Valle - Colombia CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems Asociación de Desarrollo Integral de la parte alta de Zacapa (ADIPAZ) - Guatemala CIAT Contracted AoW 2 - Pathways to Scale in Agrifood Systems Universidad de San Carlos de Guatemala (USAC) - Guatemala CIAT Potential AoW 2 - Pathways to Scale in Agrifood Systems AoW 5 - Learning for Impact World Food Program - Guatemala CIAT Potential AoW 2\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u163-166]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Limitation of Liabilities' paragraph 176 to section 'No Additional Obligations' paragraph 180\nContent: In providing funds under: Funding Agreements or Arrangements, or Window 3 Side Agreements or Arrangements, Funders do not accept any responsibility or liability towards any third parties including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund; and Financial Framework Agreements, the System Organization does not accept, any responsibility or liability towards any third parties, including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund. No Additional Obligations\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u67-70]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Ethical Standards' paragraph 71 to section 'Ethical Standards' paragraph 74\nContent: Electioneering. The System Organization and each Center will, respectively, ensure that Window 1, 2 and 3 Funds will not be used to influence the outcome of any specific public election or to directly or indirectly carry on any voter registration drive. Drug trafficking. The System Organization and each Center, respectively, confirms that they have no reasonable basis to suspect that Window 1, 2 and 3 Funds would be diverted in support of drug trafficking. Discrimination against people with disabilities. The System Organization and each Center will, respectively, agree not to discriminate against persons with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and\n\n---\n\n[ID: pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p29pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1\nFile: Food Frontiers and Security_MELIA Plan 30-06-2025.pdf\nLocation: page 29 part 3\nContent: in fragile settings Respond Policy change instance s and Quantity of new innovatio n uses identified Mozambi que Surveys and KII CASP 2024 2026 100,000 Evaluate UNHCR’s Sustainable Land Management and Environmental Rehabilitation Project in Bangladesh Adam Savelli (CIAT) I-OC 2.2 Better designed emergen cy response in fragile settings Respond Policy change instance s and Quantity of new innovatio n\n\n---\n\n[ID: pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p21pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security%2FFood%20Frontiers%20and%20Security%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP08%20%2D%20Food%20Frontiers%20and%20Security&amp;p=true&amp;ga=1\nFile: Food Frontiers and Security_MELIA Plan 30-06-2025.pdf\nLocation: page 21 part 2\nContent: for the stud y End date for the stud y Study cost (USD) How related to past evaluations (SG or others) Gendered Labor Impacts of Herder-Related Violence in Nigeria Jeff Bloem (IFPRI) I-OC 2.2 Better designed emergen cy response in fragile settings Respond Policy change instance s and Quantity of new innovatio n uses identified Nigeria Household survey (panel) n/a 2024 2025 13,100 n/a Analyzing\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p6pt3]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 6 part 3\nContent: Evaluation Recommendations are addressed by management. These responses are designed to ensure that Evaluations inform decision-making, enhance organizational effectiveness, promote learning, and strengthen accountability. They include time-bound commitments from management to implement Evaluation Recommendations and are systematically followed up as outlined in the CGIAR Evaluation Policy, which identifies follow-up as a critical component of the evaluative process.5 Since the launch of formal tracking in CGIAR’s 2022 Technical Report, the systematic monitoring and reporting of Management Response Actions has continued to evolve. This 2024 report provides information on (9) Evaluations and one (1) Evaluability Assessment (EA) completed during 2021-24 – all of which are available on the updated Evaluation and Management Response Actions Tracker. These Evaluations generated a total of 319 Recommendations and sub-Recommendations, underscoring the organization’s commitment to learning and continuous improvement. Evaluation title Date completed Date of Management Response No. of Recs. and sub-Recs No. of Actions Max. completion date for Actions Links to Evaluation Reports and Management Responses 2021 Synthesis of Learning from a Decade of CGIAR Research Programs June 2021 June 2022 41 41 2024 • Synthesis of Learning • Management Response Evaluation of CGIAR Platform for Big Data in Agriculture December 2021 February 2022 43 36 2030 • Evaluation Report • Management Response Evaluation of CGIAR Excellence in Breeding Platform April 2022 May 2022 47 35 2024 • Evaluation Report • Management Response Study of the PRMS Project\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p22pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 22 part 3\nContent: at strengthening resilience in frontier geographies Council for Scientific and Industrial Research (Ghana), Welthungerhilfe, International Potato Center / Centro Internacional de la Papa, National Agrarian University La Molina/ Universidad Nacional Agraria La Molina, World Food Programme International Water Management Institute 1.3.3 Entrepreneurship Support Program - Technical and business training programs delivered to select number of innovators and entrepreneurs to develop and scale high-potential innovations for resource- constrained food systems GISSE, Mali, UNHCR, Red Cross Red Crescent Climate Centre, Nigerian Ministry of Humanitarian Affairs, ActionAid International, University of Bamako, International Organization for Migration, Government of Jordan, Alliance of Bioversity and\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p17pt2]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-9803-398b74cab543\nFile: CGI21-507031-PORB-Food Frontiers and Security.pdf\nLocation: page 17 part 2\nContent: 2.1.1 Prevent - Guidance on anticipatory action and disaster risk reduction (DRR) for FCA food systems that showcase impacts and scalability. SP04 and SP078 will implement joint research on natural resources management and rangelands governance. Food Frontiers and Security SP04- Multifunctional Landscapes 2.2.2 Respond - Guidance to improve the effectiveness of humanitarian responses to benefit individuals and communities affected by ongoing conflict and crisis\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p6pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 6 part 4\nContent: 2022 41 41 2024 • Synthesis of Learning • Management Response Evaluation of CGIAR Platform for Big Data in Agriculture December 2021 February 2022 43 36 2030 • Evaluation Report • Management Response Evaluation of CGIAR Excellence in Breeding Platform April 2022 May 2022 47 35 2024 • Evaluation Report • Management Response Study of the PRMS Project Management Approaches and Fit-for-Purpose Information Products December 2022 December 2022 36 19 2024 • Advisory Report GENDER (Generating Evidence and New Directions for Equitable Results) Platform Evaluation December 2023 January 2024 22 21 2024 • Evaluation Report • Management Response CGIAR Genebank Platform Evaluation March 2024 March 2024 32 26 2027 • Evaluation Report • Management Response Evaluability Assessment Review of Four Regional Integrated Initiatives June 2024 June 2024 9 8 2026 • Evaluation Report • Management Response Genetic Innovation Science Group Evaluation August 2024 September 2024 42 28* 2030 • Evaluation Report • Management Response Resilient Agrifood Systems Science Group Evaluation August 2024 September 2024 26 22* 2027 • Evaluation Report • Management Response Systems Transformation Science Group Evaluation August 2024 September 2024 21 12* TBC • Evaluation Report • Management Response Total 319 248 Table 1. Evaluation details and associated Management Responses and Actions *The number of Management Response Actions for the Science Group Evaluations will likely change after Q2, 2025. May 2025 7 6 CGIAR Portfolio Practice Change (Type 3) Report\n\n---\n\n[ID: pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p10pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP12%20%2D%20Digital%20Transformation%2FDigital%20Transformation%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP12%20%2D%20Digital%20Transformation&amp;p=true&amp;ga=1\nFile: Digital Transformation_Inception Report 30-06-2025.pdf\nLocation: page 10 part 2\nContent: use cases respond to clear demand from both\n\n---\n\n[ID: pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p40pt3]\nLink: https://cgspace.cgiar.org/items/3271720b-98a5-4bcb-98</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: Who has fiduciary responsibility over the Windows 1 and 2 funds, and what must they guarantee?\n\nContext:\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u19-22]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24\nContent: Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively: ensure that such Window 1 and Window 2 Funds are used exclusively for their intended purposes; ensure that such Window 1 and Window 2 Funds are administered, used and expended in accordance with the CGIAR System Charter, the CGIAR System Framework and the applicable Fund Use Agreements entered into by it, including by taking corrective action with respect to Window 1 and Window 2 Funds not used in accordance with the relevant Fund Use Agreement; and monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u16-19]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21\nContent: Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research. Disbursement to Centers. The System Organization may, from time to time, initiate disbursements of Window 1 and Window 2 Funds to a Center for approved CGIAR Programs. Disbursement to a Program Participant. Subject to paragraph 2.4 of the Standard Provisions, Centers receiving Window 1 and Window 2 Funds may make further disbursements of such funds to Program Participants for the relevant CGIAR Program under Subagreements. Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively:\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u28-31]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 30 to section 'Window 3 Funds.' paragraph 33\nContent: ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements; monitor, evaluate as applicable, and provide quality assurance and financial and technical reporting for activities funded by Window 3 Funds in accordance with the relevant terms of these Standard Provisions; and if the Window 3 Funds are mapped to a CGIAR Program (i.e. provided for CGIAR Research activities that are aligned to the CGIAR Program's high-level outcomes and theory of change), continuously inform the System Organization and the project management unit of such CGIAR Program of the receipt of any Window 3 Funds and their use. The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u31-34]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 33 to section 'Window 3 Funds.' paragraph 36\nContent: The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds. The System Organization may, however: upon request of a Funder providing Window 3 Funds and acting through the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center; or in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u181-184]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Return of Funds. Unexpended or Uncommitted Funding.' paragraph 198 to section 'Misused Fund' paragraph 202\nContent: Window 3 Funds. At the written direction of an individual Funder, the System Organization will require Centers to promptly return any portion of Window 3 Funds that are unexpended or uncommitted at the completion of the CGIAR Research for which it was provided (including approved extensions). Such returned funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding. Misused Fund Window 1 and Window 2 Funds. The System Organization and each Center will, respectively, refund any portion of Window 1 and Window 2 Funds not used in accordance with the applicable Fund Use Agreements, and such funds will be deposited to Window 1 of the Trust Fund. Window 3 Funds. Subject to paragraph 2.3.4 of these Standard Provisions, the System Organization will require Centers to refund any portion of Window 3 Funds not used in accordance with the applicable Fund Use Agreement, and such Funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u13-16]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 15 to section 'Use and administration of the Contributions' paragraph 18\nContent: In addition to the designation of contributions to the Trust Fund in accordance with the CGIAR Trustee Agreement and the Contribution Agreements or Arrangements, Funders may further designate Window 1 Funds and/or Window 2 Funds for specific purposes at the operational level subject to a decision of the System Council enabling such designations, and in accordance with a procedure for designation of funds at operational level, as may be adopted from time to time. Responsibilities over Window 1 and Window 2 Funds Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u178-181]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Acknowledgement of Funders' paragraph 194 to section 'Return of Funds. Unexpended or Uncommitted Funding.' paragraph 198\nContent: appropriate, the corrective action undertaken to address the concern, which may include suspension of transfer of Window 1 and Window 2 Funds to the Center. Return of Funds. Unexpended or Uncommitted Funding. Window 1 and Window 2 Funds. The System Organization and each Center will, respectively, promptly return any portion of Window 1 and Window 2 Funds that is unexpended or uncommitted at the completion of a CGIAR Program or activities under the CGIAR Program for which it was provided (including approved extensions) or at the termination of a Financial Framework Agreement between the System Organization and a Center, unless decided otherwise by the System Council. Such returned funds will be deposited to Window 1 of the Trust Fund. Window 3 Funds. At the written direction of an individual Funder, the System Organization will require Centers to promptly return any portion of Window 3 Funds that are unexpended or uncommitted at the completion of the CGIAR Research for which it was provided (including approved extensions). Such returned funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u22-25]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 24 to section 'Window 3 Funds.' paragraph 27\nContent: monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions. Window 3 Funds. Window 3 Funds are directed by Funders to individual Centers. Funders may designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u172-175]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Acknowledgement of Funders' paragraph 187 to section 'Acknowledgement of Funders' paragraph 191\nContent: Acknowledgement of Funders All communications products on CGIAR Research funded by Window 1, 2 and 3 Funds, whether online or in hard copy form (e.g., publications, press releases, newsletters, website stories, blogs, posters, etc.), must acknowledge support received from Funders in accordance with applicable CGIAR Policies and Procedures on branding and communication. Suspending Transfers of Funding from Window 1 and 2 Suspension by the System Organization. The System Organization may, at any time, suspend transfers of Window 1 and Window 2 Funds allocated to a specific Center by providing a written notice to the relevant Center: (a) if the System Organization has a credible concern that the Window 1, 2 and 3 Funds are not used in accordance with the applicable Fund Use Agreements, or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) in the event of non-compliance by the Center with any of its obligations under an applicable Fund Use Agreement.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u4-7]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Introductory Provisions' paragraph 5 to section 'Introductory Provisions' paragraph 8\nContent: the Financial Framework Agreement between the System Organization and each Center with respect to Window 1, 2 and 3 Funds; and any Window 3 Side Agreement or Arrangement between a Funder and a Center with respect to Window 3 Funds. Interpretation of the Standard Provisions. Unless the context requires otherwise, the terms of these Standard Provisions governing the roles and responsibilities: between Funders and the System Organization apply to each Funding Agreement or Arrangement between a Funder and the System Organization;\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 31 part 2\nContent: protocols for data anonymization and access requests Implementation and oversight Data management responsibilities will be integrated into research staff roles with the ultimate responsibility being the\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u46-49]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Cost Sharing Percentage' paragraph 49 to section 'Standard of care.' paragraph 53\nContent: Window 1, 2 and 3 Funds. Centers will not have any obligation to collect or otherwise pay the CSP on funds disbursed through Windows 1, 2 or 3. The Funders, the System Organization and the Centers recognize that the Trustee of the CGIAR Trust Fund will collect the CSP before such funds are disbursed from the Trust Fund. Requirements on the Use of Window 1, 2 and 3 Funds CGIAR Policies and Procedures. The System Organization and each Center will, respectively ensure that Window 1, 2 and 3 Funds are used in accordance with applicable CGIAR Policies and Procedures and the relevant entity's own policies and procedures. All CGIAR Policies and Procedures will be available on the System Organization's web site. Standard of care.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u55-58]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Financial, Economic and Administrative Standards' paragraph 59 to section 'Financial, Economic and Administrative Standards' paragraph 62\nContent: Efficiency. The System Organization and each Center will, respectively: ensure that Window 1, 2 and 3 Funds are used with due regard to economy and efficiency, and that the highest standards of integrity in the administration of the funds are upheld; and ensure that Window 1, 2 and 3 Funds are used in accordance with applicable CGIAR Policies and Procedures on cost allocation, which set forth the principles of allowability, allocability, and reasonableness. Investment Income. The System Organization and each Center will, respectively, ensure that any investment income generated by the portions of the Window 1, 2 and 3 Funds they receive, including currency conversion gains, will be used for CGIAR Research or, if not needed for such purposes, returned to the Trustee for deposit into Window 1 to be made available for allocation by the System Council.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u25-28]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 27 to section 'Window 3 Funds.' paragraph 30\nContent: designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization. Centers receiving Window 3 Funds are responsible for the use of such funds and will: ensure that Window 3 Funds are used exclusively for their intended purposes; ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements;\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u34-37]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 36 to section 'Window 3 Funds.' paragraph 39\nContent: in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center. Window 3 Side Agreements or Arrangements. Nothing in the Funding Agreements or Arrangements is intended to preclude Funders and Centers from entering into Window 3 Side Agreements or Arrangements in regard to the terms governing the administration and use of Window 3 Funds. Funders may choose to make a Contribution to a Center through Window 3 without entering into a Window 3 Side Agreement or Arrangement, provided that such Contribution is made without any additional conditions attached to it. Any Window 3 Side Agreement or Arrangement will be consistent with these Standard Provisions and substantially in the form of Schedule 1 (Form of Window 3 Side Agreement or Arrangement) attached to these Standard Provisions, as may be amended from time to time. Program Participants. In engaging a Program Participant with respect to Window 1, 2 and 3 Funds, Centers will incorporate in the relevant Subagreements, and cause, and monitor, compliance with the obligations set out in the Standard Provisions, including but not limited to those set out in paragraphs 2.5-2.6, 4-6, 7.2.2, 7.1.3, 7.3.2, 8.3, 8.4.4,\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u163-166]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Limitation of Liabilities' paragraph 176 to section 'No Additional Obligations' paragraph 180\nContent: In providing funds under: Funding Agreements or Arrangements, or Window 3 Side Agreements or Arrangements, Funders do not accept any responsibility or liability towards any third parties including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund; and Financial Framework Agreements, the System Organization does not accept, any responsibility or liability towards any third parties, including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund. No Additional Obligations\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u58-61]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Financial, Economic and Administrative Standards' paragraph 62 to section 'Financial, Economic and Administrative Standards' paragraph 65\nContent: Investment Income. The System Organization and each Center will, respectively, ensure that any investment income generated by the portions of the Window 1, 2 and 3 Funds they receive, including currency conversion gains, will be used for CGIAR Research or, if not needed for such purposes, returned to the Trustee for deposit into Window 1 to be made available for allocation by the System Council. Procurement. In the event that consultants are employed or services or goods are procured with Window 1, 2 and 3 Funds, the System Organization and each Center will, respectively, ensure that the employment and supervision of such consultants and the procurement of such services or goods will be the responsibility of each entity employing or contracting such consultants or carrying out such procurement and will be conducted in conformity with applicable CGIAR Policies and Procedures on procurement, in line with the following basic principles of equal treatment and non-discrimination on grounds of nationality, competition, predictability, transparency, verifiability, and proportionality. No taxation. The System Organization and each Center will, respectively, use best efforts, to the extent allowed by applicable agreements, such as those signed with host governments, and applicable laws, to ensure that the use of Window 1, 2 and 3 Funds will be free from any taxation or fees imposed under local laws. Insurance. The System Organization and each Center will, respectively, maintain insurance coverage sufficient to cover the activities, risks, and potential omissions of the activities funded by Window 1, 2 and 3 Funds in accordance with generally accepted industry standards and as required by law.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u106-109]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Monitoring and Evaluations' paragraph 115 to section 'Monitoring' paragraph 118\nContent: Funders will manage their monitoring and evaluation requirements with respect to the CGIAR Portfolio, collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to conduct duplicative evaluations, provided that Funders providing Window 3 Funds may require supplemental monitoring and evaluations with respect to Window 3 Funds, the costs of which, including the internal costs to the System Organization or Center, would be paid by the requesting Funder. If an individual Funder wishes to request, on an exceptional basis, a review or evaluation of any activities financed with Window 1 and Window 2 Funds, such Funder will consult with a designated representative from the System Organization on the most appropriate scope and terms of reference of such review or evaluation. The designated representative will assist in arranging for such review or evaluation in accordance with the applicable CGIAR Policies and Procedures. The costs of any such review or evaluation, including the internal costs of the System Organization or Center with respect to such review or evaluation, will be paid by the requesting Funder. The System Organization and each Center will, respectively collaborate on any monitoring or evaluations conducted in connection with CGIAR Research activities funded with Window 1, 2 and 3 Funds. Monitoring\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u175-178]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Acknowledgement of Funders' paragraph 191 to section 'Acknowledgement of Funders' paragraph 194\nContent: Suspension by the System Organization. The System Organization may, at any time, suspend transfers of Window 1 and Window 2 Funds allocated to a specific Center by providing a written notice to the relevant Center: (a) if the System Organization has a credible concern that the Window 1, 2 and 3 Funds are not used in accordance with the applicable Fund Use Agreements, or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) in the event of non-compliance by the Center with any of its obligations under an applicable Fund Use Agreement. Before taking such action under paragraph 13.1, the System Organization will notify the relevant Center in writing, and consult with the System Council as well as the relevant Center with a view to identify ways and means to manage the suspension and mitigate the impact on the implementation of CGIAR Research until such time that the suspension may be lifted. If such suspension is lifted by the System Organization, it will notify the relevant Center in writing. Request by a Funder. If a Funder has a credible concern: (a) that Window 1, 2 and 3 Funds are not used by a Center in accordance with the applicable Fund Use Agreement or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) of a non-compliance by a Center with any of its obligations under an applicable Fund Use Agreement, the Funder may request, through the System Council, the System Organization to review the specific concern and, as relevant, to take appropriate corrective action. The System Organization will report to the System Council on the outcome of the review and, as appropriate, the corrective action undertaken to address the concern, which may include suspension of transfer of Window 1 and Window 2 Funds to the Center.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u184-189]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Misused Fund' paragraph 202 to section 'Inconsistency' paragraph 207\nContent: Window 3 Funds. Subject to paragraph 2.3.4 of these Standard Provisions, the System Organization will require Centers to refund any portion of Window 3 Funds not used in accordance with the applicable Fund Use Agreement, and such Funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding. Inconsistency In the event of any inconsistency between the Cover Pages and these Standard Provisions, these Standard Provisions will prevail. Amendments Amendments These Standard Provisions may only be amended by approval of the System Council subject to concurrence of the Integrated Partnership Board. The System Organization will promptly notify the Funders and Centers in writing of any such amendments to these Standard Provisions.\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p5pt1]\nLink: https://cgspace.cgiar.org/items/04bd63a9-1b58-4eb5-84f2-b54c8bde226e\nFile: Portfolio Narrative_2024.pdf\nLocation: page 5 part 1\nContent: Section 1: Connecting impact and insight: The 2024 CGIAR Portfolio Narrative 1. SGPs are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance, and fiduciary oversight. 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022–2024. 3. EiB II reported through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they provided a concise, high- level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the Technical Reports. The 2024 CGIAR Portfolio Narrative is a cornerstone of CGIAR’s Technical Reporting Arrangement. It offers a synthesis of Portfolio coherence, synergies, and collective progress across Initiatives, Impact Platforms, and Science Group Projects (SGPs)1, which represent approximately 40 percent of CGIAR’s Portfolio by dollar value. The report does not include Center-managed bilateral projects. As a key\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 5 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results\n\n---\n\n[ID: pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact%2FScaling%20for%20Impact%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact&amp;p=true&amp;ga=1\nFile: Scaling for Impact_Inception Report 30-06-2025.pdf\nLocation: page 24 part 4\nContent: the continuity of prior work that is less fit for purpose in the Program’s ToC. Windows 1, 2, 3 and bilateral funding: Approximately half of S4I’s 2025 funding is from Window 1, with the remainder from Window 2, including two $1.25 million designated W2 allocations specifically for AoWs 4 and 5. The PORB also reflects stronger alignment of Window 3 and bilateral funding with Program logic: in 2025, 47 mapped W3 and bilateral investments totaling $44.8 million support the Program ($0.42M, $26.47M, $1.55M, $15.37M, and $0.99M across AoWs 1 through 5, respectively), with 74% of these funds active in Africa, 19% in Asia, and 7% in Latin America. Engage and Empower (AoW 1): This AoW is allocated $2.98 million in W1/W2 funding and supported by $0.42 million in W3/bilaterals. It anchors S4I’s stakeholder demand intelligence 9 The section on AoW 4 in the PORB description highlights major inception period successes in leveraging Window 3 investments, with an anticipated, two-year bilateral investment in HLO 4.1 to transition TAAT into the Scaling Program that will support new work that was not part of the RIIs or NPS.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u67-70]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Ethical Standards' paragraph 71 to section 'Ethical Standards' paragraph 74\nContent: Electioneering. The System Organization and each Center will, respectively, ensure that Window 1, 2 and 3 Funds will not be used to influence the outcome of any specific public election or to directly or indirectly carry on any voter registration drive. Drug trafficking. The System Organization and each Center, respectively, confirms that they have no reasonable basis to suspect that Window 1, 2 and 3 Funds would be diverted in support of drug trafficking. Discrimination against people with disabilities. The System Organization and each Center will, respectively, agree not to discriminate against persons with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u157-160]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Statement of Assurance' paragraph 169 to section 'Additional Audits / Financial Reviews / Technical Reporting' paragraph 172\nContent: Change in Reporting Requirements. Unless decided otherwise by the System Council and/or the Integrated Partnership Board as the case may be, any change in the form or substance or periodicity of a technical or financial report will become effective only in the following calendar year. Additional Audits / Financial Reviews / Technical Reporting Funders will manage their audits, financial reviews and technical reporting with respect to the Window 1, 2 and 3 Funds collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to require duplicative reporting, provided that a Funder may require supplemental audits, financial reviews and technical reporting with respect to Window 3 Funds pursuant to its Window 3 Side Agreement or Arrangement, the costs of which would be paid by the requesting Funder. If a Funder wishes to request, on an exceptional basis, that the System Organization or a Center has an external audit or provides additional financial reviews or technical reports wi</t>
   </si>
 </sst>
 </file>
@@ -2524,7 +2640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2567,7 +2683,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2579,16 +2695,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2596,7 +2712,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -2608,16 +2724,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2625,7 +2741,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -2637,16 +2753,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2654,7 +2770,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -2666,16 +2782,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2683,7 +2799,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -2695,16 +2811,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2712,7 +2828,7 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -2724,16 +2840,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2741,7 +2857,7 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -2753,16 +2869,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2770,7 +2886,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -2782,16 +2898,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I9" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2799,7 +2915,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -2811,16 +2927,16 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2828,7 +2944,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -2840,16 +2956,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2857,7 +2973,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -2869,16 +2985,16 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H12" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I12" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2886,7 +3002,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -2898,16 +3014,16 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I13" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2915,7 +3031,7 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -2927,16 +3043,16 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H14" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I14" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2944,7 +3060,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -2956,16 +3072,16 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I15" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2973,7 +3089,7 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -2985,16 +3101,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I16" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3002,7 +3118,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -3014,16 +3130,16 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I17" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3031,7 +3147,7 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -3043,16 +3159,16 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H18" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I18" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3060,7 +3176,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -3072,16 +3188,16 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3089,7 +3205,7 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -3101,16 +3217,16 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H20" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I20" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3118,7 +3234,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -3130,22 +3246,22 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H21" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I21" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J21" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K21" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3153,7 +3269,7 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -3165,22 +3281,22 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H22" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I22" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J22" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K22" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3188,7 +3304,7 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -3200,22 +3316,22 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H23" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I23" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J23" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K23" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3223,7 +3339,7 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -3235,22 +3351,22 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H24" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I24" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J24" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K24" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3258,7 +3374,7 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -3270,22 +3386,22 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H25" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I25" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J25" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K25" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -3293,7 +3409,7 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -3305,22 +3421,22 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H26" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I26" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J26" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K26" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3328,7 +3444,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -3340,22 +3456,22 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H27" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I27" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J27" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K27" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3363,7 +3479,7 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -3375,22 +3491,22 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H28" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I28" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J28" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K28" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3398,7 +3514,7 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -3410,22 +3526,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H29" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I29" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J29" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K29" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3433,7 +3549,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -3445,22 +3561,22 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H30" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I30" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J30" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K30" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3468,7 +3584,7 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -3480,22 +3596,22 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H31" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I31" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J31" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K31" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3503,7 +3619,7 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -3515,22 +3631,22 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H32" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I32" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J32" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K32" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3538,7 +3654,7 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -3550,22 +3666,22 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H33" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J33" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K33" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3573,7 +3689,7 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -3585,22 +3701,22 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G34" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H34" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J34" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K34" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3608,7 +3724,7 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -3620,22 +3736,22 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H35" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J35" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K35" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3643,7 +3759,7 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -3655,22 +3771,22 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G36" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J36" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K36" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3678,7 +3794,7 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -3690,22 +3806,22 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G37" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J37" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K37" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3713,7 +3829,7 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -3725,22 +3841,22 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J38" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K38" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3748,7 +3864,7 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -3760,22 +3876,22 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I39" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J39" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K39" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3783,7 +3899,7 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -3795,22 +3911,22 @@
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H40" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I40" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J40" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K40" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3818,7 +3934,7 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -3830,22 +3946,22 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H41" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I41" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J41" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K41" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3853,7 +3969,7 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -3865,22 +3981,22 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H42" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I42" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J42" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K42" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -3888,7 +4004,7 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -3900,22 +4016,22 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H43" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="I43" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J43" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K43" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -3923,7 +4039,7 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -3935,22 +4051,22 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G44" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H44" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I44" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J44" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K44" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -3967,13 +4083,13 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K45" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -3981,7 +4097,7 @@
         <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -3993,22 +4109,22 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H46" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I46" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J46" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K46" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -4016,7 +4132,7 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C47">
         <v>100</v>
@@ -4028,22 +4144,22 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H47" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I47" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J47" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K47" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -4051,7 +4167,7 @@
         <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C48">
         <v>100</v>
@@ -4063,22 +4179,22 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G48" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H48" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J48" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K48" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -4086,7 +4202,7 @@
         <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -4098,22 +4214,22 @@
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G49" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H49" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J49" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K49" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -4121,7 +4237,7 @@
         <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -4133,22 +4249,22 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G50" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H50" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J50" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="K50" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -4156,7 +4272,7 @@
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -4168,22 +4284,22 @@
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G51" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H51" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J51" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="K51" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4191,7 +4307,7 @@
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -4203,22 +4319,22 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H52" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J52" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="K52" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -4226,7 +4342,7 @@
         <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -4238,22 +4354,22 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G53" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H53" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J53" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K53" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4261,7 +4377,7 @@
         <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -4273,22 +4389,22 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G54" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H54" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J54" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="K54" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4296,7 +4412,7 @@
         <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -4308,22 +4424,22 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H55" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J55" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="K55" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -4331,7 +4447,7 @@
         <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -4343,22 +4459,22 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H56" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J56" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K56" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4366,7 +4482,7 @@
         <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -4378,22 +4494,22 @@
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H57" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J57" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K57" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -4401,7 +4517,7 @@
         <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -4413,22 +4529,22 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G58" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H58" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J58" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K58" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -4436,7 +4552,7 @@
         <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -4448,22 +4564,22 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G59" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H59" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J59" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K59" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -4471,7 +4587,7 @@
         <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -4483,22 +4599,22 @@
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G60" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H60" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I60" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J60" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K60" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4506,7 +4622,7 @@
         <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -4518,22 +4634,57 @@
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G61" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H61" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I61" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J61" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="K61" t="s">
-        <v>202</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62">
+        <v>200</v>
+      </c>
+      <c r="D62">
+        <v>200</v>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>93</v>
+      </c>
+      <c r="G62" t="s">
+        <v>111</v>
+      </c>
+      <c r="H62" t="s">
+        <v>159</v>
+      </c>
+      <c r="I62" t="s">
+        <v>175</v>
+      </c>
+      <c r="J62" t="s">
+        <v>188</v>
+      </c>
+      <c r="K62" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/Logs/interaction_log.xlsx
+++ b/Logs/interaction_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="237">
   <si>
     <t>timestamp</t>
   </si>
@@ -232,6 +232,21 @@
     <t>2025-09-25T01:18:56.051769</t>
   </si>
   <si>
+    <t>2025-09-26T08:47:03.579052</t>
+  </si>
+  <si>
+    <t>2025-09-26T08:54:14.961810</t>
+  </si>
+  <si>
+    <t>2025-09-26T08:56:28.255216</t>
+  </si>
+  <si>
+    <t>2025-09-26T09:00:09.362611</t>
+  </si>
+  <si>
+    <t>2025-09-26T09:07:14.972092</t>
+  </si>
+  <si>
     <t>What funding did 2024 Technical Reporting cover?</t>
   </si>
   <si>
@@ -272,6 +287,15 @@
   </si>
   <si>
     <t>Who has fiduciary responsibility over the Windows 1 and 2 funds, and what must they guarantee?</t>
+  </si>
+  <si>
+    <t>what is an outcome</t>
+  </si>
+  <si>
+    <t>what is an outcome?</t>
+  </si>
+  <si>
+    <t>what are the different types of outputs in the cgiar results framework?</t>
   </si>
   <si>
     <t xml:space="preserve">You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:
@@ -355,6 +379,18 @@
   </si>
   <si>
     <t>docx:Standard Provisions 2026.docx:u19-22:0.500, docx:Standard Provisions 2026.docx:u16-19:0.437, docx:Standard Provisions 2026.docx:u28-31:0.324, docx:Standard Provisions 2026.docx:u31-34:0.319, docx:Standard Provisions 2026.docx:u181-184:0.262, docx:Standard Provisions 2026.docx:u13-16:0.242, docx:Standard Provisions 2026.docx:u178-181:0.234, docx:Standard Provisions 2026.docx:u22-25:0.214, docx:Standard Provisions 2026.docx:u172-175:0.211, docx:Standard Provisions 2026.docx:u4-7:0.200, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.198, docx:Standard Provisions 2026.docx:u46-49:0.196, docx:Standard Provisions 2026.docx:u55-58:0.195, docx:Standard Provisions 2026.docx:u25-28:0.191, docx:Standard Provisions 2026.docx:u34-37:0.182, docx:Standard Provisions 2026.docx:u163-166:0.181, docx:Standard Provisions 2026.docx:u58-61:0.179, docx:Standard Provisions 2026.docx:u106-109:0.167, docx:Standard Provisions 2026.docx:u175-178:0.167, docx:Standard Provisions 2026.docx:u184-189:0.160, pdf:Portfolio Narrative_2024.pdf:p5pt1:0.159, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt1:0.157, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt4:0.156, docx:Standard Provisions 2026.docx:u67-70:0.155, docx:Standard Provisions 2026.docx:u157-160:0.154, docx:Standard Provisions 2026.docx:u43-46:0.148, docx:Standard Provisions 2026.docx:u70-73:0.147, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt2:0.146, docx:Standard Provisions 2026.docx:u160-163:0.140, docx:Standard Provisions 2026.docx:u10-13:0.139, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.136, pdf:Genebanks_Inception Report 30-06-2025.pdf:p21pt2:0.136, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p4pt4:0.134, docx:Standard Provisions 2026.docx:u112-115:0.133, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt3:0.132, docx:Standard Provisions 2026.docx:u103-106:0.132, docx:2025 Technical Reporting Information (Session 1).docx:u40-43:0.131, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt1:0.129, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p19pt2:0.129, docx:Standard Provisions 2026.docx:u52-55:0.128, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p4pt1:0.127, pdf:Climate Action_Inception Report 30-06-2025.pdf:p30pt2:0.125, docx:Standard Provisions 2026.docx:u109-112:0.125, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt3:0.124, docx:User Roles and Rules for the PRMS Reporting.docx:u1-4:0.123, docx:Standard Provisions 2026.docx:u73-76:0.121, docx:Standard Provisions 2026.docx:u64-67:0.121, pdf:Climate Action_Inception Report 30-06-2025.pdf:p30pt3:0.120, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p2pt2:0.118, docx:Standard Provisions 2026.docx:u37-40:0.118, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p12pt1:0.118, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p3pt2:0.118, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p4pt4:0.118, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p2pt2:0.118, docx:2025 Technical Reporting MELIA glossary.docx:u55-58:0.118, docx:Standard Provisions 2026.docx:u166-169:0.117, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p18pt1:0.117, pdf:Type3_2024Report.pdf:p5pt1:0.116, pdf:CGI21_508012_PORB_Genebanks.pdf:p2pt2:0.116, docx:Standard Provisions 2026.docx:u97-100:0.116, pdf:Genebanks_Inception Report 30-06-2025.pdf:p35pt4:0.116, pdf:CGI21-507032-PORB-Climate Action.pdf:p2pt2:0.115, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p2pt2:0.115, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p2pt2:0.115, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p37pt4:0.115, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p2pt2:0.115, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p2pt2:0.115, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p2pt2:0.115, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt2:0.114, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt3:0.113, docx:Standard Provisions 2026.docx:u1-4:0.112, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.112, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p37pt3:0.110, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p18pt4:0.110, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.110, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p32pt1:0.108, pdf:Climate Action_Inception Report 30-06-2025.pdf:p16pt3:0.107, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p26pt3:0.107, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p2pt1:0.107, docx:User Roles and Rules for the PRMS Reporting.docx:u4-7:0.106, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p49pt2:0.105, docx:Standard Provisions 2026.docx:u61-64:0.105, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p19pt3:0.104, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p17pt2:0.103, docx:2025 Technical Reporting Information (Session 2).docx:u4-7:0.103, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p30pt2:0.103, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p5pt1:0.103, docx:Standard Provisions 2026.docx:u76-79:0.103, docx:User Roles and Rules for the PRMS Reporting.docx:u16-19:0.102, pdf:CGI21_508012_PORB_Genebanks.pdf:p2pt1:0.102, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt3:0.102, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt4:0.101, pdf:Genebanks_Inception Report 30-06-2025.pdf:p18pt1:0.101, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p18pt3:0.100, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p8pt3:0.100, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p14pt4:0.100, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p6pt4:0.099, pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3:0.099, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p12pt4:0.099, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt4:0.098, docx:Standard Provisions 2026.docx:u100-103:0.097, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p25pt4:0.097, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p9pt2:0.097, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p29pt2:0.097, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p4pt2:0.096, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p2pt1:0.096, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p5pt2:0.095, docx:Standard Provisions 2026.docx:u148-151:0.095, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p19pt1:0.095, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p3pt3:0.095, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p11pt4:0.095, pptx:Information Session on 2025 Technical Reporting.pptx:s8pt2:0.095, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p2pt1:0.095, pdf:CGI21-508004-PORB-Digital Transformation.pdf:p2pt1:0.094, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p2pt1:0.094, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p8pt4:0.094, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p5pt1:0.094, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt4:0.094, docx:Standard Provisions 2026.docx:u133-136:0.094, docx:Standard Provisions 2026.docx:u130-133:0.093, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p15pt1:0.093, docx:Standard Provisions 2026.docx:u88-91:0.093, pdf:CGI21-508004-PORB-Capacity Sharing.pdf:p2pt1:0.093, pdf:CGI21-507032-PORB-Climate Action.pdf:p2pt1:0.093, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p2pt1:0.093, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p15pt1:0.093, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p24pt1:0.093, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p29pt3:0.093, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p13pt4:0.093, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p12pt3:0.093, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p32pt4:0.092, pdf:CGI21-507031-PORB-Food Frontiers and Security.pdf:p2pt1:0.092, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p12pt2:0.092, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p19pt2:0.092, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt2:0.092, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p16pt1:0.092, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p20pt4:0.092, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p14pt4:0.092, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p26pt1:0.091, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p19pt1:0.091, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p3pt3:0.091, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4:0.091, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.091, pptx:Engagement Plan 2025 Technical Reporting.pptx:s3pt3:0.091, pptx:Information Session on 2025 Technical Reporting.pptx:s12pt3:0.091, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p21pt1:0.091, pdf:Portfolio Narrative_2024.pdf:p2pt4:0.091, docx:Standard Provisions 2026.docx:u151-154:0.090, pdf:Genebanks_Inception Report 30-06-2025.pdf:p35pt1:0.090, pdf:Genebanks_Inception Report 30-06-2025.pdf:p21pt1:0.090, docx:Guidance on reporting outputs or outcomes.docx:u10-13:0.090, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p15pt2:0.089, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p47pt4:0.089, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p7pt2:0.089, docx:Standard Provisions 2026.docx:u145-148:0.089, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p9pt2:0.089, pdf:Genebanks_Inception Report 30-06-2025.pdf:p21pt3:0.089, docx:Standard Provisions 2026.docx:u82-85:0.089, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p35pt3:0.088, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p22pt1:0.088, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt1:0.088, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt4:0.088, pdf:Portfolio Narrative_2024.pdf:p82pt2:0.088, docx:2025 Technical Reporting Information (Session 2).docx:u46-49:0.088, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p9pt2:0.088, pdf:Genebanks_Inception Report 30-06-2025.pdf:p9pt2:0.088, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p9pt3:0.088, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p2pt1:0.088, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p27pt2:0.088, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p35pt4:0.088, docx:2025 Technical Reporting Information (Session 2).docx:u25-28:0.088, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt2:0.087, docx:Standard Provisions 2026.docx:u94-97:0.087, pdf:Genebanks_Inception Report 30-06-2025.pdf:p24pt2:0.087, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt4:0.087, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.087, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.087, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt3:0.087, docx:Standard Provisions 2026.docx:u169-172:0.086, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.086, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p32pt2:0.086, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p31pt2:0.086, pdf:Genebanks_Inception Report 30-06-2025.pdf:p8pt3:0.086, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p5pt2:0.086, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p23pt1:0.086, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p7pt2:0.086, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p25pt1:0.086, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p5pt2:0.085, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p25pt3:0.085, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p4pt2:0.085, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p40pt4:0.084, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p33pt4:0.084, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p27pt1:0.084, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p49pt3:0.084, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p31pt2:0.084, docx:Standard Provisions 2026.docx:u85-88:0.084, pdf:CGIAR_PORB_Scaling_4Impact.pdf:p2pt1:0.084, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p2pt1:0.084, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt3:0.084, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p24pt4:0.084</t>
+  </si>
+  <si>
+    <t>pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4:0.302, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2:0.290, docx:Innovation use.docx:u1-4:0.281, docx:General reporting guidance.docx:u1-3:0.250, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4:0.240, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt3:0.230, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt3:0.229, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt2:0.228, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p60pt4:0.227, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3:0.226, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.226, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4:0.226, docx:Innovation development.docx:u1-4:0.222, docx:2025 Technical Reporting MELIA glossary.docx:u31-34:0.218, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4:0.214, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt2:0.214, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt4:0.213, pdf:CGI21_508012_PORB_Genebanks.pdf:p5pt2:0.213, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt1:0.202, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p15pt4:0.202, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p27pt1:0.200, pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3:0.198, pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt1:0.197, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt1:0.196, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p31pt1:0.193, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt3:0.193, pdf:CGI21_508012_PORB_Genebanks.pdf:p51pt2:0.193, pdf:CGI21_508012_PORB_Genebanks.pdf:p27pt1:0.193, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt4:0.192, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p6pt2:0.192, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt2:0.192, docx:2025 Technical Reporting MELIA glossary.docx:u28-31:0.191, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.191, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt4:0.191, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p12pt1:0.190, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p12pt1:0.189, pdf:CGI21_508012_PORB_Genebanks.pdf:p41pt1:0.188, docx:Guidance on reporting outputs or outcomes.docx:u7-10:0.187, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.186, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.185, pdf:CGI21_508012_PORB_Genebanks.pdf:p23pt3:0.184, pdf:CGI21_508012_PORB_Genebanks.pdf:p6pt2:0.184, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p11pt3:0.184, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p13pt2:0.183, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p9pt1:0.183, pdf:CGI21_508012_PORB_Genebanks.pdf:p33pt2:0.183, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt4:0.183, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p31pt4:0.181, pdf:CGI21_508012_PORB_Genebanks.pdf:p24pt1:0.180, pdf:CGI21_508012_PORB_Genebanks.pdf:p31pt3:0.179, pdf:CGI21_508012_PORB_Genebanks.pdf:p32pt3:0.178, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p15pt2:0.177, pdf:CGI21_508012_PORB_Genebanks.pdf:p22pt3:0.176, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt1:0.176, docx:2025 Technical Reporting Information (Session 1).docx:u25-28:0.173, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p21pt1:0.173, pdf:CGI21_508012_PORB_Genebanks.pdf:p40pt2:0.172, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt3:0.168, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt2:0.168, pdf:CGI21_508012_PORB_Genebanks.pdf:p27pt3:0.168, pdf:Portfolio Narrative_2024.pdf:p7pt1:0.167, pdf:CGIAR_ImpactReport_2022-24.pdf:p36pt2:0.167, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt4:0.167, pdf:CGI21_508012_PORB_Genebanks.pdf:p29pt2:0.166, pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt2:0.165, pdf:CGI21_508012_PORB_Genebanks.pdf:p47pt2:0.165, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p34pt4:0.164, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p25pt1:0.164, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p10pt2:0.163, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p6pt1:0.163, pdf:CGI21_508012_PORB_Genebanks.pdf:p35pt2:0.163, pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt3:0.163, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p4pt4:0.162, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p11pt4:0.162, pdf:CGIAR_ImpactReport_2022-24.pdf:p13pt1:0.162, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p20pt2:0.161, pdf:CGI21_508012_PORB_Genebanks.pdf:p44pt2:0.161, docx:2025 Technical Reporting Information (Session 2).docx:u19-22:0.161, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p51pt1:0.161, pdf:CGI21_508012_PORB_Genebanks.pdf:p38pt2:0.160, pdf:CGI21_508012_PORB_Genebanks.pdf:p41pt3:0.160, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt1:0.160, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt2:0.159, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p1pt4:0.159, pdf:CGI21_508012_PORB_Genebanks.pdf:p26pt2:0.159, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt1:0.159, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p11pt4:0.158, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p22pt2:0.157, pdf:Portfolio Narrative_2024.pdf:p53pt2:0.157, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1:0.156, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p29pt4:0.156, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p6pt1:0.155, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p40pt1:0.155, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p24pt2:0.155, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt3:0.155, pdf:CGIAR_ImpactReport_2022-24.pdf:p64pt3:0.154, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p10pt4:0.154, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p15pt3:0.154, pdf:CGI21_508012_PORB_Genebanks.pdf:p6pt4:0.153, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p23pt3:0.152, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt2:0.152, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt3:0.151, pdf:CGI21_508012_PORB_Genebanks.pdf:p41pt2:0.150, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt1:0.150, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p42pt2:0.150, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p18pt2:0.149, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p17pt2:0.149, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p14pt4:0.149, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.148, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt2:0.148, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p46pt3:0.148, pdf:CGI21_508012_PORB_Genebanks.pdf:p47pt3:0.147, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt3:0.147, pdf:CGI21_508012_PORB_Genebanks.pdf:p29pt3:0.147, pdf:CGI21_508012_PORB_Genebanks.pdf:p30pt2:0.147, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3:0.146, pdf:CGI21_508012_PORB_Genebanks.pdf:p39pt2:0.146, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt3:0.146, pdf:CGI21_508012_PORB_Genebanks.pdf:p13pt1:0.146, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p28pt3:0.145, pdf:CGI21_508012_PORB_Genebanks.pdf:p51pt1:0.145, pdf:CGI21_508012_PORB_Genebanks.pdf:p32pt2:0.144, pdf:CGI21_508012_PORB_Genebanks.pdf:p35pt3:0.144, pdf:CGI21_508012_PORB_Genebanks.pdf:p26pt3:0.143, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt1:0.143, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p13pt4:0.143, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt1:0.143, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1:0.143, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p11pt1:0.143, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p10pt1:0.142, pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt2:0.142, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p51pt4:0.142, docx:Guidance on reporting outputs or outcomes.docx:u19-22:0.142, pdf:CGI21_508012_PORB_Genebanks.pdf:p48pt2:0.141, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt3:0.141, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p31pt3:0.141, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.141, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt3:0.141, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p19pt2:0.141, pdf:CGI21_508012_PORB_Genebanks.pdf:p45pt2:0.141, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p11pt1:0.140, pdf:CGI21_508012_PORB_Genebanks.pdf:p12pt1:0.140, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p10pt1:0.140, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p15pt4:0.140, pdf:CGI21_508012_PORB_Genebanks.pdf:p7pt2:0.139, pdf:CGIAR_ImpactReport_2022-24.pdf:p3pt1:0.139, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p20pt1:0.139, pdf:CGI21_508012_PORB_Genebanks.pdf:p36pt2:0.139, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt1:0.139, docx:Engagement Plan 2025 Technical Reporting.docx:u61-63:0.139, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt2:0.139, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p18pt4:0.138, docx:2025 Technical Reporting Information (Session 2).docx:u13-16:0.138, pdf:CGI21_508012_PORB_Genebanks.pdf:p33pt1:0.138, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p13pt4:0.137, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt4:0.137, pdf:CGI21_508012_PORB_Genebanks.pdf:p23pt2:0.137, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p12pt2:0.137, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt2:0.137, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p12pt3:0.137, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p44pt2:0.136, pdf:CGIAR_ImpactReport_2022-24.pdf:p36pt3:0.136, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt4:0.136, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p12pt2:0.136, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p14pt4:0.136, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p9pt2:0.135, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt3:0.135, docx:Guidance on ensuring quality over quantity.docx:u1-4:0.135, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p30pt1:0.135, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt3:0.134, pdf:Portfolio Narrative_2024.pdf:p60pt1:0.134, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p24pt3:0.134, docx:Innovation use.docx:u13-16:0.134, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1:0.134, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p25pt3:0.134, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt4:0.133, pdf:CGI21_508012_PORB_Genebanks.pdf:p38pt3:0.133, pdf:CGI21_508012_PORB_Genebanks.pdf:p44pt3:0.133, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt1:0.133, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt2:0.132, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.132, pdf:CGI21_508012_PORB_Genebanks.pdf:p46pt3:0.132, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p34pt2:0.132, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt1:0.132, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p16pt3:0.132, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p9pt4:0.131, pdf:CGIAR_ImpactReport_2022-24.pdf:p65pt2:0.131, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt3:0.131, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt4:0.131, docx:Guidance on reporting outputs or outcomes.docx:u16-19:0.131</t>
+  </si>
+  <si>
+    <t>pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4:0.301, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2:0.289, docx:Innovation use.docx:u1-4:0.281, docx:General reporting guidance.docx:u1-3:0.250, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4:0.243, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p22pt4:0.243, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt3:0.230, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt3:0.229, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt2:0.227, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p60pt4:0.227, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.227, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4:0.226, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3:0.226, docx:Innovation development.docx:u1-4:0.221, docx:2025 Technical Reporting MELIA glossary.docx:u31-34:0.218, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4:0.215, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt2:0.213, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt4:0.213, pdf:CGI21_508012_PORB_Genebanks.pdf:p5pt2:0.212, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt1:0.202, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p15pt4:0.201, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p27pt1:0.200, pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3:0.199, pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt1:0.196, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt1:0.196, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p31pt1:0.193, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt3:0.193, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt4:0.192, pdf:CGI21_508012_PORB_Genebanks.pdf:p51pt2:0.192, pdf:CGI21_508012_PORB_Genebanks.pdf:p27pt1:0.192, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.192, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p6pt2:0.192, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt2:0.191, docx:2025 Technical Reporting MELIA glossary.docx:u28-31:0.191, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt4:0.191, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p12pt1:0.190, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p12pt1:0.190, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p12pt1:0.189, pdf:CGI21_508012_PORB_Genebanks.pdf:p41pt1:0.187, docx:Guidance on reporting outputs or outcomes.docx:u7-10:0.187, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.186, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.185, pdf:CGI21_508012_PORB_Genebanks.pdf:p23pt3:0.183, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p11pt3:0.183, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p13pt2:0.183, pdf:CGI21_508012_PORB_Genebanks.pdf:p6pt2:0.183, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p9pt1:0.183, pdf:CGI21_508012_PORB_Genebanks.pdf:p33pt2:0.182, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt4:0.182, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p31pt4:0.181, pdf:CGI21_508012_PORB_Genebanks.pdf:p24pt1:0.179, pdf:CGI21_508012_PORB_Genebanks.pdf:p31pt3:0.178, pdf:CGI21_508012_PORB_Genebanks.pdf:p32pt3:0.177, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p15pt2:0.176, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt1:0.176, pdf:CGI21_508012_PORB_Genebanks.pdf:p22pt3:0.175, docx:2025 Technical Reporting Information (Session 1).docx:u25-28:0.173, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p21pt1:0.172, pdf:CGI21_508012_PORB_Genebanks.pdf:p40pt2:0.171, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt2:0.170, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt3:0.168, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt4:0.167, pdf:Portfolio Narrative_2024.pdf:p7pt1:0.167, pdf:CGI21_508012_PORB_Genebanks.pdf:p27pt3:0.167, pdf:CGIAR_ImpactReport_2022-24.pdf:p36pt2:0.167, pdf:CGI21_508012_PORB_Genebanks.pdf:p29pt2:0.165, pdf:CGI21_508012_PORB_Genebanks.pdf:p47pt2:0.165, pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt2:0.165, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p25pt1:0.165, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p34pt4:0.164, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p10pt2:0.163, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p6pt1:0.162, pdf:CGI21_508012_PORB_Genebanks.pdf:p35pt2:0.162, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p11pt4:0.162, pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt3:0.162, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p4pt4:0.162, pdf:CGIAR_ImpactReport_2022-24.pdf:p13pt1:0.161, pdf:CGI21_508012_PORB_Genebanks.pdf:p44pt2:0.161, docx:2025 Technical Reporting Information (Session 2).docx:u19-22:0.161, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p20pt2:0.161, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p51pt1:0.160, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt1:0.160, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p1pt4:0.160, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt1:0.159, pdf:CGI21_508012_PORB_Genebanks.pdf:p38pt2:0.159, pdf:CGI21_508012_PORB_Genebanks.pdf:p41pt3:0.159, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt2:0.159, pdf:CGI21_508012_PORB_Genebanks.pdf:p26pt2:0.158, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p11pt4:0.158, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p22pt2:0.157, pdf:Portfolio Narrative_2024.pdf:p53pt2:0.157, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p29pt4:0.156, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1:0.156, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p6pt1:0.155, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p10pt4:0.155, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p40pt1:0.155, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt3:0.154, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p24pt2:0.154, pdf:CGIAR_ImpactReport_2022-24.pdf:p64pt3:0.154, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p15pt3:0.153, pdf:CGI21_508012_PORB_Genebanks.pdf:p6pt4:0.152, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p23pt3:0.152, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt2:0.151, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt1:0.150, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt3:0.150, pdf:CGI21_508012_PORB_Genebanks.pdf:p41pt2:0.150, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p18pt2:0.149, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p42pt2:0.149, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.149, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p17pt2:0.148, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p14pt4:0.148, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p46pt3:0.148, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt2:0.148, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt3:0.147, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3:0.147, pdf:CGI21_508012_PORB_Genebanks.pdf:p47pt3:0.146, pdf:CGI21_508012_PORB_Genebanks.pdf:p29pt3:0.146, pdf:CGI21_508012_PORB_Genebanks.pdf:p30pt2:0.146, pdf:CGI21_508012_PORB_Genebanks.pdf:p39pt2:0.146, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt3:0.145, pdf:CGI21_508012_PORB_Genebanks.pdf:p13pt1:0.145, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p28pt3:0.145, pdf:CGI21_508012_PORB_Genebanks.pdf:p51pt1:0.144, pdf:CGI21_508012_PORB_Genebanks.pdf:p32pt2:0.144, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p13pt4:0.143, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p13pt4:0.143, pdf:CGI21_508012_PORB_Genebanks.pdf:p35pt3:0.143, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt1:0.143, pdf:CGI21_508012_PORB_Genebanks.pdf:p26pt3:0.143, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt1:0.143, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt1:0.142, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p10pt1:0.142, pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt2:0.142, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p11pt1:0.142, docx:Guidance on reporting outputs or outcomes.docx:u19-22:0.142, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.142, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p51pt4:0.141, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt3:0.141, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p13pt3:0.141, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p31pt3:0.141, pdf:CGI21_508012_PORB_Genebanks.pdf:p48pt2:0.141, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p19pt2:0.140, pdf:CGI21_508012_PORB_Genebanks.pdf:p45pt2:0.140, pdf:CGI21_508012_PORB_Genebanks.pdf:p12pt1:0.140, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p10pt1:0.140, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p11pt1:0.140, docx:Engagement Plan 2025 Technical Reporting.docx:u61-63:0.139, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p15pt4:0.139, pdf:CGIAR_ImpactReport_2022-24.pdf:p3pt1:0.139, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt1:0.139, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p20pt1:0.139, pdf:CGI21_508012_PORB_Genebanks.pdf:p7pt2:0.139, pdf:CGI21_508012_PORB_Genebanks.pdf:p36pt2:0.138, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt2:0.138, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt4:0.138, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p7pt4:0.138, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p18pt4:0.138, docx:2025 Technical Reporting Information (Session 2).docx:u13-16:0.138, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p12pt2:0.137, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1:0.137, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p13pt4:0.137, pdf:CGI21_508012_PORB_Genebanks.pdf:p33pt1:0.137, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt2:0.137, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt4:0.137, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p15pt4:0.137, pdf:CGI21_508012_PORB_Genebanks.pdf:p23pt2:0.136, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p12pt3:0.136, pdf:CGIAR_ImpactReport_2022-24.pdf:p36pt3:0.136, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p14pt4:0.136, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p44pt2:0.136, docx:Guidance on ensuring quality over quantity.docx:u1-4:0.136, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p12pt2:0.135, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p30pt1:0.135, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt3:0.135, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p9pt2:0.135, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt3:0.134, docx:Innovation use.docx:u13-16:0.134, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt4:0.134, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt4:0.134, pdf:Portfolio Narrative_2024.pdf:p60pt1:0.134, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p24pt3:0.133, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p25pt3:0.133, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt1:0.133, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.132, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt2:0.132, pdf:CGI21_508012_PORB_Genebanks.pdf:p38pt3:0.132, pdf:CGI21_508012_PORB_Genebanks.pdf:p44pt3:0.132, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p16pt3:0.132, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p34pt2:0.132, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt1:0.132, docx:Guidance on reporting outputs or outcomes.docx:u16-19:0.131, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt3:0.131, pdf:CGI21_508012_PORB_Genebanks.pdf:p46pt3:0.131, pdf:CGIAR_ImpactReport_2022-24.pdf:p65pt2:0.131, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt4:0.131, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt2:0.131, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p31pt3:0.131, pdf:CGI21-507032-PORB-Gender Equality and Inclusion.pdf:p9pt4:0.131, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p12pt2:0.131, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p15pt4:0.130</t>
+  </si>
+  <si>
+    <t>pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4:0.157, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2:0.152, docx:Innovation use.docx:u1-4:0.151, docx:General reporting guidance.docx:u1-3:0.136, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt3:0.129, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p18pt4:0.129, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4:0.127, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4:0.124, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.124, docx:2025 Technical Reporting MELIA glossary.docx:u31-34:0.124, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3:0.123, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt2:0.123, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p60pt4:0.122, docx:Innovation development.docx:u1-4:0.119, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.116, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt4:0.116, pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3:0.116, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt1:0.112, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt2:0.112, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt3:0.112, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p6pt2:0.111, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt1:0.110, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4:0.110, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p22pt4:0.110, docx:2025 Technical Reporting MELIA glossary.docx:u28-31:0.109, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt3:0.108, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2:0.107, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.107, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p13pt2:0.106, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p9pt1:0.106, pdf:CGI21_508012_PORB_Genebanks.pdf:p5pt2:0.105, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt4:0.105, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p12pt1:0.105, docx:Guidance on reporting outputs or outcomes.docx:u7-10:0.104, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p15pt4:0.103, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p12pt1:0.102, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p12pt1:0.102, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt2:0.102, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt1:0.102, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p31pt4:0.100, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt4:0.100, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt2:0.099, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p27pt1:0.098, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt3:0.097, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt4:0.097, pdf:Portfolio Narrative_2024.pdf:p7pt1:0.097, docx:2025 Technical Reporting Information (Session 1).docx:u25-28:0.096, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p15pt2:0.096, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p31pt1:0.095, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p25pt1:0.095, pdf:CGIAR_ImpactReport_2022-24.pdf:p36pt2:0.095, pdf:CGI21_508012_PORB_Genebanks.pdf:p51pt2:0.094, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt4:0.094, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p4pt4:0.094, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p20pt2:0.093, pdf:CGI21_508012_PORB_Genebanks.pdf:p27pt1:0.093, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt1:0.093, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p1pt4:0.093, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p32pt1:0.092, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.091, pdf:CGIAR_ImpactReport_2022-24.pdf:p13pt1:0.091, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt2:0.091, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p29pt4:0.091, pdf:CGI21_508012_PORB_Genebanks.pdf:p31pt3:0.090, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p10pt2:0.090, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p24pt2:0.089, pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt1:0.089, pdf:CGI21_508012_PORB_Genebanks.pdf:p33pt2:0.089, pdf:CGI21_508012_PORB_Genebanks.pdf:p22pt3:0.089, docx:2025 Technical Reporting Information (Session 2).docx:u19-22:0.089, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p15pt3:0.089, pdf:CGI21_508012_PORB_Genebanks.pdf:p23pt3:0.089, pdf:CGI21_508012_PORB_Genebanks.pdf:p6pt2:0.088, pdf:CGI21_508012_PORB_Genebanks.pdf:p24pt1:0.087, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p10pt4:0.087, pdf:Portfolio Narrative_2024.pdf:p53pt2:0.087, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt3:0.087, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p34pt4:0.087, pdf:CGI21_508012_PORB_Genebanks.pdf:p40pt2:0.087, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.086, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p14pt4:0.086, pdf:Genebanks_Inception Report 30-06-2025.pdf:p8pt3:0.086, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p46pt3:0.086, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p6pt1:0.086, pdf:CGI21_508012_PORB_Genebanks.pdf:p41pt1:0.086, pdf:CGI21_508012_PORB_Genebanks.pdf:p32pt3:0.086, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p17pt2:0.085, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt1:0.085, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p11pt3:0.084, pdf:CGIAR_ImpactReport_2022-24.pdf:p64pt3:0.083, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p10pt1:0.083, docx:Guidance on reporting outputs or outcomes.docx:u19-22:0.082, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt3:0.082, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt3:0.082, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt3:0.082, pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt2:0.081, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p21pt1:0.081, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p10pt1:0.081, docx:Engagement Plan 2025 Technical Reporting.docx:u61-63:0.081, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p15pt4:0.081, pdf:CGIAR_ImpactReport_2022-24.pdf:p3pt1:0.081, pdf:CGI21_508012_PORB_Genebanks.pdf:p27pt3:0.080, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p18pt4:0.080, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p22pt2:0.080, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p12pt2:0.080, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1:0.080, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p13pt4:0.080, pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt3:0.080, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p13pt4:0.079, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p13pt4:0.079, docx:2025 Technical Reporting Information (Session 2).docx:u13-16:0.079, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt1:0.079, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p6pt1:0.079, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3:0.079, pdf:CGI21_508012_PORB_Genebanks.pdf:p41pt3:0.079, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p14pt4:0.079, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt3:0.078, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt3:0.078, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt1:0.078, docx:Innovation use.docx:u13-16:0.078, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p24pt3:0.077, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p12pt2:0.077, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt2:0.077, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p11pt4:0.077, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt1:0.077, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.077, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p16pt3:0.076, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p34pt2:0.076, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt1:0.076, docx:Guidance on reporting outputs or outcomes.docx:u16-19:0.076, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p11pt4:0.076, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p20pt2:0.076, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p18pt2:0.076, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt1:0.075, pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p16pt2:0.075, pdf:CGIAR_ImpactReport_2022-24.pdf:p5pt4:0.075, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt4:0.075, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt4:0.075, pdf:Portfolio Narrative_2024.pdf:p60pt1:0.075, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p11pt1:0.075, pdf:CGI21_508012_PORB_Genebanks.pdf:p29pt2:0.075, pdf:CGI21_508012_PORB_Genebanks.pdf:p47pt2:0.075, pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt2:0.075, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p16pt3:0.074, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p19pt3:0.074, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p19pt4:0.074, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p30pt1:0.074, pptx:Information Session on 2025 Technical Reporting.pptx:s8pt1:0.074, pdf:CGI21_508012_PORB_Genebanks.pdf:p41pt2:0.074, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p13pt2:0.074, pdf:Portfolio Narrative_2024.pdf:p15pt4:0.074, pdf:CGI21_508012_PORB_Genebanks.pdf:p51pt1:0.074, pdf:CGI21_508012_PORB_Genebanks.pdf:p35pt2:0.074, pdf:CGI21_508012_PORB_Genebanks.pdf:p6pt4:0.073, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p7pt3:0.073, pdf:CGI21_508012_PORB_Genebanks.pdf:p44pt2:0.073, pptx:Information Session on 2025 Technical Reporting.pptx:s13pt1:0.073, pdf:CGI21_508012_PORB_Genebanks.pdf:p26pt2:0.073, pdf:CGI21_508012_PORB_Genebanks.pdf:p38pt2:0.073, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p31pt3:0.072, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt2:0.072, pdf:CGI21_508012_PORB_Genebanks.pdf:p47pt3:0.072, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p9pt4:0.072, pdf:CGI21_508012_PORB_Genebanks.pdf:p29pt3:0.072, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p11pt1:0.072, docx:2025 Technical Reporting Information (Session 2).docx:u22-25:0.071, docx:2025 Technical Reporting Information (Session 2).docx:u34-37:0.071, pdf:CGI21_508012_PORB_Genebanks.pdf:p30pt2:0.071, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p51pt1:0.071, pdf:CGI21_508012_PORB_Genebanks.pdf:p39pt2:0.071, pdf:CGI21_508012_PORB_Genebanks.pdf:p35pt3:0.071, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt1:0.071, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p40pt1:0.071, pdf:CGIAR_ImpactReport_2022-24.pdf:p36pt3:0.071, pdf:CGI21_508012_PORB_Genebanks.pdf:p26pt3:0.070, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt4:0.070, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p7pt4:0.070, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt2:0.070, docx:Guidance on ensuring quality over quantity.docx:u1-4:0.070, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt2:0.070, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p4pt1:0.070, pdf:CGI21_508012_PORB_Genebanks.pdf:p33pt1:0.070, pdf:CGI21_508012_PORB_Genebanks.pdf:p46pt3:0.070, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt2:0.070, pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt1:0.070, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p12pt2:0.070, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt1:0.069, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p30pt2:0.069, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p30pt4:0.069, docx:Guidance on reporting outputs or outcomes.docx:u4-7:0.069, pdf:CGI21_508012_PORB_Genebanks.pdf:p48pt2:0.069, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p23pt3:0.069, pdf:CGI21_508012_PORB_Genebanks.pdf:p28pt3:0.069, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt1:0.068, pdf:CGI21_508012_PORB_Genebanks.pdf:p45pt2:0.068, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p42pt2:0.068, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p13pt3:0.068, pdf:CGI21_508012_PORB_Genebanks.pdf:p7pt2:0.068, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p15pt4:0.068, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p27pt2:0.068</t>
+  </si>
+  <si>
+    <t>pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt1:0.380, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p6pt2:0.339, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4:0.329, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p22pt4:0.329, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p21pt2:0.311, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p7pt1:0.292, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt1:0.281, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p5pt1:0.281, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt3:0.277, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt3:0.277, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.276, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p28pt2:0.275, docx:2025 Technical Reporting MELIA glossary.docx:u55-58:0.272, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p9pt2:0.269, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt1:0.260, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p16pt1:0.255, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p16pt1:0.255, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt2:0.247, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p8pt2:0.247, docx:2025 Technical Reporting MELIA glossary.docx:u34-37:0.239, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p32pt3:0.234, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt2:0.229, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt2:0.229, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p3pt1:0.228, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p18pt3:0.227, pdf:Type3_2024Report.pdf:p11pt4:0.226, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p13pt1:0.226, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18pt2:0.225, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p18pt2:0.225, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p13pt1:0.222, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p13pt1:0.222, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p9pt1:0.218, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p9pt2:0.216, docx:2025 Technical Reporting MELIA glossary.docx:u31-34:0.213, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p15pt3:0.213, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p10pt3:0.212, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt1:0.210, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p7pt1:0.210, pptx:Information Session on 2025 Technical Reporting.pptx:s14pt1:0.208, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p1pt1:0.207, pdf:Genebanks_Inception Report 30-06-2025.pdf:p18pt4:0.199, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p3pt1:0.196, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p26pt3:0.196, pdf:CGIAR_ImpactReport_2022-24.pdf:p9pt1:0.195, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p37pt4:0.195, docx:2025 Technical Reporting MELIA glossary.docx:u28-31:0.194, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p10pt1:0.194, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.193, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.193, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p4pt4:0.191, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p3pt2:0.190, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p12pt4:0.189, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt1:0.189, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p1pt1:0.188, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p2pt1:0.188, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3:0.186, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p3pt1:0.183, pptx:Information Session on 2025 Technical Reporting.pptx:s5pt2:0.182, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p3pt2:0.182, pdf:CGI21_508012_PORB_Genebanks.pdf:p1pt1:0.180, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p1pt1:0.180, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p1pt1:0.180, docx:Guidance on reporting outputs or outcomes.docx:u7-10:0.180, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt3:0.180, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt2:0.180, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p4pt2:0.180, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p11pt1:0.178, pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt4:0.176, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p20pt1:0.176, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt2:0.176, pdf:Genebanks_Inception Report 30-06-2025.pdf:p13pt4:0.175, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p24pt1:0.174, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p9pt1:0.173, docx:Guidance on ensuring quality over quantity.docx:u4-7:0.173, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p28pt3:0.172, pdf:Type3_2024Report.pdf:p4pt4:0.171, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p21pt2:0.171, pdf:Genebanks_Inception Report 30-06-2025.pdf:p18pt3:0.171, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3:0.170, pdf:Portfolio Narrative_2024.pdf:p11pt3:0.169, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p14pt1:0.168, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p19pt1:0.167, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p20pt1:0.167, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p33pt3:0.166, pdf:Type3_2024Report.pdf:p4pt1:0.166, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p9pt4:0.164, pdf:Genebanks_Inception Report 30-06-2025.pdf:p13pt1:0.164, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt2:0.164, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p9pt1:0.163, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt4:0.163, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt4:0.163, pdf:CGIAR_ImpactReport_2022-24.pdf:p42pt1:0.162, docx:2025 Technical Reporting MELIA glossary.docx:u52-55:0.161, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1:0.161, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p17pt1:0.161, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.161, pdf:Portfolio Narrative_2024.pdf:p5pt3:0.160, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p32pt4:0.160, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p10pt3:0.159, docx:Guidance on complementary innnov.docx:u4-7:0.159, pdf:Portfolio Narrative_2024.pdf:p30pt3:0.159, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p22pt4:0.159, pdf:Portfolio Narrative_2024.pdf:p11pt4:0.158, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p13pt2:0.157, pdf:Portfolio Narrative_2024.pdf:p75pt4:0.157, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.157, docx:Guidance on reporting outputs or outcomes.docx:u1-4:0.157, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt2:0.157, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p21pt1:0.156, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p7pt1:0.156, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.156, docx:Standard Provisions 2026.docx:u136-139:0.155, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p17pt3:0.155, pdf:CGIAR_ImpactReport_2022-24.pdf:p27pt1:0.154, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p20pt4:0.154, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p20pt4:0.154, pdf:Portfolio Narrative_2024.pdf:p62pt3:0.154, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p13pt3:0.153, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt3:0.153, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p4pt3:0.153, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p16pt3:0.153, pdf:Portfolio Narrative_2024.pdf:p18pt1:0.153, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.153, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.153, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p15pt2:0.152, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p17pt4:0.152, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p19pt4:0.152, pdf:CGI21-507032-PORB-Climate Action.pdf:p1pt1:0.151, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p21pt3:0.151, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p21pt3:0.151, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p8pt2:0.151, pdf:Portfolio Narrative_2024.pdf:p68pt2:0.151, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p2pt1:0.151, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p9pt1:0.150, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p55pt1:0.150, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p4pt1:0.150, pdf:Portfolio Narrative_2024.pdf:p75pt3:0.150, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p28pt1:0.150, pdf:CGIAR_ImpactReport_2022-24.pdf:p13pt3:0.148, pdf:Climate Action_Inception Report 30-06-2025.pdf:p15pt3:0.148, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p16pt3:0.148, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p72pt1:0.148, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p21pt4:0.148, pdf:CGIAR_ImpactReport_2022-24.pdf:p18pt1:0.148, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p14pt2:0.147, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p9pt2:0.147, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p20pt4:0.146, pdf:CGIAR_ImpactReport_2022-24.pdf:p16pt1:0.146, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt3:0.146, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p30pt4:0.145, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25pt3:0.145, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p25pt3:0.145, pdf:Quick style guide Feb 2024 (1).pdf:p7pt4:0.145, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p14pt4:0.145, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p14pt4:0.145, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p18pt2:0.145, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p30pt1:0.145, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p15pt4:0.145, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p7pt4:0.145, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p15pt3:0.144, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p22pt1:0.144, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p1pt1:0.144, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p5pt4:0.144, pdf:Portfolio Narrative_2024.pdf:p58pt2:0.143, pptx:Information Session on 2025 Technical Reporting.pptx:s8pt2:0.143, pdf:Portfolio Narrative_2024.pdf:p54pt4:0.143, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt3:0.142, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p10pt3:0.142, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p10pt3:0.142, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p12pt1:0.142, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p23pt1:0.141, docx:Guidance on reporting outputs or outcomes.docx:u4-7:0.141, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.141, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p5pt1:0.141, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p28pt4:0.141, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p15pt3:0.141, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p50pt1:0.141, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p19pt3:0.140, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p8pt1:0.139, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p8pt1:0.139, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt3:0.139, pdf:Portfolio Narrative_2024.pdf:p15pt4:0.139, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p14pt4:0.139, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p9pt2:0.139, pdf:Portfolio Narrative_2024.pdf:p67pt4:0.139, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p5pt3:0.139, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p26pt4:0.139, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25pt4:0.138, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p25pt4:0.138, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt3:0.138, docx:Standard Provisions 2026.docx:u109-112:0.138, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p3pt1:0.137, docx:General reporting guidance.docx:u1-3:0.137, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p3pt1:0.136, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt4:0.136, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt1:0.136, docx:Innovation use.docx:u1-4:0.136, docx:2025 Technical Reporting Information (Session 1).docx:u19-22:0.136, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p15pt1:0.136, pdf:Portfolio Narrative_2024.pdf:p74pt4:0.136</t>
   </si>
   <si>
     <t>I cannot find information in the provided chunks to answer this.  
@@ -750,6 +786,47 @@
 docx:Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21 — u16-19</t>
   </si>
   <si>
+    <t>An outcome refers to the specific results or changes that occur as a result of a program or initiative. In the context of the provided documents, outcomes can be categorized into various levels, such as intermediate outcomes and 2030 outcomes, which represent the final goals to be achieved by a certain date. For example, an outcome might involve the successful marketing of improved seed varieties to farmers or the strengthening of institutional capacities to guide policy decisions. These outcomes are essential for measuring the effectiveness and impact of initiatives within the CGIAR framework.
+Sources:
+- Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf — page 48 part 4 — pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1)
+- Policy Innovations_Inception Report 30-06-2025.pdf — page 13 part 2 — pdf:Policy Innovations_Inception Report 30-06-2025
+- Innovation use.docx — section 'Innovation use' paragraph 1 to section 'Innovation use' paragraph 7 — docx:Innovation use
+- General reporting guidance.docx — section 'General reporting guidance' paragraph 1 to section 'General reporting guidance' paragraph 5 — docx:General reporting guidance
+- CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 22 part 4 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30</t>
+  </si>
+  <si>
+    <t>An outcome refers to the final results or impacts achieved as a result of specific initiatives or actions. In the context of the provided documents, outcomes can be seen as the higher-level changes that occur after outputs have been delivered, such as improved capacities, policy changes, or increased access to resources. For example, one document mentions a specific outcome related to seed producers successfully marketing new varieties to farmers, highlighting the practical implications of breeding initiatives. Outcomes are often linked to broader goals, such as achieving Sustainable Development Goals (SDGs) or enhancing food security.
+Sources:
+File — Location — Cited IDs
+Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf — page 48 part 4 — pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4
+Policy Innovations_Inception Report 30-06-2025.pdf — page 13 part 2 — pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2
+Innovation use.docx — section 'Innovation use' paragraph 1 to section 'Innovation use' paragraph 7 — docx:Innovation use.docx:u1-4
+General reporting guidance.docx — section 'General reporting guidance' paragraph 1 to section 'General reporting guidance' paragraph 5 — docx:General reporting guidance.docx:u1-3
+CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 22 part 4 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4</t>
+  </si>
+  <si>
+    <t>An outcome refers to a change in knowledge, attitudes, skills, and/or relationships (KASR) that results from research and its outputs, manifesting as a change in behavior among external actors. This can include the adoption of new technologies by farmers or the use of research-based knowledge by policy actors to inform decisions. Outcomes are influenced by the research but are not directly controlled by the researchers, distinguishing them from outputs, which are tangible products or services produced by the research process. The focus on outcomes emphasizes the broader impact of research initiatives on stakeholders and systems. 
+Sources:
+File: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf — page 9 part 1 — [ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt1]
+File: 2025 Technical Reporting MELIA glossary.docx — table 1 row 28 to table 1 row 31 — [ID: docx:2025 Technical Reporting MELIA glossary.docx:u31-34]
+File: Guidance on reporting outputs or outcomes.docx — paragraph 10 to paragraph 17 — [ID: docx:Guidance on reporting outputs or outcomes.docx:u7-10]
+File: CGIAR_ImpactReport_2022-24.pdf — page 11 part 1 — [ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt1]</t>
+  </si>
+  <si>
+    <t>An outcome refers to a change in knowledge, attitudes, skills, and/or relationships (KASR) that results from research outputs and activities. It signifies a behavioral change that occurs outside the research team, influenced by the research but not directly controlled by it. Examples of outcomes include the adoption of new technologies by farmers or the use of research-based knowledge by policy actors to inform decisions. In the context of CGIAR, outcomes are often linked to broader goals such as improving food security, enhancing livelihoods, and promoting sustainable practices. 
+Sources:
+File: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf — page 9 part 1 — [ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt1]
+File: 2025 Technical Reporting MELIA glossary.docx — table 1 row 28 to table 1 row 31 — [ID: docx:2025 Technical Reporting MELIA glossary.docx:u31-34]
+File: Guidance on reporting outputs or outcomes.docx — paragraph 10 to paragraph 17 — [ID: docx:Guidance on reporting outputs or outcomes.docx:u7-10]</t>
+  </si>
+  <si>
+    <t>The CGIAR Results Framework categorizes outputs into three distinct types: outputs, outcomes, and impacts. Outputs refer to tangible products or services generated from CGIAR research, such as knowledge advancements, technical innovations, or capacity development activities. Outcomes represent changes in knowledge, attitudes, skills, or relationships that occur as a result of these outputs, while impacts reflect the long-term changes in conditions for people and their environments that result from the cumulative effects of outputs and outcomes. Each of these categories is essential for tracking progress and ensuring accountability within CGIAR's strategic goals.
+Sources:
+- File: CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf — Location: page 7 part 1 — Cited IDs: [ID: pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p7pt1]
+- File: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — Location: page 11 part 4 — Cited IDs: [ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt4]
+- File: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf — Location: page 19 part 1 — Cited IDs: [ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt1]</t>
+  </si>
+  <si>
     <t>Information Session on 2025 Technical Reporting.pptx — slide 9 — pptx:Information Session on 2025 Technical Reporting.pptx:s9, Engagement Plan 2025 Technical Reporting.docx — paragraph 2 — docx:Engagement Plan 2025 Technical Reporting.docx:p2, Information Session on 2025 Technical Reporting.pptx — slide 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s2, Guidance on reporting outputs or outcomes.docx — paragraph 22 — docx:Guidance on reporting outputs or outcomes.docx:p22, Engagement Plan 2025 Technical Reporting.docx — section 'Technical Reporting questions' — docx:Engagement Plan 2025 Technical Reporting.docx:p59, CGIAR_ImpactReport_2022-24.pdf — page 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p1, Engagement Plan 2025 Technical Reporting.docx — section 'A single location for all documents and resources' — docx:Engagement Plan 2025 Technical Reporting.docx:p31, Engagement Plan 2025 Technical Reporting.pptx — slide 1 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s1, CGSpace.docx — section 'CGSpace' — docx:CGSpace.docx:p3, CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 5 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5</t>
   </si>
   <si>
@@ -796,6 +873,12 @@
   </si>
   <si>
     <t>Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24 — docx:Standard Provisions 2026.docx:u19-22, Standard Provisions 2026.docx — section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21 — docx:Standard Provisions 2026.docx:u16-19, Standard Provisions 2026.docx — section 'Window 3 Funds.' paragraph 30 to section 'Window 3 Funds.' paragraph 33 — docx:Standard Provisions 2026.docx:u28-31</t>
+  </si>
+  <si>
+    <t>https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1 — page 48 part 4 — pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1 — page 13 part 2 — pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2, https://sites.google.com/cgxchange.org/cgiarprhub/2025-reporting?authuser=0 — section 'Innovation use' paragraph 1 to section 'Innovation use' paragraph 7 — docx:Innovation use.docx:u1-4</t>
+  </si>
+  <si>
+    <t>https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1 — page 19 part 1 — pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt1, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1 — page 6 part 2 — pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p6pt2, https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 22 part 4 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4</t>
   </si>
   <si>
     <t>[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]
@@ -2209,6 +2292,415 @@
 Nirmal, Rajalakshmi (IFPRI) 36:04 But. Colomer, Julien (One CGIAR - France) 36:06 Yeah, yeah. Basically anything that's not finished or nailed down, I get to answer for. So and then I SO look, 2025 is a Transition year and. We everybody recognizes like the amount of pressure that everyone's under. So that final step of transferring over the, let's say, key Performance indicator or target output and target outcome values from the window three and bilaterals into the theory of chan</t>
   </si>
   <si>
+    <t xml:space="preserve">[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4]
+breeding endeavors. While an earlier TOC showed the relationship between the outcomes of the initiatives, the revised TOC showed only one outcome of breeding. This outcome was ‘Seed producers successfully market new demand-driven improved varieties to more farmers’. The GI TOC essentially elevated the final output of the breeding pipeline to an outcome3, reverting to the breeding pipeline engineering view that dominates in breeding. In elevating the output to an outcome, any outcomes outside of breeding itself are diminished. Outcomes related to the quality of how breeding is done, with strategic prioritization, collaborative partnerships and efficiency have been omitted. It is these qualities of how breeding is done that build empowerment of regional partners and legacy beyond the lifecycle of a variety. 3 Note that it could be argued this is an outcome of Seed Equal. Regardless, it is not an outcome of GI, but one of the initiatives and this outcome could be achieved without investment or action in
+---
+[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2]
+leading to Intermediate Outcomes and finally to three 2030Outcomes, that correspond broadly to the three pillars. The first 2030 outcome focuses on Pillar C on capacity sharing; the 2nd outcome corresponds to Pillar B while the 3rd one addresses Pillar A.  2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs,  2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessment and governance to guide pro-poor, gender-inclusive and climate smart policies and investments  2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more coherent and sustainable development processes that deliver positive outcomes across a range of SDG targets. The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidates outputs from the 20 High-level outputs of the Policy Program. Multiple Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes
+---
+[ID: docx:Innovation use.docx:u1-4]
+Innovation use How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome levels. The development of an innovation (at various stages) is an output. The scaling, uptake and use of an innovation can be reported as outcome. In PRMS the results can be linked. What are the two ways to report innovation use results (outcomes)?
+---
+[ID: docx:General reporting guidance.docx:u1-3]
+General reporting guidance Is there guidance on what should be reported as a result? Yes, this document provides some principles for ensuring a focus on quality, rather than quantity, in terms of results reporting: Guidance on ensuring quality over quantity. Is there guidance available on how to distinguish between outputs and outcomes? Yes, information on what to report as an output or outcome can be found here: Guidance on reporting outputs or outcomes.
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4]
+CGIAR Results Framework – Portfolio Outcome
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt3]
+the Theories of Change (overall, Areas of Work and sub-Areas) for consistency and alignment with stated objectives. (more details in Section 3.1 of this report) We have revised the HLOs at sub-area of work level, to harmonize the approach, remove duplications, and prioritize. There are now 26 HLOs. − We have harmonized the intermediate outcomes across sub-AoWs, AoWs, and Accelerator level. There are now five intermediate outcomes for AoW on Solutions and three for AoW on Change. − We have moved one outcome from the intermediate level to the end-of-program level and there are now four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt3]
+Outcome Evidencing/ Outcome Trajectory evaluation instruments: Document review, workshops, key informant interviews, secondary data System-based Theory of Change Actor engagement and outcome tracker AoW6 assessments AoW7 partner capacity evaluation • To what extent does co -design of science-based processes and tools lead to ownership of results by landscape stakeholders and therefore to the sustainable uptake of solutions? • Number and type
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt2]
+in breeding contribute to increased rate of genetic gain, as captured in the extent of improvement and impact achieved by products. Efficiency is included in an intermediate outcome so any effectiveness evaluation of intermediate outcomes will be duplicative. This criterion is most relevant to AOW4 as it is designed to support efficient access and use of modernized breeding. An AOW level outcome has captured this so any effectiveness evaluation of outcomes will duplicate efficiency. Research questions will contribute to KEQ2 on effectiveness: To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? RQ12 How has the use of interoperable, scaled breeding tools and services increased
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p60pt4]
+in thriving Multifunctional Landscapes • Number of policy innovations that support the transition to sustained MFLs what was the contribution of the MFL Program interventions to these changes. This will allow us to identify the most impactful Outcomes related to the Impact Areas and orient Outcome Evidencing studies for efficient use of MELIA resources.
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3]
+of this report. Comparison with 2017–2021 Retrospective analysis of CGIAR’s 2017 to 2021 reporting cycle provides a reference point for assessing progress in outcome reporting and portfolio management under the current Results Framework. While differences in the reporting systems limit direct comparability, several structural patterns from the previous cycle remain relevant. Policy outcomes Learnings from CGIAR’s 2017 to 2021 reporting cycle demonstrate that policy outcomes were mostly oriented toward policies and strategies (75 percent), and the rest influenced budget and investment decisions or legal instruments.29 The majority reflected early uptake of research results, but 39 percent of policy outcomes were concrete decisions, policies, or programs taken or enacted. In the current 2022 to 2024 cycle, there was a slight increase in the percentage of reported policy changes that were actual policies or programs put into place (43 percent of policy outcomes). Moreover , the type of policy outcome differed, with the percentage of policy outcomes leading to modified programs or investments jumping to 29 percent. The thematic and geographic orientations of policy outcomes are similar across the two periods, generally displaying CGIAR effectiveness in all of its priority countries and across most of its Impact Areas. However , the percentage of policy outcomes which were aimed primarily at gender equality was low in both periods. Partners were critical to CGIAR’s success in informing policies. Critical partners included national and subnational governments, civil society organizations, private sector , regional bodies, and international organizations. The review of 2017 to 2021 policy outcomes also revealed that very few were evaluated for their impacts, yet many appeared to be significant. Some examples of those are in Table 3. Impacts of CGIAR’s policy research remain underanalyzed. Policy outcome type What the evidence shows Illustrative cases CGIAR partners Outcomes Policy and strategy outcomes, mainly at national level 60% of outcomes were national and 37% reached formal enactment— often when a ministry or regulatory body was part of the design team Ethiopian
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1]
+Key Evaluation Questions Some guiding questions that will inform future evaluations include: • Are the Program’s assumptions about actor behavior, incentives, and influence valid for the specific stakeholders identified, and are they likely to lead to the intended outcomes? • How do differences in AoW presence across countries affect the Program’s ability to deliver its intended outcomes? • Are the current configurations of AoWs efficient and synergistic, or are there opportunities to increase impact through structural changes? • What mechanisms exist (or are lacking) to integrate bilateral and W3-funded results into core program planning and reporting? • To what extent is MELIA evidence used to inform planning, learning, and adaptation across the Program? • How well do program assumptions and outcome pathways reflect national priorities and systems capacities in each geography? • • What types of MELIA findings
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4]
+been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E) Effectiveness (the extent that the intended results or outcomes are achieved) High This criterion directly relates to the MELIA objectives. Assessing the effectiveness of the Intermediate Outcomes will inform contribution analysis and inform the design requirements of future programs. KEQ2. To what extent has B4T and its AOWs effectively achieved the intended intermediate outcomes? RQ2 How did prioritization using the Design Standard contribute to maximized impact (AOW1 MI)? RQ7 To what extent has B4T increased uptake of varieties by scaling partners who have a widespread reach (collectively)? (AOW3 ID) RQ8 To what extent has CGIAR-NARES prioritization of products encouraged targeted investment for breeding?
+---
+[ID: docx:Innovation development.docx:u1-4]
+Innovation development How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome level. The development of an innovation (at various stages of design, testing and validation) is an output. The scaling or use of an innovation is an outcome. You may first report an innovation at the output level. If the innovation advances and starts to be used, it should then be reported as an outcome. Do I need to update innovations that were submitted during previous reporting periods?
+---
+[ID: docx:2025 Technical Reporting MELIA glossary.docx:u31-34]
+Intermediate outcome | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. 2030 outcome | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. Output | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. High-level output | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on).
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]
+four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the "challenges and megatrends" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt2]
+capacity &amp; tools. . The Program’s Theory of Change works through six interconnected Areas of Work (AoWs), their High- level Outputs (HLOs), leading to Intermediate Outcomes and finally to three 2030 Outcomes. During the inception phase the Policy Program align ed the Intermediate Outcomes and 2030 Outcomes to these 3 pillars. The 2030 Outcomes were revised to contribute to our impact around these. 2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs: represents the Capacity and tools pillar, 2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessm ent and governance to guide pro -poor, gender-inclusive and climate smart policies and investments, represents Rapid Response and policy guidance pillar while 2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt4]
+Growth) and 10 (Reduced Inequalities). The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidate outputs from the 20 High -level outputs of the Policy Program. All Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes 1.2.1 (Partners use outlook reports to inform and enhance design of their strategies and policies), 4.2.1 (Partners achieve a shared understanding of emerging ch allenges in WEFE systems and foresight data, tools and analysis), 5.2.1 (Countries co-create national strategies and policies) and 6.2.2 (CGIAR researchers and partners have enh anced capacity) all address the capacity challenge and contribute to the impact pathway achieving 2030 Outcome1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs. This 2030 Outcome in turn, also addresses CGIAR Portfolio Outcome #1: Implementation partners (e.g. NARES, NGOs, private companies) actively support
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p5pt2]
+2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) Intemediate Outcome: Crop Trust signs Long-Term Partnerships with CGIAR X X X X - Intermediate Outcome: CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness X X X X 2030 Outcome 1: National and International genebanks conserve and make diversity more widely available in a strengthened global system of enabling policies and increased capacities X X X X 2030 Outcome 2: Researchers, farmers, and students access diversity and associated data in a smarter and
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt1]
+RQ17 What proportion of marginalized beneficiaries in each market segment have accessed improved varieties? (AOW3 ID) RQ29 What extent of value proposition is needed to motivate adoption? KEQ2. To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? Coherence RQ4 How have the network strategies improved coherence with region x crop investments? (AOW5 E) RQ5 How have bottlenecks or barriers between variety development and seed systems been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E)
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p15pt4]
+intermediate outcomes that are not covered by any MELIA studies under the cross-cutting section should be entered under the relevant AoW-level outcome in the PORB
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p27pt1]
+27 Impact assessment efforts at the behavioral change level will focus on the 2030 Program Outcomes but also on unintended or unexpected significant outcomes highlighted through mid- term and final Outcome Evaluations and Policy change analyses (see Evaluation section). Data on behavioral changes will be monitored yearly through participatory outcome identification workshops with all partners engaged at the country/site level and outcome journals (see monitoring section). These yearly workshops at the country/site level are budgeted on the 20% non- assigned budget per center and have already been set aside by centers. The System Based Theory of Change approach will be applied to identify areas of success and prioritize the Outcome Evaluations (see
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3]
+the misuse of funds for purposes outside what is set up in the
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt1]
+Plan of results and budget 2025 | System Organization and center allocations | Page 50 of 52 August 2025 | CGIAR Area of Work 2: Strategic User Engagement 2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) 2030 Outcome 1: National and International genebanks conserve and make diversity more widely available in a strengthened global system of enabling policies and increased capacities X - 2030 Outcome 2: Researchers, farmers, and students access diversity and associated data in a
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt1]
+Learnings This review of CGIAR’s real-world outcomes and impacts provides valuable insights into how CGIAR generates and reports evidence. The experience of developing this report provided valuable learning opportunities to strengthen CGIAR’s evidence-generation and -aggregation processes so that future versions of this report may provide additional evidence. These insights are presented by topic. The 2022–2024 Results Framework At the outcome level, CGIAR Initiatives and Platforms report three types of outcomes: innovation use, policy change, and “other” outcomes. Although relatively few “other” outcomes were expected, well over 300 (28 percent) were reported. These correspond mainly to external engagement. In the future, consideration should be given to defining additional categories to reduce the number of “other” outcomes. In addition, CGIAR’s three Science Groups formulated a few key outcomes for their theories of change to which reported outcomes were mapped.
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p31pt1]
+31 IA studies Result Level Countries MELIA Study Type Frequency MELIA study and tools Evaluation questions Multifunctional Landscapes Results Dashboard Potential Indicators Program 2030 Outcomes Colombia, Peru, Tunisia, Kenya, India, Vietnam Outcome Evaluation Mid term (2028) Endline (2030) Outcome Evidencing/ Outcome Trajectory evaluation instruments: Document review, workshops, key informant interviews, secondary data System-based Theory of Change Actor engagement and outcome tracker AoW6 assessments AoW7 partner capacity evaluation • To what extent do multistakeholder engagement processes and co -design of science-based processes and tools lead to ownership of results by landscape stakeholders and therefore to the sustainable uptake of solutions? • Through which mechanisms does the multidisciplinary and transdisciplinary science promoted by the Multifunctional Landscapes program generate adoption of bundles of
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt3]
+gender-inclusive and climate smart policies and investments, represents Rapid Response and policy guidance pillar while 2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more coherent and sustainable development processes that deliver positive outcomes across a range of SDG targets, contributes to Agenda setting for our partners through research outputs. These Outcomes contributes to all of CGIAR Impact Areas, though the empahsis is on i) nutrition, health and food security; ii) poverty reduction, livelihoods and jobs; iii) climate adaptation and mitigation and iv) gender equality, Youth and social inclusion and to SDGs 1 (No Poverty), 8 (Decent Work and Economic Growth) and 10 (Reduced Inequalities). The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidate outputs from the 20 High -level outputs of the Policy Program. All Intermediate Outcomes
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p51pt2]
+(Approved Budget) Intermediate Outcome: National partners apply skills to the management and exchange of agrobiodiversity X X X X - 2030 Outcome 1: National and International genebanks conserve and make diversity more widely available in a strengthened global system of enabling policies and increased capacities X X X X 2030 Outcome 2: Researchers, farmers, and
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p27pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 27 of 52 Area of Work 4: Germplasm Health 2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) Intermediate Outcome: CGIAR and internal and external partners exchange genetic resources without the risk of spreading quarantine pests or diseases X X X X - 2030 Outcome 1: National and International genebanks conserve and make diversity more widely available in a strengthened global system of enabling policies and increased capacities X X X X 2030 Outcome 2: Researchers, farmers, and students access diversity and associated data in a smarter and more targeted
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt4]
+system that allow to capture outputs and outcomes real-time, based on an Output Tracker and an Actor Engagement and Outcome Journal, currently under development. These two tools will be filled on the go by the team of MELIA friends for reporting at the country level, and by AoW leads/co-leads for what concerns activities not specific to the country sites. We will follow recommendations from the CGIAR Technical Reporting Arrangement (TRA) 2025 –30 and input all required reporting information in the
+---
+[ID: pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p6pt2]
+foods? 2. How can animal and aquatic food systems support empowerment and create business opportunities and jobs for women, youth and marginalized groups? 3. What are the most effective scaling pathways to achieve SAAF outcomes combining effective partnerships, proven innovations, capacity sharing and supportive policies? 4. What are the best approaches to co-designing innovations and capacity-sharing approaches in specific contexts? 5. How do we most effectively influence, engage with and communicate to investors and policymakers the solutions, trade-offs and synergies of animal and aquatic sourced foods at the global, regional and national levels? After the CGIAR Science Week, we engaged with the Evaluability Assessment (EA) team by providing revised Theory of Change (ToC) diagrams. These revisions highlighted changes to the High -Level Outcomes (HLOs), intermediate outcomes, and 2030 outcomes. Since the overall logic of the ToC remained consistent, we did not share the narrative from the original
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt2]
+through which mechanisms agroecological and nature positive approaches, within a multifunctional landscape lens, optimize landscape multifunctionality? • What are the behavioral outcomes of such a multifunctional landscapes approach? For whom? Under what conditions? Behavior change studies are indispensable in understanding and addressing the human dimensions of agroecological transitions. By integrating socio -cultural, economic, and institutional insights, these studies ensure that interventions are not only scientifically robust but also socially acceptable and economically viable. Without excluding the analysis of other outcome generating processes, we will provide particular attention to the following outcome generating processes underlying the Program ToC: •
+---
+[ID: docx:2025 Technical Reporting MELIA glossary.docx:u28-31]
+Key result story | In-depth accounts of results that provide insight into CGIAR contribution to outcomes and/or impact. Each year, Programs and Accelerators are asked to report at least one key result story. | In-depth accounts of results that provide insight into CGIAR contribution to outcomes and/or impact. Each year, Programs and Accelerators are asked to report at least one key result story. | In-depth accounts of results that provide insight into CGIAR contribution to outcomes and/or impact. Each year, Programs and Accelerators are asked to report at least one key result story. Knowledge products | Knowledge products are intellectual assets generated from research and development activities such as articles, briefs, reports, extension and training content, databases, software, and multimedia elements that contribute to behavioural changes in particular actors. | Knowledge products are intellectual assets generated from research and development activities such as articles, briefs, reports, extension and training content, databases, software, and multimedia elements that contribute to behavioural changes in particular actors. | Knowledge products are intellectual assets generated from research and development activities such as articles, briefs, reports, extension and training content, databases, software, and multimedia elements that contribute to behavioural changes in particular actors. Outcome | A change in knowledge, attitudes, skills, and/or relationships (KASR), which manifests as a change in behaviour within the spheres of influence and interest, that results in whole or in part from the research and its outputs. Examples: use of a new technology (including outputs like a seed variety) by farmers; policy actors using research-based knowledge to inform policy decisions; participants in a CGIAR-supported process agree to new germplasm conservation and exchange protocols; researchers use CGIAR generated methods and/or databases. Key outcomes: Who will do what differently as a result of the Program/Accelerator/Project. | A change in knowledge, attitudes, skills, and/or relationships (KASR), which manifests as a change in behaviour within the spheres of influence and interest, that results in whole or in part from the research and its outputs. Examples: use of a new technology (including outputs like a seed variety) by farmers; policy actors using research-based knowledge to inform policy decisions; participants in a CGIAR-supported process agree to new germplasm conservation and exchange protocols; researchers use CGIAR generated methods and/or databases. Key outcomes: Who will do what differently as a result of the Program/Accelerator/Project. | A change in knowledge, attitudes, skills, and/or relationships (KASR), which manifests as a change in behaviour within the spheres of influence and interest, that results in whole or in part from the research and its outputs. Examples: use of a new technology (including outputs like a seed variety) by farmers; policy actors using research-based knowledge to inform policy decisions; participants in a CGIAR-supported process agree to new germplasm conservation and exchange protocols; researchers use CGIAR generated methods and/or databases. Key outcomes: Who will do what differently as a result of the Program/Accelerator/Project. Intermediate outcome | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different.
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u31-34]
+Nirmal, Rajalakshmi (IFPRI) 36:04 But. Colomer, Julien (One CGIAR - France) 36:06 Yeah, yeah. Basically anything that's not finished or nailed down, I get to answer for. So and then I SO look, 2025 is a Transition year and. We everybody recognizes like the amount of pressure that everyone's under. So that final step of transferring over the, let's say, key Performance indicator or target output and target outcome values from the window three and bilaterals into the theory of change. And into the planning module, et cetera, will not be done for the 2025 Technical report. So for the 2025 Technical report, IT being a Transition year, we want programs to report against the targets that they've already got in there obviously. And for the Window 3 bilats that have been mapped, we will really ask them to contribute the Results that they can contribute to in this first year. We have an objective and key result there for the System organization, which says that 80% of Window 3 bilats are included. In the Technical reports, exactly what is included is not defined. So we kind of have a bit of a Long leash there or You know, wide goal posts, but that's a discussion to have with centers and we'll be working with centers and with the Program and accelerators to better define like </t>
+  </si>
+  <si>
+    <t>[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4]
+breeding endeavors. While an earlier TOC showed the relationship between the outcomes of the initiatives, the revised TOC showed only one outcome of breeding. This outcome was ‘Seed producers successfully market new demand-driven improved varieties to more farmers’. The GI TOC essentially elevated the final output of the breeding pipeline to an outcome3, reverting to the breeding pipeline engineering view that dominates in breeding. In elevating the output to an outcome, any outcomes outside of breeding itself are diminished. Outcomes related to the quality of how breeding is done, with strategic prioritization, collaborative partnerships and efficiency have been omitted. It is these qualities of how breeding is done that build empowerment of regional partners and legacy beyond the lifecycle of a variety. 3 Note that it could be argued this is an outcome of Seed Equal. Regardless, it is not an outcome of GI, but one of the initiatives and this outcome could be achieved without investment or action in
+---
+[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2]
+leading to Intermediate Outcomes and finally to three 2030Outcomes, that correspond broadly to the three pillars. The first 2030 outcome focuses on Pillar C on capacity sharing; the 2nd outcome corresponds to Pillar B while the 3rd one addresses Pillar A.  2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs,  2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessment and governance to guide pro-poor, gender-inclusive and climate smart policies and investments  2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more coherent and sustainable development processes that deliver positive outcomes across a range of SDG targets. The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidates outputs from the 20 High-level outputs of the Policy Program. Multiple Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes
+---
+[ID: docx:Innovation use.docx:u1-4]
+Innovation use How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome levels. The development of an innovation (at various stages) is an output. The scaling, uptake and use of an innovation can be reported as outcome. In PRMS the results can be linked. What are the two ways to report innovation use results (outcomes)?
+---
+[ID: docx:General reporting guidance.docx:u1-3]
+General reporting guidance Is there guidance on what should be reported as a result? Yes, this document provides some principles for ensuring a focus on quality, rather than quantity, in terms of results reporting: Guidance on ensuring quality over quantity. Is there guidance available on how to distinguish between outputs and outcomes? Yes, information on what to report as an output or outcome can be found here: Guidance on reporting outputs or outcomes.
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4]
+CGIAR Results Framework – Portfolio Outcome
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p22pt4]
+CGIAR Results Framework – Portfolio Outcome
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt3]
+the Theories of Change (overall, Areas of Work and sub-Areas) for consistency and alignment with stated objectives. (more details in Section 3.1 of this report) We have revised the HLOs at sub-area of work level, to harmonize the approach, remove duplications, and prioritize. There are now 26 HLOs. − We have harmonized the intermediate outcomes across sub-AoWs, AoWs, and Accelerator level. There are now five intermediate outcomes for AoW on Solutions and three for AoW on Change. − We have moved one outcome from the intermediate level to the end-of-program level and there are now four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt3]
+Outcome Evidencing/ Outcome Trajectory evaluation instruments: Document review, workshops, key informant interviews, secondary data System-based Theory of Change Actor engagement and outcome tracker AoW6 assessments AoW7 partner capacity evaluation • To what extent does co -design of science-based processes and tools lead to ownership of results by landscape stakeholders and therefore to the sustainable uptake of solutions? • Number and type
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt2]
+in breeding contribute to increased rate of genetic gain, as captured in the extent of improvement and impact achieved by products. Efficiency is included in an intermediate outcome so any effectiveness evaluation of intermediate outcomes will be duplicative. This criterion is most relevant to AOW4 as it is designed to support efficient access and use of modernized breeding. An AOW level outcome has captured this so any effectiveness evaluation of outcomes will duplicate efficiency. Research questions will contribute to KEQ2 on effectiveness: To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? RQ12 How has the use of interoperable, scaled breeding tools and services increased
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p60pt4]
+in thriving Multifunctional Landscapes • Number of policy innovations that support the transition to sustained MFLs what was the contribution of the MFL Program interventions to these changes. This will allow us to identify the most impactful Outcomes related to the Impact Areas and orient Outcome Evidencing studies for efficient use of MELIA resources.
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1]
+Key Evaluation Questions Some guiding questions that will inform future evaluations include: • Are the Program’s assumptions about actor behavior, incentives, and influence valid for the specific stakeholders identified, and are they likely to lead to the intended outcomes? • How do differences in AoW presence across countries affect the Program’s ability to deliver its intended outcomes? • Are the current configurations of AoWs efficient and synergistic, or are there opportunities to increase impact through structural changes? • What mechanisms exist (or are lacking) to integrate bilateral and W3-funded results into core program planning and reporting? • To what extent is MELIA evidence used to inform planning, learning, and adaptation across the Program? • How well do program assumptions and outcome pathways reflect national priorities and systems capacities in each geography? • • What types of MELIA findings
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4]
+been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E) Effectiveness (the extent that the intended results or outcomes are achieved) High This criterion directly relates to the MELIA objectives. Assessing the effectiveness of the Intermediate Outcomes will inform contribution analysis and inform the design requirements of future programs. KEQ2. To what extent has B4T and its AOWs effectively achieved the intended intermediate outcomes? RQ2 How did prioritization using the Design Standard contribute to maximized impact (AOW1 MI)? RQ7 To what extent has B4T increased uptake of varieties by scaling partners who have a widespread reach (collectively)? (AOW3 ID) RQ8 To what extent has CGIAR-NARES prioritization of products encouraged targeted investment for breeding?
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3]
+of this report. Comparison with 2017–2021 Retrospective analysis of CGIAR’s 2017 to 2021 reporting cycle provides a reference point for assessing progress in outcome reporting and portfolio management under the current Results Framework. While differences in the reporting systems limit direct comparability, several structural patterns from the previous cycle remain relevant. Policy outcomes Learnings from CGIAR’s 2017 to 2021 reporting cycle demonstrate that policy outcomes were mostly oriented toward policies and strategies (75 percent), and the rest influenced budget and investment decisions or legal instruments.29 The majority reflected early uptake of research results, but 39 percent of policy outcomes were concrete decisions, policies, or programs taken or enacted. In the current 2022 to 2024 cycle, there was a slight increase in the percentage of reported policy changes that were actual policies or programs put into place (43 percent of policy outcomes). Moreover , the type of policy outcome differed, with the percentage of policy outcomes leading to modified programs or investments jumping to 29 percent. The thematic and geographic orientations of policy outcomes are similar across the two periods, generally displaying CGIAR effectiveness in all of its priority countries and across most of its Impact Areas. However , the percentage of policy outcomes which were aimed primarily at gender equality was low in both periods. Partners were critical to CGIAR’s success in informing policies. Critical partners included national and subnational governments, civil society organizations, private sector , regional bodies, and international organizations. The review of 2017 to 2021 policy outcomes also revealed that very few were evaluated for their impacts, yet many appeared to be significant. Some examples of those are in Table 3. Impacts of CGIAR’s policy research remain underanalyzed. Policy outcome type What the evidence shows Illustrative cases CGIAR partners Outcomes Policy and strategy outcomes, mainly at national level 60% of outcomes were national and 37% reached formal enactment— often when a ministry or regulatory body was part of the design team Ethiopian
+---
+[ID: docx:Innovation development.docx:u1-4]
+Innovation development How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome level. The development of an innovation (at various stages of design, testing and validation) is an output. The scaling or use of an innovation is an outcome. You may first report an innovation at the output level. If the innovation advances and starts to be used, it should then be reported as an outcome. Do I need to update innovations that were submitted during previous reporting periods?
+---
+[ID: docx:2025 Technical Reporting MELIA glossary.docx:u31-34]
+Intermediate outcome | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. 2030 outcome | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. Output | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. High-level output | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on).
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]
+four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the "challenges and megatrends" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt2]
+capacity &amp; tools. . The Program’s Theory of Change works through six interconnected Areas of Work (AoWs), their High- level Outputs (HLOs), leading to Intermediate Outcomes and finally to three 2030 Outcomes. During the inception phase the Policy Program align ed the Intermediate Outcomes and 2030 Outcomes to these 3 pillars. The 2030 Outcomes were revised to contribute to our impact around these. 2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs: represents the Capacity and tools pillar, 2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessm ent and governance to guide pro -poor, gender-inclusive and climate smart policies and investments, represents Rapid Response and policy guidance pillar while 2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt4]
+Growth) and 10 (Reduced Inequalities). The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidate outputs from the 20 High -level outputs of the Policy Program. All Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes 1.2.1 (Partners use outlook reports to inform and enhance design of their strategies and policies), 4.2.1 (Partners achieve a shared understanding of emerging ch allenges in WEFE systems and foresight data, tools and analysis), 5.2.1 (Countries co-create national strategies and policies) and 6.2.2 (CGIAR researchers and partners have enh anced capacity) all address the capacity challenge and contribute to the impact pathway achieving 2030 Outcome1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs. This 2030 Outcome in turn, also addresses CGIAR Portfolio Outcome #1: Implementation partners (e.g. NARES, NGOs, private companies) actively support
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p5pt2]
+2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) Intemediate Outcome: Crop Trust signs Long-Term Partnerships with CGIAR X X X X - Intermediate Outcome: CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness X X X X 2030 Outcome 1: National and International genebanks conserve and make diversity more widely available in a strengthened global system of enabling policies and increased capacities X X X X 2030 Outcome 2: Researchers, farmers, and students access diversity and associated data in a smarter and
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt1]
+RQ17 What proportion of marginalized beneficiaries in each market segment have accessed improved varieties? (AOW3 ID) RQ29 What extent of value proposition is needed to motivate adoption? KEQ2. To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? Coherence RQ4 How have the network strategies improved coherence with region x crop investments? (AOW5 E) RQ5 How have bottlenecks or barriers between variety development and seed systems been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E)
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p15pt4]
+intermediate outcomes that are not covered by any MELIA studies under the cross-cutting section should be entered under the relevant AoW-level outcome in the PORB
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p27pt1]
+27 Impact assessment efforts at the behavioral change level will focus on the 2030 Program Outcomes but also on unintended or unexpected significant outcomes highlighted through mid- term and final Outcome Evaluations and Policy change analyses (see Evaluation section). Data on behavioral changes will be monitored yearly through participatory outcome identification workshops with all partners engaged at the country/site level and outcome journals (see monitoring section). These yearly workshops at the country/site level are budgeted on the 20% non- assigned budget per center and have already been set aside by centers. The System Based Theory of Change approach will be applied to identify areas of success and prioritize the Outcome Evaluations (see
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3]
+the misuse of funds for purposes outside what is set up in the
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p50pt1]
+Plan of results and budget 2025 | System Organization and center allocations | Page 50 of 52 August 2025 | CGIAR Area of Work 2: Strategic User Engagement 2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) 2030 Outcome 1: National and International genebanks conserve and make diversity more widely available in a strengthened global system of enabling policies and increased capacities X - 2030 Outcome 2: Researchers, farmers, and students access diversity and associated data in a
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt1]
+Learnings This review of CGIAR’s real-world outcomes and impacts provides valuable insights into how CGIAR generates and reports evidence. The experience of developing this report provided valuable learning opportunities to strengthen CGIAR’s evidence-generation and -aggregation processes so that future versions of this report may provide additional evidence. These insights are presented by topic. The 2022–2024 Results Framework At the outcome level, CGIAR Initiatives and Platforms report three types of outcomes: innovation use, policy change, and “other” outcomes. Although relatively few “other” outcomes were expected, well over 300 (28 percent) were reported. These correspond mainly to external engagement. In the future, consideration should be given to defining additional categories to reduce the number of “other” outcomes. In addition, CGIAR’s three Science Groups formulated a few key outcomes for their theories of change to which reported outcomes were mapped.
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p31pt1]
+31 IA studies Result Level Countries MELIA Study Type Frequency MELIA study and tools Evaluation questions Multifunctional Landscapes Results Dashboard Potential Indicators Program 2030 Outcomes Colombia, Peru, Tunisia, Kenya, India, Vietnam Outcome Evaluation Mid term (2028) Endline (2030) Outcome Evidencing/ Outcome Trajectory evaluation instruments: Document review, workshops, key informant interviews, secondary data System-based Theory of Change Actor engagement and outcome tracker AoW6 assessments AoW7 partner capacity evaluation • To what extent do multistakeholder engagement processes and co -design of science-based processes and tools lead to ownership of results by landscape stakeholders and therefore to the sustainable uptake of solutions? • Through which mechanisms does the multidisciplinary and transdisciplinary science promoted by the Multifunctional Landscapes program generate adoption of bundles of
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt3]
+gender-inclusive and climate smart policies and investments, represents Rapid Response and policy guidance pillar while 2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more coherent and sustainable development processes that deliver positive outcomes across a range of SDG targets, contributes to Agenda setting for our partners through research outputs. These Outcomes contributes to all of CGIAR Impact Areas, though the empahsis is on i) nutrition, health and food security; ii) poverty reduction, livelihoods and jobs; iii) climate adaptation and mitigation and iv) gender equality, Youth and social inclusion and to SDGs 1 (No Poverty), 8 (Decent Work and Economic Growth) and 10 (Reduced Inequalities). The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidate outputs from the 20 High -level outputs of the Policy Program. All Intermediate Outcomes
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt4]
+system that allow to capture outputs and outcomes real-time, based on an Output Tracker and an Actor Engagement and Outcome Journal, currently under development. These two tools will be filled on the go by the team of MELIA friends for reporting at the country level, and by AoW leads/co-leads for what concerns activities not specific to the country sites. We will follow recommendations from the CGIAR Technical Reporting Arrangement (TRA) 2025 –30 and input all required reporting information in the
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p51pt2]
+(Approved Budget) Intermediate Outcome: National partners apply skills to the management and exchange of agrobiodiversity X X X X - 2030 Outcome 1: National and International genebanks conserve and make diversity more widely available in a strengthened global system of enabling policies and increased capacities X X X X 2030 Outcome 2: Researchers, farmers, and
+---
+[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p27pt1]
+CGIAR | August 2025 Plan of results and budget 2025 | System Organization and center allocations | Page 27 of 52 Area of Work 4: Germplasm Health 2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) Intermediate Outcome: CGIAR and internal and external partners exchange genetic resources without the risk of spreading quarantine pests or diseases X X X X - 2030 Outcome 1: National and International genebanks conserve and make diversity more widely available in a strengthened global system of enabling policies and increased capacities X X X X 2030 Outcome 2: Researchers, farmers, and students access diversity and associated data in a smarter and more targeted
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u31-34]
+Nirmal, Rajalakshmi (IFPRI) 36:04 But. Colomer, Julien (One CGIAR - France) 36:06 Yeah, yeah. Basically anything that's not finished or nailed down, I get to answer for. So and then I SO look, 2025 is a Transition year and. We everybody recognizes like the amount of pressure that everyone's under. So that final step of transferring over the, let's say, key Performance indicator or target output and target outcome values from the window three and bilaterals into the theory of change. And into the planning module, et cetera, will not be done for the 2025 Technical report. So for the 2025 Technical report, IT being a Transition year, we want programs to report against the targets that they've already got in there obviously. And for the Window 3 bilats that have been mapped, we will really ask them to contribute the Results that they can contribute to in this first year. We have an objective and key result there for the System organization, which says that 80% of Window 3 bilats are included. In the Technical reports, exactly what is included is not defined. So we kind of have a bit of a Long leash there or You know, wide goal posts, but that's a discussion to have with centers and we'll be working with centers and with the Program and accelerators to better define like what can be reported, what is the lowest cost. Path to report, et cetera for 2025. Now for 2026, however, Nicoletta put up that objective which said something like 100% of Program and accelerator plans and Results and budget and Technical reports, You know, allow for that sort of, You know, what did You plan, what did you? Deliver. And in that context, the 2026 plan of Results and budget and 2026 Technical reports, we will be asking the mapping of Window 3 bilateral targets down to the specific, You know, KPI within the high level outputs or at the intermediate outcome level. And then asking centres to then report against what they what they had planned. So that's gonna be for 2026 plan of Results and budget and the 2026 Technical report. 2025 is a Transition year. So that final step of transferring over the target information is not being done. Is that clear? Nirmal, Rajalakshmi (IFPRI) 38:32 Yeah. So for 2025, we are not reporting against bilateral projects in the RMS, right? Colomer, Julien (One CGIAR - France) 38:38 We will be, we will be. It's just that we will not be entering in target values. Yeah. So, SO I mean, unless that is useful in some way, like it's either if it's more useful to enter them in.
+---
+[ID: pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p6pt2]
+foods? 2. How can animal and aquatic food systems support empowerment and create business opportunities and jobs for women, youth and marginalized groups? 3. What are the most effective scaling pathways to achieve SAAF outcomes combining effective partnerships, proven innovations, capacity sharing and supportive policies? 4. What are the best approaches to co-designing innovations and capacity-sharing approaches in specific contexts? 5. How do we most effectively influence, engage with and communicate to investors and policymakers the solutions, trade-offs and synergies of animal and aquatic sourced foods at the global, regional and national levels? After the CGIAR Science Week, we engaged with the Evaluability Assessment (EA) team by providing revised Theory of Change (ToC) diagrams. These revisions highlighted changes to the High -Level Outcomes (HLOs), intermediate outcomes, and 2030 outcomes. Since the overall logic of the ToC remained consistent, we did not share the narrative from the original
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p24pt2]
+through which mechanisms agroecological and nature positive approaches, within a multifunctional landscape lens, optimize landscape multifunctionality? • What are the behavioral outcomes of such a multifunctional landscapes approach? For whom? Under what conditions? Behavior change studies are indispensable in understanding and addressing the human dimensions of agroecological transitions. By integrating socio -cultural, economic, and institutional insights, these studies ensure that interventions are not only scientifically robust but also socially acceptable and economically viable. Without excluding the analysis of other outcome generating processes, we will provide particular attention to the following outcome generating processes underlying the Program ToC: •
+---
+[ID: docx:2025 Technical Reporting MELIA glossary.docx:u28-31]
+Key result story | In-depth accounts of results that provide insight into CGIAR contribution to outcomes and/or impact. Each year, Programs and Accelerators are asked to report at least one key result story. | In-depth accounts of results that provide insight into CGIAR contribution to outcomes and/or impact. Each year, Programs and Accelerators are asked to report at least one key result story. | In-depth accounts of results that provide insight into CGIAR contribution to outcomes and/or impact. Each year, Programs and Accelerators are asked to report at least one key result story. Knowledge products | Knowledge products are intellectual assets generated from research and development activities such as articles, briefs, reports, extension and training content, databases, software, and multimedia elements that contribute to behavioural changes in particular actors. | Knowledge products are intellectual assets generated from research and development activities such as articles, briefs, reports, extension and training content, databases, software, and multimedia elements that contribute to behavioural changes in particular actors. | Knowledge products are intellectual assets generated from research and development activities such as articles, briefs, reports, extension and training content, databases, software, and multimedia elements that contribute to behavioural changes in particular actors. Outcome | A change in knowledge, attitudes, skills, and/or relationships (KASR), which manifests as a change in behaviour within the spheres of influence and interest, that results in whole or in part from the research and its outputs. Examples: use of a new technology (including outputs like a seed variety) by farmers; policy actors using research-based knowledge to inform policy decisions; participants in a CGIAR-supported process agree to new germplasm conservation and exchange protocols; researchers use CGIAR generated methods and/or databases. Key outcomes: Who will do what differently as a result of the Program/Accelerator/Project. | A change in knowledge, attitudes, skills, and/or relationships (KASR), which manifests as a change in behaviour within the spheres of influence and interest, that results in whole or in part from the research and its outputs. Examples: use of a new technology (including outputs like a seed variety) by farmers; policy actors using research-based knowledge to inform policy decisions; participants in a CGIAR-supported process agree to new germplasm conservation and exchange protocols; researchers use CGIAR generated methods a</t>
+  </si>
+  <si>
+    <t>[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4]
+breeding endeavors. While an earlier TOC showed the relationship between the outcomes of the initiatives, the revised TOC showed only one outcome of breeding. This outcome was ‘Seed producers successfully market new demand-driven improved varieties to more farmers’. The GI TOC essentially elevated the final output of the breeding pipeline to an outcome3, reverting to the breeding pipeline engineering view that dominates in breeding. In elevating the output to an outcome, any outcomes outside of breeding itself are diminished. Outcomes related to the quality of how breeding is done, with strategic prioritization, collaborative partnerships and efficiency have been omitted. It is these qualities of how breeding is done that build empowerment of regional partners and legacy beyond the lifecycle of a variety. 3 Note that it could be argued this is an outcome of Seed Equal. Regardless, it is not an outcome of GI, but one of the initiatives and this outcome could be achieved without investment or action in
+---
+[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2]
+leading to Intermediate Outcomes and finally to three 2030Outcomes, that correspond broadly to the three pillars. The first 2030 outcome focuses on Pillar C on capacity sharing; the 2nd outcome corresponds to Pillar B while the 3rd one addresses Pillar A.  2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs,  2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessment and governance to guide pro-poor, gender-inclusive and climate smart policies and investments  2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more coherent and sustainable development processes that deliver positive outcomes across a range of SDG targets. The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidates outputs from the 20 High-level outputs of the Policy Program. Multiple Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes
+---
+[ID: docx:Innovation use.docx:u1-4]
+Innovation use How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome levels. The development of an innovation (at various stages) is an output. The scaling, uptake and use of an innovation can be reported as outcome. In PRMS the results can be linked. What are the two ways to report innovation use results (outcomes)?
+---
+[ID: docx:General reporting guidance.docx:u1-3]
+General reporting guidance Is there guidance on what should be reported as a result? Yes, this document provides some principles for ensuring a focus on quality, rather than quantity, in terms of results reporting: Guidance on ensuring quality over quantity. Is there guidance available on how to distinguish between outputs and outcomes? Yes, information on what to report as an output or outcome can be found here: Guidance on reporting outputs or outcomes.
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt3]
+the Theories of Change (overall, Areas of Work and sub-Areas) for consistency and alignment with stated objectives. (more details in Section 3.1 of this report) We have revised the HLOs at sub-area of work level, to harmonize the approach, remove duplications, and prioritize. There are now 26 HLOs. − We have harmonized the intermediate outcomes across sub-AoWs, AoWs, and Accelerator level. There are now five intermediate outcomes for AoW on Solutions and three for AoW on Change. − We have moved one outcome from the intermediate level to the end-of-program level and there are now four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and
+---
+[ID: pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p18pt4]
+better understand farmer perspectives, motivations, and constraints concerning the adoption of SFP innovations. 4. Adoption or diffusion studies addressing learning questions on the TOC The baseline surveys conducted in Ghana, Malawi, and Ethiopia focusing on sustainable intensification technologies will form the basis for the adoption and impacts studies. These studies will seek to answer the following causal impact learning questions: ( 1) What factors are constraining/enabling the scaling and adoption as well as the intensity of use of the SFP innovations? and (2) How does adoption of the SFP innovations impact yield, farm income and household income? (3) What are the most promising inte grated farm -level innovation bundles to improve sustainability, equity, and agronomic gain at scale within the selected geographies of the program? To answer these questions, adoption and impact studies build up on the baseline studies (panel survey) to assess the extent, pathways, and determinants of
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4]
+been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E) Effectiveness (the extent that the intended results or outcomes are achieved) High This criterion directly relates to the MELIA objectives. Assessing the effectiveness of the Intermediate Outcomes will inform contribution analysis and inform the design requirements of future programs. KEQ2. To what extent has B4T and its AOWs effectively achieved the intended intermediate outcomes? RQ2 How did prioritization using the Design Standard contribute to maximized impact (AOW1 MI)? RQ7 To what extent has B4T increased uptake of varieties by scaling partners who have a widespread reach (collectively)? (AOW3 ID) RQ8 To what extent has CGIAR-NARES prioritization of products encouraged targeted investment for breeding?
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]
+four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the "challenges and megatrends" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1]
+Key Evaluation Questions Some guiding questions that will inform future evaluations include: • Are the Program’s assumptions about actor behavior, incentives, and influence valid for the specific stakeholders identified, and are they likely to lead to the intended outcomes? • How do differences in AoW presence across countries affect the Program’s ability to deliver its intended outcomes? • Are the current configurations of AoWs efficient and synergistic, or are there opportunities to increase impact through structural changes? • What mechanisms exist (or are lacking) to integrate bilateral and W3-funded results into core program planning and reporting? • To what extent is MELIA evidence used to inform planning, learning, and adaptation across the Program? • How well do program assumptions and outcome pathways reflect national priorities and systems capacities in each geography? • • What types of MELIA findings
+---
+[ID: docx:2025 Technical Reporting MELIA glossary.docx:u31-34]
+Intermediate outcome | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. 2030 outcome | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. Output | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. High-level output | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on).
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3]
+of this report. Comparison with 2017–2021 Retrospective analysis of CGIAR’s 2017 to 2021 reporting cycle provides a reference point for assessing progress in outcome reporting and portfolio management under the current Results Framework. While differences in the reporting systems limit direct comparability, several structural patterns from the previous cycle remain relevant. Policy outcomes Learnings from CGIAR’s 2017 to 2021 reporting cycle demonstrate that policy outcomes were mostly oriented toward policies and strategies (75 percent), and the rest influenced budget and investment decisions or legal instruments.29 The majority reflected early uptake of research results, but 39 percent of policy outcomes were concrete decisions, policies, or programs taken or enacted. In the current 2022 to 2024 cycle, there was a slight increase in the percentage of reported policy changes that were actual policies or programs put into place (43 percent of policy outcomes). Moreover , the type of policy outcome differed, with the percentage of policy outcomes leading to modified programs or investments jumping to 29 percent. The thematic and geographic orientations of policy outcomes are similar across the two periods, generally displaying CGIAR effectiveness in all of its priority countries and across most of its Impact Areas. However , the percentage of policy outcomes which were aimed primarily at gender equality was low in both periods. Partners were critical to CGIAR’s success in informing policies. Critical partners included national and subnational governments, civil society organizations, private sector , regional bodies, and international organizations. The review of 2017 to 2021 policy outcomes also revealed that very few were evaluated for their impacts, yet many appeared to be significant. Some examples of those are in Table 3. Impacts of CGIAR’s policy research remain underanalyzed. Policy outcome type What the evidence shows Illustrative cases CGIAR partners Outcomes Policy and strategy outcomes, mainly at national level 60% of outcomes were national and 37% reached formal enactment— often when a ministry or regulatory body was part of the design team Ethiopian
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt2]
+in breeding contribute to increased rate of genetic gain, as captured in the extent of improvement and impact achieved by products. Efficiency is included in an intermediate outcome so any effectiveness evaluation of intermediate outcomes will be duplicative. This criterion is most relevant to AOW4 as it is designed to support efficient access and use of modernized breeding. An AOW level outcome has captured this so any effectiveness evaluation of outcomes will duplicate efficiency. Research questions will contribute to KEQ2 on effectiveness: To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? RQ12 How has the use of interoperable, scaled breeding tools and services increased
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p60pt4]
+in thriving Multifunctional Landscapes • Number of policy innovations that support the transition to sustained MFLs what was the contribution of the MFL Program interventions to these changes. This will allow us to identify the most impactful Outcomes related to the Impact Areas and orient Outcome Evidencing studies for efficient use of MELIA resources.
+---
+[ID: docx:Innovation development.docx:u1-4]
+Innovation development How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome level. The development of an innovation (at various stages of design, testing and validation) is an output. The scaling or use of an innovation is an outcome. You may first report an innovation at the output level. If the innovation advances and starts to be used, it should then be reported as an outcome. Do I need to update innovations that were submitted during previous reporting periods?
+---
+[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]
+activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt4]
+Growth) and 10 (Reduced Inequalities). The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidate outputs from the 20 High -level outputs of the Policy Program. All Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes 1.2.1 (Partners use outlook reports to inform and enhance design of their strategies and policies), 4.2.1 (Partners achieve a shared understanding of emerging ch allenges in WEFE systems and foresight data, tools and analysis), 5.2.1 (Countries co-create national strategies and policies) and 6.2.2 (CGIAR researchers and partners have enh anced capacity) all address the capacity challenge and contribute to the impact pathway achieving 2030 Outcome1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs. This 2030 Outcome in turn, also addresses CGIAR Portfolio Outcome #1: Implementation partners (e.g. NARES, NGOs, private companies) actively support
+---
+[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3]
+the misuse of funds for purposes outside what is set up in the
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt1]
+RQ17 What proportion of marginalized beneficiaries in each market segment have accessed improved varieties? (AOW3 ID) RQ29 What extent of value proposition is needed to motivate adoption? KEQ2. To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? Coherence RQ4 How have the network strategies improved coherence with region x crop investments? (AOW5 E) RQ5 How have bottlenecks or barriers between variety development and seed systems been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E)
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt2]
+capacity &amp; tools. . The Program’s Theory of Change works through six interconnected Areas of Work (AoWs), their High- level Outputs (HLOs), leading to Intermediate Outcomes and finally to three 2030 Outcomes. During the inception phase the Policy Program align ed the Intermediate Outcomes and 2030 Outcomes to these 3 pillars. The 2030 Outcomes were revised to contribute to our impact around these. 2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs: represents the Capacity and tools pillar, 2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessm ent and governance to guide pro -poor, gender-inclusive and climate smart policies and investments, represents Rapid Response and policy guidance pillar while 2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more
+---
+[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt3]
+Outcome Evidencing/ Outcome Trajectory evaluation instruments: Document review, workshops, key informant interviews, secondary data System-based Theory of Change Actor engagement and outcome tracker AoW6 assessments AoW7 partner capacity evaluation • To what extent does co -design of science-based processes and tools lead to ownership of results by landscape stakeholders and therefore to the sustainable uptake of solutions? • Number and type
+---
+[ID: pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p6pt2]
+foods? 2. How can animal and aquatic food systems support empowerment and create business opportunities and jobs for women, youth and marginalized groups? 3. What are the most effective scaling pathways to achieve SAAF outcomes combining effective partnerships, proven innovations, capacity sharing and supportive policies? 4. What are the best approaches to co-designing innovations and capacity-sharing approaches in specific contexts? 5. How do we most effectively influence, engage with and communicate to investors and policymakers the solutions, trade-offs and synergies of animal and aquatic sourced foods at the global, regional and national levels? After the CGIAR Science Week, we engaged with the Evaluability Assessment (EA) team by providing revised Theory of Change (ToC) diagrams. These revisions highlighted changes to the High -Level Outcomes (HLOs), intermediate outcomes, and 2030 outcomes. Since the overall logic of the ToC remained consistent, we did not share the narrative from the original
+---
+[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt1]
+Learnings This review of CGIAR’s real-world outcomes and impacts provides valuable insights into how CGIAR generates and reports evidence. The experience of developing this report provided valuable learning opportunities to strengthen CGIAR’s evidence-generation and -aggregation processes so that future versions of this report may provide additional evidence. These insights are presented by topic. The 2022–2024 Results Framework At the outcome level, CGIAR Initiatives and Platforms report three types of outcomes: innovation use, policy change, and “other” outcomes. Although relatively few “other” outcomes were expected, well over 300 (28 percent) were reported. These correspond mainly to external engagement. In the future, consideration should be given to defining additional categories to reduce the number of “other” outcomes. In addition, CGIAR’s three Science Groups formulated a few key outcomes for their theories of change to which reported outcomes were mapped.
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4]
+CGIAR Results Framework – Portfolio Outcome
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p22pt4]
+CGIAR Results Framework – Portfolio Outcome
+---
+[ID: docx:2025 Technical Reporting MELIA glossary.docx:u28-31]
+Key result story | In-depth accounts of results that provide insight into CGIAR contribution to outcomes and/or impact. Each year, Programs and Accelerators are asked to report at least one key result story. | In-depth accounts of results that provide insight into CGIAR contribution to outcomes and/or impact. Each year, Programs and Accelerators are asked to report at least one key result story. | In-depth accounts of results that provide insight into CGIAR contribution to outcomes and/or impact. Each year, Programs and Accelerators are asked to report at least one key result story. Knowledge products | Knowledge products are intellectual assets generated from research and development activities such as articles, briefs, reports, extension and training content, databases, software, and multimedia elements that contribute to behavioural changes in particular actors. | Knowledge products are intellectual assets generated from research and development activities such as articles, briefs, reports, extension and training content, databases, software, and multimedia elements that contribute to behavioural changes in particular actors. | Knowledge products are intellectual assets generated from research and development activities such as articles, briefs, reports, extension and training content, databases, software, and multimedia elements that contribute to behavioural changes in particular actors. Outcome | A change in knowledge, attitudes, skills, and/or relationships (KASR), which manifests as a change in behaviour within the spheres of influence and interest, that results in whole or in part from the research and its outputs. Examples: use of a new technology (including outputs like a seed variety) by farmers; policy actors using research-based knowledge to inform policy decisions; participants in a CGIAR-supported process agree to new germplasm conservation and exchange protocols; researchers use CGIAR generated methods and/or databases. Key outcomes: Who will do what differently as a result of the Program/Accelerator/Project. | A change in knowledge, attitudes, skills, and/or relationships (KASR), which manifests as a change in behaviour within the spheres of influence and interest, that results in whole or in part from the research and its outputs. Examples: use of a new technology (including outputs like a seed variety) by farmers; policy actors using research-based knowledge to inform policy decisions; participants in a CGIAR-supported process agree to new germplasm conservation and exchange protocols; researchers use CGIAR generated methods and/or databases. Key outcomes: Who will do what differently as a result of the Program/Accelerator/Project. | A change in knowledge, attitudes, skills, and/or relationships (KASR), which manifests as a change in behaviour within the spheres of influence and interest, that results in whole or in part from the research and its outputs. Examples: use of a new technology (including outputs like a seed variety) by farmers; policy actors using research-based knowledge to inform policy decisions; participants in a CGIAR-supported process agree to new germplasm conservation and exchange protocols; researchers use CGIAR generated methods and/or databases. Key outcomes: Who will do what differently as a result of the Program/Accelerator/Project. Intermediate outcome | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different.
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt3]
+gender-inclusive and climate smart policies and investments, represents Rapid Response and policy guidance pillar while 2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more coherent and sustainable development processes that deliver positive outcomes across a range of SDG targets, contributes to Agenda setting for our partners through research outputs. These Outcomes contributes to all of CGIAR Impact Areas, though the empahsis is on i) nutrition, health and food security; ii) poverty reduction, livelihoods and jobs; iii) climate adaptation and mitigation and iv) gender equality, Youth and social inclusion and to SDGs 1 (No Poverty), 8 (Decent Work and Economic Growth) and 10 (Reduced Inequalities). The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidate outputs from the 20 High -level outputs of the Policy Program. All Intermediate Outcomes
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p31pt2]
+has CGIAR-NARES prioritization of products encouraged targeted investment for breeding? (AOW2 AB) RQ9 To what extent has the amount and quality of active collaboration on products increased? (AOW5 E) RQ11 To what extent has B4T influenced more equitable access to improved varieties by marginalized groups? (AOW3 ID) RQ27 To what extent have interoperable tools and services
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u31-34]
+Nirmal, Rajalakshmi (IFPRI) 36:04 But. Colomer, Julien (One CGIAR - France) 36:06 Yeah, yeah. Basically anything that's not finished or nailed down, I get to answer for. So and then I SO look, 2025 is a Transition year and. We everybody recognizes like the amount of pressure that everyone's under. So that final step of transferring over the, let's say, key Performance indicator or target output and target outcome values from the window three and bilaterals into the theory of change. And into the planning module, et cetera, will not be done for the 2025 Technical report. So for the 2025 Technical report, IT being a Transition year, we want programs to report against the targets that they've already got in there obviously. And for the Window 3 bilats that have been mapped, we will really ask them to contribute the Results that they can contribute to in this first year. We have an objective and key result there for the System organization, which says that 80% of Window 3 bilats are included. In the Technical reports, exactly what is included is not defined. So we kind of have a bit of a Long leash there or You know, wide goal posts, but that's a discussion to have with centers and we'll be working with centers and with the Program and accelerators to better define like what can be reported, what is the lowest cost. Path to report, et cetera for 2025. Now for 2026, however, Nicoletta put up that objective which said something like 100% of Program and accelerator plans and Results and budget and Technical reports, You know, allow for that sort of, You know, what did You plan, what did you? Deliver. And in that context, the 2026 plan of Results and budget and 2026 Technical reports, we will be asking the mapping of Window 3 bilateral targets down to the specific, You know, KPI within the high level outputs or at the intermediate outcome level. And then asking centres to then report against what they what they had planned. So that's gonna be for 2026 plan of Results and budget and the 2026 Technical report. 2025 is a Transition year. So that final step of transferring over the target information is not being done. Is that clear? Nirmal, Rajalakshmi (IFPRI) 38:32 Yeah. So for 2025, we are not reporting against bilateral projects in the RMS, right? Colomer, Julien (One CGIAR - France) 38:38 We will be, we will be. It's just that we will not be entering in target values. Yeah. So, SO I mean, unless that is useful in some way, like it's either if it's more useful to enter them in.
+---
+[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p13pt2]
+agrifood system actors use metrics and analytics to understand and monitor progress in addressing structural barriers to gender equality and social inclusion; and ultimately; 4. Women, youth, and socially excluded groups have equitably benefited from innovations designed to enhance sustainability and outcomes from agrifood systems. These outcomes are interconnected and interdependent, and the achievement of each is not linear. The achievement of the first three outcomes is also a precondition to the achievement of the fourth 2030 outcome. The 2030 outcomes will be achieved through the two interconnected AoWs. Since the original proposal, we have updated the high-level outputs across the two AoWs, to harmonize and clarify what key offerings the Accelerator will produce by the end of 2030. AoW on Solutions: The Accelerator’s first impact pathway will mostly be pursued through this AoW by working with partners on the ground. The AoW on Solutions builds on a conceptual framework that surfaces four
+---
+[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p9pt1]
+Program and Accelerator MELIA Plan Update Template and Guidance I March 2025 9 1. Monitoring plan for HLOs and outcomes This section outlines how the Policy Program will monitor delivery of HLOs and progress towards outcomes. For tracking progress, the high -level outputs (HLOs) and intermediate outcomes, are each supported by specific activities detailed in the Program of Work and Budget (POWB). This framework serves as the foundation for monitoring progress, ensuring not only the implementation of activities but also the validation of underlying assumptio ns to achieve the anticipated changes. Targets were developed consultatively within the AoWs but also corroborated at the Program level since this determines the overall targets committed for the 2030 Outcomes. Data collection strategy The Results Framework details the HLOs , Intermediate Outcomes and 2030 Outcomes they c</t>
+  </si>
+  <si>
+    <t>[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt1]
+Results framework The program result
+---
+[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p6pt2]
+Work 2.3 Results framework The CapSha Accelerator results framework has been
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4]
+CGIAR Results Framework – Portfolio Outcome
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p22pt4]
+CGIAR Results Framework – Portfolio Outcome
+---
+[ID: pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p21pt2]
+types For reference only, the current MELIA study types defined in
+---
+[ID: pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p7pt1]
+CGIAR Performance and Results Management Framework 2022-2030 CGIAR System Organization Page 7 of 20 4. Results framework CGIAR’s results framework is directly aligned to the five impact areas and Sustainable Development Goals. Three distinct result types: outputs, outcomes and impacts are mapped to the spheres of Control, Influence and Interest, respectively. • Output: Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples of outputs include new research methods, policy analyses, gene maps, new crop varieties and breeds, or other products of research work. • Outcome: A change in knowledge, skills, attitudes and/or relationships, which manifests as a change in behavior of users of outputs, to which a combination of research outputs and related activities have contributed. •
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt1]
+CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p5pt1]
+CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt3]
+portfolio-level outcome, and portfolio level contribution to Impact Area targets reporting. The foundations of the current Results Framework (2022-24) remain: • Impact Areas linked to Sustainable Development Goals • Impact, outcome, and output result levels • Result types/categories o Outcome: Innovation use, Policy change, Other. o Output: Innovation development, Capacity sharing, Knowledge products, Other • A small number of Standard Indicators The updated CGIAR Results Framework in Annex 1 will be finalized in Q1-2 2025. The m ain updates included in the 2025-30 Results Framework include: • Revised Impact Area indicators Shortcomings with the Impact Area indicators in the 2022-24 Results Framework have been identified, including absence of some important indicators for CGIAR (e.g.
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt3]
+portfolio-level outcome, and portfolio level contribution to Impact Area targets reporting. The foundations of the current Results Framework (2022-24) remain: • Impact Areas linked to Sustainable Development Goals • Impact, outcome, and output result levels • Result types/categories o Outcome: Innovation use, Policy change, Other. o Output: Innovation development, Capacity sharing, Knowledge products, Other • A small number of Standard Indicators The updated CGIAR Results Framework in Annex 1 will be finalized in Q1-2 2025. The m ain updates included in the 2025-30 Results Framework include: • Revised Impact Area indicators Shortcomings with the Impact Area indicators in the 2022-24 Results Framework have been identified, including absence of some important indicators for CGIAR (e.g.
+---
+[ID: pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p9pt3]
+Results Framework Please refer
+---
+[ID: pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p28pt2]
+4. MELIA study types For reference only, the current MELIA study types
+---
+[ID: docx:2025 Technical Reporting MELIA glossary.docx:u55-58]
+Policy change | Policies, strategies, legal instruments, programs, budgets, or investments at different scales (local to global) that have been modified in design or implementation, with evidence that the change was informed by CGIAR research. | Policies, strategies, legal instruments, programs, budgets, or investments at different scales (local to global) that have been modified in design or implementation, with evidence that the change was informed by CGIAR research. | Policies, strategies, legal instruments, programs, budgets, or investments at different scales (local to global) that have been modified in design or implementation, with evidence that the change was informed by CGIAR research. Portfolio | The CGIAR System Framework approved by the System’s Funders and Centers in June 2016, and then amended in October 2024, defines “CGIAR Portfolio” as the research programs and/or platforms carried out by the Centers and the CGIAR System Partners in support of the CGIAR Strategy and Results Framework and which are supported by (i) the CGIAR Trust Fund and/or (ii) bilateral sources contractually aligned to such programs and/or platforms. | The CGIAR System Framework approved by the System’s Funders and Centers in June 2016, and then amended in October 2024, defines “CGIAR Portfolio” as the research programs and/or platforms carried out by the Centers and the CGIAR System Partners in support of the CGIAR Strategy and Results Framework and which are supported by (i) the CGIAR Trust Fund and/or (ii) bilateral sources contractually aligned to such programs and/or platforms. | The CGIAR System Framework approved by the System’s Funders and Centers in June 2016, and then amended in October 2024, defines “CGIAR Portfolio” as the research programs and/or platforms carried out by the Centers and the CGIAR System Partners in support of the CGIAR Strategy and Results Framework and which are supported by (i) the CGIAR Trust Fund and/or (ii) bilateral sources contractually aligned to such programs and/or platforms. Program | CGIAR Programs are the main vehicle for delivery of research and innovation by CGIAR from 2025 to 2030. Programs serve as entry points to describe CGIAR’s offer on a key topic, elevating CGIAR’s visibility in global agendas and facilitating the continuation and formation of inclusive alliances and partnerships. They state quantitatively what impacts and outcomes they intend to achieve, along a theory of change. They come with evaluable results frameworks and clear reporting of results against investment. Bilateral and window 3 projects are aligned to Programs and Accelerators and their results are reported as part of Program and Accelerator reporting. | CGIAR Programs are the main vehicle for delivery of research and innovation by CGIAR from 2025 to 2030. Programs serve as entry points to describe CGIAR’s offer on a key topic, elevating CGIAR’s visibility in global agendas and facilitating the continuation and formation of inclusive alliances and partnerships. They state quantitatively what impacts and outcomes they intend to achieve, along a theory of change. They come with evaluable results frameworks and clear reporting of results against investment. Bilateral and window 3 projects are aligned to Programs and Accelerators and their results are reported as part of Program and Accelerator reporting. | CGIAR Programs are the main vehicle for delivery of research and innovation by CGIAR from 2025 to 2030. Programs serve as entry points to describe CGIAR’s offer on a key topic, elevating CGIAR’s visibility in global agendas and facilitating the continuation and formation of inclusive alliances and partnerships. They state quantitatively what impacts and outcomes they intend to achieve, along a theory of change. They come with evaluable results frameworks and clear reporting of results against investment. Bilateral and window 3 projects are aligned to Programs and Accelerators and their results are reported as part of Program and Accelerator reporting. Result | The product of an activity by CGIAR staff or due in part to CGIAR staff, described as an output, outcome or impact. | The product of an activity by CGIAR staff or due in part to CGIAR staff, described as an output, outcome or impact. | The product of an activity by CGIAR staff or due in part to CGIAR staff, described as an output, outcome or impact.
+---
+[ID: pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p9pt2]
+Mitigation, Nutrition, Poverty Reduction and Livelihoods, Gender Equality and Social Inclusion, and Environmental Health and Biodiversity. The SFP results framework operationalizes this contribution by aligning program indicators and learning activities with CGIAR’s Performance and Results Management Framework (PRMF) and systematically collect evidence across the eight AoWs. Each AoW is designed to deliver results that directly or indirectly support one or more CGIAR Impact Areas. The framework provides a coherent roadmap for measuring the SFP contributions. Open Access link for both the ToC and the Results Framework . (Download the Results Framework as part of several other worksheets-e.g., assumptions, research questions, etc using the 3rd icon on the top left conner of the page). 3. Monitoring plan for HLOs and outcomes This section outlines how the Program will monitor delivery of HLOs and progress towards
+---
+[ID: pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt1]
+7 Results framework The Result Framework presents a structured articulation of the intended results under CGIAR’s strategic Areas of Work (AOWs) for the period 2025 to 2030. It distinguishes between two types of results: High-Level Outputs (HLOs), which represent tangible, near-term deliverables from research eƯorts, and Intermediate Outcomes (IOCs), which indicate progress toward longer- term development goals and systemic change. Each result entry captures several key variables—among many others—that collectively deﬁne the pathway from research to impact. These include the thematic Area of Work to which the result contributes, the classiﬁcation of the result as either an output or outcome, and a short title paired with a detailed result statement that describes the intended change, innovation, or contribution. The responsible organization(s), often CGIAR centers, are identiﬁed alongside any listed partners and outcome actors, with additional information on whether those actors are directly engaged and what
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p16pt1]
+CGIAR Technical Reporting Arrangement 2025-30 June 2025 16 In doing so the line of sight will primarily focus on the outputs produced with pooled resources (sphere of control) while the outcomes are co -produced and do not require differentiation by source of funding. The rate of change Because Technical Report products will progressively integrate bilateral and W3 information, we expect that they will contain differing levels and types of W3 and bilateral project technical content (e.g. results data and narrative) and that this will evolve over time. There are likely to be different levels of bilateral and W3 technical information:
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p16pt1]
+CGIAR Technical Reporting Arrangement 2025-30 June 2025 16 In doing so the line of sight will primarily focus on the outputs produced with pooled resources (sphere of control) while the outcomes are co -produced and do not require differentiation by source of funding. The rate of change Because Technical Report products will progressively integrate bilateral and W3 information, we expect that they will contain differing levels and types of W3 and bilateral project technical content (e.g. results data and narrative) and that this will evolve over time. There are likely to be different levels of bilateral and W3 technical information:
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt2]
+result framework is accessible from
+---
+[ID: pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p8pt2]
+the Program and Area of Work levels. This link gives the ToC tables-overall and AoW ToCs) and Open Access link for both the ToC and the Results Framework . (Zoom out to see the linkages of the various AoW ToCs and download the ToC tables using the 4 th icon on the top left conner of the page). Figure 1. Sustainable Farming Program level Theory of Change Results framework The SFP Results Framework reflects the logical sequence from high-level outputs to intermediate outcomes, aligned with the program’s Theory of Change. It captures the intended contributions of each AoW,
+---
+[ID: docx:2025 Technical Reporting MELIA glossary.docx:u34-37]
+High-level output | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). Partner | Organizations or individual stakeholders that CGIAR collaborates with to achieve its goals for which proof exists, i.e., memorandum of understanding, joint code of practice, a contract under a joint proposal. Partners can also be beneficiaries of CGIAR’s interventions. Examples: demand partner, innovation partner and scaling partner. | Organizations or individual stakeholders that CGIAR collaborates with to achieve its goals for which proof exists, i.e., memorandum of understanding, joint code of practice, a contract under a joint proposal. Partners can also be beneficiaries of CGIAR’s interventions. Examples: demand partner, innovation partner and scaling partner. | Organizations or individual stakeholders that CGIAR collaborates with to achieve its goals for which proof exists, i.e., memorandum of understanding, joint code of practice, a contract under a joint proposal. Partners can also be beneficiaries of CGIAR’s interventions. Examples: demand partner, innovation partner and scaling partner. Partner typology (CGIAR) | CGIAR uses a partner typology to define partner types. Definitions are presented below. | CGIAR uses a partner typology to define partner types. Definitions are presented below. | CGIAR uses a partner typology to define partner types. Definitions are presented below. Partner typology (CGIAR) | CGIAR type | CGIAR type definition
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p32pt3]
+tab in the program result s framework accessible
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt2]
+Reporting. We will progressively add curated datasets (such as Center-level databases) into the QA process to remove to the extent possible the need for double reporting. Existing experience gained through automated PRMS solutions (e.g. screening knowledge products against FAIR criteria) will be leveraged. 3. CGIAR Results Framework, MELIA, Indicator Toolkit and data collection protocols CGIAR Results Framework The CGIAR Results Framework will be used by Programs and Accelerators as the basis of their TOC design, MELIA and Technical Reporting. It will provide the basis for geographic portfolio-level outcome, and portfolio level contribution to Impact Area targets reporting. The foundations of the current Results Framework (2022-24) remain: • Impact Areas linked to Sustainable Development Goals
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt2]
+Reporting. We will progressively add curated datasets (such as Center-level databases) into the QA process to remove to the extent possible the need for double reporting. Existing experience gained through automated PRMS solutions (e.g. screening knowledge products against FAIR criteria) will be leveraged. 3. CGIAR Results Framework, MELIA, Indicator Toolkit and data collection protocols CGIAR Results Framework The CGIAR Results Framework will be used by Programs and Accelerators as the basis of their TOC design, MELIA and Technical Reporting. It will provide the basis for geographic portfolio-level outcome, and portfolio level contribution to Impact Area targets reporting. The foundations of the current Results Framework (2022-24) remain: • Impact Areas linked to Sustainable Development Goals
+---
+[ID: pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p3pt1]
+3 1. Reviewing guidance for developing the MELIA Plan Developing the Sustainable Farming program (SFP) MELIA plan, started with the review of the ISDC feedback on the overall program Theory of Change (ToC) and the Area of Work (AoW) ToCs. This feedback has been used in updating the ToC, (example, creating indicators for AoW 8 - Program Efficiency and Delivery . In addition, the core assessment criteria from the IAES evaluability assessment guide were used as reference checks in developing the MELIA plan. 2. Program overview and results framework This section provides a n overview of the Sustainable Farming Program (SFP), outlining its intervention logic and the results framework. It also details the alignment of the Program’s results framework with the CGIAR Performance and Results Management Framework (PRMF) and Portfolio outcomes, ensuring system thinking. Program overview SFP is designed to respond to
+---
+[ID: pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p18pt3]
+2030 Outcome, or Impact Indicate the result short title from the Results Framework Indicate the indicator title from the Results Framework Provide the assumption( s) statem ent from the Results Framework Indicate the location(s) where the study will be conducted Indicate the methods and design approaches that will be used for the study List the Program(s) and Accelerator( s ) you will collaborate with or coordinate for the implementati on of this study. Indicate the Start
+---
+[ID: pdf:Type3_2024Report.pdf:p11pt4]
+System (PRMS): The PRMS serves as the central reporting platform, powering the Results Dashboard and supporting the development of Type 1 Reports with real-time data aggregation and analysis. These components were instrumental in driving the 2024 Technical Reporting process, and key elements will be carried forward to shape Technical Reporting in the next CGIAR Portfolio, ensuring continuity, alignment, and continuous improvement. Monitoring tools tailored to suit core indicators Non-pooled projects Type 1 Type 3 Science Group Projects Research and Performance and Results Management Framework Arrangement CGIAR Results Framework Standard Indicator Theory of Change and Scaling Readiness (IPSR) Quality Assurance criteria, process Performance and Results Management System Type 2 Triennial Outcome/Impact Report Annual Technical Report Results Dashboard $771M Revenue 2% 23% 44% 31% Revenue by Funding Source Windows 1&amp;2 | Window 3 | Bilateral | Other 1 2 3 4 5 6 7 8 9 10 13 12 11 6. CGIAR 2030 Research and Innovation Strategy 7. Performance and Results Management Framework 8. Technical Reporting Arrangement 9. CGIAR Results Framework 10. Standard Indicator Description Sheets: • Output level • Outcome level 11. Theory of Change 12. IPSR • Output level • Outcome level • IPM for responsible food systems transformation • Scaling Readiness website • Online course on Innovation and Scaling • Scaling Readiness calculator • Scaling Directory 13. Adaptive Management 14. Quality Assurance 15. PRMS &amp; TOC board 16. Results Dashboard 17. 2022 &amp; 2023 Annual Technical Reports 18. Type 2 report Grass pea production in Odisha. Credit: IRRI May 2025 17 16 CGIAR Portfolio Practice Change (Type 3) Report
+---
+[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p13pt1]
+Genebank Accelerator MELIA Plan 13 The Annual Genebank Meetings (AGMs) are an important forum to review and reflect on the CGIAR Genebanks past year’s activities, progress and achievements, and to make plans for the next year. National partners, CGIAR programs, and technical and scientific experts are represented in the AGMs, and the location of the meeting is in a different region each year to assure better interaction with multiple stakeholders from different regions. By doing this, we are constantly consulting with partners in different regions of the world, understanding their realities and needs so we can better plan the
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18pt2]
+we will approach this as a learning journey with stakeholders, building on existing expertise, studies and approaches to land on an approach that is meaningful and cost-effective. Linking $ to results CGIAR aims to establish a fit for purpose solution that provides intelligence on how financial inputs connect to different types of outputs, outcomes and impacts across CGIAR's portfolio. This is crucial for improving transparency and accountability, as well as for resource prioritization and portfolio man agement. The primary objective is to establish a transparent link , at an appropriate level of granularity, between financial investments and the tangible results they yield. Having such linkages will also allow CGIAR to better: 1. Ensure successful CGIAR 2030 Research and Innovation Strategy implementation under different funding scenarios 2. Make
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p18pt2]
+we will approach this as a learning journey with stakeholders, building on existing expertise, studies and approaches to land on an approach that is meaningful and cost-effective. Linking $ to results CGIAR aims to establish a fit for purpose solution that provides intelligence on how financial inputs connect to different types of outputs, outcomes and impacts across CGIAR's portfolio. This is crucial for improving transparency and accountability, as well as for resource prioritization and portfolio man agement. The primary objective is to establish a transparent link , at an appropriate level of granularity, between financial investments and the tangible results they yield. Having such linkages will also allow CGIAR to better: 1. Ensure successful CGIAR 2030 Research and Innovation Strategy implementation under different funding scenarios 2. Make
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p13pt1]
+CGIAR Technical Reporting Arrangement 2025-30 June 2025 13 operational plans. They will underpin geography and impact pathway -specific outcome and impact assessments at different levels. They will provide more consistent information for future evaluations and other studies. • There are in the order of 10,000 indicators in use across CGIAR’s 900+ active projects with limited consistency among them. Most indicators (around 80%) map well to existing CGIAR Results Framework categories but are defined and measured in different ways, meaning that effective transfer of data and learning between extant and successive generations of Portfolio components is suboptimal. The resulting high rate of single use results data in the CGIAR hampers effective delivery and learning at all levels. If standard indicators, data collection tools, protocols, and collected data are integrated into new w3 and
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p13pt1]
+CGIAR Technical Reporting Arrangement 2025-30 June 2025 13 operational plans. They will underpin geography and impact pathway -specific outcome and impact assessments at different levels. They will provide more consistent information for future evaluations and other studies. • There are in the order of 10,000 indicators in use across CGIAR’s 900+ active projects with limited consistency among them. Most indicators (around 80%) map well to existing CGIAR Results Framework categories but are defined and measured in different ways, meaning that effective transfer of data and learning between extant and successive generations of Portfolio components is suboptimal. The resulting high rate of single use results data in the CGIAR hampers effective delivery and learning at all levels. If standard indicators, data collection tools, protocols, and collected data are integrated into new w3 and
+---
+[ID: pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p9pt1]
+7 Results framework Aligned with the Program’s updated ToC, the results framework outlines the identiﬁed indicators per result and corresponding targets. It further speciﬁes monitoring, and evaluation approaches that document and assess progress toward each indicator target to inform performance review and adaptive management. This guides the overall MELIA Plan, particularly the data collection strategy, MELIA studies, and other MELIA activities in target countries in close collaboration with other Programs, Accelerators, and bilateral projects. Refer to the Results Framework attachment for additional information. 2. Monitoring plan for high-level outputs (HLOs) and outcomes Data collection strategy The Climate Action Program will adopt a monitoring-for-learning approach grounded in results-based management (RBM) principles and aligned with CGIAR’s Performance and Results Management Framework (PRMF). Progress will be tracked against deﬁned indicators and targets as outlined in
+---
+[ID: pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p9pt2]
+the municipal market in Tucuru, Guatemala. Using several different strategies tailored to different contexts, the Better Diets and Nutrition program aims to
+---
+[ID: docx:2025 Technical Reporting MELIA glossary.docx:u31-34]
+Intermediate outcome | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. 2030 outcome | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. Output | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. High-level output | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on).
+---
+[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p15pt3]
+AOW results and
+---
+[ID: pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p10pt3]
+Impact Indicate the result short title from the Results Framework Indicate the indicator title from the Results Framewo rk Provid e the assu mptio n(s) state ment from the Resul ts Fram ework Indicate the location( s) where the study will be conducte d Indicate the methods and design approache s that will be used for the study List the Progr am(s) and Accel erato
+---
+[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt1]
+2. Monitoring plan for HLOs and outcomes This section outlines how Better Diets and Nutrition will monitor the delivery of high-level outputs (HLOs) and progress toward defined outcomes. The monitoring approach reflects the Program's decentralized structure with strong central coordination, ensuring that routine tracking of indicators against the logical framework is feasible, relevant, and aligned with resource availability. Indicators will be reviewed annually and revised as necessary, based on implementation progress, emerging priorities, and feedback from AoW teams and partners. The Program ToC and result s framework comprises 22 HLOs and 30 outcomes . The results framework for the program will be submitted through the Performance and Results Management System (PRMS) ToC Board, and exported in Excel format for review, as per guidance. HLOs represent results such as tools, guidelines, datasets, and tested solutions; outcomes represent the behavioral and systemic changes these outputs are expected to generate. We will use the
+---
+[ID: pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p7pt1]
+Results framework Program/Accelerator results framework Please refer to the Results Framework attachment 2. Monitoring plan for HLOs and outcomes The genebanks will continue to use an online reporting tool (ORT), which was set up in 2014 to monitor the status of individual collections with respect to performance targets. Through the QMS adopted in AoW 1, genebank operations, data, and accession numbers are audit ed internally and externally and are subject to regular review by the Crop Trust. The audits ensure that international standards are complied with, and deviations and risks are documented and managed. FAO’s monitoring of UN SDG 2.5, State of the World of PGRFA, and the Global Plan of Action</t>
+  </si>
+  <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: According to the Annex pie chart, what was total 2024 revenue and the split by funding source?\n\nContext:\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 6\nContent: Research results can be defined according to the nature of the change and the control over it.\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p14]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 14\nContent: Figure 1: Research results according to the kind of change and the control over it.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 23 Annex 2: ISDC feedback relating to pooled &amp; non-pooled alignment5 This section provides a direct extract from the ISDC Feedback on CGIAR Portfolio Narrative 2025- 2030. Comments relating to the alignment of pooled and non -pooled have been extracted from the broader set of comments. They have not been edited to e.g. update Program and Accelerator nomenclature. • Articulation of how the Portfolio, including bilateral and W1 funding, will be bundled into Megaprograms is still lacking. Bilateral funding is restricted and is provided for a specific purpose and with specific intended impacts. This needs to be honored a nd the lack of flexibility in shifting those funds into other areas should be clearly acknowledged. • Alignment of the entire Portfolio with the CGIAR 2030 Research and Innovation Strategy needs to be strong and explicit. How will management ensure that bilateral funding delivers against this Strategy? In addition: o What happens if a bilateral project is not strongly aligned with the Strategy and how will CGIAR ensure that opportunity costs are covered? o Will all bilateral projects across all Centers be mapped to support the Portfolio? • A challenge that should be acknowledged is incorporating bilateral funding into Megaprograms. Each Megaprogram and Accelerator will be large scale and staff will be consumed by the implementation of contracted work. Trying to build Megaprogram linkages in parallel with bilateral funding should be additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative 2025-2030\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p5]\nFile: Type3_2024Report.pdf\nLocation: page 5\nContent: Section 2: Portfolio Performance and Project Coordination Progress 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022-2024. 3. Science Group Projects (SGPs) are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance and fiduciary oversight. 4. EiB II will report through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they will provide a concise, high-level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the technical reports. 2.1. Technical Reporting Arrangement 2022-24 CGIAR Technical Reporting fulfils the System-level programmatic reporting requirements set out in the Standard Provisions annexed to the Funding Agreement or Arrangement signed between each Funder and the System Organization.2 The 2024 Technical Report includes the following Initiatives, Impact Platforms and SGPs3: • All 32 Initiatives • Five Impact Platforms – Gender Equality, Youth and Social Inclusion – Environmental Health and Biodiversity – Nutrition, Health and Food Security – Climate Adaptation and Mitigation – Poverty Reduction, Livelihoods and Jobs • Six SGPs – Accelerated Varietal Improvement and Seed Delivery of Legumes and dryland Cereals in Africa (AVISA) – Roots Tubers and Banana (RTB) Breeding – Accelerating Genetic Gain and Varietal Replacement in Rice - Phase 2 (AGGRi 2) – Excellence in Breeding (EiB) II: Cross-Crop Support Services for Breeding Acceleration4 – Accelerating Crop Improvement Through Genome Editing 2023-2025 – Climate Adaptation Insight For 2024, CGIAR will produce and deliver a total of 46 Technical Reporting outputs: • March 2025: Results from 2024 published on the online CGIAR Results Dashboard (1). • May 2025: Publication of 42 Type 1 (32 x Initiative reports; 5 x Impact Platform reports; 5 x SGP reports) Reports and a Type 3 Report (1). • End of June 2025: Publication of the Portfolio Narrative (1). • End of June 2025: Publication of the Type 2 Report: CGIAR Contributions to Impact in Agrifood Systems (2022-24) (1). Each of these reports is released separately and will be available in PDF format. 2024 Technical Reporting covers USD 370 million (USD 322 million for Initiatives and Impact Platforms, and USD 49 million for W3 SGPs), representing nearly 40 percent of CGIAR’s total pooled and non-pooled funding for 2024. 2.1.1. Streamlining the process and adding value to stakeholders In 2022 CGIAR launched a new 2022-24 Technical Reporting Arrangement, co-developed with the System Council’s Strategic Impact Monitoring and Evaluation Committee (SIMEC). The 2022 rollout was regarded as a “first pancake” or trial phase, establishing minimum viable functionality and setting the foundation for annual improvements. Key achievements of 2022 Technical Reporting included the adoption of a common report template aligned with the Technical Reporting Arrangement for Initiatives and Impact Platforms; integration with CGIAR’s Results Framework; digital linking of results to theories of change (TOCs); and the introduction of quality assurance processes mediated by third parties. Additionally, a new interactive CGIAR Results Dashboard was launched, and the Performance and Results Management System (PRMS) – an online reporting system – was developed, alongside adaptive management processes and the rollout of Innovation Packages and Scaling Readiness plans. Building on this, 2023 Technical Reporting incorporated lessons from a 2022 Learning and Optimization process, documented in a 2022 Learning and Optimization report. Key advancements included transitioning to “Always on” reporting by opening the PRMS from September 2023, more than doubling the reporting window compared to 2022 and allowing greater flexibility for Initiatives, Impact Platforms, and SGPs. Quality assurance was optimized through four staggered batches across 2023 and 2024. Further enhancements included expanding per-result tagging to all five Impact Areas. A Risk Management Module was launched to support risk identification and reporting at the Initiative level. A large number of participants joined training sessions to support reporting, dashboard use, and onboarding, and the rapid uptake of adaptive management strengthened strategic agility, with positive feedback from across the Portfolio. The Research Plans of Results and Budgets section of the CGIAR website was updated to ensure easy open access to Initiative, SGP and Impact Platform Plans of Results and Budgets (PORBs). The 2024 reporting cycle continued this trajectory, integrating insights from the 2023 Learning and Optimization process and Action Plan to further refine CGIAR’s Technical Reporting processes and products. Key improvements in 2024 included: • Launching the PRMS Planning Module to support the replan process: The launch of an online Planning Module synchronized TOC and Planning data in the PRMS, improving the efficiency and quality of planning workflows. Enhanced replan guidelines were provided to help Initiatives, Impact Platforms, and SGPs implement 2023 Reflect recommendations and align budget forecasts with updated budget envelopes. To support continuous learning and adaptive management, a user experience survey on the Planning Module was conducted to assess effectiveness and inform user-centered enhancements for the 2025-30 Portfolio. • Further simplifying reporting processes and tools: A series of enhancements to PRMS functionalities were implemented to improve efficiency and usability. Improved filtering options, enhanced notification systems, and more clearly structured result PDFs now enable quicker access to relevant information. Innovation Packages and Scaling Readiness language and templates were simplified. Reporting was streamlined and modified to suit the final year of reporting for the Portfolio, with an Outcome Indicator Module co-developed with input from Initiatives, Impact Platforms and SGPs to provide them with the opportunity to assess their progress against targets for Work Package outcomes and end-of-Initiative outcomes; summative and yearly highlights were combined into a single report; and adaptive management processes removed. • Improving decision-making within the PRMS: Broader engagement from PRMS testers across reporting entities and Senior Program Managers was integrated into PRMS feature development, ensuring that system updates were aligned with user needs and supported consistent decision-making. • Enhancing product clarity: The Type 1 Annual Report template was reviewed to better accommodate end-of-Initiative outcome reporting for the final year of the Portfolio. Improvements to the Results Dashboard were made to enhance the accessibility of IPSR insights. • Strengthening quality assurance: Examples include updated and enhanced QA guidance, and updated guidance on Impact Area tagging. An AI tool was prototyped and tested on a series of data fields, with the intent to leverage lessons learned and develop an enhanced AI tool that can be applied to a broader set of reported data and integrated into the PRMS, supporting both the reporting and QA phases. • Developing the Semantic Natural Language Processing Aggregator Platform (SNAP): SNAP is an AI-powered tool enhancing access to and analysis of CGIAR’s reported outputs, outcomes, and impacts. It improves access to Portfolio information and results evidence through semantic searches, thematic clustering, and automated summaries, complementing the CGIAR Results Dashboard. SNAP-supported narratives were integrated into the CGIAR 2024 Portfolio Narrative, and ongoing refinements will further enhance its role in Portfolio reporting. • Further integrating SGPs and Impact Platforms: Between 2022 and 2024, CGIAR progressively aligned these entities with its Technical Reporting processes and common systems to enhance consistency and coherence. In 2023, three Impact Platforms – Nutrition, Health and Food Security; Climate Adaptation and Mitigation; and Environmental Health and Biodiversity – were onboarded alongside the Gender Equality, Youth and Social Inclusion Impact Platform (which reported in 2022), each receiving tailored support such as TOC and results framework development. The SGP pilot launched in 2023 further expanded CGIAR’s reporting ecosystem by integrating Center-specific Window 3 awards, with two SGPs submitting first-year results using the PRMS Reporting Tool and Type 1 Report template. In 2024, integration expanded to include the Poverty Reduction, Livelihoods and Jobs Impact Platform and four additional SGPs, further broadening the reporting ecosystem. • Enhancing risk management through the PRMS Risk Module: The Risk Management Module, launched in 2023 to support Initiative management and reporting of risks, was further enhanced in 2024, allowing Initiatives to capture transition-focused risks. It enabled Initiatives to review, update, or close risks, contributing to the design of the 2025-30 Portfolio. The updated Risk Management Module will be used by Programs and Accelerators from 2025 onward. Climate-Smart Village set-up under the Adaptation and Mitigation Initiative in Agriculture (AMIA) of the Department of Agriculture. Credit: Miguel Mamon/CIAT May 2025 54 CGIAR Portfolio Practice Change (Type 3) Report 2024\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 4\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 4 1. Technical Reporting Arrangement purpose, scope, value proposition, delivery and optimization, Purpose The purpose of th e Technical Reporting Arrangement 2025 -2030 (“TRA 25-30”) is to set out the technical reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. The TRA 25-30: • Provides the parameters that e nable the Centers, the CGIAR System Partners and the System Organization to fulfil their technical reporting obligations under the funding agreements that apply to the use of Window 1 and Window 2 funds from the CGIAR Trust Fund (“Pooled Funding”). These parameters also allow the Integrated Partnership Board to fulfil its responsibility under the CGIAR System Charter to report on programmatic performance of CGIAR Research on an annual basis. • Provides, through the establishment of common technical reporting principles, enabling tools and mechanisms, progressive alignment and synergy between the technical reporting requirements that apply to components of the CGIAR Portfolio that are funded by Pooled Funding and those that apply to the components that are funded by other sources of funds (“Non-Pooled Funding”). • Sets transparency, performance tracking, and accountability expectations between CGIAR System Funders and CGIAR including Centres, • Informs decision making at different levels, underpins research management, operationalizes the Performance and Results Management Framework (PRMF), and guides portfolio -level MELIA and the design of the next Performance and Results management System (PRMS). The current Technical Reporting Arrangement that applies to the CGIAR Portfolio during the period 2022-24 (“TRA 22-24”) was co-developed by CGIAR and System Council/Strategic Impact Monitoring and Evaluation Committee (SIMEC) members in 2022. A new TRA is needed to match 2025-30 portfolio parameters, notably the alignment of pooled and non-pooled funding sources, and to apply lessons learnt from 2022-24. Scope The TRA 25-30 provides the operational and enabling basis to plan, monitor, learn and report on the 25-30 Portfolio. It is designed to progressively enable Programs and Accelerators, Centers and their research teams to report on the pooled, bilaterally and W3-funded components of the 2025- 30 portfolio in an integrated and aligned way, without increasing reporting burdens of Centers and Scientists. Going forward, the CGIAR Integrated Partnership will work towards progressively greater alignment of W3/bilateral projects and programs with the 2030 outcomes and theories of change of the Programs and Accelerators. Centers will provide key agreed information on their W3/bilaterally funded projects and programs to enable Program/Accelerator leaderships to explore ways to achieve alignment based on, inter alia, complementarity of results as well as actual or potential thematic, geographic, and partnership overlaps. Reporting on and attribution\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 5\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results framework, underpinned by a new Technical Reporting Arrangement, will provide robust, continuous performance and results reporting across all funding sources, as well as adaptive management of the Portfolio. 1 Value Proposition The TRA 25-30: - Creates value by delivering an integrated approach that tracks the performance of each Program and Accelerator, - Brings together the inputs (including costs), outputs, outcomes and impacts of the total portfolio to allow for easier and more robust Return on Investment (ROI) calculations. - Avoids creating a significant additional and duplicative layer of complex reporting requirements for W3/ bilaterally funded work. - Informs decision making through providing ready access to demand-driven quality raw and curated data products. Delivery The TRA 25 -30 will be delivered in line with Management arrangements for CGIAR’s 2025 —30 science and innovation Portfolio. Specific roles and responsibilities will be defined in 2025. 1 CGIAR Portfolio Narrative, 1 November 2024\n\n---\n\n[ID: docx:2025 Technical Reporting Information (Session 1).docx:p7]\nFile: 2025 Technical Reporting Information (Session 1).docx\nLocation: paragraph 7\nContent: Trifa, Nicoleta (CGIAR System Organization) 0:48 Yep. OK, good. So thank you. This session is the first of two session plans for today, planned for today, with the second being scheduled later at 3:00 PM CET to accommodate colleagues in other time zones. Technical reporting. My name is Nicoletta Trifa. By the way, I'm part of the Portfolio Performance Unit, the support unit within the Office of the Chief Scientist. Here is an overview of what we'll cover in the next minutes. I believe my presentation will take 2025 minutes and then we'll leave room for questions at the end, if that's OK. So what we'll cover an update of the technical reporting arrangements 2025 to 2030, priorities and changes for 2025, a brief introduction on the annual technical report and the neighbors. So this mean the performance and results. Management system and the quality assurance, the technical reporting timeline, available resources and support and what's next and how to stay engaged. I want to mention that this session marks the start of the conversation around 2025 technical reporting. We want to give you the early look at the key priorities and plans for the months ahead, and the goal is to make sure that you stay informed, prepared and supported with a clear understanding of upcoming deliverables and timelines. And also clarity on who to reach out to if you have questions or if you need help along the way. Good. Technical reporting arrangements for the new portfolio. The 2025 to 2030 portfolio has been approved by the CGR Global Leadership team on in June 2025 and provides the operational basis to plan, monitor, learn and report. On the new portfolio. It is designed to progressively enable programs, accelerators and centers to report on the pooled and window 3 bilateral projects of the new portfolio in an integrated and aligned way without increasing the burden on centers and the scientists. Main changes compared to the previous technical reporting arrangements, streamline reported reporting. So less products, more integration, lower transaction costs, stronger impact, focus results. To be clearly linked and packaged under impacts, outcomes and associated agreed indicator targets and better linkages between the theory of change or so plan of results and budget and technical reporting. The primary audiences for technical reporting are funders and CGR staff at integrated partnership, portfolio and program and accelerator levels. A secondary audience is the partners. Annual technical reporting covers the individual annual technical reports for program and accelerators, as well as a portfolio view of aggregate contribution to thematic and geographic targets. And relevant content from this technical reports are integrated into the CJR corporate reporting. In terms of the 2025 technical reporting priorities, 2025 is a transition year with technical reporting arrangements, implementation again focusing on streamlined reporting and on strengthening the linkages between theory of change. Porb, media and technical reporting. As many of you know, in the previous portfolio these components were not properly linked, so it was a bit challenging to demonstrate progress against the theory of change or the plans, as you know. In terms of deliverables for 2025. These are the program and accelerator technical reports, which are due in April 2026, the portfolio narrative, which is due in 2026 in June. Integration of top 80% of window tree and bilateral projects by central dollar value into reporting and planning. Application of the minimum data standards for window tree and bilateral reporting. And mapping of refinement during the pause and reflect process which will take place early Q 1/20/26. So as I was mentioning, this year is seen more as a transition year towards KPI based planning and reporting and efforts are underway to enable planning and reporting at the KPI level, which is aligned with the system office objective and key results for 2026 and 20. These are to be confirmed, so they haven't been confirmed yet, but I've pasted them here so that you can see the 2026 objective and key results for the system office. So 100% program and accelerate the work plans and budget. An annual technical report. Which provide for software enabled monitoring of erformance and results against smart Ki by center, ear and ooled funds invested. So next year, 80% of centres, CGR, window three and bilateral funded work by value included in 2025 technical reports and then the following year in 2027, this will increase to 90% of centres. Window 3 and bilateral funded work included in 2026 technical reports. The following slides, what I have, what I have included in the following slides, it's a brief introduction into. What is expected in terms of deliverables from programs and accelerators together with an overview of the performance and results management system and the QA. I realized that some in this call some of you are already familiar with the reporting arrangements from the previous portfolio. While for others this might be entirely new. So our goal is to bring everyone to the same level of understanding so that we can move forward with clarity and shared expectations for the 2025 technical reporting. OK, so technical reporting for program and accelerator. We'll focus on three key deliverables. So first is reporting results, the 2025 results in the Performance and Reporting Management system, PRMS. Each program accelerator and mapped window 3 project will report 2025 results in the system and we strongly encourage to report results that were planned and budgeted. So results which have been included in the reports. As the outdated technical reporting system will allow for tracking results against plans. Secondly is the quality assurance of reporting results. As you know, the results submitted go through the quality assessment process and we will share more details on this process in the timeline in an info session scheduled for later. Which we will schedule later in in September, October and the quality assess results will be available on the results dashboard. Inform the pause and reflect and will be included in the technical reports in the annual technical reports. A third deliverable for program and accelerators is drafting estimation of the 2025 Annual Technical Report. So each program and accelerator is responsible for drafting and internally validating quality assessing their 2025 Annual Technical Report. Before submitting it to the PPU, so to the perform portfolio performance unit. Again, guidance on this, the detailed process and validation process will be shared with you timely. Also to support this process, an AI generated V0 draft will be provided as a starting point. The annual technical reports. What are they? This the annual technical report. The the the aim is to make them short, so to 20 to 30 pages, concise and targeted. They provide assurance on annual program accelerator delivery against the boards, so plan of results and budget and progress on theory of change. They are based on quality assess results, the template guidance and as I mentioned and. AI V0 will be provided to all rogram and accelerator teams. Annual technical reports need to be submitted by each program and accelerator in March, April, so more details on this will follow and publication is intended to happen end of April, beginning of May. Here to the right side you have the. Content of the annual the proposed content for the annual technical report as per the technical reporting arrangements. Many of you will notice that there are not no big changes compared to previous portfolio, so the idea is to have a fact sheet and executive summary. The annual progress on theory of change, area of work details, a section on results, section on partnerships, portfolio linkages, adaptive management and then one key result story. But again, we will plan a detailed deep dive session on the annual technical report template and the guidance. So there will be time for you to ask questions in detail about about this and to receive support obviously. I've also included here for reference links to the 2024 Annual Technical Reports from the initiatives and impact platforms, and also a link to the 2024 Portfolio Narrative Report. In case you want to, you want to have a look to see, um, what it captures. PRMS. So this stands for Performance and Results Management System is the system the the the the environment where results need to be submitted. Again, the team is working on updating their resources. There will be. New users onboarding decks created with the links to different information and I I believe the PCU Alison together with the program coordinators. Are. The all the PRMS roles. So PCU is leading a work to define the PRMS roles and to get the information from program and accelerators regarding who from each program accelerator should have what role in PRMS. To enable us to to provide the right access to the platform when the time comes to report. Quality assurance process. So results submitted by program and accelerators in the PRMS will be quality assessed by a quality assessment team in February 2026. Your participation in this process is required. Guidance and resource resources will be provided and also an info session will be scheduled later this year. What is the QA? It is a process that aims to improve the quality of the reported data to provide consistency across the system, ensure reliability of reported results. Inform the learning process and improve the overall CGR accountability and transparency. Quality assess data informs the reflect process which takes place early Q12026, the results dashboard. So once the quality assessment of the results is finalized, the quality assess results will be pushed to results dashboard. You most probably have seen that. Reading. It also informs and are the results. The practices results are included in the annual report, in the portfolio narrative, and then in the overall CGIR annual report. In terms of the the timeline, so we have this info session now to provide an overview on the technical reporting and there will be several other info session and deep dive scheduled. Throughout September and October of reporting 2025 results, we believe that it will be feasible to open the PRMS in November for program and accelerators to to report. The date is still to be confirmed. We're aiming to to, yeah, to meet to to to end November. Hopefully this will be this is feasible from the technical side quality assurance. It's planned for February 2026 reflect process as I was mentioning Q 1/20/26 and then annual technical reports are due in March, April 2026 as well. Where to find information pertaining to technical reporting and planning and media? There is a one stop shop for for um all this. It's called the Performance and Results Hub. I'm gonna stop sharing cause I wanna share. Um, I'm gonna stop sharing the deck. I wanna. We could resent the hub. I'm not going to go through each section, but at least. So that you can see for those who are new more specifically to see and we will also share the link obviously the performance and results hub as I was mentioning it has detail on reporting, planning, reflect, replan. So you come in here, you click on 2025 reporting and then you will have access to the latest information, to the timeline, latest update, upcoming events. So all the information, information. Session dates will be listed here. We'll also have a subsection here with. Recording from from meetings, so that will be posted. For example today after this session we'll post a recording and the deck here for you to access and there is a section on frequently asked question. We recycled a couple of questions from the previous portfolio and updated them so that they are applicable to the program and accelerator teams, so feel free to go here and and browse. As resources become available, we will place them here and we will notify you by e-mail. OK. Going back to my deck. Which? In terms of engagement plan, so in order to streamline communication and optimize support for program accelerators and centers with mapped window 3 bilateral projects, we will send bi-weekly emails to everyone in this. This goal with key updates on technical reporting, with reminders and also with the latest questions and answers available on the hub. There will be targeted emails focusing on specific categories within the program accelerators. We want to engage with some of you on technical reporting, revisions, developments. And the aim is to gather feedback from you. Program coordinators will be copied on these emails. Info session. So a specific topic and we'll plan info session on specific topics, for example the standard indicator, description shades, the guidance on technical reporting, quality assurance. Reporting on innovations, the PRMS, so deep dive on the PRMS, the updates, the tool and so on. And during the reporting phase and the QA we will have weekly drop-ins. So this drop-ins is there will be no presentation. Presentation during the during this drop-ins. The purpose is for us to provide live support, so to answer your questions on the spot and the primary focus will be as I was mentioning, reporting and the QA. For if you know for every question you have, we invite you to use this e-mail address performanceandresults@cgr.org. This is the. The e-mail address we use for all technical reporting questions. So you have the questions right to us at performanceandresult@cjr.org and you will receive a response. We are aiming to respond within the 24 hours. Just to give an example, you know going back here I've gotten the targeted targeted emails and feedback. So this is a good example on for example how we plan to engage and get get feedback from from you on the PRMS enhancements so. Usually we send there's an e-mail sent to invite you to provide feedback on a o</t>
   </si>
   <si>
@@ -2270,6 +2762,18 @@
   </si>
   <si>
     <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: Who has fiduciary responsibility over the Windows 1 and 2 funds, and what must they guarantee?\n\nContext:\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u19-22]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 21 to section 'Use and administration of the Contributions' paragraph 24\nContent: Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively: ensure that such Window 1 and Window 2 Funds are used exclusively for their intended purposes; ensure that such Window 1 and Window 2 Funds are administered, used and expended in accordance with the CGIAR System Charter, the CGIAR System Framework and the applicable Fund Use Agreements entered into by it, including by taking corrective action with respect to Window 1 and Window 2 Funds not used in accordance with the relevant Fund Use Agreement; and monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u16-19]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 18 to section 'Use and administration of the Contributions' paragraph 21\nContent: Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research. Disbursement to Centers. The System Organization may, from time to time, initiate disbursements of Window 1 and Window 2 Funds to a Center for approved CGIAR Programs. Disbursement to a Program Participant. Subject to paragraph 2.4 of the Standard Provisions, Centers receiving Window 1 and Window 2 Funds may make further disbursements of such funds to Program Participants for the relevant CGIAR Program under Subagreements. Fiduciary Responsibility for the Use of Window 1 and Window 2 Funds. The System Organization has fiduciary responsibility toward Funders for the use of Window 1 and Window 2 Funds. Each Center has fiduciary responsibility toward the System Organization for the use of the Window 1 and Window 2 Funds it receives. With respect to the funds for which they have fiduciary responsibility, the System Organization and each Center will, respectively:\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u28-31]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 30 to section 'Window 3 Funds.' paragraph 33\nContent: ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements; monitor, evaluate as applicable, and provide quality assurance and financial and technical reporting for activities funded by Window 3 Funds in accordance with the relevant terms of these Standard Provisions; and if the Window 3 Funds are mapped to a CGIAR Program (i.e. provided for CGIAR Research activities that are aligned to the CGIAR Program's high-level outcomes and theory of change), continuously inform the System Organization and the project management unit of such CGIAR Program of the receipt of any Window 3 Funds and their use. The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u31-34]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 33 to section 'Window 3 Funds.' paragraph 36\nContent: The System Organization will not have fiduciary or programmatic responsibility over, or responsibility to supervise or monitor, Window 3 Funds. The System Organization may, however: upon request of a Funder providing Window 3 Funds and acting through the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center; or in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u181-184]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Return of Funds. Unexpended or Uncommitted Funding.' paragraph 198 to section 'Misused Fund' paragraph 202\nContent: Window 3 Funds. At the written direction of an individual Funder, the System Organization will require Centers to promptly return any portion of Window 3 Funds that are unexpended or uncommitted at the completion of the CGIAR Research for which it was provided (including approved extensions). Such returned funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding. Misused Fund Window 1 and Window 2 Funds. The System Organization and each Center will, respectively, refund any portion of Window 1 and Window 2 Funds not used in accordance with the applicable Fund Use Agreements, and such funds will be deposited to Window 1 of the Trust Fund. Window 3 Funds. Subject to paragraph 2.3.4 of these Standard Provisions, the System Organization will require Centers to refund any portion of Window 3 Funds not used in accordance with the applicable Fund Use Agreement, and such Funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u13-16]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 15 to section 'Use and administration of the Contributions' paragraph 18\nContent: In addition to the designation of contributions to the Trust Fund in accordance with the CGIAR Trustee Agreement and the Contribution Agreements or Arrangements, Funders may further designate Window 1 Funds and/or Window 2 Funds for specific purposes at the operational level subject to a decision of the System Council enabling such designations, and in accordance with a procedure for designation of funds at operational level, as may be adopted from time to time. Responsibilities over Window 1 and Window 2 Funds Disbursement to the System Organization. Window 1 and Window 2 Funds will be disbursed from time to time for the activities of the System Organization (including System Costs) and for CGIAR Research.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u178-181]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Acknowledgement of Funders' paragraph 194 to section 'Return of Funds. Unexpended or Uncommitted Funding.' paragraph 198\nContent: appropriate, the corrective action undertaken to address the concern, which may include suspension of transfer of Window 1 and Window 2 Funds to the Center. Return of Funds. Unexpended or Uncommitted Funding. Window 1 and Window 2 Funds. The System Organization and each Center will, respectively, promptly return any portion of Window 1 and Window 2 Funds that is unexpended or uncommitted at the completion of a CGIAR Program or activities under the CGIAR Program for which it was provided (including approved extensions) or at the termination of a Financial Framework Agreement between the System Organization and a Center, unless decided otherwise by the System Council. Such returned funds will be deposited to Window 1 of the Trust Fund. Window 3 Funds. At the written direction of an individual Funder, the System Organization will require Centers to promptly return any portion of Window 3 Funds that are unexpended or uncommitted at the completion of the CGIAR Research for which it was provided (including approved extensions). Such returned funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u22-25]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Use and administration of the Contributions' paragraph 24 to section 'Window 3 Funds.' paragraph 27\nContent: monitor, evaluate, and provide quality assurance and financial and technical reporting for activities funded by Window 1 and Window 2 Funds in accordance with the relevant terms and requirements of these Standard Provisions. Window 3 Funds. Window 3 Funds are directed by Funders to individual Centers. Funders may designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u172-175]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Acknowledgement of Funders' paragraph 187 to section 'Acknowledgement of Funders' paragraph 191\nContent: Acknowledgement of Funders All communications products on CGIAR Research funded by Window 1, 2 and 3 Funds, whether online or in hard copy form (e.g., publications, press releases, newsletters, website stories, blogs, posters, etc.), must acknowledge support received from Funders in accordance with applicable CGIAR Policies and Procedures on branding and communication. Suspending Transfers of Funding from Window 1 and 2 Suspension by the System Organization. The System Organization may, at any time, suspend transfers of Window 1 and Window 2 Funds allocated to a specific Center by providing a written notice to the relevant Center: (a) if the System Organization has a credible concern that the Window 1, 2 and 3 Funds are not used in accordance with the applicable Fund Use Agreements, or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) in the event of non-compliance by the Center with any of its obligations under an applicable Fund Use Agreement.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u4-7]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Introductory Provisions' paragraph 5 to section 'Introductory Provisions' paragraph 8\nContent: the Financial Framework Agreement between the System Organization and each Center with respect to Window 1, 2 and 3 Funds; and any Window 3 Side Agreement or Arrangement between a Funder and a Center with respect to Window 3 Funds. Interpretation of the Standard Provisions. Unless the context requires otherwise, the terms of these Standard Provisions governing the roles and responsibilities: between Funders and the System Organization apply to each Funding Agreement or Arrangement between a Funder and the System Organization;\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p31pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 31 part 2\nContent: protocols for data anonymization and access requests Implementation and oversight Data management responsibilities will be integrated into research staff roles with the ultimate responsibility being the\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u46-49]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Cost Sharing Percentage' paragraph 49 to section 'Standard of care.' paragraph 53\nContent: Window 1, 2 and 3 Funds. Centers will not have any obligation to collect or otherwise pay the CSP on funds disbursed through Windows 1, 2 or 3. The Funders, the System Organization and the Centers recognize that the Trustee of the CGIAR Trust Fund will collect the CSP before such funds are disbursed from the Trust Fund. Requirements on the Use of Window 1, 2 and 3 Funds CGIAR Policies and Procedures. The System Organization and each Center will, respectively ensure that Window 1, 2 and 3 Funds are used in accordance with applicable CGIAR Policies and Procedures and the relevant entity's own policies and procedures. All CGIAR Policies and Procedures will be available on the System Organization's web site. Standard of care.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u55-58]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Financial, Economic and Administrative Standards' paragraph 59 to section 'Financial, Economic and Administrative Standards' paragraph 62\nContent: Efficiency. The System Organization and each Center will, respectively: ensure that Window 1, 2 and 3 Funds are used with due regard to economy and efficiency, and that the highest standards of integrity in the administration of the funds are upheld; and ensure that Window 1, 2 and 3 Funds are used in accordance with applicable CGIAR Policies and Procedures on cost allocation, which set forth the principles of allowability, allocability, and reasonableness. Investment Income. The System Organization and each Center will, respectively, ensure that any investment income generated by the portions of the Window 1, 2 and 3 Funds they receive, including currency conversion gains, will be used for CGIAR Research or, if not needed for such purposes, returned to the Trustee for deposit into Window 1 to be made available for allocation by the System Council.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u25-28]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 27 to section 'Window 3 Funds.' paragraph 30\nContent: designate specific amounts to specific Centers for use by the Center; provided such funds are used to implement aspects of the Strategy and Research Framework and provided further that such funds are used in accordance with applicable CGIAR Policies and Procedures. Designations of Window 3 Funds by Funders to Centers are not subject to review, allocation or approval by the System Organization. Centers receiving Window 3 Funds are responsible for the use of such funds and will: ensure that Window 3 Funds are used exclusively for their intended purposes; ensure that Window 3 Funds are administered, used and expended in accordance with the applicable Fund Use Agreements entered into by them, including by taking corrective action with respect to those funds not used in accordance with such Fund Use Agreements;\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u34-37]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Window 3 Funds.' paragraph 36 to section 'Window 3 Funds.' paragraph 39\nContent: in consultation with the relevant Funder providing Window 3 Funds and the System Council, take corrective action vis-â-vis a Center in the event such Window 3 Funds are not used in accordance with any applicable Fund Use Agreement entered into by such Center. Window 3 Side Agreements or Arrangements. Nothing in the Funding Agreements or Arrangements is intended to preclude Funders and Centers from entering into Window 3 Side Agreements or Arrangements in regard to the terms governing the administration and use of Window 3 Funds. Funders may choose to make a Contribution to a Center through Window 3 without entering into a Window 3 Side Agreement or Arrangement, provided that such Contribution is made without any additional conditions attached to it. Any Window 3 Side Agreement or Arrangement will be consistent with these Standard Provisions and substantially in the form of Schedule 1 (Form of Window 3 Side Agreement or Arrangement) attached to these Standard Provisions, as may be amended from time to time. Program Participants. In engaging a Program Participant with respect to Window 1, 2 and 3 Funds, Centers will incorporate in the relevant Subagreements, and cause, and monitor, compliance with the obligations set out in the Standard Provisions, including but not limited to those set out in paragraphs 2.5-2.6, 4-6, 7.2.2, 7.1.3, 7.3.2, 8.3, 8.4.4,\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u163-166]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Limitation of Liabilities' paragraph 176 to section 'No Additional Obligations' paragraph 180\nContent: In providing funds under: Funding Agreements or Arrangements, or Window 3 Side Agreements or Arrangements, Funders do not accept any responsibility or liability towards any third parties including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund; and Financial Framework Agreements, the System Organization does not accept, any responsibility or liability towards any third parties, including any claims, debts, demands, damage or loss as a result of the implementation of activities with funds from the Trust Fund. No Additional Obligations\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u58-61]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Financial, Economic and Administrative Standards' paragraph 62 to section 'Financial, Economic and Administrative Standards' paragraph 65\nContent: Investment Income. The System Organization and each Center will, respectively, ensure that any investment income generated by the portions of the Window 1, 2 and 3 Funds they receive, including currency conversion gains, will be used for CGIAR Research or, if not needed for such purposes, returned to the Trustee for deposit into Window 1 to be made available for allocation by the System Council. Procurement. In the event that consultants are employed or services or goods are procured with Window 1, 2 and 3 Funds, the System Organization and each Center will, respectively, ensure that the employment and supervision of such consultants and the procurement of such services or goods will be the responsibility of each entity employing or contracting such consultants or carrying out such procurement and will be conducted in conformity with applicable CGIAR Policies and Procedures on procurement, in line with the following basic principles of equal treatment and non-discrimination on grounds of nationality, competition, predictability, transparency, verifiability, and proportionality. No taxation. The System Organization and each Center will, respectively, use best efforts, to the extent allowed by applicable agreements, such as those signed with host governments, and applicable laws, to ensure that the use of Window 1, 2 and 3 Funds will be free from any taxation or fees imposed under local laws. Insurance. The System Organization and each Center will, respectively, maintain insurance coverage sufficient to cover the activities, risks, and potential omissions of the activities funded by Window 1, 2 and 3 Funds in accordance with generally accepted industry standards and as required by law.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u106-109]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Monitoring and Evaluations' paragraph 115 to section 'Monitoring' paragraph 118\nContent: Funders will manage their monitoring and evaluation requirements with respect to the CGIAR Portfolio, collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to conduct duplicative evaluations, provided that Funders providing Window 3 Funds may require supplemental monitoring and evaluations with respect to Window 3 Funds, the costs of which, including the internal costs to the System Organization or Center, would be paid by the requesting Funder. If an individual Funder wishes to request, on an exceptional basis, a review or evaluation of any activities financed with Window 1 and Window 2 Funds, such Funder will consult with a designated representative from the System Organization on the most appropriate scope and terms of reference of such review or evaluation. The designated representative will assist in arranging for such review or evaluation in accordance with the applicable CGIAR Policies and Procedures. The costs of any such review or evaluation, including the internal costs of the System Organization or Center with respect to such review or evaluation, will be paid by the requesting Funder. The System Organization and each Center will, respectively collaborate on any monitoring or evaluations conducted in connection with CGIAR Research activities funded with Window 1, 2 and 3 Funds. Monitoring\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u175-178]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Acknowledgement of Funders' paragraph 191 to section 'Acknowledgement of Funders' paragraph 194\nContent: Suspension by the System Organization. The System Organization may, at any time, suspend transfers of Window 1 and Window 2 Funds allocated to a specific Center by providing a written notice to the relevant Center: (a) if the System Organization has a credible concern that the Window 1, 2 and 3 Funds are not used in accordance with the applicable Fund Use Agreements, or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) in the event of non-compliance by the Center with any of its obligations under an applicable Fund Use Agreement. Before taking such action under paragraph 13.1, the System Organization will notify the relevant Center in writing, and consult with the System Council as well as the relevant Center with a view to identify ways and means to manage the suspension and mitigate the impact on the implementation of CGIAR Research until such time that the suspension may be lifted. If such suspension is lifted by the System Organization, it will notify the relevant Center in writing. Request by a Funder. If a Funder has a credible concern: (a) that Window 1, 2 and 3 Funds are not used by a Center in accordance with the applicable Fund Use Agreement or of an interpersonal misconduct in connection with the implementation of activities financed by Window 1, 2 and 3 Funds; and/or (b) of a non-compliance by a Center with any of its obligations under an applicable Fund Use Agreement, the Funder may request, through the System Council, the System Organization to review the specific concern and, as relevant, to take appropriate corrective action. The System Organization will report to the System Council on the outcome of the review and, as appropriate, the corrective action undertaken to address the concern, which may include suspension of transfer of Window 1 and Window 2 Funds to the Center.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u184-189]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Misused Fund' paragraph 202 to section 'Inconsistency' paragraph 207\nContent: Window 3 Funds. Subject to paragraph 2.3.4 of these Standard Provisions, the System Organization will require Centers to refund any portion of Window 3 Funds not used in accordance with the applicable Fund Use Agreement, and such Funds will be deposited to Window 1, Window 2 or Window 3 of the Trust Fund as directed by the Funder that contributed such funding. Inconsistency In the event of any inconsistency between the Cover Pages and these Standard Provisions, these Standard Provisions will prevail. Amendments Amendments These Standard Provisions may only be amended by approval of the System Council subject to concurrence of the Integrated Partnership Board. The System Organization will promptly notify the Funders and Centers in writing of any such amendments to these Standard Provisions.\n\n---\n\n[ID: pdf:Portfolio Narrative_2024.pdf:p5pt1]\nLink: https://cgspace.cgiar.org/items/04bd63a9-1b58-4eb5-84f2-b54c8bde226e\nFile: Portfolio Narrative_2024.pdf\nLocation: page 5 part 1\nContent: Section 1: Connecting impact and insight: The 2024 CGIAR Portfolio Narrative 1. SGPs are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance, and fiduciary oversight. 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022–2024. 3. EiB II reported through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they provided a concise, high- level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the Technical Reports. The 2024 CGIAR Portfolio Narrative is a cornerstone of CGIAR’s Technical Reporting Arrangement. It offers a synthesis of Portfolio coherence, synergies, and collective progress across Initiatives, Impact Platforms, and Science Group Projects (SGPs)1, which represent approximately 40 percent of CGIAR’s Portfolio by dollar value. The report does not include Center-managed bilateral projects. As a key\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 5 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results\n\n---\n\n[ID: pdf:Scaling for Impact_Inception Report 30-06-2025.pdf:p24pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact%2FScaling%20for%20Impact%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact&amp;p=true&amp;ga=1\nFile: Scaling for Impact_Inception Report 30-06-2025.pdf\nLocation: page 24 part 4\nContent: the continuity of prior work that is less fit for purpose in the Program’s ToC. Windows 1, 2, 3 and bilateral funding: Approximately half of S4I’s 2025 funding is from Window 1, with the remainder from Window 2, including two $1.25 million designated W2 allocations specifically for AoWs 4 and 5. The PORB also reflects stronger alignment of Window 3 and bilateral funding with Program logic: in 2025, 47 mapped W3 and bilateral investments totaling $44.8 million support the Program ($0.42M, $26.47M, $1.55M, $15.37M, and $0.99M across AoWs 1 through 5, respectively), with 74% of these funds active in Africa, 19% in Asia, and 7% in Latin America. Engage and Empower (AoW 1): This AoW is allocated $2.98 million in W1/W2 funding and supported by $0.42 million in W3/bilaterals. It anchors S4I’s stakeholder demand intelligence 9 The section on AoW 4 in the PORB description highlights major inception period successes in leveraging Window 3 investments, with an anticipated, two-year bilateral investment in HLO 4.1 to transition TAAT into the Scaling Program that will support new work that was not part of the RIIs or NPS.\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u67-70]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Ethical Standards' paragraph 71 to section 'Ethical Standards' paragraph 74\nContent: Electioneering. The System Organization and each Center will, respectively, ensure that Window 1, 2 and 3 Funds will not be used to influence the outcome of any specific public election or to directly or indirectly carry on any voter registration drive. Drug trafficking. The System Organization and each Center, respectively, confirms that they have no reasonable basis to suspect that Window 1, 2 and 3 Funds would be diverted in support of drug trafficking. Discrimination against people with disabilities. The System Organization and each Center will, respectively, agree not to discriminate against persons with disabilities in the implementation of activities financed by Window 1, 2 and 3 Funds, and to make every effort to respect the principles of the UN Convention on the Rights of Persons with Disabilities in performing such activities. To that end, and to the extent this goal can be accomplished within the scope of the objectives of CGIAR Research, the System Organization and Centers involved in an activity financed by Window 1, 2 and 3 Funds should demonstrate a comprehensive and consistent approach for including men, women and children with disabilities consistent with such principles: (i) respect for inherent dignity, individual autonomy including the freedom to make one's own choices, and independence of persons; (ii) non-discrimination; (iii) full and effective participation and inclusion in society; (iv) respect for difference and acceptance of persons with disabilities as part of human diversity and humanity; (v) equality of opportunity; (vi) accessibility; (vii) equality between men and women; and\n\n---\n\n[ID: docx:Standard Provisions 2026.docx:u157-160]\nLink: N/A\nFile: Standard Provisions 2026.docx\nLocation: section 'Statement of Assurance' paragraph 169 to section 'Additional Audits / Financial Reviews / Technical Reporting' paragraph 172\nContent: Change in Reporting Requirements. Unless decided otherwise by the System Council and/or the Integrated Partnership Board as the case may be, any change in the form or substance or periodicity of a technical or financial report will become effective only in the following calendar year. Additional Audits / Financial Reviews / Technical Reporting Funders will manage their audits, financial reviews and technical reporting with respect to the Window 1, 2 and 3 Funds collectively through the System Council, including relying on applicable CGIAR Policies and Procedures, thereby endeavoring not to require duplicative reporting, provided that a Funder may require supplemental audits, financial reviews and technical reporting with respect to Window 3 Funds pursuant to its Window 3 Side Agreement or Arrangement, the costs of which would be paid by the requesting Funder. If a Funder wishes to request, on an exceptional basis, that the System Organization or a Center has an external audit or provides additional financial reviews or technical reports wi</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: what is an outcome\n\nContext:\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 48 part 4\nContent: breeding endeavors. While an earlier TOC showed the relationship between the outcomes of the initiatives, the revised TOC showed only one outcome of breeding. This outcome was ‘Seed producers successfully market new demand-driven improved varieties to more farmers’. The GI TOC essentially elevated the final output of the breeding pipeline to an outcome3, reverting to the breeding pipeline engineering view that dominates in breeding. In elevating the output to an outcome, any outcomes outside of breeding itself are diminished. Outcomes related to the quality of how breeding is done, with strategic prioritization, collaborative partnerships and efficiency have been omitted. It is these qualities of how breeding is done that build empowerment of regional partners and legacy beyond the lifecycle of a variety. 3 Note that it could be argued this is an outcome of Seed Equal. Regardless, it is not an outcome of GI, but one of the initiatives and this outcome could be achieved without investment or action in\n\n---\n\n[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations_Inception Report 30-06-2025.pdf\nLocation: page 13 part 2\nContent: leading to Intermediate Outcomes and finally to three 2030Outcomes, that correspond broadly to the three pillars. The first 2030 outcome focuses on Pillar C on capacity sharing; the 2nd outcome corresponds to Pillar B while the 3rd one addresses Pillar A.  2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs,  2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessment and governance to guide pro-poor, gender-inclusive and climate smart policies and investments  2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more coherent and sustainable development processes that deliver positive outcomes across a range of SDG targets. The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidates outputs from the 20 High-level outputs of the Policy Program. Multiple Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes\n\n---\n\n[ID: docx:Innovation use.docx:u1-4]\nLink: https://sites.google.com/cgxchange.org/cgiarprhub/2025-reporting?authuser=0\nFile: Innovation use.docx\nLocation: section 'Innovation use' paragraph 1 to section 'Innovation use' paragraph 7\nContent: Innovation use How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome levels. The development of an innovation (at various stages) is an output. The scaling, uptake and use of an innovation can be reported as outcome. In PRMS the results can be linked. What are the two ways to report innovation use results (outcomes)?\n\n---\n\n[ID: docx:General reporting guidance.docx:u1-3]\nLink: https://sites.google.com/cgxchange.org/cgiarprhub/2025-reporting?authuser=0\nFile: General reporting guidance.docx\nLocation: section 'General reporting guidance' paragraph 1 to section 'General reporting guidance' paragraph 5\nContent: General reporting guidance Is there guidance on what should be reported as a result? Yes, this document provides some principles for ensuring a focus on quality, rather than quantity, in terms of results reporting: Guidance on ensuring quality over quantity. Is there guidance available on how to distinguish between outputs and outcomes? Yes, information on what to report as an output or outcome can be found here: Guidance on reporting outputs or outcomes.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 22 part 4\nContent: CGIAR Results Framework – Portfolio Outcome\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 31 part 3\nContent: the Theories of Change (overall, Areas of Work and sub-Areas) for consistency and alignment with stated objectives. (more details in Section 3.1 of this report) We have revised the HLOs at sub-area of work level, to harmonize the approach, remove duplications, and prioritize. There are now 26 HLOs. − We have harmonized the intermediate outcomes across sub-AoWs, AoWs, and Accelerator level. There are now five intermediate outcomes for AoW on Solutions and three for AoW on Change. − We have moved one outcome from the intermediate level to the end-of-program level and there are now four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 32 part 3\nContent: Outcome Evidencing/ Outcome Trajectory evaluation instruments: Document review, workshops, key informant interviews, secondary data System-based Theory of Change Actor engagement and outcome tracker AoW6 assessments AoW7 partner capacity evaluation • To what extent does co -design of science-based processes and tools lead to ownership of results by landscape stakeholders and therefore to the sustainable uptake of solutions? • Number and type\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 2\nContent: in breeding contribute to increased rate of genetic gain, as captured in the extent of improvement and impact achieved by products. Efficiency is included in an intermediate outcome so any effectiveness evaluation of intermediate outcomes will be duplicative. This criterion is most relevant to AOW4 as it is designed to support efficient access and use of modernized breeding. An AOW level outcome has captured this so any effectiveness evaluation of outcomes will duplicate efficiency. Research questions will contribute to KEQ2 on effectiveness: To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? RQ12 How has the use of interoperable, scaled breeding tools and services increased\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p60pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 60 part 4\nContent: in thriving Multifunctional Landscapes • Number of policy innovations that support the transition to sustained MFLs what was the contribution of the MFL Program interventions to these changes. This will allow us to identify the most impactful Outcomes related to the Impact Areas and orient Outcome Evidencing studies for efficient use of MELIA resources.\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 47 part 3\nContent: of this report. Comparison with 2017–2021 Retrospective analysis of CGIAR’s 2017 to 2021 reporting cycle provides a reference point for assessing progress in outcome reporting and portfolio management under the current Results Framework. While differences in the reporting systems limit direct comparability, several structural patterns from the previous cycle remain relevant. Policy outcomes Learnings from CGIAR’s 2017 to 2021 reporting cycle demonstrate that policy outcomes were mostly oriented toward policies and strategies (75 percent), and the rest influenced budget and investment decisions or legal instruments.29 The majority reflected early uptake of research results, but 39 percent of policy outcomes were concrete decisions, policies, or programs taken or enacted. In the current 2022 to 2024 cycle, there was a slight increase in the percentage of reported policy changes that were actual policies or programs put into place (43 percent of policy outcomes). Moreover , the type of policy outcome differed, with the percentage of policy outcomes leading to modified programs or investments jumping to 29 percent. The thematic and geographic orientations of policy outcomes are similar across the two periods, generally displaying CGIAR effectiveness in all of its priority countries and across most of its Impact Areas. However , the percentage of policy outcomes which were aimed primarily at gender equality was low in both periods. Partners were critical to CGIAR’s success in informing policies. Critical partners included national and subnational governments, civil society organizations, private sector , regional bodies, and international organizations. The review of 2017 to 2021 policy outcomes also revealed that very few were evaluated for their impacts, yet many appeared to be significant. Some examples of those are in Table 3. Impacts of CGIAR’s policy research remain underanalyzed. Policy outcome type What the evidence shows Illustrative cases CGIAR partners Outcomes Policy and strategy outcomes, mainly at national level 60% of outcomes were national and 37% reached formal enactment— often when a ministry or regulatory body was part of the design team Ethiopian\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 23 part 1\nContent: Key Evaluation Questions Some guiding questions that will inform future evaluations include: • Are the Program’s assumptions about actor behavior, incentives, and influence valid for the specific stakeholders identified, and are they likely to lead to the intended outcomes? • How do differences in AoW presence across countries affect the Program’s ability to deliver its intended outcomes? • Are the current configurations of AoWs efficient and synergistic, or are there opportunities to increase impact through structural changes? • What mechanisms exist (or are lacking) to integrate bilateral and W3-funded results into core program planning and reporting? • To what extent is MELIA evidence used to inform planning, learning, and adaptation across the Program? • How well do program assumptions and outcome pathways reflect national priorities and systems capacities in each geography? • • What types of MELIA findings\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 8 part 4\nContent: been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E) Effectiveness (the extent that the intended results or outcomes are achieved) High This criterion directly relates to the MELIA objectives. Assessing the effectiveness of the Intermediate Outcomes will inform contribution analysis and inform the design requirements of future programs. KEQ2. To what extent has B4T and its AOWs effectively achieved the intended intermediate outcomes? RQ2 How did prioritization using the Design Standard contribute to maximized impact (AOW1 MI)? RQ7 To what extent has B4T increased uptake of varieties by scaling partners who have a widespread reach (collectively)? (AOW3 ID) RQ8 To what extent has CGIAR-NARES prioritization of products encouraged targeted investment for breeding?\n\n---\n\n[ID: docx:Innovation development.docx:u1-4]\nLink: https://sites.google.com/cgxchange.org/cgiarprhub/2025-reporting?authuser=0\nFile: Innovation development.docx\nLocation: section 'Innovation development' paragraph 1 to section 'Innovation development' paragraph 7\nContent: Innovation development How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome level. The development of an innovation (at various stages of design, testing and validation) is an output. The scaling or use of an innovation is an outcome. You may first report an innovation at the output level. If the innovation advances and starts to be used, it should then be reported as an outcome. Do I need to update innovations that were submitted during previous reporting periods?\n\n---\n\n[ID: docx:2025 Technical Reporting MELIA glossary.docx:u31-34]\nLink: https://docs.google.com/document/d/19V8HwQN50riKrU7GomHQ4J8_aBuyngrh/edit\nFile: 2025 Technical Reporting MELIA glossary.docx\nLocation: table 1 row 28 to table 1 row 31\nContent: Intermediate outcome | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. 2030 outcome | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. Output | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. High-level output | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on).\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 31 part 4\nContent: four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the \"challenges and megatrends\" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.\n\n---\n\n[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%20%2D%20MELIA%20Plan%2030%2D06%2D2025%2D%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations - MELIA Plan 30-06-2025-.pdf\nLocation: page 5 part 2\nContent: capacity &amp; tools. . The Program’s Theory of Change works through six interconnected Areas of Work (AoWs), their High- level Outputs (HLOs), leading to Intermediate Outcomes and finally to three 2030 Outcomes. During the inception phase the Policy Program align ed the Intermediate Outcomes and 2030 Outcomes to these 3 pillars. The 2030 Outcomes were revised to contribute to our impact around these. 2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs: represents the Capacity and tools pillar, 2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessm ent and governance to guide pro -poor, gender-inclusive and climate smart policies and investments, represents Rapid Response and policy guidance pillar while 2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more\n\n---\n\n[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%20%2D%20MELIA%20Plan%2030%2D06%2D2025%2D%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations - MELIA Plan 30-06-2025-.pdf\nLocation: page 5 part 4\nContent: Growth) and 10 (Reduced Inequalities). The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidate outputs from the 20 High -level outputs of the Policy Program. All Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes 1.2.1 (Partners use outlook reports to inform and enhance design of their strategies and policies), 4.2.1 (Partners achieve a shared understanding of emerging ch allenges in WEFE systems and foresight data, tools and analysis), 5.2.1 (Countries co-create national strategies and policies) and 6.2.2 (CGIAR researchers and partners have enh anced capacity) all address the capacity challenge and contribute to the impact pathway achieving 2030 Outcome1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs. This 2030 Outcome in turn, also addresses CGIAR Portfolio Outcome #1: Implementation partners (e.g. NARES, NGOs, private companies) actively support\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p5pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 5 part 2\nContent: 2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) Intemediate Outcome: Crop Trust signs Long-Term Partnerships with CGIAR X X X X - Intermediate Outcome: CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness X X X X 2030 Outcome 1: National and International genebanks conserve and make diversity more widely available in a strengthened global system of enabling policies and increased capacities X X X X 2030 Outcome 2: Researchers, farmers, and students access diversity and associated data in a smarter and\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 30 part 1\nContent: RQ17 What proportion of marginalized beneficiaries in each market segment have accessed improved varieties? (AOW3 ID) RQ29 What extent of value proposition is needed to motivate adoption? KEQ2. To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? Coherence RQ4 How have the network strategies improved coherence with region x crop investments? (AOW5 E) RQ5 How have bottlenecks or barriers between variety development and seed systems been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E)\n\n---\n\n[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p15pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%20%2D%20MELIA%20Plan%2030%2D06%2D2025%2D%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations - MELIA Plan 30-06-2025-.pdf\nLocation: page 15 part 4\nContent: intermediate outcomes that are not covered by any MELIA studies under the cross-cutting section should be entered under the relevant AoW-level outcome in the PORB\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p27pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 27 part 1\nContent: 27 Impact assessment efforts at the behavioral change level will focus on the 2030 Program Outcomes but also on unintended or unexpected significant outcomes highlighted through mid- term and final Outcome Evaluations and Policy change analyses (see Evaluation section). Data on behavioral changes will be monitored yearly through participatory outcome identification workshops with all partners engaged at the country/site level and outcome journals (see monitoring section). These yearly workshops at the country/site level are budgeted on the 20% non- assigned budget per center and have already been set aside by centers. The System Based Theory of Change approach will be applied to identify areas of success and prioritize the Outcome Evaluations (see\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsi</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: what is an outcome\n\nContext:\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 48 part 4\nContent: breeding endeavors. While an earlier TOC showed the relationship between the outcomes of the initiatives, the revised TOC showed only one outcome of breeding. This outcome was ‘Seed producers successfully market new demand-driven improved varieties to more farmers’. The GI TOC essentially elevated the final output of the breeding pipeline to an outcome3, reverting to the breeding pipeline engineering view that dominates in breeding. In elevating the output to an outcome, any outcomes outside of breeding itself are diminished. Outcomes related to the quality of how breeding is done, with strategic prioritization, collaborative partnerships and efficiency have been omitted. It is these qualities of how breeding is done that build empowerment of regional partners and legacy beyond the lifecycle of a variety. 3 Note that it could be argued this is an outcome of Seed Equal. Regardless, it is not an outcome of GI, but one of the initiatives and this outcome could be achieved without investment or action in\n\n---\n\n[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations_Inception Report 30-06-2025.pdf\nLocation: page 13 part 2\nContent: leading to Intermediate Outcomes and finally to three 2030Outcomes, that correspond broadly to the three pillars. The first 2030 outcome focuses on Pillar C on capacity sharing; the 2nd outcome corresponds to Pillar B while the 3rd one addresses Pillar A.  2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs,  2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessment and governance to guide pro-poor, gender-inclusive and climate smart policies and investments  2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more coherent and sustainable development processes that deliver positive outcomes across a range of SDG targets. The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidates outputs from the 20 High-level outputs of the Policy Program. Multiple Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes\n\n---\n\n[ID: docx:Innovation use.docx:u1-4]\nLink: https://sites.google.com/cgxchange.org/cgiarprhub/2025-reporting?authuser=0\nFile: Innovation use.docx\nLocation: section 'Innovation use' paragraph 1 to section 'Innovation use' paragraph 7\nContent: Innovation use How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome levels. The development of an innovation (at various stages) is an output. The scaling, uptake and use of an innovation can be reported as outcome. In PRMS the results can be linked. What are the two ways to report innovation use results (outcomes)?\n\n---\n\n[ID: docx:General reporting guidance.docx:u1-3]\nLink: https://sites.google.com/cgxchange.org/cgiarprhub/2025-reporting?authuser=0\nFile: General reporting guidance.docx\nLocation: section 'General reporting guidance' paragraph 1 to section 'General reporting guidance' paragraph 5\nContent: General reporting guidance Is there guidance on what should be reported as a result? Yes, this document provides some principles for ensuring a focus on quality, rather than quantity, in terms of results reporting: Guidance on ensuring quality over quantity. Is there guidance available on how to distinguish between outputs and outcomes? Yes, information on what to report as an output or outcome can be found here: Guidance on reporting outputs or outcomes.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 22 part 4\nContent: CGIAR Results Framework – Portfolio Outcome\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p22pt4]\nLink: N/A\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf\nLocation: page 22 part 4\nContent: CGIAR Results Framework – Portfolio Outcome\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 31 part 3\nContent: the Theories of Change (overall, Areas of Work and sub-Areas) for consistency and alignment with stated objectives. (more details in Section 3.1 of this report) We have revised the HLOs at sub-area of work level, to harmonize the approach, remove duplications, and prioritize. There are now 26 HLOs. − We have harmonized the intermediate outcomes across sub-AoWs, AoWs, and Accelerator level. There are now five intermediate outcomes for AoW on Solutions and three for AoW on Change. − We have moved one outcome from the intermediate level to the end-of-program level and there are now four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 32 part 3\nContent: Outcome Evidencing/ Outcome Trajectory evaluation instruments: Document review, workshops, key informant interviews, secondary data System-based Theory of Change Actor engagement and outcome tracker AoW6 assessments AoW7 partner capacity evaluation • To what extent does co -design of science-based processes and tools lead to ownership of results by landscape stakeholders and therefore to the sustainable uptake of solutions? • Number and type\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 2\nContent: in breeding contribute to increased rate of genetic gain, as captured in the extent of improvement and impact achieved by products. Efficiency is included in an intermediate outcome so any effectiveness evaluation of intermediate outcomes will be duplicative. This criterion is most relevant to AOW4 as it is designed to support efficient access and use of modernized breeding. An AOW level outcome has captured this so any effectiveness evaluation of outcomes will duplicate efficiency. Research questions will contribute to KEQ2 on effectiveness: To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? RQ12 How has the use of interoperable, scaled breeding tools and services increased\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p60pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 60 part 4\nContent: in thriving Multifunctional Landscapes • Number of policy innovations that support the transition to sustained MFLs what was the contribution of the MFL Program interventions to these changes. This will allow us to identify the most impactful Outcomes related to the Impact Areas and orient Outcome Evidencing studies for efficient use of MELIA resources.\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 23 part 1\nContent: Key Evaluation Questions Some guiding questions that will inform future evaluations include: • Are the Program’s assumptions about actor behavior, incentives, and influence valid for the specific stakeholders identified, and are they likely to lead to the intended outcomes? • How do differences in AoW presence across countries affect the Program’s ability to deliver its intended outcomes? • Are the current configurations of AoWs efficient and synergistic, or are there opportunities to increase impact through structural changes? • What mechanisms exist (or are lacking) to integrate bilateral and W3-funded results into core program planning and reporting? • To what extent is MELIA evidence used to inform planning, learning, and adaptation across the Program? • How well do program assumptions and outcome pathways reflect national priorities and systems capacities in each geography? • • What types of MELIA findings\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 8 part 4\nContent: been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E) Effectiveness (the extent that the intended results or outcomes are achieved) High This criterion directly relates to the MELIA objectives. Assessing the effectiveness of the Intermediate Outcomes will inform contribution analysis and inform the design requirements of future programs. KEQ2. To what extent has B4T and its AOWs effectively achieved the intended intermediate outcomes? RQ2 How did prioritization using the Design Standard contribute to maximized impact (AOW1 MI)? RQ7 To what extent has B4T increased uptake of varieties by scaling partners who have a widespread reach (collectively)? (AOW3 ID) RQ8 To what extent has CGIAR-NARES prioritization of products encouraged targeted investment for breeding?\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 47 part 3\nContent: of this report. Comparison with 2017–2021 Retrospective analysis of CGIAR’s 2017 to 2021 reporting cycle provides a reference point for assessing progress in outcome reporting and portfolio management under the current Results Framework. While differences in the reporting systems limit direct comparability, several structural patterns from the previous cycle remain relevant. Policy outcomes Learnings from CGIAR’s 2017 to 2021 reporting cycle demonstrate that policy outcomes were mostly oriented toward policies and strategies (75 percent), and the rest influenced budget and investment decisions or legal instruments.29 The majority reflected early uptake of research results, but 39 percent of policy outcomes were concrete decisions, policies, or programs taken or enacted. In the current 2022 to 2024 cycle, there was a slight increase in the percentage of reported policy changes that were actual policies or programs put into place (43 percent of policy outcomes). Moreover , the type of policy outcome differed, with the percentage of policy outcomes leading to modified programs or investments jumping to 29 percent. The thematic and geographic orientations of policy outcomes are similar across the two periods, generally displaying CGIAR effectiveness in all of its priority countries and across most of its Impact Areas. However , the percentage of policy outcomes which were aimed primarily at gender equality was low in both periods. Partners were critical to CGIAR’s success in informing policies. Critical partners included national and subnational governments, civil society organizations, private sector , regional bodies, and international organizations. The review of 2017 to 2021 policy outcomes also revealed that very few were evaluated for their impacts, yet many appeared to be significant. Some examples of those are in Table 3. Impacts of CGIAR’s policy research remain underanalyzed. Policy outcome type What the evidence shows Illustrative cases CGIAR partners Outcomes Policy and strategy outcomes, mainly at national level 60% of outcomes were national and 37% reached formal enactment— often when a ministry or regulatory body was part of the design team Ethiopian\n\n---\n\n[ID: docx:Innovation development.docx:u1-4]\nLink: https://sites.google.com/cgxchange.org/cgiarprhub/2025-reporting?authuser=0\nFile: Innovation development.docx\nLocation: section 'Innovation development' paragraph 1 to section 'Innovation development' paragraph 7\nContent: Innovation development How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome level. The development of an innovation (at various stages of design, testing and validation) is an output. The scaling or use of an innovation is an outcome. You may first report an innovation at the output level. If the innovation advances and starts to be used, it should then be reported as an outcome. Do I need to update innovations that were submitted during previous reporting periods?\n\n---\n\n[ID: docx:2025 Technical Reporting MELIA glossary.docx:u31-34]\nLink: https://docs.google.com/document/d/19V8HwQN50riKrU7GomHQ4J8_aBuyngrh/edit\nFile: 2025 Technical Reporting MELIA glossary.docx\nLocation: table 1 row 28 to table 1 row 31\nContent: Intermediate outcome | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. 2030 outcome | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. Output | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. High-level output | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on).\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 31 part 4\nContent: four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the \"challenges and megatrends\" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.\n\n---\n\n[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%20%2D%20MELIA%20Plan%2030%2D06%2D2025%2D%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations - MELIA Plan 30-06-2025-.pdf\nLocation: page 5 part 2\nContent: capacity &amp; tools. . The Program’s Theory of Change works through six interconnected Areas of Work (AoWs), their High- level Outputs (HLOs), leading to Intermediate Outcomes and finally to three 2030 Outcomes. During the inception phase the Policy Program align ed the Intermediate Outcomes and 2030 Outcomes to these 3 pillars. The 2030 Outcomes were revised to contribute to our impact around these. 2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs: represents the Capacity and tools pillar, 2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessm ent and governance to guide pro -poor, gender-inclusive and climate smart policies and investments, represents Rapid Response and policy guidance pillar while 2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more\n\n---\n\n[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%20%2D%20MELIA%20Plan%2030%2D06%2D2025%2D%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations - MELIA Plan 30-06-2025-.pdf\nLocation: page 5 part 4\nContent: Growth) and 10 (Reduced Inequalities). The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidate outputs from the 20 High -level outputs of the Policy Program. All Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes 1.2.1 (Partners use outlook reports to inform and enhance design of their strategies and policies), 4.2.1 (Partners achieve a shared understanding of emerging ch allenges in WEFE systems and foresight data, tools and analysis), 5.2.1 (Countries co-create national strategies and policies) and 6.2.2 (CGIAR researchers and partners have enh anced capacity) all address the capacity challenge and contribute to the impact pathway achieving 2030 Outcome1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs. This 2030 Outcome in turn, also addresses CGIAR Portfolio Outcome #1: Implementation partners (e.g. NARES, NGOs, private companies) actively support\n\n---\n\n[ID: pdf:CGI21_508012_PORB_Genebanks.pdf:p5pt2]\nLink: N/A\nFile: CGI21_508012_PORB_Genebanks.pdf\nLocation: page 5 part 2\nContent: 2025 Outcome Q1 Q2 Q3 Q4 2025 (Approved Budget) Intemediate Outcome: Crop Trust signs Long-Term Partnerships with CGIAR X X X X - Intermediate Outcome: CGIAR genebanks conserve and make available crop diversity in perpetuity with greater efficiency and effectiveness X X X X 2030 Outcome 1: National and International genebanks conserve and make diversity more widely available in a strengthened global system of enabling policies and increased capacities X X X X 2030 Outcome 2: Researchers, farmers, and students access diversity and associated data in a smarter and\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 30 part 1\nContent: RQ17 What proportion of marginalized beneficiaries in each market segment have accessed improved varieties? (AOW3 ID) RQ29 What extent of value proposition is needed to motivate adoption? KEQ2. To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? Coherence RQ4 How have the network strategies improved coherence with region x crop investments? (AOW5 E) RQ5 How have bottlenecks or barriers between variety development and seed systems been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E)\n\n---\n\n[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p15pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%20%2D%20MELIA%20Plan%2030%2D06%2D2025%2D%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations - MELIA Plan 30-06-2025-.pdf\nLocation: page 15 part 4\nContent: intermediate outcomes that are not covered by any MELIA studies under the cross-cutting section should be entered under the relevant AoW-level outcome in the PORB\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p27pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 27 part 1\nContent: 27 Impact assessment efforts at the behavioral change level will focus on the 2030 Program Outcomes but also on unintended or unexpected significant outcomes highlighted through mid- term and final Outcome Evaluations and Policy change analyses (see Evaluation section). Data on behavioral changes will be monitored yearly through participatory outcome identification workshops with all partners engaged at the country/site level and outcome journals (see monitoring section). These yearly workshops at the country/site level are budgeted on the 20% non- assigned budget per center and have already been set aside by centers. The System Based Theory of Change approach will be applied to identify areas of success and prioritize the Outcome Evaluations (see\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%2</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: what is an outcome?\n\nContext:\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p48pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 48 part 4\nContent: breeding endeavors. While an earlier TOC showed the relationship between the outcomes of the initiatives, the revised TOC showed only one outcome of breeding. This outcome was ‘Seed producers successfully market new demand-driven improved varieties to more farmers’. The GI TOC essentially elevated the final output of the breeding pipeline to an outcome3, reverting to the breeding pipeline engineering view that dominates in breeding. In elevating the output to an outcome, any outcomes outside of breeding itself are diminished. Outcomes related to the quality of how breeding is done, with strategic prioritization, collaborative partnerships and efficiency have been omitted. It is these qualities of how breeding is done that build empowerment of regional partners and legacy beyond the lifecycle of a variety. 3 Note that it could be argued this is an outcome of Seed Equal. Regardless, it is not an outcome of GI, but one of the initiatives and this outcome could be achieved without investment or action in\n\n---\n\n[ID: pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p13pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations_Inception Report 30-06-2025.pdf\nLocation: page 13 part 2\nContent: leading to Intermediate Outcomes and finally to three 2030Outcomes, that correspond broadly to the three pillars. The first 2030 outcome focuses on Pillar C on capacity sharing; the 2nd outcome corresponds to Pillar B while the 3rd one addresses Pillar A.  2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs,  2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessment and governance to guide pro-poor, gender-inclusive and climate smart policies and investments  2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more coherent and sustainable development processes that deliver positive outcomes across a range of SDG targets. The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidates outputs from the 20 High-level outputs of the Policy Program. Multiple Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes\n\n---\n\n[ID: docx:Innovation use.docx:u1-4]\nLink: https://sites.google.com/cgxchange.org/cgiarprhub/2025-reporting?authuser=0\nFile: Innovation use.docx\nLocation: section 'Innovation use' paragraph 1 to section 'Innovation use' paragraph 7\nContent: Innovation use How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome levels. The development of an innovation (at various stages) is an output. The scaling, uptake and use of an innovation can be reported as outcome. In PRMS the results can be linked. What are the two ways to report innovation use results (outcomes)?\n\n---\n\n[ID: docx:General reporting guidance.docx:u1-3]\nLink: https://sites.google.com/cgxchange.org/cgiarprhub/2025-reporting?authuser=0\nFile: General reporting guidance.docx\nLocation: section 'General reporting guidance' paragraph 1 to section 'General reporting guidance' paragraph 5\nContent: General reporting guidance Is there guidance on what should be reported as a result? Yes, this document provides some principles for ensuring a focus on quality, rather than quantity, in terms of results reporting: Guidance on ensuring quality over quantity. Is there guidance available on how to distinguish between outputs and outcomes? Yes, information on what to report as an output or outcome can be found here: Guidance on reporting outputs or outcomes.\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 31 part 3\nContent: the Theories of Change (overall, Areas of Work and sub-Areas) for consistency and alignment with stated objectives. (more details in Section 3.1 of this report) We have revised the HLOs at sub-area of work level, to harmonize the approach, remove duplications, and prioritize. There are now 26 HLOs. − We have harmonized the intermediate outcomes across sub-AoWs, AoWs, and Accelerator level. There are now five intermediate outcomes for AoW on Solutions and three for AoW on Change. − We have moved one outcome from the intermediate level to the end-of-program level and there are now four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and\n\n---\n\n[ID: pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p18pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP02%20%2D%20Sustainable%20Farming%2FSustainable%20Farming%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP02%20%2D%20Sustainable%20Farming&amp;p=true&amp;ga=1\nFile: Sustainable Farming_MELIA Plan 30-06-2025.pdf\nLocation: page 18 part 4\nContent: better understand farmer perspectives, motivations, and constraints concerning the adoption of SFP innovations. 4. Adoption or diffusion studies addressing learning questions on the TOC The baseline surveys conducted in Ghana, Malawi, and Ethiopia focusing on sustainable intensification technologies will form the basis for the adoption and impacts studies. These studies will seek to answer the following causal impact learning questions: ( 1) What factors are constraining/enabling the scaling and adoption as well as the intensity of use of the SFP innovations? and (2) How does adoption of the SFP innovations impact yield, farm income and household income? (3) What are the most promising inte grated farm -level innovation bundles to improve sustainability, equity, and agronomic gain at scale within the selected geographies of the program? To answer these questions, adoption and impact studies build up on the baseline studies (panel survey) to assess the extent, pathways, and determinants of\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p8pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 8 part 4\nContent: been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E) Effectiveness (the extent that the intended results or outcomes are achieved) High This criterion directly relates to the MELIA objectives. Assessing the effectiveness of the Intermediate Outcomes will inform contribution analysis and inform the design requirements of future programs. KEQ2. To what extent has B4T and its AOWs effectively achieved the intended intermediate outcomes? RQ2 How did prioritization using the Design Standard contribute to maximized impact (AOW1 MI)? RQ7 To what extent has B4T increased uptake of varieties by scaling partners who have a widespread reach (collectively)? (AOW3 ID) RQ8 To what extent has CGIAR-NARES prioritization of products encouraged targeted investment for breeding?\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p31pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_Inception Report 30-06-2025.pdf\nLocation: page 31 part 4\nContent: four 2030 outcomes. − We have updated the indicators and targets for HLOs and outcomes, ensuring it is clear what the Accelerator will deliver, what changes it aims to influence, and how those would be measured. − We have revised and clearly defined assumptions that underpin each individual HLO and outcome, as well as explaining the connections between the HLOs and outcomes. Bill and Melinda Gates Foundation High-level vision lacks any data points. The FAO data on women's increase in hunger (vis- a-vis men's) would seem to fit well with the \"challenges and megatrends\" for example. More recent FAO data points on gender issues in climate change might help set the table for Data points have been added in the final version of the proposal.\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 23 part 1\nContent: Key Evaluation Questions Some guiding questions that will inform future evaluations include: • Are the Program’s assumptions about actor behavior, incentives, and influence valid for the specific stakeholders identified, and are they likely to lead to the intended outcomes? • How do differences in AoW presence across countries affect the Program’s ability to deliver its intended outcomes? • Are the current configurations of AoWs efficient and synergistic, or are there opportunities to increase impact through structural changes? • What mechanisms exist (or are lacking) to integrate bilateral and W3-funded results into core program planning and reporting? • To what extent is MELIA evidence used to inform planning, learning, and adaptation across the Program? • How well do program assumptions and outcome pathways reflect national priorities and systems capacities in each geography? • • What types of MELIA findings\n\n---\n\n[ID: docx:2025 Technical Reporting MELIA glossary.docx:u31-34]\nLink: https://docs.google.com/document/d/19V8HwQN50riKrU7GomHQ4J8_aBuyngrh/edit\nFile: 2025 Technical Reporting MELIA glossary.docx\nLocation: table 1 row 28 to table 1 row 31\nContent: Intermediate outcome | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. | Intermediate outcomes are necessary steps towards achieving the 2030 outcomes. Intermediate outcomes will lead to the 2030 outcomes, although the actors and units of measure may be different. 2030 outcome | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. | 2030 outcomes are the final, highest-level outcomes to be achieved by the end of 2030 by the Programs/Accelerators/Projects. It is expected that these 2030 outcomes would lead to measurable impacts. Output | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. | Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples: new research methods, policy analyses, gene maps, new crop varieties and breeds, institutional innovations or other products of research work, partnerships because of a signed memorandum of understanding. High-level output | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on).\n\n---\n\n[ID: pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3]\nLink: https://cgspace.cgiar.org/items/ee7728da-7575-4e37-9b7e-c2a7cd23b1c9\nFile: CGIAR_ImpactReport_2022-24.pdf\nLocation: page 47 part 3\nContent: of this report. Comparison with 2017–2021 Retrospective analysis of CGIAR’s 2017 to 2021 reporting cycle provides a reference point for assessing progress in outcome reporting and portfolio management under the current Results Framework. While differences in the reporting systems limit direct comparability, several structural patterns from the previous cycle remain relevant. Policy outcomes Learnings from CGIAR’s 2017 to 2021 reporting cycle demonstrate that policy outcomes were mostly oriented toward policies and strategies (75 percent), and the rest influenced budget and investment decisions or legal instruments.29 The majority reflected early uptake of research results, but 39 percent of policy outcomes were concrete decisions, policies, or programs taken or enacted. In the current 2022 to 2024 cycle, there was a slight increase in the percentage of reported policy changes that were actual policies or programs put into place (43 percent of policy outcomes). Moreover , the type of policy outcome differed, with the percentage of policy outcomes leading to modified programs or investments jumping to 29 percent. The thematic and geographic orientations of policy outcomes are similar across the two periods, generally displaying CGIAR effectiveness in all of its priority countries and across most of its Impact Areas. However , the percentage of policy outcomes which were aimed primarily at gender equality was low in both periods. Partners were critical to CGIAR’s success in informing policies. Critical partners included national and subnational governments, civil society organizations, private sector , regional bodies, and international organizations. The review of 2017 to 2021 policy outcomes also revealed that very few were evaluated for their impacts, yet many appeared to be significant. Some examples of those are in Table 3. Impacts of CGIAR’s policy research remain underanalyzed. Policy outcome type What the evidence shows Illustrative cases CGIAR partners Outcomes Policy and strategy outcomes, mainly at national level 60% of outcomes were national and 37% reached formal enactment— often when a ministry or regulatory body was part of the design team Ethiopian\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 2\nContent: in breeding contribute to increased rate of genetic gain, as captured in the extent of improvement and impact achieved by products. Efficiency is included in an intermediate outcome so any effectiveness evaluation of intermediate outcomes will be duplicative. This criterion is most relevant to AOW4 as it is designed to support efficient access and use of modernized breeding. An AOW level outcome has captured this so any effectiveness evaluation of outcomes will duplicate efficiency. Research questions will contribute to KEQ2 on effectiveness: To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? RQ12 How has the use of interoperable, scaled breeding tools and services increased\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p60pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 60 part 4\nContent: in thriving Multifunctional Landscapes • Number of policy innovations that support the transition to sustained MFLs what was the contribution of the MFL Program interventions to these changes. This will allow us to identify the most impactful Outcomes related to the Impact Areas and orient Outcome Evidencing studies for efficient use of MELIA resources.\n\n---\n\n[ID: docx:Innovation development.docx:u1-4]\nLink: https://sites.google.com/cgxchange.org/cgiarprhub/2025-reporting?authuser=0\nFile: Innovation development.docx\nLocation: section 'Innovation development' paragraph 1 to section 'Innovation development' paragraph 7\nContent: Innovation development How do I determine if I should report an innovation as an output (innovation development) or an outcome (innovation use)? Innovations can be reported at both the output and outcome level. The development of an innovation (at various stages of design, testing and validation) is an output. The scaling or use of an innovation is an outcome. You may first report an innovation at the output level. If the innovation advances and starts to be used, it should then be reported as an outcome. Do I need to update innovations that were submitted during previous reporting periods?\n\n---\n\n[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 3\nContent: activities of the CapSha Accelerator, its products and services, contribute to improved capacity development practices, resulting in more equitable partnerships? • Are CGIAR NARES partners, donors and CapSha expert institutions making use of CapSha products and services? • Are CGIAR NARES partners, donors and CapSha expert institutions member of the CapSha Cop? • To what extent are the CapSha Accelerator’s objectives aligned with the needs and priorities of Southern partners? • What elements of the partnership model have the potential to be scaled or replicated in other regions or contexts? What are the enabling and limiting factors affecting scalability? How have Southern partners contributed to or led scaling efforts, and what support mechanisms have been most effective? • What measurable\n\n---\n\n[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt4]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%20%2D%20MELIA%20Plan%2030%2D06%2D2025%2D%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations - MELIA Plan 30-06-2025-.pdf\nLocation: page 5 part 4\nContent: Growth) and 10 (Reduced Inequalities). The progress towards the 2030 Outcomes is operationalized via six AoWs, contributing to 11 Intermediate outcomes which consolidate outputs from the 20 High -level outputs of the Policy Program. All Intermediate Outcomes contribute towards the 2030 Outcomes. For example, Intermediate outcomes 1.2.1 (Partners use outlook reports to inform and enhance design of their strategies and policies), 4.2.1 (Partners achieve a shared understanding of emerging ch allenges in WEFE systems and foresight data, tools and analysis), 5.2.1 (Countries co-create national strategies and policies) and 6.2.2 (CGIAR researchers and partners have enh anced capacity) all address the capacity challenge and contribute to the impact pathway achieving 2030 Outcome1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs. This 2030 Outcome in turn, also addresses CGIAR Portfolio Outcome #1: Implementation partners (e.g. NARES, NGOs, private companies) actively support\n\n---\n\n[ID: pdf:Genebanks_Inception Report 30-06-2025.pdf:p31pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks%2FGenebanks%5FInception%20Report%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP13%20%2D%20Genebanks&amp;p=true&amp;ga=1\nFile: Genebanks_Inception Report 30-06-2025.pdf\nLocation: page 31 part 3\nContent: the misuse of funds for purposes outside what is set up in the\n\n---\n\n[ID: pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow%2FBreeding%20for%20Tomorrow%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP01%20%2D%20Breeding%20for%20Tomorrow&amp;p=true&amp;ga=1\nFile: Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 30 part 1\nContent: RQ17 What proportion of marginalized beneficiaries in each market segment have accessed improved varieties? (AOW3 ID) RQ29 What extent of value proposition is needed to motivate adoption? KEQ2. To what extent has B4T and its AOW effectively achieved the intended intermediate outcomes? Coherence RQ4 How have the network strategies improved coherence with region x crop investments? (AOW5 E) RQ5 How have bottlenecks or barriers between variety development and seed systems been overcome to improve smallholder access to seed? (AOW3 ID) RQ6 How has B4T’s work with other CGIAR investments increased or improved the achievement of 2030 outcomes? (AOW5 E)\n\n---\n\n[ID: pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p5pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations%2FPolicy%20Innovations%20%2D%20MELIA%20Plan%2030%2D06%2D2025%2D%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP07%20%2D%20Policy%20Innovations&amp;p=true&amp;ga=1\nFile: Policy Innovations - MELIA Plan 30-06-2025-.pdf\nLocation: page 5 part 2\nContent: capacity &amp; tools. . The Program’s Theory of Change works through six interconnected Areas of Work (AoWs), their High- level Outputs (HLOs), leading to Intermediate Outcomes and finally to three 2030 Outcomes. During the inception phase the Policy Program align ed the Intermediate Outcomes and 2030 Outcomes to these 3 pillars. The 2030 Outcomes were revised to contribute to our impact around these. 2030 Outcome 1: National think tanks analytical and institutional capacity strengthened to guide policy and investment decisions considering trade-offs between SDGs: represents the Capacity and tools pillar, 2030 Outcome 2: Global, regional institutions and governments use knowledge products on foresight, impact assessm ent and governance to guide pro -poor, gender-inclusive and climate smart policies and investments, represents Rapid Response and policy guidance pillar while 2030 Outcome 3: Governments and partners adopt policy responses to address local, national, regional and global challenges and shocks, contributing to more\n\n---\n\n[ID: pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p32pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes%2FMultifunctional%20Landscapes%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP04%20%2D%20Multifunctional%20Landscapes&amp;p=true&amp;ga=1\nFile: Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf\nLocation: page 32 part 3\nContent: Outcome Evidencing/ Outcome Trajectory evaluation instruments: Document review, workshops, key informant interviews, secondary data System-based Theory of Change Actor engagement and outcome tracker AoW6 assessments AoW7 partner capacity evaluation • To what extent does co</t>
+  </si>
+  <si>
+    <t>[{"role": "system", "content": "You are a RAG assistant for deeper research. Preserve acronyms EXACTLY as written. Exactly phrase: 'I cannot find information in the provided chunks to answer this.' Output instructions: - 3 to 5 sentences, neutral and direct style, no lists. - ALWAYS answer in English and adapt wording to the question's context. - End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'."}, {"role": "user", "content": "Question: what are the different types of outputs in the cgiar results framework?\n\nContext:\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 19 part 1\nContent: Results framework The program result\n\n---\n\n[ID: pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p6pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1\nFile: Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 6 part 2\nContent: Work 2.3 Results framework The CapSha Accelerator results framework has been\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 22 part 4\nContent: CGIAR Results Framework – Portfolio Outcome\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p22pt4]\nLink: N/A\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf\nLocation: page 22 part 4\nContent: CGIAR Results Framework – Portfolio Outcome\n\n---\n\n[ID: pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p21pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP12%20%2D%20Digital%20Transformation%2FDigital%20Transformation%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP12%20%2D%20Digital%20Transformation&amp;p=true&amp;ga=1\nFile: Digital Transformation_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 21 part 2\nContent: types For reference only, the current MELIA study types defined in\n\n---\n\n[ID: pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p7pt1]\nLink: N/A\nFile: CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf\nLocation: page 7 part 1\nContent: CGIAR Performance and Results Management Framework 2022-2030 CGIAR System Organization Page 7 of 20 4. Results framework CGIAR’s results framework is directly aligned to the five impact areas and Sustainable Development Goals. Three distinct result types: outputs, outcomes and impacts are mapped to the spheres of Control, Influence and Interest, respectively. • Output: Knowledge, technical or institutional advancement produced by CGIAR research, engagement and/or capacity development activities. Examples of outputs include new research methods, policy analyses, gene maps, new crop varieties and breeds, or other products of research work. • Outcome: A change in knowledge, skills, attitudes and/or relationships, which manifests as a change in behavior of users of outputs, to which a combination of research outputs and related activities have contributed. •\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 5 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p5pt1]\nLink: N/A\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf\nLocation: page 5 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 5 of results across different sources of funding will be set out as part of this Technical Reporting Arrangement. The Programs and Accelerators aim to provide frameworks for greater complementarity and synergy across different sources and types of funding (CGIAR Trust Fund Windows 1 -2, Window 3 and bilateral funding), while enhancing transparency and accountability. A n updated results\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt3]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 11 part 3\nContent: portfolio-level outcome, and portfolio level contribution to Impact Area targets reporting. The foundations of the current Results Framework (2022-24) remain: • Impact Areas linked to Sustainable Development Goals • Impact, outcome, and output result levels • Result types/categories o Outcome: Innovation use, Policy change, Other. o Output: Innovation development, Capacity sharing, Knowledge products, Other • A small number of Standard Indicators The updated CGIAR Results Framework in Annex 1 will be finalized in Q1-2 2025. The m ain updates included in the 2025-30 Results Framework include: • Revised Impact Area indicators Shortcomings with the Impact Area indicators in the 2022-24 Results Framework have been identified, including absence of some important indicators for CGIAR (e.g.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt3]\nLink: N/A\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf\nLocation: page 11 part 3\nContent: portfolio-level outcome, and portfolio level contribution to Impact Area targets reporting. The foundations of the current Results Framework (2022-24) remain: • Impact Areas linked to Sustainable Development Goals • Impact, outcome, and output result levels • Result types/categories o Outcome: Innovation use, Policy change, Other. o Output: Innovation development, Capacity sharing, Knowledge products, Other • A small number of Standard Indicators The updated CGIAR Results Framework in Annex 1 will be finalized in Q1-2 2025. The m ain updates included in the 2025-30 Results Framework include: • Revised Impact Area indicators Shortcomings with the Impact Area indicators in the 2022-24 Results Framework have been identified, including absence of some important indicators for CGIAR (e.g.\n\n---\n\n[ID: pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p9pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP12%20%2D%20Digital%20Transformation%2FDigital%20Transformation%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP12%20%2D%20Digital%20Transformation&amp;p=true&amp;ga=1\nFile: Digital Transformation_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 9 part 3\nContent: Results Framework Please refer\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p28pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf\nLocation: page 28 part 2\nContent: 4. MELIA study types For reference only, the current MELIA study types\n\n---\n\n[ID: docx:2025 Technical Reporting MELIA glossary.docx:u55-58]\nLink: https://docs.google.com/document/d/19V8HwQN50riKrU7GomHQ4J8_aBuyngrh/edit\nFile: 2025 Technical Reporting MELIA glossary.docx\nLocation: table 1 row 52 to table 1 row 55\nContent: Policy change | Policies, strategies, legal instruments, programs, budgets, or investments at different scales (local to global) that have been modified in design or implementation, with evidence that the change was informed by CGIAR research. | Policies, strategies, legal instruments, programs, budgets, or investments at different scales (local to global) that have been modified in design or implementation, with evidence that the change was informed by CGIAR research. | Policies, strategies, legal instruments, programs, budgets, or investments at different scales (local to global) that have been modified in design or implementation, with evidence that the change was informed by CGIAR research. Portfolio | The CGIAR System Framework approved by the System’s Funders and Centers in June 2016, and then amended in October 2024, defines “CGIAR Portfolio” as the research programs and/or platforms carried out by the Centers and the CGIAR System Partners in support of the CGIAR Strategy and Results Framework and which are supported by (i) the CGIAR Trust Fund and/or (ii) bilateral sources contractually aligned to such programs and/or platforms. | The CGIAR System Framework approved by the System’s Funders and Centers in June 2016, and then amended in October 2024, defines “CGIAR Portfolio” as the research programs and/or platforms carried out by the Centers and the CGIAR System Partners in support of the CGIAR Strategy and Results Framework and which are supported by (i) the CGIAR Trust Fund and/or (ii) bilateral sources contractually aligned to such programs and/or platforms. | The CGIAR System Framework approved by the System’s Funders and Centers in June 2016, and then amended in October 2024, defines “CGIAR Portfolio” as the research programs and/or platforms carried out by the Centers and the CGIAR System Partners in support of the CGIAR Strategy and Results Framework and which are supported by (i) the CGIAR Trust Fund and/or (ii) bilateral sources contractually aligned to such programs and/or platforms. Program | CGIAR Programs are the main vehicle for delivery of research and innovation by CGIAR from 2025 to 2030. Programs serve as entry points to describe CGIAR’s offer on a key topic, elevating CGIAR’s visibility in global agendas and facilitating the continuation and formation of inclusive alliances and partnerships. They state quantitatively what impacts and outcomes they intend to achieve, along a theory of change. They come with evaluable results frameworks and clear reporting of results against investment. Bilateral and window 3 projects are aligned to Programs and Accelerators and their results are reported as part of Program and Accelerator reporting. | CGIAR Programs are the main vehicle for delivery of research and innovation by CGIAR from 2025 to 2030. Programs serve as entry points to describe CGIAR’s offer on a key topic, elevating CGIAR’s visibility in global agendas and facilitating the continuation and formation of inclusive alliances and partnerships. They state quantitatively what impacts and outcomes they intend to achieve, along a theory of change. They come with evaluable results frameworks and clear reporting of results against investment. Bilateral and window 3 projects are aligned to Programs and Accelerators and their results are reported as part of Program and Accelerator reporting. | CGIAR Programs are the main vehicle for delivery of research and innovation by CGIAR from 2025 to 2030. Programs serve as entry points to describe CGIAR’s offer on a key topic, elevating CGIAR’s visibility in global agendas and facilitating the continuation and formation of inclusive alliances and partnerships. They state quantitatively what impacts and outcomes they intend to achieve, along a theory of change. They come with evaluable results frameworks and clear reporting of results against investment. Bilateral and window 3 projects are aligned to Programs and Accelerators and their results are reported as part of Program and Accelerator reporting. Result | The product of an activity by CGIAR staff or due in part to CGIAR staff, described as an output, outcome or impact. | The product of an activity by CGIAR staff or due in part to CGIAR staff, described as an output, outcome or impact. | The product of an activity by CGIAR staff or due in part to CGIAR staff, described as an output, outcome or impact.\n\n---\n\n[ID: pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p9pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP02%20%2D%20Sustainable%20Farming%2FSustainable%20Farming%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP02%20%2D%20Sustainable%20Farming&amp;p=true&amp;ga=1\nFile: Sustainable Farming_MELIA Plan 30-06-2025.pdf\nLocation: page 9 part 2\nContent: Mitigation, Nutrition, Poverty Reduction and Livelihoods, Gender Equality and Social Inclusion, and Environmental Health and Biodiversity. The SFP results framework operationalizes this contribution by aligning program indicators and learning activities with CGIAR’s Performance and Results Management Framework (PRMF) and systematically collect evidence across the eight AoWs. Each AoW is designed to deliver results that directly or indirectly support one or more CGIAR Impact Areas. The framework provides a coherent roadmap for measuring the SFP contributions. Open Access link for both the ToC and the Results Framework . (Download the Results Framework as part of several other worksheets-e.g., assumptions, research questions, etc using the 3rd icon on the top left conner of the page). 3. Monitoring plan for HLOs and outcomes This section outlines how the Program will monitor delivery of HLOs and progress towards\n\n---\n\n[ID: pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact%2FScaling%20for%20Impact%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP09%20%2D%20Scaling%20for%20Impact&amp;p=true&amp;ga=1\nFile: Scaling for Impact_MELIA Plan 30-06-2025.pdf\nLocation: page 7 part 1\nContent: 7 Results framework The Result Framework presents a structured articulation of the intended results under CGIAR’s strategic Areas of Work (AOWs) for the period 2025 to 2030. It distinguishes between two types of results: High-Level Outputs (HLOs), which represent tangible, near-term deliverables from research eƯorts, and Intermediate Outcomes (IOCs), which indicate progress toward longer- term development goals and systemic change. Each result entry captures several key variables—among many others—that collectively deﬁne the pathway from research to impact. These include the thematic Area of Work to which the result contributes, the classiﬁcation of the result as either an output or outcome, and a short title paired with a detailed result statement that describes the intended change, innovation, or contribution. The responsible organization(s), often CGIAR centers, are identiﬁed alongside any listed partners and outcome actors, with additional information on whether those actors are directly engaged and what\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p16pt1]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 16 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 16 In doing so the line of sight will primarily focus on the outputs produced with pooled resources (sphere of control) while the outcomes are co -produced and do not require differentiation by source of funding. The rate of change Because Technical Report products will progressively integrate bilateral and W3 information, we expect that they will contain differing levels and types of W3 and bilateral project technical content (e.g. results data and narrative) and that this will evolve over time. There are likely to be different levels of bilateral and W3 technical information:\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p16pt1]\nLink: N/A\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf\nLocation: page 16 part 1\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 16 In doing so the line of sight will primarily focus on the outputs produced with pooled resources (sphere of control) while the outcomes are co -produced and do not require differentiation by source of funding. The rate of change Because Technical Report products will progressively integrate bilateral and W3 information, we expect that they will contain differing levels and types of W3 and bilateral project technical content (e.g. results data and narrative) and that this will evolve over time. There are likely to be different levels of bilateral and W3 technical information:\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 19 part 2\nContent: result framework is accessible from\n\n---\n\n[ID: pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p8pt2]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP02%20%2D%20Sustainable%20Farming%2FSustainable%20Farming%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP02%20%2D%20Sustainable%20Farming&amp;p=true&amp;ga=1\nFile: Sustainable Farming_MELIA Plan 30-06-2025.pdf\nLocation: page 8 part 2\nContent: the Program and Area of Work levels. This link gives the ToC tables-overall and AoW ToCs) and Open Access link for both the ToC and the Results Framework . (Zoom out to see the linkages of the various AoW ToCs and download the ToC tables using the 4 th icon on the top left conner of the page). Figure 1. Sustainable Farming Program level Theory of Change Results framework The SFP Results Framework reflects the logical sequence from high-level outputs to intermediate outcomes, aligned with the program’s Theory of Change. It captures the intended contributions of each AoW,\n\n---\n\n[ID: docx:2025 Technical Reporting MELIA glossary.docx:u34-37]\nLink: https://docs.google.com/document/d/19V8HwQN50riKrU7GomHQ4J8_aBuyngrh/edit\nFile: 2025 Technical Reporting MELIA glossary.docx\nLocation: table 1 row 31 to table 1 row 34\nContent: High-level output | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). | High-level outputs are aggregated clusters of outputs which are linked by the intention to achieve a specific outcome. The high-level outputs should be relatively downstream – i.e. ready to be used by next/end users – and would often be composed of various different types of outputs (e.g. knowledge products, innovations, capacity sharing activities and so on). Partner | Organizations or individual stakeholders that CGIAR collaborates with to achieve its goals for which proof exists, i.e., memorandum of understanding, joint code of practice, a contract under a joint proposal. Partners can also be beneficiaries of CGIAR’s interventions. Examples: demand partner, innovation partner and scaling partner. | Organizations or individual stakeholders that CGIAR collaborates with to achieve its goals for which proof exists, i.e., memorandum of understanding, joint code of practice, a contract under a joint proposal. Partners can also be beneficiaries of CGIAR’s interventions. Examples: demand partner, innovation partner and scaling partner. | Organizations or individual stakeholders that CGIAR collaborates with to achieve its goals for which proof exists, i.e., memorandum of understanding, joint code of practice, a contract under a joint proposal. Partners can also be beneficiaries of CGIAR’s interventions. Examples: demand partner, innovation partner and scaling partner. Partner typology (CGIAR) | CGIAR uses a partner typology to define partner types. Definitions are presented below. | CGIAR uses a partner typology to define partner types. Definitions are presented below. | CGIAR uses a partner typology to define partner types. Definitions are presented below. Partner typology (CGIAR) | CGIAR type | CGIAR type definition\n\n---\n\n[ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p32pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1\nFile: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf\nLocation: page 32 part 3\nContent: tab in the program result s framework accessible\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt2]\nLink: https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 11 part 2\nContent: Reporting. We will progressively add curated datasets (such as Center-level databases) into the QA process to remove to the extent possible the need for double reporting. Existing experience gained through automated PRMS solutions (e.g. screening knowledge products against FAIR criteria) will be leveraged. 3. CGIAR Results Framework, MELIA, Indicator Toolkit and data collection protocols CGIAR Results Framework The CGIAR Results Framework will be used by Programs and Accelerators as the basis of their TOC design, MELIA and Technical Reporting. It will provide the basis for geographic portfolio-level outcome, and portfolio level contribution to Impact Area targets reporting. The foundations of the current Results Framework (2022-24) remain: • Impact Areas linked to Sustainable Development Goals\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt2]\nLink: N/A\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf\nLocation: page 11 part 2\nContent: Reporting. We will progressively add curated datasets (such as Center-level databases) into the QA process to remove to the extent possible the need for double reporting. Existing experience gained through automated PRMS solutions (e.g. screening knowledge products against FAIR criteria) will be leveraged. 3. CGIAR Results Framework, MELIA, Indicator Toolkit and data collection protocols CGIAR Results Framework The CGIAR Results Framework will be used by Programs and Accelerators as the basis of their TOC design, MELIA and Technical Reporting. It will provide the basis for geographic portfolio-level outcome, and portfolio level contribution to Impact Area targets reporting. The foundations of the current Results Framework (2022-24) remain: • Impact Areas linked to Sustainable Development Goals\n\n---\n\n[ID: pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p3pt1]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP02%20%2D%20Sustainable%20Farming%2FSustainable%20Farming%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP02%20%2D%20Sustainable%20Farming&amp;p=true&amp;ga=1\nFile: Sustainable Farming_MELIA Plan 30-06-2025.pdf\nLocation: page 3 part 1\nContent: 3 1. Reviewing guidance for developing the MELIA Plan Developing the Sustainable Farming program (SFP) MELIA plan, started with the review of the ISDC feedback on the overall program Theory of Change (ToC) and the Area of Work (AoW) ToCs. This feedback has been used in updating the ToC, (example, creating indicators for AoW 8 - Program Efficiency and Delivery . In addition, the core assessment criteria from the IAES evaluability assessment guide were used as reference checks in developing the MELIA plan. 2. Program overview and results framework This section provides a n overview of the Sustainable Farming Program (SFP), outlining its intervention logic and the results framework. It also details the alignment of the Program’s results framework with the CGIAR Performance and Results Management Framework (PRMF) and Portfolio outcomes, ensuring system thinking. Program overview SFP is designed to respond to\n\n---\n\n[ID: pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p18pt3]\nLink: https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion%2FGender%20Equality%20and%20Inclusion%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP10%20%2D%20Gender%20Equality%20and%20Inclusion&amp;p=true&amp;ga=1\nFile: Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf\nLocation: page 18 part 3\nContent: 2030 Outcome, or Impact Indicate the result short title from the Results Framework Indicate the indicator title from the Results Framework Provide the assumption( s) statem ent from the Results Framework Indicate the location(s) where the study will be conducted Indicate the methods and design approaches that will be used for the study List the Program(s) and Accelerator( s ) you will collaborate with or coordinate for the implementati on of this study. Indicate the Start\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p11pt4]\nLink: https://storage.googleapis.com/cgiarorg/2025/05/Type3_2024Report.pdf\nFile: Type3_2024Report.pdf\nLocation: page 11 part 4\nContent: System (PRMS): The PRMS serves as the central reporting platform, powering the Results Dashboard and supporting the development of Type 1 Reports with real-time data aggregation and analysis. These components were instrumental in driving the 2024 Technical Reporting process, and key elements will be carried forward to shape Technical Reporting in the next CGIAR Portfolio, ensuring continuity, alignment, and continuous improvement. Monitoring tools tailored to suit core indicators Non-pooled projects Type 1 Type 3 Science Group Projects Research and Performance and Results Management Framework Arrangement CGIAR Results Framework Standard Indicator Theory of Change and Scaling Readiness (IPSR) Quality Assurance criteria, process Performance and Results Management System Type 2 Triennial Outcome/Impact Report Annual Technical Report Results Dashboard $771M Revenue 2% 23% 44% 31% Revenue by Funding Source Windows 1&amp;2 | Window 3 | Bilateral | Other 1 2 3 4 5 6 7 8 9 10 13 12 11 6. CGIAR 2030 Research and Innovation Strategy 7. Performance and Results Management Framework 8. Technical Reporting Arrangement 9. CGIAR Results Framework 10. Standard Indicator Description Sheets: • Output level • Outcome level 11. Theory of Change 12. IPSR • Output level • Outcome level • IPM for responsible food systems transformation • Scaling Readiness website • Online course on Innovation and Scaling • Scaling Readiness calculator • Scaling Directory 13. Adaptive Management 14. Quality Assurance 15. PRMS &amp; TOC board 16. Results Dashboard 17. 2022 &amp; 2023 Annual Technical Reports 18. Type 2 repo</t>
   </si>
 </sst>
 </file>
@@ -2640,7 +3144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2683,7 +3187,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2695,16 +3199,16 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="I2" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2712,7 +3216,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -2724,16 +3228,16 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H3" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="I3" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2741,7 +3245,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -2753,16 +3257,16 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H4" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I4" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2770,7 +3274,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -2782,16 +3286,16 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H5" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="I5" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2799,7 +3303,7 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -2811,16 +3315,16 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I6" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2828,7 +3332,7 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -2840,16 +3344,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G7" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H7" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="I7" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2857,7 +3361,7 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -2869,16 +3373,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G8" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H8" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="I8" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2886,7 +3390,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -2898,16 +3402,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G9" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I9" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2915,7 +3419,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -2927,16 +3431,16 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H10" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="I10" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2944,7 +3448,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -2956,16 +3460,16 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G11" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="I11" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2973,7 +3477,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -2985,16 +3489,16 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G12" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H12" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="I12" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3002,7 +3506,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -3014,16 +3518,16 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G13" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H13" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I13" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3031,7 +3535,7 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -3043,16 +3547,16 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G14" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H14" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="I14" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3060,7 +3564,7 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -3072,16 +3576,16 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H15" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="I15" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3089,7 +3593,7 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -3101,16 +3605,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G16" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H16" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I16" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3118,7 +3622,7 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -3130,16 +3634,16 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G17" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H17" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I17" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3147,7 +3651,7 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -3159,16 +3663,16 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G18" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H18" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="I18" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3176,7 +3680,7 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -3188,16 +3692,16 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G19" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H19" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="I19" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3205,7 +3709,7 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -3217,16 +3721,16 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H20" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="I20" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3234,7 +3738,7 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -3246,22 +3750,22 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H21" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="I21" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="J21" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="K21" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3269,7 +3773,7 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -3281,22 +3785,22 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H22" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="I22" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="J22" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="K22" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3304,7 +3808,7 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -3316,22 +3820,22 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H23" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="I23" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="J23" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="K23" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3339,7 +3843,7 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C24">
         <v>200</v>
@@ -3351,22 +3855,22 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H24" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="I24" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="J24" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="K24" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3374,7 +3878,7 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C25">
         <v>200</v>
@@ -3386,22 +3890,22 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H25" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="I25" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="J25" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="K25" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -3409,7 +3913,7 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C26">
         <v>200</v>
@@ -3421,22 +3925,22 @@
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H26" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="I26" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="J26" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="K26" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3444,7 +3948,7 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C27">
         <v>200</v>
@@ -3456,22 +3960,22 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H27" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="I27" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="J27" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="K27" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3479,7 +3983,7 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C28">
         <v>200</v>
@@ -3491,22 +3995,22 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H28" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="I28" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="J28" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="K28" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3514,7 +4018,7 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C29">
         <v>200</v>
@@ -3526,22 +4030,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G29" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I29" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="J29" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="K29" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3549,7 +4053,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -3561,22 +4065,22 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H30" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="I30" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="J30" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="K30" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3584,7 +4088,7 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -3596,22 +4100,22 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H31" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I31" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="J31" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="K31" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3619,7 +4123,7 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -3631,22 +4135,22 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G32" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H32" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="I32" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="J32" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K32" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3654,7 +4158,7 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -3666,22 +4170,22 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H33" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J33" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K33" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3689,7 +4193,7 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -3701,22 +4205,22 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G34" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H34" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J34" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K34" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3724,7 +4228,7 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -3736,22 +4240,22 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G35" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H35" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J35" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K35" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3759,7 +4263,7 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C36">
         <v>100</v>
@@ -3771,22 +4275,22 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G36" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H36" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J36" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K36" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3794,7 +4298,7 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C37">
         <v>100</v>
@@ -3806,22 +4310,22 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H37" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="J37" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K37" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3829,7 +4333,7 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -3841,22 +4345,22 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H38" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J38" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K38" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3864,7 +4368,7 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -3876,22 +4380,22 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G39" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H39" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="I39" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J39" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="K39" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3899,7 +4403,7 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C40">
         <v>100</v>
@@ -3911,22 +4415,22 @@
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H40" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="I40" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J40" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="K40" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3934,7 +4438,7 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C41">
         <v>100</v>
@@ -3946,22 +4450,22 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H41" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="I41" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J41" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="K41" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -3969,7 +4473,7 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C42">
         <v>100</v>
@@ -3981,22 +4485,22 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G42" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H42" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="I42" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J42" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="K42" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -4004,7 +4508,7 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C43">
         <v>100</v>
@@ -4016,22 +4520,22 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G43" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H43" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I43" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J43" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="K43" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -4039,7 +4543,7 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C44">
         <v>100</v>
@@ -4051,22 +4555,22 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G44" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H44" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="I44" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J44" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="K44" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -4083,13 +4587,13 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="K45" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -4097,7 +4601,7 @@
         <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C46">
         <v>100</v>
@@ -4109,22 +4613,22 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H46" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="I46" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J46" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="K46" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -4132,7 +4636,7 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C47">
         <v>100</v>
@@ -4144,22 +4648,22 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G47" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H47" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="I47" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J47" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="K47" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -4167,7 +4671,7 @@
         <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C48">
         <v>100</v>
@@ -4179,22 +4683,22 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H48" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="J48" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="K48" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -4202,7 +4706,7 @@
         <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C49">
         <v>200</v>
@@ -4214,22 +4718,22 @@
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G49" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="H49" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="J49" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="K49" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -4237,7 +4741,7 @@
         <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C50">
         <v>200</v>
@@ -4249,22 +4753,22 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G50" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H50" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="J50" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="K50" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -4272,7 +4776,7 @@
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C51">
         <v>200</v>
@@ -4284,22 +4788,22 @@
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G51" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H51" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="J51" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="K51" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4307,7 +4811,7 @@
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C52">
         <v>200</v>
@@ -4319,22 +4823,22 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G52" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H52" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="J52" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="K52" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -4342,7 +4846,7 @@
         <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C53">
         <v>200</v>
@@ -4354,22 +4858,22 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G53" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H53" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="J53" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="K53" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4377,7 +4881,7 @@
         <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C54">
         <v>200</v>
@@ -4389,22 +4893,22 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G54" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H54" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="J54" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="K54" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4412,7 +4916,7 @@
         <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C55">
         <v>200</v>
@@ -4424,22 +4928,22 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G55" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H55" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="J55" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="K55" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -4447,7 +4951,7 @@
         <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C56">
         <v>200</v>
@@ -4459,22 +4963,22 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G56" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="H56" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="J56" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="K56" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4482,7 +4986,7 @@
         <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C57">
         <v>200</v>
@@ -4494,22 +4998,22 @@
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G57" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H57" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="J57" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="K57" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -4517,7 +5021,7 @@
         <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C58">
         <v>200</v>
@@ -4529,22 +5033,22 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G58" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H58" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="J58" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="K58" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -4552,7 +5056,7 @@
         <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C59">
         <v>200</v>
@@ -4564,22 +5068,22 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G59" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="H59" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="J59" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="K59" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -4587,7 +5091,7 @@
         <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C60">
         <v>200</v>
@@ -4599,22 +5103,22 @@
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G60" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H60" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="I60" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="J60" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="K60" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4622,7 +5126,7 @@
         <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C61">
         <v>200</v>
@@ -4634,22 +5138,22 @@
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G61" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H61" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="I61" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="J61" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="K61" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -4657,7 +5161,7 @@
         <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C62">
         <v>200</v>
@@ -4669,22 +5173,197 @@
         <v>1</v>
       </c>
       <c r="F62" t="s">
+        <v>101</v>
+      </c>
+      <c r="G62" t="s">
+        <v>119</v>
+      </c>
+      <c r="H62" t="s">
+        <v>171</v>
+      </c>
+      <c r="I62" t="s">
+        <v>192</v>
+      </c>
+      <c r="J62" t="s">
+        <v>207</v>
+      </c>
+      <c r="K62" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63">
+        <v>190</v>
+      </c>
+      <c r="D63">
+        <v>190</v>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>101</v>
+      </c>
+      <c r="G63" t="s">
+        <v>120</v>
+      </c>
+      <c r="H63" t="s">
+        <v>172</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J63" t="s">
+        <v>208</v>
+      </c>
+      <c r="K63" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64">
+        <v>200</v>
+      </c>
+      <c r="D64">
+        <v>200</v>
+      </c>
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>101</v>
+      </c>
+      <c r="G64" t="s">
+        <v>121</v>
+      </c>
+      <c r="H64" t="s">
+        <v>173</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J64" t="s">
+        <v>209</v>
+      </c>
+      <c r="K64" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" t="s">
+        <v>92</v>
+      </c>
+      <c r="C65">
+        <v>200</v>
+      </c>
+      <c r="D65">
+        <v>200</v>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>101</v>
+      </c>
+      <c r="G65" t="s">
+        <v>122</v>
+      </c>
+      <c r="H65" t="s">
+        <v>174</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J65" t="s">
+        <v>210</v>
+      </c>
+      <c r="K65" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" t="s">
+        <v>92</v>
+      </c>
+      <c r="C66">
+        <v>200</v>
+      </c>
+      <c r="D66">
+        <v>200</v>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>101</v>
+      </c>
+      <c r="G66" t="s">
+        <v>122</v>
+      </c>
+      <c r="H66" t="s">
+        <v>175</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J66" t="s">
+        <v>210</v>
+      </c>
+      <c r="K66" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" t="s">
         <v>93</v>
       </c>
-      <c r="G62" t="s">
-        <v>111</v>
-      </c>
-      <c r="H62" t="s">
-        <v>159</v>
-      </c>
-      <c r="I62" t="s">
-        <v>175</v>
-      </c>
-      <c r="J62" t="s">
-        <v>188</v>
-      </c>
-      <c r="K62" t="s">
-        <v>209</v>
+      <c r="C67">
+        <v>200</v>
+      </c>
+      <c r="D67">
+        <v>200</v>
+      </c>
+      <c r="E67" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G67" t="s">
+        <v>123</v>
+      </c>
+      <c r="H67" t="s">
+        <v>176</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="J67" t="s">
+        <v>211</v>
+      </c>
+      <c r="K67" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -4707,6 +5386,11 @@
     <hyperlink ref="I57" r:id="rId16"/>
     <hyperlink ref="I58" r:id="rId17"/>
     <hyperlink ref="I59" r:id="rId18"/>
+    <hyperlink ref="I63" r:id="rId19"/>
+    <hyperlink ref="I64" r:id="rId20"/>
+    <hyperlink ref="I65" r:id="rId21"/>
+    <hyperlink ref="I66" r:id="rId22"/>
+    <hyperlink ref="I67" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Logs/interaction_log.xlsx
+++ b/Logs/interaction_log.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="244">
   <si>
     <t>timestamp</t>
   </si>
@@ -247,6 +247,9 @@
     <t>2025-09-26T09:07:14.972092</t>
   </si>
   <si>
+    <t>2025-09-26T11:34:52.334743</t>
+  </si>
+  <si>
     <t>What funding did 2024 Technical Reporting cover?</t>
   </si>
   <si>
@@ -296,6 +299,9 @@
   </si>
   <si>
     <t>what are the different types of outputs in the cgiar results framework?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who is responsible for approving changes to reporting categories and for balancing the benefits of collecting detailed information against the reporting burden on P/A? </t>
   </si>
   <si>
     <t xml:space="preserve">You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:
@@ -391,6 +397,9 @@
   </si>
   <si>
     <t>pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt1:0.380, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p6pt2:0.339, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4:0.329, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p22pt4:0.329, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p21pt2:0.311, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p7pt1:0.292, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5pt1:0.281, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p5pt1:0.281, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt3:0.277, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt3:0.277, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.276, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p28pt2:0.275, docx:2025 Technical Reporting MELIA glossary.docx:u55-58:0.272, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p9pt2:0.269, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt1:0.260, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p16pt1:0.255, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p16pt1:0.255, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt2:0.247, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p8pt2:0.247, docx:2025 Technical Reporting MELIA glossary.docx:u34-37:0.239, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p32pt3:0.234, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt2:0.229, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt2:0.229, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p3pt1:0.228, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p18pt3:0.227, pdf:Type3_2024Report.pdf:p11pt4:0.226, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p13pt1:0.226, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18pt2:0.225, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p18pt2:0.225, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p13pt1:0.222, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p13pt1:0.222, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p9pt1:0.218, pdf:CGI21-507032-PORB-Better Diets and Nutrition.pdf:p9pt2:0.216, docx:2025 Technical Reporting MELIA glossary.docx:u31-34:0.213, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p15pt3:0.213, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p10pt3:0.212, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt1:0.210, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p7pt1:0.210, pptx:Information Session on 2025 Technical Reporting.pptx:s14pt1:0.208, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p1pt1:0.207, pdf:Genebanks_Inception Report 30-06-2025.pdf:p18pt4:0.199, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p3pt1:0.196, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p26pt3:0.196, pdf:CGIAR_ImpactReport_2022-24.pdf:p9pt1:0.195, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p37pt4:0.195, docx:2025 Technical Reporting MELIA glossary.docx:u28-31:0.194, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p10pt1:0.194, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p23pt1:0.193, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.193, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p4pt4:0.191, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p3pt2:0.190, pdf:Sustainable Animal and Aquatic Foods_Inception Report 30-06-2025.pdf:p12pt4:0.189, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt1:0.189, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p1pt1:0.188, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p2pt1:0.188, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3:0.186, pdf:Food Frontiers and Security_MELIA Plan 30-06-2025.pdf:p3pt1:0.183, pptx:Information Session on 2025 Technical Reporting.pptx:s5pt2:0.182, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p3pt2:0.182, pdf:CGI21_508012_PORB_Genebanks.pdf:p1pt1:0.180, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p1pt1:0.180, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p1pt1:0.180, docx:Guidance on reporting outputs or outcomes.docx:u7-10:0.180, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt3:0.180, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt2:0.180, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p4pt2:0.180, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p11pt1:0.178, pdf:CGIAR_ImpactReport_2022-24.pdf:p12pt4:0.176, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p20pt1:0.176, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt2:0.176, pdf:Genebanks_Inception Report 30-06-2025.pdf:p13pt4:0.175, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p24pt1:0.174, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p9pt1:0.173, docx:Guidance on ensuring quality over quantity.docx:u4-7:0.173, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p28pt3:0.172, pdf:Type3_2024Report.pdf:p4pt4:0.171, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p21pt2:0.171, pdf:Genebanks_Inception Report 30-06-2025.pdf:p18pt3:0.171, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt3:0.170, pdf:Portfolio Narrative_2024.pdf:p11pt3:0.169, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p14pt1:0.168, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p19pt1:0.167, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p20pt1:0.167, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p33pt3:0.166, pdf:Type3_2024Report.pdf:p4pt1:0.166, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p9pt4:0.164, pdf:Genebanks_Inception Report 30-06-2025.pdf:p13pt1:0.164, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p8pt2:0.164, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p9pt1:0.163, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt4:0.163, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt4:0.163, pdf:CGIAR_ImpactReport_2022-24.pdf:p42pt1:0.162, docx:2025 Technical Reporting MELIA glossary.docx:u52-55:0.161, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p17pt1:0.161, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p17pt1:0.161, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.161, pdf:Portfolio Narrative_2024.pdf:p5pt3:0.160, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p32pt4:0.160, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p10pt3:0.159, docx:Guidance on complementary innnov.docx:u4-7:0.159, pdf:Portfolio Narrative_2024.pdf:p30pt3:0.159, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p22pt4:0.159, pdf:Portfolio Narrative_2024.pdf:p11pt4:0.158, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p13pt2:0.157, pdf:Portfolio Narrative_2024.pdf:p75pt4:0.157, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.157, docx:Guidance on reporting outputs or outcomes.docx:u1-4:0.157, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt2:0.157, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p21pt1:0.156, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p7pt1:0.156, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.156, docx:Standard Provisions 2026.docx:u136-139:0.155, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p17pt3:0.155, pdf:CGIAR_ImpactReport_2022-24.pdf:p27pt1:0.154, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p20pt4:0.154, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p20pt4:0.154, pdf:Portfolio Narrative_2024.pdf:p62pt3:0.154, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p13pt3:0.153, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt3:0.153, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p4pt3:0.153, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p16pt3:0.153, pdf:Portfolio Narrative_2024.pdf:p18pt1:0.153, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.153, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.153, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p15pt2:0.152, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p17pt4:0.152, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p19pt4:0.152, pdf:CGI21-507032-PORB-Climate Action.pdf:p1pt1:0.151, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p21pt3:0.151, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p21pt3:0.151, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p8pt2:0.151, pdf:Portfolio Narrative_2024.pdf:p68pt2:0.151, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p2pt1:0.151, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p9pt1:0.150, pdf:CGI21-507033-PORB-Policy Innovations.pdf:p55pt1:0.150, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p4pt1:0.150, pdf:Portfolio Narrative_2024.pdf:p75pt3:0.150, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p28pt1:0.150, pdf:CGIAR_ImpactReport_2022-24.pdf:p13pt3:0.148, pdf:Climate Action_Inception Report 30-06-2025.pdf:p15pt3:0.148, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p16pt3:0.148, pdf:CGI21-508007-PORB-Multifunctional Landscapes.pdf:p72pt1:0.148, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p21pt4:0.148, pdf:CGIAR_ImpactReport_2022-24.pdf:p18pt1:0.148, pdf:Gender Equality and Inclusion_Inception Report 30-06-2025.pdf:p14pt2:0.147, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p9pt2:0.147, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p20pt4:0.146, pdf:CGIAR_ImpactReport_2022-24.pdf:p16pt1:0.146, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p20pt3:0.146, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p30pt4:0.145, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25pt3:0.145, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p25pt3:0.145, pdf:Quick style guide Feb 2024 (1).pdf:p7pt4:0.145, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p14pt4:0.145, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p14pt4:0.145, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p18pt2:0.145, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p30pt1:0.145, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p15pt4:0.145, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p7pt4:0.145, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p15pt3:0.144, pdf:CGI21-508002-PORB-Sustainable Animal and Aquatic Foods.pdf:p22pt1:0.144, pdf:CGIAR_PORB_Breeding_Tomorrow.pdf:p1pt1:0.144, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p5pt4:0.144, pdf:Portfolio Narrative_2024.pdf:p58pt2:0.143, pptx:Information Session on 2025 Technical Reporting.pptx:s8pt2:0.143, pdf:Portfolio Narrative_2024.pdf:p54pt4:0.143, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p23pt3:0.142, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p10pt3:0.142, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p10pt3:0.142, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p12pt1:0.142, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p23pt1:0.141, docx:Guidance on reporting outputs or outcomes.docx:u4-7:0.141, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.141, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p5pt1:0.141, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p28pt4:0.141, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p15pt3:0.141, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p50pt1:0.141, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p19pt3:0.140, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p8pt1:0.139, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p8pt1:0.139, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p7pt3:0.139, pdf:Portfolio Narrative_2024.pdf:p15pt4:0.139, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p14pt4:0.139, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p9pt2:0.139, pdf:Portfolio Narrative_2024.pdf:p67pt4:0.139, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p5pt3:0.139, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p26pt4:0.139, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p25pt4:0.138, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p25pt4:0.138, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p30pt3:0.138, docx:Standard Provisions 2026.docx:u109-112:0.138, pdf:CGIAR Open and FAIR Data Assets Policy.pdf:p3pt1:0.137, docx:General reporting guidance.docx:u1-3:0.137, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p3pt1:0.136, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt4:0.136, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt1:0.136, docx:Innovation use.docx:u1-4:0.136, docx:2025 Technical Reporting Information (Session 1).docx:u19-22:0.136, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p15pt1:0.136, pdf:Portfolio Narrative_2024.pdf:p74pt4:0.136</t>
+  </si>
+  <si>
+    <t>docx:Questions and Answers from Tech reporting info sessions.docx:u7-10:0.538, pptx:Engagement Plan 2025 Technical Reporting.pptx:s1pt4:0.379, pptx:Information Session on 2025 Technical Reporting.pptx:s9pt2:0.311, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p12pt2:0.303, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p12pt2:0.303, docx:2025 Technical Reporting Information (Session 2).docx:u4-7:0.284, docx:2025 Technical Reporting Information (Session 1).docx:u7-10:0.283, docx:2025 Technical Reporting Information (Session 1).docx:u4-7:0.280, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt1:0.266, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p15pt1:0.266, docx:Questions and Answers from Tech reporting info sessions.docx:u10-13:0.255, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt2:0.245, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p21pt2:0.244, docx:Engagement Plan 2025 Technical Reporting.docx:u16-19:0.243, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p7pt4:0.242, pdf:Type3_2024Report.pdf:p5pt2:0.241, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p8pt3:0.240, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p14pt4:0.238, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p12pt1:0.237, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p12pt1:0.237, pptx:Information Session on 2025 Technical Reporting.pptx:s9pt4:0.236, docx:General information on Technical Reporting .docx:u1-6:0.233, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p14pt3:0.231, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p9pt3:0.231, pdf:Type3_2024Report.pdf:p4pt1:0.229, pptx:Information Session on 2025 Technical Reporting.pptx:s5pt1:0.225, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p15pt3:0.223, docx:Guidance on ensuring quality over quantity.docx:u4-7:0.223, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p11pt3:0.223, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p9pt2:0.222, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p15pt4:0.220, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt4:0.219, pdf:Type3_2024Report.pdf:p11pt2:0.217, docx:Using the PRMS Reporting Tool.docx:u1-4:0.217, pdf:CGIAR_ImpactReport_2022-24.pdf:p2pt3:0.217, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p10pt1:0.217, docx:Engagement Plan 2025 Technical Reporting.docx:u13-16:0.217, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt3:0.216, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p3pt3:0.216, pdf:Portfolio Narrative_2024.pdf:p6pt4:0.215, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p11pt1:0.214, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p8pt2:0.214, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p10pt4:0.213, pdf:Type3_2024Report.pdf:p4pt3:0.212, pdf:Type3_2024Report.pdf:p11pt3:0.212, docx:Engagement Plan 2025 Technical Reporting.docx:u19-22:0.211, pdf:Type3_2024Report.pdf:p5pt3:0.211, docx:2025 Technical Reporting MELIA glossary.docx:u61-66:0.210, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p13pt4:0.210, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p9pt1:0.209, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt2:0.208, pdf:Type3_2024Report.pdf:p5pt1:0.208, docx:Engagement Plan 2025 Technical Reporting.docx:u4-7:0.207, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt4:0.206, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p7pt4:0.206, pdf:Type3_2024Report.pdf:p5pt4:0.205, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p18pt1:0.205, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p18pt1:0.205, pdf:CGIAR_ImpactReport_2022-24.pdf:p1pt1:0.205, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p19pt1:0.205, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p27pt1:0.204, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p11pt3:0.204, pdf:Type3_2024Report.pdf:p4pt2:0.200, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p11pt2:0.199, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p11pt2:0.199, pptx:Information Session on 2025 Technical Reporting.pptx:s3pt2:0.198, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p10pt3:0.197, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt2:0.197, pdf:Portfolio Narrative_2024.pdf:p5pt3:0.197, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p15pt1:0.197, pdf:CGIAR_ImpactReport_2022-24.pdf:p8pt4:0.196, pdf:Breeding for Tomorrow_MELIA Plan 30-06-2025 (1).pdf:p47pt4:0.194, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p21pt3:0.194, pdf:CGIAR_ImpactReport_2022-24.pdf:p67pt3:0.194, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt1:0.193, docx:Questions and Answers from Tech reporting info sessions.docx:u19-22:0.192, pptx:Information Session on 2025 Technical Reporting.pptx:s1pt2:0.191, pdf:Type3_2024Report.pdf:p8pt1:0.191, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p1pt3:0.190, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p1pt3:0.190, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p20pt3:0.190, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p6pt4:0.190, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p6pt4:0.190, pptx:Information Session on 2025 Technical Reporting.pptx:s4pt3:0.190, pdf:Policy Innovations_Inception Report 30-06-2025.pdf:p15pt2:0.189, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt1:0.189, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p7pt1:0.189, docx:2025 Technical Reporting Information (Session 1).docx:u34-37:0.189, pdf:Type3_2024Report.pdf:p11pt4:0.189, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p23pt4:0.189, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt1:0.188, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p4pt1:0.188, pptx:Information Session on 2025 Technical Reporting.pptx:s10pt2:0.188, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p12pt3:0.187, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p12pt3:0.187, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p15pt2:0.187, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p11pt2:0.186, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p11pt2:0.186, docx:2025 Technical Reporting Information (Session 2).docx:u7-10:0.186, pdf:Type3_2024Report.pdf:p4pt4:0.184, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt1:0.184, docx:Standard Provisions 2026.docx:u157-160:0.183, docx:Standard Provisions 2026.docx:u130-133:0.183, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p6pt1:0.182, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p6pt1:0.182, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt2:0.182, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p34pt4:0.182, docx:Questions and Answers from Tech reporting info sessions.docx:u1-4:0.181, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p13pt3:0.181, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p10pt4:0.180, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4pt4:0.180, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p4pt4:0.180, pdf:Portfolio Narrative_2024.pdf:p63pt2:0.179, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p12pt3:0.178, pptx:Information Session on 2025 Technical Reporting.pptx:s10pt3:0.178, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p9pt4:0.178, docx:2025 Technical Reporting Information (Session 1).docx:u19-22:0.178, pdf:CGIAR_ImpactReport_2022-24.pdf:p64pt2:0.178, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p6pt2:0.177, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p6pt2:0.177, pdf:CGIAR_ImpactReport_2022-24.pdf:p48pt1:0.177, pdf:Type3_2024Report.pdf:p1pt2:0.176, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p62pt3:0.176, docx:Capacity sharing for development.docx:u1-6:0.175, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p19pt3:0.175, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p11pt4:0.175, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p7pt3:0.174, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p7pt3:0.174, pdf:Gender Equality and Inclusion_MELIA Plan 30-06-2025.pdf:p10pt2:0.174, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p6pt4:0.174, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p14pt3:0.174, pdf:CGIAR_ImpactReport_2022-24.pdf:p7pt3:0.173, pdf:Portfolio Narrative_2024.pdf:p5pt1:0.173, docx:General reporting guidance.docx:u1-3:0.173, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p15pt2:0.173, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p15pt2:0.173, pdf:Genebanks_MELIA Plan 30-06-2025.pdf:p7pt3:0.172, pdf:Multifunctional Landscapes_MELIA Plan 30-06-2025.pdf:p37pt2:0.172, pptx:Information Session on 2025 Technical Reporting.pptx:s2pt2:0.172, pdf:Better Diets and Nutrition_Inception Report 30-06-2025.pdf:p13pt2:0.172, pdf:Type3_2024Report.pdf:p6pt2:0.172, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p21pt1:0.172, docx:2025 Technical Reporting Information (Session 1).docx:u40-43:0.171, pdf:Portfolio Narrative_2024.pdf:p5pt2:0.170, pdf:CGIAR-Performance-and-Results-Management-Framework-2022-30.pdf:p11pt3:0.170, pdf:Genebanks_Inception Report 30-06-2025.pdf:p35pt2:0.170, pdf:Capacity Sharing_Inception Report 30-06-2025.pdf:p18pt2:0.169, pdf:Breeding for Tomorrow_Inception Report 30-06-2025.pdf:p14pt4:0.169, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt1:0.169, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p3pt1:0.169, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p16pt2:0.169, docx:Guidance on ensuring quality over quantity.docx:u1-4:0.168, pdf:CGIAR_ImpactReport_2022-24.pdf:p6pt4:0.168, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p16pt4:0.168, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p16pt4:0.168, pdf:CGIAR_ImpactReport_2022-24.pdf:p64pt3:0.168, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p3pt2:0.168, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p3pt2:0.168, docx:Standard Provisions 2026.docx:u133-136:0.167, pdf:Portfolio Narrative_2024.pdf:p1pt2:0.167, pdf:Policy Innovations - MELIA Plan 30-06-2025-.pdf:p10pt2:0.167, pdf:CGIAR_ImpactReport_2022-24.pdf:p46pt1:0.166, pdf:Scaling for Impact_MELIA Plan 30-06-2025.pdf:p8pt4:0.165, pdf:CGIAR_ImpactReport_2022-24.pdf:p11pt3:0.165, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p13pt1:0.165, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p13pt1:0.165, docx:Questions and Answers from Tech reporting info sessions.docx:u13-16:0.165, pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p29pt3:0.165, pdf:Food Frontiers and Security_Inception Report 30-06-2025.pdf:p15pt1:0.165, pdf:Sustainable Farming_Inception Report 30-06-2025.pdf:p8pt1:0.164, pdf:CGIAR_ImpactReport_2022-24.pdf:p47pt2:0.164, pptx:Information Session on 2025 Technical Reporting.pptx:s4pt1:0.164, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p10pt3:0.163, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p21pt4:0.163, docx:2025 Technical Reporting Information (Session 2).docx:u10-13:0.163, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p14pt4:0.163, pdf:CGI21-509002-PORB-Sustainable Farming (1).pdf:p24pt3:0.163, pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p11pt2:0.162, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p13pt3:0.162, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p13pt3:0.162, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p17pt1:0.162, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p24pt1:0.161, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p24pt1:0.161, pdf:Digital Transformation_MELIA Plan 30-06-2025 (1).pdf:p11pt1:0.161, docx:2025 Technical Reporting Information (Session 2).docx:u31-34:0.161, docx:Innovation development.docx:u4-7:0.160, pdf:Sustainable Farming_MELIA Plan 30-06-2025.pdf:p13pt1:0.160, docx:Questions and Answers from Tech reporting info sessions.docx:u16-19:0.160, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p14pt1:0.159, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p14pt1:0.159, pptx:Information Session on 2025 Technical Reporting.pptx:s5pt3:0.159, pptx:Information Session on 2025 Technical Reporting.pptx:s7pt1:0.159, pptx:Information Session on 2025 Technical Reporting.pptx:s7pt2:0.159, pdf:Digital Transformation_Inception Report 30-06-2025.pdf:p15pt3:0.159, pdf:Portfolio Narrative_2024.pdf:p12pt4:0.159, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p9pt1:0.159, pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p9pt1:0.159, pdf:Climate Action_MELIA Plan 30-06-2025 (1).pdf:p19pt4:0.159, pdf:Multifunctional Landscapes_Inception Report_MFL 30-06-2025.pdf:p9pt2:0.158, pdf:Sustainable Animal and Aquatic Foods_MELIA Plan 30-06-2025.pdf:p7pt2:0.158</t>
   </si>
   <si>
     <t>I cannot find information in the provided chunks to answer this.  
@@ -827,6 +836,14 @@
 - File: Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf — Location: page 19 part 1 — Cited IDs: [ID: pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt1]</t>
   </si>
   <si>
+    <t>The responsibility for approving changes to reporting categories and balancing the benefits of collecting detailed information against the reporting burden on Programs/Accelerators (P/A) lies with the CGIAR. This process involves organizing focus group discussions, workshops, and individual meetings with various stakeholders, including donors and initiative leads, to gather feedback on reporting fields. The feedback is prioritized based on feasibility and strategic relevance, and decisions are documented in the annual Learning &amp; Optimization report. Adjustments to reporting categories are made through this iterative consultation and refinement process.
+Sources:
+File — Location — Cited IDs
+Questions and Answers from Tech reporting info sessions.docx — paragraph 8 to paragraph 11 — u7-10
+CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 12 part 1 — p12pt1
+CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf — page 12 part 1 — p12pt1</t>
+  </si>
+  <si>
     <t>Information Session on 2025 Technical Reporting.pptx — slide 9 — pptx:Information Session on 2025 Technical Reporting.pptx:s9, Engagement Plan 2025 Technical Reporting.docx — paragraph 2 — docx:Engagement Plan 2025 Technical Reporting.docx:p2, Information Session on 2025 Technical Reporting.pptx — slide 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s2, Guidance on reporting outputs or outcomes.docx — paragraph 22 — docx:Guidance on reporting outputs or outcomes.docx:p22, Engagement Plan 2025 Technical Reporting.docx — section 'Technical Reporting questions' — docx:Engagement Plan 2025 Technical Reporting.docx:p59, CGIAR_ImpactReport_2022-24.pdf — page 1 — pdf:CGIAR_ImpactReport_2022-24.pdf:p1, Engagement Plan 2025 Technical Reporting.docx — section 'A single location for all documents and resources' — docx:Engagement Plan 2025 Technical Reporting.docx:p31, Engagement Plan 2025 Technical Reporting.pptx — slide 1 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s1, CGSpace.docx — section 'CGSpace' — docx:CGSpace.docx:p3, CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 5 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p5</t>
   </si>
   <si>
@@ -879,6 +896,9 @@
   </si>
   <si>
     <t>https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition%2FBetter%20Diets%20and%20Nutrition%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP05%20%2D%20Better%20Diets%20and%20Nutrition&amp;p=true&amp;ga=1 — page 19 part 1 — pdf:Better Diets and Nutrition_MELIA Plan 30-06-2025 (1).pdf:p19pt1, https://cgiar.sharepoint.com/sites/PCUInterim/Shared%20Documents/Forms/AllItems.aspx?id=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing%2FCapacity%20Sharing%5FMELIA%20Plan%2030%2D06%2D2025%2Epdf&amp;parent=%2Fsites%2FPCUInterim%2FShared%20Documents%2F04%2E%20Technical%20Reporting%20%28Allison%29%2F7%2E%20P25%20Inception%2F000%2E%20Inception%20Report%20%2D%20Final%20Attachments%20%2826%20June%29%2FSP11%20%2D%20Capacity%20Sharing&amp;p=true&amp;ga=1 — page 6 part 2 — pdf:Capacity Sharing_MELIA Plan 30-06-2025 (1).pdf:p6pt2, https://storage.googleapis.com/cgiarorg/2025/06/CGIAR-Technical-Reporting-Arrangement-2025-30.pdf — page 22 part 4 — pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p22pt4</t>
+  </si>
+  <si>
+    <t>Questions and Answers from Tech reporting info sessions.docx — paragraph 8 to paragraph 11 — docx:Questions and Answers from Tech reporting info sessions.docx:u7-10, https://docs.google.com/presentation/d/1WbVFx3MD32HUZXlnY_sMF2APNxr6JgGG/edit?slide=id.p1#slide=id.p1 — slide 1 part 4 — pptx:Engagement Plan 2025 Technical Reporting.pptx:s1pt4, https://docs.google.com/presentation/d/1iH7kEQrUqQywkG9wVkCCBq_tRp-d1Ws0/edit?slide=id.p1#slide=id.p1 — slide 9 part 2 — pptx:Information Session on 2025 Technical Reporting.pptx:s9pt2</t>
   </si>
   <si>
     <t>[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]
@@ -2701,6 +2721,28 @@
 Results framework Program/Accelerator results framework Please refer to the Results Framework attachment 2. Monitoring plan for HLOs and outcomes The genebanks will continue to use an online reporting tool (ORT), which was set up in 2014 to monitor the status of individual collections with respect to performance targets. Through the QMS adopted in AoW 1, genebank operations, data, and accession numbers are audit ed internally and externally and are subject to regular review by the Crop Trust. The audits ensure that international standards are complied with, and deviations and risks are documented and managed. FAO’s monitoring of UN SDG 2.5, State of the World of PGRFA, and the Global Plan of Action</t>
   </si>
   <si>
+    <t>[ID: docx:Questions and Answers from Tech reporting info sessions.docx:u7-10]
+Governance: Q: Who is responsible for approving changes to reporting categories and for balancing the benefits of collecting detailed information against the reporting burden on P/A? A: Ahead of each reporting cycle, CGIAR organizes focus group discussions, workshops, and individual meetings with donors and stakeholders (e.g., Initiative/Program leads/co-leads, MELIA experts, SO MEL, IPSR team, and Center representatives). Through these exchanges, feedback is collected on which reporting fields are valuable to keep, remove, or add, ensuring both alignment with CGIAR’s strategy and responsiveness to donor requirements. This input is then prioritized based on feasibility and strategic relevance, with decisions documented in the annual Learning &amp; Optimization (L&amp;O) report. In practice, adjustments to reporting categories are made through this iterative process of consultation, review, and refinement.
+---
+[ID: pptx:Engagement Plan 2025 Technical Reporting.pptx:s1pt4]
+Reporting
+---
+[ID: pptx:Information Session on 2025 Technical Reporting.pptx:s9pt2]
+Reporting High
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p12pt2]
+a new category. • 'Other' result categories to be better defined 2022-24 results reported in the ‘Other’ output and outcome categories are by definition a mixed bag, however do point to the need for a specific new category on partner engagement/ partnership building. Improved guidance on the use of the ‘Other’ categories has been available since mid-2024 and we will continue to improve guidance and support to results submitters. • Continuation and optimization of existing Genebank data integration Existing data flow from the Genebanks’ Online Reporting Tool (ORT), powering the CGIAR Results Dashboard Genebanks section will continue. Optimization of those data flows will form part of ongoing engagement with the Genebanks. • Streamline results reporting requirements The reporting burden will be minimized by a) critically assessing each data field against requirements, b)
+---
+[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30 (1).pdf:p12pt2]
+a new category. • 'Other' result categories to be better defined 2022-24 results reported in the ‘Other’ output and outcome categories are by definition a mixed bag, however do point to the need for a specific new category on partner engagement/ partnership building. Improved guidance on the use of the ‘Other’ categories has been available since mid-2024 and we will continue to improve guidance and support to results submitters. • Continuation and optimization of existing Genebank data integration Existing data flow from the Genebanks’ Online Reporting Tool (ORT), powering the CGIAR Results Dashboard Genebanks section will continue. Optimization of those data flows will form part of ongoing engagement with the Genebanks. • Streamline results reporting requirements The reporting burden will be minimized by a) critically assessing each data field against requirements, b)
+---
+[ID: docx:2025 Technical Reporting Information (Session 2).docx:u4-7]
+Trifa, Nicoleta (CGIAR System Organization) ha iniciado la transcripción Trifa, Nicoleta (CGIAR System Organization) 0:04 5 minutes and then we will move into. I will leave the floor for your questions if that's OK. OK. Presentation mode. This means I no longer see the chat, the questions in the chat, or if hands are raised. So please interrupt me if you have questions or if you you know you you don't see the deck or anything else. I would like to welcome everyone and thank you for joining today's session on the 2025 Technical Reporting. My name is Nicoletta Trifa. I'm part of the Portfolio Performance Unit, a support unit within the Office of the Chief Scientist. This session is the second of two plan, two session plans for today, planned for today. We had an another session this morning to accommodate colleagues in other time zones. Um. Coming straight to the agenda, here's an overview of of what I'm going to cover in the next couple of minutes. So I will provide an update on the technical reporting arrangements. We'll discuss priorities and changes for 2025 technical reporting. A brief introduction on the annual Technical reports and the enablers, so being the Performance and Reporting Management System and the quality assurance, Technical reporting timeline, available resources and support and also what's what's next and how to stay engaged. This session marks the start of the conversation around 2025 Technical reporting. We want to give you the early look at the key priorities and plans for the months ahead. The goal is to make sure that you all stay informed, prepared and supported. With a clear understanding of deliverables and timelines that it is clear for you who to reach out to in case you have questions or in case you need help along the way. Some of the people in this call are already familiar with the technical reporting arrangements. From the previous portfolio, while for others this might be entirely new. Our goal is to bring everyone to the same level of understanding so that we can move forward with clarity and shared expectations for the 2025 technical reporting. OK, with this let me kick off. So the technical reporting arrangements for the new portfolio, the 2025 to 2030 portfolio has been approved by CJRGLD, so Global Leadership Team in June 2025. And provides the operational basis to plan, monitor, learn and report on the new portfolio. It is designed to progressively enable programs and accelerators and centres to report on the pooled and the Window 3 Bilateral projects. In an aligned and integrated way without increasing reporting burdens on centers or on the scientist. Main changes compared to previous technical reporting arrangement. So the focus will be on streamlined reporting, less products, more integration, lower transaction costs, stronger impact focus results to be clearly linked. To impact outcomes and their associated indicator targets and also better linkages between the annual program and accelerator theory of change, final results and budget, media and technical reporting. The primary audiences for technical reporting are funders and CGR staff at the Integrated Partnership, Portfolio and Program and Accelerator levels. A secondary audience is the partners. The Annual Technical Reporting covers the program and Accelerators Annual Technical Reports and the Portfolio Narrative report, which provides an overall view to thematic and geographic targets. Relevant components of the technical reporting products are also integrated into the CGR corporate reporting, so CGR annual report. 2025 priorities for technical reporting. So 2025 is a transition year. I believe everyone has a line on this being a transition year with the technical reporting arrangements, implementation focusing again as I mentioned on streamlined reporting. And also on strengthening linkages between the theory of change, the poor media and technical reporting. Many of you know are aware that. These components were not properly linked in the previous portfolio, so it was challenging to demonstrate progress against plans against theory of change. In terms of deliverables for 2025, these are the program and the accelerator technical reports which are due in. April 2026 A Portfolio Narrative report which is due in June 2026 Integration of top 80% window 3 bilateral projects by center and dollar value into technical reporting and planning. Application of the minimum data standards for window 3 and bilateral reporting and mapping refinement which will take place during reflect early Q12026. So as I was mentioning 2025 transition year toward KPI based planning and reporting. So efforts are underway to enable planning and reporting at the KPI level and this is aligned with the System Office objectives and key results for 2026 and 20. 2027 I've listed them here on the slide, but be mindful that these are to be confirmed, so not confirmed yet. So uh for 2026 OK Rs. 100 of Program Accelerator. PRBS and the Annual Technical Reporting starting with the 2026 will provide monitoring of performance and result against Smart KPIs by center, by year, by pooled fund invested. So for 2026, the aim is to have 80% of centers, window free and bilateral projects included in 2025 Technical reports, while for 2027 this will increase to 90% of center window free and bilateral projects included in 2026. Technical reports. Yep. Specifically for programs and accelerators deliverables, here the focus is on three key deliverables. So first one being reporting the 2025 results in the Performance and Reporting Management System, the PRMS. Programs and accelerators are strongly encouraged to report results that were planned and budgeted, so included in their PORB, since the technical reporting system will allow for tracking results against plans. Secondly is the quality assurance of the reported reported results. The 2025 results will be quality assessed following a defined process and timeline. Once this is done, the quality assessed results will be available on the Results dashboard and it will also be available for you to inform, pause and reflect. And to fill into your technical reports and to your annual technical reports. A third deliverable is drafting and submission of the 2025 Annual Technical Report. So each program and accelerators is responsible for drafting and internally validating quality assessing their. Annual Technical Report before submitting it to to us to the PPU. To support this process, this year we will have an AI generated V0 draft of this report which will include pre-filled text, some narrative and analytics for each report section. And this will be available for you as a starting point to further refine and and finalize your annual technical report. On the three deliverables, I want to mention that we will plan in September, October specific info session. So there will be info session on PRMS. Like a deep dive on PRMS, there will be a deep dive on quality assurance and the process timeline, who does what and so on, and also a deep dive on the Annual Technical Report to further make you familiar with its content, the internal approval process. The external approval process, I mean by external, I mean outside of program and accelerator approval process, what will be available, where AI will help and so on. So more information on this will come. For the annual technical report, what are these? These reports provide assurance on the annual program and accelerator delivery against PORP and progress on theory of change. They are short, concise and targeted. They are based on the quality assess results. The requirement is to have this report submitted in April and then the aim is to publish them early May as I was mentioning template guidance and and. A I generated V0 report will be will be provided to You to the right on the right side of the screen You can see that the content areas of the annual Technical report. This is extracted from the Technical reporting arrangements document and IT has it's very similar to what we had for the initiatives and impact platforms in the previous portfolio. So You have a fact sheet, an executive summary, annual progress area for work details. A Results section, Partnerships, Portfolio Linkages, Adaptive Management and then Key Results story. For reference or especially for for People new to Technical reporting, which who want You to have a look at, You know how this this reports might look like in the end. I've I've pasted here the. Annual reports from initiatives, impact platforms and science Group projects from 2024, SO from this year and You also have a link to the Portfolio narrative report. And the Type 2 report, sorry, the Type 2 impact report, which is drafted every three years. The System where this will take Place with reporting will take place. It's called Performance and Results Management System, PRMS in short. We are currently validating the PRMS roles, SO we have reached out to Program Coordinators and asked them to. Give us the name and the role of the People in their teams which will be involved in Technical reporting. A reminder on this will be sent on Thursday to finalize the process and this will enable the Technical Team to. Create proper accesses in the System when the reporting period starts. Similar to previous information, SO we are working to to to draft the new users onboarding deck where You can find relevant information on PRMS and. We will keep You updated on what's new in the pyramids or on the enhancements that we're working on this year as we advance towards Technical reporting to the reporting period later in the year. Quality assurance process what IT is. So Results submitted by programs and accelerators in the PRMS are quality assessed by QA Team in February 2026. Your participation in this process is required. Guidance and resources will be provided and then also as I was mentioning, an info session will be scheduled for September, October. What is QA? It is a process that aims to improve the quality of reported data, to provide consistency across the system, to ensure reliability of reported results, inform learning, and overall improve CGR accountability and transparency. Quality assessed data, SO the Results quality assessed inform the reflect process. They Go into the Results dashboard. They are also featured in the annual reports in the Portfolio narrative and then further into the CJR corporate report. And oh, there's I I only noticed now the title says 2024. Apologies for this. It's 2025 Technical reporting timeline. This is a print screenshot of. Same information that can be seen on the PNR hub. So we have the first info session on Technical reporting now in July, August through November. We will engage Program accelerators and centers, media People in preparation of. Various guidance materials, testing, PRMS enhancement. We'll plan information sessions which will take Place in September, October to make sure that we everyone is properly prepared for the reporting period. Reporting 2025 results. Our intent is to open PRMS in November. Let's see how how well we advance with the changes to the System again 2025. Is a Transition year. There are many changes to be done since we moved from 1 Portfolio to another, many adjustments which need to take Place in the system, but hopefully in November we can open reporting on 2025 results. We will keep You updated on this though. Quality assurance will take Place as mentioned in February 2026. Reflect same thing will take Place in Q 1/20/26. And then the annual Technical reports are due in in April, in March, April for publication early May. The Performance and Results Hub is your one-stop shop for planning, Technical reporting and managing information. You'll find I want to stop sharing this deck for now and I want to. Take You to the PNR hub. Let me know if You see when I switch screens. Rose, Sabrina ( Alliance Bioversity-CIAT) 16:48 Yes, we can see. Trifa, Nicoleta (CGIAR System Organization) 16:49 Yes. OK, good. So this is the revised PNR Hub adapted, updated with the new CGR logo and branding colors. You'll have the homepage reporting, planning, reflect and replan and then archive if you. If You Go to archive, You will find previous information on Technical reporting from previous years. What's of interest for this presentation as well As for Technical reporting, You will Go to 2025 reporting and this is where You will find pertinent information to Technical reporting this year. So again, it's the timeline here. Latest update. This section will post and keep this section updated as information comes becomes available. Upcoming events, so. We've only listed today's info session, but the other info session will follow once we have defined a date for them. Event event recording, SO meeting recording and link to the decks will also be available here. And under the frequently asked questions, we were able to recycle to say SO a couple of key questions from previous Portfolio which still apply to to this Portfolio to the Program and accelerator team. So I invite You to Go there. And and browse a bit the the questions and answers under various section. Be mindful that this is this Hub is live a live Hub SO as information becomes available we want to make IT available to the end users here so. Any feedback on how to improve, what You improve and SO on is is welcome. So feel free to reach out to us if You have any suggestions or would like to see some things more preeminently maybe. Features here. Good. Back to this. I only have 1-2 slides and then I will will open for questions. In terms of engaging with Program accelerators and centers on Technical reporting this year, the we have a couple of channels to engage with you. So first is through the bi-weekly emails. Every two weeks You will receive an e-mail with technical. Supporting updates that will include reminders, summaries, latest questions and answers we want to share with everyone and SO on. There will be targeted emails and this emails will engage specific categories within the program. Accelerators and the centers center many Focal Points based on Technical reporting, revisions, developments and that the purpose is to gather targeted feedback on nonspecific things. Um. Info session planned for on specific topics, for example QA, PRMS, innovation, reporting on outputs, reporting on on outputs and SO on. So those info session will be planned for September, October and we will keep You appraised on the exact. Select dates and themes topics ahead of time and then the drop ins. We've seen that it was specifically valuable to initiatives when these drop ins were planned during reporting and during QA. So during this drop-ins will not come with presentations, but you will have several people from our team be available to respond to your questions live and the primary focus as I was mentioning will be reporting and the QA. Um. This is the process that we used with initiatives and it worked pretty well to to test PRMS enhancements and receive feedback from initiatives and the same process will be used this year to engage programs and accelerators and center media focal point. So usually when a new enhancement is proposed, we will send the targeted e-mail. We'll invite specific roles within the PMUs to test, provide feedback, then the feedback. Becomes an update in the PRMS and once it's live, we will notify you so that everyone has access to that enhancements, to those enhancements in the PRMS with an explanation of why the enhancement, who asked for it. You know, oh, and so on. In terms of upcoming activities, as I was mentioning the bi-weekly technical reporting updates, the first e-mail will get out this Thursday with the link to this deck and to the recording for people who were not able to join today. There are the targeted engagement goals for PRMS testing, info session on specific topics and there is also an engagement on window 3 bilateral. Jules Colomer is leading on this together with alignment working group. I believe this is it. I only have a link here to a theory of change dashboard. I will take advantage of Jules being in this call. So to briefly introduce this, but what I understand this. The Theory of Change dashboard, I hope you can see it on my screen now, has been developed based on all theory of change of programs and accelerators as per the inception reports. So you have an overview of. Of the Results framework of the 2030 outcome, outcomes, media studies and also on map which you can filter. So you have V1 and V2 here and the request to you. We will share the link to this dashboard. It's an internal dashboard. We will share the link with you. You and the request is to have a look at your program and accelerator and the data in this dashboard and if you notice error, please let us know right e-mail us at Performance and Results at cgr.org. So that we can fix the error either in the dashboard or you know, whatever needs to be fixed in the original data source.
+---
+[ID: docx:2025 Technical Reporting Information (Session 1).docx:u7-10]
+Trifa, Nicoleta (CGIAR System Organization) 0:48 Yep. OK, good. So thank you. This session is the first of two session plans for today, planned for today, with the second being scheduled later at 3:00 PM CET to accommodate colleagues in other time zones. Technical reporting. My name is Nicoletta Trifa. By the way, I'm part of the Portfolio Performance Unit, the support unit within the Office of the Chief Scientist. Here is an overview of what we'll cover in the next minutes. I believe my presentation will take 2025 minutes and then we'll leave room for questions at the end, if that's OK. So what we'll cover an update of the technical reporting arrangements 2025 to 2030, priorities and changes for 2025, a brief introduction on the annual technical report and the neighbors. So this mean the performance and results. Management system and the quality assurance, the technical reporting timeline, available resources and support and what's next and how to stay engaged. I want to mention that this session marks the start of the conversation around 2025 technical reporting. We want to give you the early look at the key priorities and plans for the months ahead, and the goal is to make sure that you stay informed, prepared and supported with a clear understanding of upcoming deliverables and timelines. And also clarity on who to reach out to if you have questions or if you need help along the way. Good. Technical reporting arrangements for the new portfolio. The 2025 to 2030 portfolio has been approved by the CGR Global Leadership team on in June 2025 and provides the operational basis to plan, monitor, learn and report. On the new portfolio. It is designed to progressively enable programs, accelerators and centers to report on the pooled and window 3 bilateral projects of the new portfolio in an integrated and aligned way without increasing the burden on centers and the scientists. Main changes compared to the previous technical reporting arrangements, streamline reported reporting. So less products, more integration, lower transaction costs, stronger impact, focus results. To be clearly linked and packaged under impacts, outcomes and associated agreed indicator targets and better linkages between the theory of change or so plan of results and budget and technical reporting. The primary audiences for technical reporting are funders and CGR staff at integrated partnership, portfolio and program and accelerator levels. A secondary audience is the partners. Annual technical reporting covers the individual annual technical reports for program and accelerators, as well as a portfolio view of aggregate contribution to thematic and geographic targets. And relevant content from this technical reports are integrated into the CJR corporate reporting. In terms of the 2025 technical reporting priorities, 2025 is a transition year with technical reporting arrangements, implementation again focusing on streamlined reporting and on strengthening the linkages between theory of change. Porb, media and technical reporting. As many of you know, in the previous portfolio these components were not properly linked, so it was a bit challenging to demonstrate progress against the theory of change or the plans, as you know. In terms of deliverables for 2025. These are the program and accelerator technical reports, which are due in April 2026, the portfolio narrative, which is due in 2026 in June. Integration of top 80% of window tree and bilateral projects by central dollar value into reporting and planning. Application of the minimum data standards for window tree and bilateral reporting. And mapping of refinement during the pause and reflect process which will take place early Q 1/20/26. So as I was mentioning, this year is seen more as a transition year towards KPI based planning and reporting and efforts are underway to enable planning and reporting at the KPI level, which is aligned with the system office objective and key results for 2026 and 20. These are to be confirmed, so they haven't been confirmed yet, but I've pasted them here so that you can see the 2026 objective and key results for the system office. So 100% program and accelerate the work plans and budget. An annual technical report. Which provide for software enabled monitoring of erformance and results against smart Ki by center, ear and ooled funds invested. So next year, 80% of centres, CGR, window three and bilateral funded work by value included in 2025 technical reports and then the following year in 2027, this will increase to 90% of centres. Window 3 and bilateral funded work included in 2026 technical reports. The following slides, what I have, what I have included in the following slides, it's a brief introduction into. What is expected in terms of deliverables from programs and accelerators together with an overview of the performance and results management system and the QA. I realized that some in this call some of you are already familiar with the reporting arrangements from the previous portfolio. While for others this might be entirely new. So our goal is to bring everyone to the same level of understanding so that we can move forward with clarity and shared expectations for the 2025 technical reporting. OK, so technical reporting for program and accelerator. We'll focus on three key deliverables. So first is reporting results, the 2025 results in the Performance and Reporting Management system, PRMS. Each program accelerator and mapped window 3 project will report 2025 results in the system and we strongly encourage to report results that were planned and budgeted. So results which have been included in the reports. As the outdated technical reporting system will allow for tracking results against plans. Secondly is the quality assurance of reporting results. As you know, the results submitted go through the quality assessment process and we will share more details on this process in the timeline in an info session scheduled for later. Which we will schedule later in in September, October and the quality assess results will be available on the results dashboard. Inform the pause and reflect and will be included in the technical reports in the annual technical reports. A third deliverable for program and accelerators is drafting estimation of the 2025 Annual Technical Report. So each program and accelerator is responsible for drafting and internally validating quality assessing their 2025 Annual Technical Report. Before submitting it to the PPU, so to the perform portfolio performance unit. Again, guidance on this, the detailed process and validation process will be shared with you timely. Also to support this process, an AI generated V0 draft will be provided as a starting point. The annual technical reports. What are they? This the annual technical report. The the the aim is to make them short, so to 20 to 30 pages, concise and targeted. They provide assurance on annual program accelerator delivery against the boards, so plan of results and budget and progress on theory of change. They are based on quality assess results, the template guidance and as I mentioned and. AI V0 will be provided to all rogram and accelerator teams. Annual technical reports need to be submitted by each program and accelerator in March, April, so more details on this will follow and publication is intended to happen end of April, beginning of May. Here to the right side you have the. Content of the annual the proposed content for the annual technical report as per the technical reporting arrangements. Many of you will notice that there are not no big changes compared to previous portfolio, so the idea is to have a fact sheet and executive summary. The annual progress on theory of change, area of work details, a section on results, section on partnerships, portfolio linkages, adaptive management and then one key result story. But again, we will plan a detailed deep dive session on the annual technical report template and the guidance. So there will be time for you to ask questions in detail about about this and to receive support obviously. I've also included here for reference links to the 2024 Annual Technical Reports from the initiatives and impact platforms, and also a link to the 2024 Portfolio Narrative Report. In case you want to, you want to have a look to see, um, what it captures. PRMS. So this stands for Performance and Results Management System is the system the the the the environment where results need to be submitted. Again, the team is working on updating their resources. There will be. New users onboarding decks created with the links to different information and I I believe the PCU Alison together with the program coordinators. Are. The all the PRMS roles. So PCU is leading a work to define the PRMS roles and to get the information from program and accelerators regarding who from each program accelerator should have what role in PRMS. To enable us to to provide the right access to the platform when the time comes to report. Quality assurance process. So results submitted by program and accelerators in the PRMS will be quality assessed by a quality assessment team in February 2026. Your participation in this process is required. Guidance and resource resources will be provided and also an info session will be scheduled later this year. What is the QA? It is a process that aims to improve the quality of the reported data to provide consistency across the system, ensure reliability of reported results. Inform the learning process and improve the overall CGR accountability and transparency. Quality assess data informs the reflect process which takes place early Q12026, the results dashboard. So once the quality assessment of the results is finalized, the quality assess results will be pushed to results dashboard. You most probably have seen that. Reading. It also informs and are the results. The practices results are included in the annual report, in the portfolio narrative, and then in the overall CGIR annual report. In terms of the the timeline, so we have this info session now to provide an overview on the technical reporting and there will be several other info session and deep dive scheduled. Throughout September and October of reporting 2025 results, we believe that it will be feasible to open the PRMS in November for program and accelerators to to report. The date is still to be confirmed. We're aiming to to, yeah, to meet to to to end November. Hopefully this will be this is feasible from the technical side quality assurance. It's planned for February 2026 reflect process as I was mentioning Q 1/20/26 and then annual technical reports are due in March, April 2026 as well. Where to find information pertaining to technical reporting and planning and media? There is a one stop shop for for um all this. It's called the Performance and Results Hub. I'm gonna stop sharing cause I wanna share. Um, I'm gonna stop sharing the deck. I wanna. We could resent the hub. I'm not going to go through each section, but at least. So that you can see for those who are new more specifically to see and we will also share the link obviously the performance and results hub as I was mentioning it has detail on reporting, planning, reflect, replan. So you come in here, you click on 2025 reporting and then you will have access to the latest information, to the timeline, latest update, upcoming events. So all the information, information. Session dates will be listed here. We'll also have a subsection here with. Recording from from meetings, so that will be posted. For example today after this session we'll post a recording and the deck here for you to access and there is a section on frequently asked question. We recycled a couple of questions from the previous portfolio and updated them so that they are applicable to the program and accelerator teams, so feel free to go here and and browse. As resources become available, we will place them here and we will notify you by e-mail. OK. Going back to my deck. Which? In terms of engagement plan, so in order to streamline communication and optimize support for program accelerators and centers with mapped window 3 bilateral projects, we will send bi-weekly emails to everyone in this. This goal with key updates on technical reporting, with reminders and also with the latest questions and answers available on the hub. There will be targeted emails focusing on specific categories</t>
+  </si>
+  <si>
     <t>[{"role": "system", "content": "You are a RAG assistant. Use ONLY the provided context as your source, without copying full sentences verbatim from chunks (max 10 consecutive words). Write clearly and cohesively, interpreting the usage context to adapt the response. Do not invent or extrapolate beyond the context and preserve acronyms EXACTLY as written. ALWAYS answer in English, regardless of the user's language. If there is insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'Output instructions:\n- 3 to 5 sentences, neutral and direct style, no lists.\n- ALWAYS answer in English and adapt wording to the question's context.\n- End with the literal 'Sources:' and then, as a list, each line as 'File — Location — Cited IDs'.\n- If insufficient evidence, return EXACTLY: 'I cannot find information in the provided chunks to answer this.'\n\n"}, {"role": "user", "content": "Question: According to the Annex pie chart, what was total 2024 revenue and the split by funding source?\n\nContext:\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p6]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 6\nContent: Research results can be defined according to the nature of the change and the control over it.\n\n---\n\n[ID: docx:Guidance on reporting outputs or outcomes.docx:p14]\nFile: Guidance on reporting outputs or outcomes.docx\nLocation: paragraph 14\nContent: Figure 1: Research results according to the kind of change and the control over it.\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p23]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 23\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 23 Annex 2: ISDC feedback relating to pooled &amp; non-pooled alignment5 This section provides a direct extract from the ISDC Feedback on CGIAR Portfolio Narrative 2025- 2030. Comments relating to the alignment of pooled and non -pooled have been extracted from the broader set of comments. They have not been edited to e.g. update Program and Accelerator nomenclature. • Articulation of how the Portfolio, including bilateral and W1 funding, will be bundled into Megaprograms is still lacking. Bilateral funding is restricted and is provided for a specific purpose and with specific intended impacts. This needs to be honored a nd the lack of flexibility in shifting those funds into other areas should be clearly acknowledged. • Alignment of the entire Portfolio with the CGIAR 2030 Research and Innovation Strategy needs to be strong and explicit. How will management ensure that bilateral funding delivers against this Strategy? In addition: o What happens if a bilateral project is not strongly aligned with the Strategy and how will CGIAR ensure that opportunity costs are covered? o Will all bilateral projects across all Centers be mapped to support the Portfolio? • A challenge that should be acknowledged is incorporating bilateral funding into Megaprograms. Each Megaprogram and Accelerator will be large scale and staff will be consumed by the implementation of contracted work. Trying to build Megaprogram linkages in parallel with bilateral funding should be additional, allowing sufficient effort dedicated to ensuring the prevention of silos within the new Portfolio. • Including bilateral funding into the organizational structure will be challenging. Clearly articulating the KPIs for this task for 2025 would be helpful. • The efforts needed to transition to Megaprograms are considerable and may be underestimated given the funding integration foreseen. Integration of pooled and bilateral at the reporting stage, as indicated, might be too late. Avoiding the duplication and ensuring clear implementation will be key. How will duplication of outputs/outcomes be avoided with both pooled and bilateral funding towards shared results? 5 ISDC Feedback on CGIAR Portfolio Narrative 2025-2030\n\n---\n\n[ID: pdf:Type3_2024Report.pdf:p5]\nFile: Type3_2024Report.pdf\nLocation: page 5\nContent: Section 2: Portfolio Performance and Project Coordination Progress 2. As per the Charter of the CGIAR System Organization, Article 8.2, and CGIAR’s Technical Reporting Arrangement 2022-2024. 3. Science Group Projects (SGPs) are Center-specific awards looking to integrate holistic quality assurance and implementation processes that build on efficiencies and value-for-money approaches through One CGIAR Common Systems and Window 1 budgeting practices. They operate under an integrated structure by Science Group, following similar principles and processes to Initiatives, while recognizing the role and responsibility of Centers for project delivery, compliance and fiduciary oversight. 4. EiB II will report through two Genetic Innovation Initiatives: Accelerated Breeding and Breeding Resources. For each Initiative report, they will provide a concise, high-level summary (approximately one page) outlining the contributions of the Gates Foundation-funded work toward the outcomes described in the technical reports. 2.1. Technical Reporting Arrangement 2022-24 CGIAR Technical Reporting fulfils the System-level programmatic reporting requirements set out in the Standard Provisions annexed to the Funding Agreement or Arrangement signed between each Funder and the System Organization.2 The 2024 Technical Report includes the following Initiatives, Impact Platforms and SGPs3: • All 32 Initiatives • Five Impact Platforms – Gender Equality, Youth and Social Inclusion – Environmental Health and Biodiversity – Nutrition, Health and Food Security – Climate Adaptation and Mitigation – Poverty Reduction, Livelihoods and Jobs • Six SGPs – Accelerated Varietal Improvement and Seed Delivery of Legumes and dryland Cereals in Africa (AVISA) – Roots Tubers and Banana (RTB) Breeding – Accelerating Genetic Gain and Varietal Replacement in Rice - Phase 2 (AGGRi 2) – Excellence in Breeding (EiB) II: Cross-Crop Support Services for Breeding Acceleration4 – Accelerating Crop Improvement Through Genome Editing 2023-2025 – Climate Adaptation Insight For 2024, CGIAR will produce and deliver a total of 46 Technical Reporting outputs: • March 2025: Results from 2024 published on the online CGIAR Results Dashboard (1). • May 2025: Publication of 42 Type 1 (32 x Initiative reports; 5 x Impact Platform reports; 5 x SGP reports) Reports and a Type 3 Report (1). • End of June 2025: Publication of the Portfolio Narrative (1). • End of June 2025: Publication of the Type 2 Report: CGIAR Contributions to Impact in Agrifood Systems (2022-24) (1). Each of these reports is released separately and will be available in PDF format. 2024 Technical Reporting covers USD 370 million (USD 322 million for Initiatives and Impact Platforms, and USD 49 million for W3 SGPs), representing nearly 40 percent of CGIAR’s total pooled and non-pooled funding for 2024. 2.1.1. Streamlining the process and adding value to stakeholders In 2022 CGIAR launched a new 2022-24 Technical Reporting Arrangement, co-developed with the System Council’s Strategic Impact Monitoring and Evaluation Committee (SIMEC). The 2022 rollout was regarded as a “first pancake” or trial phase, establishing minimum viable functionality and setting the foundation for annual improvements. Key achievements of 2022 Technical Reporting included the adoption of a common report template aligned with the Technical Reporting Arrangement for Initiatives and Impact Platforms; integration with CGIAR’s Results Framework; digital linking of results to theories of change (TOCs); and the introduction of quality assurance processes mediated by third parties. Additionally, a new interactive CGIAR Results Dashboard was launched, and the Performance and Results Management System (PRMS) – an online reporting system – was developed, alongside adaptive management processes and the rollout of Innovation Packages and Scaling Readiness plans. Building on this, 2023 Technical Reporting incorporated lessons from a 2022 Learning and Optimization process, documented in a 2022 Learning and Optimization report. Key advancements included transitioning to “Always on” reporting by opening the PRMS from September 2023, more than doubling the reporting window compared to 2022 and allowing greater flexibility for Initiatives, Impact Platforms, and SGPs. Quality assurance was optimized through four staggered batches across 2023 and 2024. Further enhancements included expanding per-result tagging to all five Impact Areas. A Risk Management Module was launched to support risk identification and reporting at the Initiative level. A large number of participants joined training sessions to support reporting, dashboard use, and onboarding, and the rapid uptake of adaptive management strengthened strategic agility, with positive feedback from across the Portfolio. The Research Plans of Results and Budgets section of the CGIAR website was updated to ensure easy open access to Initiative, SGP and Impact Platform Plans of Results and Budgets (PORBs). The 2024 reporting cycle continued this trajectory, integrating insights from the 2023 Learning and Optimization process and Action Plan to further refine CGIAR’s Technical Reporting processes and products. Key improvements in 2024 included: • Launching the PRMS Planning Module to support the replan process: The launch of an online Planning Module synchronized TOC and Planning data in the PRMS, improving the efficiency and quality of planning workflows. Enhanced replan guidelines were provided to help Initiatives, Impact Platforms, and SGPs implement 2023 Reflect recommendations and align budget forecasts with updated budget envelopes. To support continuous learning and adaptive management, a user experience survey on the Planning Module was conducted to assess effectiveness and inform user-centered enhancements for the 2025-30 Portfolio. • Further simplifying reporting processes and tools: A series of enhancements to PRMS functionalities were implemented to improve efficiency and usability. Improved filtering options, enhanced notification systems, and more clearly structured result PDFs now enable quicker access to relevant information. Innovation Packages and Scaling Readiness language and templates were simplified. Reporting was streamlined and modified to suit the final year of reporting for the Portfolio, with an Outcome Indicator Module co-developed with input from Initiatives, Impact Platforms and SGPs to provide them with the opportunity to assess their progress against targets for Work Package outcomes and end-of-Initiative outcomes; summative and yearly highlights were combined into a single report; and adaptive management processes removed. • Improving decision-making within the PRMS: Broader engagement from PRMS testers across reporting entities and Senior Program Managers was integrated into PRMS feature development, ensuring that system updates were aligned with user needs and supported consistent decision-making. • Enhancing product clarity: The Type 1 Annual Report template was reviewed to better accommodate end-of-Initiative outcome reporting for the final year of the Portfolio. Improvements to the Results Dashboard were made to enhance the accessibility of IPSR insights. • Strengthening quality assurance: Examples include updated and enhanced QA guidance, and updated guidance on Impact Area tagging. An AI tool was prototyped and tested on a series of data fields, with the intent to leverage lessons learned and develop an enhanced AI tool that can be applied to a broader set of reported data and integrated into the PRMS, supporting both the reporting and QA phases. • Developing the Semantic Natural Language Processing Aggregator Platform (SNAP): SNAP is an AI-powered tool enhancing access to and analysis of CGIAR’s reported outputs, outcomes, and impacts. It improves access to Portfolio information and results evidence through semantic searches, thematic clustering, and automated summaries, complementing the CGIAR Results Dashboard. SNAP-supported narratives were integrated into the CGIAR 2024 Portfolio Narrative, and ongoing refinements will further enhance its role in Portfolio reporting. • Further integrating SGPs and Impact Platforms: Between 2022 and 2024, CGIAR progressively aligned these entities with its Technical Reporting processes and common systems to enhance consistency and coherence. In 2023, three Impact Platforms – Nutrition, Health and Food Security; Climate Adaptation and Mitigation; and Environmental Health and Biodiversity – were onboarded alongside the Gender Equality, Youth and Social Inclusion Impact Platform (which reported in 2022), each receiving tailored support such as TOC and results framework development. The SGP pilot launched in 2023 further expanded CGIAR’s reporting ecosystem by integrating Center-specific Window 3 awards, with two SGPs submitting first-year results using the PRMS Reporting Tool and Type 1 Report template. In 2024, integration expanded to include the Poverty Reduction, Livelihoods and Jobs Impact Platform and four additional SGPs, further broadening the reporting ecosystem. • Enhancing risk management through the PRMS Risk Module: The Risk Management Module, launched in 2023 to support Initiative management and reporting of risks, was further enhanced in 2024, allowing Initiatives to capture transition-focused risks. It enabled Initiatives to review, update, or close risks, contributing to the design of the 2025-30 Portfolio. The updated Risk Management Module will be used by Programs and Accelerators from 2025 onward. Climate-Smart Village set-up under the Adaptation and Mitigation Initiative in Agriculture (AMIA) of the Department of Agriculture. Credit: Miguel Mamon/CIAT May 2025 54 CGIAR Portfolio Practice Change (Type 3) Report 2024\n\n---\n\n[ID: pdf:CGIAR-Technical-Reporting-Arrangement-2025-30.pdf:p4]\nFile: CGIAR-Technical-Reporting-Arrangement-2025-30.pdf\nLocation: page 4\nContent: CGIAR Technical Reporting Arrangement 2025-30 June 2025 4 1. Technical Reporting Arrangement purpose, scope, value proposition, delivery and optimization, Purpose The purpose of th e Technical Reporting Arrangement 2025 -2030 (“TRA 25-30”) is to set out the technical reporting requirements that apply to the CGIAR Portfolio during the period 2025-2030. The TRA 25-30: • Provides the parameters that e nable the Centers, the CGIAR System Partners and the System Organization to fulfil their technical reporting obligations under the funding agreements that apply to the use of Window 1 and Window 2 funds from the CGIAR Trust Fund (“Pooled Funding”). These parameters also allow the Integrated Partnership Board to fulfil its responsibility under the CGIAR System Charter to report on programmatic performance of CGIAR Research on an annual basis. • Provides, through the establishment of common technical reporting principles, enabling tools and mechanisms, progressive alignment and synergy between the technical reporting requirements that apply to components of the CGIAR Portfolio that are funded by Pooled Funding and those that apply to the components that are funded by other sources of funds (“Non-Pooled Funding”). • Sets transparency, performance tracking, and accountability expectations between CGIAR System Funders and CGIAR including Centres, • Informs decision making at different levels, underpins research management, operationalizes the Performance and Results Management Framework (PRMF), and guides portfolio -level MELIA and the design of the next Performance and Results management System (PRMS). The current Technical Reporting Arrangement that applies to the CGIAR Portfolio during the period 2022-24 (“TRA 22-24”) was co-developed by CGIAR and System Council/Strategic Impact Monitoring and Evaluation Committee (SIMEC) members in 2022. A new TRA is needed to match 2025-30 portfolio parameters, notably the alignment of pooled and non-pooled funding sources, and to apply lessons learnt from 2022-24. Scope The TRA 25-30 provides the operational and enabling basis to plan, monitor, learn and report on the 25-30 Portfolio. It is designed to progressively enable Programs and Accelerators, Centers and their research teams to report on the pooled, bilaterally and W3-funded components of the 2025- 30 portfolio in an integrated and aligned way, without increasing reporting burdens of Centers and Scientists. Going forward, the CGIAR Integrated Partnership will work towards progressively greater alignment of W3/bilateral projects and programs with the 2030 outcomes and theories of change of the Programs and Accelerators. Centers will provide key agreed information on their 